--- a/IG/7日版/AI Native-バイブコーディング_IG.xlsx
+++ b/IG/7日版/AI Native-バイブコーディング_IG.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\myrepo\ai_navive\IG\7日版\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D23BAE26-B3E9-428E-92DD-3500B30ADA50}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD57E835-E1F2-4B11-AF10-353BD671472F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="860" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -88,7 +88,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="820" uniqueCount="434">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="820" uniqueCount="435">
   <si>
     <t>1 日目</t>
     <rPh sb="2" eb="3">
@@ -4202,10 +4202,6 @@
     <phoneticPr fontId="3"/>
   </si>
   <si>
-    <t>VS Codeでは、Gitの操作を「ソース管理」機能から行う。</t>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
     <t xml:space="preserve">以下の手順を簡単に説明する。
 ・リポジトリの作成
 ・ファイルの変更
@@ -4306,6 +4302,15 @@
     <rPh sb="89" eb="91">
       <t>ヘンコウ</t>
     </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>VS Codeでは、Gitの操作を「ソース管理」機能から行うことを伝える。</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t xml:space="preserve">・AI-07
+</t>
     <phoneticPr fontId="3"/>
   </si>
 </sst>
@@ -9481,7 +9486,7 @@
         <v>コンフリクトの解消</v>
       </c>
       <c r="D119" s="106" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="E119" s="107"/>
       <c r="F119" s="108"/>
@@ -9530,7 +9535,7 @@
       <c r="M120" s="6"/>
       <c r="N120" s="6"/>
     </row>
-    <row r="121" spans="1:14" ht="37.799999999999997">
+    <row r="121" spans="1:14" ht="25.2">
       <c r="A121" s="11"/>
       <c r="B121" s="120"/>
       <c r="C121" s="48" t="str">
@@ -9538,12 +9543,12 @@
         <v>VSCodeのソース管理機能</v>
       </c>
       <c r="D121" s="106" t="s">
-        <v>429</v>
+        <v>433</v>
       </c>
       <c r="E121" s="107"/>
       <c r="F121" s="108"/>
       <c r="G121" s="48" t="s">
-        <v>337</v>
+        <v>434</v>
       </c>
       <c r="H121" s="12"/>
       <c r="I121" s="46" t="s">
@@ -9565,7 +9570,7 @@
         <v>ローカルリポジトリの操作</v>
       </c>
       <c r="D122" s="106" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="E122" s="107"/>
       <c r="F122" s="108"/>
@@ -9592,7 +9597,7 @@
         <v>リモートリポジトリの操作</v>
       </c>
       <c r="D123" s="106" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="E123" s="107"/>
       <c r="F123" s="108"/>
@@ -9619,7 +9624,7 @@
         <v>ブランチの操作</v>
       </c>
       <c r="D124" s="106" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="E124" s="107"/>
       <c r="F124" s="108"/>

--- a/IG/7日版/AI Native-バイブコーディング_IG.xlsx
+++ b/IG/7日版/AI Native-バイブコーディング_IG.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\myrepo\ai_navive\IG\7日版\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD57E835-E1F2-4B11-AF10-353BD671472F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E8E394DB-9C5C-4F7E-9B6F-FFF752E87D04}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="860" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -88,7 +88,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="820" uniqueCount="435">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="826" uniqueCount="447">
   <si>
     <t>1 日目</t>
     <rPh sb="2" eb="3">
@@ -4202,81 +4202,6 @@
     <phoneticPr fontId="3"/>
   </si>
   <si>
-    <t xml:space="preserve">以下の手順を簡単に説明する。
-・リポジトリの作成
-・ファイルの変更
-・変更内容の確認
-・変更内容のステージ
-・変更内容のコミット
-</t>
-    <rPh sb="0" eb="2">
-      <t>イカ</t>
-    </rPh>
-    <rPh sb="3" eb="5">
-      <t>テジュン</t>
-    </rPh>
-    <rPh sb="6" eb="8">
-      <t>カンタン</t>
-    </rPh>
-    <rPh sb="9" eb="11">
-      <t>セツメイ</t>
-    </rPh>
-    <rPh sb="31" eb="33">
-      <t>ヘンコウ</t>
-    </rPh>
-    <rPh sb="35" eb="39">
-      <t>ヘンコウナイヨウ</t>
-    </rPh>
-    <rPh sb="40" eb="42">
-      <t>カクニン</t>
-    </rPh>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
-    <t xml:space="preserve">以下の手順を簡単に説明する。
-・リポジトリの取得
-・リモートからの取得と反映
-・リモートへの反映
-</t>
-    <rPh sb="6" eb="8">
-      <t>カンタン</t>
-    </rPh>
-    <rPh sb="22" eb="24">
-      <t>シュトク</t>
-    </rPh>
-    <rPh sb="33" eb="35">
-      <t>シュトク</t>
-    </rPh>
-    <rPh sb="36" eb="38">
-      <t>ハンエイ</t>
-    </rPh>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
-    <t xml:space="preserve">以下の手順を簡単に説明する。
-・ブランチの作成
-・ブランチの切り替え
-・ブランチのマージ
-・コンフリクトの解消
-</t>
-    <rPh sb="6" eb="8">
-      <t>カンタン</t>
-    </rPh>
-    <rPh sb="21" eb="23">
-      <t>サクセイ</t>
-    </rPh>
-    <rPh sb="30" eb="31">
-      <t>キ</t>
-    </rPh>
-    <rPh sb="32" eb="33">
-      <t>カ</t>
-    </rPh>
-    <rPh sb="53" eb="55">
-      <t>カイショウ</t>
-    </rPh>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
     <t xml:space="preserve">コンフリクトとは、「どちらの変更を採用すべきか自動的に判断できない状態」のこと。
 コンフリクトの解決手順を説明する。
 1. 競合箇所を確認
@@ -4306,6 +4231,297 @@
   </si>
   <si>
     <t>VS Codeでは、Gitの操作を「ソース管理」機能から行うことを伝える。</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t xml:space="preserve">・AI-07
+</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>以下の手順を簡単に説明する。
+・リポジトリの取得
+・リモートからの取得と反映
+・リモートへの反映</t>
+    <rPh sb="6" eb="8">
+      <t>カンタン</t>
+    </rPh>
+    <rPh sb="22" eb="24">
+      <t>シュトク</t>
+    </rPh>
+    <rPh sb="33" eb="35">
+      <t>シュトク</t>
+    </rPh>
+    <rPh sb="36" eb="38">
+      <t>ハンエイ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>※本研修ではリモートリポジトリは利用しない。</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t xml:space="preserve">・AI-08
+</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>演習の全体構成について説明する。
+・VS Codeによるローカルリポジトリの操作
+・VS Codeによるブランチの操作</t>
+    <rPh sb="0" eb="2">
+      <t>エンシュウ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>ゼンタイ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>コウセイ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>演習で利用するソフトウェアについて説明する。
+・VS Code（拡張機能を含む）
+・Git</t>
+    <rPh sb="0" eb="2">
+      <t>エンシュウ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>リヨウ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>※基本的にGitコマンドを直接使うことはない。</t>
+    <rPh sb="1" eb="4">
+      <t>キホンテキ</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>チョクセツ</t>
+    </rPh>
+    <rPh sb="15" eb="16">
+      <t>ツカ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">実施手順に従い、演習を実施することを説明する。
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Meiryo UI"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>※ハンズオンとして実施する。</t>
+    </r>
+    <rPh sb="0" eb="2">
+      <t>ジッシ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>テジュン</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>シタガ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>エンシュウ</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>ジッシ</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>セツメイ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t xml:space="preserve">・AI-08
+</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t xml:space="preserve">・AI-08
+</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">本演習の全体像について説明する。
+■概要
+ローカルリポジトリの操作
+■詳細
+1. VS Codeによるリポジトリの作成
+2. VS Codeによる変更内容の確認
+3. VS Codeによる変更内容のステージング
+4. VS Codeによる変更内容のコミット
+■事前準備
+実施手順に従い、演習を実施することを説明する。
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Meiryo UI"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>※ハンズオンとして実施する。</t>
+    </r>
+    <rPh sb="0" eb="1">
+      <t>ホン</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>セツメイ</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>ガイヨウ</t>
+    </rPh>
+    <rPh sb="31" eb="33">
+      <t>ソウサ</t>
+    </rPh>
+    <rPh sb="36" eb="38">
+      <t>ショウサイ</t>
+    </rPh>
+    <rPh sb="132" eb="136">
+      <t>ジゼンジュンビ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">本演習の全体像について説明する。
+■概要
+ブランチの操作
+■詳細
+1. VS Codeによるブランチの作成
+2.　VS Codeによるブランチの切り替え
+3.　VS Codeによるブランチのマージ
+■事前準備
+実施手順に従い、演習を実施することを説明する。
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Meiryo UI"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>※ハンズオンとして実施する。</t>
+    </r>
+    <rPh sb="0" eb="1">
+      <t>ホン</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>セツメイ</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>ガイヨウ</t>
+    </rPh>
+    <rPh sb="26" eb="28">
+      <t>ソウサ</t>
+    </rPh>
+    <rPh sb="31" eb="33">
+      <t>ショウサイ</t>
+    </rPh>
+    <rPh sb="102" eb="106">
+      <t>ジゼンジュンビ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t xml:space="preserve">・AI-07
+</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">以下の手順を簡単に説明する。
+・リポジトリの作成
+・ファイルの変更
+・変更内容の確認
+・変更内容のステージ
+・変更内容のコミット
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Meiryo UI"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>※本項目は演習で実施する内容です。
+　受講者が利用方法に困った場合は、本資料を参照するよう案内してください。</t>
+    </r>
+    <rPh sb="0" eb="2">
+      <t>イカ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>テジュン</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>カンタン</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>セツメイ</t>
+    </rPh>
+    <rPh sb="31" eb="33">
+      <t>ヘンコウ</t>
+    </rPh>
+    <rPh sb="35" eb="39">
+      <t>ヘンコウナイヨウ</t>
+    </rPh>
+    <rPh sb="40" eb="42">
+      <t>カクニン</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">以下の手順を簡単に説明する。
+・ブランチの作成
+・ブランチの切り替え
+・ブランチのマージ
+・コンフリクトの解消
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Meiryo UI"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>※本項目は演習で実施する内容です。
+　受講者が利用方法に困った場合は、本資料を参照するよう案内してください。</t>
+    </r>
+    <rPh sb="6" eb="8">
+      <t>カンタン</t>
+    </rPh>
+    <rPh sb="21" eb="23">
+      <t>サクセイ</t>
+    </rPh>
+    <rPh sb="30" eb="31">
+      <t>キ</t>
+    </rPh>
+    <rPh sb="32" eb="33">
+      <t>カ</t>
+    </rPh>
+    <rPh sb="53" eb="55">
+      <t>カイショウ</t>
+    </rPh>
     <phoneticPr fontId="3"/>
   </si>
   <si>
@@ -5005,6 +5221,9 @@
     <xf numFmtId="0" fontId="5" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -5047,71 +5266,68 @@
     <xf numFmtId="0" fontId="11" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -5487,17 +5703,17 @@
   <sheetData>
     <row r="2" spans="1:10" ht="27">
       <c r="A2" s="13"/>
-      <c r="B2" s="90" t="str">
+      <c r="B2" s="91" t="str">
         <f>"コースプラン/インストラクションガイド 「"&amp;master!$B$1&amp;"_IG」"</f>
         <v>コースプラン/インストラクションガイド 「AI Native-バイブコーディング_IG」</v>
       </c>
-      <c r="C2" s="90"/>
-      <c r="D2" s="90"/>
-      <c r="E2" s="90"/>
-      <c r="F2" s="90"/>
-      <c r="G2" s="90"/>
-      <c r="H2" s="90"/>
-      <c r="I2" s="90"/>
+      <c r="C2" s="91"/>
+      <c r="D2" s="91"/>
+      <c r="E2" s="91"/>
+      <c r="F2" s="91"/>
+      <c r="G2" s="91"/>
+      <c r="H2" s="91"/>
+      <c r="I2" s="91"/>
     </row>
     <row r="3" spans="1:10" ht="27.6" thickBot="1">
       <c r="A3" s="13"/>
@@ -5512,10 +5728,10 @@
     </row>
     <row r="4" spans="1:10" ht="27.6" thickBot="1">
       <c r="A4" s="13"/>
-      <c r="B4" s="91" t="s">
+      <c r="B4" s="92" t="s">
         <v>11</v>
       </c>
-      <c r="C4" s="92"/>
+      <c r="C4" s="93"/>
       <c r="D4" s="13"/>
       <c r="E4" s="13"/>
       <c r="F4" s="13"/>
@@ -5525,8 +5741,8 @@
     </row>
     <row r="5" spans="1:10" ht="27.6" thickBot="1">
       <c r="A5" s="13"/>
-      <c r="B5" s="93"/>
-      <c r="C5" s="94"/>
+      <c r="B5" s="94"/>
+      <c r="C5" s="95"/>
       <c r="D5" s="13"/>
       <c r="E5" s="13"/>
       <c r="F5" s="13"/>
@@ -5535,10 +5751,10 @@
       <c r="I5" s="13"/>
     </row>
     <row r="7" spans="1:10" ht="16.2">
-      <c r="B7" s="95" t="s">
+      <c r="B7" s="96" t="s">
         <v>2</v>
       </c>
-      <c r="C7" s="95"/>
+      <c r="C7" s="96"/>
     </row>
     <row r="8" spans="1:10">
       <c r="E8" s="15"/>
@@ -6259,10 +6475,10 @@
       <c r="K3" s="9"/>
     </row>
     <row r="4" spans="1:12" ht="16.2">
-      <c r="B4" s="99" t="s">
+      <c r="B4" s="100" t="s">
         <v>4</v>
       </c>
-      <c r="C4" s="99"/>
+      <c r="C4" s="100"/>
       <c r="D4" s="8"/>
       <c r="E4" s="8"/>
       <c r="F4" s="8"/>
@@ -6273,16 +6489,16 @@
       <c r="K4" s="9"/>
     </row>
     <row r="5" spans="1:12" ht="36" customHeight="1">
-      <c r="B5" s="100"/>
-      <c r="C5" s="100"/>
-      <c r="D5" s="100"/>
-      <c r="E5" s="100"/>
-      <c r="F5" s="100"/>
-      <c r="G5" s="100"/>
-      <c r="H5" s="100"/>
-      <c r="I5" s="100"/>
-      <c r="J5" s="100"/>
-      <c r="K5" s="100"/>
+      <c r="B5" s="101"/>
+      <c r="C5" s="101"/>
+      <c r="D5" s="101"/>
+      <c r="E5" s="101"/>
+      <c r="F5" s="101"/>
+      <c r="G5" s="101"/>
+      <c r="H5" s="101"/>
+      <c r="I5" s="101"/>
+      <c r="J5" s="101"/>
+      <c r="K5" s="101"/>
     </row>
     <row r="6" spans="1:12">
       <c r="B6" s="10"/>
@@ -6297,10 +6513,10 @@
       <c r="C7" s="30" t="s">
         <v>15</v>
       </c>
-      <c r="D7" s="101" t="s">
+      <c r="D7" s="102" t="s">
         <v>20</v>
       </c>
-      <c r="E7" s="101"/>
+      <c r="E7" s="102"/>
       <c r="F7" s="30" t="s">
         <v>10</v>
       </c>
@@ -6332,46 +6548,46 @@
     </row>
     <row r="10" spans="1:12">
       <c r="A10" s="10"/>
-      <c r="B10" s="97"/>
-      <c r="C10" s="97" t="s">
+      <c r="B10" s="98"/>
+      <c r="C10" s="98" t="s">
         <v>7</v>
       </c>
-      <c r="D10" s="97" t="s">
+      <c r="D10" s="98" t="s">
         <v>8</v>
       </c>
-      <c r="E10" s="97"/>
-      <c r="F10" s="97"/>
-      <c r="G10" s="97" t="s">
+      <c r="E10" s="98"/>
+      <c r="F10" s="98"/>
+      <c r="G10" s="98" t="s">
         <v>9</v>
       </c>
-      <c r="H10" s="102" t="s">
+      <c r="H10" s="103" t="s">
         <v>23</v>
       </c>
-      <c r="I10" s="96" t="s">
+      <c r="I10" s="97" t="s">
         <v>31</v>
       </c>
-      <c r="J10" s="96"/>
-      <c r="K10" s="96" t="s">
+      <c r="J10" s="97"/>
+      <c r="K10" s="97" t="s">
         <v>30</v>
       </c>
       <c r="L10" s="10"/>
     </row>
     <row r="11" spans="1:12">
       <c r="A11" s="10"/>
-      <c r="B11" s="97"/>
-      <c r="C11" s="97"/>
-      <c r="D11" s="97"/>
-      <c r="E11" s="97"/>
-      <c r="F11" s="97"/>
-      <c r="G11" s="97"/>
-      <c r="H11" s="103"/>
+      <c r="B11" s="98"/>
+      <c r="C11" s="98"/>
+      <c r="D11" s="98"/>
+      <c r="E11" s="98"/>
+      <c r="F11" s="98"/>
+      <c r="G11" s="98"/>
+      <c r="H11" s="104"/>
       <c r="I11" s="25" t="s">
         <v>25</v>
       </c>
       <c r="J11" s="25" t="s">
         <v>6</v>
       </c>
-      <c r="K11" s="97"/>
+      <c r="K11" s="98"/>
       <c r="L11" s="10"/>
     </row>
     <row r="12" spans="1:12" ht="63">
@@ -6380,11 +6596,11 @@
       <c r="C12" s="19" t="s">
         <v>332</v>
       </c>
-      <c r="D12" s="98" t="s">
+      <c r="D12" s="99" t="s">
         <v>50</v>
       </c>
-      <c r="E12" s="98"/>
-      <c r="F12" s="98"/>
+      <c r="E12" s="99"/>
+      <c r="F12" s="99"/>
       <c r="G12" s="88" t="s">
         <v>51</v>
       </c>
@@ -6404,11 +6620,11 @@
       <c r="C13" s="19" t="s">
         <v>333</v>
       </c>
-      <c r="D13" s="98" t="s">
+      <c r="D13" s="99" t="s">
         <v>330</v>
       </c>
-      <c r="E13" s="98"/>
-      <c r="F13" s="98"/>
+      <c r="E13" s="99"/>
+      <c r="F13" s="99"/>
       <c r="G13" s="88" t="s">
         <v>331</v>
       </c>
@@ -6508,12 +6724,12 @@
       <c r="M3" s="9"/>
     </row>
     <row r="4" spans="2:14" ht="16.2">
-      <c r="B4" s="99" t="s">
+      <c r="B4" s="100" t="s">
         <v>4</v>
       </c>
-      <c r="C4" s="99"/>
-      <c r="D4" s="99"/>
-      <c r="E4" s="99"/>
+      <c r="C4" s="100"/>
+      <c r="D4" s="100"/>
+      <c r="E4" s="100"/>
       <c r="F4" s="8"/>
       <c r="G4" s="8"/>
       <c r="H4" s="7"/>
@@ -6524,16 +6740,16 @@
       <c r="M4" s="9"/>
     </row>
     <row r="5" spans="2:14" ht="36" customHeight="1">
-      <c r="B5" s="124"/>
-      <c r="C5" s="124"/>
-      <c r="D5" s="124"/>
-      <c r="E5" s="124"/>
-      <c r="F5" s="124"/>
-      <c r="G5" s="124"/>
-      <c r="H5" s="124"/>
-      <c r="I5" s="124"/>
-      <c r="J5" s="124"/>
-      <c r="K5" s="124"/>
+      <c r="B5" s="122"/>
+      <c r="C5" s="122"/>
+      <c r="D5" s="122"/>
+      <c r="E5" s="122"/>
+      <c r="F5" s="122"/>
+      <c r="G5" s="122"/>
+      <c r="H5" s="122"/>
+      <c r="I5" s="122"/>
+      <c r="J5" s="122"/>
+      <c r="K5" s="122"/>
       <c r="L5" s="26"/>
       <c r="M5" s="27"/>
     </row>
@@ -6553,10 +6769,10 @@
       <c r="C7" s="30" t="s">
         <v>15</v>
       </c>
-      <c r="D7" s="101" t="s">
+      <c r="D7" s="102" t="s">
         <v>20</v>
       </c>
-      <c r="E7" s="101"/>
+      <c r="E7" s="102"/>
       <c r="F7" s="30" t="s">
         <v>10</v>
       </c>
@@ -6811,28 +7027,28 @@
     </row>
     <row r="20" spans="1:14" ht="24" customHeight="1">
       <c r="A20" s="10"/>
-      <c r="B20" s="97" t="s">
+      <c r="B20" s="98" t="s">
         <v>5</v>
       </c>
-      <c r="C20" s="97" t="s">
+      <c r="C20" s="98" t="s">
         <v>7</v>
       </c>
-      <c r="D20" s="97" t="s">
+      <c r="D20" s="98" t="s">
         <v>8</v>
       </c>
-      <c r="E20" s="97"/>
-      <c r="F20" s="97"/>
-      <c r="G20" s="97" t="s">
+      <c r="E20" s="98"/>
+      <c r="F20" s="98"/>
+      <c r="G20" s="98" t="s">
         <v>9</v>
       </c>
-      <c r="H20" s="96" t="s">
+      <c r="H20" s="97" t="s">
         <v>23</v>
       </c>
-      <c r="I20" s="122" t="s">
+      <c r="I20" s="120" t="s">
         <v>31</v>
       </c>
-      <c r="J20" s="123"/>
-      <c r="K20" s="96" t="s">
+      <c r="J20" s="121"/>
+      <c r="K20" s="97" t="s">
         <v>32</v>
       </c>
       <c r="L20" s="6"/>
@@ -6841,20 +7057,20 @@
     </row>
     <row r="21" spans="1:14">
       <c r="A21" s="10"/>
-      <c r="B21" s="97"/>
-      <c r="C21" s="97"/>
-      <c r="D21" s="97"/>
-      <c r="E21" s="97"/>
-      <c r="F21" s="97"/>
-      <c r="G21" s="97"/>
-      <c r="H21" s="96"/>
+      <c r="B21" s="98"/>
+      <c r="C21" s="98"/>
+      <c r="D21" s="98"/>
+      <c r="E21" s="98"/>
+      <c r="F21" s="98"/>
+      <c r="G21" s="98"/>
+      <c r="H21" s="97"/>
       <c r="I21" s="25" t="s">
         <v>25</v>
       </c>
       <c r="J21" s="25" t="s">
         <v>6</v>
       </c>
-      <c r="K21" s="97"/>
+      <c r="K21" s="98"/>
       <c r="L21" s="6"/>
       <c r="M21" s="6"/>
       <c r="N21" s="6"/>
@@ -6869,11 +7085,11 @@
         <f>master!C3</f>
         <v>講義の目的</v>
       </c>
-      <c r="D22" s="106" t="s">
+      <c r="D22" s="105" t="s">
         <v>95</v>
       </c>
-      <c r="E22" s="107"/>
-      <c r="F22" s="108"/>
+      <c r="E22" s="106"/>
+      <c r="F22" s="107"/>
       <c r="G22" s="48" t="s">
         <v>96</v>
       </c>
@@ -6891,7 +7107,7 @@
     </row>
     <row r="23" spans="1:14" ht="138.6" customHeight="1">
       <c r="A23" s="10"/>
-      <c r="B23" s="119" t="str">
+      <c r="B23" s="108" t="str">
         <f>master!B4</f>
         <v>Webアプリケーションとは</v>
       </c>
@@ -6899,11 +7115,11 @@
         <f>master!C4</f>
         <v>Webアプリケーションとは</v>
       </c>
-      <c r="D23" s="106" t="s">
+      <c r="D23" s="105" t="s">
         <v>97</v>
       </c>
-      <c r="E23" s="107"/>
-      <c r="F23" s="108"/>
+      <c r="E23" s="106"/>
+      <c r="F23" s="107"/>
       <c r="G23" s="48" t="s">
         <v>40</v>
       </c>
@@ -6921,16 +7137,16 @@
     </row>
     <row r="24" spans="1:14" ht="75.599999999999994">
       <c r="A24" s="11"/>
-      <c r="B24" s="120"/>
+      <c r="B24" s="109"/>
       <c r="C24" s="48" t="str">
         <f>master!C5</f>
         <v>Webアプリケーションの種類</v>
       </c>
-      <c r="D24" s="106" t="s">
+      <c r="D24" s="105" t="s">
         <v>98</v>
       </c>
-      <c r="E24" s="107"/>
-      <c r="F24" s="108"/>
+      <c r="E24" s="106"/>
+      <c r="F24" s="107"/>
       <c r="G24" s="48" t="s">
         <v>44</v>
       </c>
@@ -6948,16 +7164,16 @@
     </row>
     <row r="25" spans="1:14" ht="37.799999999999997">
       <c r="A25" s="11"/>
-      <c r="B25" s="120"/>
+      <c r="B25" s="109"/>
       <c r="C25" s="48" t="str">
         <f>master!C6</f>
         <v>アプリケーションとは</v>
       </c>
-      <c r="D25" s="106" t="s">
+      <c r="D25" s="105" t="s">
         <v>99</v>
       </c>
-      <c r="E25" s="107"/>
-      <c r="F25" s="108"/>
+      <c r="E25" s="106"/>
+      <c r="F25" s="107"/>
       <c r="G25" s="48" t="s">
         <v>42</v>
       </c>
@@ -6975,16 +7191,16 @@
     </row>
     <row r="26" spans="1:14" ht="63">
       <c r="A26" s="11"/>
-      <c r="B26" s="120"/>
+      <c r="B26" s="109"/>
       <c r="C26" s="48" t="str">
         <f>master!C7</f>
         <v>Web画面アプリケーション</v>
       </c>
-      <c r="D26" s="106" t="s">
+      <c r="D26" s="105" t="s">
         <v>100</v>
       </c>
-      <c r="E26" s="107"/>
-      <c r="F26" s="108"/>
+      <c r="E26" s="106"/>
+      <c r="F26" s="107"/>
       <c r="G26" s="48" t="s">
         <v>41</v>
       </c>
@@ -7002,13 +7218,13 @@
     </row>
     <row r="27" spans="1:14" ht="63">
       <c r="A27" s="11"/>
-      <c r="B27" s="120"/>
+      <c r="B27" s="109"/>
       <c r="C27" s="48"/>
-      <c r="D27" s="106" t="s">
+      <c r="D27" s="105" t="s">
         <v>101</v>
       </c>
-      <c r="E27" s="107"/>
-      <c r="F27" s="108"/>
+      <c r="E27" s="106"/>
+      <c r="F27" s="107"/>
       <c r="G27" s="48" t="s">
         <v>41</v>
       </c>
@@ -7026,16 +7242,16 @@
     </row>
     <row r="28" spans="1:14" ht="113.4">
       <c r="A28" s="11"/>
-      <c r="B28" s="121"/>
+      <c r="B28" s="110"/>
       <c r="C28" s="48" t="str">
         <f>master!C8</f>
         <v>ブラウザからのリクエスト種類</v>
       </c>
-      <c r="D28" s="106" t="s">
+      <c r="D28" s="105" t="s">
         <v>102</v>
       </c>
-      <c r="E28" s="107"/>
-      <c r="F28" s="108"/>
+      <c r="E28" s="106"/>
+      <c r="F28" s="107"/>
       <c r="G28" s="48" t="s">
         <v>45</v>
       </c>
@@ -7053,7 +7269,7 @@
     </row>
     <row r="29" spans="1:14" ht="102" customHeight="1">
       <c r="A29" s="11"/>
-      <c r="B29" s="119" t="str">
+      <c r="B29" s="108" t="str">
         <f>master!B9</f>
         <v>データベースとは</v>
       </c>
@@ -7061,11 +7277,11 @@
         <f>master!C9</f>
         <v>データベースとは</v>
       </c>
-      <c r="D29" s="106" t="s">
+      <c r="D29" s="105" t="s">
         <v>103</v>
       </c>
-      <c r="E29" s="107"/>
-      <c r="F29" s="108"/>
+      <c r="E29" s="106"/>
+      <c r="F29" s="107"/>
       <c r="G29" s="48" t="s">
         <v>42</v>
       </c>
@@ -7083,16 +7299,16 @@
     </row>
     <row r="30" spans="1:14" ht="88.2">
       <c r="A30" s="11"/>
-      <c r="B30" s="120"/>
+      <c r="B30" s="109"/>
       <c r="C30" s="48" t="str">
         <f>master!C10</f>
         <v>リレーショナルデータベース</v>
       </c>
-      <c r="D30" s="106" t="s">
+      <c r="D30" s="105" t="s">
         <v>104</v>
       </c>
-      <c r="E30" s="107"/>
-      <c r="F30" s="108"/>
+      <c r="E30" s="106"/>
+      <c r="F30" s="107"/>
       <c r="G30" s="48" t="s">
         <v>46</v>
       </c>
@@ -7110,16 +7326,16 @@
     </row>
     <row r="31" spans="1:14" ht="25.2">
       <c r="A31" s="11"/>
-      <c r="B31" s="120"/>
+      <c r="B31" s="109"/>
       <c r="C31" s="48" t="str">
         <f>master!C11</f>
         <v>データベースの役割</v>
       </c>
-      <c r="D31" s="106" t="s">
+      <c r="D31" s="105" t="s">
         <v>105</v>
       </c>
-      <c r="E31" s="107"/>
-      <c r="F31" s="108"/>
+      <c r="E31" s="106"/>
+      <c r="F31" s="107"/>
       <c r="G31" s="48" t="s">
         <v>47</v>
       </c>
@@ -7139,16 +7355,16 @@
     </row>
     <row r="32" spans="1:14" ht="75.599999999999994">
       <c r="A32" s="11"/>
-      <c r="B32" s="120"/>
+      <c r="B32" s="109"/>
       <c r="C32" s="48" t="str">
         <f>master!C12</f>
         <v>2.1.テーブル</v>
       </c>
-      <c r="D32" s="106" t="s">
+      <c r="D32" s="105" t="s">
         <v>106</v>
       </c>
-      <c r="E32" s="107"/>
-      <c r="F32" s="108"/>
+      <c r="E32" s="106"/>
+      <c r="F32" s="107"/>
       <c r="G32" s="48" t="s">
         <v>44</v>
       </c>
@@ -7166,16 +7382,16 @@
     </row>
     <row r="33" spans="1:14" ht="100.8">
       <c r="A33" s="11"/>
-      <c r="B33" s="120"/>
+      <c r="B33" s="109"/>
       <c r="C33" s="48" t="str">
         <f>master!C13</f>
         <v>2.2.データ型１</v>
       </c>
-      <c r="D33" s="106" t="s">
+      <c r="D33" s="105" t="s">
         <v>107</v>
       </c>
-      <c r="E33" s="107"/>
-      <c r="F33" s="108"/>
+      <c r="E33" s="106"/>
+      <c r="F33" s="107"/>
       <c r="G33" s="48" t="s">
         <v>48</v>
       </c>
@@ -7193,16 +7409,16 @@
     </row>
     <row r="34" spans="1:14" ht="37.799999999999997">
       <c r="A34" s="11"/>
-      <c r="B34" s="120"/>
+      <c r="B34" s="109"/>
       <c r="C34" s="48" t="str">
         <f>master!C14</f>
         <v>2.2.データ型２</v>
       </c>
-      <c r="D34" s="106" t="s">
+      <c r="D34" s="105" t="s">
         <v>108</v>
       </c>
-      <c r="E34" s="107"/>
-      <c r="F34" s="108"/>
+      <c r="E34" s="106"/>
+      <c r="F34" s="107"/>
       <c r="G34" s="48" t="s">
         <v>42</v>
       </c>
@@ -7220,16 +7436,16 @@
     </row>
     <row r="35" spans="1:14" ht="37.799999999999997">
       <c r="A35" s="11"/>
-      <c r="B35" s="120"/>
+      <c r="B35" s="109"/>
       <c r="C35" s="48" t="str">
         <f>master!C15</f>
         <v>2.3.リレーション</v>
       </c>
-      <c r="D35" s="106" t="s">
+      <c r="D35" s="105" t="s">
         <v>109</v>
       </c>
-      <c r="E35" s="107"/>
-      <c r="F35" s="108"/>
+      <c r="E35" s="106"/>
+      <c r="F35" s="107"/>
       <c r="G35" s="48" t="s">
         <v>42</v>
       </c>
@@ -7247,16 +7463,16 @@
     </row>
     <row r="36" spans="1:14" ht="37.799999999999997">
       <c r="A36" s="11"/>
-      <c r="B36" s="121"/>
+      <c r="B36" s="110"/>
       <c r="C36" s="48" t="str">
         <f>master!C16</f>
         <v>2.4.データを結合して取得（Join）</v>
       </c>
-      <c r="D36" s="106" t="s">
+      <c r="D36" s="105" t="s">
         <v>110</v>
       </c>
-      <c r="E36" s="107"/>
-      <c r="F36" s="108"/>
+      <c r="E36" s="106"/>
+      <c r="F36" s="107"/>
       <c r="G36" s="48" t="s">
         <v>42</v>
       </c>
@@ -7274,7 +7490,7 @@
     </row>
     <row r="37" spans="1:14" ht="88.2">
       <c r="A37" s="11"/>
-      <c r="B37" s="119" t="str">
+      <c r="B37" s="108" t="str">
         <f>master!B17</f>
         <v>Java言語、Springフレームワークとは</v>
       </c>
@@ -7282,11 +7498,11 @@
         <f>master!C17</f>
         <v>Webアプリケーションを作成するためのプログラミング言語</v>
       </c>
-      <c r="D37" s="106" t="s">
+      <c r="D37" s="105" t="s">
         <v>111</v>
       </c>
-      <c r="E37" s="107"/>
-      <c r="F37" s="108"/>
+      <c r="E37" s="106"/>
+      <c r="F37" s="107"/>
       <c r="G37" s="48" t="s">
         <v>46</v>
       </c>
@@ -7304,16 +7520,16 @@
     </row>
     <row r="38" spans="1:14" ht="75.599999999999994">
       <c r="A38" s="11"/>
-      <c r="B38" s="120"/>
+      <c r="B38" s="109"/>
       <c r="C38" s="48" t="str">
         <f>master!C18</f>
         <v>Java</v>
       </c>
-      <c r="D38" s="106" t="s">
+      <c r="D38" s="105" t="s">
         <v>112</v>
       </c>
-      <c r="E38" s="107"/>
-      <c r="F38" s="108"/>
+      <c r="E38" s="106"/>
+      <c r="F38" s="107"/>
       <c r="G38" s="48" t="s">
         <v>44</v>
       </c>
@@ -7331,16 +7547,16 @@
     </row>
     <row r="39" spans="1:14" ht="75.599999999999994">
       <c r="A39" s="11"/>
-      <c r="B39" s="120"/>
+      <c r="B39" s="109"/>
       <c r="C39" s="48" t="str">
         <f>master!C19</f>
         <v>Java言語の構成要素</v>
       </c>
-      <c r="D39" s="106" t="s">
+      <c r="D39" s="105" t="s">
         <v>113</v>
       </c>
-      <c r="E39" s="107"/>
-      <c r="F39" s="108"/>
+      <c r="E39" s="106"/>
+      <c r="F39" s="107"/>
       <c r="G39" s="48" t="s">
         <v>44</v>
       </c>
@@ -7358,16 +7574,16 @@
     </row>
     <row r="40" spans="1:14" ht="50.4">
       <c r="A40" s="11"/>
-      <c r="B40" s="120"/>
+      <c r="B40" s="109"/>
       <c r="C40" s="48" t="str">
         <f>master!C20</f>
         <v>Webアプリケーションを構成するクラス</v>
       </c>
-      <c r="D40" s="106" t="s">
+      <c r="D40" s="105" t="s">
         <v>114</v>
       </c>
-      <c r="E40" s="107"/>
-      <c r="F40" s="108"/>
+      <c r="E40" s="106"/>
+      <c r="F40" s="107"/>
       <c r="G40" s="48" t="s">
         <v>43</v>
       </c>
@@ -7385,16 +7601,16 @@
     </row>
     <row r="41" spans="1:14" ht="88.2">
       <c r="A41" s="11"/>
-      <c r="B41" s="120"/>
+      <c r="B41" s="109"/>
       <c r="C41" s="48" t="str">
         <f>master!C21</f>
         <v>Nレイヤーアーキテクチャ</v>
       </c>
-      <c r="D41" s="106" t="s">
+      <c r="D41" s="105" t="s">
         <v>116</v>
       </c>
-      <c r="E41" s="107"/>
-      <c r="F41" s="108"/>
+      <c r="E41" s="106"/>
+      <c r="F41" s="107"/>
       <c r="G41" s="48" t="s">
         <v>46</v>
       </c>
@@ -7414,16 +7630,16 @@
     </row>
     <row r="42" spans="1:14" ht="201.6">
       <c r="A42" s="11"/>
-      <c r="B42" s="120"/>
+      <c r="B42" s="109"/>
       <c r="C42" s="48" t="str">
         <f>master!C22</f>
         <v>View と Controller と Service と Repository</v>
       </c>
-      <c r="D42" s="106" t="s">
+      <c r="D42" s="105" t="s">
         <v>117</v>
       </c>
-      <c r="E42" s="107"/>
-      <c r="F42" s="108"/>
+      <c r="E42" s="106"/>
+      <c r="F42" s="107"/>
       <c r="G42" s="48" t="s">
         <v>118</v>
       </c>
@@ -7441,16 +7657,16 @@
     </row>
     <row r="43" spans="1:14" ht="37.799999999999997">
       <c r="A43" s="11"/>
-      <c r="B43" s="120"/>
+      <c r="B43" s="109"/>
       <c r="C43" s="48" t="str">
         <f>master!C23</f>
         <v>Nレイヤーアーキテクチャ</v>
       </c>
-      <c r="D43" s="106" t="s">
+      <c r="D43" s="105" t="s">
         <v>119</v>
       </c>
-      <c r="E43" s="107"/>
-      <c r="F43" s="108"/>
+      <c r="E43" s="106"/>
+      <c r="F43" s="107"/>
       <c r="G43" s="48" t="s">
         <v>42</v>
       </c>
@@ -7468,16 +7684,16 @@
     </row>
     <row r="44" spans="1:14" ht="163.80000000000001">
       <c r="A44" s="11"/>
-      <c r="B44" s="120"/>
+      <c r="B44" s="109"/>
       <c r="C44" s="48" t="str">
         <f>master!C24</f>
         <v>Webアプリケーション フレームワーク</v>
       </c>
-      <c r="D44" s="106" t="s">
+      <c r="D44" s="105" t="s">
         <v>120</v>
       </c>
-      <c r="E44" s="107"/>
-      <c r="F44" s="108"/>
+      <c r="E44" s="106"/>
+      <c r="F44" s="107"/>
       <c r="G44" s="48" t="s">
         <v>121</v>
       </c>
@@ -7495,16 +7711,16 @@
     </row>
     <row r="45" spans="1:14" ht="25.2">
       <c r="A45" s="11"/>
-      <c r="B45" s="120"/>
+      <c r="B45" s="109"/>
       <c r="C45" s="48" t="str">
         <f>master!C25</f>
         <v>Java向けWebアプリケーションフレームワーク</v>
       </c>
-      <c r="D45" s="106" t="s">
+      <c r="D45" s="105" t="s">
         <v>122</v>
       </c>
-      <c r="E45" s="107"/>
-      <c r="F45" s="108"/>
+      <c r="E45" s="106"/>
+      <c r="F45" s="107"/>
       <c r="G45" s="48" t="s">
         <v>47</v>
       </c>
@@ -7522,16 +7738,16 @@
     </row>
     <row r="46" spans="1:14" ht="189">
       <c r="A46" s="11"/>
-      <c r="B46" s="120"/>
+      <c r="B46" s="109"/>
       <c r="C46" s="48" t="str">
         <f>master!C26</f>
         <v>Springフレームワーク</v>
       </c>
-      <c r="D46" s="106" t="s">
+      <c r="D46" s="105" t="s">
         <v>123</v>
       </c>
-      <c r="E46" s="107"/>
-      <c r="F46" s="108"/>
+      <c r="E46" s="106"/>
+      <c r="F46" s="107"/>
       <c r="G46" s="48" t="s">
         <v>124</v>
       </c>
@@ -7549,16 +7765,16 @@
     </row>
     <row r="47" spans="1:14" ht="88.2">
       <c r="A47" s="11"/>
-      <c r="B47" s="120"/>
+      <c r="B47" s="109"/>
       <c r="C47" s="48" t="str">
         <f>master!C27</f>
         <v>Springフレームワーク：DIコンテナとは</v>
       </c>
-      <c r="D47" s="106" t="s">
+      <c r="D47" s="105" t="s">
         <v>125</v>
       </c>
-      <c r="E47" s="107"/>
-      <c r="F47" s="108"/>
+      <c r="E47" s="106"/>
+      <c r="F47" s="107"/>
       <c r="G47" s="48" t="s">
         <v>46</v>
       </c>
@@ -7578,16 +7794,16 @@
     </row>
     <row r="48" spans="1:14" ht="63">
       <c r="A48" s="11"/>
-      <c r="B48" s="120"/>
+      <c r="B48" s="109"/>
       <c r="C48" s="48" t="str">
         <f>master!C28</f>
         <v>DIコンテナ：DIコンテナが部品を注入する</v>
       </c>
-      <c r="D48" s="106" t="s">
+      <c r="D48" s="105" t="s">
         <v>126</v>
       </c>
-      <c r="E48" s="107"/>
-      <c r="F48" s="108"/>
+      <c r="E48" s="106"/>
+      <c r="F48" s="107"/>
       <c r="G48" s="48" t="s">
         <v>41</v>
       </c>
@@ -7605,16 +7821,16 @@
     </row>
     <row r="49" spans="1:14" ht="100.8">
       <c r="A49" s="11"/>
-      <c r="B49" s="120"/>
+      <c r="B49" s="109"/>
       <c r="C49" s="48" t="str">
         <f>master!C29</f>
         <v>DIコンテナ：DIコンテナによる部品と注入対象になるための目印</v>
       </c>
-      <c r="D49" s="106" t="s">
+      <c r="D49" s="105" t="s">
         <v>127</v>
       </c>
-      <c r="E49" s="107"/>
-      <c r="F49" s="108"/>
+      <c r="E49" s="106"/>
+      <c r="F49" s="107"/>
       <c r="G49" s="48" t="s">
         <v>48</v>
       </c>
@@ -7632,16 +7848,16 @@
     </row>
     <row r="50" spans="1:14" ht="100.8">
       <c r="A50" s="11"/>
-      <c r="B50" s="120"/>
+      <c r="B50" s="109"/>
       <c r="C50" s="48" t="str">
         <f>master!C30</f>
         <v>Springフレームワークにおける部品の設定</v>
       </c>
-      <c r="D50" s="106" t="s">
+      <c r="D50" s="105" t="s">
         <v>128</v>
       </c>
-      <c r="E50" s="107"/>
-      <c r="F50" s="108"/>
+      <c r="E50" s="106"/>
+      <c r="F50" s="107"/>
       <c r="G50" s="48" t="s">
         <v>48</v>
       </c>
@@ -7659,16 +7875,16 @@
     </row>
     <row r="51" spans="1:14" ht="88.2">
       <c r="A51" s="11"/>
-      <c r="B51" s="120"/>
+      <c r="B51" s="109"/>
       <c r="C51" s="48" t="str">
         <f>master!C31</f>
         <v>Spring Boot</v>
       </c>
-      <c r="D51" s="106" t="s">
+      <c r="D51" s="105" t="s">
         <v>129</v>
       </c>
-      <c r="E51" s="107"/>
-      <c r="F51" s="108"/>
+      <c r="E51" s="106"/>
+      <c r="F51" s="107"/>
       <c r="G51" s="48" t="s">
         <v>46</v>
       </c>
@@ -7686,16 +7902,16 @@
     </row>
     <row r="52" spans="1:14" ht="63">
       <c r="A52" s="11"/>
-      <c r="B52" s="120"/>
+      <c r="B52" s="109"/>
       <c r="C52" s="48" t="str">
         <f>master!C32</f>
         <v>Spring Boot：オートコンフィグレーション</v>
       </c>
-      <c r="D52" s="106" t="s">
+      <c r="D52" s="105" t="s">
         <v>130</v>
       </c>
-      <c r="E52" s="107"/>
-      <c r="F52" s="108"/>
+      <c r="E52" s="106"/>
+      <c r="F52" s="107"/>
       <c r="G52" s="48" t="s">
         <v>41</v>
       </c>
@@ -7713,16 +7929,16 @@
     </row>
     <row r="53" spans="1:14" ht="50.4">
       <c r="A53" s="11"/>
-      <c r="B53" s="120"/>
+      <c r="B53" s="109"/>
       <c r="C53" s="48" t="str">
         <f>master!C33</f>
         <v>Spring Boot：Starters</v>
       </c>
-      <c r="D53" s="106" t="s">
+      <c r="D53" s="105" t="s">
         <v>131</v>
       </c>
-      <c r="E53" s="107"/>
-      <c r="F53" s="108"/>
+      <c r="E53" s="106"/>
+      <c r="F53" s="107"/>
       <c r="G53" s="48" t="s">
         <v>43</v>
       </c>
@@ -7740,16 +7956,16 @@
     </row>
     <row r="54" spans="1:14" ht="88.2">
       <c r="A54" s="11"/>
-      <c r="B54" s="120"/>
+      <c r="B54" s="109"/>
       <c r="C54" s="48" t="str">
         <f>master!C34</f>
         <v>Spring Boot：組込みWebAPサーバ</v>
       </c>
-      <c r="D54" s="106" t="s">
+      <c r="D54" s="105" t="s">
         <v>132</v>
       </c>
-      <c r="E54" s="107"/>
-      <c r="F54" s="108"/>
+      <c r="E54" s="106"/>
+      <c r="F54" s="107"/>
       <c r="G54" s="48" t="s">
         <v>46</v>
       </c>
@@ -7767,14 +7983,14 @@
     </row>
     <row r="55" spans="1:14" ht="25.2">
       <c r="A55" s="11"/>
-      <c r="B55" s="121"/>
+      <c r="B55" s="110"/>
       <c r="C55" s="48" t="str">
         <f>master!C35</f>
         <v>おすすめ書籍：『プロになるためのSpring入門』</v>
       </c>
-      <c r="D55" s="106"/>
-      <c r="E55" s="107"/>
-      <c r="F55" s="108"/>
+      <c r="D55" s="105"/>
+      <c r="E55" s="106"/>
+      <c r="F55" s="107"/>
       <c r="G55" s="48" t="s">
         <v>47</v>
       </c>
@@ -7792,7 +8008,7 @@
     </row>
     <row r="56" spans="1:14" ht="37.799999999999997">
       <c r="A56" s="11"/>
-      <c r="B56" s="116" t="str">
+      <c r="B56" s="114" t="str">
         <f>master!B37</f>
         <v>課題1の導入</v>
       </c>
@@ -7800,11 +8016,11 @@
         <f>master!C37</f>
         <v>演習課題の概要</v>
       </c>
-      <c r="D56" s="109" t="s">
+      <c r="D56" s="111" t="s">
         <v>165</v>
       </c>
-      <c r="E56" s="110"/>
-      <c r="F56" s="111"/>
+      <c r="E56" s="112"/>
+      <c r="F56" s="113"/>
       <c r="G56" s="58" t="s">
         <v>289</v>
       </c>
@@ -7822,16 +8038,16 @@
     </row>
     <row r="57" spans="1:14" ht="37.799999999999997">
       <c r="A57" s="11"/>
-      <c r="B57" s="117"/>
+      <c r="B57" s="115"/>
       <c r="C57" s="58" t="str">
         <f>master!C38</f>
         <v>作成物</v>
       </c>
-      <c r="D57" s="109" t="s">
+      <c r="D57" s="111" t="s">
         <v>166</v>
       </c>
-      <c r="E57" s="110"/>
-      <c r="F57" s="111"/>
+      <c r="E57" s="112"/>
+      <c r="F57" s="113"/>
       <c r="G57" s="58" t="s">
         <v>289</v>
       </c>
@@ -7849,16 +8065,16 @@
     </row>
     <row r="58" spans="1:14" ht="75.599999999999994">
       <c r="A58" s="11"/>
-      <c r="B58" s="118"/>
+      <c r="B58" s="116"/>
       <c r="C58" s="58" t="str">
         <f>master!C39</f>
         <v>演習課題の進め方</v>
       </c>
-      <c r="D58" s="109" t="s">
+      <c r="D58" s="111" t="s">
         <v>167</v>
       </c>
-      <c r="E58" s="110"/>
-      <c r="F58" s="111"/>
+      <c r="E58" s="112"/>
+      <c r="F58" s="113"/>
       <c r="G58" s="58" t="s">
         <v>290</v>
       </c>
@@ -7876,7 +8092,7 @@
     </row>
     <row r="59" spans="1:14" ht="15" customHeight="1">
       <c r="A59" s="11"/>
-      <c r="B59" s="116" t="str">
+      <c r="B59" s="114" t="str">
         <f>master!B40</f>
         <v>Spring Bootプロジェクトの_x000B_準備、起動確認</v>
       </c>
@@ -7884,9 +8100,9 @@
         <f>master!C40</f>
         <v>前提条件</v>
       </c>
-      <c r="D59" s="109"/>
-      <c r="E59" s="110"/>
-      <c r="F59" s="111"/>
+      <c r="D59" s="111"/>
+      <c r="E59" s="112"/>
+      <c r="F59" s="113"/>
       <c r="G59" s="58" t="s">
         <v>291</v>
       </c>
@@ -7904,16 +8120,16 @@
     </row>
     <row r="60" spans="1:14" ht="37.799999999999997">
       <c r="A60" s="11"/>
-      <c r="B60" s="117"/>
+      <c r="B60" s="115"/>
       <c r="C60" s="58" t="str">
         <f>master!C41</f>
         <v>Spring Bootプロジェクトの準備</v>
       </c>
-      <c r="D60" s="109" t="s">
+      <c r="D60" s="111" t="s">
         <v>168</v>
       </c>
-      <c r="E60" s="110"/>
-      <c r="F60" s="111"/>
+      <c r="E60" s="112"/>
+      <c r="F60" s="113"/>
       <c r="G60" s="58" t="s">
         <v>289</v>
       </c>
@@ -7931,16 +8147,16 @@
     </row>
     <row r="61" spans="1:14" ht="25.2">
       <c r="A61" s="11"/>
-      <c r="B61" s="117"/>
+      <c r="B61" s="115"/>
       <c r="C61" s="58" t="str">
         <f>master!C42</f>
         <v>（補足）Spring Bootプロジェクトの準備</v>
       </c>
-      <c r="D61" s="109" t="s">
+      <c r="D61" s="111" t="s">
         <v>169</v>
       </c>
-      <c r="E61" s="110"/>
-      <c r="F61" s="111"/>
+      <c r="E61" s="112"/>
+      <c r="F61" s="113"/>
       <c r="G61" s="58" t="s">
         <v>292</v>
       </c>
@@ -7958,16 +8174,16 @@
     </row>
     <row r="62" spans="1:14" ht="88.2">
       <c r="A62" s="11"/>
-      <c r="B62" s="118"/>
+      <c r="B62" s="116"/>
       <c r="C62" s="58" t="str">
         <f>master!C43</f>
         <v>Spring Bootアプリケーションの起動確認</v>
       </c>
-      <c r="D62" s="109" t="s">
+      <c r="D62" s="111" t="s">
         <v>191</v>
       </c>
-      <c r="E62" s="110"/>
-      <c r="F62" s="111"/>
+      <c r="E62" s="112"/>
+      <c r="F62" s="113"/>
       <c r="G62" s="58" t="s">
         <v>293</v>
       </c>
@@ -7985,7 +8201,7 @@
     </row>
     <row r="63" spans="1:14" ht="190.2" customHeight="1">
       <c r="A63" s="11"/>
-      <c r="B63" s="116" t="str">
+      <c r="B63" s="114" t="str">
         <f>master!B44</f>
         <v>ECサイト Webアプリの要件</v>
       </c>
@@ -7993,11 +8209,11 @@
         <f>master!C44</f>
         <v>ECサイト Webアプリの要件 – はじめに</v>
       </c>
-      <c r="D63" s="109" t="s">
+      <c r="D63" s="111" t="s">
         <v>170</v>
       </c>
-      <c r="E63" s="110"/>
-      <c r="F63" s="111"/>
+      <c r="E63" s="112"/>
+      <c r="F63" s="113"/>
       <c r="G63" s="58" t="s">
         <v>294</v>
       </c>
@@ -8015,16 +8231,16 @@
     </row>
     <row r="64" spans="1:14" ht="151.19999999999999">
       <c r="A64" s="11"/>
-      <c r="B64" s="117"/>
+      <c r="B64" s="115"/>
       <c r="C64" s="58" t="str">
         <f>master!C45</f>
         <v>ECサイト Webアプリの要件➊ 画面</v>
       </c>
-      <c r="D64" s="109" t="s">
+      <c r="D64" s="111" t="s">
         <v>172</v>
       </c>
-      <c r="E64" s="110"/>
-      <c r="F64" s="111"/>
+      <c r="E64" s="112"/>
+      <c r="F64" s="113"/>
       <c r="G64" s="58" t="s">
         <v>295</v>
       </c>
@@ -8042,16 +8258,16 @@
     </row>
     <row r="65" spans="1:14" ht="214.2">
       <c r="A65" s="11"/>
-      <c r="B65" s="117"/>
+      <c r="B65" s="115"/>
       <c r="C65" s="58" t="str">
         <f>master!C46</f>
         <v>ECサイト Webアプリの要件➋ 機能</v>
       </c>
-      <c r="D65" s="109" t="s">
+      <c r="D65" s="111" t="s">
         <v>173</v>
       </c>
-      <c r="E65" s="110"/>
-      <c r="F65" s="111"/>
+      <c r="E65" s="112"/>
+      <c r="F65" s="113"/>
       <c r="G65" s="58" t="s">
         <v>296</v>
       </c>
@@ -8069,16 +8285,16 @@
     </row>
     <row r="66" spans="1:14" ht="63">
       <c r="A66" s="11"/>
-      <c r="B66" s="117"/>
+      <c r="B66" s="115"/>
       <c r="C66" s="58" t="str">
         <f>master!C47</f>
         <v>ECサイト Webアプリの要件➌ 画面遷移</v>
       </c>
-      <c r="D66" s="109" t="s">
+      <c r="D66" s="111" t="s">
         <v>174</v>
       </c>
-      <c r="E66" s="110"/>
-      <c r="F66" s="111"/>
+      <c r="E66" s="112"/>
+      <c r="F66" s="113"/>
       <c r="G66" s="58" t="s">
         <v>297</v>
       </c>
@@ -8096,16 +8312,16 @@
     </row>
     <row r="67" spans="1:14" ht="163.80000000000001">
       <c r="A67" s="11"/>
-      <c r="B67" s="117"/>
+      <c r="B67" s="115"/>
       <c r="C67" s="58" t="str">
         <f>master!C48</f>
         <v>ECサイト Webアプリの要件❹ データ設計</v>
       </c>
-      <c r="D67" s="109" t="s">
+      <c r="D67" s="111" t="s">
         <v>176</v>
       </c>
-      <c r="E67" s="110"/>
-      <c r="F67" s="111"/>
+      <c r="E67" s="112"/>
+      <c r="F67" s="113"/>
       <c r="G67" s="58" t="s">
         <v>298</v>
       </c>
@@ -8123,16 +8339,16 @@
     </row>
     <row r="68" spans="1:14" ht="50.4">
       <c r="A68" s="11"/>
-      <c r="B68" s="117"/>
+      <c r="B68" s="115"/>
       <c r="C68" s="58" t="str">
         <f>master!C49</f>
         <v>ECサイト Webアプリの要件❺ 初期データ</v>
       </c>
-      <c r="D68" s="109" t="s">
+      <c r="D68" s="111" t="s">
         <v>177</v>
       </c>
-      <c r="E68" s="110"/>
-      <c r="F68" s="111"/>
+      <c r="E68" s="112"/>
+      <c r="F68" s="113"/>
       <c r="G68" s="58" t="s">
         <v>294</v>
       </c>
@@ -8150,16 +8366,16 @@
     </row>
     <row r="69" spans="1:14" ht="37.799999999999997">
       <c r="A69" s="11"/>
-      <c r="B69" s="117"/>
+      <c r="B69" s="115"/>
       <c r="C69" s="58" t="str">
         <f>master!C50</f>
         <v>ECサイト Webアプリの要件❻ ディレクトリ構成</v>
       </c>
-      <c r="D69" s="109" t="s">
+      <c r="D69" s="111" t="s">
         <v>178</v>
       </c>
-      <c r="E69" s="110"/>
-      <c r="F69" s="111"/>
+      <c r="E69" s="112"/>
+      <c r="F69" s="113"/>
       <c r="G69" s="58" t="s">
         <v>289</v>
       </c>
@@ -8177,16 +8393,16 @@
     </row>
     <row r="70" spans="1:14" ht="37.799999999999997">
       <c r="A70" s="11"/>
-      <c r="B70" s="117"/>
+      <c r="B70" s="115"/>
       <c r="C70" s="58" t="str">
         <f>master!C51</f>
         <v>ECサイト Webアプリの要件❼ パッケージ構成</v>
       </c>
-      <c r="D70" s="109" t="s">
+      <c r="D70" s="111" t="s">
         <v>180</v>
       </c>
-      <c r="E70" s="110"/>
-      <c r="F70" s="111"/>
+      <c r="E70" s="112"/>
+      <c r="F70" s="113"/>
       <c r="G70" s="58" t="s">
         <v>289</v>
       </c>
@@ -8204,16 +8420,16 @@
     </row>
     <row r="71" spans="1:14" ht="37.799999999999997">
       <c r="A71" s="11"/>
-      <c r="B71" s="118"/>
+      <c r="B71" s="116"/>
       <c r="C71" s="58" t="str">
         <f>master!C52</f>
         <v>ECサイト Webアプリの要件❽ リソース構成</v>
       </c>
-      <c r="D71" s="109" t="s">
+      <c r="D71" s="111" t="s">
         <v>179</v>
       </c>
-      <c r="E71" s="110"/>
-      <c r="F71" s="111"/>
+      <c r="E71" s="112"/>
+      <c r="F71" s="113"/>
       <c r="G71" s="58" t="s">
         <v>289</v>
       </c>
@@ -8231,7 +8447,7 @@
     </row>
     <row r="72" spans="1:14" ht="25.2">
       <c r="A72" s="11"/>
-      <c r="B72" s="116" t="str">
+      <c r="B72" s="114" t="str">
         <f>master!B53</f>
         <v>ハンズオン</v>
       </c>
@@ -8239,11 +8455,11 @@
         <f>master!C53</f>
         <v>バイブコーディング – はじめに</v>
       </c>
-      <c r="D72" s="109" t="s">
+      <c r="D72" s="111" t="s">
         <v>181</v>
       </c>
-      <c r="E72" s="110"/>
-      <c r="F72" s="111"/>
+      <c r="E72" s="112"/>
+      <c r="F72" s="113"/>
       <c r="G72" s="58" t="s">
         <v>292</v>
       </c>
@@ -8261,16 +8477,16 @@
     </row>
     <row r="73" spans="1:14" ht="138.6">
       <c r="A73" s="11"/>
-      <c r="B73" s="117"/>
+      <c r="B73" s="115"/>
       <c r="C73" s="58" t="str">
         <f>master!C54</f>
         <v>[構造理解] Webアプリケーションで必要なもの</v>
       </c>
-      <c r="D73" s="109" t="s">
+      <c r="D73" s="111" t="s">
         <v>182</v>
       </c>
-      <c r="E73" s="110"/>
-      <c r="F73" s="111"/>
+      <c r="E73" s="112"/>
+      <c r="F73" s="113"/>
       <c r="G73" s="58" t="s">
         <v>299</v>
       </c>
@@ -8288,16 +8504,16 @@
     </row>
     <row r="74" spans="1:14" ht="50.4">
       <c r="A74" s="11"/>
-      <c r="B74" s="117"/>
+      <c r="B74" s="115"/>
       <c r="C74" s="76" t="str">
         <f>master!C55</f>
         <v>バイブコーディング➊ 画面モックアップを作ってデザインを決める</v>
       </c>
-      <c r="D74" s="109" t="s">
+      <c r="D74" s="111" t="s">
         <v>192</v>
       </c>
-      <c r="E74" s="110"/>
-      <c r="F74" s="111"/>
+      <c r="E74" s="112"/>
+      <c r="F74" s="113"/>
       <c r="G74" s="58" t="s">
         <v>294</v>
       </c>
@@ -8315,13 +8531,13 @@
     </row>
     <row r="75" spans="1:14" ht="88.2" customHeight="1">
       <c r="A75" s="11"/>
-      <c r="B75" s="117"/>
+      <c r="B75" s="115"/>
       <c r="C75" s="77"/>
-      <c r="D75" s="109" t="s">
+      <c r="D75" s="111" t="s">
         <v>183</v>
       </c>
-      <c r="E75" s="110"/>
-      <c r="F75" s="111"/>
+      <c r="E75" s="112"/>
+      <c r="F75" s="113"/>
       <c r="G75" s="58" t="s">
         <v>293</v>
       </c>
@@ -8335,16 +8551,16 @@
     </row>
     <row r="76" spans="1:14" ht="50.4">
       <c r="A76" s="11"/>
-      <c r="B76" s="117"/>
+      <c r="B76" s="115"/>
       <c r="C76" s="76" t="str">
         <f>master!C56</f>
         <v>バイブコーディング➋ データベースのテーブルを準備する</v>
       </c>
-      <c r="D76" s="109" t="s">
+      <c r="D76" s="111" t="s">
         <v>196</v>
       </c>
-      <c r="E76" s="110"/>
-      <c r="F76" s="111"/>
+      <c r="E76" s="112"/>
+      <c r="F76" s="113"/>
       <c r="G76" s="58" t="s">
         <v>294</v>
       </c>
@@ -8362,13 +8578,13 @@
     </row>
     <row r="77" spans="1:14" ht="88.2">
       <c r="A77" s="11"/>
-      <c r="B77" s="117"/>
+      <c r="B77" s="115"/>
       <c r="C77" s="77"/>
-      <c r="D77" s="109" t="s">
+      <c r="D77" s="111" t="s">
         <v>183</v>
       </c>
-      <c r="E77" s="110"/>
-      <c r="F77" s="111"/>
+      <c r="E77" s="112"/>
+      <c r="F77" s="113"/>
       <c r="G77" s="58" t="s">
         <v>293</v>
       </c>
@@ -8382,16 +8598,16 @@
     </row>
     <row r="78" spans="1:14" ht="50.4">
       <c r="A78" s="11"/>
-      <c r="B78" s="117"/>
+      <c r="B78" s="115"/>
       <c r="C78" s="76" t="str">
         <f>master!C57</f>
         <v>バイブコーディング➌ データベースのデータを準備する</v>
       </c>
-      <c r="D78" s="109" t="s">
+      <c r="D78" s="111" t="s">
         <v>195</v>
       </c>
-      <c r="E78" s="110"/>
-      <c r="F78" s="111"/>
+      <c r="E78" s="112"/>
+      <c r="F78" s="113"/>
       <c r="G78" s="58" t="s">
         <v>294</v>
       </c>
@@ -8409,13 +8625,13 @@
     </row>
     <row r="79" spans="1:14" ht="88.2">
       <c r="A79" s="11"/>
-      <c r="B79" s="117"/>
+      <c r="B79" s="115"/>
       <c r="C79" s="77"/>
-      <c r="D79" s="109" t="s">
+      <c r="D79" s="111" t="s">
         <v>183</v>
       </c>
-      <c r="E79" s="110"/>
-      <c r="F79" s="111"/>
+      <c r="E79" s="112"/>
+      <c r="F79" s="113"/>
       <c r="G79" s="58" t="s">
         <v>293</v>
       </c>
@@ -8429,16 +8645,16 @@
     </row>
     <row r="80" spans="1:14" ht="63">
       <c r="A80" s="11"/>
-      <c r="B80" s="117"/>
+      <c r="B80" s="115"/>
       <c r="C80" s="76" t="str">
         <f>master!C58</f>
         <v>バイブコーディング❹ データベース処理とビジネスロジックを作る</v>
       </c>
-      <c r="D80" s="109" t="s">
+      <c r="D80" s="111" t="s">
         <v>194</v>
       </c>
-      <c r="E80" s="110"/>
-      <c r="F80" s="111"/>
+      <c r="E80" s="112"/>
+      <c r="F80" s="113"/>
       <c r="G80" s="58" t="s">
         <v>297</v>
       </c>
@@ -8456,13 +8672,13 @@
     </row>
     <row r="81" spans="1:14" ht="88.2">
       <c r="A81" s="11"/>
-      <c r="B81" s="117"/>
+      <c r="B81" s="115"/>
       <c r="C81" s="77"/>
-      <c r="D81" s="109" t="s">
+      <c r="D81" s="111" t="s">
         <v>183</v>
       </c>
-      <c r="E81" s="110"/>
-      <c r="F81" s="111"/>
+      <c r="E81" s="112"/>
+      <c r="F81" s="113"/>
       <c r="G81" s="58" t="s">
         <v>293</v>
       </c>
@@ -8476,16 +8692,16 @@
     </row>
     <row r="82" spans="1:14" ht="50.4">
       <c r="A82" s="11"/>
-      <c r="B82" s="117"/>
+      <c r="B82" s="115"/>
       <c r="C82" s="58" t="str">
         <f>master!C59</f>
         <v>[解説] RepositoryクラスとSQLの例（抜粋）</v>
       </c>
-      <c r="D82" s="109" t="s">
+      <c r="D82" s="111" t="s">
         <v>184</v>
       </c>
-      <c r="E82" s="110"/>
-      <c r="F82" s="111"/>
+      <c r="E82" s="112"/>
+      <c r="F82" s="113"/>
       <c r="G82" s="58" t="s">
         <v>294</v>
       </c>
@@ -8503,16 +8719,16 @@
     </row>
     <row r="83" spans="1:14" ht="50.4">
       <c r="A83" s="11"/>
-      <c r="B83" s="117"/>
+      <c r="B83" s="115"/>
       <c r="C83" s="58" t="str">
         <f>master!C60</f>
         <v>[解説] Entity/Modelクラスの例（抜粋）</v>
       </c>
-      <c r="D83" s="109" t="s">
+      <c r="D83" s="111" t="s">
         <v>185</v>
       </c>
-      <c r="E83" s="110"/>
-      <c r="F83" s="111"/>
+      <c r="E83" s="112"/>
+      <c r="F83" s="113"/>
       <c r="G83" s="58" t="s">
         <v>294</v>
       </c>
@@ -8530,16 +8746,16 @@
     </row>
     <row r="84" spans="1:14" ht="37.799999999999997">
       <c r="A84" s="11"/>
-      <c r="B84" s="117"/>
+      <c r="B84" s="115"/>
       <c r="C84" s="58" t="str">
         <f>master!C61</f>
         <v>[解説] Serviceクラスの例（抜粋）</v>
       </c>
-      <c r="D84" s="109" t="s">
+      <c r="D84" s="111" t="s">
         <v>186</v>
       </c>
-      <c r="E84" s="110"/>
-      <c r="F84" s="111"/>
+      <c r="E84" s="112"/>
+      <c r="F84" s="113"/>
       <c r="G84" s="58" t="s">
         <v>289</v>
       </c>
@@ -8557,16 +8773,16 @@
     </row>
     <row r="85" spans="1:14" ht="50.4">
       <c r="A85" s="11"/>
-      <c r="B85" s="117"/>
+      <c r="B85" s="115"/>
       <c r="C85" s="76" t="str">
         <f>master!C62</f>
         <v>バイブコーディング❺ モックアップをもとに画面表示/処理を作る</v>
       </c>
-      <c r="D85" s="109" t="s">
+      <c r="D85" s="111" t="s">
         <v>193</v>
       </c>
-      <c r="E85" s="110"/>
-      <c r="F85" s="111"/>
+      <c r="E85" s="112"/>
+      <c r="F85" s="113"/>
       <c r="G85" s="58" t="s">
         <v>294</v>
       </c>
@@ -8584,13 +8800,13 @@
     </row>
     <row r="86" spans="1:14" ht="88.2">
       <c r="A86" s="11"/>
-      <c r="B86" s="117"/>
+      <c r="B86" s="115"/>
       <c r="C86" s="77"/>
-      <c r="D86" s="109" t="s">
+      <c r="D86" s="111" t="s">
         <v>183</v>
       </c>
-      <c r="E86" s="110"/>
-      <c r="F86" s="111"/>
+      <c r="E86" s="112"/>
+      <c r="F86" s="113"/>
       <c r="G86" s="58" t="s">
         <v>293</v>
       </c>
@@ -8604,16 +8820,16 @@
     </row>
     <row r="87" spans="1:14" ht="37.799999999999997">
       <c r="A87" s="11"/>
-      <c r="B87" s="117"/>
+      <c r="B87" s="115"/>
       <c r="C87" s="58" t="str">
         <f>master!C63</f>
         <v>[解説] Controllerクラスの例（抜粋）</v>
       </c>
-      <c r="D87" s="109" t="s">
+      <c r="D87" s="111" t="s">
         <v>187</v>
       </c>
-      <c r="E87" s="110"/>
-      <c r="F87" s="111"/>
+      <c r="E87" s="112"/>
+      <c r="F87" s="113"/>
       <c r="G87" s="58" t="s">
         <v>289</v>
       </c>
@@ -8631,16 +8847,16 @@
     </row>
     <row r="88" spans="1:14" ht="37.799999999999997">
       <c r="A88" s="11"/>
-      <c r="B88" s="117"/>
+      <c r="B88" s="115"/>
       <c r="C88" s="58" t="str">
         <f>master!C64</f>
         <v>[解説] Thymeleafテンプレートの例（抜粋）</v>
       </c>
-      <c r="D88" s="109" t="s">
+      <c r="D88" s="111" t="s">
         <v>188</v>
       </c>
-      <c r="E88" s="110"/>
-      <c r="F88" s="111"/>
+      <c r="E88" s="112"/>
+      <c r="F88" s="113"/>
       <c r="G88" s="58" t="s">
         <v>289</v>
       </c>
@@ -8658,16 +8874,16 @@
     </row>
     <row r="89" spans="1:14" ht="37.799999999999997">
       <c r="A89" s="11"/>
-      <c r="B89" s="117"/>
+      <c r="B89" s="115"/>
       <c r="C89" s="58" t="str">
         <f>master!C65</f>
         <v>[解説] Formクラスの例（抜粋）</v>
       </c>
-      <c r="D89" s="109" t="s">
+      <c r="D89" s="111" t="s">
         <v>189</v>
       </c>
-      <c r="E89" s="110"/>
-      <c r="F89" s="111"/>
+      <c r="E89" s="112"/>
+      <c r="F89" s="113"/>
       <c r="G89" s="58" t="s">
         <v>289</v>
       </c>
@@ -8685,16 +8901,16 @@
     </row>
     <row r="90" spans="1:14" ht="75.599999999999994">
       <c r="A90" s="11"/>
-      <c r="B90" s="117"/>
+      <c r="B90" s="115"/>
       <c r="C90" s="76" t="str">
         <f>master!C66</f>
         <v>バイブコーディング❻ 動作を確認する</v>
       </c>
-      <c r="D90" s="109" t="s">
+      <c r="D90" s="111" t="s">
         <v>190</v>
       </c>
-      <c r="E90" s="110"/>
-      <c r="F90" s="111"/>
+      <c r="E90" s="112"/>
+      <c r="F90" s="113"/>
       <c r="G90" s="58" t="s">
         <v>290</v>
       </c>
@@ -8712,13 +8928,13 @@
     </row>
     <row r="91" spans="1:14" ht="63">
       <c r="A91" s="11"/>
-      <c r="B91" s="118"/>
+      <c r="B91" s="116"/>
       <c r="C91" s="77"/>
-      <c r="D91" s="109" t="s">
+      <c r="D91" s="111" t="s">
         <v>197</v>
       </c>
-      <c r="E91" s="110"/>
-      <c r="F91" s="111"/>
+      <c r="E91" s="112"/>
+      <c r="F91" s="113"/>
       <c r="G91" s="58" t="s">
         <v>297</v>
       </c>
@@ -8736,7 +8952,7 @@
     </row>
     <row r="92" spans="1:14" ht="50.4">
       <c r="A92" s="11"/>
-      <c r="B92" s="119" t="str">
+      <c r="B92" s="108" t="str">
         <f>master!B69</f>
         <v>Gitとは</v>
       </c>
@@ -8744,11 +8960,11 @@
         <f>master!C69</f>
         <v>はじめに</v>
       </c>
-      <c r="D92" s="106" t="s">
+      <c r="D92" s="105" t="s">
         <v>423</v>
       </c>
-      <c r="E92" s="107"/>
-      <c r="F92" s="108"/>
+      <c r="E92" s="106"/>
+      <c r="F92" s="107"/>
       <c r="G92" s="48" t="s">
         <v>338</v>
       </c>
@@ -8757,25 +8973,25 @@
         <v>24</v>
       </c>
       <c r="J92" s="44">
-        <v>3.472222222222222E-3</v>
-      </c>
-      <c r="K92" s="125"/>
+        <v>1.3888888888888889E-3</v>
+      </c>
+      <c r="K92" s="90"/>
       <c r="L92" s="6"/>
       <c r="M92" s="6"/>
       <c r="N92" s="6"/>
     </row>
     <row r="93" spans="1:14" ht="37.799999999999997">
       <c r="A93" s="11"/>
-      <c r="B93" s="120"/>
+      <c r="B93" s="109"/>
       <c r="C93" s="48" t="str">
         <f>master!C70</f>
         <v>バージョン管理とは</v>
       </c>
-      <c r="D93" s="106" t="s">
+      <c r="D93" s="105" t="s">
         <v>398</v>
       </c>
-      <c r="E93" s="107"/>
-      <c r="F93" s="108"/>
+      <c r="E93" s="106"/>
+      <c r="F93" s="107"/>
       <c r="G93" s="48" t="s">
         <v>337</v>
       </c>
@@ -8784,25 +9000,25 @@
         <v>24</v>
       </c>
       <c r="J93" s="44">
-        <v>3.472222222222222E-3</v>
-      </c>
-      <c r="K93" s="125"/>
+        <v>2.0833333333333333E-3</v>
+      </c>
+      <c r="K93" s="90"/>
       <c r="L93" s="6"/>
       <c r="M93" s="6"/>
       <c r="N93" s="6"/>
     </row>
     <row r="94" spans="1:14" ht="151.19999999999999">
       <c r="A94" s="11"/>
-      <c r="B94" s="121"/>
+      <c r="B94" s="110"/>
       <c r="C94" s="48" t="str">
         <f>master!C71</f>
         <v>Gitの概要</v>
       </c>
-      <c r="D94" s="106" t="s">
+      <c r="D94" s="105" t="s">
         <v>399</v>
       </c>
-      <c r="E94" s="107"/>
-      <c r="F94" s="108"/>
+      <c r="E94" s="106"/>
+      <c r="F94" s="107"/>
       <c r="G94" s="48" t="s">
         <v>400</v>
       </c>
@@ -8811,16 +9027,16 @@
         <v>24</v>
       </c>
       <c r="J94" s="44">
-        <v>6.9444444444444441E-3</v>
-      </c>
-      <c r="K94" s="125"/>
+        <v>2.0833333333333333E-3</v>
+      </c>
+      <c r="K94" s="90"/>
       <c r="L94" s="6"/>
       <c r="M94" s="6"/>
       <c r="N94" s="6"/>
     </row>
     <row r="95" spans="1:14" ht="75.599999999999994">
       <c r="A95" s="11"/>
-      <c r="B95" s="119" t="str">
+      <c r="B95" s="108" t="str">
         <f>master!B72</f>
         <v>Gitの基本構成</v>
       </c>
@@ -8828,11 +9044,11 @@
         <f>master!C72</f>
         <v>はじめに</v>
       </c>
-      <c r="D95" s="106" t="s">
+      <c r="D95" s="105" t="s">
         <v>422</v>
       </c>
-      <c r="E95" s="107"/>
-      <c r="F95" s="108"/>
+      <c r="E95" s="106"/>
+      <c r="F95" s="107"/>
       <c r="G95" s="48" t="s">
         <v>401</v>
       </c>
@@ -8841,25 +9057,25 @@
         <v>24</v>
       </c>
       <c r="J95" s="44">
-        <v>3.472222222222222E-3</v>
-      </c>
-      <c r="K95" s="125"/>
+        <v>1.3888888888888889E-3</v>
+      </c>
+      <c r="K95" s="90"/>
       <c r="L95" s="6"/>
       <c r="M95" s="6"/>
       <c r="N95" s="6"/>
     </row>
     <row r="96" spans="1:14" ht="37.799999999999997">
       <c r="A96" s="11"/>
-      <c r="B96" s="120"/>
+      <c r="B96" s="109"/>
       <c r="C96" s="48" t="str">
         <f>master!C73</f>
         <v>ワーキングツリー</v>
       </c>
-      <c r="D96" s="106" t="s">
+      <c r="D96" s="105" t="s">
         <v>402</v>
       </c>
-      <c r="E96" s="107"/>
-      <c r="F96" s="108"/>
+      <c r="E96" s="106"/>
+      <c r="F96" s="107"/>
       <c r="G96" s="48" t="s">
         <v>337</v>
       </c>
@@ -8868,25 +9084,25 @@
         <v>24</v>
       </c>
       <c r="J96" s="44">
-        <v>3.472222222222222E-3</v>
-      </c>
-      <c r="K96" s="125"/>
+        <v>2.0833333333333333E-3</v>
+      </c>
+      <c r="K96" s="90"/>
       <c r="L96" s="6"/>
       <c r="M96" s="6"/>
       <c r="N96" s="6"/>
     </row>
     <row r="97" spans="1:14" ht="37.799999999999997">
       <c r="A97" s="11"/>
-      <c r="B97" s="120"/>
+      <c r="B97" s="109"/>
       <c r="C97" s="48" t="str">
         <f>master!C74</f>
         <v>ステージングエリア</v>
       </c>
-      <c r="D97" s="106" t="s">
+      <c r="D97" s="105" t="s">
         <v>403</v>
       </c>
-      <c r="E97" s="107"/>
-      <c r="F97" s="108"/>
+      <c r="E97" s="106"/>
+      <c r="F97" s="107"/>
       <c r="G97" s="48" t="s">
         <v>337</v>
       </c>
@@ -8895,25 +9111,25 @@
         <v>24</v>
       </c>
       <c r="J97" s="44">
-        <v>3.472222222222222E-3</v>
-      </c>
-      <c r="K97" s="125"/>
+        <v>2.0833333333333333E-3</v>
+      </c>
+      <c r="K97" s="90"/>
       <c r="L97" s="6"/>
       <c r="M97" s="6"/>
       <c r="N97" s="6"/>
     </row>
     <row r="98" spans="1:14" ht="37.799999999999997">
       <c r="A98" s="11"/>
-      <c r="B98" s="120"/>
+      <c r="B98" s="109"/>
       <c r="C98" s="48" t="str">
         <f>master!C75</f>
         <v>ローカルリポジトリ</v>
       </c>
-      <c r="D98" s="106" t="s">
+      <c r="D98" s="105" t="s">
         <v>404</v>
       </c>
-      <c r="E98" s="107"/>
-      <c r="F98" s="108"/>
+      <c r="E98" s="106"/>
+      <c r="F98" s="107"/>
       <c r="G98" s="48" t="s">
         <v>337</v>
       </c>
@@ -8922,25 +9138,25 @@
         <v>24</v>
       </c>
       <c r="J98" s="44">
-        <v>3.472222222222222E-3</v>
-      </c>
-      <c r="K98" s="125"/>
+        <v>2.0833333333333333E-3</v>
+      </c>
+      <c r="K98" s="90"/>
       <c r="L98" s="6"/>
       <c r="M98" s="6"/>
       <c r="N98" s="6"/>
     </row>
     <row r="99" spans="1:14" ht="50.4">
       <c r="A99" s="11"/>
-      <c r="B99" s="121"/>
+      <c r="B99" s="110"/>
       <c r="C99" s="48" t="str">
         <f>master!C76</f>
         <v>リモートリポジトリ</v>
       </c>
-      <c r="D99" s="106" t="s">
+      <c r="D99" s="105" t="s">
         <v>405</v>
       </c>
-      <c r="E99" s="107"/>
-      <c r="F99" s="108"/>
+      <c r="E99" s="106"/>
+      <c r="F99" s="107"/>
       <c r="G99" s="48" t="s">
         <v>338</v>
       </c>
@@ -8949,16 +9165,16 @@
         <v>24</v>
       </c>
       <c r="J99" s="44">
-        <v>3.472222222222222E-3</v>
-      </c>
-      <c r="K99" s="125"/>
+        <v>2.0833333333333333E-3</v>
+      </c>
+      <c r="K99" s="90"/>
       <c r="L99" s="6"/>
       <c r="M99" s="6"/>
       <c r="N99" s="6"/>
     </row>
     <row r="100" spans="1:14" ht="88.2">
       <c r="A100" s="11"/>
-      <c r="B100" s="119" t="str">
+      <c r="B100" s="108" t="str">
         <f>master!B77</f>
         <v>ローカルリポジトリの操作</v>
       </c>
@@ -8966,11 +9182,11 @@
         <f>master!C77</f>
         <v>はじめに</v>
       </c>
-      <c r="D100" s="106" t="s">
+      <c r="D100" s="105" t="s">
         <v>421</v>
       </c>
-      <c r="E100" s="107"/>
-      <c r="F100" s="108"/>
+      <c r="E100" s="106"/>
+      <c r="F100" s="107"/>
       <c r="G100" s="48" t="s">
         <v>406</v>
       </c>
@@ -8979,25 +9195,25 @@
         <v>24</v>
       </c>
       <c r="J100" s="44">
-        <v>3.472222222222222E-3</v>
-      </c>
-      <c r="K100" s="125"/>
+        <v>6.9444444444444447E-4</v>
+      </c>
+      <c r="K100" s="90"/>
       <c r="L100" s="6"/>
       <c r="M100" s="6"/>
       <c r="N100" s="6"/>
     </row>
     <row r="101" spans="1:14" ht="37.799999999999997">
       <c r="A101" s="11"/>
-      <c r="B101" s="120"/>
+      <c r="B101" s="109"/>
       <c r="C101" s="48" t="str">
         <f>master!C78</f>
         <v>リポジトリの作成</v>
       </c>
-      <c r="D101" s="106" t="s">
+      <c r="D101" s="105" t="s">
         <v>407</v>
       </c>
-      <c r="E101" s="107"/>
-      <c r="F101" s="108"/>
+      <c r="E101" s="106"/>
+      <c r="F101" s="107"/>
       <c r="G101" s="48" t="s">
         <v>337</v>
       </c>
@@ -9006,25 +9222,25 @@
         <v>24</v>
       </c>
       <c r="J101" s="44">
-        <v>6.9444444444444441E-3</v>
-      </c>
-      <c r="K101" s="125"/>
+        <v>1.3888888888888889E-3</v>
+      </c>
+      <c r="K101" s="90"/>
       <c r="L101" s="6"/>
       <c r="M101" s="6"/>
       <c r="N101" s="6"/>
     </row>
     <row r="102" spans="1:14" ht="37.799999999999997" customHeight="1">
       <c r="A102" s="11"/>
-      <c r="B102" s="120"/>
+      <c r="B102" s="109"/>
       <c r="C102" s="48" t="str">
         <f>master!C79</f>
         <v>ファイルの変更</v>
       </c>
-      <c r="D102" s="106" t="s">
+      <c r="D102" s="105" t="s">
         <v>408</v>
       </c>
-      <c r="E102" s="107"/>
-      <c r="F102" s="108"/>
+      <c r="E102" s="106"/>
+      <c r="F102" s="107"/>
       <c r="G102" s="48" t="s">
         <v>337</v>
       </c>
@@ -9033,25 +9249,25 @@
         <v>24</v>
       </c>
       <c r="J102" s="44">
-        <v>3.472222222222222E-3</v>
-      </c>
-      <c r="K102" s="125"/>
+        <v>1.3888888888888889E-3</v>
+      </c>
+      <c r="K102" s="90"/>
       <c r="L102" s="6"/>
       <c r="M102" s="6"/>
       <c r="N102" s="6"/>
     </row>
     <row r="103" spans="1:14" ht="37.799999999999997">
       <c r="A103" s="11"/>
-      <c r="B103" s="120"/>
+      <c r="B103" s="109"/>
       <c r="C103" s="48" t="str">
         <f>master!C80</f>
         <v>変更内容の確認</v>
       </c>
-      <c r="D103" s="106" t="s">
+      <c r="D103" s="105" t="s">
         <v>409</v>
       </c>
-      <c r="E103" s="107"/>
-      <c r="F103" s="108"/>
+      <c r="E103" s="106"/>
+      <c r="F103" s="107"/>
       <c r="G103" s="48" t="s">
         <v>337</v>
       </c>
@@ -9060,25 +9276,25 @@
         <v>24</v>
       </c>
       <c r="J103" s="44">
-        <v>3.472222222222222E-3</v>
-      </c>
-      <c r="K103" s="125"/>
+        <v>1.3888888888888889E-3</v>
+      </c>
+      <c r="K103" s="90"/>
       <c r="L103" s="6"/>
       <c r="M103" s="6"/>
       <c r="N103" s="6"/>
     </row>
     <row r="104" spans="1:14" ht="37.799999999999997">
       <c r="A104" s="11"/>
-      <c r="B104" s="120"/>
+      <c r="B104" s="109"/>
       <c r="C104" s="48" t="str">
         <f>master!C81</f>
         <v>変更内容のステージ</v>
       </c>
-      <c r="D104" s="106" t="s">
+      <c r="D104" s="105" t="s">
         <v>410</v>
       </c>
-      <c r="E104" s="107"/>
-      <c r="F104" s="108"/>
+      <c r="E104" s="106"/>
+      <c r="F104" s="107"/>
       <c r="G104" s="48" t="s">
         <v>337</v>
       </c>
@@ -9087,25 +9303,25 @@
         <v>24</v>
       </c>
       <c r="J104" s="44">
-        <v>6.9444444444444441E-3</v>
-      </c>
-      <c r="K104" s="125"/>
+        <v>1.3888888888888889E-3</v>
+      </c>
+      <c r="K104" s="90"/>
       <c r="L104" s="6"/>
       <c r="M104" s="6"/>
       <c r="N104" s="6"/>
     </row>
     <row r="105" spans="1:14" ht="37.799999999999997">
       <c r="A105" s="11"/>
-      <c r="B105" s="120"/>
+      <c r="B105" s="109"/>
       <c r="C105" s="48" t="str">
         <f>master!C82</f>
         <v>変更内容のコミット</v>
       </c>
-      <c r="D105" s="106" t="s">
+      <c r="D105" s="105" t="s">
         <v>411</v>
       </c>
-      <c r="E105" s="107"/>
-      <c r="F105" s="108"/>
+      <c r="E105" s="106"/>
+      <c r="F105" s="107"/>
       <c r="G105" s="48" t="s">
         <v>337</v>
       </c>
@@ -9114,25 +9330,25 @@
         <v>24</v>
       </c>
       <c r="J105" s="44">
-        <v>3.472222222222222E-3</v>
-      </c>
-      <c r="K105" s="125"/>
+        <v>1.3888888888888889E-3</v>
+      </c>
+      <c r="K105" s="90"/>
       <c r="L105" s="6"/>
       <c r="M105" s="6"/>
       <c r="N105" s="6"/>
     </row>
     <row r="106" spans="1:14" ht="37.799999999999997">
       <c r="A106" s="11"/>
-      <c r="B106" s="120"/>
+      <c r="B106" s="109"/>
       <c r="C106" s="48" t="str">
         <f>master!C83</f>
         <v>ワーキングツリーの変更の取り消し</v>
       </c>
-      <c r="D106" s="106" t="s">
+      <c r="D106" s="105" t="s">
         <v>412</v>
       </c>
-      <c r="E106" s="107"/>
-      <c r="F106" s="108"/>
+      <c r="E106" s="106"/>
+      <c r="F106" s="107"/>
       <c r="G106" s="48" t="s">
         <v>337</v>
       </c>
@@ -9141,25 +9357,25 @@
         <v>24</v>
       </c>
       <c r="J106" s="44">
-        <v>3.472222222222222E-3</v>
-      </c>
-      <c r="K106" s="125"/>
+        <v>1.3888888888888889E-3</v>
+      </c>
+      <c r="K106" s="90"/>
       <c r="L106" s="6"/>
       <c r="M106" s="6"/>
       <c r="N106" s="6"/>
     </row>
     <row r="107" spans="1:14" ht="37.799999999999997">
       <c r="A107" s="11"/>
-      <c r="B107" s="120"/>
+      <c r="B107" s="109"/>
       <c r="C107" s="48" t="str">
         <f>master!C84</f>
         <v>ステージングの取り消し</v>
       </c>
-      <c r="D107" s="106" t="s">
+      <c r="D107" s="105" t="s">
         <v>413</v>
       </c>
-      <c r="E107" s="107"/>
-      <c r="F107" s="108"/>
+      <c r="E107" s="106"/>
+      <c r="F107" s="107"/>
       <c r="G107" s="48" t="s">
         <v>337</v>
       </c>
@@ -9168,25 +9384,25 @@
         <v>24</v>
       </c>
       <c r="J107" s="44">
-        <v>3.472222222222222E-3</v>
-      </c>
-      <c r="K107" s="125"/>
+        <v>1.3888888888888889E-3</v>
+      </c>
+      <c r="K107" s="90"/>
       <c r="L107" s="6"/>
       <c r="M107" s="6"/>
       <c r="N107" s="6"/>
     </row>
     <row r="108" spans="1:14" ht="37.799999999999997">
       <c r="A108" s="11"/>
-      <c r="B108" s="121"/>
+      <c r="B108" s="110"/>
       <c r="C108" s="48" t="str">
         <f>master!C85</f>
         <v>コミットの取り消し</v>
       </c>
-      <c r="D108" s="106" t="s">
+      <c r="D108" s="105" t="s">
         <v>414</v>
       </c>
-      <c r="E108" s="107"/>
-      <c r="F108" s="108"/>
+      <c r="E108" s="106"/>
+      <c r="F108" s="107"/>
       <c r="G108" s="48" t="s">
         <v>337</v>
       </c>
@@ -9195,16 +9411,16 @@
         <v>24</v>
       </c>
       <c r="J108" s="44">
-        <v>3.472222222222222E-3</v>
-      </c>
-      <c r="K108" s="125"/>
+        <v>1.3888888888888889E-3</v>
+      </c>
+      <c r="K108" s="90"/>
       <c r="L108" s="6"/>
       <c r="M108" s="6"/>
       <c r="N108" s="6"/>
     </row>
     <row r="109" spans="1:14" ht="75.599999999999994">
       <c r="A109" s="11"/>
-      <c r="B109" s="119" t="str">
+      <c r="B109" s="108" t="str">
         <f>master!B86</f>
         <v>リモートリポジトリの操作</v>
       </c>
@@ -9212,137 +9428,147 @@
         <f>master!C86</f>
         <v>はじめに</v>
       </c>
-      <c r="D109" s="106" t="s">
+      <c r="D109" s="105" t="s">
         <v>419</v>
       </c>
-      <c r="E109" s="107"/>
-      <c r="F109" s="108"/>
+      <c r="E109" s="106"/>
+      <c r="F109" s="107"/>
       <c r="G109" s="48" t="s">
         <v>401</v>
       </c>
       <c r="H109" s="12"/>
       <c r="I109" s="46" t="s">
-        <v>24</v>
+        <v>49</v>
       </c>
       <c r="J109" s="44">
-        <v>3.472222222222222E-3</v>
-      </c>
-      <c r="K109" s="125"/>
+        <v>0</v>
+      </c>
+      <c r="K109" s="90" t="s">
+        <v>433</v>
+      </c>
       <c r="L109" s="6"/>
       <c r="M109" s="6"/>
       <c r="N109" s="6"/>
     </row>
     <row r="110" spans="1:14" ht="37.799999999999997">
       <c r="A110" s="11"/>
-      <c r="B110" s="120"/>
+      <c r="B110" s="109"/>
       <c r="C110" s="48" t="str">
         <f>master!C87</f>
         <v>リポジトリの取得</v>
       </c>
-      <c r="D110" s="106" t="s">
+      <c r="D110" s="105" t="s">
         <v>415</v>
       </c>
-      <c r="E110" s="107"/>
-      <c r="F110" s="108"/>
+      <c r="E110" s="106"/>
+      <c r="F110" s="107"/>
       <c r="G110" s="48" t="s">
         <v>337</v>
       </c>
       <c r="H110" s="12"/>
       <c r="I110" s="46" t="s">
-        <v>24</v>
+        <v>49</v>
       </c>
       <c r="J110" s="44">
-        <v>3.472222222222222E-3</v>
-      </c>
-      <c r="K110" s="125"/>
+        <v>0</v>
+      </c>
+      <c r="K110" s="90" t="s">
+        <v>433</v>
+      </c>
       <c r="L110" s="6"/>
       <c r="M110" s="6"/>
       <c r="N110" s="6"/>
     </row>
     <row r="111" spans="1:14" ht="37.799999999999997">
       <c r="A111" s="11"/>
-      <c r="B111" s="120"/>
+      <c r="B111" s="109"/>
       <c r="C111" s="48" t="str">
         <f>master!C88</f>
         <v>リモートからの取得</v>
       </c>
-      <c r="D111" s="106" t="s">
+      <c r="D111" s="105" t="s">
         <v>416</v>
       </c>
-      <c r="E111" s="107"/>
-      <c r="F111" s="108"/>
+      <c r="E111" s="106"/>
+      <c r="F111" s="107"/>
       <c r="G111" s="48" t="s">
         <v>337</v>
       </c>
       <c r="H111" s="12"/>
       <c r="I111" s="46" t="s">
-        <v>24</v>
+        <v>49</v>
       </c>
       <c r="J111" s="44">
-        <v>3.472222222222222E-3</v>
-      </c>
-      <c r="K111" s="125"/>
+        <v>0</v>
+      </c>
+      <c r="K111" s="90" t="s">
+        <v>433</v>
+      </c>
       <c r="L111" s="6"/>
       <c r="M111" s="6"/>
       <c r="N111" s="6"/>
     </row>
     <row r="112" spans="1:14" ht="37.799999999999997">
       <c r="A112" s="11"/>
-      <c r="B112" s="120"/>
+      <c r="B112" s="109"/>
       <c r="C112" s="48" t="str">
         <f>master!C89</f>
         <v>リモートからの取得と反映</v>
       </c>
-      <c r="D112" s="106" t="s">
+      <c r="D112" s="105" t="s">
         <v>418</v>
       </c>
-      <c r="E112" s="107"/>
-      <c r="F112" s="108"/>
+      <c r="E112" s="106"/>
+      <c r="F112" s="107"/>
       <c r="G112" s="48" t="s">
         <v>337</v>
       </c>
       <c r="H112" s="12"/>
       <c r="I112" s="46" t="s">
-        <v>24</v>
+        <v>49</v>
       </c>
       <c r="J112" s="44">
-        <v>3.472222222222222E-3</v>
-      </c>
-      <c r="K112" s="125"/>
+        <v>0</v>
+      </c>
+      <c r="K112" s="90" t="s">
+        <v>433</v>
+      </c>
       <c r="L112" s="6"/>
       <c r="M112" s="6"/>
       <c r="N112" s="6"/>
     </row>
     <row r="113" spans="1:14" ht="37.799999999999997">
       <c r="A113" s="11"/>
-      <c r="B113" s="121"/>
+      <c r="B113" s="110"/>
       <c r="C113" s="48" t="str">
         <f>master!C90</f>
         <v>リモートへの反映</v>
       </c>
-      <c r="D113" s="106" t="s">
+      <c r="D113" s="105" t="s">
         <v>417</v>
       </c>
-      <c r="E113" s="107"/>
-      <c r="F113" s="108"/>
+      <c r="E113" s="106"/>
+      <c r="F113" s="107"/>
       <c r="G113" s="48" t="s">
         <v>337</v>
       </c>
       <c r="H113" s="12"/>
       <c r="I113" s="46" t="s">
-        <v>24</v>
+        <v>49</v>
       </c>
       <c r="J113" s="44">
-        <v>3.472222222222222E-3</v>
-      </c>
-      <c r="K113" s="125"/>
+        <v>0</v>
+      </c>
+      <c r="K113" s="90" t="s">
+        <v>433</v>
+      </c>
       <c r="L113" s="6"/>
       <c r="M113" s="6"/>
       <c r="N113" s="6"/>
     </row>
     <row r="114" spans="1:14" ht="88.2">
       <c r="A114" s="11"/>
-      <c r="B114" s="119" t="str">
+      <c r="B114" s="108" t="str">
         <f>master!B91</f>
         <v>ブランチの操作</v>
       </c>
@@ -9350,11 +9576,11 @@
         <f>master!C91</f>
         <v>はじめに</v>
       </c>
-      <c r="D114" s="106" t="s">
+      <c r="D114" s="105" t="s">
         <v>420</v>
       </c>
-      <c r="E114" s="107"/>
-      <c r="F114" s="108"/>
+      <c r="E114" s="106"/>
+      <c r="F114" s="107"/>
       <c r="G114" s="48" t="s">
         <v>406</v>
       </c>
@@ -9363,25 +9589,25 @@
         <v>24</v>
       </c>
       <c r="J114" s="44">
-        <v>3.472222222222222E-3</v>
-      </c>
-      <c r="K114" s="125"/>
+        <v>6.9444444444444447E-4</v>
+      </c>
+      <c r="K114" s="90"/>
       <c r="L114" s="6"/>
       <c r="M114" s="6"/>
       <c r="N114" s="6"/>
     </row>
     <row r="115" spans="1:14" ht="37.799999999999997">
       <c r="A115" s="11"/>
-      <c r="B115" s="120"/>
+      <c r="B115" s="109"/>
       <c r="C115" s="48" t="str">
         <f>master!C92</f>
         <v>ブランチとは</v>
       </c>
-      <c r="D115" s="106" t="s">
+      <c r="D115" s="105" t="s">
         <v>424</v>
       </c>
-      <c r="E115" s="107"/>
-      <c r="F115" s="108"/>
+      <c r="E115" s="106"/>
+      <c r="F115" s="107"/>
       <c r="G115" s="48" t="s">
         <v>337</v>
       </c>
@@ -9390,25 +9616,25 @@
         <v>24</v>
       </c>
       <c r="J115" s="44">
-        <v>3.472222222222222E-3</v>
-      </c>
-      <c r="K115" s="125"/>
+        <v>1.3888888888888889E-3</v>
+      </c>
+      <c r="K115" s="90"/>
       <c r="L115" s="6"/>
       <c r="M115" s="6"/>
       <c r="N115" s="6"/>
     </row>
     <row r="116" spans="1:14" ht="37.799999999999997">
       <c r="A116" s="11"/>
-      <c r="B116" s="120"/>
+      <c r="B116" s="109"/>
       <c r="C116" s="48" t="str">
         <f>master!C93</f>
         <v>ブランチの作成</v>
       </c>
-      <c r="D116" s="106" t="s">
+      <c r="D116" s="105" t="s">
         <v>425</v>
       </c>
-      <c r="E116" s="107"/>
-      <c r="F116" s="108"/>
+      <c r="E116" s="106"/>
+      <c r="F116" s="107"/>
       <c r="G116" s="48" t="s">
         <v>337</v>
       </c>
@@ -9417,25 +9643,25 @@
         <v>24</v>
       </c>
       <c r="J116" s="44">
-        <v>3.472222222222222E-3</v>
-      </c>
-      <c r="K116" s="125"/>
+        <v>1.3888888888888889E-3</v>
+      </c>
+      <c r="K116" s="90"/>
       <c r="L116" s="6"/>
       <c r="M116" s="6"/>
       <c r="N116" s="6"/>
     </row>
     <row r="117" spans="1:14" ht="37.799999999999997">
       <c r="A117" s="11"/>
-      <c r="B117" s="120"/>
+      <c r="B117" s="109"/>
       <c r="C117" s="48" t="str">
         <f>master!C94</f>
         <v>ブランチの切り替え</v>
       </c>
-      <c r="D117" s="106" t="s">
+      <c r="D117" s="105" t="s">
         <v>426</v>
       </c>
-      <c r="E117" s="107"/>
-      <c r="F117" s="108"/>
+      <c r="E117" s="106"/>
+      <c r="F117" s="107"/>
       <c r="G117" s="48" t="s">
         <v>337</v>
       </c>
@@ -9444,25 +9670,25 @@
         <v>24</v>
       </c>
       <c r="J117" s="44">
-        <v>3.472222222222222E-3</v>
-      </c>
-      <c r="K117" s="125"/>
+        <v>1.3888888888888889E-3</v>
+      </c>
+      <c r="K117" s="90"/>
       <c r="L117" s="6"/>
       <c r="M117" s="6"/>
       <c r="N117" s="6"/>
     </row>
     <row r="118" spans="1:14" ht="37.799999999999997">
       <c r="A118" s="11"/>
-      <c r="B118" s="120"/>
+      <c r="B118" s="109"/>
       <c r="C118" s="48" t="str">
         <f>master!C95</f>
         <v>ブランチのマージ</v>
       </c>
-      <c r="D118" s="106" t="s">
+      <c r="D118" s="105" t="s">
         <v>427</v>
       </c>
-      <c r="E118" s="107"/>
-      <c r="F118" s="108"/>
+      <c r="E118" s="106"/>
+      <c r="F118" s="107"/>
       <c r="G118" s="48" t="s">
         <v>337</v>
       </c>
@@ -9471,25 +9697,25 @@
         <v>24</v>
       </c>
       <c r="J118" s="44">
-        <v>3.472222222222222E-3</v>
-      </c>
-      <c r="K118" s="125"/>
+        <v>1.3888888888888889E-3</v>
+      </c>
+      <c r="K118" s="90"/>
       <c r="L118" s="6"/>
       <c r="M118" s="6"/>
       <c r="N118" s="6"/>
     </row>
     <row r="119" spans="1:14" ht="100.8">
       <c r="A119" s="11"/>
-      <c r="B119" s="121"/>
+      <c r="B119" s="110"/>
       <c r="C119" s="48" t="str">
         <f>master!C96</f>
         <v>コンフリクトの解消</v>
       </c>
-      <c r="D119" s="106" t="s">
-        <v>432</v>
-      </c>
-      <c r="E119" s="107"/>
-      <c r="F119" s="108"/>
+      <c r="D119" s="105" t="s">
+        <v>429</v>
+      </c>
+      <c r="E119" s="106"/>
+      <c r="F119" s="107"/>
       <c r="G119" s="48" t="s">
         <v>336</v>
       </c>
@@ -9498,16 +9724,16 @@
         <v>24</v>
       </c>
       <c r="J119" s="44">
-        <v>3.472222222222222E-3</v>
-      </c>
-      <c r="K119" s="125"/>
+        <v>2.0833333333333333E-3</v>
+      </c>
+      <c r="K119" s="90"/>
       <c r="L119" s="6"/>
       <c r="M119" s="6"/>
       <c r="N119" s="6"/>
     </row>
     <row r="120" spans="1:14" ht="75.599999999999994">
       <c r="A120" s="11"/>
-      <c r="B120" s="119" t="str">
+      <c r="B120" s="108" t="str">
         <f>master!B97</f>
         <v>VSCodeによるGitの操作</v>
       </c>
@@ -9515,11 +9741,11 @@
         <f>master!C97</f>
         <v>はじめに</v>
       </c>
-      <c r="D120" s="106" t="s">
+      <c r="D120" s="105" t="s">
         <v>428</v>
       </c>
-      <c r="E120" s="107"/>
-      <c r="F120" s="108"/>
+      <c r="E120" s="106"/>
+      <c r="F120" s="107"/>
       <c r="G120" s="48" t="s">
         <v>401</v>
       </c>
@@ -9528,124 +9754,126 @@
         <v>24</v>
       </c>
       <c r="J120" s="44">
-        <v>3.472222222222222E-3</v>
-      </c>
-      <c r="K120" s="125"/>
+        <v>6.9444444444444447E-4</v>
+      </c>
+      <c r="K120" s="90"/>
       <c r="L120" s="6"/>
       <c r="M120" s="6"/>
       <c r="N120" s="6"/>
     </row>
     <row r="121" spans="1:14" ht="25.2">
       <c r="A121" s="11"/>
-      <c r="B121" s="120"/>
+      <c r="B121" s="109"/>
       <c r="C121" s="48" t="str">
         <f>master!C98</f>
         <v>VSCodeのソース管理機能</v>
       </c>
-      <c r="D121" s="106" t="s">
-        <v>433</v>
-      </c>
-      <c r="E121" s="107"/>
-      <c r="F121" s="108"/>
+      <c r="D121" s="105" t="s">
+        <v>430</v>
+      </c>
+      <c r="E121" s="106"/>
+      <c r="F121" s="107"/>
       <c r="G121" s="48" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="H121" s="12"/>
       <c r="I121" s="46" t="s">
         <v>24</v>
       </c>
       <c r="J121" s="44">
-        <v>3.472222222222222E-3</v>
-      </c>
-      <c r="K121" s="125"/>
+        <v>6.9444444444444447E-4</v>
+      </c>
+      <c r="K121" s="90"/>
       <c r="L121" s="6"/>
       <c r="M121" s="6"/>
       <c r="N121" s="6"/>
     </row>
-    <row r="122" spans="1:14" ht="88.2">
+    <row r="122" spans="1:14" ht="126">
       <c r="A122" s="11"/>
-      <c r="B122" s="120"/>
+      <c r="B122" s="109"/>
       <c r="C122" s="48" t="str">
         <f>master!C99</f>
         <v>ローカルリポジトリの操作</v>
       </c>
-      <c r="D122" s="106" t="s">
-        <v>429</v>
-      </c>
-      <c r="E122" s="107"/>
-      <c r="F122" s="108"/>
+      <c r="D122" s="105" t="s">
+        <v>444</v>
+      </c>
+      <c r="E122" s="106"/>
+      <c r="F122" s="107"/>
       <c r="G122" s="48" t="s">
-        <v>406</v>
+        <v>443</v>
       </c>
       <c r="H122" s="12"/>
       <c r="I122" s="46" t="s">
-        <v>24</v>
+        <v>49</v>
       </c>
       <c r="J122" s="44">
-        <v>3.472222222222222E-3</v>
-      </c>
-      <c r="K122" s="125"/>
+        <v>0</v>
+      </c>
+      <c r="K122" s="90"/>
       <c r="L122" s="6"/>
       <c r="M122" s="6"/>
       <c r="N122" s="6"/>
     </row>
     <row r="123" spans="1:14" ht="63">
       <c r="A123" s="11"/>
-      <c r="B123" s="120"/>
+      <c r="B123" s="109"/>
       <c r="C123" s="48" t="str">
         <f>master!C100</f>
         <v>リモートリポジトリの操作</v>
       </c>
-      <c r="D123" s="106" t="s">
-        <v>430</v>
-      </c>
-      <c r="E123" s="107"/>
-      <c r="F123" s="108"/>
+      <c r="D123" s="105" t="s">
+        <v>432</v>
+      </c>
+      <c r="E123" s="106"/>
+      <c r="F123" s="107"/>
       <c r="G123" s="48" t="s">
         <v>339</v>
       </c>
       <c r="H123" s="12"/>
       <c r="I123" s="46" t="s">
-        <v>24</v>
+        <v>49</v>
       </c>
       <c r="J123" s="44">
-        <v>3.472222222222222E-3</v>
-      </c>
-      <c r="K123" s="125"/>
+        <v>0</v>
+      </c>
+      <c r="K123" s="90" t="s">
+        <v>433</v>
+      </c>
       <c r="L123" s="6"/>
       <c r="M123" s="6"/>
       <c r="N123" s="6"/>
     </row>
-    <row r="124" spans="1:14" ht="75.599999999999994">
+    <row r="124" spans="1:14" ht="113.4">
       <c r="A124" s="11"/>
-      <c r="B124" s="121"/>
+      <c r="B124" s="110"/>
       <c r="C124" s="48" t="str">
         <f>master!C101</f>
         <v>ブランチの操作</v>
       </c>
-      <c r="D124" s="106" t="s">
-        <v>431</v>
-      </c>
-      <c r="E124" s="107"/>
-      <c r="F124" s="108"/>
+      <c r="D124" s="105" t="s">
+        <v>445</v>
+      </c>
+      <c r="E124" s="106"/>
+      <c r="F124" s="107"/>
       <c r="G124" s="48" t="s">
-        <v>401</v>
+        <v>446</v>
       </c>
       <c r="H124" s="12"/>
       <c r="I124" s="46" t="s">
-        <v>24</v>
+        <v>49</v>
       </c>
       <c r="J124" s="44">
-        <v>3.472222222222222E-3</v>
-      </c>
-      <c r="K124" s="125"/>
+        <v>0</v>
+      </c>
+      <c r="K124" s="90"/>
       <c r="L124" s="6"/>
       <c r="M124" s="6"/>
       <c r="N124" s="6"/>
     </row>
-    <row r="125" spans="1:14" ht="76.8" customHeight="1">
+    <row r="125" spans="1:14" ht="25.2">
       <c r="A125" s="11"/>
-      <c r="B125" s="116" t="str">
+      <c r="B125" s="114" t="str">
         <f>master!B103</f>
         <v>演習について</v>
       </c>
@@ -9653,9 +9881,9 @@
         <f>master!C103</f>
         <v>はじめに</v>
       </c>
-      <c r="D125" s="109"/>
-      <c r="E125" s="110"/>
-      <c r="F125" s="111"/>
+      <c r="D125" s="111"/>
+      <c r="E125" s="112"/>
+      <c r="F125" s="113"/>
       <c r="G125" s="58" t="s">
         <v>341</v>
       </c>
@@ -9663,67 +9891,73 @@
       <c r="I125" s="60" t="s">
         <v>24</v>
       </c>
-      <c r="J125" s="61" t="s">
-        <v>348</v>
+      <c r="J125" s="61">
+        <v>6.9444444444444447E-4</v>
       </c>
       <c r="K125" s="62"/>
       <c r="L125" s="6"/>
       <c r="M125" s="6"/>
       <c r="N125" s="6"/>
     </row>
-    <row r="126" spans="1:14" ht="25.2">
+    <row r="126" spans="1:14" ht="50.4">
       <c r="A126" s="11"/>
-      <c r="B126" s="117"/>
+      <c r="B126" s="115"/>
       <c r="C126" s="58" t="str">
         <f>master!C104</f>
         <v>演習の構成</v>
       </c>
-      <c r="D126" s="109"/>
-      <c r="E126" s="110"/>
-      <c r="F126" s="111"/>
+      <c r="D126" s="111" t="s">
+        <v>435</v>
+      </c>
+      <c r="E126" s="112"/>
+      <c r="F126" s="113"/>
       <c r="G126" s="58" t="s">
-        <v>341</v>
+        <v>434</v>
       </c>
       <c r="H126" s="59"/>
       <c r="I126" s="60" t="s">
         <v>24</v>
       </c>
-      <c r="J126" s="61" t="s">
-        <v>348</v>
+      <c r="J126" s="61">
+        <v>6.9444444444444447E-4</v>
       </c>
       <c r="K126" s="62"/>
       <c r="L126" s="6"/>
       <c r="M126" s="6"/>
       <c r="N126" s="6"/>
     </row>
-    <row r="127" spans="1:14" ht="25.2">
+    <row r="127" spans="1:14" ht="50.4">
       <c r="A127" s="11"/>
-      <c r="B127" s="118"/>
+      <c r="B127" s="116"/>
       <c r="C127" s="58" t="str">
         <f>master!C105</f>
         <v>演習で利用するソフトウェア</v>
       </c>
-      <c r="D127" s="109"/>
-      <c r="E127" s="110"/>
-      <c r="F127" s="111"/>
+      <c r="D127" s="111" t="s">
+        <v>436</v>
+      </c>
+      <c r="E127" s="112"/>
+      <c r="F127" s="113"/>
       <c r="G127" s="58" t="s">
-        <v>341</v>
+        <v>434</v>
       </c>
       <c r="H127" s="59"/>
       <c r="I127" s="60" t="s">
         <v>24</v>
       </c>
-      <c r="J127" s="61" t="s">
-        <v>348</v>
-      </c>
-      <c r="K127" s="62"/>
+      <c r="J127" s="61">
+        <v>6.9444444444444447E-4</v>
+      </c>
+      <c r="K127" s="62" t="s">
+        <v>437</v>
+      </c>
       <c r="L127" s="6"/>
       <c r="M127" s="6"/>
       <c r="N127" s="6"/>
     </row>
-    <row r="128" spans="1:14" ht="25.2">
+    <row r="128" spans="1:14" ht="176.4">
       <c r="A128" s="11"/>
-      <c r="B128" s="116" t="str">
+      <c r="B128" s="114" t="str">
         <f>master!B106</f>
         <v>VS Codeによるローカルリポジトリの操作</v>
       </c>
@@ -9731,127 +9965,137 @@
         <f>master!C106</f>
         <v>演習の前に</v>
       </c>
-      <c r="D128" s="109"/>
-      <c r="E128" s="110"/>
-      <c r="F128" s="111"/>
+      <c r="D128" s="111" t="s">
+        <v>441</v>
+      </c>
+      <c r="E128" s="112"/>
+      <c r="F128" s="113"/>
       <c r="G128" s="58" t="s">
-        <v>341</v>
+        <v>440</v>
       </c>
       <c r="H128" s="59"/>
       <c r="I128" s="60" t="s">
         <v>24</v>
       </c>
-      <c r="J128" s="61" t="s">
-        <v>348</v>
+      <c r="J128" s="61">
+        <v>3.472222222222222E-3</v>
       </c>
       <c r="K128" s="62"/>
       <c r="L128" s="6"/>
       <c r="M128" s="6"/>
       <c r="N128" s="6"/>
     </row>
-    <row r="129" spans="1:14" ht="25.2">
+    <row r="129" spans="1:14" ht="37.799999999999997">
       <c r="A129" s="11"/>
-      <c r="B129" s="117"/>
+      <c r="B129" s="115"/>
       <c r="C129" s="58" t="str">
         <f>master!C107</f>
         <v>VS Codeによるリポジトリの作成</v>
       </c>
-      <c r="D129" s="109"/>
-      <c r="E129" s="110"/>
-      <c r="F129" s="111"/>
+      <c r="D129" s="111" t="s">
+        <v>438</v>
+      </c>
+      <c r="E129" s="112"/>
+      <c r="F129" s="113"/>
       <c r="G129" s="58" t="s">
-        <v>341</v>
+        <v>439</v>
       </c>
       <c r="H129" s="59"/>
       <c r="I129" s="60" t="s">
         <v>24</v>
       </c>
-      <c r="J129" s="61" t="s">
-        <v>348</v>
+      <c r="J129" s="61">
+        <v>3.472222222222222E-3</v>
       </c>
       <c r="K129" s="62"/>
       <c r="L129" s="6"/>
       <c r="M129" s="6"/>
       <c r="N129" s="6"/>
     </row>
-    <row r="130" spans="1:14" ht="25.2">
+    <row r="130" spans="1:14" ht="37.799999999999997">
       <c r="A130" s="11"/>
-      <c r="B130" s="117"/>
+      <c r="B130" s="115"/>
       <c r="C130" s="58" t="str">
         <f>master!C108</f>
         <v>VS Codeによる変更内容の確認</v>
       </c>
-      <c r="D130" s="109"/>
-      <c r="E130" s="110"/>
-      <c r="F130" s="111"/>
+      <c r="D130" s="111" t="s">
+        <v>438</v>
+      </c>
+      <c r="E130" s="112"/>
+      <c r="F130" s="113"/>
       <c r="G130" s="58" t="s">
-        <v>341</v>
+        <v>439</v>
       </c>
       <c r="H130" s="59"/>
       <c r="I130" s="60" t="s">
         <v>24</v>
       </c>
-      <c r="J130" s="61" t="s">
-        <v>348</v>
+      <c r="J130" s="61">
+        <v>3.472222222222222E-3</v>
       </c>
       <c r="K130" s="62"/>
       <c r="L130" s="6"/>
       <c r="M130" s="6"/>
       <c r="N130" s="6"/>
     </row>
-    <row r="131" spans="1:14" ht="25.2">
+    <row r="131" spans="1:14" ht="37.799999999999997">
       <c r="A131" s="11"/>
-      <c r="B131" s="117"/>
+      <c r="B131" s="115"/>
       <c r="C131" s="58" t="str">
         <f>master!C109</f>
         <v>VS Codeによる変更内容のステージング</v>
       </c>
-      <c r="D131" s="109"/>
-      <c r="E131" s="110"/>
-      <c r="F131" s="111"/>
+      <c r="D131" s="111" t="s">
+        <v>438</v>
+      </c>
+      <c r="E131" s="112"/>
+      <c r="F131" s="113"/>
       <c r="G131" s="58" t="s">
-        <v>341</v>
+        <v>439</v>
       </c>
       <c r="H131" s="59"/>
       <c r="I131" s="60" t="s">
         <v>24</v>
       </c>
-      <c r="J131" s="61" t="s">
-        <v>348</v>
+      <c r="J131" s="61">
+        <v>3.472222222222222E-3</v>
       </c>
       <c r="K131" s="62"/>
       <c r="L131" s="6"/>
       <c r="M131" s="6"/>
       <c r="N131" s="6"/>
     </row>
-    <row r="132" spans="1:14" ht="25.2">
+    <row r="132" spans="1:14" ht="37.799999999999997">
       <c r="A132" s="11"/>
-      <c r="B132" s="118"/>
+      <c r="B132" s="116"/>
       <c r="C132" s="58" t="str">
         <f>master!C110</f>
         <v>VS Codeによる変更内容のコミット</v>
       </c>
-      <c r="D132" s="109"/>
-      <c r="E132" s="110"/>
-      <c r="F132" s="111"/>
+      <c r="D132" s="111" t="s">
+        <v>438</v>
+      </c>
+      <c r="E132" s="112"/>
+      <c r="F132" s="113"/>
       <c r="G132" s="58" t="s">
-        <v>341</v>
+        <v>439</v>
       </c>
       <c r="H132" s="59"/>
       <c r="I132" s="60" t="s">
         <v>24</v>
       </c>
-      <c r="J132" s="61" t="s">
-        <v>348</v>
+      <c r="J132" s="61">
+        <v>3.472222222222222E-3</v>
       </c>
       <c r="K132" s="62"/>
       <c r="L132" s="6"/>
       <c r="M132" s="6"/>
       <c r="N132" s="6"/>
     </row>
-    <row r="133" spans="1:14" ht="25.2">
+    <row r="133" spans="1:14" ht="163.80000000000001">
       <c r="A133" s="11"/>
-      <c r="B133" s="116" t="str">
+      <c r="B133" s="114" t="str">
         <f>master!B111</f>
         <v>VS Codeによるブランチの操作</v>
       </c>
@@ -9859,93 +10103,101 @@
         <f>master!C111</f>
         <v>演習の前に</v>
       </c>
-      <c r="D133" s="109"/>
-      <c r="E133" s="110"/>
-      <c r="F133" s="111"/>
+      <c r="D133" s="111" t="s">
+        <v>442</v>
+      </c>
+      <c r="E133" s="112"/>
+      <c r="F133" s="113"/>
       <c r="G133" s="58" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="H133" s="59"/>
       <c r="I133" s="60" t="s">
         <v>24</v>
       </c>
-      <c r="J133" s="61" t="s">
-        <v>348</v>
+      <c r="J133" s="61">
+        <v>3.472222222222222E-3</v>
       </c>
       <c r="K133" s="62"/>
       <c r="L133" s="6"/>
       <c r="M133" s="6"/>
       <c r="N133" s="6"/>
     </row>
-    <row r="134" spans="1:14" ht="25.2">
+    <row r="134" spans="1:14" ht="37.799999999999997">
       <c r="A134" s="11"/>
-      <c r="B134" s="117"/>
+      <c r="B134" s="115"/>
       <c r="C134" s="58" t="str">
         <f>master!C112</f>
         <v>VS Codeによるブランチの作成</v>
       </c>
-      <c r="D134" s="109"/>
-      <c r="E134" s="110"/>
-      <c r="F134" s="111"/>
+      <c r="D134" s="111" t="s">
+        <v>438</v>
+      </c>
+      <c r="E134" s="112"/>
+      <c r="F134" s="113"/>
       <c r="G134" s="58" t="s">
-        <v>341</v>
+        <v>439</v>
       </c>
       <c r="H134" s="59"/>
       <c r="I134" s="60" t="s">
         <v>24</v>
       </c>
-      <c r="J134" s="61" t="s">
-        <v>348</v>
+      <c r="J134" s="61">
+        <v>3.472222222222222E-3</v>
       </c>
       <c r="K134" s="62"/>
       <c r="L134" s="6"/>
       <c r="M134" s="6"/>
       <c r="N134" s="6"/>
     </row>
-    <row r="135" spans="1:14" ht="25.2">
+    <row r="135" spans="1:14" ht="37.799999999999997">
       <c r="A135" s="11"/>
-      <c r="B135" s="117"/>
+      <c r="B135" s="115"/>
       <c r="C135" s="58" t="str">
         <f>master!C113</f>
         <v>VS Codeによるブランチの切り替え</v>
       </c>
-      <c r="D135" s="109"/>
-      <c r="E135" s="110"/>
-      <c r="F135" s="111"/>
+      <c r="D135" s="111" t="s">
+        <v>438</v>
+      </c>
+      <c r="E135" s="112"/>
+      <c r="F135" s="113"/>
       <c r="G135" s="58" t="s">
-        <v>341</v>
+        <v>439</v>
       </c>
       <c r="H135" s="59"/>
       <c r="I135" s="60" t="s">
         <v>24</v>
       </c>
-      <c r="J135" s="61" t="s">
-        <v>348</v>
+      <c r="J135" s="61">
+        <v>3.472222222222222E-3</v>
       </c>
       <c r="K135" s="62"/>
       <c r="L135" s="6"/>
       <c r="M135" s="6"/>
       <c r="N135" s="6"/>
     </row>
-    <row r="136" spans="1:14" ht="25.2">
+    <row r="136" spans="1:14" ht="37.799999999999997">
       <c r="A136" s="11"/>
-      <c r="B136" s="118"/>
+      <c r="B136" s="116"/>
       <c r="C136" s="58" t="str">
         <f>master!C114</f>
         <v>VS Codeによるブランチのマージ</v>
       </c>
-      <c r="D136" s="109"/>
-      <c r="E136" s="110"/>
-      <c r="F136" s="111"/>
+      <c r="D136" s="111" t="s">
+        <v>438</v>
+      </c>
+      <c r="E136" s="112"/>
+      <c r="F136" s="113"/>
       <c r="G136" s="58" t="s">
-        <v>341</v>
+        <v>439</v>
       </c>
       <c r="H136" s="59"/>
       <c r="I136" s="60" t="s">
         <v>24</v>
       </c>
-      <c r="J136" s="61" t="s">
-        <v>348</v>
+      <c r="J136" s="61">
+        <v>3.472222222222222E-3</v>
       </c>
       <c r="K136" s="62"/>
       <c r="L136" s="6"/>
@@ -9962,11 +10214,11 @@
         <f>master!C67</f>
         <v>ここから各自で演習を始めましょう。</v>
       </c>
-      <c r="D137" s="109" t="s">
+      <c r="D137" s="111" t="s">
         <v>198</v>
       </c>
-      <c r="E137" s="110"/>
-      <c r="F137" s="111"/>
+      <c r="E137" s="112"/>
+      <c r="F137" s="113"/>
       <c r="G137" s="58" t="s">
         <v>296</v>
       </c>
@@ -9984,7 +10236,7 @@
     </row>
     <row r="138" spans="1:14" ht="50.4">
       <c r="A138" s="11"/>
-      <c r="B138" s="104" t="str">
+      <c r="B138" s="123" t="str">
         <f>master!B116</f>
         <v>単体テストとJunitの導入</v>
       </c>
@@ -9992,11 +10244,11 @@
         <f>master!C116</f>
         <v>講義の目的</v>
       </c>
-      <c r="D138" s="106" t="s">
+      <c r="D138" s="105" t="s">
         <v>227</v>
       </c>
-      <c r="E138" s="107"/>
-      <c r="F138" s="108"/>
+      <c r="E138" s="106"/>
+      <c r="F138" s="107"/>
       <c r="G138" s="48" t="s">
         <v>300</v>
       </c>
@@ -10014,14 +10266,14 @@
     </row>
     <row r="139" spans="1:14" ht="25.2">
       <c r="A139" s="11"/>
-      <c r="B139" s="115"/>
+      <c r="B139" s="124"/>
       <c r="C139" s="78" t="str">
         <f>master!C117</f>
         <v>TERASOLUNA 開発手順　 ※再掲</v>
       </c>
-      <c r="D139" s="106"/>
-      <c r="E139" s="107"/>
-      <c r="F139" s="108"/>
+      <c r="D139" s="105"/>
+      <c r="E139" s="106"/>
+      <c r="F139" s="107"/>
       <c r="G139" s="48" t="s">
         <v>301</v>
       </c>
@@ -10039,16 +10291,16 @@
     </row>
     <row r="140" spans="1:14" ht="25.2">
       <c r="A140" s="11"/>
-      <c r="B140" s="105"/>
+      <c r="B140" s="125"/>
       <c r="C140" s="78" t="str">
         <f>master!C118</f>
         <v>V字モデル　 ※再掲</v>
       </c>
-      <c r="D140" s="106" t="s">
+      <c r="D140" s="105" t="s">
         <v>228</v>
       </c>
-      <c r="E140" s="107"/>
-      <c r="F140" s="108"/>
+      <c r="E140" s="106"/>
+      <c r="F140" s="107"/>
       <c r="G140" s="48" t="s">
         <v>301</v>
       </c>
@@ -10066,7 +10318,7 @@
     </row>
     <row r="141" spans="1:14" ht="50.4">
       <c r="A141" s="11"/>
-      <c r="B141" s="104" t="str">
+      <c r="B141" s="123" t="str">
         <f>master!B119</f>
         <v>テストとは</v>
       </c>
@@ -10074,11 +10326,11 @@
         <f>master!C119</f>
         <v>テストとは</v>
       </c>
-      <c r="D141" s="106" t="s">
+      <c r="D141" s="105" t="s">
         <v>229</v>
       </c>
-      <c r="E141" s="107"/>
-      <c r="F141" s="108"/>
+      <c r="E141" s="106"/>
+      <c r="F141" s="107"/>
       <c r="G141" s="48" t="s">
         <v>300</v>
       </c>
@@ -10096,16 +10348,16 @@
     </row>
     <row r="142" spans="1:14" ht="315">
       <c r="A142" s="11"/>
-      <c r="B142" s="115"/>
+      <c r="B142" s="124"/>
       <c r="C142" s="78" t="str">
         <f>master!C120</f>
         <v>テストの目的</v>
       </c>
-      <c r="D142" s="106" t="s">
+      <c r="D142" s="105" t="s">
         <v>230</v>
       </c>
-      <c r="E142" s="107"/>
-      <c r="F142" s="108"/>
+      <c r="E142" s="106"/>
+      <c r="F142" s="107"/>
       <c r="G142" s="48" t="s">
         <v>302</v>
       </c>
@@ -10123,16 +10375,16 @@
     </row>
     <row r="143" spans="1:14" ht="25.2">
       <c r="A143" s="11"/>
-      <c r="B143" s="115"/>
+      <c r="B143" s="124"/>
       <c r="C143" s="78" t="str">
         <f>master!C121</f>
         <v>テストを実施しなかった場合…</v>
       </c>
-      <c r="D143" s="106" t="s">
+      <c r="D143" s="105" t="s">
         <v>231</v>
       </c>
-      <c r="E143" s="107"/>
-      <c r="F143" s="108"/>
+      <c r="E143" s="106"/>
+      <c r="F143" s="107"/>
       <c r="G143" s="48" t="s">
         <v>301</v>
       </c>
@@ -10150,16 +10402,16 @@
     </row>
     <row r="144" spans="1:14" ht="100.8">
       <c r="A144" s="11"/>
-      <c r="B144" s="105"/>
+      <c r="B144" s="125"/>
       <c r="C144" s="78" t="str">
         <f>master!C122</f>
         <v>コラム：テストとデバッグ</v>
       </c>
-      <c r="D144" s="106" t="s">
+      <c r="D144" s="105" t="s">
         <v>232</v>
       </c>
-      <c r="E144" s="107"/>
-      <c r="F144" s="108"/>
+      <c r="E144" s="106"/>
+      <c r="F144" s="107"/>
       <c r="G144" s="48" t="s">
         <v>303</v>
       </c>
@@ -10177,7 +10429,7 @@
     </row>
     <row r="145" spans="1:14" ht="50.4">
       <c r="A145" s="11"/>
-      <c r="B145" s="104" t="str">
+      <c r="B145" s="123" t="str">
         <f>master!B123</f>
         <v>単体テストとは</v>
       </c>
@@ -10185,11 +10437,11 @@
         <f>master!C123</f>
         <v>単体テスト（Unit Test）とは</v>
       </c>
-      <c r="D145" s="106" t="s">
+      <c r="D145" s="105" t="s">
         <v>233</v>
       </c>
-      <c r="E145" s="107"/>
-      <c r="F145" s="108"/>
+      <c r="E145" s="106"/>
+      <c r="F145" s="107"/>
       <c r="G145" s="48" t="s">
         <v>300</v>
       </c>
@@ -10207,14 +10459,14 @@
     </row>
     <row r="146" spans="1:14" ht="25.2">
       <c r="A146" s="11"/>
-      <c r="B146" s="115"/>
+      <c r="B146" s="124"/>
       <c r="C146" s="78" t="str">
         <f>master!C124</f>
         <v xml:space="preserve">V字モデル　– 製造/単体テスト –　※再掲 </v>
       </c>
-      <c r="D146" s="106"/>
-      <c r="E146" s="107"/>
-      <c r="F146" s="108"/>
+      <c r="D146" s="105"/>
+      <c r="E146" s="106"/>
+      <c r="F146" s="107"/>
       <c r="G146" s="48" t="s">
         <v>301</v>
       </c>
@@ -10232,16 +10484,16 @@
     </row>
     <row r="147" spans="1:14" ht="302.39999999999998">
       <c r="A147" s="11"/>
-      <c r="B147" s="115"/>
+      <c r="B147" s="124"/>
       <c r="C147" s="78" t="str">
         <f>master!C125</f>
         <v>テスト設計の流れ</v>
       </c>
-      <c r="D147" s="106" t="s">
+      <c r="D147" s="105" t="s">
         <v>234</v>
       </c>
-      <c r="E147" s="107"/>
-      <c r="F147" s="108"/>
+      <c r="E147" s="106"/>
+      <c r="F147" s="107"/>
       <c r="G147" s="48" t="s">
         <v>304</v>
       </c>
@@ -10259,16 +10511,16 @@
     </row>
     <row r="148" spans="1:14" ht="37.799999999999997">
       <c r="A148" s="11"/>
-      <c r="B148" s="115"/>
+      <c r="B148" s="124"/>
       <c r="C148" s="78" t="str">
         <f>master!C126</f>
         <v>テスト設計の例</v>
       </c>
-      <c r="D148" s="106" t="s">
+      <c r="D148" s="105" t="s">
         <v>235</v>
       </c>
-      <c r="E148" s="107"/>
-      <c r="F148" s="108"/>
+      <c r="E148" s="106"/>
+      <c r="F148" s="107"/>
       <c r="G148" s="48" t="s">
         <v>305</v>
       </c>
@@ -10286,16 +10538,16 @@
     </row>
     <row r="149" spans="1:14" ht="75.599999999999994">
       <c r="A149" s="11"/>
-      <c r="B149" s="115"/>
+      <c r="B149" s="124"/>
       <c r="C149" s="78" t="str">
         <f>master!C127</f>
         <v>単体テスト（Unit Test）とは</v>
       </c>
-      <c r="D149" s="106" t="s">
+      <c r="D149" s="105" t="s">
         <v>236</v>
       </c>
-      <c r="E149" s="107"/>
-      <c r="F149" s="108"/>
+      <c r="E149" s="106"/>
+      <c r="F149" s="107"/>
       <c r="G149" s="48" t="s">
         <v>306</v>
       </c>
@@ -10313,16 +10565,16 @@
     </row>
     <row r="150" spans="1:14" ht="113.4">
       <c r="A150" s="11"/>
-      <c r="B150" s="115"/>
+      <c r="B150" s="124"/>
       <c r="C150" s="78" t="str">
         <f>master!C128</f>
         <v>テスト技法 – ブラックボックステスト技法 –</v>
       </c>
-      <c r="D150" s="106" t="s">
+      <c r="D150" s="105" t="s">
         <v>237</v>
       </c>
-      <c r="E150" s="107"/>
-      <c r="F150" s="108"/>
+      <c r="E150" s="106"/>
+      <c r="F150" s="107"/>
       <c r="G150" s="48" t="s">
         <v>307</v>
       </c>
@@ -10340,16 +10592,16 @@
     </row>
     <row r="151" spans="1:14" ht="201.6">
       <c r="A151" s="11"/>
-      <c r="B151" s="115"/>
+      <c r="B151" s="124"/>
       <c r="C151" s="78" t="str">
         <f>master!C129</f>
         <v>ブラックボックステスト：同値分割法</v>
       </c>
-      <c r="D151" s="106" t="s">
+      <c r="D151" s="105" t="s">
         <v>240</v>
       </c>
-      <c r="E151" s="107"/>
-      <c r="F151" s="108"/>
+      <c r="E151" s="106"/>
+      <c r="F151" s="107"/>
       <c r="G151" s="48" t="s">
         <v>308</v>
       </c>
@@ -10367,16 +10619,16 @@
     </row>
     <row r="152" spans="1:14" ht="113.4">
       <c r="A152" s="11"/>
-      <c r="B152" s="115"/>
+      <c r="B152" s="124"/>
       <c r="C152" s="78" t="str">
         <f>master!C130</f>
         <v>ブラックボックステスト：境界値分析</v>
       </c>
-      <c r="D152" s="106" t="s">
+      <c r="D152" s="105" t="s">
         <v>239</v>
       </c>
-      <c r="E152" s="107"/>
-      <c r="F152" s="108"/>
+      <c r="E152" s="106"/>
+      <c r="F152" s="107"/>
       <c r="G152" s="48" t="s">
         <v>307</v>
       </c>
@@ -10394,16 +10646,16 @@
     </row>
     <row r="153" spans="1:14" ht="176.4">
       <c r="A153" s="11"/>
-      <c r="B153" s="115"/>
+      <c r="B153" s="124"/>
       <c r="C153" s="78" t="str">
         <f>master!C131</f>
         <v>ブラックボックステスト：ディシジョンテーブルテスト</v>
       </c>
-      <c r="D153" s="106" t="s">
+      <c r="D153" s="105" t="s">
         <v>238</v>
       </c>
-      <c r="E153" s="107"/>
-      <c r="F153" s="108"/>
+      <c r="E153" s="106"/>
+      <c r="F153" s="107"/>
       <c r="G153" s="48" t="s">
         <v>309</v>
       </c>
@@ -10421,16 +10673,16 @@
     </row>
     <row r="154" spans="1:14" ht="37.799999999999997">
       <c r="A154" s="11"/>
-      <c r="B154" s="115"/>
+      <c r="B154" s="124"/>
       <c r="C154" s="78" t="str">
         <f>master!C132</f>
         <v>ブラックボックステスト：状態遷移テスト</v>
       </c>
-      <c r="D154" s="106" t="s">
+      <c r="D154" s="105" t="s">
         <v>241</v>
       </c>
-      <c r="E154" s="107"/>
-      <c r="F154" s="108"/>
+      <c r="E154" s="106"/>
+      <c r="F154" s="107"/>
       <c r="G154" s="48" t="s">
         <v>305</v>
       </c>
@@ -10448,16 +10700,16 @@
     </row>
     <row r="155" spans="1:14" ht="88.2">
       <c r="A155" s="11"/>
-      <c r="B155" s="115"/>
+      <c r="B155" s="124"/>
       <c r="C155" s="78" t="str">
         <f>master!C133</f>
         <v>テスト技法 – ホワイトボックステスト技法 –</v>
       </c>
-      <c r="D155" s="106" t="s">
+      <c r="D155" s="105" t="s">
         <v>242</v>
       </c>
-      <c r="E155" s="107"/>
-      <c r="F155" s="108"/>
+      <c r="E155" s="106"/>
+      <c r="F155" s="107"/>
       <c r="G155" s="48" t="s">
         <v>310</v>
       </c>
@@ -10475,16 +10727,16 @@
     </row>
     <row r="156" spans="1:14" ht="151.19999999999999">
       <c r="A156" s="11"/>
-      <c r="B156" s="115"/>
+      <c r="B156" s="124"/>
       <c r="C156" s="78" t="str">
         <f>master!C134</f>
         <v>ホワイトボックステストの評価基準</v>
       </c>
-      <c r="D156" s="106" t="s">
+      <c r="D156" s="105" t="s">
         <v>243</v>
       </c>
-      <c r="E156" s="107"/>
-      <c r="F156" s="108"/>
+      <c r="E156" s="106"/>
+      <c r="F156" s="107"/>
       <c r="G156" s="48" t="s">
         <v>311</v>
       </c>
@@ -10502,16 +10754,16 @@
     </row>
     <row r="157" spans="1:14" ht="37.799999999999997">
       <c r="A157" s="11"/>
-      <c r="B157" s="115"/>
+      <c r="B157" s="124"/>
       <c r="C157" s="78" t="str">
         <f>master!C135</f>
         <v>ホワイトボックステスト：ステートメントテスト</v>
       </c>
-      <c r="D157" s="106" t="s">
+      <c r="D157" s="105" t="s">
         <v>244</v>
       </c>
-      <c r="E157" s="107"/>
-      <c r="F157" s="108"/>
+      <c r="E157" s="106"/>
+      <c r="F157" s="107"/>
       <c r="G157" s="48" t="s">
         <v>305</v>
       </c>
@@ -10529,16 +10781,16 @@
     </row>
     <row r="158" spans="1:14" ht="37.799999999999997">
       <c r="A158" s="11"/>
-      <c r="B158" s="115"/>
+      <c r="B158" s="124"/>
       <c r="C158" s="78" t="str">
         <f>master!C136</f>
         <v>ホワイトボックステスト：ブランチテスト</v>
       </c>
-      <c r="D158" s="106" t="s">
+      <c r="D158" s="105" t="s">
         <v>245</v>
       </c>
-      <c r="E158" s="107"/>
-      <c r="F158" s="108"/>
+      <c r="E158" s="106"/>
+      <c r="F158" s="107"/>
       <c r="G158" s="48" t="s">
         <v>305</v>
       </c>
@@ -10556,16 +10808,16 @@
     </row>
     <row r="159" spans="1:14" ht="37.799999999999997">
       <c r="A159" s="11"/>
-      <c r="B159" s="115"/>
+      <c r="B159" s="124"/>
       <c r="C159" s="78" t="str">
         <f>master!C137</f>
         <v>ホワイトボックステスト：コンディションテスト</v>
       </c>
-      <c r="D159" s="106" t="s">
+      <c r="D159" s="105" t="s">
         <v>246</v>
       </c>
-      <c r="E159" s="107"/>
-      <c r="F159" s="108"/>
+      <c r="E159" s="106"/>
+      <c r="F159" s="107"/>
       <c r="G159" s="48" t="s">
         <v>305</v>
       </c>
@@ -10583,16 +10835,16 @@
     </row>
     <row r="160" spans="1:14" ht="37.799999999999997">
       <c r="A160" s="11"/>
-      <c r="B160" s="115"/>
+      <c r="B160" s="124"/>
       <c r="C160" s="78" t="str">
         <f>master!C138</f>
         <v>テスト技法 – 経験ベースの技法 –</v>
       </c>
-      <c r="D160" s="106" t="s">
+      <c r="D160" s="105" t="s">
         <v>247</v>
       </c>
-      <c r="E160" s="107"/>
-      <c r="F160" s="108"/>
+      <c r="E160" s="106"/>
+      <c r="F160" s="107"/>
       <c r="G160" s="48" t="s">
         <v>305</v>
       </c>
@@ -10610,16 +10862,16 @@
     </row>
     <row r="161" spans="1:14" ht="100.8">
       <c r="A161" s="11"/>
-      <c r="B161" s="115"/>
+      <c r="B161" s="124"/>
       <c r="C161" s="78" t="str">
         <f>master!C139</f>
         <v>スタブとドライバ</v>
       </c>
-      <c r="D161" s="106" t="s">
+      <c r="D161" s="105" t="s">
         <v>248</v>
       </c>
-      <c r="E161" s="107"/>
-      <c r="F161" s="108"/>
+      <c r="E161" s="106"/>
+      <c r="F161" s="107"/>
       <c r="G161" s="48" t="s">
         <v>303</v>
       </c>
@@ -10637,16 +10889,16 @@
     </row>
     <row r="162" spans="1:14" ht="75.599999999999994">
       <c r="A162" s="11"/>
-      <c r="B162" s="105"/>
+      <c r="B162" s="125"/>
       <c r="C162" s="78" t="str">
         <f>master!C140</f>
         <v>スタブとモック</v>
       </c>
-      <c r="D162" s="106" t="s">
+      <c r="D162" s="105" t="s">
         <v>249</v>
       </c>
-      <c r="E162" s="107"/>
-      <c r="F162" s="108"/>
+      <c r="E162" s="106"/>
+      <c r="F162" s="107"/>
       <c r="G162" s="48" t="s">
         <v>306</v>
       </c>
@@ -10664,7 +10916,7 @@
     </row>
     <row r="163" spans="1:14" ht="37.799999999999997">
       <c r="A163" s="11"/>
-      <c r="B163" s="104" t="str">
+      <c r="B163" s="123" t="str">
         <f>master!B141</f>
         <v>JUnit</v>
       </c>
@@ -10672,11 +10924,11 @@
         <f>master!C141</f>
         <v>JUnitとは</v>
       </c>
-      <c r="D163" s="106" t="s">
+      <c r="D163" s="105" t="s">
         <v>250</v>
       </c>
-      <c r="E163" s="107"/>
-      <c r="F163" s="108"/>
+      <c r="E163" s="106"/>
+      <c r="F163" s="107"/>
       <c r="G163" s="48" t="s">
         <v>305</v>
       </c>
@@ -10694,14 +10946,14 @@
     </row>
     <row r="164" spans="1:14" ht="25.2">
       <c r="A164" s="11"/>
-      <c r="B164" s="105"/>
+      <c r="B164" s="125"/>
       <c r="C164" s="78" t="str">
         <f>master!C142</f>
         <v>参考文献</v>
       </c>
-      <c r="D164" s="106"/>
-      <c r="E164" s="107"/>
-      <c r="F164" s="108"/>
+      <c r="D164" s="105"/>
+      <c r="E164" s="106"/>
+      <c r="F164" s="107"/>
       <c r="G164" s="48" t="s">
         <v>301</v>
       </c>
@@ -10727,11 +10979,11 @@
         <f>master!C67</f>
         <v>ここから各自で演習を始めましょう。</v>
       </c>
-      <c r="D165" s="109" t="s">
+      <c r="D165" s="111" t="s">
         <v>251</v>
       </c>
-      <c r="E165" s="110"/>
-      <c r="F165" s="111"/>
+      <c r="E165" s="112"/>
+      <c r="F165" s="113"/>
       <c r="G165" s="58" t="s">
         <v>42</v>
       </c>
@@ -10749,7 +11001,7 @@
     </row>
     <row r="166" spans="1:14" ht="25.2">
       <c r="A166" s="11"/>
-      <c r="B166" s="112" t="str">
+      <c r="B166" s="117" t="str">
         <f>master!B144</f>
         <v>課題2の導入</v>
       </c>
@@ -10757,11 +11009,11 @@
         <f>master!C144</f>
         <v>演習課題の概要</v>
       </c>
-      <c r="D166" s="109" t="s">
+      <c r="D166" s="111" t="s">
         <v>267</v>
       </c>
-      <c r="E166" s="110"/>
-      <c r="F166" s="111"/>
+      <c r="E166" s="112"/>
+      <c r="F166" s="113"/>
       <c r="G166" s="58" t="s">
         <v>312</v>
       </c>
@@ -10779,16 +11031,16 @@
     </row>
     <row r="167" spans="1:14" ht="138.6">
       <c r="A167" s="11"/>
-      <c r="B167" s="113"/>
+      <c r="B167" s="119"/>
       <c r="C167" s="58" t="str">
         <f>master!C145</f>
         <v>[構造理解] Webアプリケーションで必要なもの  ※再掲</v>
       </c>
-      <c r="D167" s="109" t="s">
+      <c r="D167" s="111" t="s">
         <v>268</v>
       </c>
-      <c r="E167" s="110"/>
-      <c r="F167" s="111"/>
+      <c r="E167" s="112"/>
+      <c r="F167" s="113"/>
       <c r="G167" s="58" t="s">
         <v>313</v>
       </c>
@@ -10806,16 +11058,16 @@
     </row>
     <row r="168" spans="1:14" ht="50.4">
       <c r="A168" s="11"/>
-      <c r="B168" s="113"/>
+      <c r="B168" s="119"/>
       <c r="C168" s="58" t="str">
         <f>master!C146</f>
         <v>テストクラスを作成する単位</v>
       </c>
-      <c r="D168" s="109" t="s">
+      <c r="D168" s="111" t="s">
         <v>269</v>
       </c>
-      <c r="E168" s="110"/>
-      <c r="F168" s="111"/>
+      <c r="E168" s="112"/>
+      <c r="F168" s="113"/>
       <c r="G168" s="58" t="s">
         <v>314</v>
       </c>
@@ -10833,16 +11085,16 @@
     </row>
     <row r="169" spans="1:14" ht="113.4">
       <c r="A169" s="11"/>
-      <c r="B169" s="114"/>
+      <c r="B169" s="118"/>
       <c r="C169" s="58" t="str">
         <f>master!C147</f>
         <v>JUnitで単体テスト</v>
       </c>
-      <c r="D169" s="109" t="s">
+      <c r="D169" s="111" t="s">
         <v>270</v>
       </c>
-      <c r="E169" s="110"/>
-      <c r="F169" s="111"/>
+      <c r="E169" s="112"/>
+      <c r="F169" s="113"/>
       <c r="G169" s="58" t="s">
         <v>315</v>
       </c>
@@ -10860,7 +11112,7 @@
     </row>
     <row r="170" spans="1:14" ht="25.2">
       <c r="A170" s="11"/>
-      <c r="B170" s="112" t="str">
+      <c r="B170" s="117" t="str">
         <f>master!B148</f>
         <v>ハンズオン</v>
       </c>
@@ -10868,11 +11120,11 @@
         <f>master!C148</f>
         <v>バイブコーディングで単体テスト – はじめに</v>
       </c>
-      <c r="D170" s="109" t="s">
+      <c r="D170" s="111" t="s">
         <v>271</v>
       </c>
-      <c r="E170" s="110"/>
-      <c r="F170" s="111"/>
+      <c r="E170" s="112"/>
+      <c r="F170" s="113"/>
       <c r="G170" s="58" t="s">
         <v>312</v>
       </c>
@@ -10890,16 +11142,16 @@
     </row>
     <row r="171" spans="1:14" ht="50.4">
       <c r="A171" s="11"/>
-      <c r="B171" s="113"/>
+      <c r="B171" s="119"/>
       <c r="C171" s="58" t="str">
         <f>master!C149</f>
         <v>バイブコーディング単体テスト①テスト項目表を作る</v>
       </c>
-      <c r="D171" s="109" t="s">
+      <c r="D171" s="111" t="s">
         <v>272</v>
       </c>
-      <c r="E171" s="110"/>
-      <c r="F171" s="111"/>
+      <c r="E171" s="112"/>
+      <c r="F171" s="113"/>
       <c r="G171" s="58" t="s">
         <v>314</v>
       </c>
@@ -10917,13 +11169,13 @@
     </row>
     <row r="172" spans="1:14" ht="88.2">
       <c r="A172" s="11"/>
-      <c r="B172" s="113"/>
+      <c r="B172" s="119"/>
       <c r="C172" s="58"/>
-      <c r="D172" s="109" t="s">
+      <c r="D172" s="111" t="s">
         <v>183</v>
       </c>
-      <c r="E172" s="110"/>
-      <c r="F172" s="111"/>
+      <c r="E172" s="112"/>
+      <c r="F172" s="113"/>
       <c r="G172" s="58" t="s">
         <v>316</v>
       </c>
@@ -10941,16 +11193,16 @@
     </row>
     <row r="173" spans="1:14" ht="50.4">
       <c r="A173" s="11"/>
-      <c r="B173" s="113"/>
+      <c r="B173" s="119"/>
       <c r="C173" s="76" t="str">
         <f>master!C150</f>
         <v>バイブコーディング単体テスト②Repositoryのテストを作る</v>
       </c>
-      <c r="D173" s="109" t="s">
+      <c r="D173" s="111" t="s">
         <v>273</v>
       </c>
-      <c r="E173" s="110"/>
-      <c r="F173" s="111"/>
+      <c r="E173" s="112"/>
+      <c r="F173" s="113"/>
       <c r="G173" s="58" t="s">
         <v>314</v>
       </c>
@@ -10968,13 +11220,13 @@
     </row>
     <row r="174" spans="1:14" ht="88.2">
       <c r="A174" s="11"/>
-      <c r="B174" s="113"/>
+      <c r="B174" s="119"/>
       <c r="C174" s="77"/>
-      <c r="D174" s="109" t="s">
+      <c r="D174" s="111" t="s">
         <v>183</v>
       </c>
-      <c r="E174" s="110"/>
-      <c r="F174" s="111"/>
+      <c r="E174" s="112"/>
+      <c r="F174" s="113"/>
       <c r="G174" s="58" t="s">
         <v>316</v>
       </c>
@@ -10992,16 +11244,16 @@
     </row>
     <row r="175" spans="1:14" ht="138.6">
       <c r="A175" s="11"/>
-      <c r="B175" s="113"/>
+      <c r="B175" s="119"/>
       <c r="C175" s="58" t="str">
         <f>master!C151</f>
         <v>[解説] Repositoryのテストクラス（抜粋）</v>
       </c>
-      <c r="D175" s="109" t="s">
+      <c r="D175" s="111" t="s">
         <v>275</v>
       </c>
-      <c r="E175" s="110"/>
-      <c r="F175" s="111"/>
+      <c r="E175" s="112"/>
+      <c r="F175" s="113"/>
       <c r="G175" s="58" t="s">
         <v>313</v>
       </c>
@@ -11019,16 +11271,16 @@
     </row>
     <row r="176" spans="1:14" ht="50.4">
       <c r="A176" s="11"/>
-      <c r="B176" s="113"/>
+      <c r="B176" s="119"/>
       <c r="C176" s="76" t="str">
         <f>master!C152</f>
         <v>バイブコーディング単体テスト③Serviceのテストを作る</v>
       </c>
-      <c r="D176" s="109" t="s">
+      <c r="D176" s="111" t="s">
         <v>273</v>
       </c>
-      <c r="E176" s="110"/>
-      <c r="F176" s="111"/>
+      <c r="E176" s="112"/>
+      <c r="F176" s="113"/>
       <c r="G176" s="58" t="s">
         <v>314</v>
       </c>
@@ -11046,13 +11298,13 @@
     </row>
     <row r="177" spans="1:14" ht="88.2">
       <c r="A177" s="11"/>
-      <c r="B177" s="113"/>
+      <c r="B177" s="119"/>
       <c r="C177" s="77"/>
-      <c r="D177" s="109" t="s">
+      <c r="D177" s="111" t="s">
         <v>183</v>
       </c>
-      <c r="E177" s="110"/>
-      <c r="F177" s="111"/>
+      <c r="E177" s="112"/>
+      <c r="F177" s="113"/>
       <c r="G177" s="58" t="s">
         <v>316</v>
       </c>
@@ -11070,16 +11322,16 @@
     </row>
     <row r="178" spans="1:14" ht="138.6">
       <c r="A178" s="11"/>
-      <c r="B178" s="113"/>
+      <c r="B178" s="119"/>
       <c r="C178" s="58" t="str">
         <f>master!C153</f>
         <v>[解説] Serviceのテストクラス（抜粋）</v>
       </c>
-      <c r="D178" s="109" t="s">
+      <c r="D178" s="111" t="s">
         <v>274</v>
       </c>
-      <c r="E178" s="110"/>
-      <c r="F178" s="111"/>
+      <c r="E178" s="112"/>
+      <c r="F178" s="113"/>
       <c r="G178" s="58" t="s">
         <v>313</v>
       </c>
@@ -11097,16 +11349,16 @@
     </row>
     <row r="179" spans="1:14" ht="50.4">
       <c r="A179" s="11"/>
-      <c r="B179" s="113"/>
+      <c r="B179" s="119"/>
       <c r="C179" s="76" t="str">
         <f>master!C154</f>
         <v>バイブコーディング単体テスト④Controllerのテストを作る</v>
       </c>
-      <c r="D179" s="109" t="s">
+      <c r="D179" s="111" t="s">
         <v>273</v>
       </c>
-      <c r="E179" s="110"/>
-      <c r="F179" s="111"/>
+      <c r="E179" s="112"/>
+      <c r="F179" s="113"/>
       <c r="G179" s="58" t="s">
         <v>314</v>
       </c>
@@ -11124,13 +11376,13 @@
     </row>
     <row r="180" spans="1:14" ht="88.2">
       <c r="A180" s="11"/>
-      <c r="B180" s="113"/>
+      <c r="B180" s="119"/>
       <c r="C180" s="77"/>
-      <c r="D180" s="109" t="s">
+      <c r="D180" s="111" t="s">
         <v>183</v>
       </c>
-      <c r="E180" s="110"/>
-      <c r="F180" s="111"/>
+      <c r="E180" s="112"/>
+      <c r="F180" s="113"/>
       <c r="G180" s="58" t="s">
         <v>316</v>
       </c>
@@ -11148,16 +11400,16 @@
     </row>
     <row r="181" spans="1:14" ht="163.80000000000001">
       <c r="A181" s="11"/>
-      <c r="B181" s="114"/>
+      <c r="B181" s="118"/>
       <c r="C181" s="58" t="str">
         <f>master!C155</f>
         <v>[解説] Controllerのテストクラス（抜粋）</v>
       </c>
-      <c r="D181" s="109" t="s">
+      <c r="D181" s="111" t="s">
         <v>276</v>
       </c>
-      <c r="E181" s="110"/>
-      <c r="F181" s="111"/>
+      <c r="E181" s="112"/>
+      <c r="F181" s="113"/>
       <c r="G181" s="58" t="s">
         <v>317</v>
       </c>
@@ -11175,7 +11427,7 @@
     </row>
     <row r="182" spans="1:14" ht="165" customHeight="1">
       <c r="A182" s="11"/>
-      <c r="B182" s="112" t="str">
+      <c r="B182" s="117" t="str">
         <f>master!B156</f>
         <v>課題2の実施</v>
       </c>
@@ -11183,11 +11435,11 @@
         <f>master!C156</f>
         <v>ここから各自で演習を始めましょう。</v>
       </c>
-      <c r="D182" s="109" t="s">
+      <c r="D182" s="111" t="s">
         <v>277</v>
       </c>
-      <c r="E182" s="110"/>
-      <c r="F182" s="111"/>
+      <c r="E182" s="112"/>
+      <c r="F182" s="113"/>
       <c r="G182" s="58" t="s">
         <v>317</v>
       </c>
@@ -11205,16 +11457,16 @@
     </row>
     <row r="183" spans="1:14" ht="151.19999999999999">
       <c r="A183" s="11"/>
-      <c r="B183" s="114"/>
+      <c r="B183" s="118"/>
       <c r="C183" s="58" t="str">
         <f>master!C157</f>
         <v>[終了条件] 講師配布のテストプログラム(JUnit)が成功すること</v>
       </c>
-      <c r="D183" s="109" t="s">
+      <c r="D183" s="111" t="s">
         <v>347</v>
       </c>
-      <c r="E183" s="110"/>
-      <c r="F183" s="111"/>
+      <c r="E183" s="112"/>
+      <c r="F183" s="113"/>
       <c r="G183" s="58" t="s">
         <v>346</v>
       </c>
@@ -11232,7 +11484,7 @@
     </row>
     <row r="184" spans="1:14" ht="163.80000000000001">
       <c r="A184" s="11"/>
-      <c r="B184" s="112" t="str">
+      <c r="B184" s="117" t="str">
         <f>master!B159</f>
         <v>追加課題</v>
       </c>
@@ -11240,11 +11492,11 @@
         <f>master!C159</f>
         <v>演習課題の概要</v>
       </c>
-      <c r="D184" s="109" t="s">
+      <c r="D184" s="111" t="s">
         <v>279</v>
       </c>
-      <c r="E184" s="110"/>
-      <c r="F184" s="111"/>
+      <c r="E184" s="112"/>
+      <c r="F184" s="113"/>
       <c r="G184" s="58" t="s">
         <v>340</v>
       </c>
@@ -11262,16 +11514,16 @@
     </row>
     <row r="185" spans="1:14" ht="25.2">
       <c r="A185" s="11"/>
-      <c r="B185" s="113"/>
+      <c r="B185" s="119"/>
       <c r="C185" s="58" t="str">
         <f>master!C160</f>
         <v>追加課題①：送料の表示機能</v>
       </c>
-      <c r="D185" s="109" t="s">
+      <c r="D185" s="111" t="s">
         <v>281</v>
       </c>
-      <c r="E185" s="110"/>
-      <c r="F185" s="111"/>
+      <c r="E185" s="112"/>
+      <c r="F185" s="113"/>
       <c r="G185" s="58" t="s">
         <v>341</v>
       </c>
@@ -11289,16 +11541,16 @@
     </row>
     <row r="186" spans="1:14" ht="25.2">
       <c r="A186" s="11"/>
-      <c r="B186" s="113"/>
+      <c r="B186" s="119"/>
       <c r="C186" s="58" t="str">
         <f>master!C161</f>
         <v>追加課題②：クーポン機能</v>
       </c>
-      <c r="D186" s="109" t="s">
+      <c r="D186" s="111" t="s">
         <v>281</v>
       </c>
-      <c r="E186" s="110"/>
-      <c r="F186" s="111"/>
+      <c r="E186" s="112"/>
+      <c r="F186" s="113"/>
       <c r="G186" s="58" t="s">
         <v>341</v>
       </c>
@@ -11316,16 +11568,16 @@
     </row>
     <row r="187" spans="1:14" ht="25.2">
       <c r="A187" s="11"/>
-      <c r="B187" s="114"/>
+      <c r="B187" s="118"/>
       <c r="C187" s="58" t="str">
         <f>master!C162</f>
         <v>追加課題③：ユーザーアカウント機能</v>
       </c>
-      <c r="D187" s="109" t="s">
+      <c r="D187" s="111" t="s">
         <v>281</v>
       </c>
-      <c r="E187" s="110"/>
-      <c r="F187" s="111"/>
+      <c r="E187" s="112"/>
+      <c r="F187" s="113"/>
       <c r="G187" s="58" t="s">
         <v>341</v>
       </c>
@@ -11343,7 +11595,7 @@
     </row>
     <row r="188" spans="1:14" ht="176.4">
       <c r="A188" s="11"/>
-      <c r="B188" s="112" t="str">
+      <c r="B188" s="117" t="str">
         <f>master!B164</f>
         <v>課題の振り返り</v>
       </c>
@@ -11351,11 +11603,11 @@
         <f>master!C164</f>
         <v>サンプルのAPとの自分のAPとの比較</v>
       </c>
-      <c r="D188" s="109" t="s">
+      <c r="D188" s="111" t="s">
         <v>343</v>
       </c>
-      <c r="E188" s="110"/>
-      <c r="F188" s="111"/>
+      <c r="E188" s="112"/>
+      <c r="F188" s="113"/>
       <c r="G188" s="58" t="s">
         <v>344</v>
       </c>
@@ -11373,16 +11625,16 @@
     </row>
     <row r="189" spans="1:14" ht="63">
       <c r="A189" s="11"/>
-      <c r="B189" s="114"/>
+      <c r="B189" s="118"/>
       <c r="C189" s="58" t="str">
         <f>master!C165</f>
         <v>レポートの作成</v>
       </c>
-      <c r="D189" s="109" t="s">
+      <c r="D189" s="111" t="s">
         <v>345</v>
       </c>
-      <c r="E189" s="110"/>
-      <c r="F189" s="111"/>
+      <c r="E189" s="112"/>
+      <c r="F189" s="113"/>
       <c r="G189" s="58" t="s">
         <v>342</v>
       </c>
@@ -11404,6 +11656,185 @@
     <row r="191" spans="1:14" ht="15" customHeight="1"/>
   </sheetData>
   <mergeCells count="203">
+    <mergeCell ref="D153:F153"/>
+    <mergeCell ref="B138:B140"/>
+    <mergeCell ref="B163:B164"/>
+    <mergeCell ref="D165:F165"/>
+    <mergeCell ref="D188:F188"/>
+    <mergeCell ref="D185:F185"/>
+    <mergeCell ref="D184:F184"/>
+    <mergeCell ref="D166:F166"/>
+    <mergeCell ref="D167:F167"/>
+    <mergeCell ref="D168:F168"/>
+    <mergeCell ref="D181:F181"/>
+    <mergeCell ref="D182:F182"/>
+    <mergeCell ref="D169:F169"/>
+    <mergeCell ref="D170:F170"/>
+    <mergeCell ref="D178:F178"/>
+    <mergeCell ref="D172:F172"/>
+    <mergeCell ref="D174:F174"/>
+    <mergeCell ref="D175:F175"/>
+    <mergeCell ref="B170:B181"/>
+    <mergeCell ref="B166:B169"/>
+    <mergeCell ref="B141:B144"/>
+    <mergeCell ref="B145:B162"/>
+    <mergeCell ref="D140:F140"/>
+    <mergeCell ref="D141:F141"/>
+    <mergeCell ref="D142:F142"/>
+    <mergeCell ref="D143:F143"/>
+    <mergeCell ref="D145:F145"/>
+    <mergeCell ref="D146:F146"/>
+    <mergeCell ref="D147:F147"/>
+    <mergeCell ref="D148:F148"/>
+    <mergeCell ref="D149:F149"/>
+    <mergeCell ref="D161:F161"/>
+    <mergeCell ref="D162:F162"/>
+    <mergeCell ref="D144:F144"/>
+    <mergeCell ref="D156:F156"/>
+    <mergeCell ref="D157:F157"/>
+    <mergeCell ref="D158:F158"/>
+    <mergeCell ref="D159:F159"/>
+    <mergeCell ref="D160:F160"/>
+    <mergeCell ref="D155:F155"/>
+    <mergeCell ref="D154:F154"/>
+    <mergeCell ref="D150:F150"/>
+    <mergeCell ref="D151:F151"/>
+    <mergeCell ref="D152:F152"/>
+    <mergeCell ref="D139:F139"/>
+    <mergeCell ref="D138:F138"/>
+    <mergeCell ref="D112:F112"/>
+    <mergeCell ref="D111:F111"/>
+    <mergeCell ref="D110:F110"/>
+    <mergeCell ref="D113:F113"/>
+    <mergeCell ref="D104:F104"/>
+    <mergeCell ref="D100:F100"/>
+    <mergeCell ref="D124:F124"/>
+    <mergeCell ref="D137:F137"/>
+    <mergeCell ref="D102:F102"/>
+    <mergeCell ref="D103:F103"/>
+    <mergeCell ref="D105:F105"/>
+    <mergeCell ref="D106:F106"/>
+    <mergeCell ref="D107:F107"/>
+    <mergeCell ref="D108:F108"/>
+    <mergeCell ref="D79:F79"/>
+    <mergeCell ref="D81:F81"/>
+    <mergeCell ref="D75:F75"/>
+    <mergeCell ref="D86:F86"/>
+    <mergeCell ref="D91:F91"/>
+    <mergeCell ref="D83:F83"/>
+    <mergeCell ref="D84:F84"/>
+    <mergeCell ref="B72:B91"/>
+    <mergeCell ref="D85:F85"/>
+    <mergeCell ref="D87:F87"/>
+    <mergeCell ref="D88:F88"/>
+    <mergeCell ref="D89:F89"/>
+    <mergeCell ref="D90:F90"/>
+    <mergeCell ref="D78:F78"/>
+    <mergeCell ref="D80:F80"/>
+    <mergeCell ref="D82:F82"/>
+    <mergeCell ref="D76:F76"/>
+    <mergeCell ref="D74:F74"/>
+    <mergeCell ref="B56:B58"/>
+    <mergeCell ref="D70:F70"/>
+    <mergeCell ref="D71:F71"/>
+    <mergeCell ref="D72:F72"/>
+    <mergeCell ref="D73:F73"/>
+    <mergeCell ref="D63:F63"/>
+    <mergeCell ref="D57:F57"/>
+    <mergeCell ref="D58:F58"/>
+    <mergeCell ref="D59:F59"/>
+    <mergeCell ref="D60:F60"/>
+    <mergeCell ref="D67:F67"/>
+    <mergeCell ref="D68:F68"/>
+    <mergeCell ref="D61:F61"/>
+    <mergeCell ref="D62:F62"/>
+    <mergeCell ref="D64:F64"/>
+    <mergeCell ref="D65:F65"/>
+    <mergeCell ref="D66:F66"/>
+    <mergeCell ref="D69:F69"/>
+    <mergeCell ref="D56:F56"/>
+    <mergeCell ref="B63:B71"/>
+    <mergeCell ref="B59:B62"/>
+    <mergeCell ref="B23:B28"/>
+    <mergeCell ref="B29:B36"/>
+    <mergeCell ref="B37:B55"/>
+    <mergeCell ref="D50:F50"/>
+    <mergeCell ref="D51:F51"/>
+    <mergeCell ref="D52:F52"/>
+    <mergeCell ref="D53:F53"/>
+    <mergeCell ref="D54:F54"/>
+    <mergeCell ref="D38:F38"/>
+    <mergeCell ref="D39:F39"/>
+    <mergeCell ref="D40:F40"/>
+    <mergeCell ref="D41:F41"/>
+    <mergeCell ref="D42:F42"/>
+    <mergeCell ref="D43:F43"/>
+    <mergeCell ref="D44:F44"/>
+    <mergeCell ref="D45:F45"/>
+    <mergeCell ref="D46:F46"/>
+    <mergeCell ref="I20:J20"/>
+    <mergeCell ref="H20:H21"/>
+    <mergeCell ref="B4:E4"/>
+    <mergeCell ref="B5:K5"/>
+    <mergeCell ref="D20:F21"/>
+    <mergeCell ref="G20:G21"/>
+    <mergeCell ref="B20:B21"/>
+    <mergeCell ref="C20:C21"/>
+    <mergeCell ref="K20:K21"/>
+    <mergeCell ref="D7:E7"/>
+    <mergeCell ref="D163:F163"/>
+    <mergeCell ref="D164:F164"/>
+    <mergeCell ref="D22:F22"/>
+    <mergeCell ref="D36:F36"/>
+    <mergeCell ref="D23:F23"/>
+    <mergeCell ref="D29:F29"/>
+    <mergeCell ref="D24:F24"/>
+    <mergeCell ref="D26:F26"/>
+    <mergeCell ref="D28:F28"/>
+    <mergeCell ref="D35:F35"/>
+    <mergeCell ref="D25:F25"/>
+    <mergeCell ref="D27:F27"/>
+    <mergeCell ref="D30:F30"/>
+    <mergeCell ref="D31:F31"/>
+    <mergeCell ref="D32:F32"/>
+    <mergeCell ref="D33:F33"/>
+    <mergeCell ref="D34:F34"/>
+    <mergeCell ref="D47:F47"/>
+    <mergeCell ref="D48:F48"/>
+    <mergeCell ref="D49:F49"/>
+    <mergeCell ref="D55:F55"/>
+    <mergeCell ref="D37:F37"/>
+    <mergeCell ref="D92:F92"/>
+    <mergeCell ref="D77:F77"/>
+    <mergeCell ref="D187:F187"/>
+    <mergeCell ref="D186:F186"/>
+    <mergeCell ref="D189:F189"/>
+    <mergeCell ref="B188:B189"/>
+    <mergeCell ref="D171:F171"/>
+    <mergeCell ref="D173:F173"/>
+    <mergeCell ref="D176:F176"/>
+    <mergeCell ref="D177:F177"/>
+    <mergeCell ref="D179:F179"/>
+    <mergeCell ref="D180:F180"/>
+    <mergeCell ref="B184:B187"/>
+    <mergeCell ref="D183:F183"/>
+    <mergeCell ref="B182:B183"/>
+    <mergeCell ref="D121:F121"/>
+    <mergeCell ref="D120:F120"/>
+    <mergeCell ref="D119:F119"/>
+    <mergeCell ref="D118:F118"/>
+    <mergeCell ref="D117:F117"/>
+    <mergeCell ref="D116:F116"/>
+    <mergeCell ref="D115:F115"/>
+    <mergeCell ref="D114:F114"/>
+    <mergeCell ref="D93:F93"/>
+    <mergeCell ref="D94:F94"/>
+    <mergeCell ref="D95:F95"/>
+    <mergeCell ref="D96:F96"/>
+    <mergeCell ref="D97:F97"/>
+    <mergeCell ref="D98:F98"/>
+    <mergeCell ref="D99:F99"/>
+    <mergeCell ref="D101:F101"/>
     <mergeCell ref="D123:F123"/>
     <mergeCell ref="B120:B124"/>
     <mergeCell ref="B114:B119"/>
@@ -11428,185 +11859,6 @@
     <mergeCell ref="B125:B127"/>
     <mergeCell ref="D109:F109"/>
     <mergeCell ref="D122:F122"/>
-    <mergeCell ref="D121:F121"/>
-    <mergeCell ref="D120:F120"/>
-    <mergeCell ref="D119:F119"/>
-    <mergeCell ref="D118:F118"/>
-    <mergeCell ref="D117:F117"/>
-    <mergeCell ref="D116:F116"/>
-    <mergeCell ref="D115:F115"/>
-    <mergeCell ref="D114:F114"/>
-    <mergeCell ref="D93:F93"/>
-    <mergeCell ref="D94:F94"/>
-    <mergeCell ref="D95:F95"/>
-    <mergeCell ref="D96:F96"/>
-    <mergeCell ref="D97:F97"/>
-    <mergeCell ref="D98:F98"/>
-    <mergeCell ref="D99:F99"/>
-    <mergeCell ref="D101:F101"/>
-    <mergeCell ref="D187:F187"/>
-    <mergeCell ref="D186:F186"/>
-    <mergeCell ref="D189:F189"/>
-    <mergeCell ref="B188:B189"/>
-    <mergeCell ref="D171:F171"/>
-    <mergeCell ref="D173:F173"/>
-    <mergeCell ref="D176:F176"/>
-    <mergeCell ref="D177:F177"/>
-    <mergeCell ref="D179:F179"/>
-    <mergeCell ref="D180:F180"/>
-    <mergeCell ref="B184:B187"/>
-    <mergeCell ref="D183:F183"/>
-    <mergeCell ref="B182:B183"/>
-    <mergeCell ref="D163:F163"/>
-    <mergeCell ref="D164:F164"/>
-    <mergeCell ref="D22:F22"/>
-    <mergeCell ref="D36:F36"/>
-    <mergeCell ref="D23:F23"/>
-    <mergeCell ref="D29:F29"/>
-    <mergeCell ref="D24:F24"/>
-    <mergeCell ref="D26:F26"/>
-    <mergeCell ref="D28:F28"/>
-    <mergeCell ref="D35:F35"/>
-    <mergeCell ref="D25:F25"/>
-    <mergeCell ref="D27:F27"/>
-    <mergeCell ref="D30:F30"/>
-    <mergeCell ref="D31:F31"/>
-    <mergeCell ref="D32:F32"/>
-    <mergeCell ref="D33:F33"/>
-    <mergeCell ref="D34:F34"/>
-    <mergeCell ref="I20:J20"/>
-    <mergeCell ref="H20:H21"/>
-    <mergeCell ref="B4:E4"/>
-    <mergeCell ref="B5:K5"/>
-    <mergeCell ref="D20:F21"/>
-    <mergeCell ref="G20:G21"/>
-    <mergeCell ref="B20:B21"/>
-    <mergeCell ref="C20:C21"/>
-    <mergeCell ref="K20:K21"/>
-    <mergeCell ref="D7:E7"/>
-    <mergeCell ref="D47:F47"/>
-    <mergeCell ref="D48:F48"/>
-    <mergeCell ref="D49:F49"/>
-    <mergeCell ref="D55:F55"/>
-    <mergeCell ref="D37:F37"/>
-    <mergeCell ref="B23:B28"/>
-    <mergeCell ref="B29:B36"/>
-    <mergeCell ref="B37:B55"/>
-    <mergeCell ref="D50:F50"/>
-    <mergeCell ref="D51:F51"/>
-    <mergeCell ref="D52:F52"/>
-    <mergeCell ref="D53:F53"/>
-    <mergeCell ref="D54:F54"/>
-    <mergeCell ref="D38:F38"/>
-    <mergeCell ref="D39:F39"/>
-    <mergeCell ref="D40:F40"/>
-    <mergeCell ref="D41:F41"/>
-    <mergeCell ref="D42:F42"/>
-    <mergeCell ref="D43:F43"/>
-    <mergeCell ref="D44:F44"/>
-    <mergeCell ref="D45:F45"/>
-    <mergeCell ref="D46:F46"/>
-    <mergeCell ref="B56:B58"/>
-    <mergeCell ref="D70:F70"/>
-    <mergeCell ref="D71:F71"/>
-    <mergeCell ref="D72:F72"/>
-    <mergeCell ref="D73:F73"/>
-    <mergeCell ref="D63:F63"/>
-    <mergeCell ref="D57:F57"/>
-    <mergeCell ref="D58:F58"/>
-    <mergeCell ref="D59:F59"/>
-    <mergeCell ref="D60:F60"/>
-    <mergeCell ref="D67:F67"/>
-    <mergeCell ref="D68:F68"/>
-    <mergeCell ref="D61:F61"/>
-    <mergeCell ref="D62:F62"/>
-    <mergeCell ref="D64:F64"/>
-    <mergeCell ref="D65:F65"/>
-    <mergeCell ref="D66:F66"/>
-    <mergeCell ref="D69:F69"/>
-    <mergeCell ref="D56:F56"/>
-    <mergeCell ref="B63:B71"/>
-    <mergeCell ref="B59:B62"/>
-    <mergeCell ref="D92:F92"/>
-    <mergeCell ref="D77:F77"/>
-    <mergeCell ref="D79:F79"/>
-    <mergeCell ref="D81:F81"/>
-    <mergeCell ref="D75:F75"/>
-    <mergeCell ref="D86:F86"/>
-    <mergeCell ref="D91:F91"/>
-    <mergeCell ref="D83:F83"/>
-    <mergeCell ref="D84:F84"/>
-    <mergeCell ref="B72:B91"/>
-    <mergeCell ref="D85:F85"/>
-    <mergeCell ref="D87:F87"/>
-    <mergeCell ref="D88:F88"/>
-    <mergeCell ref="D89:F89"/>
-    <mergeCell ref="D90:F90"/>
-    <mergeCell ref="D78:F78"/>
-    <mergeCell ref="D80:F80"/>
-    <mergeCell ref="D82:F82"/>
-    <mergeCell ref="D76:F76"/>
-    <mergeCell ref="D74:F74"/>
-    <mergeCell ref="D139:F139"/>
-    <mergeCell ref="D138:F138"/>
-    <mergeCell ref="D112:F112"/>
-    <mergeCell ref="D111:F111"/>
-    <mergeCell ref="D110:F110"/>
-    <mergeCell ref="D113:F113"/>
-    <mergeCell ref="D104:F104"/>
-    <mergeCell ref="D100:F100"/>
-    <mergeCell ref="D124:F124"/>
-    <mergeCell ref="D137:F137"/>
-    <mergeCell ref="D102:F102"/>
-    <mergeCell ref="D103:F103"/>
-    <mergeCell ref="D105:F105"/>
-    <mergeCell ref="D106:F106"/>
-    <mergeCell ref="D107:F107"/>
-    <mergeCell ref="D108:F108"/>
-    <mergeCell ref="B141:B144"/>
-    <mergeCell ref="B145:B162"/>
-    <mergeCell ref="D140:F140"/>
-    <mergeCell ref="D141:F141"/>
-    <mergeCell ref="D142:F142"/>
-    <mergeCell ref="D143:F143"/>
-    <mergeCell ref="D145:F145"/>
-    <mergeCell ref="D146:F146"/>
-    <mergeCell ref="D147:F147"/>
-    <mergeCell ref="D148:F148"/>
-    <mergeCell ref="D149:F149"/>
-    <mergeCell ref="D161:F161"/>
-    <mergeCell ref="D162:F162"/>
-    <mergeCell ref="D144:F144"/>
-    <mergeCell ref="D156:F156"/>
-    <mergeCell ref="D157:F157"/>
-    <mergeCell ref="D158:F158"/>
-    <mergeCell ref="D159:F159"/>
-    <mergeCell ref="D160:F160"/>
-    <mergeCell ref="D155:F155"/>
-    <mergeCell ref="D154:F154"/>
-    <mergeCell ref="B163:B164"/>
-    <mergeCell ref="D165:F165"/>
-    <mergeCell ref="D188:F188"/>
-    <mergeCell ref="D185:F185"/>
-    <mergeCell ref="D184:F184"/>
-    <mergeCell ref="D166:F166"/>
-    <mergeCell ref="D167:F167"/>
-    <mergeCell ref="D168:F168"/>
-    <mergeCell ref="D181:F181"/>
-    <mergeCell ref="D182:F182"/>
-    <mergeCell ref="D169:F169"/>
-    <mergeCell ref="D170:F170"/>
-    <mergeCell ref="D178:F178"/>
-    <mergeCell ref="D172:F172"/>
-    <mergeCell ref="D174:F174"/>
-    <mergeCell ref="D175:F175"/>
-    <mergeCell ref="B170:B181"/>
-    <mergeCell ref="B166:B169"/>
-    <mergeCell ref="D150:F150"/>
-    <mergeCell ref="D151:F151"/>
-    <mergeCell ref="D152:F152"/>
-    <mergeCell ref="D153:F153"/>
-    <mergeCell ref="B138:B140"/>
   </mergeCells>
   <phoneticPr fontId="3"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -11614,7 +11866,7 @@
   <legacyDrawing r:id="rId2"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" disablePrompts="1" count="1">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0200-000000000000}">
           <x14:formula1>
             <xm:f>master!#REF!</xm:f>

--- a/IG/7日版/AI Native-バイブコーディング_IG.xlsx
+++ b/IG/7日版/AI Native-バイブコーディング_IG.xlsx
@@ -8,19 +8,19 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\myrepo\ai_navive\IG\7日版\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E8E394DB-9C5C-4F7E-9B6F-FFF752E87D04}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A591C377-0B6F-4D87-915E-0593B7387203}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="860" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="860" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="スケジュール（4日）" sheetId="33" r:id="rId1"/>
+    <sheet name="スケジュール（3日）" sheetId="33" r:id="rId1"/>
     <sheet name="特記イベント" sheetId="36" r:id="rId2"/>
     <sheet name="講義" sheetId="31" r:id="rId3"/>
     <sheet name="master" sheetId="21" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'スケジュール（4日）'!$A$1:$J$44</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="2">講義!$A$1:$L$190</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'スケジュール（3日）'!$A$1:$H$44</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="2">講義!$A$1:$L$189</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="1">特記イベント!$A$1:$L$14</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -88,7 +88,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="826" uniqueCount="447">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="828" uniqueCount="450">
   <si>
     <t>1 日目</t>
     <rPh sb="2" eb="3">
@@ -3119,9 +3119,6 @@
     <t>AI-10</t>
   </si>
   <si>
-    <t>AI-11</t>
-  </si>
-  <si>
     <t xml:space="preserve">・AI-04
 </t>
     <phoneticPr fontId="3"/>
@@ -3277,16 +3274,6 @@
   </si>
   <si>
     <t>3 日目</t>
-    <rPh sb="2" eb="3">
-      <t>ニチ</t>
-    </rPh>
-    <rPh sb="3" eb="4">
-      <t>メ</t>
-    </rPh>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
-    <t>4 日目</t>
     <rPh sb="2" eb="3">
       <t>ニチ</t>
     </rPh>
@@ -3409,19 +3396,6 @@
     <phoneticPr fontId="3"/>
   </si>
   <si>
-    <t>AWS講義（詳細は別紙に記載）</t>
-    <rPh sb="3" eb="5">
-      <t>コウギ</t>
-    </rPh>
-    <rPh sb="9" eb="11">
-      <t>ベッシ</t>
-    </rPh>
-    <rPh sb="12" eb="14">
-      <t>キサイ</t>
-    </rPh>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
     <t>AI-06</t>
     <phoneticPr fontId="3"/>
   </si>
@@ -3452,12 +3426,6 @@
   </si>
   <si>
     <t xml:space="preserve">・AI-08
-</t>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
-    <t xml:space="preserve">・AI-10
-・AI-11
 </t>
     <phoneticPr fontId="3"/>
   </si>
@@ -3537,12 +3505,6 @@
     <phoneticPr fontId="3"/>
   </si>
   <si>
-    <t xml:space="preserve">・AI-10
-・AI-11
-</t>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
     <t>振り返りレポートを作成することを説明する。
 ①自身のAPとサンプルAPの違い
 ②自身のAPをどのように改善できるか
@@ -4258,10 +4220,6 @@
     <phoneticPr fontId="3"/>
   </si>
   <si>
-    <t>※本研修ではリモートリポジトリは利用しない。</t>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
     <t xml:space="preserve">・AI-08
 </t>
     <phoneticPr fontId="3"/>
@@ -4290,19 +4248,6 @@
     </rPh>
     <rPh sb="3" eb="5">
       <t>リヨウ</t>
-    </rPh>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
-    <t>※基本的にGitコマンドを直接使うことはない。</t>
-    <rPh sb="1" eb="4">
-      <t>キホンテキ</t>
-    </rPh>
-    <rPh sb="13" eb="15">
-      <t>チョクセツ</t>
-    </rPh>
-    <rPh sb="15" eb="16">
-      <t>ツカ</t>
     </rPh>
     <phoneticPr fontId="3"/>
   </si>
@@ -4526,6 +4471,86 @@
   </si>
   <si>
     <t xml:space="preserve">・AI-07
+</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>※本研修ではブランチの利用は任意です。</t>
+    <rPh sb="11" eb="13">
+      <t>リヨウ</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>ニンイ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>※本研修ではブランチの利用は任意です。</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>※本研修ではリモートリポジトリは利用しません。</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>※基本的にGitコマンドを直接使うことはありません。</t>
+    <rPh sb="1" eb="4">
+      <t>キホンテキ</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>チョクセツ</t>
+    </rPh>
+    <rPh sb="15" eb="16">
+      <t>ツカ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>〇</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>Git</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>※本研修では追加演習の実施は不要です。</t>
+    <rPh sb="6" eb="10">
+      <t>ツイカエンシュウ</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>ジッシ</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>フヨウ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>※本研修で講師配布テストの実施は不要です。</t>
+    <rPh sb="5" eb="7">
+      <t>コウシ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>ハイフ</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>ジッシ</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>フヨウ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t xml:space="preserve">・AI-09
+・AI-10
+</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t xml:space="preserve">・AI-09
+・AI-10
 </t>
     <phoneticPr fontId="3"/>
   </si>
@@ -4950,7 +4975,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="126">
+  <cellXfs count="130">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -5203,9 +5228,6 @@
     <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="20" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
     <xf numFmtId="20" fontId="15" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
@@ -5328,6 +5350,21 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -5685,7 +5722,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A2:J44"/>
+  <dimension ref="A2:H44"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="7" style="1" bestFit="1" customWidth="1"/>
@@ -5695,27 +5732,23 @@
     <col min="5" max="5" width="45" style="1" customWidth="1"/>
     <col min="6" max="6" width="7.33203125" style="1" customWidth="1"/>
     <col min="7" max="7" width="45" style="1" customWidth="1"/>
-    <col min="8" max="8" width="7.33203125" style="1" customWidth="1"/>
-    <col min="9" max="9" width="45" style="1" customWidth="1"/>
-    <col min="10" max="10" width="5" style="1" customWidth="1"/>
-    <col min="11" max="16384" width="9" style="6"/>
+    <col min="8" max="8" width="5" style="1" customWidth="1"/>
+    <col min="9" max="16384" width="9" style="6"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:10" ht="27">
+    <row r="2" spans="1:8" ht="27">
       <c r="A2" s="13"/>
-      <c r="B2" s="91" t="str">
+      <c r="B2" s="90" t="str">
         <f>"コースプラン/インストラクションガイド 「"&amp;master!$B$1&amp;"_IG」"</f>
         <v>コースプラン/インストラクションガイド 「AI Native-バイブコーディング_IG」</v>
       </c>
-      <c r="C2" s="91"/>
-      <c r="D2" s="91"/>
-      <c r="E2" s="91"/>
-      <c r="F2" s="91"/>
-      <c r="G2" s="91"/>
-      <c r="H2" s="91"/>
-      <c r="I2" s="91"/>
-    </row>
-    <row r="3" spans="1:10" ht="27.6" thickBot="1">
+      <c r="C2" s="90"/>
+      <c r="D2" s="90"/>
+      <c r="E2" s="90"/>
+      <c r="F2" s="90"/>
+      <c r="G2" s="90"/>
+    </row>
+    <row r="3" spans="1:8" ht="27.6" thickBot="1">
       <c r="A3" s="13"/>
       <c r="B3" s="14"/>
       <c r="C3" s="13"/>
@@ -5723,63 +5756,52 @@
       <c r="E3" s="13"/>
       <c r="F3" s="13"/>
       <c r="G3" s="13"/>
-      <c r="H3" s="13"/>
-      <c r="I3" s="13"/>
-    </row>
-    <row r="4" spans="1:10" ht="27.6" thickBot="1">
+    </row>
+    <row r="4" spans="1:8" ht="27.6" thickBot="1">
       <c r="A4" s="13"/>
-      <c r="B4" s="92" t="s">
+      <c r="B4" s="91" t="s">
         <v>11</v>
       </c>
-      <c r="C4" s="93"/>
+      <c r="C4" s="92"/>
       <c r="D4" s="13"/>
       <c r="E4" s="13"/>
       <c r="F4" s="13"/>
       <c r="G4" s="13"/>
-      <c r="H4" s="13"/>
-      <c r="I4" s="13"/>
-    </row>
-    <row r="5" spans="1:10" ht="27.6" thickBot="1">
+    </row>
+    <row r="5" spans="1:8" ht="27.6" thickBot="1">
       <c r="A5" s="13"/>
-      <c r="B5" s="94"/>
-      <c r="C5" s="95"/>
+      <c r="B5" s="93"/>
+      <c r="C5" s="94"/>
       <c r="D5" s="13"/>
       <c r="E5" s="13"/>
       <c r="F5" s="13"/>
       <c r="G5" s="13"/>
-      <c r="H5" s="13"/>
-      <c r="I5" s="13"/>
-    </row>
-    <row r="7" spans="1:10" ht="16.2">
-      <c r="B7" s="96" t="s">
+    </row>
+    <row r="7" spans="1:8" ht="16.2">
+      <c r="B7" s="95" t="s">
         <v>2</v>
       </c>
-      <c r="C7" s="96"/>
-    </row>
-    <row r="8" spans="1:10">
+      <c r="C7" s="95"/>
+    </row>
+    <row r="8" spans="1:8">
       <c r="E8" s="15"/>
       <c r="G8" s="15"/>
-      <c r="I8" s="15"/>
-    </row>
-    <row r="9" spans="1:10">
+    </row>
+    <row r="9" spans="1:8">
       <c r="B9" s="21"/>
       <c r="C9" s="21" t="s">
         <v>0</v>
       </c>
       <c r="D9" s="21"/>
       <c r="E9" s="21" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="F9" s="21"/>
       <c r="G9" s="21" t="s">
-        <v>319</v>
-      </c>
-      <c r="H9" s="21"/>
-      <c r="I9" s="21" t="s">
-        <v>320</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10" ht="14.25" customHeight="1">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" ht="14.25" customHeight="1">
       <c r="A10" s="34">
         <v>0.39583333333333331</v>
       </c>
@@ -5798,17 +5820,11 @@
       <c r="F10" s="34">
         <v>0.39583333333333331</v>
       </c>
-      <c r="G10" s="69" t="s">
+      <c r="G10" s="127" t="s">
         <v>3</v>
       </c>
-      <c r="H10" s="34">
-        <v>0.39583333333333331</v>
-      </c>
-      <c r="I10" s="69" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10">
+    </row>
+    <row r="11" spans="1:8">
       <c r="A11" s="36"/>
       <c r="B11" s="56">
         <v>0.40625</v>
@@ -5820,25 +5836,19 @@
       <c r="D11" s="56">
         <v>0.40625</v>
       </c>
-      <c r="E11" s="66">
-        <f>master!B104</f>
-        <v>0</v>
+      <c r="E11" s="55" t="str">
+        <f>master!B67</f>
+        <v>課題1の実施</v>
       </c>
       <c r="F11" s="56">
         <v>0.40625</v>
       </c>
-      <c r="G11" s="66" t="str">
-        <f>master!B116</f>
-        <v>単体テストとJunitの導入</v>
-      </c>
-      <c r="H11" s="56">
-        <v>0.40625</v>
-      </c>
-      <c r="I11" s="66" t="s">
-        <v>334</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10">
+      <c r="G11" s="55" t="str">
+        <f>master!B67</f>
+        <v>課題1の実施</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8">
       <c r="A12" s="34">
         <v>0.41666666666666669</v>
       </c>
@@ -5847,20 +5857,15 @@
         <f>master!B4</f>
         <v>Webアプリケーションとは</v>
       </c>
-      <c r="D12" s="64"/>
-      <c r="E12" s="66">
-        <f>master!B105</f>
-        <v>0</v>
-      </c>
+      <c r="D12" s="63"/>
+      <c r="E12" s="51"/>
       <c r="F12" s="63"/>
-      <c r="G12" s="66" t="str">
-        <f>master!B119</f>
-        <v>テストとは</v>
-      </c>
-      <c r="H12" s="63"/>
-      <c r="I12" s="67"/>
-    </row>
-    <row r="13" spans="1:10">
+      <c r="G12" s="51" t="str">
+        <f>master!B156</f>
+        <v>課題2の実施</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8">
       <c r="A13" s="35"/>
       <c r="B13" s="56">
         <v>0.42708333333333331</v>
@@ -5869,42 +5874,23 @@
         <f>master!B9</f>
         <v>データベースとは</v>
       </c>
-      <c r="D13" s="84">
-        <v>0.42708333333333331</v>
-      </c>
-      <c r="E13" s="66" t="str">
-        <f>master!B106</f>
-        <v>VS Codeによるローカルリポジトリの操作</v>
-      </c>
-      <c r="F13" s="56">
-        <v>0.42708333333333331</v>
-      </c>
-      <c r="G13" s="66" t="str">
-        <f>master!B123</f>
-        <v>単体テストとは</v>
-      </c>
-      <c r="H13" s="63"/>
-      <c r="I13" s="67"/>
-      <c r="J13" s="6"/>
-    </row>
-    <row r="14" spans="1:10">
+      <c r="D13" s="63"/>
+      <c r="E13" s="51"/>
+      <c r="F13" s="63"/>
+      <c r="G13" s="51"/>
+      <c r="H13" s="6"/>
+    </row>
+    <row r="14" spans="1:8">
       <c r="A14" s="35"/>
       <c r="B14" s="64"/>
       <c r="C14" s="68"/>
-      <c r="D14" s="63">
-        <v>0.43402777777777779</v>
-      </c>
-      <c r="E14" s="66">
-        <f>master!B108</f>
-        <v>0</v>
-      </c>
+      <c r="D14" s="63"/>
+      <c r="E14" s="51"/>
       <c r="F14" s="63"/>
-      <c r="G14" s="67"/>
-      <c r="H14" s="63"/>
-      <c r="I14" s="67"/>
-      <c r="J14" s="6"/>
-    </row>
-    <row r="15" spans="1:10">
+      <c r="G14" s="51"/>
+      <c r="H14" s="6"/>
+    </row>
+    <row r="15" spans="1:8">
       <c r="A15" s="36"/>
       <c r="B15" s="56">
         <v>0.44791666666666669</v>
@@ -5914,74 +5900,54 @@
         <v>Java言語、Springフレームワークとは</v>
       </c>
       <c r="D15" s="63"/>
-      <c r="E15" s="67"/>
+      <c r="E15" s="51"/>
       <c r="F15" s="63"/>
-      <c r="G15" s="67"/>
-      <c r="H15" s="63"/>
-      <c r="I15" s="67"/>
-      <c r="J15" s="6"/>
-    </row>
-    <row r="16" spans="1:10">
+      <c r="G15" s="51"/>
+      <c r="H15" s="6"/>
+    </row>
+    <row r="16" spans="1:8">
       <c r="A16" s="34">
         <v>0.45833333333333331</v>
       </c>
       <c r="B16" s="63"/>
       <c r="C16" s="67"/>
       <c r="D16" s="63"/>
-      <c r="E16" s="67"/>
+      <c r="E16" s="51"/>
       <c r="F16" s="63"/>
-      <c r="G16" s="67"/>
-      <c r="H16" s="63"/>
-      <c r="I16" s="67"/>
-      <c r="J16" s="6"/>
-    </row>
-    <row r="17" spans="1:10">
+      <c r="G16" s="51"/>
+      <c r="H16" s="6"/>
+    </row>
+    <row r="17" spans="1:8">
       <c r="A17" s="35"/>
       <c r="B17" s="63"/>
       <c r="C17" s="67"/>
-      <c r="D17" s="64"/>
-      <c r="E17" s="68"/>
+      <c r="D17" s="63"/>
+      <c r="E17" s="51"/>
       <c r="F17" s="63"/>
-      <c r="G17" s="67"/>
-      <c r="H17" s="63"/>
-      <c r="I17" s="67"/>
-      <c r="J17" s="6"/>
-    </row>
-    <row r="18" spans="1:10">
+      <c r="G17" s="51"/>
+      <c r="H17" s="6"/>
+    </row>
+    <row r="18" spans="1:8">
       <c r="A18" s="35"/>
       <c r="B18" s="63"/>
       <c r="C18" s="67"/>
-      <c r="D18" s="56">
-        <v>0.47916666666666669</v>
-      </c>
-      <c r="E18" s="55" t="str">
-        <f>master!B67</f>
-        <v>課題1の実施</v>
-      </c>
-      <c r="F18" s="64"/>
-      <c r="G18" s="68"/>
-      <c r="H18" s="63"/>
-      <c r="I18" s="67"/>
-      <c r="J18" s="6"/>
-    </row>
-    <row r="19" spans="1:10">
+      <c r="D18" s="63"/>
+      <c r="E18" s="51"/>
+      <c r="F18" s="63"/>
+      <c r="G18" s="51"/>
+      <c r="H18" s="6"/>
+    </row>
+    <row r="19" spans="1:8">
       <c r="A19" s="36"/>
       <c r="B19" s="64"/>
       <c r="C19" s="68"/>
       <c r="D19" s="63"/>
       <c r="E19" s="51"/>
-      <c r="F19" s="56">
-        <v>0.48958333333333331</v>
-      </c>
-      <c r="G19" s="66" t="str">
-        <f>master!B141</f>
-        <v>JUnit</v>
-      </c>
-      <c r="H19" s="63"/>
-      <c r="I19" s="67"/>
-      <c r="J19" s="6"/>
-    </row>
-    <row r="20" spans="1:10">
+      <c r="F19" s="63"/>
+      <c r="G19" s="51"/>
+      <c r="H19" s="6"/>
+    </row>
+    <row r="20" spans="1:8">
       <c r="A20" s="54">
         <v>0.5</v>
       </c>
@@ -5993,30 +5959,21 @@
       </c>
       <c r="D20" s="63"/>
       <c r="E20" s="51"/>
-      <c r="F20" s="54">
-        <v>0.5</v>
-      </c>
-      <c r="G20" s="55" t="str">
-        <f>master!B67</f>
-        <v>課題1の実施</v>
-      </c>
-      <c r="H20" s="63"/>
-      <c r="I20" s="67"/>
-      <c r="J20" s="6"/>
-    </row>
-    <row r="21" spans="1:10">
+      <c r="F20" s="63"/>
+      <c r="G20" s="51"/>
+      <c r="H20" s="6"/>
+    </row>
+    <row r="21" spans="1:8">
       <c r="A21" s="49"/>
       <c r="B21" s="50"/>
       <c r="C21" s="38"/>
       <c r="D21" s="64"/>
       <c r="E21" s="52"/>
-      <c r="F21" s="36"/>
+      <c r="F21" s="64"/>
       <c r="G21" s="52"/>
-      <c r="H21" s="64"/>
-      <c r="I21" s="68"/>
-      <c r="J21" s="6"/>
-    </row>
-    <row r="22" spans="1:10">
+      <c r="H21" s="6"/>
+    </row>
+    <row r="22" spans="1:8">
       <c r="A22" s="35"/>
       <c r="B22" s="35">
         <v>0.52083333333333337</v>
@@ -6036,15 +5993,9 @@
       <c r="G22" s="71" t="s">
         <v>1</v>
       </c>
-      <c r="H22" s="35">
-        <v>0.52083333333333337</v>
-      </c>
-      <c r="I22" s="71" t="s">
-        <v>1</v>
-      </c>
-      <c r="J22" s="6"/>
-    </row>
-    <row r="23" spans="1:10">
+      <c r="H22" s="6"/>
+    </row>
+    <row r="23" spans="1:8">
       <c r="A23" s="36"/>
       <c r="B23" s="35" t="s">
         <v>29</v>
@@ -6058,13 +6009,9 @@
         <v>29</v>
       </c>
       <c r="G23" s="71"/>
-      <c r="H23" s="35" t="s">
-        <v>29</v>
-      </c>
-      <c r="I23" s="71"/>
-      <c r="J23" s="6"/>
-    </row>
-    <row r="24" spans="1:10">
+      <c r="H23" s="6"/>
+    </row>
+    <row r="24" spans="1:8">
       <c r="A24" s="34">
         <v>0.54166666666666663</v>
       </c>
@@ -6080,13 +6027,9 @@
         <v>29</v>
       </c>
       <c r="G24" s="71"/>
-      <c r="H24" s="35" t="s">
-        <v>29</v>
-      </c>
-      <c r="I24" s="71"/>
-      <c r="J24" s="6"/>
-    </row>
-    <row r="25" spans="1:10">
+      <c r="H24" s="6"/>
+    </row>
+    <row r="25" spans="1:8">
       <c r="A25" s="35"/>
       <c r="B25" s="36" t="s">
         <v>29</v>
@@ -6100,13 +6043,9 @@
         <v>29</v>
       </c>
       <c r="G25" s="72"/>
-      <c r="H25" s="36" t="s">
-        <v>29</v>
-      </c>
-      <c r="I25" s="72"/>
-      <c r="J25" s="6"/>
-    </row>
-    <row r="26" spans="1:10">
+      <c r="H25" s="6"/>
+    </row>
+    <row r="26" spans="1:8">
       <c r="A26" s="35"/>
       <c r="B26" s="37">
         <v>0.5625</v>
@@ -6118,44 +6057,30 @@
       <c r="D26" s="37">
         <v>0.5625</v>
       </c>
-      <c r="E26" s="55"/>
-      <c r="F26" s="85">
+      <c r="E26" s="66" t="str">
+        <f>master!B116</f>
+        <v>単体テストとJunitの導入</v>
+      </c>
+      <c r="F26" s="37">
         <v>0.5625</v>
       </c>
-      <c r="G26" s="86" t="str">
-        <f>master!B144</f>
-        <v>課題2の導入</v>
-      </c>
-      <c r="H26" s="37">
-        <v>0.5625</v>
-      </c>
-      <c r="I26" s="55" t="str">
-        <f>master!B67</f>
-        <v>課題1の実施</v>
-      </c>
-      <c r="J26" s="6"/>
-    </row>
-    <row r="27" spans="1:10">
+      <c r="G26" s="55"/>
+      <c r="H26" s="6"/>
+    </row>
+    <row r="27" spans="1:8">
       <c r="A27" s="36"/>
       <c r="B27" s="38"/>
       <c r="C27" s="52"/>
       <c r="D27" s="39"/>
-      <c r="E27" s="51"/>
-      <c r="F27" s="39">
-        <v>0.57291666666666663</v>
-      </c>
-      <c r="G27" s="55" t="str">
-        <f>master!B148</f>
-        <v>ハンズオン</v>
-      </c>
-      <c r="H27" s="39"/>
-      <c r="I27" s="51" t="str">
-        <f>master!B156</f>
-        <v>課題2の実施</v>
-      </c>
-      <c r="J27" s="6"/>
-    </row>
-    <row r="28" spans="1:10">
+      <c r="E27" s="66" t="str">
+        <f>master!B119</f>
+        <v>テストとは</v>
+      </c>
+      <c r="F27" s="39"/>
+      <c r="G27" s="51"/>
+      <c r="H27" s="6"/>
+    </row>
+    <row r="28" spans="1:8">
       <c r="A28" s="34">
         <v>0.58333333333333337</v>
       </c>
@@ -6166,27 +6091,28 @@
         <f>master!B40</f>
         <v>Spring Bootプロジェクトの_x000B_準備、起動確認</v>
       </c>
-      <c r="D28" s="39"/>
-      <c r="E28" s="51"/>
+      <c r="D28" s="34">
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="E28" s="66" t="str">
+        <f>master!B123</f>
+        <v>単体テストとは</v>
+      </c>
       <c r="F28" s="39"/>
       <c r="G28" s="51"/>
-      <c r="H28" s="39"/>
-      <c r="I28" s="51"/>
-      <c r="J28" s="6"/>
-    </row>
-    <row r="29" spans="1:10">
+      <c r="H28" s="6"/>
+    </row>
+    <row r="29" spans="1:8">
       <c r="A29" s="35"/>
       <c r="B29" s="38"/>
       <c r="C29" s="52"/>
       <c r="D29" s="39"/>
-      <c r="E29" s="51"/>
+      <c r="E29" s="67"/>
       <c r="F29" s="39"/>
       <c r="G29" s="51"/>
-      <c r="H29" s="39"/>
-      <c r="I29" s="51"/>
-      <c r="J29" s="6"/>
-    </row>
-    <row r="30" spans="1:10">
+      <c r="H29" s="6"/>
+    </row>
+    <row r="30" spans="1:8">
       <c r="A30" s="35"/>
       <c r="B30" s="39">
         <v>0.60416666666666663</v>
@@ -6196,26 +6122,22 @@
         <v>ECサイト Webアプリの要件</v>
       </c>
       <c r="D30" s="39"/>
-      <c r="E30" s="51"/>
+      <c r="E30" s="67"/>
       <c r="F30" s="39"/>
       <c r="G30" s="51"/>
-      <c r="H30" s="39"/>
-      <c r="I30" s="51"/>
-      <c r="J30" s="6"/>
-    </row>
-    <row r="31" spans="1:10">
+      <c r="H30" s="6"/>
+    </row>
+    <row r="31" spans="1:8">
       <c r="A31" s="36"/>
       <c r="B31" s="39"/>
       <c r="C31" s="52"/>
       <c r="D31" s="39"/>
-      <c r="E31" s="51"/>
+      <c r="E31" s="67"/>
       <c r="F31" s="39"/>
       <c r="G31" s="51"/>
-      <c r="H31" s="39"/>
-      <c r="I31" s="51"/>
-      <c r="J31" s="6"/>
-    </row>
-    <row r="32" spans="1:10">
+      <c r="H31" s="6"/>
+    </row>
+    <row r="32" spans="1:8">
       <c r="A32" s="54">
         <v>0.625</v>
       </c>
@@ -6227,120 +6149,108 @@
         <v>ハンズオン</v>
       </c>
       <c r="D32" s="39"/>
-      <c r="E32" s="51"/>
+      <c r="E32" s="67"/>
       <c r="F32" s="39"/>
-      <c r="G32" s="52"/>
-      <c r="H32" s="39"/>
-      <c r="I32" s="51"/>
-      <c r="J32" s="6"/>
-    </row>
-    <row r="33" spans="1:10">
+      <c r="G32" s="51"/>
+      <c r="H32" s="6"/>
+    </row>
+    <row r="33" spans="1:8">
       <c r="A33" s="49"/>
       <c r="B33" s="39"/>
       <c r="C33" s="51"/>
-      <c r="D33" s="39"/>
-      <c r="E33" s="51"/>
-      <c r="F33" s="54">
-        <v>0.63541666666666663</v>
-      </c>
-      <c r="G33" s="51" t="str">
-        <f>master!B156</f>
-        <v>課題2の実施</v>
-      </c>
-      <c r="H33" s="39"/>
-      <c r="I33" s="51"/>
-      <c r="J33" s="6"/>
-    </row>
-    <row r="34" spans="1:10">
+      <c r="D33" s="38"/>
+      <c r="E33" s="68"/>
+      <c r="F33" s="39"/>
+      <c r="G33" s="51"/>
+      <c r="H33" s="6"/>
+    </row>
+    <row r="34" spans="1:8">
       <c r="A34" s="49"/>
       <c r="B34" s="39"/>
       <c r="C34" s="51"/>
-      <c r="D34" s="39"/>
-      <c r="E34" s="51"/>
+      <c r="D34" s="84">
+        <v>0.64583333333333337</v>
+      </c>
+      <c r="E34" s="65" t="str">
+        <f>master!B141</f>
+        <v>JUnit</v>
+      </c>
       <c r="F34" s="39"/>
       <c r="G34" s="51"/>
-      <c r="H34" s="39"/>
-      <c r="I34" s="51"/>
-      <c r="J34" s="6"/>
-    </row>
-    <row r="35" spans="1:10">
+      <c r="H34" s="6"/>
+    </row>
+    <row r="35" spans="1:8">
       <c r="A35" s="36"/>
       <c r="B35" s="39"/>
       <c r="C35" s="51"/>
-      <c r="D35" s="39"/>
-      <c r="E35" s="51"/>
+      <c r="D35" s="84">
+        <v>0.65277777777777779</v>
+      </c>
+      <c r="E35" s="85" t="str">
+        <f>master!B144</f>
+        <v>課題2の導入</v>
+      </c>
       <c r="F35" s="39"/>
       <c r="G35" s="51"/>
-      <c r="H35" s="39"/>
-      <c r="I35" s="51"/>
-      <c r="J35" s="6"/>
-    </row>
-    <row r="36" spans="1:10">
+      <c r="H35" s="6"/>
+    </row>
+    <row r="36" spans="1:8">
       <c r="A36" s="34">
         <v>0.66666666666666663</v>
       </c>
       <c r="B36" s="39"/>
       <c r="C36" s="51"/>
-      <c r="D36" s="39"/>
-      <c r="E36" s="51"/>
+      <c r="D36" s="34">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="E36" s="55" t="str">
+        <f>master!B148</f>
+        <v>ハンズオン</v>
+      </c>
       <c r="F36" s="39"/>
       <c r="G36" s="51"/>
-      <c r="H36" s="39"/>
-      <c r="I36" s="51"/>
-      <c r="J36" s="6"/>
-    </row>
-    <row r="37" spans="1:10">
+      <c r="H36" s="6"/>
+    </row>
+    <row r="37" spans="1:8">
       <c r="A37" s="35"/>
       <c r="B37" s="39"/>
       <c r="C37" s="52"/>
       <c r="D37" s="39"/>
       <c r="E37" s="51"/>
-      <c r="F37" s="39"/>
-      <c r="G37" s="51"/>
-      <c r="H37" s="39"/>
-      <c r="I37" s="51"/>
-      <c r="J37" s="6"/>
-    </row>
-    <row r="38" spans="1:10">
+      <c r="F37" s="38"/>
+      <c r="G37" s="52"/>
+      <c r="H37" s="6"/>
+    </row>
+    <row r="38" spans="1:8">
       <c r="A38" s="35"/>
-      <c r="B38" s="84">
+      <c r="B38" s="56">
         <v>0.6875</v>
       </c>
-      <c r="C38" s="65" t="str">
-        <f>master!B69</f>
-        <v>Gitとは</v>
+      <c r="C38" s="66" t="s">
+        <v>445</v>
       </c>
       <c r="D38" s="39"/>
       <c r="E38" s="51"/>
-      <c r="F38" s="39"/>
-      <c r="G38" s="51"/>
-      <c r="H38" s="38"/>
-      <c r="I38" s="52"/>
-      <c r="J38" s="6"/>
-    </row>
-    <row r="39" spans="1:10">
+      <c r="F38" s="63">
+        <v>0.6875</v>
+      </c>
+      <c r="G38" s="51" t="str">
+        <f>master!B164</f>
+        <v>課題の振り返り</v>
+      </c>
+      <c r="H38" s="6"/>
+    </row>
+    <row r="39" spans="1:8">
       <c r="A39" s="35"/>
-      <c r="B39" s="63">
-        <v>0.69791666666666663</v>
-      </c>
-      <c r="C39" s="67">
-        <f>master!B84</f>
-        <v>0</v>
-      </c>
+      <c r="B39" s="63"/>
+      <c r="C39" s="67"/>
       <c r="D39" s="39"/>
       <c r="E39" s="51"/>
       <c r="F39" s="39"/>
       <c r="G39" s="51"/>
-      <c r="H39" s="56">
-        <v>0.69791666666666663</v>
-      </c>
-      <c r="I39" s="51" t="str">
-        <f>master!B164</f>
-        <v>課題の振り返り</v>
-      </c>
-      <c r="J39" s="6"/>
-    </row>
-    <row r="40" spans="1:10">
+      <c r="H39" s="6"/>
+    </row>
+    <row r="40" spans="1:8">
       <c r="A40" s="37">
         <v>0.70833333333333337</v>
       </c>
@@ -6350,40 +6260,37 @@
       <c r="E40" s="51"/>
       <c r="F40" s="39"/>
       <c r="G40" s="51"/>
-      <c r="H40" s="63"/>
-      <c r="I40" s="51"/>
-      <c r="J40" s="6"/>
-    </row>
-    <row r="41" spans="1:10">
+      <c r="H40" s="6"/>
+    </row>
+    <row r="41" spans="1:8">
       <c r="A41" s="35"/>
       <c r="B41" s="37">
         <v>0.71875</v>
       </c>
-      <c r="C41" s="55" t="str">
-        <f>master!B67</f>
-        <v>課題1の実施</v>
+      <c r="C41" s="55" t="s">
+        <v>445</v>
       </c>
       <c r="D41" s="39"/>
-      <c r="E41" s="51"/>
+      <c r="E41" s="125"/>
       <c r="F41" s="39"/>
       <c r="G41" s="51"/>
-      <c r="H41" s="39"/>
-      <c r="I41" s="51"/>
-      <c r="J41" s="6"/>
-    </row>
-    <row r="42" spans="1:10">
+      <c r="H41" s="6"/>
+    </row>
+    <row r="42" spans="1:8">
       <c r="A42" s="39"/>
       <c r="B42" s="64"/>
       <c r="C42" s="52"/>
       <c r="D42" s="39"/>
-      <c r="E42" s="52"/>
-      <c r="F42" s="39"/>
-      <c r="G42" s="52"/>
-      <c r="H42" s="39"/>
-      <c r="I42" s="52"/>
-      <c r="J42" s="6"/>
-    </row>
-    <row r="43" spans="1:10" ht="14.25" customHeight="1">
+      <c r="E42" s="126"/>
+      <c r="F42" s="37">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="G42" s="128" t="s">
+        <v>52</v>
+      </c>
+      <c r="H42" s="6"/>
+    </row>
+    <row r="43" spans="1:8" ht="14.25" customHeight="1">
       <c r="A43" s="38"/>
       <c r="B43" s="74">
         <v>0.73958333333333337</v>
@@ -6397,32 +6304,22 @@
       <c r="E43" s="73" t="s">
         <v>52</v>
       </c>
-      <c r="F43" s="74">
-        <v>0.73958333333333337</v>
-      </c>
-      <c r="G43" s="73" t="s">
-        <v>52</v>
-      </c>
-      <c r="H43" s="74">
-        <v>0.73958333333333337</v>
-      </c>
-      <c r="I43" s="73" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="44" spans="1:10" ht="15.6" thickBot="1">
+      <c r="F43" s="38"/>
+      <c r="G43" s="129"/>
+    </row>
+    <row r="44" spans="1:8" ht="15.6" thickBot="1">
       <c r="A44" s="6"/>
       <c r="D44" s="20"/>
       <c r="F44" s="20"/>
-      <c r="H44" s="20"/>
-      <c r="J44" s="6"/>
+      <c r="H44" s="6"/>
     </row>
   </sheetData>
-  <mergeCells count="4">
-    <mergeCell ref="B2:I2"/>
+  <mergeCells count="5">
+    <mergeCell ref="B2:G2"/>
     <mergeCell ref="B4:C4"/>
     <mergeCell ref="B5:C5"/>
     <mergeCell ref="B7:C7"/>
+    <mergeCell ref="E41:E42"/>
   </mergeCells>
   <phoneticPr fontId="3"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -6475,10 +6372,10 @@
       <c r="K3" s="9"/>
     </row>
     <row r="4" spans="1:12" ht="16.2">
-      <c r="B4" s="100" t="s">
+      <c r="B4" s="99" t="s">
         <v>4</v>
       </c>
-      <c r="C4" s="100"/>
+      <c r="C4" s="99"/>
       <c r="D4" s="8"/>
       <c r="E4" s="8"/>
       <c r="F4" s="8"/>
@@ -6489,16 +6386,16 @@
       <c r="K4" s="9"/>
     </row>
     <row r="5" spans="1:12" ht="36" customHeight="1">
-      <c r="B5" s="101"/>
-      <c r="C5" s="101"/>
-      <c r="D5" s="101"/>
-      <c r="E5" s="101"/>
-      <c r="F5" s="101"/>
-      <c r="G5" s="101"/>
-      <c r="H5" s="101"/>
-      <c r="I5" s="101"/>
-      <c r="J5" s="101"/>
-      <c r="K5" s="101"/>
+      <c r="B5" s="100"/>
+      <c r="C5" s="100"/>
+      <c r="D5" s="100"/>
+      <c r="E5" s="100"/>
+      <c r="F5" s="100"/>
+      <c r="G5" s="100"/>
+      <c r="H5" s="100"/>
+      <c r="I5" s="100"/>
+      <c r="J5" s="100"/>
+      <c r="K5" s="100"/>
     </row>
     <row r="6" spans="1:12">
       <c r="B6" s="10"/>
@@ -6513,10 +6410,10 @@
       <c r="C7" s="30" t="s">
         <v>15</v>
       </c>
-      <c r="D7" s="102" t="s">
+      <c r="D7" s="101" t="s">
         <v>20</v>
       </c>
-      <c r="E7" s="102"/>
+      <c r="E7" s="101"/>
       <c r="F7" s="30" t="s">
         <v>10</v>
       </c>
@@ -6548,60 +6445,60 @@
     </row>
     <row r="10" spans="1:12">
       <c r="A10" s="10"/>
-      <c r="B10" s="98"/>
-      <c r="C10" s="98" t="s">
+      <c r="B10" s="97"/>
+      <c r="C10" s="97" t="s">
         <v>7</v>
       </c>
-      <c r="D10" s="98" t="s">
+      <c r="D10" s="97" t="s">
         <v>8</v>
       </c>
-      <c r="E10" s="98"/>
-      <c r="F10" s="98"/>
-      <c r="G10" s="98" t="s">
+      <c r="E10" s="97"/>
+      <c r="F10" s="97"/>
+      <c r="G10" s="97" t="s">
         <v>9</v>
       </c>
-      <c r="H10" s="103" t="s">
+      <c r="H10" s="102" t="s">
         <v>23</v>
       </c>
-      <c r="I10" s="97" t="s">
+      <c r="I10" s="96" t="s">
         <v>31</v>
       </c>
-      <c r="J10" s="97"/>
-      <c r="K10" s="97" t="s">
+      <c r="J10" s="96"/>
+      <c r="K10" s="96" t="s">
         <v>30</v>
       </c>
       <c r="L10" s="10"/>
     </row>
     <row r="11" spans="1:12">
       <c r="A11" s="10"/>
-      <c r="B11" s="98"/>
-      <c r="C11" s="98"/>
-      <c r="D11" s="98"/>
-      <c r="E11" s="98"/>
-      <c r="F11" s="98"/>
-      <c r="G11" s="98"/>
-      <c r="H11" s="104"/>
+      <c r="B11" s="97"/>
+      <c r="C11" s="97"/>
+      <c r="D11" s="97"/>
+      <c r="E11" s="97"/>
+      <c r="F11" s="97"/>
+      <c r="G11" s="97"/>
+      <c r="H11" s="103"/>
       <c r="I11" s="25" t="s">
         <v>25</v>
       </c>
       <c r="J11" s="25" t="s">
         <v>6</v>
       </c>
-      <c r="K11" s="98"/>
+      <c r="K11" s="97"/>
       <c r="L11" s="10"/>
     </row>
     <row r="12" spans="1:12" ht="63">
       <c r="A12" s="10"/>
       <c r="B12" s="19"/>
       <c r="C12" s="19" t="s">
-        <v>332</v>
-      </c>
-      <c r="D12" s="99" t="s">
+        <v>330</v>
+      </c>
+      <c r="D12" s="98" t="s">
         <v>50</v>
       </c>
-      <c r="E12" s="99"/>
-      <c r="F12" s="99"/>
-      <c r="G12" s="88" t="s">
+      <c r="E12" s="98"/>
+      <c r="F12" s="98"/>
+      <c r="G12" s="87" t="s">
         <v>51</v>
       </c>
       <c r="H12" s="19"/>
@@ -6618,15 +6515,15 @@
       <c r="A13" s="10"/>
       <c r="B13" s="19"/>
       <c r="C13" s="19" t="s">
-        <v>333</v>
-      </c>
-      <c r="D13" s="99" t="s">
-        <v>330</v>
-      </c>
-      <c r="E13" s="99"/>
-      <c r="F13" s="99"/>
-      <c r="G13" s="88" t="s">
         <v>331</v>
+      </c>
+      <c r="D13" s="98" t="s">
+        <v>328</v>
+      </c>
+      <c r="E13" s="98"/>
+      <c r="F13" s="98"/>
+      <c r="G13" s="87" t="s">
+        <v>329</v>
       </c>
       <c r="H13" s="19"/>
       <c r="I13" s="47" t="s">
@@ -6674,7 +6571,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A2:N191"/>
+  <dimension ref="A2:N190"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="4.33203125" style="1" customWidth="1"/>
@@ -6724,12 +6621,12 @@
       <c r="M3" s="9"/>
     </row>
     <row r="4" spans="2:14" ht="16.2">
-      <c r="B4" s="100" t="s">
+      <c r="B4" s="99" t="s">
         <v>4</v>
       </c>
-      <c r="C4" s="100"/>
-      <c r="D4" s="100"/>
-      <c r="E4" s="100"/>
+      <c r="C4" s="99"/>
+      <c r="D4" s="99"/>
+      <c r="E4" s="99"/>
       <c r="F4" s="8"/>
       <c r="G4" s="8"/>
       <c r="H4" s="7"/>
@@ -6740,16 +6637,16 @@
       <c r="M4" s="9"/>
     </row>
     <row r="5" spans="2:14" ht="36" customHeight="1">
-      <c r="B5" s="122"/>
-      <c r="C5" s="122"/>
-      <c r="D5" s="122"/>
-      <c r="E5" s="122"/>
-      <c r="F5" s="122"/>
-      <c r="G5" s="122"/>
-      <c r="H5" s="122"/>
-      <c r="I5" s="122"/>
-      <c r="J5" s="122"/>
-      <c r="K5" s="122"/>
+      <c r="B5" s="121"/>
+      <c r="C5" s="121"/>
+      <c r="D5" s="121"/>
+      <c r="E5" s="121"/>
+      <c r="F5" s="121"/>
+      <c r="G5" s="121"/>
+      <c r="H5" s="121"/>
+      <c r="I5" s="121"/>
+      <c r="J5" s="121"/>
+      <c r="K5" s="121"/>
       <c r="L5" s="26"/>
       <c r="M5" s="27"/>
     </row>
@@ -6769,10 +6666,10 @@
       <c r="C7" s="30" t="s">
         <v>15</v>
       </c>
-      <c r="D7" s="102" t="s">
+      <c r="D7" s="101" t="s">
         <v>20</v>
       </c>
-      <c r="E7" s="102"/>
+      <c r="E7" s="101"/>
       <c r="F7" s="30" t="s">
         <v>10</v>
       </c>
@@ -6898,7 +6795,7 @@
     </row>
     <row r="13" spans="2:14">
       <c r="B13" s="31" t="s">
-        <v>335</v>
+        <v>332</v>
       </c>
       <c r="C13" s="57" t="s">
         <v>37</v>
@@ -6923,7 +6820,7 @@
         <v>93</v>
       </c>
       <c r="C14" s="57" t="s">
-        <v>396</v>
+        <v>391</v>
       </c>
       <c r="D14" s="42" t="s">
         <v>19</v>
@@ -6945,7 +6842,7 @@
         <v>94</v>
       </c>
       <c r="C15" s="57" t="s">
-        <v>397</v>
+        <v>392</v>
       </c>
       <c r="D15" s="42" t="s">
         <v>19</v>
@@ -6966,6 +6863,9 @@
       <c r="B16" s="31" t="s">
         <v>284</v>
       </c>
+      <c r="C16" s="57" t="s">
+        <v>285</v>
+      </c>
       <c r="D16" s="42" t="s">
         <v>19</v>
       </c>
@@ -6986,7 +6886,7 @@
         <v>287</v>
       </c>
       <c r="C17" s="57" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="D17" s="42" t="s">
         <v>19</v>
@@ -7003,125 +6903,130 @@
       <c r="M17" s="6"/>
       <c r="N17" s="6"/>
     </row>
-    <row r="18" spans="1:14">
-      <c r="B18" s="31" t="s">
-        <v>288</v>
-      </c>
-      <c r="C18" s="57" t="s">
-        <v>286</v>
-      </c>
-      <c r="D18" s="42" t="s">
-        <v>19</v>
-      </c>
-      <c r="E18" s="41"/>
-      <c r="F18" s="33" t="s">
-        <v>21</v>
-      </c>
-      <c r="G18" s="33" t="s">
-        <v>18</v>
-      </c>
-      <c r="K18" s="6"/>
-      <c r="L18" s="6"/>
-      <c r="M18" s="6"/>
-      <c r="N18" s="6"/>
-    </row>
-    <row r="20" spans="1:14" ht="24" customHeight="1">
+    <row r="19" spans="1:14" ht="24" customHeight="1">
+      <c r="A19" s="10"/>
+      <c r="B19" s="97" t="s">
+        <v>5</v>
+      </c>
+      <c r="C19" s="97" t="s">
+        <v>7</v>
+      </c>
+      <c r="D19" s="97" t="s">
+        <v>8</v>
+      </c>
+      <c r="E19" s="97"/>
+      <c r="F19" s="97"/>
+      <c r="G19" s="97" t="s">
+        <v>9</v>
+      </c>
+      <c r="H19" s="96" t="s">
+        <v>23</v>
+      </c>
+      <c r="I19" s="119" t="s">
+        <v>31</v>
+      </c>
+      <c r="J19" s="120"/>
+      <c r="K19" s="96" t="s">
+        <v>32</v>
+      </c>
+      <c r="L19" s="6"/>
+      <c r="M19" s="6"/>
+      <c r="N19" s="6"/>
+    </row>
+    <row r="20" spans="1:14">
       <c r="A20" s="10"/>
-      <c r="B20" s="98" t="s">
-        <v>5</v>
-      </c>
-      <c r="C20" s="98" t="s">
-        <v>7</v>
-      </c>
-      <c r="D20" s="98" t="s">
-        <v>8</v>
-      </c>
-      <c r="E20" s="98"/>
-      <c r="F20" s="98"/>
-      <c r="G20" s="98" t="s">
-        <v>9</v>
-      </c>
-      <c r="H20" s="97" t="s">
-        <v>23</v>
-      </c>
-      <c r="I20" s="120" t="s">
-        <v>31</v>
-      </c>
-      <c r="J20" s="121"/>
-      <c r="K20" s="97" t="s">
-        <v>32</v>
-      </c>
+      <c r="B20" s="97"/>
+      <c r="C20" s="97"/>
+      <c r="D20" s="97"/>
+      <c r="E20" s="97"/>
+      <c r="F20" s="97"/>
+      <c r="G20" s="97"/>
+      <c r="H20" s="96"/>
+      <c r="I20" s="25" t="s">
+        <v>25</v>
+      </c>
+      <c r="J20" s="25" t="s">
+        <v>6</v>
+      </c>
+      <c r="K20" s="97"/>
       <c r="L20" s="6"/>
       <c r="M20" s="6"/>
       <c r="N20" s="6"/>
     </row>
-    <row r="21" spans="1:14">
+    <row r="21" spans="1:14" ht="151.19999999999999">
       <c r="A21" s="10"/>
-      <c r="B21" s="98"/>
-      <c r="C21" s="98"/>
-      <c r="D21" s="98"/>
-      <c r="E21" s="98"/>
-      <c r="F21" s="98"/>
-      <c r="G21" s="98"/>
-      <c r="H21" s="97"/>
-      <c r="I21" s="25" t="s">
-        <v>25</v>
-      </c>
-      <c r="J21" s="25" t="s">
-        <v>6</v>
-      </c>
-      <c r="K21" s="98"/>
+      <c r="B21" s="75" t="str">
+        <f>master!B3</f>
+        <v>バイブコーディングの導入</v>
+      </c>
+      <c r="C21" s="48" t="str">
+        <f>master!C3</f>
+        <v>講義の目的</v>
+      </c>
+      <c r="D21" s="104" t="s">
+        <v>95</v>
+      </c>
+      <c r="E21" s="105"/>
+      <c r="F21" s="106"/>
+      <c r="G21" s="48" t="s">
+        <v>96</v>
+      </c>
+      <c r="H21" s="12"/>
+      <c r="I21" s="46" t="s">
+        <v>24</v>
+      </c>
+      <c r="J21" s="44">
+        <v>2.0833333333333333E-3</v>
+      </c>
+      <c r="K21" s="40"/>
       <c r="L21" s="6"/>
       <c r="M21" s="6"/>
       <c r="N21" s="6"/>
     </row>
-    <row r="22" spans="1:14" ht="151.19999999999999">
+    <row r="22" spans="1:14" ht="138.6" customHeight="1">
       <c r="A22" s="10"/>
-      <c r="B22" s="75" t="str">
-        <f>master!B3</f>
-        <v>バイブコーディングの導入</v>
+      <c r="B22" s="107" t="str">
+        <f>master!B4</f>
+        <v>Webアプリケーションとは</v>
       </c>
       <c r="C22" s="48" t="str">
-        <f>master!C3</f>
-        <v>講義の目的</v>
-      </c>
-      <c r="D22" s="105" t="s">
-        <v>95</v>
-      </c>
-      <c r="E22" s="106"/>
-      <c r="F22" s="107"/>
+        <f>master!C4</f>
+        <v>Webアプリケーションとは</v>
+      </c>
+      <c r="D22" s="104" t="s">
+        <v>97</v>
+      </c>
+      <c r="E22" s="105"/>
+      <c r="F22" s="106"/>
       <c r="G22" s="48" t="s">
-        <v>96</v>
+        <v>40</v>
       </c>
       <c r="H22" s="12"/>
       <c r="I22" s="46" t="s">
         <v>24</v>
       </c>
       <c r="J22" s="44">
-        <v>2.0833333333333333E-3</v>
+        <v>3.472222222222222E-3</v>
       </c>
       <c r="K22" s="40"/>
       <c r="L22" s="6"/>
       <c r="M22" s="6"/>
       <c r="N22" s="6"/>
     </row>
-    <row r="23" spans="1:14" ht="138.6" customHeight="1">
-      <c r="A23" s="10"/>
-      <c r="B23" s="108" t="str">
-        <f>master!B4</f>
-        <v>Webアプリケーションとは</v>
-      </c>
+    <row r="23" spans="1:14" ht="75.599999999999994">
+      <c r="A23" s="11"/>
+      <c r="B23" s="108"/>
       <c r="C23" s="48" t="str">
-        <f>master!C4</f>
-        <v>Webアプリケーションとは</v>
-      </c>
-      <c r="D23" s="105" t="s">
-        <v>97</v>
-      </c>
-      <c r="E23" s="106"/>
-      <c r="F23" s="107"/>
+        <f>master!C5</f>
+        <v>Webアプリケーションの種類</v>
+      </c>
+      <c r="D23" s="104" t="s">
+        <v>98</v>
+      </c>
+      <c r="E23" s="105"/>
+      <c r="F23" s="106"/>
       <c r="G23" s="48" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="H23" s="12"/>
       <c r="I23" s="46" t="s">
@@ -7135,47 +7040,47 @@
       <c r="M23" s="6"/>
       <c r="N23" s="6"/>
     </row>
-    <row r="24" spans="1:14" ht="75.599999999999994">
+    <row r="24" spans="1:14" ht="37.799999999999997">
       <c r="A24" s="11"/>
-      <c r="B24" s="109"/>
+      <c r="B24" s="108"/>
       <c r="C24" s="48" t="str">
-        <f>master!C5</f>
-        <v>Webアプリケーションの種類</v>
-      </c>
-      <c r="D24" s="105" t="s">
-        <v>98</v>
-      </c>
-      <c r="E24" s="106"/>
-      <c r="F24" s="107"/>
+        <f>master!C6</f>
+        <v>アプリケーションとは</v>
+      </c>
+      <c r="D24" s="104" t="s">
+        <v>99</v>
+      </c>
+      <c r="E24" s="105"/>
+      <c r="F24" s="106"/>
       <c r="G24" s="48" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="H24" s="12"/>
       <c r="I24" s="46" t="s">
         <v>24</v>
       </c>
       <c r="J24" s="44">
-        <v>3.472222222222222E-3</v>
+        <v>2.0833333333333333E-3</v>
       </c>
       <c r="K24" s="40"/>
       <c r="L24" s="6"/>
       <c r="M24" s="6"/>
       <c r="N24" s="6"/>
     </row>
-    <row r="25" spans="1:14" ht="37.799999999999997">
+    <row r="25" spans="1:14" ht="63">
       <c r="A25" s="11"/>
-      <c r="B25" s="109"/>
+      <c r="B25" s="108"/>
       <c r="C25" s="48" t="str">
-        <f>master!C6</f>
-        <v>アプリケーションとは</v>
-      </c>
-      <c r="D25" s="105" t="s">
-        <v>99</v>
-      </c>
-      <c r="E25" s="106"/>
-      <c r="F25" s="107"/>
+        <f>master!C7</f>
+        <v>Web画面アプリケーション</v>
+      </c>
+      <c r="D25" s="104" t="s">
+        <v>100</v>
+      </c>
+      <c r="E25" s="105"/>
+      <c r="F25" s="106"/>
       <c r="G25" s="48" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="H25" s="12"/>
       <c r="I25" s="46" t="s">
@@ -7191,16 +7096,13 @@
     </row>
     <row r="26" spans="1:14" ht="63">
       <c r="A26" s="11"/>
-      <c r="B26" s="109"/>
-      <c r="C26" s="48" t="str">
-        <f>master!C7</f>
-        <v>Web画面アプリケーション</v>
-      </c>
-      <c r="D26" s="105" t="s">
-        <v>100</v>
-      </c>
-      <c r="E26" s="106"/>
-      <c r="F26" s="107"/>
+      <c r="B26" s="108"/>
+      <c r="C26" s="48"/>
+      <c r="D26" s="104" t="s">
+        <v>101</v>
+      </c>
+      <c r="E26" s="105"/>
+      <c r="F26" s="106"/>
       <c r="G26" s="48" t="s">
         <v>41</v>
       </c>
@@ -7209,51 +7111,57 @@
         <v>24</v>
       </c>
       <c r="J26" s="44">
-        <v>2.0833333333333333E-3</v>
+        <v>6.9444444444444447E-4</v>
       </c>
       <c r="K26" s="40"/>
       <c r="L26" s="6"/>
       <c r="M26" s="6"/>
       <c r="N26" s="6"/>
     </row>
-    <row r="27" spans="1:14" ht="63">
+    <row r="27" spans="1:14" ht="113.4">
       <c r="A27" s="11"/>
       <c r="B27" s="109"/>
-      <c r="C27" s="48"/>
-      <c r="D27" s="105" t="s">
-        <v>101</v>
-      </c>
-      <c r="E27" s="106"/>
-      <c r="F27" s="107"/>
+      <c r="C27" s="48" t="str">
+        <f>master!C8</f>
+        <v>ブラウザからのリクエスト種類</v>
+      </c>
+      <c r="D27" s="104" t="s">
+        <v>102</v>
+      </c>
+      <c r="E27" s="105"/>
+      <c r="F27" s="106"/>
       <c r="G27" s="48" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="H27" s="12"/>
       <c r="I27" s="46" t="s">
         <v>24</v>
       </c>
       <c r="J27" s="44">
-        <v>6.9444444444444447E-4</v>
+        <v>2.0833333333333333E-3</v>
       </c>
       <c r="K27" s="40"/>
       <c r="L27" s="6"/>
       <c r="M27" s="6"/>
       <c r="N27" s="6"/>
     </row>
-    <row r="28" spans="1:14" ht="113.4">
+    <row r="28" spans="1:14" ht="102" customHeight="1">
       <c r="A28" s="11"/>
-      <c r="B28" s="110"/>
+      <c r="B28" s="107" t="str">
+        <f>master!B9</f>
+        <v>データベースとは</v>
+      </c>
       <c r="C28" s="48" t="str">
-        <f>master!C8</f>
-        <v>ブラウザからのリクエスト種類</v>
-      </c>
-      <c r="D28" s="105" t="s">
-        <v>102</v>
-      </c>
-      <c r="E28" s="106"/>
-      <c r="F28" s="107"/>
+        <f>master!C9</f>
+        <v>データベースとは</v>
+      </c>
+      <c r="D28" s="104" t="s">
+        <v>103</v>
+      </c>
+      <c r="E28" s="105"/>
+      <c r="F28" s="106"/>
       <c r="G28" s="48" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="H28" s="12"/>
       <c r="I28" s="46" t="s">
@@ -7267,50 +7175,47 @@
       <c r="M28" s="6"/>
       <c r="N28" s="6"/>
     </row>
-    <row r="29" spans="1:14" ht="102" customHeight="1">
+    <row r="29" spans="1:14" ht="88.2">
       <c r="A29" s="11"/>
-      <c r="B29" s="108" t="str">
-        <f>master!B9</f>
-        <v>データベースとは</v>
-      </c>
+      <c r="B29" s="108"/>
       <c r="C29" s="48" t="str">
-        <f>master!C9</f>
-        <v>データベースとは</v>
-      </c>
-      <c r="D29" s="105" t="s">
-        <v>103</v>
-      </c>
-      <c r="E29" s="106"/>
-      <c r="F29" s="107"/>
+        <f>master!C10</f>
+        <v>リレーショナルデータベース</v>
+      </c>
+      <c r="D29" s="104" t="s">
+        <v>104</v>
+      </c>
+      <c r="E29" s="105"/>
+      <c r="F29" s="106"/>
       <c r="G29" s="48" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="H29" s="12"/>
       <c r="I29" s="46" t="s">
         <v>24</v>
       </c>
       <c r="J29" s="44">
-        <v>2.0833333333333333E-3</v>
+        <v>3.472222222222222E-3</v>
       </c>
       <c r="K29" s="40"/>
       <c r="L29" s="6"/>
       <c r="M29" s="6"/>
       <c r="N29" s="6"/>
     </row>
-    <row r="30" spans="1:14" ht="88.2">
+    <row r="30" spans="1:14" ht="25.2">
       <c r="A30" s="11"/>
-      <c r="B30" s="109"/>
+      <c r="B30" s="108"/>
       <c r="C30" s="48" t="str">
-        <f>master!C10</f>
-        <v>リレーショナルデータベース</v>
-      </c>
-      <c r="D30" s="105" t="s">
-        <v>104</v>
-      </c>
-      <c r="E30" s="106"/>
-      <c r="F30" s="107"/>
+        <f>master!C11</f>
+        <v>データベースの役割</v>
+      </c>
+      <c r="D30" s="104" t="s">
+        <v>105</v>
+      </c>
+      <c r="E30" s="105"/>
+      <c r="F30" s="106"/>
       <c r="G30" s="48" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H30" s="12"/>
       <c r="I30" s="46" t="s">
@@ -7319,54 +7224,54 @@
       <c r="J30" s="44">
         <v>3.472222222222222E-3</v>
       </c>
-      <c r="K30" s="40"/>
+      <c r="K30" s="40" t="s">
+        <v>115</v>
+      </c>
       <c r="L30" s="6"/>
       <c r="M30" s="6"/>
       <c r="N30" s="6"/>
     </row>
-    <row r="31" spans="1:14" ht="25.2">
+    <row r="31" spans="1:14" ht="75.599999999999994">
       <c r="A31" s="11"/>
-      <c r="B31" s="109"/>
+      <c r="B31" s="108"/>
       <c r="C31" s="48" t="str">
-        <f>master!C11</f>
-        <v>データベースの役割</v>
-      </c>
-      <c r="D31" s="105" t="s">
-        <v>105</v>
-      </c>
-      <c r="E31" s="106"/>
-      <c r="F31" s="107"/>
+        <f>master!C12</f>
+        <v>2.1.テーブル</v>
+      </c>
+      <c r="D31" s="104" t="s">
+        <v>106</v>
+      </c>
+      <c r="E31" s="105"/>
+      <c r="F31" s="106"/>
       <c r="G31" s="48" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="H31" s="12"/>
       <c r="I31" s="46" t="s">
         <v>24</v>
       </c>
       <c r="J31" s="44">
-        <v>3.472222222222222E-3</v>
-      </c>
-      <c r="K31" s="40" t="s">
-        <v>115</v>
-      </c>
+        <v>2.0833333333333333E-3</v>
+      </c>
+      <c r="K31" s="40"/>
       <c r="L31" s="6"/>
       <c r="M31" s="6"/>
       <c r="N31" s="6"/>
     </row>
-    <row r="32" spans="1:14" ht="75.599999999999994">
+    <row r="32" spans="1:14" ht="100.8">
       <c r="A32" s="11"/>
-      <c r="B32" s="109"/>
+      <c r="B32" s="108"/>
       <c r="C32" s="48" t="str">
-        <f>master!C12</f>
-        <v>2.1.テーブル</v>
-      </c>
-      <c r="D32" s="105" t="s">
-        <v>106</v>
-      </c>
-      <c r="E32" s="106"/>
-      <c r="F32" s="107"/>
+        <f>master!C13</f>
+        <v>2.2.データ型１</v>
+      </c>
+      <c r="D32" s="104" t="s">
+        <v>107</v>
+      </c>
+      <c r="E32" s="105"/>
+      <c r="F32" s="106"/>
       <c r="G32" s="48" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="H32" s="12"/>
       <c r="I32" s="46" t="s">
@@ -7380,20 +7285,20 @@
       <c r="M32" s="6"/>
       <c r="N32" s="6"/>
     </row>
-    <row r="33" spans="1:14" ht="100.8">
+    <row r="33" spans="1:14" ht="37.799999999999997">
       <c r="A33" s="11"/>
-      <c r="B33" s="109"/>
+      <c r="B33" s="108"/>
       <c r="C33" s="48" t="str">
-        <f>master!C13</f>
-        <v>2.2.データ型１</v>
-      </c>
-      <c r="D33" s="105" t="s">
-        <v>107</v>
-      </c>
-      <c r="E33" s="106"/>
-      <c r="F33" s="107"/>
+        <f>master!C14</f>
+        <v>2.2.データ型２</v>
+      </c>
+      <c r="D33" s="104" t="s">
+        <v>108</v>
+      </c>
+      <c r="E33" s="105"/>
+      <c r="F33" s="106"/>
       <c r="G33" s="48" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="H33" s="12"/>
       <c r="I33" s="46" t="s">
@@ -7409,16 +7314,16 @@
     </row>
     <row r="34" spans="1:14" ht="37.799999999999997">
       <c r="A34" s="11"/>
-      <c r="B34" s="109"/>
+      <c r="B34" s="108"/>
       <c r="C34" s="48" t="str">
-        <f>master!C14</f>
-        <v>2.2.データ型２</v>
-      </c>
-      <c r="D34" s="105" t="s">
-        <v>108</v>
-      </c>
-      <c r="E34" s="106"/>
-      <c r="F34" s="107"/>
+        <f>master!C15</f>
+        <v>2.3.リレーション</v>
+      </c>
+      <c r="D34" s="104" t="s">
+        <v>109</v>
+      </c>
+      <c r="E34" s="105"/>
+      <c r="F34" s="106"/>
       <c r="G34" s="48" t="s">
         <v>42</v>
       </c>
@@ -7427,7 +7332,7 @@
         <v>24</v>
       </c>
       <c r="J34" s="44">
-        <v>2.0833333333333333E-3</v>
+        <v>3.472222222222222E-3</v>
       </c>
       <c r="K34" s="40"/>
       <c r="L34" s="6"/>
@@ -7438,14 +7343,14 @@
       <c r="A35" s="11"/>
       <c r="B35" s="109"/>
       <c r="C35" s="48" t="str">
-        <f>master!C15</f>
-        <v>2.3.リレーション</v>
-      </c>
-      <c r="D35" s="105" t="s">
-        <v>109</v>
-      </c>
-      <c r="E35" s="106"/>
-      <c r="F35" s="107"/>
+        <f>master!C16</f>
+        <v>2.4.データを結合して取得（Join）</v>
+      </c>
+      <c r="D35" s="104" t="s">
+        <v>110</v>
+      </c>
+      <c r="E35" s="105"/>
+      <c r="F35" s="106"/>
       <c r="G35" s="48" t="s">
         <v>42</v>
       </c>
@@ -7454,27 +7359,30 @@
         <v>24</v>
       </c>
       <c r="J35" s="44">
-        <v>3.472222222222222E-3</v>
+        <v>2.0833333333333333E-3</v>
       </c>
       <c r="K35" s="40"/>
       <c r="L35" s="6"/>
       <c r="M35" s="6"/>
       <c r="N35" s="6"/>
     </row>
-    <row r="36" spans="1:14" ht="37.799999999999997">
+    <row r="36" spans="1:14" ht="88.2">
       <c r="A36" s="11"/>
-      <c r="B36" s="110"/>
+      <c r="B36" s="107" t="str">
+        <f>master!B17</f>
+        <v>Java言語、Springフレームワークとは</v>
+      </c>
       <c r="C36" s="48" t="str">
-        <f>master!C16</f>
-        <v>2.4.データを結合して取得（Join）</v>
-      </c>
-      <c r="D36" s="105" t="s">
-        <v>110</v>
-      </c>
-      <c r="E36" s="106"/>
-      <c r="F36" s="107"/>
+        <f>master!C17</f>
+        <v>Webアプリケーションを作成するためのプログラミング言語</v>
+      </c>
+      <c r="D36" s="104" t="s">
+        <v>111</v>
+      </c>
+      <c r="E36" s="105"/>
+      <c r="F36" s="106"/>
       <c r="G36" s="48" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="H36" s="12"/>
       <c r="I36" s="46" t="s">
@@ -7488,30 +7396,27 @@
       <c r="M36" s="6"/>
       <c r="N36" s="6"/>
     </row>
-    <row r="37" spans="1:14" ht="88.2">
+    <row r="37" spans="1:14" ht="75.599999999999994">
       <c r="A37" s="11"/>
-      <c r="B37" s="108" t="str">
-        <f>master!B17</f>
-        <v>Java言語、Springフレームワークとは</v>
-      </c>
+      <c r="B37" s="108"/>
       <c r="C37" s="48" t="str">
-        <f>master!C17</f>
-        <v>Webアプリケーションを作成するためのプログラミング言語</v>
-      </c>
-      <c r="D37" s="105" t="s">
-        <v>111</v>
-      </c>
-      <c r="E37" s="106"/>
-      <c r="F37" s="107"/>
+        <f>master!C18</f>
+        <v>Java</v>
+      </c>
+      <c r="D37" s="104" t="s">
+        <v>112</v>
+      </c>
+      <c r="E37" s="105"/>
+      <c r="F37" s="106"/>
       <c r="G37" s="48" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="H37" s="12"/>
       <c r="I37" s="46" t="s">
         <v>24</v>
       </c>
       <c r="J37" s="44">
-        <v>2.0833333333333333E-3</v>
+        <v>3.472222222222222E-3</v>
       </c>
       <c r="K37" s="40"/>
       <c r="L37" s="6"/>
@@ -7520,16 +7425,16 @@
     </row>
     <row r="38" spans="1:14" ht="75.599999999999994">
       <c r="A38" s="11"/>
-      <c r="B38" s="109"/>
+      <c r="B38" s="108"/>
       <c r="C38" s="48" t="str">
-        <f>master!C18</f>
-        <v>Java</v>
-      </c>
-      <c r="D38" s="105" t="s">
-        <v>112</v>
-      </c>
-      <c r="E38" s="106"/>
-      <c r="F38" s="107"/>
+        <f>master!C19</f>
+        <v>Java言語の構成要素</v>
+      </c>
+      <c r="D38" s="104" t="s">
+        <v>113</v>
+      </c>
+      <c r="E38" s="105"/>
+      <c r="F38" s="106"/>
       <c r="G38" s="48" t="s">
         <v>44</v>
       </c>
@@ -7538,54 +7443,54 @@
         <v>24</v>
       </c>
       <c r="J38" s="44">
-        <v>3.472222222222222E-3</v>
+        <v>2.0833333333333333E-3</v>
       </c>
       <c r="K38" s="40"/>
       <c r="L38" s="6"/>
       <c r="M38" s="6"/>
       <c r="N38" s="6"/>
     </row>
-    <row r="39" spans="1:14" ht="75.599999999999994">
+    <row r="39" spans="1:14" ht="50.4">
       <c r="A39" s="11"/>
-      <c r="B39" s="109"/>
+      <c r="B39" s="108"/>
       <c r="C39" s="48" t="str">
-        <f>master!C19</f>
-        <v>Java言語の構成要素</v>
-      </c>
-      <c r="D39" s="105" t="s">
-        <v>113</v>
-      </c>
-      <c r="E39" s="106"/>
-      <c r="F39" s="107"/>
+        <f>master!C20</f>
+        <v>Webアプリケーションを構成するクラス</v>
+      </c>
+      <c r="D39" s="104" t="s">
+        <v>114</v>
+      </c>
+      <c r="E39" s="105"/>
+      <c r="F39" s="106"/>
       <c r="G39" s="48" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H39" s="12"/>
       <c r="I39" s="46" t="s">
         <v>24</v>
       </c>
       <c r="J39" s="44">
-        <v>2.0833333333333333E-3</v>
+        <v>3.472222222222222E-3</v>
       </c>
       <c r="K39" s="40"/>
       <c r="L39" s="6"/>
       <c r="M39" s="6"/>
       <c r="N39" s="6"/>
     </row>
-    <row r="40" spans="1:14" ht="50.4">
+    <row r="40" spans="1:14" ht="88.2">
       <c r="A40" s="11"/>
-      <c r="B40" s="109"/>
+      <c r="B40" s="108"/>
       <c r="C40" s="48" t="str">
-        <f>master!C20</f>
-        <v>Webアプリケーションを構成するクラス</v>
-      </c>
-      <c r="D40" s="105" t="s">
-        <v>114</v>
-      </c>
-      <c r="E40" s="106"/>
-      <c r="F40" s="107"/>
+        <f>master!C21</f>
+        <v>Nレイヤーアーキテクチャ</v>
+      </c>
+      <c r="D40" s="104" t="s">
+        <v>116</v>
+      </c>
+      <c r="E40" s="105"/>
+      <c r="F40" s="106"/>
       <c r="G40" s="48" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="H40" s="12"/>
       <c r="I40" s="46" t="s">
@@ -7594,162 +7499,162 @@
       <c r="J40" s="44">
         <v>3.472222222222222E-3</v>
       </c>
-      <c r="K40" s="40"/>
+      <c r="K40" s="40" t="s">
+        <v>115</v>
+      </c>
       <c r="L40" s="6"/>
       <c r="M40" s="6"/>
       <c r="N40" s="6"/>
     </row>
-    <row r="41" spans="1:14" ht="88.2">
+    <row r="41" spans="1:14" ht="201.6">
       <c r="A41" s="11"/>
-      <c r="B41" s="109"/>
+      <c r="B41" s="108"/>
       <c r="C41" s="48" t="str">
-        <f>master!C21</f>
-        <v>Nレイヤーアーキテクチャ</v>
-      </c>
-      <c r="D41" s="105" t="s">
-        <v>116</v>
-      </c>
-      <c r="E41" s="106"/>
-      <c r="F41" s="107"/>
+        <f>master!C22</f>
+        <v>View と Controller と Service と Repository</v>
+      </c>
+      <c r="D41" s="104" t="s">
+        <v>117</v>
+      </c>
+      <c r="E41" s="105"/>
+      <c r="F41" s="106"/>
       <c r="G41" s="48" t="s">
-        <v>46</v>
+        <v>118</v>
       </c>
       <c r="H41" s="12"/>
       <c r="I41" s="46" t="s">
-        <v>24</v>
+        <v>49</v>
       </c>
       <c r="J41" s="44">
         <v>3.472222222222222E-3</v>
       </c>
-      <c r="K41" s="40" t="s">
-        <v>115</v>
-      </c>
+      <c r="K41" s="40"/>
       <c r="L41" s="6"/>
       <c r="M41" s="6"/>
       <c r="N41" s="6"/>
     </row>
-    <row r="42" spans="1:14" ht="201.6">
+    <row r="42" spans="1:14" ht="37.799999999999997">
       <c r="A42" s="11"/>
-      <c r="B42" s="109"/>
+      <c r="B42" s="108"/>
       <c r="C42" s="48" t="str">
-        <f>master!C22</f>
-        <v>View と Controller と Service と Repository</v>
-      </c>
-      <c r="D42" s="105" t="s">
-        <v>117</v>
-      </c>
-      <c r="E42" s="106"/>
-      <c r="F42" s="107"/>
+        <f>master!C23</f>
+        <v>Nレイヤーアーキテクチャ</v>
+      </c>
+      <c r="D42" s="104" t="s">
+        <v>119</v>
+      </c>
+      <c r="E42" s="105"/>
+      <c r="F42" s="106"/>
       <c r="G42" s="48" t="s">
-        <v>118</v>
+        <v>42</v>
       </c>
       <c r="H42" s="12"/>
       <c r="I42" s="46" t="s">
-        <v>49</v>
+        <v>24</v>
       </c>
       <c r="J42" s="44">
-        <v>3.472222222222222E-3</v>
+        <v>2.0833333333333333E-3</v>
       </c>
       <c r="K42" s="40"/>
       <c r="L42" s="6"/>
       <c r="M42" s="6"/>
       <c r="N42" s="6"/>
     </row>
-    <row r="43" spans="1:14" ht="37.799999999999997">
+    <row r="43" spans="1:14" ht="163.80000000000001">
       <c r="A43" s="11"/>
-      <c r="B43" s="109"/>
+      <c r="B43" s="108"/>
       <c r="C43" s="48" t="str">
-        <f>master!C23</f>
-        <v>Nレイヤーアーキテクチャ</v>
-      </c>
-      <c r="D43" s="105" t="s">
-        <v>119</v>
-      </c>
-      <c r="E43" s="106"/>
-      <c r="F43" s="107"/>
+        <f>master!C24</f>
+        <v>Webアプリケーション フレームワーク</v>
+      </c>
+      <c r="D43" s="104" t="s">
+        <v>120</v>
+      </c>
+      <c r="E43" s="105"/>
+      <c r="F43" s="106"/>
       <c r="G43" s="48" t="s">
-        <v>42</v>
+        <v>121</v>
       </c>
       <c r="H43" s="12"/>
       <c r="I43" s="46" t="s">
         <v>24</v>
       </c>
       <c r="J43" s="44">
-        <v>2.0833333333333333E-3</v>
+        <v>3.472222222222222E-3</v>
       </c>
       <c r="K43" s="40"/>
       <c r="L43" s="6"/>
       <c r="M43" s="6"/>
       <c r="N43" s="6"/>
     </row>
-    <row r="44" spans="1:14" ht="163.80000000000001">
+    <row r="44" spans="1:14" ht="25.2">
       <c r="A44" s="11"/>
-      <c r="B44" s="109"/>
+      <c r="B44" s="108"/>
       <c r="C44" s="48" t="str">
-        <f>master!C24</f>
-        <v>Webアプリケーション フレームワーク</v>
-      </c>
-      <c r="D44" s="105" t="s">
-        <v>120</v>
-      </c>
-      <c r="E44" s="106"/>
-      <c r="F44" s="107"/>
+        <f>master!C25</f>
+        <v>Java向けWebアプリケーションフレームワーク</v>
+      </c>
+      <c r="D44" s="104" t="s">
+        <v>122</v>
+      </c>
+      <c r="E44" s="105"/>
+      <c r="F44" s="106"/>
       <c r="G44" s="48" t="s">
-        <v>121</v>
+        <v>47</v>
       </c>
       <c r="H44" s="12"/>
       <c r="I44" s="46" t="s">
         <v>24</v>
       </c>
       <c r="J44" s="44">
-        <v>3.472222222222222E-3</v>
+        <v>6.9444444444444447E-4</v>
       </c>
       <c r="K44" s="40"/>
       <c r="L44" s="6"/>
       <c r="M44" s="6"/>
       <c r="N44" s="6"/>
     </row>
-    <row r="45" spans="1:14" ht="25.2">
+    <row r="45" spans="1:14" ht="189">
       <c r="A45" s="11"/>
-      <c r="B45" s="109"/>
+      <c r="B45" s="108"/>
       <c r="C45" s="48" t="str">
-        <f>master!C25</f>
-        <v>Java向けWebアプリケーションフレームワーク</v>
-      </c>
-      <c r="D45" s="105" t="s">
-        <v>122</v>
-      </c>
-      <c r="E45" s="106"/>
-      <c r="F45" s="107"/>
+        <f>master!C26</f>
+        <v>Springフレームワーク</v>
+      </c>
+      <c r="D45" s="104" t="s">
+        <v>123</v>
+      </c>
+      <c r="E45" s="105"/>
+      <c r="F45" s="106"/>
       <c r="G45" s="48" t="s">
-        <v>47</v>
+        <v>124</v>
       </c>
       <c r="H45" s="12"/>
       <c r="I45" s="46" t="s">
         <v>24</v>
       </c>
       <c r="J45" s="44">
-        <v>6.9444444444444447E-4</v>
+        <v>3.472222222222222E-3</v>
       </c>
       <c r="K45" s="40"/>
       <c r="L45" s="6"/>
       <c r="M45" s="6"/>
       <c r="N45" s="6"/>
     </row>
-    <row r="46" spans="1:14" ht="189">
+    <row r="46" spans="1:14" ht="88.2">
       <c r="A46" s="11"/>
-      <c r="B46" s="109"/>
+      <c r="B46" s="108"/>
       <c r="C46" s="48" t="str">
-        <f>master!C26</f>
-        <v>Springフレームワーク</v>
-      </c>
-      <c r="D46" s="105" t="s">
-        <v>123</v>
-      </c>
-      <c r="E46" s="106"/>
-      <c r="F46" s="107"/>
+        <f>master!C27</f>
+        <v>Springフレームワーク：DIコンテナとは</v>
+      </c>
+      <c r="D46" s="104" t="s">
+        <v>125</v>
+      </c>
+      <c r="E46" s="105"/>
+      <c r="F46" s="106"/>
       <c r="G46" s="48" t="s">
-        <v>124</v>
+        <v>46</v>
       </c>
       <c r="H46" s="12"/>
       <c r="I46" s="46" t="s">
@@ -7758,54 +7663,54 @@
       <c r="J46" s="44">
         <v>3.472222222222222E-3</v>
       </c>
-      <c r="K46" s="40"/>
+      <c r="K46" s="40" t="s">
+        <v>115</v>
+      </c>
       <c r="L46" s="6"/>
       <c r="M46" s="6"/>
       <c r="N46" s="6"/>
     </row>
-    <row r="47" spans="1:14" ht="88.2">
+    <row r="47" spans="1:14" ht="63">
       <c r="A47" s="11"/>
-      <c r="B47" s="109"/>
+      <c r="B47" s="108"/>
       <c r="C47" s="48" t="str">
-        <f>master!C27</f>
-        <v>Springフレームワーク：DIコンテナとは</v>
-      </c>
-      <c r="D47" s="105" t="s">
-        <v>125</v>
-      </c>
-      <c r="E47" s="106"/>
-      <c r="F47" s="107"/>
+        <f>master!C28</f>
+        <v>DIコンテナ：DIコンテナが部品を注入する</v>
+      </c>
+      <c r="D47" s="104" t="s">
+        <v>126</v>
+      </c>
+      <c r="E47" s="105"/>
+      <c r="F47" s="106"/>
       <c r="G47" s="48" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="H47" s="12"/>
       <c r="I47" s="46" t="s">
         <v>24</v>
       </c>
       <c r="J47" s="44">
-        <v>3.472222222222222E-3</v>
-      </c>
-      <c r="K47" s="40" t="s">
-        <v>115</v>
-      </c>
+        <v>2.0833333333333333E-3</v>
+      </c>
+      <c r="K47" s="40"/>
       <c r="L47" s="6"/>
       <c r="M47" s="6"/>
       <c r="N47" s="6"/>
     </row>
-    <row r="48" spans="1:14" ht="63">
+    <row r="48" spans="1:14" ht="100.8">
       <c r="A48" s="11"/>
-      <c r="B48" s="109"/>
+      <c r="B48" s="108"/>
       <c r="C48" s="48" t="str">
-        <f>master!C28</f>
-        <v>DIコンテナ：DIコンテナが部品を注入する</v>
-      </c>
-      <c r="D48" s="105" t="s">
-        <v>126</v>
-      </c>
-      <c r="E48" s="106"/>
-      <c r="F48" s="107"/>
+        <f>master!C29</f>
+        <v>DIコンテナ：DIコンテナによる部品と注入対象になるための目印</v>
+      </c>
+      <c r="D48" s="104" t="s">
+        <v>127</v>
+      </c>
+      <c r="E48" s="105"/>
+      <c r="F48" s="106"/>
       <c r="G48" s="48" t="s">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="H48" s="12"/>
       <c r="I48" s="46" t="s">
@@ -7821,16 +7726,16 @@
     </row>
     <row r="49" spans="1:14" ht="100.8">
       <c r="A49" s="11"/>
-      <c r="B49" s="109"/>
+      <c r="B49" s="108"/>
       <c r="C49" s="48" t="str">
-        <f>master!C29</f>
-        <v>DIコンテナ：DIコンテナによる部品と注入対象になるための目印</v>
-      </c>
-      <c r="D49" s="105" t="s">
-        <v>127</v>
-      </c>
-      <c r="E49" s="106"/>
-      <c r="F49" s="107"/>
+        <f>master!C30</f>
+        <v>Springフレームワークにおける部品の設定</v>
+      </c>
+      <c r="D49" s="104" t="s">
+        <v>128</v>
+      </c>
+      <c r="E49" s="105"/>
+      <c r="F49" s="106"/>
       <c r="G49" s="48" t="s">
         <v>48</v>
       </c>
@@ -7846,20 +7751,20 @@
       <c r="M49" s="6"/>
       <c r="N49" s="6"/>
     </row>
-    <row r="50" spans="1:14" ht="100.8">
+    <row r="50" spans="1:14" ht="88.2">
       <c r="A50" s="11"/>
-      <c r="B50" s="109"/>
+      <c r="B50" s="108"/>
       <c r="C50" s="48" t="str">
-        <f>master!C30</f>
-        <v>Springフレームワークにおける部品の設定</v>
-      </c>
-      <c r="D50" s="105" t="s">
-        <v>128</v>
-      </c>
-      <c r="E50" s="106"/>
-      <c r="F50" s="107"/>
+        <f>master!C31</f>
+        <v>Spring Boot</v>
+      </c>
+      <c r="D50" s="104" t="s">
+        <v>129</v>
+      </c>
+      <c r="E50" s="105"/>
+      <c r="F50" s="106"/>
       <c r="G50" s="48" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="H50" s="12"/>
       <c r="I50" s="46" t="s">
@@ -7873,20 +7778,20 @@
       <c r="M50" s="6"/>
       <c r="N50" s="6"/>
     </row>
-    <row r="51" spans="1:14" ht="88.2">
+    <row r="51" spans="1:14" ht="63">
       <c r="A51" s="11"/>
-      <c r="B51" s="109"/>
+      <c r="B51" s="108"/>
       <c r="C51" s="48" t="str">
-        <f>master!C31</f>
-        <v>Spring Boot</v>
-      </c>
-      <c r="D51" s="105" t="s">
-        <v>129</v>
-      </c>
-      <c r="E51" s="106"/>
-      <c r="F51" s="107"/>
+        <f>master!C32</f>
+        <v>Spring Boot：オートコンフィグレーション</v>
+      </c>
+      <c r="D51" s="104" t="s">
+        <v>130</v>
+      </c>
+      <c r="E51" s="105"/>
+      <c r="F51" s="106"/>
       <c r="G51" s="48" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="H51" s="12"/>
       <c r="I51" s="46" t="s">
@@ -7900,47 +7805,47 @@
       <c r="M51" s="6"/>
       <c r="N51" s="6"/>
     </row>
-    <row r="52" spans="1:14" ht="63">
+    <row r="52" spans="1:14" ht="50.4">
       <c r="A52" s="11"/>
-      <c r="B52" s="109"/>
+      <c r="B52" s="108"/>
       <c r="C52" s="48" t="str">
-        <f>master!C32</f>
-        <v>Spring Boot：オートコンフィグレーション</v>
-      </c>
-      <c r="D52" s="105" t="s">
-        <v>130</v>
-      </c>
-      <c r="E52" s="106"/>
-      <c r="F52" s="107"/>
+        <f>master!C33</f>
+        <v>Spring Boot：Starters</v>
+      </c>
+      <c r="D52" s="104" t="s">
+        <v>131</v>
+      </c>
+      <c r="E52" s="105"/>
+      <c r="F52" s="106"/>
       <c r="G52" s="48" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="H52" s="12"/>
       <c r="I52" s="46" t="s">
         <v>24</v>
       </c>
       <c r="J52" s="44">
-        <v>2.0833333333333333E-3</v>
+        <v>1.3888888888888889E-3</v>
       </c>
       <c r="K52" s="40"/>
       <c r="L52" s="6"/>
       <c r="M52" s="6"/>
       <c r="N52" s="6"/>
     </row>
-    <row r="53" spans="1:14" ht="50.4">
+    <row r="53" spans="1:14" ht="88.2">
       <c r="A53" s="11"/>
-      <c r="B53" s="109"/>
+      <c r="B53" s="108"/>
       <c r="C53" s="48" t="str">
-        <f>master!C33</f>
-        <v>Spring Boot：Starters</v>
-      </c>
-      <c r="D53" s="105" t="s">
-        <v>131</v>
-      </c>
-      <c r="E53" s="106"/>
-      <c r="F53" s="107"/>
+        <f>master!C34</f>
+        <v>Spring Boot：組込みWebAPサーバ</v>
+      </c>
+      <c r="D53" s="104" t="s">
+        <v>132</v>
+      </c>
+      <c r="E53" s="105"/>
+      <c r="F53" s="106"/>
       <c r="G53" s="48" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="H53" s="12"/>
       <c r="I53" s="46" t="s">
@@ -7954,75 +7859,75 @@
       <c r="M53" s="6"/>
       <c r="N53" s="6"/>
     </row>
-    <row r="54" spans="1:14" ht="88.2">
+    <row r="54" spans="1:14" ht="25.2">
       <c r="A54" s="11"/>
       <c r="B54" s="109"/>
       <c r="C54" s="48" t="str">
-        <f>master!C34</f>
-        <v>Spring Boot：組込みWebAPサーバ</v>
-      </c>
-      <c r="D54" s="105" t="s">
-        <v>132</v>
-      </c>
-      <c r="E54" s="106"/>
-      <c r="F54" s="107"/>
+        <f>master!C35</f>
+        <v>おすすめ書籍：『プロになるためのSpring入門』</v>
+      </c>
+      <c r="D54" s="104"/>
+      <c r="E54" s="105"/>
+      <c r="F54" s="106"/>
       <c r="G54" s="48" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H54" s="12"/>
       <c r="I54" s="46" t="s">
         <v>24</v>
       </c>
       <c r="J54" s="44">
-        <v>1.3888888888888889E-3</v>
+        <v>6.9444444444444447E-4</v>
       </c>
       <c r="K54" s="40"/>
       <c r="L54" s="6"/>
       <c r="M54" s="6"/>
       <c r="N54" s="6"/>
     </row>
-    <row r="55" spans="1:14" ht="25.2">
+    <row r="55" spans="1:14" ht="37.799999999999997">
       <c r="A55" s="11"/>
-      <c r="B55" s="110"/>
-      <c r="C55" s="48" t="str">
-        <f>master!C35</f>
-        <v>おすすめ書籍：『プロになるためのSpring入門』</v>
-      </c>
-      <c r="D55" s="105"/>
-      <c r="E55" s="106"/>
-      <c r="F55" s="107"/>
-      <c r="G55" s="48" t="s">
-        <v>47</v>
-      </c>
-      <c r="H55" s="12"/>
-      <c r="I55" s="46" t="s">
-        <v>24</v>
-      </c>
-      <c r="J55" s="44">
+      <c r="B55" s="113" t="str">
+        <f>master!B37</f>
+        <v>課題1の導入</v>
+      </c>
+      <c r="C55" s="58" t="str">
+        <f>master!C37</f>
+        <v>演習課題の概要</v>
+      </c>
+      <c r="D55" s="110" t="s">
+        <v>165</v>
+      </c>
+      <c r="E55" s="111"/>
+      <c r="F55" s="112"/>
+      <c r="G55" s="58" t="s">
+        <v>288</v>
+      </c>
+      <c r="H55" s="59"/>
+      <c r="I55" s="60" t="s">
+        <v>24</v>
+      </c>
+      <c r="J55" s="61">
         <v>6.9444444444444447E-4</v>
       </c>
-      <c r="K55" s="40"/>
+      <c r="K55" s="62"/>
       <c r="L55" s="6"/>
       <c r="M55" s="6"/>
       <c r="N55" s="6"/>
     </row>
     <row r="56" spans="1:14" ht="37.799999999999997">
       <c r="A56" s="11"/>
-      <c r="B56" s="114" t="str">
-        <f>master!B37</f>
-        <v>課題1の導入</v>
-      </c>
+      <c r="B56" s="114"/>
       <c r="C56" s="58" t="str">
-        <f>master!C37</f>
-        <v>演習課題の概要</v>
-      </c>
-      <c r="D56" s="111" t="s">
-        <v>165</v>
-      </c>
-      <c r="E56" s="112"/>
-      <c r="F56" s="113"/>
+        <f>master!C38</f>
+        <v>作成物</v>
+      </c>
+      <c r="D56" s="110" t="s">
+        <v>166</v>
+      </c>
+      <c r="E56" s="111"/>
+      <c r="F56" s="112"/>
       <c r="G56" s="58" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="H56" s="59"/>
       <c r="I56" s="60" t="s">
@@ -8036,18 +7941,18 @@
       <c r="M56" s="6"/>
       <c r="N56" s="6"/>
     </row>
-    <row r="57" spans="1:14" ht="37.799999999999997">
+    <row r="57" spans="1:14" ht="75.599999999999994">
       <c r="A57" s="11"/>
       <c r="B57" s="115"/>
       <c r="C57" s="58" t="str">
-        <f>master!C38</f>
-        <v>作成物</v>
-      </c>
-      <c r="D57" s="111" t="s">
-        <v>166</v>
-      </c>
-      <c r="E57" s="112"/>
-      <c r="F57" s="113"/>
+        <f>master!C39</f>
+        <v>演習課題の進め方</v>
+      </c>
+      <c r="D57" s="110" t="s">
+        <v>167</v>
+      </c>
+      <c r="E57" s="111"/>
+      <c r="F57" s="112"/>
       <c r="G57" s="58" t="s">
         <v>289</v>
       </c>
@@ -8056,25 +7961,26 @@
         <v>24</v>
       </c>
       <c r="J57" s="61">
-        <v>6.9444444444444447E-4</v>
+        <v>1.3888888888888888E-2</v>
       </c>
       <c r="K57" s="62"/>
       <c r="L57" s="6"/>
       <c r="M57" s="6"/>
       <c r="N57" s="6"/>
     </row>
-    <row r="58" spans="1:14" ht="75.599999999999994">
+    <row r="58" spans="1:14" ht="15" customHeight="1">
       <c r="A58" s="11"/>
-      <c r="B58" s="116"/>
+      <c r="B58" s="113" t="str">
+        <f>master!B40</f>
+        <v>Spring Bootプロジェクトの_x000B_準備、起動確認</v>
+      </c>
       <c r="C58" s="58" t="str">
-        <f>master!C39</f>
-        <v>演習課題の進め方</v>
-      </c>
-      <c r="D58" s="111" t="s">
-        <v>167</v>
-      </c>
-      <c r="E58" s="112"/>
-      <c r="F58" s="113"/>
+        <f>master!C40</f>
+        <v>前提条件</v>
+      </c>
+      <c r="D58" s="110"/>
+      <c r="E58" s="111"/>
+      <c r="F58" s="112"/>
       <c r="G58" s="58" t="s">
         <v>290</v>
       </c>
@@ -8083,80 +7989,79 @@
         <v>24</v>
       </c>
       <c r="J58" s="61">
-        <v>1.3888888888888888E-2</v>
+        <v>6.9444444444444447E-4</v>
       </c>
       <c r="K58" s="62"/>
       <c r="L58" s="6"/>
       <c r="M58" s="6"/>
       <c r="N58" s="6"/>
     </row>
-    <row r="59" spans="1:14" ht="15" customHeight="1">
+    <row r="59" spans="1:14" ht="37.799999999999997">
       <c r="A59" s="11"/>
-      <c r="B59" s="114" t="str">
-        <f>master!B40</f>
-        <v>Spring Bootプロジェクトの_x000B_準備、起動確認</v>
-      </c>
+      <c r="B59" s="114"/>
       <c r="C59" s="58" t="str">
-        <f>master!C40</f>
-        <v>前提条件</v>
-      </c>
-      <c r="D59" s="111"/>
-      <c r="E59" s="112"/>
-      <c r="F59" s="113"/>
+        <f>master!C41</f>
+        <v>Spring Bootプロジェクトの準備</v>
+      </c>
+      <c r="D59" s="110" t="s">
+        <v>168</v>
+      </c>
+      <c r="E59" s="111"/>
+      <c r="F59" s="112"/>
       <c r="G59" s="58" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="H59" s="59"/>
       <c r="I59" s="60" t="s">
         <v>24</v>
       </c>
       <c r="J59" s="61">
-        <v>6.9444444444444447E-4</v>
+        <v>6.9444444444444441E-3</v>
       </c>
       <c r="K59" s="62"/>
       <c r="L59" s="6"/>
       <c r="M59" s="6"/>
       <c r="N59" s="6"/>
     </row>
-    <row r="60" spans="1:14" ht="37.799999999999997">
+    <row r="60" spans="1:14" ht="25.2">
       <c r="A60" s="11"/>
-      <c r="B60" s="115"/>
+      <c r="B60" s="114"/>
       <c r="C60" s="58" t="str">
-        <f>master!C41</f>
-        <v>Spring Bootプロジェクトの準備</v>
-      </c>
-      <c r="D60" s="111" t="s">
-        <v>168</v>
-      </c>
-      <c r="E60" s="112"/>
-      <c r="F60" s="113"/>
+        <f>master!C42</f>
+        <v>（補足）Spring Bootプロジェクトの準備</v>
+      </c>
+      <c r="D60" s="110" t="s">
+        <v>169</v>
+      </c>
+      <c r="E60" s="111"/>
+      <c r="F60" s="112"/>
       <c r="G60" s="58" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="H60" s="59"/>
       <c r="I60" s="60" t="s">
-        <v>24</v>
+        <v>49</v>
       </c>
       <c r="J60" s="61">
-        <v>6.9444444444444441E-3</v>
+        <v>0</v>
       </c>
       <c r="K60" s="62"/>
       <c r="L60" s="6"/>
       <c r="M60" s="6"/>
       <c r="N60" s="6"/>
     </row>
-    <row r="61" spans="1:14" ht="25.2">
+    <row r="61" spans="1:14" ht="88.2">
       <c r="A61" s="11"/>
       <c r="B61" s="115"/>
       <c r="C61" s="58" t="str">
-        <f>master!C42</f>
-        <v>（補足）Spring Bootプロジェクトの準備</v>
-      </c>
-      <c r="D61" s="111" t="s">
-        <v>169</v>
-      </c>
-      <c r="E61" s="112"/>
-      <c r="F61" s="113"/>
+        <f>master!C43</f>
+        <v>Spring Bootアプリケーションの起動確認</v>
+      </c>
+      <c r="D61" s="110" t="s">
+        <v>191</v>
+      </c>
+      <c r="E61" s="111"/>
+      <c r="F61" s="112"/>
       <c r="G61" s="58" t="s">
         <v>292</v>
       </c>
@@ -8165,55 +8070,55 @@
         <v>49</v>
       </c>
       <c r="J61" s="61">
-        <v>0</v>
+        <v>6.9444444444444441E-3</v>
       </c>
       <c r="K61" s="62"/>
       <c r="L61" s="6"/>
       <c r="M61" s="6"/>
       <c r="N61" s="6"/>
     </row>
-    <row r="62" spans="1:14" ht="88.2">
+    <row r="62" spans="1:14" ht="190.2" customHeight="1">
       <c r="A62" s="11"/>
-      <c r="B62" s="116"/>
+      <c r="B62" s="113" t="str">
+        <f>master!B44</f>
+        <v>ECサイト Webアプリの要件</v>
+      </c>
       <c r="C62" s="58" t="str">
-        <f>master!C43</f>
-        <v>Spring Bootアプリケーションの起動確認</v>
-      </c>
-      <c r="D62" s="111" t="s">
-        <v>191</v>
-      </c>
-      <c r="E62" s="112"/>
-      <c r="F62" s="113"/>
+        <f>master!C44</f>
+        <v>ECサイト Webアプリの要件 – はじめに</v>
+      </c>
+      <c r="D62" s="110" t="s">
+        <v>170</v>
+      </c>
+      <c r="E62" s="111"/>
+      <c r="F62" s="112"/>
       <c r="G62" s="58" t="s">
         <v>293</v>
       </c>
       <c r="H62" s="59"/>
       <c r="I62" s="60" t="s">
-        <v>49</v>
+        <v>24</v>
       </c>
       <c r="J62" s="61">
-        <v>6.9444444444444441E-3</v>
+        <v>6.9444444444444447E-4</v>
       </c>
       <c r="K62" s="62"/>
       <c r="L62" s="6"/>
       <c r="M62" s="6"/>
       <c r="N62" s="6"/>
     </row>
-    <row r="63" spans="1:14" ht="190.2" customHeight="1">
+    <row r="63" spans="1:14" ht="151.19999999999999">
       <c r="A63" s="11"/>
-      <c r="B63" s="114" t="str">
-        <f>master!B44</f>
-        <v>ECサイト Webアプリの要件</v>
-      </c>
+      <c r="B63" s="114"/>
       <c r="C63" s="58" t="str">
-        <f>master!C44</f>
-        <v>ECサイト Webアプリの要件 – はじめに</v>
-      </c>
-      <c r="D63" s="111" t="s">
-        <v>170</v>
-      </c>
-      <c r="E63" s="112"/>
-      <c r="F63" s="113"/>
+        <f>master!C45</f>
+        <v>ECサイト Webアプリの要件➊ 画面</v>
+      </c>
+      <c r="D63" s="110" t="s">
+        <v>172</v>
+      </c>
+      <c r="E63" s="111"/>
+      <c r="F63" s="112"/>
       <c r="G63" s="58" t="s">
         <v>294</v>
       </c>
@@ -8229,18 +8134,18 @@
       <c r="M63" s="6"/>
       <c r="N63" s="6"/>
     </row>
-    <row r="64" spans="1:14" ht="151.19999999999999">
+    <row r="64" spans="1:14" ht="214.2">
       <c r="A64" s="11"/>
-      <c r="B64" s="115"/>
+      <c r="B64" s="114"/>
       <c r="C64" s="58" t="str">
-        <f>master!C45</f>
-        <v>ECサイト Webアプリの要件➊ 画面</v>
-      </c>
-      <c r="D64" s="111" t="s">
-        <v>172</v>
-      </c>
-      <c r="E64" s="112"/>
-      <c r="F64" s="113"/>
+        <f>master!C46</f>
+        <v>ECサイト Webアプリの要件➋ 機能</v>
+      </c>
+      <c r="D64" s="110" t="s">
+        <v>173</v>
+      </c>
+      <c r="E64" s="111"/>
+      <c r="F64" s="112"/>
       <c r="G64" s="58" t="s">
         <v>295</v>
       </c>
@@ -8256,18 +8161,18 @@
       <c r="M64" s="6"/>
       <c r="N64" s="6"/>
     </row>
-    <row r="65" spans="1:14" ht="214.2">
+    <row r="65" spans="1:14" ht="63">
       <c r="A65" s="11"/>
-      <c r="B65" s="115"/>
+      <c r="B65" s="114"/>
       <c r="C65" s="58" t="str">
-        <f>master!C46</f>
-        <v>ECサイト Webアプリの要件➋ 機能</v>
-      </c>
-      <c r="D65" s="111" t="s">
-        <v>173</v>
-      </c>
-      <c r="E65" s="112"/>
-      <c r="F65" s="113"/>
+        <f>master!C47</f>
+        <v>ECサイト Webアプリの要件➌ 画面遷移</v>
+      </c>
+      <c r="D65" s="110" t="s">
+        <v>174</v>
+      </c>
+      <c r="E65" s="111"/>
+      <c r="F65" s="112"/>
       <c r="G65" s="58" t="s">
         <v>296</v>
       </c>
@@ -8276,25 +8181,25 @@
         <v>24</v>
       </c>
       <c r="J65" s="61">
-        <v>6.9444444444444447E-4</v>
+        <v>1.3888888888888889E-3</v>
       </c>
       <c r="K65" s="62"/>
       <c r="L65" s="6"/>
       <c r="M65" s="6"/>
       <c r="N65" s="6"/>
     </row>
-    <row r="66" spans="1:14" ht="63">
+    <row r="66" spans="1:14" ht="163.80000000000001">
       <c r="A66" s="11"/>
-      <c r="B66" s="115"/>
+      <c r="B66" s="114"/>
       <c r="C66" s="58" t="str">
-        <f>master!C47</f>
-        <v>ECサイト Webアプリの要件➌ 画面遷移</v>
-      </c>
-      <c r="D66" s="111" t="s">
-        <v>174</v>
-      </c>
-      <c r="E66" s="112"/>
-      <c r="F66" s="113"/>
+        <f>master!C48</f>
+        <v>ECサイト Webアプリの要件❹ データ設計</v>
+      </c>
+      <c r="D66" s="110" t="s">
+        <v>176</v>
+      </c>
+      <c r="E66" s="111"/>
+      <c r="F66" s="112"/>
       <c r="G66" s="58" t="s">
         <v>297</v>
       </c>
@@ -8303,61 +8208,61 @@
         <v>24</v>
       </c>
       <c r="J66" s="61">
-        <v>1.3888888888888889E-3</v>
+        <v>2.0833333333333333E-3</v>
       </c>
       <c r="K66" s="62"/>
       <c r="L66" s="6"/>
       <c r="M66" s="6"/>
       <c r="N66" s="6"/>
     </row>
-    <row r="67" spans="1:14" ht="163.80000000000001">
+    <row r="67" spans="1:14" ht="50.4">
       <c r="A67" s="11"/>
-      <c r="B67" s="115"/>
+      <c r="B67" s="114"/>
       <c r="C67" s="58" t="str">
-        <f>master!C48</f>
-        <v>ECサイト Webアプリの要件❹ データ設計</v>
-      </c>
-      <c r="D67" s="111" t="s">
-        <v>176</v>
-      </c>
-      <c r="E67" s="112"/>
-      <c r="F67" s="113"/>
+        <f>master!C49</f>
+        <v>ECサイト Webアプリの要件❺ 初期データ</v>
+      </c>
+      <c r="D67" s="110" t="s">
+        <v>177</v>
+      </c>
+      <c r="E67" s="111"/>
+      <c r="F67" s="112"/>
       <c r="G67" s="58" t="s">
-        <v>298</v>
+        <v>293</v>
       </c>
       <c r="H67" s="59"/>
       <c r="I67" s="60" t="s">
         <v>24</v>
       </c>
       <c r="J67" s="61">
-        <v>2.0833333333333333E-3</v>
+        <v>6.9444444444444447E-4</v>
       </c>
       <c r="K67" s="62"/>
       <c r="L67" s="6"/>
       <c r="M67" s="6"/>
       <c r="N67" s="6"/>
     </row>
-    <row r="68" spans="1:14" ht="50.4">
+    <row r="68" spans="1:14" ht="37.799999999999997">
       <c r="A68" s="11"/>
-      <c r="B68" s="115"/>
+      <c r="B68" s="114"/>
       <c r="C68" s="58" t="str">
-        <f>master!C49</f>
-        <v>ECサイト Webアプリの要件❺ 初期データ</v>
-      </c>
-      <c r="D68" s="111" t="s">
-        <v>177</v>
-      </c>
-      <c r="E68" s="112"/>
-      <c r="F68" s="113"/>
+        <f>master!C50</f>
+        <v>ECサイト Webアプリの要件❻ ディレクトリ構成</v>
+      </c>
+      <c r="D68" s="110" t="s">
+        <v>178</v>
+      </c>
+      <c r="E68" s="111"/>
+      <c r="F68" s="112"/>
       <c r="G68" s="58" t="s">
-        <v>294</v>
+        <v>288</v>
       </c>
       <c r="H68" s="59"/>
       <c r="I68" s="60" t="s">
         <v>24</v>
       </c>
       <c r="J68" s="61">
-        <v>6.9444444444444447E-4</v>
+        <v>1.0416666666666666E-2</v>
       </c>
       <c r="K68" s="62"/>
       <c r="L68" s="6"/>
@@ -8366,25 +8271,25 @@
     </row>
     <row r="69" spans="1:14" ht="37.799999999999997">
       <c r="A69" s="11"/>
-      <c r="B69" s="115"/>
+      <c r="B69" s="114"/>
       <c r="C69" s="58" t="str">
-        <f>master!C50</f>
-        <v>ECサイト Webアプリの要件❻ ディレクトリ構成</v>
-      </c>
-      <c r="D69" s="111" t="s">
-        <v>178</v>
-      </c>
-      <c r="E69" s="112"/>
-      <c r="F69" s="113"/>
+        <f>master!C51</f>
+        <v>ECサイト Webアプリの要件❼ パッケージ構成</v>
+      </c>
+      <c r="D69" s="110" t="s">
+        <v>180</v>
+      </c>
+      <c r="E69" s="111"/>
+      <c r="F69" s="112"/>
       <c r="G69" s="58" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="H69" s="59"/>
       <c r="I69" s="60" t="s">
         <v>24</v>
       </c>
       <c r="J69" s="61">
-        <v>1.0416666666666666E-2</v>
+        <v>3.472222222222222E-3</v>
       </c>
       <c r="K69" s="62"/>
       <c r="L69" s="6"/>
@@ -8395,296 +8300,296 @@
       <c r="A70" s="11"/>
       <c r="B70" s="115"/>
       <c r="C70" s="58" t="str">
-        <f>master!C51</f>
-        <v>ECサイト Webアプリの要件❼ パッケージ構成</v>
-      </c>
-      <c r="D70" s="111" t="s">
-        <v>180</v>
-      </c>
-      <c r="E70" s="112"/>
-      <c r="F70" s="113"/>
+        <f>master!C52</f>
+        <v>ECサイト Webアプリの要件❽ リソース構成</v>
+      </c>
+      <c r="D70" s="110" t="s">
+        <v>179</v>
+      </c>
+      <c r="E70" s="111"/>
+      <c r="F70" s="112"/>
       <c r="G70" s="58" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="H70" s="59"/>
       <c r="I70" s="60" t="s">
         <v>24</v>
       </c>
       <c r="J70" s="61">
-        <v>3.472222222222222E-3</v>
+        <v>6.9444444444444447E-4</v>
       </c>
       <c r="K70" s="62"/>
       <c r="L70" s="6"/>
       <c r="M70" s="6"/>
       <c r="N70" s="6"/>
     </row>
-    <row r="71" spans="1:14" ht="37.799999999999997">
+    <row r="71" spans="1:14" ht="25.2">
       <c r="A71" s="11"/>
-      <c r="B71" s="116"/>
+      <c r="B71" s="113" t="str">
+        <f>master!B53</f>
+        <v>ハンズオン</v>
+      </c>
       <c r="C71" s="58" t="str">
-        <f>master!C52</f>
-        <v>ECサイト Webアプリの要件❽ リソース構成</v>
-      </c>
-      <c r="D71" s="111" t="s">
-        <v>179</v>
-      </c>
-      <c r="E71" s="112"/>
-      <c r="F71" s="113"/>
+        <f>master!C53</f>
+        <v>バイブコーディング – はじめに</v>
+      </c>
+      <c r="D71" s="110" t="s">
+        <v>181</v>
+      </c>
+      <c r="E71" s="111"/>
+      <c r="F71" s="112"/>
       <c r="G71" s="58" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="H71" s="59"/>
       <c r="I71" s="60" t="s">
         <v>24</v>
       </c>
       <c r="J71" s="61">
-        <v>6.9444444444444447E-4</v>
+        <v>1.0416666666666666E-2</v>
       </c>
       <c r="K71" s="62"/>
       <c r="L71" s="6"/>
       <c r="M71" s="6"/>
       <c r="N71" s="6"/>
     </row>
-    <row r="72" spans="1:14" ht="25.2">
+    <row r="72" spans="1:14" ht="138.6">
       <c r="A72" s="11"/>
-      <c r="B72" s="114" t="str">
-        <f>master!B53</f>
-        <v>ハンズオン</v>
-      </c>
+      <c r="B72" s="114"/>
       <c r="C72" s="58" t="str">
-        <f>master!C53</f>
-        <v>バイブコーディング – はじめに</v>
-      </c>
-      <c r="D72" s="111" t="s">
-        <v>181</v>
-      </c>
-      <c r="E72" s="112"/>
-      <c r="F72" s="113"/>
+        <f>master!C54</f>
+        <v>[構造理解] Webアプリケーションで必要なもの</v>
+      </c>
+      <c r="D72" s="110" t="s">
+        <v>182</v>
+      </c>
+      <c r="E72" s="111"/>
+      <c r="F72" s="112"/>
       <c r="G72" s="58" t="s">
-        <v>292</v>
+        <v>298</v>
       </c>
       <c r="H72" s="59"/>
       <c r="I72" s="60" t="s">
         <v>24</v>
       </c>
       <c r="J72" s="61">
-        <v>1.0416666666666666E-2</v>
+        <v>1.3888888888888889E-3</v>
       </c>
       <c r="K72" s="62"/>
       <c r="L72" s="6"/>
       <c r="M72" s="6"/>
       <c r="N72" s="6"/>
     </row>
-    <row r="73" spans="1:14" ht="138.6">
+    <row r="73" spans="1:14" ht="50.4">
       <c r="A73" s="11"/>
-      <c r="B73" s="115"/>
-      <c r="C73" s="58" t="str">
-        <f>master!C54</f>
-        <v>[構造理解] Webアプリケーションで必要なもの</v>
-      </c>
-      <c r="D73" s="111" t="s">
-        <v>182</v>
-      </c>
-      <c r="E73" s="112"/>
-      <c r="F73" s="113"/>
+      <c r="B73" s="114"/>
+      <c r="C73" s="76" t="str">
+        <f>master!C55</f>
+        <v>バイブコーディング➊ 画面モックアップを作ってデザインを決める</v>
+      </c>
+      <c r="D73" s="110" t="s">
+        <v>192</v>
+      </c>
+      <c r="E73" s="111"/>
+      <c r="F73" s="112"/>
       <c r="G73" s="58" t="s">
-        <v>299</v>
+        <v>293</v>
       </c>
       <c r="H73" s="59"/>
       <c r="I73" s="60" t="s">
         <v>24</v>
       </c>
       <c r="J73" s="61">
-        <v>1.3888888888888889E-3</v>
+        <v>1.3888888888888888E-2</v>
       </c>
       <c r="K73" s="62"/>
       <c r="L73" s="6"/>
       <c r="M73" s="6"/>
       <c r="N73" s="6"/>
     </row>
-    <row r="74" spans="1:14" ht="50.4">
+    <row r="74" spans="1:14" ht="88.2" customHeight="1">
       <c r="A74" s="11"/>
-      <c r="B74" s="115"/>
-      <c r="C74" s="76" t="str">
-        <f>master!C55</f>
-        <v>バイブコーディング➊ 画面モックアップを作ってデザインを決める</v>
-      </c>
-      <c r="D74" s="111" t="s">
-        <v>192</v>
-      </c>
-      <c r="E74" s="112"/>
-      <c r="F74" s="113"/>
+      <c r="B74" s="114"/>
+      <c r="C74" s="77"/>
+      <c r="D74" s="110" t="s">
+        <v>183</v>
+      </c>
+      <c r="E74" s="111"/>
+      <c r="F74" s="112"/>
       <c r="G74" s="58" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="H74" s="59"/>
-      <c r="I74" s="60" t="s">
-        <v>24</v>
-      </c>
-      <c r="J74" s="61">
-        <v>1.3888888888888888E-2</v>
-      </c>
+      <c r="I74" s="60"/>
+      <c r="J74" s="61"/>
       <c r="K74" s="62"/>
       <c r="L74" s="6"/>
       <c r="M74" s="6"/>
       <c r="N74" s="6"/>
     </row>
-    <row r="75" spans="1:14" ht="88.2" customHeight="1">
+    <row r="75" spans="1:14" ht="50.4">
       <c r="A75" s="11"/>
-      <c r="B75" s="115"/>
-      <c r="C75" s="77"/>
-      <c r="D75" s="111" t="s">
-        <v>183</v>
-      </c>
-      <c r="E75" s="112"/>
-      <c r="F75" s="113"/>
+      <c r="B75" s="114"/>
+      <c r="C75" s="76" t="str">
+        <f>master!C56</f>
+        <v>バイブコーディング➋ データベースのテーブルを準備する</v>
+      </c>
+      <c r="D75" s="110" t="s">
+        <v>196</v>
+      </c>
+      <c r="E75" s="111"/>
+      <c r="F75" s="112"/>
       <c r="G75" s="58" t="s">
         <v>293</v>
       </c>
       <c r="H75" s="59"/>
-      <c r="I75" s="60"/>
-      <c r="J75" s="61"/>
+      <c r="I75" s="60" t="s">
+        <v>24</v>
+      </c>
+      <c r="J75" s="61">
+        <v>1.3888888888888889E-3</v>
+      </c>
       <c r="K75" s="62"/>
       <c r="L75" s="6"/>
       <c r="M75" s="6"/>
       <c r="N75" s="6"/>
     </row>
-    <row r="76" spans="1:14" ht="50.4">
+    <row r="76" spans="1:14" ht="88.2">
       <c r="A76" s="11"/>
-      <c r="B76" s="115"/>
-      <c r="C76" s="76" t="str">
-        <f>master!C56</f>
-        <v>バイブコーディング➋ データベースのテーブルを準備する</v>
-      </c>
-      <c r="D76" s="111" t="s">
-        <v>196</v>
-      </c>
-      <c r="E76" s="112"/>
-      <c r="F76" s="113"/>
+      <c r="B76" s="114"/>
+      <c r="C76" s="77"/>
+      <c r="D76" s="110" t="s">
+        <v>183</v>
+      </c>
+      <c r="E76" s="111"/>
+      <c r="F76" s="112"/>
       <c r="G76" s="58" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="H76" s="59"/>
-      <c r="I76" s="60" t="s">
-        <v>24</v>
-      </c>
-      <c r="J76" s="61">
-        <v>1.3888888888888889E-3</v>
-      </c>
+      <c r="I76" s="60"/>
+      <c r="J76" s="61"/>
       <c r="K76" s="62"/>
       <c r="L76" s="6"/>
       <c r="M76" s="6"/>
       <c r="N76" s="6"/>
     </row>
-    <row r="77" spans="1:14" ht="88.2">
+    <row r="77" spans="1:14" ht="50.4">
       <c r="A77" s="11"/>
-      <c r="B77" s="115"/>
-      <c r="C77" s="77"/>
-      <c r="D77" s="111" t="s">
-        <v>183</v>
-      </c>
-      <c r="E77" s="112"/>
-      <c r="F77" s="113"/>
+      <c r="B77" s="114"/>
+      <c r="C77" s="76" t="str">
+        <f>master!C57</f>
+        <v>バイブコーディング➌ データベースのデータを準備する</v>
+      </c>
+      <c r="D77" s="110" t="s">
+        <v>195</v>
+      </c>
+      <c r="E77" s="111"/>
+      <c r="F77" s="112"/>
       <c r="G77" s="58" t="s">
         <v>293</v>
       </c>
       <c r="H77" s="59"/>
-      <c r="I77" s="60"/>
-      <c r="J77" s="61"/>
+      <c r="I77" s="60" t="s">
+        <v>24</v>
+      </c>
+      <c r="J77" s="61">
+        <v>1.3888888888888889E-3</v>
+      </c>
       <c r="K77" s="62"/>
       <c r="L77" s="6"/>
       <c r="M77" s="6"/>
       <c r="N77" s="6"/>
     </row>
-    <row r="78" spans="1:14" ht="50.4">
+    <row r="78" spans="1:14" ht="88.2">
       <c r="A78" s="11"/>
-      <c r="B78" s="115"/>
-      <c r="C78" s="76" t="str">
-        <f>master!C57</f>
-        <v>バイブコーディング➌ データベースのデータを準備する</v>
-      </c>
-      <c r="D78" s="111" t="s">
-        <v>195</v>
-      </c>
-      <c r="E78" s="112"/>
-      <c r="F78" s="113"/>
+      <c r="B78" s="114"/>
+      <c r="C78" s="77"/>
+      <c r="D78" s="110" t="s">
+        <v>183</v>
+      </c>
+      <c r="E78" s="111"/>
+      <c r="F78" s="112"/>
       <c r="G78" s="58" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="H78" s="59"/>
-      <c r="I78" s="60" t="s">
-        <v>24</v>
-      </c>
-      <c r="J78" s="61">
-        <v>1.3888888888888889E-3</v>
-      </c>
+      <c r="I78" s="60"/>
+      <c r="J78" s="61"/>
       <c r="K78" s="62"/>
       <c r="L78" s="6"/>
       <c r="M78" s="6"/>
       <c r="N78" s="6"/>
     </row>
-    <row r="79" spans="1:14" ht="88.2">
+    <row r="79" spans="1:14" ht="63">
       <c r="A79" s="11"/>
-      <c r="B79" s="115"/>
-      <c r="C79" s="77"/>
-      <c r="D79" s="111" t="s">
-        <v>183</v>
-      </c>
-      <c r="E79" s="112"/>
-      <c r="F79" s="113"/>
+      <c r="B79" s="114"/>
+      <c r="C79" s="76" t="str">
+        <f>master!C58</f>
+        <v>バイブコーディング❹ データベース処理とビジネスロジックを作る</v>
+      </c>
+      <c r="D79" s="110" t="s">
+        <v>194</v>
+      </c>
+      <c r="E79" s="111"/>
+      <c r="F79" s="112"/>
       <c r="G79" s="58" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="H79" s="59"/>
-      <c r="I79" s="60"/>
-      <c r="J79" s="61"/>
+      <c r="I79" s="60" t="s">
+        <v>24</v>
+      </c>
+      <c r="J79" s="61">
+        <v>3.472222222222222E-3</v>
+      </c>
       <c r="K79" s="62"/>
       <c r="L79" s="6"/>
       <c r="M79" s="6"/>
       <c r="N79" s="6"/>
     </row>
-    <row r="80" spans="1:14" ht="63">
+    <row r="80" spans="1:14" ht="88.2">
       <c r="A80" s="11"/>
-      <c r="B80" s="115"/>
-      <c r="C80" s="76" t="str">
-        <f>master!C58</f>
-        <v>バイブコーディング❹ データベース処理とビジネスロジックを作る</v>
-      </c>
-      <c r="D80" s="111" t="s">
-        <v>194</v>
-      </c>
-      <c r="E80" s="112"/>
-      <c r="F80" s="113"/>
+      <c r="B80" s="114"/>
+      <c r="C80" s="77"/>
+      <c r="D80" s="110" t="s">
+        <v>183</v>
+      </c>
+      <c r="E80" s="111"/>
+      <c r="F80" s="112"/>
       <c r="G80" s="58" t="s">
-        <v>297</v>
+        <v>292</v>
       </c>
       <c r="H80" s="59"/>
-      <c r="I80" s="60" t="s">
-        <v>24</v>
-      </c>
-      <c r="J80" s="61">
-        <v>3.472222222222222E-3</v>
-      </c>
+      <c r="I80" s="60"/>
+      <c r="J80" s="61"/>
       <c r="K80" s="62"/>
       <c r="L80" s="6"/>
       <c r="M80" s="6"/>
       <c r="N80" s="6"/>
     </row>
-    <row r="81" spans="1:14" ht="88.2">
+    <row r="81" spans="1:14" ht="50.4">
       <c r="A81" s="11"/>
-      <c r="B81" s="115"/>
-      <c r="C81" s="77"/>
-      <c r="D81" s="111" t="s">
-        <v>183</v>
-      </c>
-      <c r="E81" s="112"/>
-      <c r="F81" s="113"/>
+      <c r="B81" s="114"/>
+      <c r="C81" s="58" t="str">
+        <f>master!C59</f>
+        <v>[解説] RepositoryクラスとSQLの例（抜粋）</v>
+      </c>
+      <c r="D81" s="110" t="s">
+        <v>184</v>
+      </c>
+      <c r="E81" s="111"/>
+      <c r="F81" s="112"/>
       <c r="G81" s="58" t="s">
         <v>293</v>
       </c>
       <c r="H81" s="59"/>
-      <c r="I81" s="60"/>
-      <c r="J81" s="61"/>
+      <c r="I81" s="60" t="s">
+        <v>24</v>
+      </c>
+      <c r="J81" s="61">
+        <v>2.0833333333333333E-3</v>
+      </c>
       <c r="K81" s="62"/>
       <c r="L81" s="6"/>
       <c r="M81" s="6"/>
@@ -8692,127 +8597,127 @@
     </row>
     <row r="82" spans="1:14" ht="50.4">
       <c r="A82" s="11"/>
-      <c r="B82" s="115"/>
+      <c r="B82" s="114"/>
       <c r="C82" s="58" t="str">
-        <f>master!C59</f>
-        <v>[解説] RepositoryクラスとSQLの例（抜粋）</v>
-      </c>
-      <c r="D82" s="111" t="s">
-        <v>184</v>
-      </c>
-      <c r="E82" s="112"/>
-      <c r="F82" s="113"/>
+        <f>master!C60</f>
+        <v>[解説] Entity/Modelクラスの例（抜粋）</v>
+      </c>
+      <c r="D82" s="110" t="s">
+        <v>185</v>
+      </c>
+      <c r="E82" s="111"/>
+      <c r="F82" s="112"/>
       <c r="G82" s="58" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="H82" s="59"/>
       <c r="I82" s="60" t="s">
         <v>24</v>
       </c>
       <c r="J82" s="61">
-        <v>2.0833333333333333E-3</v>
+        <v>1.3888888888888889E-3</v>
       </c>
       <c r="K82" s="62"/>
       <c r="L82" s="6"/>
       <c r="M82" s="6"/>
       <c r="N82" s="6"/>
     </row>
-    <row r="83" spans="1:14" ht="50.4">
+    <row r="83" spans="1:14" ht="37.799999999999997">
       <c r="A83" s="11"/>
-      <c r="B83" s="115"/>
+      <c r="B83" s="114"/>
       <c r="C83" s="58" t="str">
-        <f>master!C60</f>
-        <v>[解説] Entity/Modelクラスの例（抜粋）</v>
-      </c>
-      <c r="D83" s="111" t="s">
-        <v>185</v>
-      </c>
-      <c r="E83" s="112"/>
-      <c r="F83" s="113"/>
+        <f>master!C61</f>
+        <v>[解説] Serviceクラスの例（抜粋）</v>
+      </c>
+      <c r="D83" s="110" t="s">
+        <v>186</v>
+      </c>
+      <c r="E83" s="111"/>
+      <c r="F83" s="112"/>
       <c r="G83" s="58" t="s">
-        <v>294</v>
+        <v>288</v>
       </c>
       <c r="H83" s="59"/>
       <c r="I83" s="60" t="s">
         <v>24</v>
       </c>
       <c r="J83" s="61">
-        <v>1.3888888888888889E-3</v>
+        <v>6.9444444444444447E-4</v>
       </c>
       <c r="K83" s="62"/>
       <c r="L83" s="6"/>
       <c r="M83" s="6"/>
       <c r="N83" s="6"/>
     </row>
-    <row r="84" spans="1:14" ht="37.799999999999997">
+    <row r="84" spans="1:14" ht="50.4">
       <c r="A84" s="11"/>
-      <c r="B84" s="115"/>
-      <c r="C84" s="58" t="str">
-        <f>master!C61</f>
-        <v>[解説] Serviceクラスの例（抜粋）</v>
-      </c>
-      <c r="D84" s="111" t="s">
-        <v>186</v>
-      </c>
-      <c r="E84" s="112"/>
-      <c r="F84" s="113"/>
+      <c r="B84" s="114"/>
+      <c r="C84" s="76" t="str">
+        <f>master!C62</f>
+        <v>バイブコーディング❺ モックアップをもとに画面表示/処理を作る</v>
+      </c>
+      <c r="D84" s="110" t="s">
+        <v>193</v>
+      </c>
+      <c r="E84" s="111"/>
+      <c r="F84" s="112"/>
       <c r="G84" s="58" t="s">
-        <v>289</v>
+        <v>293</v>
       </c>
       <c r="H84" s="59"/>
       <c r="I84" s="60" t="s">
         <v>24</v>
       </c>
       <c r="J84" s="61">
-        <v>6.9444444444444447E-4</v>
+        <v>6.9444444444444441E-3</v>
       </c>
       <c r="K84" s="62"/>
       <c r="L84" s="6"/>
       <c r="M84" s="6"/>
       <c r="N84" s="6"/>
     </row>
-    <row r="85" spans="1:14" ht="50.4">
+    <row r="85" spans="1:14" ht="88.2">
       <c r="A85" s="11"/>
-      <c r="B85" s="115"/>
-      <c r="C85" s="76" t="str">
-        <f>master!C62</f>
-        <v>バイブコーディング❺ モックアップをもとに画面表示/処理を作る</v>
-      </c>
-      <c r="D85" s="111" t="s">
-        <v>193</v>
-      </c>
-      <c r="E85" s="112"/>
-      <c r="F85" s="113"/>
+      <c r="B85" s="114"/>
+      <c r="C85" s="77"/>
+      <c r="D85" s="110" t="s">
+        <v>183</v>
+      </c>
+      <c r="E85" s="111"/>
+      <c r="F85" s="112"/>
       <c r="G85" s="58" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="H85" s="59"/>
-      <c r="I85" s="60" t="s">
-        <v>24</v>
-      </c>
-      <c r="J85" s="61">
-        <v>6.9444444444444441E-3</v>
-      </c>
+      <c r="I85" s="60"/>
+      <c r="J85" s="61"/>
       <c r="K85" s="62"/>
       <c r="L85" s="6"/>
       <c r="M85" s="6"/>
       <c r="N85" s="6"/>
     </row>
-    <row r="86" spans="1:14" ht="88.2">
+    <row r="86" spans="1:14" ht="37.799999999999997">
       <c r="A86" s="11"/>
-      <c r="B86" s="115"/>
-      <c r="C86" s="77"/>
-      <c r="D86" s="111" t="s">
-        <v>183</v>
-      </c>
-      <c r="E86" s="112"/>
-      <c r="F86" s="113"/>
+      <c r="B86" s="114"/>
+      <c r="C86" s="58" t="str">
+        <f>master!C63</f>
+        <v>[解説] Controllerクラスの例（抜粋）</v>
+      </c>
+      <c r="D86" s="110" t="s">
+        <v>187</v>
+      </c>
+      <c r="E86" s="111"/>
+      <c r="F86" s="112"/>
       <c r="G86" s="58" t="s">
-        <v>293</v>
+        <v>288</v>
       </c>
       <c r="H86" s="59"/>
-      <c r="I86" s="60"/>
-      <c r="J86" s="61"/>
+      <c r="I86" s="60" t="s">
+        <v>24</v>
+      </c>
+      <c r="J86" s="61">
+        <v>1.3888888888888889E-3</v>
+      </c>
       <c r="K86" s="62"/>
       <c r="L86" s="6"/>
       <c r="M86" s="6"/>
@@ -8820,18 +8725,18 @@
     </row>
     <row r="87" spans="1:14" ht="37.799999999999997">
       <c r="A87" s="11"/>
-      <c r="B87" s="115"/>
+      <c r="B87" s="114"/>
       <c r="C87" s="58" t="str">
-        <f>master!C63</f>
-        <v>[解説] Controllerクラスの例（抜粋）</v>
-      </c>
-      <c r="D87" s="111" t="s">
-        <v>187</v>
-      </c>
-      <c r="E87" s="112"/>
-      <c r="F87" s="113"/>
+        <f>master!C64</f>
+        <v>[解説] Thymeleafテンプレートの例（抜粋）</v>
+      </c>
+      <c r="D87" s="110" t="s">
+        <v>188</v>
+      </c>
+      <c r="E87" s="111"/>
+      <c r="F87" s="112"/>
       <c r="G87" s="58" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="H87" s="59"/>
       <c r="I87" s="60" t="s">
@@ -8847,43 +8752,43 @@
     </row>
     <row r="88" spans="1:14" ht="37.799999999999997">
       <c r="A88" s="11"/>
-      <c r="B88" s="115"/>
+      <c r="B88" s="114"/>
       <c r="C88" s="58" t="str">
-        <f>master!C64</f>
-        <v>[解説] Thymeleafテンプレートの例（抜粋）</v>
-      </c>
-      <c r="D88" s="111" t="s">
-        <v>188</v>
-      </c>
-      <c r="E88" s="112"/>
-      <c r="F88" s="113"/>
+        <f>master!C65</f>
+        <v>[解説] Formクラスの例（抜粋）</v>
+      </c>
+      <c r="D88" s="110" t="s">
+        <v>189</v>
+      </c>
+      <c r="E88" s="111"/>
+      <c r="F88" s="112"/>
       <c r="G88" s="58" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="H88" s="59"/>
       <c r="I88" s="60" t="s">
         <v>24</v>
       </c>
       <c r="J88" s="61">
-        <v>1.3888888888888889E-3</v>
+        <v>6.9444444444444447E-4</v>
       </c>
       <c r="K88" s="62"/>
       <c r="L88" s="6"/>
       <c r="M88" s="6"/>
       <c r="N88" s="6"/>
     </row>
-    <row r="89" spans="1:14" ht="37.799999999999997">
+    <row r="89" spans="1:14" ht="75.599999999999994">
       <c r="A89" s="11"/>
-      <c r="B89" s="115"/>
-      <c r="C89" s="58" t="str">
-        <f>master!C65</f>
-        <v>[解説] Formクラスの例（抜粋）</v>
-      </c>
-      <c r="D89" s="111" t="s">
-        <v>189</v>
-      </c>
-      <c r="E89" s="112"/>
-      <c r="F89" s="113"/>
+      <c r="B89" s="114"/>
+      <c r="C89" s="76" t="str">
+        <f>master!C66</f>
+        <v>バイブコーディング❻ 動作を確認する</v>
+      </c>
+      <c r="D89" s="110" t="s">
+        <v>190</v>
+      </c>
+      <c r="E89" s="111"/>
+      <c r="F89" s="112"/>
       <c r="G89" s="58" t="s">
         <v>289</v>
       </c>
@@ -8899,101 +8804,101 @@
       <c r="M89" s="6"/>
       <c r="N89" s="6"/>
     </row>
-    <row r="90" spans="1:14" ht="75.599999999999994">
+    <row r="90" spans="1:14" ht="63">
       <c r="A90" s="11"/>
       <c r="B90" s="115"/>
-      <c r="C90" s="76" t="str">
-        <f>master!C66</f>
-        <v>バイブコーディング❻ 動作を確認する</v>
-      </c>
-      <c r="D90" s="111" t="s">
-        <v>190</v>
-      </c>
-      <c r="E90" s="112"/>
-      <c r="F90" s="113"/>
+      <c r="C90" s="77"/>
+      <c r="D90" s="110" t="s">
+        <v>197</v>
+      </c>
+      <c r="E90" s="111"/>
+      <c r="F90" s="112"/>
       <c r="G90" s="58" t="s">
-        <v>290</v>
+        <v>296</v>
       </c>
       <c r="H90" s="59"/>
       <c r="I90" s="60" t="s">
         <v>24</v>
       </c>
       <c r="J90" s="61">
-        <v>6.9444444444444447E-4</v>
+        <v>6.9444444444444441E-3</v>
       </c>
       <c r="K90" s="62"/>
       <c r="L90" s="6"/>
       <c r="M90" s="6"/>
       <c r="N90" s="6"/>
     </row>
-    <row r="91" spans="1:14" ht="63">
+    <row r="91" spans="1:14" ht="50.4">
       <c r="A91" s="11"/>
-      <c r="B91" s="116"/>
-      <c r="C91" s="77"/>
-      <c r="D91" s="111" t="s">
-        <v>197</v>
-      </c>
-      <c r="E91" s="112"/>
-      <c r="F91" s="113"/>
-      <c r="G91" s="58" t="s">
-        <v>297</v>
-      </c>
-      <c r="H91" s="59"/>
-      <c r="I91" s="60" t="s">
-        <v>24</v>
-      </c>
-      <c r="J91" s="61">
-        <v>6.9444444444444441E-3</v>
-      </c>
-      <c r="K91" s="62"/>
+      <c r="B91" s="107" t="str">
+        <f>master!B69</f>
+        <v>Gitとは</v>
+      </c>
+      <c r="C91" s="48" t="str">
+        <f>master!C69</f>
+        <v>はじめに</v>
+      </c>
+      <c r="D91" s="104" t="s">
+        <v>418</v>
+      </c>
+      <c r="E91" s="105"/>
+      <c r="F91" s="106"/>
+      <c r="G91" s="48" t="s">
+        <v>335</v>
+      </c>
+      <c r="H91" s="12"/>
+      <c r="I91" s="46" t="s">
+        <v>24</v>
+      </c>
+      <c r="J91" s="44">
+        <v>1.3888888888888889E-3</v>
+      </c>
+      <c r="K91" s="89"/>
       <c r="L91" s="6"/>
       <c r="M91" s="6"/>
       <c r="N91" s="6"/>
     </row>
-    <row r="92" spans="1:14" ht="50.4">
+    <row r="92" spans="1:14" ht="37.799999999999997">
       <c r="A92" s="11"/>
-      <c r="B92" s="108" t="str">
-        <f>master!B69</f>
-        <v>Gitとは</v>
-      </c>
+      <c r="B92" s="108"/>
       <c r="C92" s="48" t="str">
-        <f>master!C69</f>
-        <v>はじめに</v>
-      </c>
-      <c r="D92" s="105" t="s">
-        <v>423</v>
-      </c>
-      <c r="E92" s="106"/>
-      <c r="F92" s="107"/>
+        <f>master!C70</f>
+        <v>バージョン管理とは</v>
+      </c>
+      <c r="D92" s="104" t="s">
+        <v>393</v>
+      </c>
+      <c r="E92" s="105"/>
+      <c r="F92" s="106"/>
       <c r="G92" s="48" t="s">
-        <v>338</v>
+        <v>334</v>
       </c>
       <c r="H92" s="12"/>
       <c r="I92" s="46" t="s">
         <v>24</v>
       </c>
       <c r="J92" s="44">
-        <v>1.3888888888888889E-3</v>
-      </c>
-      <c r="K92" s="90"/>
+        <v>2.0833333333333333E-3</v>
+      </c>
+      <c r="K92" s="89"/>
       <c r="L92" s="6"/>
       <c r="M92" s="6"/>
       <c r="N92" s="6"/>
     </row>
-    <row r="93" spans="1:14" ht="37.799999999999997">
+    <row r="93" spans="1:14" ht="151.19999999999999">
       <c r="A93" s="11"/>
       <c r="B93" s="109"/>
       <c r="C93" s="48" t="str">
-        <f>master!C70</f>
-        <v>バージョン管理とは</v>
-      </c>
-      <c r="D93" s="105" t="s">
-        <v>398</v>
-      </c>
-      <c r="E93" s="106"/>
-      <c r="F93" s="107"/>
+        <f>master!C71</f>
+        <v>Gitの概要</v>
+      </c>
+      <c r="D93" s="104" t="s">
+        <v>394</v>
+      </c>
+      <c r="E93" s="105"/>
+      <c r="F93" s="106"/>
       <c r="G93" s="48" t="s">
-        <v>337</v>
+        <v>395</v>
       </c>
       <c r="H93" s="12"/>
       <c r="I93" s="46" t="s">
@@ -9002,82 +8907,82 @@
       <c r="J93" s="44">
         <v>2.0833333333333333E-3</v>
       </c>
-      <c r="K93" s="90"/>
+      <c r="K93" s="89"/>
       <c r="L93" s="6"/>
       <c r="M93" s="6"/>
       <c r="N93" s="6"/>
     </row>
-    <row r="94" spans="1:14" ht="151.19999999999999">
+    <row r="94" spans="1:14" ht="75.599999999999994">
       <c r="A94" s="11"/>
-      <c r="B94" s="110"/>
+      <c r="B94" s="107" t="str">
+        <f>master!B72</f>
+        <v>Gitの基本構成</v>
+      </c>
       <c r="C94" s="48" t="str">
-        <f>master!C71</f>
-        <v>Gitの概要</v>
-      </c>
-      <c r="D94" s="105" t="s">
-        <v>399</v>
-      </c>
-      <c r="E94" s="106"/>
-      <c r="F94" s="107"/>
+        <f>master!C72</f>
+        <v>はじめに</v>
+      </c>
+      <c r="D94" s="104" t="s">
+        <v>417</v>
+      </c>
+      <c r="E94" s="105"/>
+      <c r="F94" s="106"/>
       <c r="G94" s="48" t="s">
-        <v>400</v>
+        <v>396</v>
       </c>
       <c r="H94" s="12"/>
       <c r="I94" s="46" t="s">
         <v>24</v>
       </c>
       <c r="J94" s="44">
-        <v>2.0833333333333333E-3</v>
-      </c>
-      <c r="K94" s="90"/>
+        <v>1.3888888888888889E-3</v>
+      </c>
+      <c r="K94" s="89"/>
       <c r="L94" s="6"/>
       <c r="M94" s="6"/>
       <c r="N94" s="6"/>
     </row>
-    <row r="95" spans="1:14" ht="75.599999999999994">
+    <row r="95" spans="1:14" ht="37.799999999999997">
       <c r="A95" s="11"/>
-      <c r="B95" s="108" t="str">
-        <f>master!B72</f>
-        <v>Gitの基本構成</v>
-      </c>
+      <c r="B95" s="108"/>
       <c r="C95" s="48" t="str">
-        <f>master!C72</f>
-        <v>はじめに</v>
-      </c>
-      <c r="D95" s="105" t="s">
-        <v>422</v>
-      </c>
-      <c r="E95" s="106"/>
-      <c r="F95" s="107"/>
+        <f>master!C73</f>
+        <v>ワーキングツリー</v>
+      </c>
+      <c r="D95" s="104" t="s">
+        <v>397</v>
+      </c>
+      <c r="E95" s="105"/>
+      <c r="F95" s="106"/>
       <c r="G95" s="48" t="s">
-        <v>401</v>
+        <v>334</v>
       </c>
       <c r="H95" s="12"/>
       <c r="I95" s="46" t="s">
         <v>24</v>
       </c>
       <c r="J95" s="44">
-        <v>1.3888888888888889E-3</v>
-      </c>
-      <c r="K95" s="90"/>
+        <v>2.0833333333333333E-3</v>
+      </c>
+      <c r="K95" s="89"/>
       <c r="L95" s="6"/>
       <c r="M95" s="6"/>
       <c r="N95" s="6"/>
     </row>
     <row r="96" spans="1:14" ht="37.799999999999997">
       <c r="A96" s="11"/>
-      <c r="B96" s="109"/>
+      <c r="B96" s="108"/>
       <c r="C96" s="48" t="str">
-        <f>master!C73</f>
-        <v>ワーキングツリー</v>
-      </c>
-      <c r="D96" s="105" t="s">
-        <v>402</v>
-      </c>
-      <c r="E96" s="106"/>
-      <c r="F96" s="107"/>
+        <f>master!C74</f>
+        <v>ステージングエリア</v>
+      </c>
+      <c r="D96" s="104" t="s">
+        <v>398</v>
+      </c>
+      <c r="E96" s="105"/>
+      <c r="F96" s="106"/>
       <c r="G96" s="48" t="s">
-        <v>337</v>
+        <v>334</v>
       </c>
       <c r="H96" s="12"/>
       <c r="I96" s="46" t="s">
@@ -9086,25 +8991,25 @@
       <c r="J96" s="44">
         <v>2.0833333333333333E-3</v>
       </c>
-      <c r="K96" s="90"/>
+      <c r="K96" s="89"/>
       <c r="L96" s="6"/>
       <c r="M96" s="6"/>
       <c r="N96" s="6"/>
     </row>
     <row r="97" spans="1:14" ht="37.799999999999997">
       <c r="A97" s="11"/>
-      <c r="B97" s="109"/>
+      <c r="B97" s="108"/>
       <c r="C97" s="48" t="str">
-        <f>master!C74</f>
-        <v>ステージングエリア</v>
-      </c>
-      <c r="D97" s="105" t="s">
-        <v>403</v>
-      </c>
-      <c r="E97" s="106"/>
-      <c r="F97" s="107"/>
+        <f>master!C75</f>
+        <v>ローカルリポジトリ</v>
+      </c>
+      <c r="D97" s="104" t="s">
+        <v>399</v>
+      </c>
+      <c r="E97" s="105"/>
+      <c r="F97" s="106"/>
       <c r="G97" s="48" t="s">
-        <v>337</v>
+        <v>334</v>
       </c>
       <c r="H97" s="12"/>
       <c r="I97" s="46" t="s">
@@ -9113,25 +9018,25 @@
       <c r="J97" s="44">
         <v>2.0833333333333333E-3</v>
       </c>
-      <c r="K97" s="90"/>
+      <c r="K97" s="89"/>
       <c r="L97" s="6"/>
       <c r="M97" s="6"/>
       <c r="N97" s="6"/>
     </row>
-    <row r="98" spans="1:14" ht="37.799999999999997">
+    <row r="98" spans="1:14" ht="50.4">
       <c r="A98" s="11"/>
       <c r="B98" s="109"/>
       <c r="C98" s="48" t="str">
-        <f>master!C75</f>
-        <v>ローカルリポジトリ</v>
-      </c>
-      <c r="D98" s="105" t="s">
-        <v>404</v>
-      </c>
-      <c r="E98" s="106"/>
-      <c r="F98" s="107"/>
+        <f>master!C76</f>
+        <v>リモートリポジトリ</v>
+      </c>
+      <c r="D98" s="104" t="s">
+        <v>400</v>
+      </c>
+      <c r="E98" s="105"/>
+      <c r="F98" s="106"/>
       <c r="G98" s="48" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="H98" s="12"/>
       <c r="I98" s="46" t="s">
@@ -9140,82 +9045,82 @@
       <c r="J98" s="44">
         <v>2.0833333333333333E-3</v>
       </c>
-      <c r="K98" s="90"/>
+      <c r="K98" s="89"/>
       <c r="L98" s="6"/>
       <c r="M98" s="6"/>
       <c r="N98" s="6"/>
     </row>
-    <row r="99" spans="1:14" ht="50.4">
+    <row r="99" spans="1:14" ht="88.2">
       <c r="A99" s="11"/>
-      <c r="B99" s="110"/>
+      <c r="B99" s="107" t="str">
+        <f>master!B77</f>
+        <v>ローカルリポジトリの操作</v>
+      </c>
       <c r="C99" s="48" t="str">
-        <f>master!C76</f>
-        <v>リモートリポジトリ</v>
-      </c>
-      <c r="D99" s="105" t="s">
-        <v>405</v>
-      </c>
-      <c r="E99" s="106"/>
-      <c r="F99" s="107"/>
+        <f>master!C77</f>
+        <v>はじめに</v>
+      </c>
+      <c r="D99" s="104" t="s">
+        <v>416</v>
+      </c>
+      <c r="E99" s="105"/>
+      <c r="F99" s="106"/>
       <c r="G99" s="48" t="s">
-        <v>338</v>
+        <v>401</v>
       </c>
       <c r="H99" s="12"/>
       <c r="I99" s="46" t="s">
         <v>24</v>
       </c>
       <c r="J99" s="44">
-        <v>2.0833333333333333E-3</v>
-      </c>
-      <c r="K99" s="90"/>
+        <v>6.9444444444444447E-4</v>
+      </c>
+      <c r="K99" s="89"/>
       <c r="L99" s="6"/>
       <c r="M99" s="6"/>
       <c r="N99" s="6"/>
     </row>
-    <row r="100" spans="1:14" ht="88.2">
+    <row r="100" spans="1:14" ht="37.799999999999997">
       <c r="A100" s="11"/>
-      <c r="B100" s="108" t="str">
-        <f>master!B77</f>
-        <v>ローカルリポジトリの操作</v>
-      </c>
+      <c r="B100" s="108"/>
       <c r="C100" s="48" t="str">
-        <f>master!C77</f>
-        <v>はじめに</v>
-      </c>
-      <c r="D100" s="105" t="s">
-        <v>421</v>
-      </c>
-      <c r="E100" s="106"/>
-      <c r="F100" s="107"/>
+        <f>master!C78</f>
+        <v>リポジトリの作成</v>
+      </c>
+      <c r="D100" s="104" t="s">
+        <v>402</v>
+      </c>
+      <c r="E100" s="105"/>
+      <c r="F100" s="106"/>
       <c r="G100" s="48" t="s">
-        <v>406</v>
+        <v>334</v>
       </c>
       <c r="H100" s="12"/>
       <c r="I100" s="46" t="s">
         <v>24</v>
       </c>
       <c r="J100" s="44">
-        <v>6.9444444444444447E-4</v>
-      </c>
-      <c r="K100" s="90"/>
+        <v>1.3888888888888889E-3</v>
+      </c>
+      <c r="K100" s="89"/>
       <c r="L100" s="6"/>
       <c r="M100" s="6"/>
       <c r="N100" s="6"/>
     </row>
-    <row r="101" spans="1:14" ht="37.799999999999997">
+    <row r="101" spans="1:14" ht="37.799999999999997" customHeight="1">
       <c r="A101" s="11"/>
-      <c r="B101" s="109"/>
+      <c r="B101" s="108"/>
       <c r="C101" s="48" t="str">
-        <f>master!C78</f>
-        <v>リポジトリの作成</v>
-      </c>
-      <c r="D101" s="105" t="s">
-        <v>407</v>
-      </c>
-      <c r="E101" s="106"/>
-      <c r="F101" s="107"/>
+        <f>master!C79</f>
+        <v>ファイルの変更</v>
+      </c>
+      <c r="D101" s="104" t="s">
+        <v>403</v>
+      </c>
+      <c r="E101" s="105"/>
+      <c r="F101" s="106"/>
       <c r="G101" s="48" t="s">
-        <v>337</v>
+        <v>334</v>
       </c>
       <c r="H101" s="12"/>
       <c r="I101" s="46" t="s">
@@ -9224,25 +9129,25 @@
       <c r="J101" s="44">
         <v>1.3888888888888889E-3</v>
       </c>
-      <c r="K101" s="90"/>
+      <c r="K101" s="89"/>
       <c r="L101" s="6"/>
       <c r="M101" s="6"/>
       <c r="N101" s="6"/>
     </row>
-    <row r="102" spans="1:14" ht="37.799999999999997" customHeight="1">
+    <row r="102" spans="1:14" ht="37.799999999999997">
       <c r="A102" s="11"/>
-      <c r="B102" s="109"/>
+      <c r="B102" s="108"/>
       <c r="C102" s="48" t="str">
-        <f>master!C79</f>
-        <v>ファイルの変更</v>
-      </c>
-      <c r="D102" s="105" t="s">
-        <v>408</v>
-      </c>
-      <c r="E102" s="106"/>
-      <c r="F102" s="107"/>
+        <f>master!C80</f>
+        <v>変更内容の確認</v>
+      </c>
+      <c r="D102" s="104" t="s">
+        <v>404</v>
+      </c>
+      <c r="E102" s="105"/>
+      <c r="F102" s="106"/>
       <c r="G102" s="48" t="s">
-        <v>337</v>
+        <v>334</v>
       </c>
       <c r="H102" s="12"/>
       <c r="I102" s="46" t="s">
@@ -9251,25 +9156,25 @@
       <c r="J102" s="44">
         <v>1.3888888888888889E-3</v>
       </c>
-      <c r="K102" s="90"/>
+      <c r="K102" s="89"/>
       <c r="L102" s="6"/>
       <c r="M102" s="6"/>
       <c r="N102" s="6"/>
     </row>
     <row r="103" spans="1:14" ht="37.799999999999997">
       <c r="A103" s="11"/>
-      <c r="B103" s="109"/>
+      <c r="B103" s="108"/>
       <c r="C103" s="48" t="str">
-        <f>master!C80</f>
-        <v>変更内容の確認</v>
-      </c>
-      <c r="D103" s="105" t="s">
-        <v>409</v>
-      </c>
-      <c r="E103" s="106"/>
-      <c r="F103" s="107"/>
+        <f>master!C81</f>
+        <v>変更内容のステージ</v>
+      </c>
+      <c r="D103" s="104" t="s">
+        <v>405</v>
+      </c>
+      <c r="E103" s="105"/>
+      <c r="F103" s="106"/>
       <c r="G103" s="48" t="s">
-        <v>337</v>
+        <v>334</v>
       </c>
       <c r="H103" s="12"/>
       <c r="I103" s="46" t="s">
@@ -9278,25 +9183,25 @@
       <c r="J103" s="44">
         <v>1.3888888888888889E-3</v>
       </c>
-      <c r="K103" s="90"/>
+      <c r="K103" s="89"/>
       <c r="L103" s="6"/>
       <c r="M103" s="6"/>
       <c r="N103" s="6"/>
     </row>
     <row r="104" spans="1:14" ht="37.799999999999997">
       <c r="A104" s="11"/>
-      <c r="B104" s="109"/>
+      <c r="B104" s="108"/>
       <c r="C104" s="48" t="str">
-        <f>master!C81</f>
-        <v>変更内容のステージ</v>
-      </c>
-      <c r="D104" s="105" t="s">
-        <v>410</v>
-      </c>
-      <c r="E104" s="106"/>
-      <c r="F104" s="107"/>
+        <f>master!C82</f>
+        <v>変更内容のコミット</v>
+      </c>
+      <c r="D104" s="104" t="s">
+        <v>406</v>
+      </c>
+      <c r="E104" s="105"/>
+      <c r="F104" s="106"/>
       <c r="G104" s="48" t="s">
-        <v>337</v>
+        <v>334</v>
       </c>
       <c r="H104" s="12"/>
       <c r="I104" s="46" t="s">
@@ -9305,25 +9210,25 @@
       <c r="J104" s="44">
         <v>1.3888888888888889E-3</v>
       </c>
-      <c r="K104" s="90"/>
+      <c r="K104" s="89"/>
       <c r="L104" s="6"/>
       <c r="M104" s="6"/>
       <c r="N104" s="6"/>
     </row>
     <row r="105" spans="1:14" ht="37.799999999999997">
       <c r="A105" s="11"/>
-      <c r="B105" s="109"/>
+      <c r="B105" s="108"/>
       <c r="C105" s="48" t="str">
-        <f>master!C82</f>
-        <v>変更内容のコミット</v>
-      </c>
-      <c r="D105" s="105" t="s">
-        <v>411</v>
-      </c>
-      <c r="E105" s="106"/>
-      <c r="F105" s="107"/>
+        <f>master!C83</f>
+        <v>ワーキングツリーの変更の取り消し</v>
+      </c>
+      <c r="D105" s="104" t="s">
+        <v>407</v>
+      </c>
+      <c r="E105" s="105"/>
+      <c r="F105" s="106"/>
       <c r="G105" s="48" t="s">
-        <v>337</v>
+        <v>334</v>
       </c>
       <c r="H105" s="12"/>
       <c r="I105" s="46" t="s">
@@ -9332,25 +9237,25 @@
       <c r="J105" s="44">
         <v>1.3888888888888889E-3</v>
       </c>
-      <c r="K105" s="90"/>
+      <c r="K105" s="89"/>
       <c r="L105" s="6"/>
       <c r="M105" s="6"/>
       <c r="N105" s="6"/>
     </row>
     <row r="106" spans="1:14" ht="37.799999999999997">
       <c r="A106" s="11"/>
-      <c r="B106" s="109"/>
+      <c r="B106" s="108"/>
       <c r="C106" s="48" t="str">
-        <f>master!C83</f>
-        <v>ワーキングツリーの変更の取り消し</v>
-      </c>
-      <c r="D106" s="105" t="s">
-        <v>412</v>
-      </c>
-      <c r="E106" s="106"/>
-      <c r="F106" s="107"/>
+        <f>master!C84</f>
+        <v>ステージングの取り消し</v>
+      </c>
+      <c r="D106" s="104" t="s">
+        <v>408</v>
+      </c>
+      <c r="E106" s="105"/>
+      <c r="F106" s="106"/>
       <c r="G106" s="48" t="s">
-        <v>337</v>
+        <v>334</v>
       </c>
       <c r="H106" s="12"/>
       <c r="I106" s="46" t="s">
@@ -9359,7 +9264,7 @@
       <c r="J106" s="44">
         <v>1.3888888888888889E-3</v>
       </c>
-      <c r="K106" s="90"/>
+      <c r="K106" s="89"/>
       <c r="L106" s="6"/>
       <c r="M106" s="6"/>
       <c r="N106" s="6"/>
@@ -9368,16 +9273,16 @@
       <c r="A107" s="11"/>
       <c r="B107" s="109"/>
       <c r="C107" s="48" t="str">
-        <f>master!C84</f>
-        <v>ステージングの取り消し</v>
-      </c>
-      <c r="D107" s="105" t="s">
-        <v>413</v>
-      </c>
-      <c r="E107" s="106"/>
-      <c r="F107" s="107"/>
+        <f>master!C85</f>
+        <v>コミットの取り消し</v>
+      </c>
+      <c r="D107" s="104" t="s">
+        <v>409</v>
+      </c>
+      <c r="E107" s="105"/>
+      <c r="F107" s="106"/>
       <c r="G107" s="48" t="s">
-        <v>337</v>
+        <v>334</v>
       </c>
       <c r="H107" s="12"/>
       <c r="I107" s="46" t="s">
@@ -9386,55 +9291,57 @@
       <c r="J107" s="44">
         <v>1.3888888888888889E-3</v>
       </c>
-      <c r="K107" s="90"/>
+      <c r="K107" s="89"/>
       <c r="L107" s="6"/>
       <c r="M107" s="6"/>
       <c r="N107" s="6"/>
     </row>
-    <row r="108" spans="1:14" ht="37.799999999999997">
+    <row r="108" spans="1:14" ht="75.599999999999994">
       <c r="A108" s="11"/>
-      <c r="B108" s="110"/>
+      <c r="B108" s="107" t="str">
+        <f>master!B86</f>
+        <v>リモートリポジトリの操作</v>
+      </c>
       <c r="C108" s="48" t="str">
-        <f>master!C85</f>
-        <v>コミットの取り消し</v>
-      </c>
-      <c r="D108" s="105" t="s">
+        <f>master!C86</f>
+        <v>はじめに</v>
+      </c>
+      <c r="D108" s="104" t="s">
         <v>414</v>
       </c>
-      <c r="E108" s="106"/>
-      <c r="F108" s="107"/>
+      <c r="E108" s="105"/>
+      <c r="F108" s="106"/>
       <c r="G108" s="48" t="s">
-        <v>337</v>
+        <v>396</v>
       </c>
       <c r="H108" s="12"/>
       <c r="I108" s="46" t="s">
-        <v>24</v>
+        <v>49</v>
       </c>
       <c r="J108" s="44">
-        <v>1.3888888888888889E-3</v>
-      </c>
-      <c r="K108" s="90"/>
+        <v>0</v>
+      </c>
+      <c r="K108" s="89" t="s">
+        <v>442</v>
+      </c>
       <c r="L108" s="6"/>
       <c r="M108" s="6"/>
       <c r="N108" s="6"/>
     </row>
-    <row r="109" spans="1:14" ht="75.599999999999994">
+    <row r="109" spans="1:14" ht="37.799999999999997">
       <c r="A109" s="11"/>
-      <c r="B109" s="108" t="str">
-        <f>master!B86</f>
-        <v>リモートリポジトリの操作</v>
-      </c>
+      <c r="B109" s="108"/>
       <c r="C109" s="48" t="str">
-        <f>master!C86</f>
-        <v>はじめに</v>
-      </c>
-      <c r="D109" s="105" t="s">
-        <v>419</v>
-      </c>
-      <c r="E109" s="106"/>
-      <c r="F109" s="107"/>
+        <f>master!C87</f>
+        <v>リポジトリの取得</v>
+      </c>
+      <c r="D109" s="104" t="s">
+        <v>410</v>
+      </c>
+      <c r="E109" s="105"/>
+      <c r="F109" s="106"/>
       <c r="G109" s="48" t="s">
-        <v>401</v>
+        <v>334</v>
       </c>
       <c r="H109" s="12"/>
       <c r="I109" s="46" t="s">
@@ -9443,8 +9350,8 @@
       <c r="J109" s="44">
         <v>0</v>
       </c>
-      <c r="K109" s="90" t="s">
-        <v>433</v>
+      <c r="K109" s="89" t="s">
+        <v>442</v>
       </c>
       <c r="L109" s="6"/>
       <c r="M109" s="6"/>
@@ -9452,18 +9359,18 @@
     </row>
     <row r="110" spans="1:14" ht="37.799999999999997">
       <c r="A110" s="11"/>
-      <c r="B110" s="109"/>
+      <c r="B110" s="108"/>
       <c r="C110" s="48" t="str">
-        <f>master!C87</f>
-        <v>リポジトリの取得</v>
-      </c>
-      <c r="D110" s="105" t="s">
-        <v>415</v>
-      </c>
-      <c r="E110" s="106"/>
-      <c r="F110" s="107"/>
+        <f>master!C88</f>
+        <v>リモートからの取得</v>
+      </c>
+      <c r="D110" s="104" t="s">
+        <v>411</v>
+      </c>
+      <c r="E110" s="105"/>
+      <c r="F110" s="106"/>
       <c r="G110" s="48" t="s">
-        <v>337</v>
+        <v>334</v>
       </c>
       <c r="H110" s="12"/>
       <c r="I110" s="46" t="s">
@@ -9472,8 +9379,8 @@
       <c r="J110" s="44">
         <v>0</v>
       </c>
-      <c r="K110" s="90" t="s">
-        <v>433</v>
+      <c r="K110" s="89" t="s">
+        <v>442</v>
       </c>
       <c r="L110" s="6"/>
       <c r="M110" s="6"/>
@@ -9481,18 +9388,18 @@
     </row>
     <row r="111" spans="1:14" ht="37.799999999999997">
       <c r="A111" s="11"/>
-      <c r="B111" s="109"/>
+      <c r="B111" s="108"/>
       <c r="C111" s="48" t="str">
-        <f>master!C88</f>
-        <v>リモートからの取得</v>
-      </c>
-      <c r="D111" s="105" t="s">
-        <v>416</v>
-      </c>
-      <c r="E111" s="106"/>
-      <c r="F111" s="107"/>
+        <f>master!C89</f>
+        <v>リモートからの取得と反映</v>
+      </c>
+      <c r="D111" s="104" t="s">
+        <v>413</v>
+      </c>
+      <c r="E111" s="105"/>
+      <c r="F111" s="106"/>
       <c r="G111" s="48" t="s">
-        <v>337</v>
+        <v>334</v>
       </c>
       <c r="H111" s="12"/>
       <c r="I111" s="46" t="s">
@@ -9501,8 +9408,8 @@
       <c r="J111" s="44">
         <v>0</v>
       </c>
-      <c r="K111" s="90" t="s">
-        <v>433</v>
+      <c r="K111" s="89" t="s">
+        <v>442</v>
       </c>
       <c r="L111" s="6"/>
       <c r="M111" s="6"/>
@@ -9512,16 +9419,16 @@
       <c r="A112" s="11"/>
       <c r="B112" s="109"/>
       <c r="C112" s="48" t="str">
-        <f>master!C89</f>
-        <v>リモートからの取得と反映</v>
-      </c>
-      <c r="D112" s="105" t="s">
-        <v>418</v>
-      </c>
-      <c r="E112" s="106"/>
-      <c r="F112" s="107"/>
+        <f>master!C90</f>
+        <v>リモートへの反映</v>
+      </c>
+      <c r="D112" s="104" t="s">
+        <v>412</v>
+      </c>
+      <c r="E112" s="105"/>
+      <c r="F112" s="106"/>
       <c r="G112" s="48" t="s">
-        <v>337</v>
+        <v>334</v>
       </c>
       <c r="H112" s="12"/>
       <c r="I112" s="46" t="s">
@@ -9530,27 +9437,30 @@
       <c r="J112" s="44">
         <v>0</v>
       </c>
-      <c r="K112" s="90" t="s">
-        <v>433</v>
+      <c r="K112" s="89" t="s">
+        <v>442</v>
       </c>
       <c r="L112" s="6"/>
       <c r="M112" s="6"/>
       <c r="N112" s="6"/>
     </row>
-    <row r="113" spans="1:14" ht="37.799999999999997">
+    <row r="113" spans="1:14" ht="88.2">
       <c r="A113" s="11"/>
-      <c r="B113" s="110"/>
+      <c r="B113" s="107" t="str">
+        <f>master!B91</f>
+        <v>ブランチの操作</v>
+      </c>
       <c r="C113" s="48" t="str">
-        <f>master!C90</f>
-        <v>リモートへの反映</v>
-      </c>
-      <c r="D113" s="105" t="s">
-        <v>417</v>
-      </c>
-      <c r="E113" s="106"/>
-      <c r="F113" s="107"/>
+        <f>master!C91</f>
+        <v>はじめに</v>
+      </c>
+      <c r="D113" s="104" t="s">
+        <v>415</v>
+      </c>
+      <c r="E113" s="105"/>
+      <c r="F113" s="106"/>
       <c r="G113" s="48" t="s">
-        <v>337</v>
+        <v>401</v>
       </c>
       <c r="H113" s="12"/>
       <c r="I113" s="46" t="s">
@@ -9559,195 +9469,192 @@
       <c r="J113" s="44">
         <v>0</v>
       </c>
-      <c r="K113" s="90" t="s">
-        <v>433</v>
+      <c r="K113" s="89" t="s">
+        <v>440</v>
       </c>
       <c r="L113" s="6"/>
       <c r="M113" s="6"/>
       <c r="N113" s="6"/>
     </row>
-    <row r="114" spans="1:14" ht="88.2">
+    <row r="114" spans="1:14" ht="37.799999999999997">
       <c r="A114" s="11"/>
-      <c r="B114" s="108" t="str">
-        <f>master!B91</f>
-        <v>ブランチの操作</v>
-      </c>
+      <c r="B114" s="108"/>
       <c r="C114" s="48" t="str">
-        <f>master!C91</f>
-        <v>はじめに</v>
-      </c>
-      <c r="D114" s="105" t="s">
-        <v>420</v>
-      </c>
-      <c r="E114" s="106"/>
-      <c r="F114" s="107"/>
+        <f>master!C92</f>
+        <v>ブランチとは</v>
+      </c>
+      <c r="D114" s="104" t="s">
+        <v>419</v>
+      </c>
+      <c r="E114" s="105"/>
+      <c r="F114" s="106"/>
       <c r="G114" s="48" t="s">
-        <v>406</v>
+        <v>334</v>
       </c>
       <c r="H114" s="12"/>
       <c r="I114" s="46" t="s">
-        <v>24</v>
+        <v>49</v>
       </c>
       <c r="J114" s="44">
-        <v>6.9444444444444447E-4</v>
-      </c>
-      <c r="K114" s="90"/>
+        <v>0</v>
+      </c>
+      <c r="K114" s="89"/>
       <c r="L114" s="6"/>
       <c r="M114" s="6"/>
       <c r="N114" s="6"/>
     </row>
     <row r="115" spans="1:14" ht="37.799999999999997">
       <c r="A115" s="11"/>
-      <c r="B115" s="109"/>
+      <c r="B115" s="108"/>
       <c r="C115" s="48" t="str">
-        <f>master!C92</f>
-        <v>ブランチとは</v>
-      </c>
-      <c r="D115" s="105" t="s">
-        <v>424</v>
-      </c>
-      <c r="E115" s="106"/>
-      <c r="F115" s="107"/>
+        <f>master!C93</f>
+        <v>ブランチの作成</v>
+      </c>
+      <c r="D115" s="104" t="s">
+        <v>420</v>
+      </c>
+      <c r="E115" s="105"/>
+      <c r="F115" s="106"/>
       <c r="G115" s="48" t="s">
-        <v>337</v>
+        <v>334</v>
       </c>
       <c r="H115" s="12"/>
       <c r="I115" s="46" t="s">
-        <v>24</v>
+        <v>49</v>
       </c>
       <c r="J115" s="44">
-        <v>1.3888888888888889E-3</v>
-      </c>
-      <c r="K115" s="90"/>
+        <v>0</v>
+      </c>
+      <c r="K115" s="89"/>
       <c r="L115" s="6"/>
       <c r="M115" s="6"/>
       <c r="N115" s="6"/>
     </row>
     <row r="116" spans="1:14" ht="37.799999999999997">
       <c r="A116" s="11"/>
-      <c r="B116" s="109"/>
+      <c r="B116" s="108"/>
       <c r="C116" s="48" t="str">
-        <f>master!C93</f>
-        <v>ブランチの作成</v>
-      </c>
-      <c r="D116" s="105" t="s">
-        <v>425</v>
-      </c>
-      <c r="E116" s="106"/>
-      <c r="F116" s="107"/>
+        <f>master!C94</f>
+        <v>ブランチの切り替え</v>
+      </c>
+      <c r="D116" s="104" t="s">
+        <v>421</v>
+      </c>
+      <c r="E116" s="105"/>
+      <c r="F116" s="106"/>
       <c r="G116" s="48" t="s">
-        <v>337</v>
+        <v>334</v>
       </c>
       <c r="H116" s="12"/>
       <c r="I116" s="46" t="s">
-        <v>24</v>
+        <v>49</v>
       </c>
       <c r="J116" s="44">
-        <v>1.3888888888888889E-3</v>
-      </c>
-      <c r="K116" s="90"/>
+        <v>0</v>
+      </c>
+      <c r="K116" s="89"/>
       <c r="L116" s="6"/>
       <c r="M116" s="6"/>
       <c r="N116" s="6"/>
     </row>
     <row r="117" spans="1:14" ht="37.799999999999997">
       <c r="A117" s="11"/>
-      <c r="B117" s="109"/>
+      <c r="B117" s="108"/>
       <c r="C117" s="48" t="str">
-        <f>master!C94</f>
-        <v>ブランチの切り替え</v>
-      </c>
-      <c r="D117" s="105" t="s">
-        <v>426</v>
-      </c>
-      <c r="E117" s="106"/>
-      <c r="F117" s="107"/>
+        <f>master!C95</f>
+        <v>ブランチのマージ</v>
+      </c>
+      <c r="D117" s="104" t="s">
+        <v>422</v>
+      </c>
+      <c r="E117" s="105"/>
+      <c r="F117" s="106"/>
       <c r="G117" s="48" t="s">
-        <v>337</v>
+        <v>334</v>
       </c>
       <c r="H117" s="12"/>
       <c r="I117" s="46" t="s">
-        <v>24</v>
+        <v>49</v>
       </c>
       <c r="J117" s="44">
-        <v>1.3888888888888889E-3</v>
-      </c>
-      <c r="K117" s="90"/>
+        <v>0</v>
+      </c>
+      <c r="K117" s="89"/>
       <c r="L117" s="6"/>
       <c r="M117" s="6"/>
       <c r="N117" s="6"/>
     </row>
-    <row r="118" spans="1:14" ht="37.799999999999997">
+    <row r="118" spans="1:14" ht="100.8">
       <c r="A118" s="11"/>
       <c r="B118" s="109"/>
       <c r="C118" s="48" t="str">
-        <f>master!C95</f>
-        <v>ブランチのマージ</v>
-      </c>
-      <c r="D118" s="105" t="s">
-        <v>427</v>
-      </c>
-      <c r="E118" s="106"/>
-      <c r="F118" s="107"/>
+        <f>master!C96</f>
+        <v>コンフリクトの解消</v>
+      </c>
+      <c r="D118" s="104" t="s">
+        <v>424</v>
+      </c>
+      <c r="E118" s="105"/>
+      <c r="F118" s="106"/>
       <c r="G118" s="48" t="s">
-        <v>337</v>
+        <v>333</v>
       </c>
       <c r="H118" s="12"/>
       <c r="I118" s="46" t="s">
-        <v>24</v>
+        <v>49</v>
       </c>
       <c r="J118" s="44">
-        <v>1.3888888888888889E-3</v>
-      </c>
-      <c r="K118" s="90"/>
+        <v>0</v>
+      </c>
+      <c r="K118" s="89"/>
       <c r="L118" s="6"/>
       <c r="M118" s="6"/>
       <c r="N118" s="6"/>
     </row>
-    <row r="119" spans="1:14" ht="100.8">
+    <row r="119" spans="1:14" ht="75.599999999999994">
       <c r="A119" s="11"/>
-      <c r="B119" s="110"/>
+      <c r="B119" s="107" t="str">
+        <f>master!B97</f>
+        <v>VSCodeによるGitの操作</v>
+      </c>
       <c r="C119" s="48" t="str">
-        <f>master!C96</f>
-        <v>コンフリクトの解消</v>
-      </c>
-      <c r="D119" s="105" t="s">
-        <v>429</v>
-      </c>
-      <c r="E119" s="106"/>
-      <c r="F119" s="107"/>
+        <f>master!C97</f>
+        <v>はじめに</v>
+      </c>
+      <c r="D119" s="104" t="s">
+        <v>423</v>
+      </c>
+      <c r="E119" s="105"/>
+      <c r="F119" s="106"/>
       <c r="G119" s="48" t="s">
-        <v>336</v>
+        <v>396</v>
       </c>
       <c r="H119" s="12"/>
       <c r="I119" s="46" t="s">
         <v>24</v>
       </c>
       <c r="J119" s="44">
-        <v>2.0833333333333333E-3</v>
-      </c>
-      <c r="K119" s="90"/>
+        <v>6.9444444444444447E-4</v>
+      </c>
+      <c r="K119" s="89"/>
       <c r="L119" s="6"/>
       <c r="M119" s="6"/>
       <c r="N119" s="6"/>
     </row>
-    <row r="120" spans="1:14" ht="75.599999999999994">
+    <row r="120" spans="1:14" ht="25.2">
       <c r="A120" s="11"/>
-      <c r="B120" s="108" t="str">
-        <f>master!B97</f>
-        <v>VSCodeによるGitの操作</v>
-      </c>
+      <c r="B120" s="108"/>
       <c r="C120" s="48" t="str">
-        <f>master!C97</f>
-        <v>はじめに</v>
-      </c>
-      <c r="D120" s="105" t="s">
-        <v>428</v>
-      </c>
-      <c r="E120" s="106"/>
-      <c r="F120" s="107"/>
+        <f>master!C98</f>
+        <v>VSCodeのソース管理機能</v>
+      </c>
+      <c r="D120" s="104" t="s">
+        <v>425</v>
+      </c>
+      <c r="E120" s="105"/>
+      <c r="F120" s="106"/>
       <c r="G120" s="48" t="s">
-        <v>401</v>
+        <v>426</v>
       </c>
       <c r="H120" s="12"/>
       <c r="I120" s="46" t="s">
@@ -9756,52 +9663,52 @@
       <c r="J120" s="44">
         <v>6.9444444444444447E-4</v>
       </c>
-      <c r="K120" s="90"/>
+      <c r="K120" s="89"/>
       <c r="L120" s="6"/>
       <c r="M120" s="6"/>
       <c r="N120" s="6"/>
     </row>
-    <row r="121" spans="1:14" ht="25.2">
+    <row r="121" spans="1:14" ht="126">
       <c r="A121" s="11"/>
-      <c r="B121" s="109"/>
+      <c r="B121" s="108"/>
       <c r="C121" s="48" t="str">
-        <f>master!C98</f>
-        <v>VSCodeのソース管理機能</v>
-      </c>
-      <c r="D121" s="105" t="s">
-        <v>430</v>
-      </c>
-      <c r="E121" s="106"/>
-      <c r="F121" s="107"/>
+        <f>master!C99</f>
+        <v>ローカルリポジトリの操作</v>
+      </c>
+      <c r="D121" s="104" t="s">
+        <v>437</v>
+      </c>
+      <c r="E121" s="105"/>
+      <c r="F121" s="106"/>
       <c r="G121" s="48" t="s">
-        <v>431</v>
+        <v>436</v>
       </c>
       <c r="H121" s="12"/>
       <c r="I121" s="46" t="s">
-        <v>24</v>
+        <v>49</v>
       </c>
       <c r="J121" s="44">
-        <v>6.9444444444444447E-4</v>
-      </c>
-      <c r="K121" s="90"/>
+        <v>0</v>
+      </c>
+      <c r="K121" s="89"/>
       <c r="L121" s="6"/>
       <c r="M121" s="6"/>
       <c r="N121" s="6"/>
     </row>
-    <row r="122" spans="1:14" ht="126">
+    <row r="122" spans="1:14" ht="63">
       <c r="A122" s="11"/>
-      <c r="B122" s="109"/>
+      <c r="B122" s="108"/>
       <c r="C122" s="48" t="str">
-        <f>master!C99</f>
-        <v>ローカルリポジトリの操作</v>
-      </c>
-      <c r="D122" s="105" t="s">
-        <v>444</v>
-      </c>
-      <c r="E122" s="106"/>
-      <c r="F122" s="107"/>
+        <f>master!C100</f>
+        <v>リモートリポジトリの操作</v>
+      </c>
+      <c r="D122" s="104" t="s">
+        <v>427</v>
+      </c>
+      <c r="E122" s="105"/>
+      <c r="F122" s="106"/>
       <c r="G122" s="48" t="s">
-        <v>443</v>
+        <v>336</v>
       </c>
       <c r="H122" s="12"/>
       <c r="I122" s="46" t="s">
@@ -9810,25 +9717,27 @@
       <c r="J122" s="44">
         <v>0</v>
       </c>
-      <c r="K122" s="90"/>
+      <c r="K122" s="89" t="s">
+        <v>442</v>
+      </c>
       <c r="L122" s="6"/>
       <c r="M122" s="6"/>
       <c r="N122" s="6"/>
     </row>
-    <row r="123" spans="1:14" ht="63">
+    <row r="123" spans="1:14" ht="113.4">
       <c r="A123" s="11"/>
       <c r="B123" s="109"/>
       <c r="C123" s="48" t="str">
-        <f>master!C100</f>
-        <v>リモートリポジトリの操作</v>
-      </c>
-      <c r="D123" s="105" t="s">
-        <v>432</v>
-      </c>
-      <c r="E123" s="106"/>
-      <c r="F123" s="107"/>
+        <f>master!C101</f>
+        <v>ブランチの操作</v>
+      </c>
+      <c r="D123" s="104" t="s">
+        <v>438</v>
+      </c>
+      <c r="E123" s="105"/>
+      <c r="F123" s="106"/>
       <c r="G123" s="48" t="s">
-        <v>339</v>
+        <v>439</v>
       </c>
       <c r="H123" s="12"/>
       <c r="I123" s="46" t="s">
@@ -9837,55 +9746,55 @@
       <c r="J123" s="44">
         <v>0</v>
       </c>
-      <c r="K123" s="90" t="s">
-        <v>433</v>
+      <c r="K123" s="89" t="s">
+        <v>441</v>
       </c>
       <c r="L123" s="6"/>
       <c r="M123" s="6"/>
       <c r="N123" s="6"/>
     </row>
-    <row r="124" spans="1:14" ht="113.4">
+    <row r="124" spans="1:14" ht="25.2">
       <c r="A124" s="11"/>
-      <c r="B124" s="110"/>
-      <c r="C124" s="48" t="str">
-        <f>master!C101</f>
-        <v>ブランチの操作</v>
-      </c>
-      <c r="D124" s="105" t="s">
-        <v>445</v>
-      </c>
-      <c r="E124" s="106"/>
-      <c r="F124" s="107"/>
-      <c r="G124" s="48" t="s">
-        <v>446</v>
-      </c>
-      <c r="H124" s="12"/>
-      <c r="I124" s="46" t="s">
-        <v>49</v>
-      </c>
-      <c r="J124" s="44">
-        <v>0</v>
-      </c>
-      <c r="K124" s="90"/>
+      <c r="B124" s="113" t="str">
+        <f>master!B103</f>
+        <v>演習について</v>
+      </c>
+      <c r="C124" s="58" t="str">
+        <f>master!C103</f>
+        <v>はじめに</v>
+      </c>
+      <c r="D124" s="110"/>
+      <c r="E124" s="111"/>
+      <c r="F124" s="112"/>
+      <c r="G124" s="58" t="s">
+        <v>338</v>
+      </c>
+      <c r="H124" s="59"/>
+      <c r="I124" s="60" t="s">
+        <v>24</v>
+      </c>
+      <c r="J124" s="61">
+        <v>6.9444444444444447E-4</v>
+      </c>
+      <c r="K124" s="62"/>
       <c r="L124" s="6"/>
       <c r="M124" s="6"/>
       <c r="N124" s="6"/>
     </row>
-    <row r="125" spans="1:14" ht="25.2">
+    <row r="125" spans="1:14" ht="50.4">
       <c r="A125" s="11"/>
-      <c r="B125" s="114" t="str">
-        <f>master!B103</f>
-        <v>演習について</v>
-      </c>
+      <c r="B125" s="114"/>
       <c r="C125" s="58" t="str">
-        <f>master!C103</f>
-        <v>はじめに</v>
-      </c>
-      <c r="D125" s="111"/>
-      <c r="E125" s="112"/>
-      <c r="F125" s="113"/>
+        <f>master!C104</f>
+        <v>演習の構成</v>
+      </c>
+      <c r="D125" s="110" t="s">
+        <v>429</v>
+      </c>
+      <c r="E125" s="111"/>
+      <c r="F125" s="112"/>
       <c r="G125" s="58" t="s">
-        <v>341</v>
+        <v>428</v>
       </c>
       <c r="H125" s="59"/>
       <c r="I125" s="60" t="s">
@@ -9903,16 +9812,16 @@
       <c r="A126" s="11"/>
       <c r="B126" s="115"/>
       <c r="C126" s="58" t="str">
-        <f>master!C104</f>
-        <v>演習の構成</v>
-      </c>
-      <c r="D126" s="111" t="s">
-        <v>435</v>
-      </c>
-      <c r="E126" s="112"/>
-      <c r="F126" s="113"/>
+        <f>master!C105</f>
+        <v>演習で利用するソフトウェア</v>
+      </c>
+      <c r="D126" s="110" t="s">
+        <v>430</v>
+      </c>
+      <c r="E126" s="111"/>
+      <c r="F126" s="112"/>
       <c r="G126" s="58" t="s">
-        <v>434</v>
+        <v>428</v>
       </c>
       <c r="H126" s="59"/>
       <c r="I126" s="60" t="s">
@@ -9921,57 +9830,57 @@
       <c r="J126" s="61">
         <v>6.9444444444444447E-4</v>
       </c>
-      <c r="K126" s="62"/>
+      <c r="K126" s="62" t="s">
+        <v>443</v>
+      </c>
       <c r="L126" s="6"/>
       <c r="M126" s="6"/>
       <c r="N126" s="6"/>
     </row>
-    <row r="127" spans="1:14" ht="50.4">
+    <row r="127" spans="1:14" ht="176.4">
       <c r="A127" s="11"/>
-      <c r="B127" s="116"/>
+      <c r="B127" s="113" t="str">
+        <f>master!B106</f>
+        <v>VS Codeによるローカルリポジトリの操作</v>
+      </c>
       <c r="C127" s="58" t="str">
-        <f>master!C105</f>
-        <v>演習で利用するソフトウェア</v>
-      </c>
-      <c r="D127" s="111" t="s">
-        <v>436</v>
-      </c>
-      <c r="E127" s="112"/>
-      <c r="F127" s="113"/>
+        <f>master!C106</f>
+        <v>演習の前に</v>
+      </c>
+      <c r="D127" s="110" t="s">
+        <v>434</v>
+      </c>
+      <c r="E127" s="111"/>
+      <c r="F127" s="112"/>
       <c r="G127" s="58" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="H127" s="59"/>
       <c r="I127" s="60" t="s">
         <v>24</v>
       </c>
       <c r="J127" s="61">
-        <v>6.9444444444444447E-4</v>
-      </c>
-      <c r="K127" s="62" t="s">
-        <v>437</v>
-      </c>
+        <v>3.472222222222222E-3</v>
+      </c>
+      <c r="K127" s="62"/>
       <c r="L127" s="6"/>
       <c r="M127" s="6"/>
       <c r="N127" s="6"/>
     </row>
-    <row r="128" spans="1:14" ht="176.4">
+    <row r="128" spans="1:14" ht="37.799999999999997">
       <c r="A128" s="11"/>
-      <c r="B128" s="114" t="str">
-        <f>master!B106</f>
-        <v>VS Codeによるローカルリポジトリの操作</v>
-      </c>
+      <c r="B128" s="114"/>
       <c r="C128" s="58" t="str">
-        <f>master!C106</f>
-        <v>演習の前に</v>
-      </c>
-      <c r="D128" s="111" t="s">
-        <v>441</v>
-      </c>
-      <c r="E128" s="112"/>
-      <c r="F128" s="113"/>
+        <f>master!C107</f>
+        <v>VS Codeによるリポジトリの作成</v>
+      </c>
+      <c r="D128" s="110" t="s">
+        <v>431</v>
+      </c>
+      <c r="E128" s="111"/>
+      <c r="F128" s="112"/>
       <c r="G128" s="58" t="s">
-        <v>440</v>
+        <v>432</v>
       </c>
       <c r="H128" s="59"/>
       <c r="I128" s="60" t="s">
@@ -9987,18 +9896,18 @@
     </row>
     <row r="129" spans="1:14" ht="37.799999999999997">
       <c r="A129" s="11"/>
-      <c r="B129" s="115"/>
+      <c r="B129" s="114"/>
       <c r="C129" s="58" t="str">
-        <f>master!C107</f>
-        <v>VS Codeによるリポジトリの作成</v>
-      </c>
-      <c r="D129" s="111" t="s">
-        <v>438</v>
-      </c>
-      <c r="E129" s="112"/>
-      <c r="F129" s="113"/>
+        <f>master!C108</f>
+        <v>VS Codeによる変更内容の確認</v>
+      </c>
+      <c r="D129" s="110" t="s">
+        <v>431</v>
+      </c>
+      <c r="E129" s="111"/>
+      <c r="F129" s="112"/>
       <c r="G129" s="58" t="s">
-        <v>439</v>
+        <v>432</v>
       </c>
       <c r="H129" s="59"/>
       <c r="I129" s="60" t="s">
@@ -10014,18 +9923,18 @@
     </row>
     <row r="130" spans="1:14" ht="37.799999999999997">
       <c r="A130" s="11"/>
-      <c r="B130" s="115"/>
+      <c r="B130" s="114"/>
       <c r="C130" s="58" t="str">
-        <f>master!C108</f>
-        <v>VS Codeによる変更内容の確認</v>
-      </c>
-      <c r="D130" s="111" t="s">
-        <v>438</v>
-      </c>
-      <c r="E130" s="112"/>
-      <c r="F130" s="113"/>
+        <f>master!C109</f>
+        <v>VS Codeによる変更内容のステージング</v>
+      </c>
+      <c r="D130" s="110" t="s">
+        <v>431</v>
+      </c>
+      <c r="E130" s="111"/>
+      <c r="F130" s="112"/>
       <c r="G130" s="58" t="s">
-        <v>439</v>
+        <v>432</v>
       </c>
       <c r="H130" s="59"/>
       <c r="I130" s="60" t="s">
@@ -10043,16 +9952,16 @@
       <c r="A131" s="11"/>
       <c r="B131" s="115"/>
       <c r="C131" s="58" t="str">
-        <f>master!C109</f>
-        <v>VS Codeによる変更内容のステージング</v>
-      </c>
-      <c r="D131" s="111" t="s">
-        <v>438</v>
-      </c>
-      <c r="E131" s="112"/>
-      <c r="F131" s="113"/>
+        <f>master!C110</f>
+        <v>VS Codeによる変更内容のコミット</v>
+      </c>
+      <c r="D131" s="110" t="s">
+        <v>431</v>
+      </c>
+      <c r="E131" s="111"/>
+      <c r="F131" s="112"/>
       <c r="G131" s="58" t="s">
-        <v>439</v>
+        <v>432</v>
       </c>
       <c r="H131" s="59"/>
       <c r="I131" s="60" t="s">
@@ -10066,86 +9975,92 @@
       <c r="M131" s="6"/>
       <c r="N131" s="6"/>
     </row>
-    <row r="132" spans="1:14" ht="37.799999999999997">
+    <row r="132" spans="1:14" ht="163.80000000000001">
       <c r="A132" s="11"/>
-      <c r="B132" s="116"/>
+      <c r="B132" s="113" t="str">
+        <f>master!B111</f>
+        <v>VS Codeによるブランチの操作</v>
+      </c>
       <c r="C132" s="58" t="str">
-        <f>master!C110</f>
-        <v>VS Codeによる変更内容のコミット</v>
-      </c>
-      <c r="D132" s="111" t="s">
-        <v>438</v>
-      </c>
-      <c r="E132" s="112"/>
-      <c r="F132" s="113"/>
+        <f>master!C111</f>
+        <v>演習の前に</v>
+      </c>
+      <c r="D132" s="110" t="s">
+        <v>435</v>
+      </c>
+      <c r="E132" s="111"/>
+      <c r="F132" s="112"/>
       <c r="G132" s="58" t="s">
-        <v>439</v>
+        <v>337</v>
       </c>
       <c r="H132" s="59"/>
       <c r="I132" s="60" t="s">
-        <v>24</v>
+        <v>49</v>
       </c>
       <c r="J132" s="61">
-        <v>3.472222222222222E-3</v>
-      </c>
-      <c r="K132" s="62"/>
+        <v>0</v>
+      </c>
+      <c r="K132" s="62" t="s">
+        <v>441</v>
+      </c>
       <c r="L132" s="6"/>
       <c r="M132" s="6"/>
       <c r="N132" s="6"/>
     </row>
-    <row r="133" spans="1:14" ht="163.80000000000001">
+    <row r="133" spans="1:14" ht="37.799999999999997">
       <c r="A133" s="11"/>
-      <c r="B133" s="114" t="str">
-        <f>master!B111</f>
-        <v>VS Codeによるブランチの操作</v>
-      </c>
+      <c r="B133" s="114"/>
       <c r="C133" s="58" t="str">
-        <f>master!C111</f>
-        <v>演習の前に</v>
-      </c>
-      <c r="D133" s="111" t="s">
-        <v>442</v>
-      </c>
-      <c r="E133" s="112"/>
-      <c r="F133" s="113"/>
+        <f>master!C112</f>
+        <v>VS Codeによるブランチの作成</v>
+      </c>
+      <c r="D133" s="110" t="s">
+        <v>431</v>
+      </c>
+      <c r="E133" s="111"/>
+      <c r="F133" s="112"/>
       <c r="G133" s="58" t="s">
-        <v>340</v>
+        <v>432</v>
       </c>
       <c r="H133" s="59"/>
       <c r="I133" s="60" t="s">
-        <v>24</v>
+        <v>49</v>
       </c>
       <c r="J133" s="61">
-        <v>3.472222222222222E-3</v>
-      </c>
-      <c r="K133" s="62"/>
+        <v>0</v>
+      </c>
+      <c r="K133" s="62" t="s">
+        <v>441</v>
+      </c>
       <c r="L133" s="6"/>
       <c r="M133" s="6"/>
       <c r="N133" s="6"/>
     </row>
     <row r="134" spans="1:14" ht="37.799999999999997">
       <c r="A134" s="11"/>
-      <c r="B134" s="115"/>
+      <c r="B134" s="114"/>
       <c r="C134" s="58" t="str">
-        <f>master!C112</f>
-        <v>VS Codeによるブランチの作成</v>
-      </c>
-      <c r="D134" s="111" t="s">
-        <v>438</v>
-      </c>
-      <c r="E134" s="112"/>
-      <c r="F134" s="113"/>
+        <f>master!C113</f>
+        <v>VS Codeによるブランチの切り替え</v>
+      </c>
+      <c r="D134" s="110" t="s">
+        <v>431</v>
+      </c>
+      <c r="E134" s="111"/>
+      <c r="F134" s="112"/>
       <c r="G134" s="58" t="s">
-        <v>439</v>
+        <v>432</v>
       </c>
       <c r="H134" s="59"/>
       <c r="I134" s="60" t="s">
-        <v>24</v>
+        <v>49</v>
       </c>
       <c r="J134" s="61">
-        <v>3.472222222222222E-3</v>
-      </c>
-      <c r="K134" s="62"/>
+        <v>0</v>
+      </c>
+      <c r="K134" s="62" t="s">
+        <v>441</v>
+      </c>
       <c r="L134" s="6"/>
       <c r="M134" s="6"/>
       <c r="N134" s="6"/>
@@ -10154,101 +10069,101 @@
       <c r="A135" s="11"/>
       <c r="B135" s="115"/>
       <c r="C135" s="58" t="str">
-        <f>master!C113</f>
-        <v>VS Codeによるブランチの切り替え</v>
-      </c>
-      <c r="D135" s="111" t="s">
-        <v>438</v>
-      </c>
-      <c r="E135" s="112"/>
-      <c r="F135" s="113"/>
+        <f>master!C114</f>
+        <v>VS Codeによるブランチのマージ</v>
+      </c>
+      <c r="D135" s="110" t="s">
+        <v>431</v>
+      </c>
+      <c r="E135" s="111"/>
+      <c r="F135" s="112"/>
       <c r="G135" s="58" t="s">
-        <v>439</v>
+        <v>432</v>
       </c>
       <c r="H135" s="59"/>
       <c r="I135" s="60" t="s">
-        <v>24</v>
+        <v>49</v>
       </c>
       <c r="J135" s="61">
-        <v>3.472222222222222E-3</v>
-      </c>
-      <c r="K135" s="62"/>
+        <v>0</v>
+      </c>
+      <c r="K135" s="62" t="s">
+        <v>441</v>
+      </c>
       <c r="L135" s="6"/>
       <c r="M135" s="6"/>
       <c r="N135" s="6"/>
     </row>
-    <row r="136" spans="1:14" ht="37.799999999999997">
+    <row r="136" spans="1:14" ht="214.2">
       <c r="A136" s="11"/>
-      <c r="B136" s="116"/>
+      <c r="B136" s="86" t="str">
+        <f>master!B67</f>
+        <v>課題1の実施</v>
+      </c>
       <c r="C136" s="58" t="str">
-        <f>master!C114</f>
-        <v>VS Codeによるブランチのマージ</v>
-      </c>
-      <c r="D136" s="111" t="s">
-        <v>438</v>
-      </c>
-      <c r="E136" s="112"/>
-      <c r="F136" s="113"/>
+        <f>master!C67</f>
+        <v>ここから各自で演習を始めましょう。</v>
+      </c>
+      <c r="D136" s="110" t="s">
+        <v>198</v>
+      </c>
+      <c r="E136" s="111"/>
+      <c r="F136" s="112"/>
       <c r="G136" s="58" t="s">
-        <v>439</v>
+        <v>295</v>
       </c>
       <c r="H136" s="59"/>
       <c r="I136" s="60" t="s">
-        <v>24</v>
-      </c>
-      <c r="J136" s="61">
-        <v>3.472222222222222E-3</v>
+        <v>444</v>
+      </c>
+      <c r="J136" s="61" t="s">
+        <v>343</v>
       </c>
       <c r="K136" s="62"/>
       <c r="L136" s="6"/>
       <c r="M136" s="6"/>
       <c r="N136" s="6"/>
     </row>
-    <row r="137" spans="1:14" ht="214.2">
+    <row r="137" spans="1:14" ht="50.4">
       <c r="A137" s="11"/>
-      <c r="B137" s="87" t="str">
-        <f>master!B67</f>
-        <v>課題1の実施</v>
-      </c>
-      <c r="C137" s="58" t="str">
-        <f>master!C67</f>
-        <v>ここから各自で演習を始めましょう。</v>
-      </c>
-      <c r="D137" s="111" t="s">
-        <v>198</v>
-      </c>
-      <c r="E137" s="112"/>
-      <c r="F137" s="113"/>
-      <c r="G137" s="58" t="s">
-        <v>296</v>
-      </c>
-      <c r="H137" s="59"/>
-      <c r="I137" s="60" t="s">
-        <v>24</v>
-      </c>
-      <c r="J137" s="61" t="s">
-        <v>348</v>
-      </c>
-      <c r="K137" s="62"/>
+      <c r="B137" s="122" t="str">
+        <f>master!B116</f>
+        <v>単体テストとJunitの導入</v>
+      </c>
+      <c r="C137" s="78" t="str">
+        <f>master!C116</f>
+        <v>講義の目的</v>
+      </c>
+      <c r="D137" s="104" t="s">
+        <v>227</v>
+      </c>
+      <c r="E137" s="105"/>
+      <c r="F137" s="106"/>
+      <c r="G137" s="48" t="s">
+        <v>299</v>
+      </c>
+      <c r="H137" s="12"/>
+      <c r="I137" s="46" t="s">
+        <v>24</v>
+      </c>
+      <c r="J137" s="44">
+        <v>6.9444444444444447E-4</v>
+      </c>
+      <c r="K137" s="40"/>
       <c r="L137" s="6"/>
       <c r="M137" s="6"/>
       <c r="N137" s="6"/>
     </row>
-    <row r="138" spans="1:14" ht="50.4">
+    <row r="138" spans="1:14" ht="25.2">
       <c r="A138" s="11"/>
-      <c r="B138" s="123" t="str">
-        <f>master!B116</f>
-        <v>単体テストとJunitの導入</v>
-      </c>
+      <c r="B138" s="123"/>
       <c r="C138" s="78" t="str">
-        <f>master!C116</f>
-        <v>講義の目的</v>
-      </c>
-      <c r="D138" s="105" t="s">
-        <v>227</v>
-      </c>
-      <c r="E138" s="106"/>
-      <c r="F138" s="107"/>
+        <f>master!C117</f>
+        <v>TERASOLUNA 開発手順　 ※再掲</v>
+      </c>
+      <c r="D138" s="104"/>
+      <c r="E138" s="105"/>
+      <c r="F138" s="106"/>
       <c r="G138" s="48" t="s">
         <v>300</v>
       </c>
@@ -10268,14 +10183,16 @@
       <c r="A139" s="11"/>
       <c r="B139" s="124"/>
       <c r="C139" s="78" t="str">
-        <f>master!C117</f>
-        <v>TERASOLUNA 開発手順　 ※再掲</v>
-      </c>
-      <c r="D139" s="105"/>
-      <c r="E139" s="106"/>
-      <c r="F139" s="107"/>
+        <f>master!C118</f>
+        <v>V字モデル　 ※再掲</v>
+      </c>
+      <c r="D139" s="104" t="s">
+        <v>228</v>
+      </c>
+      <c r="E139" s="105"/>
+      <c r="F139" s="106"/>
       <c r="G139" s="48" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="H139" s="12"/>
       <c r="I139" s="46" t="s">
@@ -10289,104 +10206,104 @@
       <c r="M139" s="6"/>
       <c r="N139" s="6"/>
     </row>
-    <row r="140" spans="1:14" ht="25.2">
+    <row r="140" spans="1:14" ht="50.4">
       <c r="A140" s="11"/>
-      <c r="B140" s="125"/>
+      <c r="B140" s="122" t="str">
+        <f>master!B119</f>
+        <v>テストとは</v>
+      </c>
       <c r="C140" s="78" t="str">
-        <f>master!C118</f>
-        <v>V字モデル　 ※再掲</v>
-      </c>
-      <c r="D140" s="105" t="s">
-        <v>228</v>
-      </c>
-      <c r="E140" s="106"/>
-      <c r="F140" s="107"/>
+        <f>master!C119</f>
+        <v>テストとは</v>
+      </c>
+      <c r="D140" s="104" t="s">
+        <v>229</v>
+      </c>
+      <c r="E140" s="105"/>
+      <c r="F140" s="106"/>
       <c r="G140" s="48" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="H140" s="12"/>
       <c r="I140" s="46" t="s">
         <v>24</v>
       </c>
       <c r="J140" s="44">
-        <v>6.9444444444444447E-4</v>
+        <v>2.0833333333333333E-3</v>
       </c>
       <c r="K140" s="40"/>
       <c r="L140" s="6"/>
       <c r="M140" s="6"/>
       <c r="N140" s="6"/>
     </row>
-    <row r="141" spans="1:14" ht="50.4">
+    <row r="141" spans="1:14" ht="315">
       <c r="A141" s="11"/>
-      <c r="B141" s="123" t="str">
-        <f>master!B119</f>
-        <v>テストとは</v>
-      </c>
+      <c r="B141" s="123"/>
       <c r="C141" s="78" t="str">
-        <f>master!C119</f>
-        <v>テストとは</v>
-      </c>
-      <c r="D141" s="105" t="s">
-        <v>229</v>
-      </c>
-      <c r="E141" s="106"/>
-      <c r="F141" s="107"/>
+        <f>master!C120</f>
+        <v>テストの目的</v>
+      </c>
+      <c r="D141" s="104" t="s">
+        <v>230</v>
+      </c>
+      <c r="E141" s="105"/>
+      <c r="F141" s="106"/>
       <c r="G141" s="48" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="H141" s="12"/>
       <c r="I141" s="46" t="s">
         <v>24</v>
       </c>
       <c r="J141" s="44">
-        <v>2.0833333333333333E-3</v>
+        <v>3.472222222222222E-3</v>
       </c>
       <c r="K141" s="40"/>
       <c r="L141" s="6"/>
       <c r="M141" s="6"/>
       <c r="N141" s="6"/>
     </row>
-    <row r="142" spans="1:14" ht="315">
+    <row r="142" spans="1:14" ht="25.2">
       <c r="A142" s="11"/>
-      <c r="B142" s="124"/>
+      <c r="B142" s="123"/>
       <c r="C142" s="78" t="str">
-        <f>master!C120</f>
-        <v>テストの目的</v>
-      </c>
-      <c r="D142" s="105" t="s">
-        <v>230</v>
-      </c>
-      <c r="E142" s="106"/>
-      <c r="F142" s="107"/>
+        <f>master!C121</f>
+        <v>テストを実施しなかった場合…</v>
+      </c>
+      <c r="D142" s="104" t="s">
+        <v>231</v>
+      </c>
+      <c r="E142" s="105"/>
+      <c r="F142" s="106"/>
       <c r="G142" s="48" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="H142" s="12"/>
       <c r="I142" s="46" t="s">
         <v>24</v>
       </c>
       <c r="J142" s="44">
-        <v>3.472222222222222E-3</v>
+        <v>2.0833333333333333E-3</v>
       </c>
       <c r="K142" s="40"/>
       <c r="L142" s="6"/>
       <c r="M142" s="6"/>
       <c r="N142" s="6"/>
     </row>
-    <row r="143" spans="1:14" ht="25.2">
+    <row r="143" spans="1:14" ht="100.8">
       <c r="A143" s="11"/>
       <c r="B143" s="124"/>
       <c r="C143" s="78" t="str">
-        <f>master!C121</f>
-        <v>テストを実施しなかった場合…</v>
-      </c>
-      <c r="D143" s="105" t="s">
-        <v>231</v>
-      </c>
-      <c r="E143" s="106"/>
-      <c r="F143" s="107"/>
+        <f>master!C122</f>
+        <v>コラム：テストとデバッグ</v>
+      </c>
+      <c r="D143" s="104" t="s">
+        <v>232</v>
+      </c>
+      <c r="E143" s="105"/>
+      <c r="F143" s="106"/>
       <c r="G143" s="48" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="H143" s="12"/>
       <c r="I143" s="46" t="s">
@@ -10400,48 +10317,46 @@
       <c r="M143" s="6"/>
       <c r="N143" s="6"/>
     </row>
-    <row r="144" spans="1:14" ht="100.8">
+    <row r="144" spans="1:14" ht="50.4">
       <c r="A144" s="11"/>
-      <c r="B144" s="125"/>
+      <c r="B144" s="122" t="str">
+        <f>master!B123</f>
+        <v>単体テストとは</v>
+      </c>
       <c r="C144" s="78" t="str">
-        <f>master!C122</f>
-        <v>コラム：テストとデバッグ</v>
-      </c>
-      <c r="D144" s="105" t="s">
-        <v>232</v>
-      </c>
-      <c r="E144" s="106"/>
-      <c r="F144" s="107"/>
+        <f>master!C123</f>
+        <v>単体テスト（Unit Test）とは</v>
+      </c>
+      <c r="D144" s="104" t="s">
+        <v>233</v>
+      </c>
+      <c r="E144" s="105"/>
+      <c r="F144" s="106"/>
       <c r="G144" s="48" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="H144" s="12"/>
       <c r="I144" s="46" t="s">
         <v>24</v>
       </c>
       <c r="J144" s="44">
-        <v>2.0833333333333333E-3</v>
+        <v>6.9444444444444447E-4</v>
       </c>
       <c r="K144" s="40"/>
       <c r="L144" s="6"/>
       <c r="M144" s="6"/>
       <c r="N144" s="6"/>
     </row>
-    <row r="145" spans="1:14" ht="50.4">
+    <row r="145" spans="1:14" ht="25.2">
       <c r="A145" s="11"/>
-      <c r="B145" s="123" t="str">
-        <f>master!B123</f>
-        <v>単体テストとは</v>
-      </c>
+      <c r="B145" s="123"/>
       <c r="C145" s="78" t="str">
-        <f>master!C123</f>
-        <v>単体テスト（Unit Test）とは</v>
-      </c>
-      <c r="D145" s="105" t="s">
-        <v>233</v>
-      </c>
-      <c r="E145" s="106"/>
-      <c r="F145" s="107"/>
+        <f>master!C124</f>
+        <v xml:space="preserve">V字モデル　– 製造/単体テスト –　※再掲 </v>
+      </c>
+      <c r="D145" s="104"/>
+      <c r="E145" s="105"/>
+      <c r="F145" s="106"/>
       <c r="G145" s="48" t="s">
         <v>300</v>
       </c>
@@ -10457,43 +10372,45 @@
       <c r="M145" s="6"/>
       <c r="N145" s="6"/>
     </row>
-    <row r="146" spans="1:14" ht="25.2">
+    <row r="146" spans="1:14" ht="302.39999999999998">
       <c r="A146" s="11"/>
-      <c r="B146" s="124"/>
+      <c r="B146" s="123"/>
       <c r="C146" s="78" t="str">
-        <f>master!C124</f>
-        <v xml:space="preserve">V字モデル　– 製造/単体テスト –　※再掲 </v>
-      </c>
-      <c r="D146" s="105"/>
-      <c r="E146" s="106"/>
-      <c r="F146" s="107"/>
+        <f>master!C125</f>
+        <v>テスト設計の流れ</v>
+      </c>
+      <c r="D146" s="104" t="s">
+        <v>234</v>
+      </c>
+      <c r="E146" s="105"/>
+      <c r="F146" s="106"/>
       <c r="G146" s="48" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="H146" s="12"/>
       <c r="I146" s="46" t="s">
         <v>24</v>
       </c>
       <c r="J146" s="44">
-        <v>6.9444444444444447E-4</v>
+        <v>3.472222222222222E-3</v>
       </c>
       <c r="K146" s="40"/>
       <c r="L146" s="6"/>
       <c r="M146" s="6"/>
       <c r="N146" s="6"/>
     </row>
-    <row r="147" spans="1:14" ht="302.39999999999998">
+    <row r="147" spans="1:14" ht="37.799999999999997">
       <c r="A147" s="11"/>
-      <c r="B147" s="124"/>
+      <c r="B147" s="123"/>
       <c r="C147" s="78" t="str">
-        <f>master!C125</f>
-        <v>テスト設計の流れ</v>
-      </c>
-      <c r="D147" s="105" t="s">
-        <v>234</v>
-      </c>
-      <c r="E147" s="106"/>
-      <c r="F147" s="107"/>
+        <f>master!C126</f>
+        <v>テスト設計の例</v>
+      </c>
+      <c r="D147" s="104" t="s">
+        <v>235</v>
+      </c>
+      <c r="E147" s="105"/>
+      <c r="F147" s="106"/>
       <c r="G147" s="48" t="s">
         <v>304</v>
       </c>
@@ -10509,18 +10426,18 @@
       <c r="M147" s="6"/>
       <c r="N147" s="6"/>
     </row>
-    <row r="148" spans="1:14" ht="37.799999999999997">
+    <row r="148" spans="1:14" ht="75.599999999999994">
       <c r="A148" s="11"/>
-      <c r="B148" s="124"/>
+      <c r="B148" s="123"/>
       <c r="C148" s="78" t="str">
-        <f>master!C126</f>
-        <v>テスト設計の例</v>
-      </c>
-      <c r="D148" s="105" t="s">
-        <v>235</v>
-      </c>
-      <c r="E148" s="106"/>
-      <c r="F148" s="107"/>
+        <f>master!C127</f>
+        <v>単体テスト（Unit Test）とは</v>
+      </c>
+      <c r="D148" s="104" t="s">
+        <v>236</v>
+      </c>
+      <c r="E148" s="105"/>
+      <c r="F148" s="106"/>
       <c r="G148" s="48" t="s">
         <v>305</v>
       </c>
@@ -10529,25 +10446,25 @@
         <v>24</v>
       </c>
       <c r="J148" s="44">
-        <v>3.472222222222222E-3</v>
+        <v>6.9444444444444447E-4</v>
       </c>
       <c r="K148" s="40"/>
       <c r="L148" s="6"/>
       <c r="M148" s="6"/>
       <c r="N148" s="6"/>
     </row>
-    <row r="149" spans="1:14" ht="75.599999999999994">
+    <row r="149" spans="1:14" ht="113.4">
       <c r="A149" s="11"/>
-      <c r="B149" s="124"/>
+      <c r="B149" s="123"/>
       <c r="C149" s="78" t="str">
-        <f>master!C127</f>
-        <v>単体テスト（Unit Test）とは</v>
-      </c>
-      <c r="D149" s="105" t="s">
-        <v>236</v>
-      </c>
-      <c r="E149" s="106"/>
-      <c r="F149" s="107"/>
+        <f>master!C128</f>
+        <v>テスト技法 – ブラックボックステスト技法 –</v>
+      </c>
+      <c r="D149" s="104" t="s">
+        <v>237</v>
+      </c>
+      <c r="E149" s="105"/>
+      <c r="F149" s="106"/>
       <c r="G149" s="48" t="s">
         <v>306</v>
       </c>
@@ -10556,25 +10473,25 @@
         <v>24</v>
       </c>
       <c r="J149" s="44">
-        <v>6.9444444444444447E-4</v>
+        <v>2.0833333333333333E-3</v>
       </c>
       <c r="K149" s="40"/>
       <c r="L149" s="6"/>
       <c r="M149" s="6"/>
       <c r="N149" s="6"/>
     </row>
-    <row r="150" spans="1:14" ht="113.4">
+    <row r="150" spans="1:14" ht="201.6">
       <c r="A150" s="11"/>
-      <c r="B150" s="124"/>
+      <c r="B150" s="123"/>
       <c r="C150" s="78" t="str">
-        <f>master!C128</f>
-        <v>テスト技法 – ブラックボックステスト技法 –</v>
-      </c>
-      <c r="D150" s="105" t="s">
-        <v>237</v>
-      </c>
-      <c r="E150" s="106"/>
-      <c r="F150" s="107"/>
+        <f>master!C129</f>
+        <v>ブラックボックステスト：同値分割法</v>
+      </c>
+      <c r="D150" s="104" t="s">
+        <v>240</v>
+      </c>
+      <c r="E150" s="105"/>
+      <c r="F150" s="106"/>
       <c r="G150" s="48" t="s">
         <v>307</v>
       </c>
@@ -10583,81 +10500,81 @@
         <v>24</v>
       </c>
       <c r="J150" s="44">
-        <v>2.0833333333333333E-3</v>
+        <v>3.472222222222222E-3</v>
       </c>
       <c r="K150" s="40"/>
       <c r="L150" s="6"/>
       <c r="M150" s="6"/>
       <c r="N150" s="6"/>
     </row>
-    <row r="151" spans="1:14" ht="201.6">
+    <row r="151" spans="1:14" ht="113.4">
       <c r="A151" s="11"/>
-      <c r="B151" s="124"/>
+      <c r="B151" s="123"/>
       <c r="C151" s="78" t="str">
-        <f>master!C129</f>
-        <v>ブラックボックステスト：同値分割法</v>
-      </c>
-      <c r="D151" s="105" t="s">
-        <v>240</v>
-      </c>
-      <c r="E151" s="106"/>
-      <c r="F151" s="107"/>
+        <f>master!C130</f>
+        <v>ブラックボックステスト：境界値分析</v>
+      </c>
+      <c r="D151" s="104" t="s">
+        <v>239</v>
+      </c>
+      <c r="E151" s="105"/>
+      <c r="F151" s="106"/>
       <c r="G151" s="48" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="H151" s="12"/>
       <c r="I151" s="46" t="s">
         <v>24</v>
       </c>
       <c r="J151" s="44">
-        <v>3.472222222222222E-3</v>
+        <v>6.9444444444444441E-3</v>
       </c>
       <c r="K151" s="40"/>
       <c r="L151" s="6"/>
       <c r="M151" s="6"/>
       <c r="N151" s="6"/>
     </row>
-    <row r="152" spans="1:14" ht="113.4">
+    <row r="152" spans="1:14" ht="176.4">
       <c r="A152" s="11"/>
-      <c r="B152" s="124"/>
+      <c r="B152" s="123"/>
       <c r="C152" s="78" t="str">
-        <f>master!C130</f>
-        <v>ブラックボックステスト：境界値分析</v>
-      </c>
-      <c r="D152" s="105" t="s">
-        <v>239</v>
-      </c>
-      <c r="E152" s="106"/>
-      <c r="F152" s="107"/>
+        <f>master!C131</f>
+        <v>ブラックボックステスト：ディシジョンテーブルテスト</v>
+      </c>
+      <c r="D152" s="104" t="s">
+        <v>238</v>
+      </c>
+      <c r="E152" s="105"/>
+      <c r="F152" s="106"/>
       <c r="G152" s="48" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="H152" s="12"/>
       <c r="I152" s="46" t="s">
         <v>24</v>
       </c>
       <c r="J152" s="44">
-        <v>6.9444444444444441E-3</v>
+        <v>3.472222222222222E-3</v>
       </c>
       <c r="K152" s="40"/>
       <c r="L152" s="6"/>
       <c r="M152" s="6"/>
       <c r="N152" s="6"/>
     </row>
-    <row r="153" spans="1:14" ht="176.4">
+    <row r="153" spans="1:14" ht="37.799999999999997">
       <c r="A153" s="11"/>
-      <c r="B153" s="124"/>
+      <c r="B153" s="123"/>
       <c r="C153" s="78" t="str">
-        <f>master!C131</f>
-        <v>ブラックボックステスト：ディシジョンテーブルテスト</v>
-      </c>
-      <c r="D153" s="105" t="s">
-        <v>238</v>
-      </c>
-      <c r="E153" s="106"/>
-      <c r="F153" s="107"/>
+        <f>master!C132</f>
+        <v>ブラックボックステスト：状態遷移テスト</v>
+      </c>
+      <c r="D153" s="104" t="s">
+        <v>241</v>
+      </c>
+      <c r="E153" s="105"/>
+      <c r="F153" s="106"/>
       <c r="G153" s="48" t="s">
-        <v>309</v>
+        <v>304</v>
       </c>
       <c r="H153" s="12"/>
       <c r="I153" s="46" t="s">
@@ -10671,45 +10588,45 @@
       <c r="M153" s="6"/>
       <c r="N153" s="6"/>
     </row>
-    <row r="154" spans="1:14" ht="37.799999999999997">
+    <row r="154" spans="1:14" ht="88.2">
       <c r="A154" s="11"/>
-      <c r="B154" s="124"/>
+      <c r="B154" s="123"/>
       <c r="C154" s="78" t="str">
-        <f>master!C132</f>
-        <v>ブラックボックステスト：状態遷移テスト</v>
-      </c>
-      <c r="D154" s="105" t="s">
-        <v>241</v>
-      </c>
-      <c r="E154" s="106"/>
-      <c r="F154" s="107"/>
+        <f>master!C133</f>
+        <v>テスト技法 – ホワイトボックステスト技法 –</v>
+      </c>
+      <c r="D154" s="104" t="s">
+        <v>242</v>
+      </c>
+      <c r="E154" s="105"/>
+      <c r="F154" s="106"/>
       <c r="G154" s="48" t="s">
-        <v>305</v>
+        <v>309</v>
       </c>
       <c r="H154" s="12"/>
       <c r="I154" s="46" t="s">
         <v>24</v>
       </c>
       <c r="J154" s="44">
-        <v>3.472222222222222E-3</v>
+        <v>2.0833333333333333E-3</v>
       </c>
       <c r="K154" s="40"/>
       <c r="L154" s="6"/>
       <c r="M154" s="6"/>
       <c r="N154" s="6"/>
     </row>
-    <row r="155" spans="1:14" ht="88.2">
+    <row r="155" spans="1:14" ht="151.19999999999999">
       <c r="A155" s="11"/>
-      <c r="B155" s="124"/>
+      <c r="B155" s="123"/>
       <c r="C155" s="78" t="str">
-        <f>master!C133</f>
-        <v>テスト技法 – ホワイトボックステスト技法 –</v>
-      </c>
-      <c r="D155" s="105" t="s">
-        <v>242</v>
-      </c>
-      <c r="E155" s="106"/>
-      <c r="F155" s="107"/>
+        <f>master!C134</f>
+        <v>ホワイトボックステストの評価基準</v>
+      </c>
+      <c r="D155" s="104" t="s">
+        <v>243</v>
+      </c>
+      <c r="E155" s="105"/>
+      <c r="F155" s="106"/>
       <c r="G155" s="48" t="s">
         <v>310</v>
       </c>
@@ -10718,27 +10635,27 @@
         <v>24</v>
       </c>
       <c r="J155" s="44">
-        <v>2.0833333333333333E-3</v>
+        <v>3.472222222222222E-3</v>
       </c>
       <c r="K155" s="40"/>
       <c r="L155" s="6"/>
       <c r="M155" s="6"/>
       <c r="N155" s="6"/>
     </row>
-    <row r="156" spans="1:14" ht="151.19999999999999">
+    <row r="156" spans="1:14" ht="37.799999999999997">
       <c r="A156" s="11"/>
-      <c r="B156" s="124"/>
+      <c r="B156" s="123"/>
       <c r="C156" s="78" t="str">
-        <f>master!C134</f>
-        <v>ホワイトボックステストの評価基準</v>
-      </c>
-      <c r="D156" s="105" t="s">
-        <v>243</v>
-      </c>
-      <c r="E156" s="106"/>
-      <c r="F156" s="107"/>
+        <f>master!C135</f>
+        <v>ホワイトボックステスト：ステートメントテスト</v>
+      </c>
+      <c r="D156" s="104" t="s">
+        <v>244</v>
+      </c>
+      <c r="E156" s="105"/>
+      <c r="F156" s="106"/>
       <c r="G156" s="48" t="s">
-        <v>311</v>
+        <v>304</v>
       </c>
       <c r="H156" s="12"/>
       <c r="I156" s="46" t="s">
@@ -10754,18 +10671,18 @@
     </row>
     <row r="157" spans="1:14" ht="37.799999999999997">
       <c r="A157" s="11"/>
-      <c r="B157" s="124"/>
+      <c r="B157" s="123"/>
       <c r="C157" s="78" t="str">
-        <f>master!C135</f>
-        <v>ホワイトボックステスト：ステートメントテスト</v>
-      </c>
-      <c r="D157" s="105" t="s">
-        <v>244</v>
-      </c>
-      <c r="E157" s="106"/>
-      <c r="F157" s="107"/>
+        <f>master!C136</f>
+        <v>ホワイトボックステスト：ブランチテスト</v>
+      </c>
+      <c r="D157" s="104" t="s">
+        <v>245</v>
+      </c>
+      <c r="E157" s="105"/>
+      <c r="F157" s="106"/>
       <c r="G157" s="48" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="H157" s="12"/>
       <c r="I157" s="46" t="s">
@@ -10781,18 +10698,18 @@
     </row>
     <row r="158" spans="1:14" ht="37.799999999999997">
       <c r="A158" s="11"/>
-      <c r="B158" s="124"/>
+      <c r="B158" s="123"/>
       <c r="C158" s="78" t="str">
-        <f>master!C136</f>
-        <v>ホワイトボックステスト：ブランチテスト</v>
-      </c>
-      <c r="D158" s="105" t="s">
-        <v>245</v>
-      </c>
-      <c r="E158" s="106"/>
-      <c r="F158" s="107"/>
+        <f>master!C137</f>
+        <v>ホワイトボックステスト：コンディションテスト</v>
+      </c>
+      <c r="D158" s="104" t="s">
+        <v>246</v>
+      </c>
+      <c r="E158" s="105"/>
+      <c r="F158" s="106"/>
       <c r="G158" s="48" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="H158" s="12"/>
       <c r="I158" s="46" t="s">
@@ -10808,18 +10725,18 @@
     </row>
     <row r="159" spans="1:14" ht="37.799999999999997">
       <c r="A159" s="11"/>
-      <c r="B159" s="124"/>
+      <c r="B159" s="123"/>
       <c r="C159" s="78" t="str">
-        <f>master!C137</f>
-        <v>ホワイトボックステスト：コンディションテスト</v>
-      </c>
-      <c r="D159" s="105" t="s">
-        <v>246</v>
-      </c>
-      <c r="E159" s="106"/>
-      <c r="F159" s="107"/>
+        <f>master!C138</f>
+        <v>テスト技法 – 経験ベースの技法 –</v>
+      </c>
+      <c r="D159" s="104" t="s">
+        <v>247</v>
+      </c>
+      <c r="E159" s="105"/>
+      <c r="F159" s="106"/>
       <c r="G159" s="48" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="H159" s="12"/>
       <c r="I159" s="46" t="s">
@@ -10833,20 +10750,20 @@
       <c r="M159" s="6"/>
       <c r="N159" s="6"/>
     </row>
-    <row r="160" spans="1:14" ht="37.799999999999997">
+    <row r="160" spans="1:14" ht="100.8">
       <c r="A160" s="11"/>
-      <c r="B160" s="124"/>
+      <c r="B160" s="123"/>
       <c r="C160" s="78" t="str">
-        <f>master!C138</f>
-        <v>テスト技法 – 経験ベースの技法 –</v>
-      </c>
-      <c r="D160" s="105" t="s">
-        <v>247</v>
-      </c>
-      <c r="E160" s="106"/>
-      <c r="F160" s="107"/>
+        <f>master!C139</f>
+        <v>スタブとドライバ</v>
+      </c>
+      <c r="D160" s="104" t="s">
+        <v>248</v>
+      </c>
+      <c r="E160" s="105"/>
+      <c r="F160" s="106"/>
       <c r="G160" s="48" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="H160" s="12"/>
       <c r="I160" s="46" t="s">
@@ -10860,20 +10777,20 @@
       <c r="M160" s="6"/>
       <c r="N160" s="6"/>
     </row>
-    <row r="161" spans="1:14" ht="100.8">
+    <row r="161" spans="1:14" ht="75.599999999999994">
       <c r="A161" s="11"/>
       <c r="B161" s="124"/>
       <c r="C161" s="78" t="str">
-        <f>master!C139</f>
-        <v>スタブとドライバ</v>
-      </c>
-      <c r="D161" s="105" t="s">
-        <v>248</v>
-      </c>
-      <c r="E161" s="106"/>
-      <c r="F161" s="107"/>
+        <f>master!C140</f>
+        <v>スタブとモック</v>
+      </c>
+      <c r="D161" s="104" t="s">
+        <v>249</v>
+      </c>
+      <c r="E161" s="105"/>
+      <c r="F161" s="106"/>
       <c r="G161" s="48" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="H161" s="12"/>
       <c r="I161" s="46" t="s">
@@ -10887,133 +10804,133 @@
       <c r="M161" s="6"/>
       <c r="N161" s="6"/>
     </row>
-    <row r="162" spans="1:14" ht="75.599999999999994">
+    <row r="162" spans="1:14" ht="37.799999999999997">
       <c r="A162" s="11"/>
-      <c r="B162" s="125"/>
+      <c r="B162" s="122" t="str">
+        <f>master!B141</f>
+        <v>JUnit</v>
+      </c>
       <c r="C162" s="78" t="str">
-        <f>master!C140</f>
-        <v>スタブとモック</v>
-      </c>
-      <c r="D162" s="105" t="s">
-        <v>249</v>
-      </c>
-      <c r="E162" s="106"/>
-      <c r="F162" s="107"/>
+        <f>master!C141</f>
+        <v>JUnitとは</v>
+      </c>
+      <c r="D162" s="104" t="s">
+        <v>250</v>
+      </c>
+      <c r="E162" s="105"/>
+      <c r="F162" s="106"/>
       <c r="G162" s="48" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="H162" s="12"/>
       <c r="I162" s="46" t="s">
         <v>24</v>
       </c>
       <c r="J162" s="44">
-        <v>3.472222222222222E-3</v>
+        <v>1.3888888888888889E-3</v>
       </c>
       <c r="K162" s="40"/>
       <c r="L162" s="6"/>
       <c r="M162" s="6"/>
       <c r="N162" s="6"/>
     </row>
-    <row r="163" spans="1:14" ht="37.799999999999997">
+    <row r="163" spans="1:14" ht="25.2">
       <c r="A163" s="11"/>
-      <c r="B163" s="123" t="str">
-        <f>master!B141</f>
-        <v>JUnit</v>
-      </c>
+      <c r="B163" s="124"/>
       <c r="C163" s="78" t="str">
-        <f>master!C141</f>
-        <v>JUnitとは</v>
-      </c>
-      <c r="D163" s="105" t="s">
-        <v>250</v>
-      </c>
-      <c r="E163" s="106"/>
-      <c r="F163" s="107"/>
+        <f>master!C142</f>
+        <v>参考文献</v>
+      </c>
+      <c r="D163" s="104"/>
+      <c r="E163" s="105"/>
+      <c r="F163" s="106"/>
       <c r="G163" s="48" t="s">
-        <v>305</v>
+        <v>300</v>
       </c>
       <c r="H163" s="12"/>
       <c r="I163" s="46" t="s">
         <v>24</v>
       </c>
       <c r="J163" s="44">
-        <v>1.3888888888888889E-3</v>
+        <v>6.9444444444444447E-4</v>
       </c>
       <c r="K163" s="40"/>
       <c r="L163" s="6"/>
       <c r="M163" s="6"/>
       <c r="N163" s="6"/>
     </row>
-    <row r="164" spans="1:14" ht="25.2">
+    <row r="164" spans="1:14" ht="37.799999999999997">
       <c r="A164" s="11"/>
-      <c r="B164" s="125"/>
-      <c r="C164" s="78" t="str">
-        <f>master!C142</f>
-        <v>参考文献</v>
-      </c>
-      <c r="D164" s="105"/>
-      <c r="E164" s="106"/>
-      <c r="F164" s="107"/>
-      <c r="G164" s="48" t="s">
-        <v>301</v>
-      </c>
-      <c r="H164" s="12"/>
-      <c r="I164" s="46" t="s">
-        <v>24</v>
-      </c>
-      <c r="J164" s="44">
-        <v>6.9444444444444447E-4</v>
-      </c>
-      <c r="K164" s="40"/>
+      <c r="B164" s="88" t="str">
+        <f>master!B67</f>
+        <v>課題1の実施</v>
+      </c>
+      <c r="C164" s="58" t="str">
+        <f>master!C67</f>
+        <v>ここから各自で演習を始めましょう。</v>
+      </c>
+      <c r="D164" s="110" t="s">
+        <v>251</v>
+      </c>
+      <c r="E164" s="111"/>
+      <c r="F164" s="112"/>
+      <c r="G164" s="58" t="s">
+        <v>42</v>
+      </c>
+      <c r="H164" s="59"/>
+      <c r="I164" s="60" t="s">
+        <v>24</v>
+      </c>
+      <c r="J164" s="61" t="s">
+        <v>343</v>
+      </c>
+      <c r="K164" s="62"/>
       <c r="L164" s="6"/>
       <c r="M164" s="6"/>
       <c r="N164" s="6"/>
     </row>
-    <row r="165" spans="1:14" ht="37.799999999999997">
+    <row r="165" spans="1:14" ht="25.2">
       <c r="A165" s="11"/>
-      <c r="B165" s="89" t="str">
-        <f>master!B67</f>
-        <v>課題1の実施</v>
+      <c r="B165" s="116" t="str">
+        <f>master!B144</f>
+        <v>課題2の導入</v>
       </c>
       <c r="C165" s="58" t="str">
-        <f>master!C67</f>
-        <v>ここから各自で演習を始めましょう。</v>
-      </c>
-      <c r="D165" s="111" t="s">
-        <v>251</v>
-      </c>
-      <c r="E165" s="112"/>
-      <c r="F165" s="113"/>
+        <f>master!C144</f>
+        <v>演習課題の概要</v>
+      </c>
+      <c r="D165" s="110" t="s">
+        <v>267</v>
+      </c>
+      <c r="E165" s="111"/>
+      <c r="F165" s="112"/>
       <c r="G165" s="58" t="s">
-        <v>42</v>
+        <v>311</v>
       </c>
       <c r="H165" s="59"/>
       <c r="I165" s="60" t="s">
         <v>24</v>
       </c>
-      <c r="J165" s="61" t="s">
-        <v>348</v>
+      <c r="J165" s="61">
+        <v>6.9444444444444447E-4</v>
       </c>
       <c r="K165" s="62"/>
       <c r="L165" s="6"/>
       <c r="M165" s="6"/>
       <c r="N165" s="6"/>
     </row>
-    <row r="166" spans="1:14" ht="25.2">
+    <row r="166" spans="1:14" ht="138.6">
       <c r="A166" s="11"/>
-      <c r="B166" s="117" t="str">
-        <f>master!B144</f>
-        <v>課題2の導入</v>
-      </c>
+      <c r="B166" s="118"/>
       <c r="C166" s="58" t="str">
-        <f>master!C144</f>
-        <v>演習課題の概要</v>
-      </c>
-      <c r="D166" s="111" t="s">
-        <v>267</v>
-      </c>
-      <c r="E166" s="112"/>
-      <c r="F166" s="113"/>
+        <f>master!C145</f>
+        <v>[構造理解] Webアプリケーションで必要なもの  ※再掲</v>
+      </c>
+      <c r="D166" s="110" t="s">
+        <v>268</v>
+      </c>
+      <c r="E166" s="111"/>
+      <c r="F166" s="112"/>
       <c r="G166" s="58" t="s">
         <v>312</v>
       </c>
@@ -11022,25 +10939,25 @@
         <v>24</v>
       </c>
       <c r="J166" s="61">
-        <v>6.9444444444444447E-4</v>
+        <v>2.0833333333333333E-3</v>
       </c>
       <c r="K166" s="62"/>
       <c r="L166" s="6"/>
       <c r="M166" s="6"/>
       <c r="N166" s="6"/>
     </row>
-    <row r="167" spans="1:14" ht="138.6">
+    <row r="167" spans="1:14" ht="50.4">
       <c r="A167" s="11"/>
-      <c r="B167" s="119"/>
+      <c r="B167" s="118"/>
       <c r="C167" s="58" t="str">
-        <f>master!C145</f>
-        <v>[構造理解] Webアプリケーションで必要なもの  ※再掲</v>
-      </c>
-      <c r="D167" s="111" t="s">
-        <v>268</v>
-      </c>
-      <c r="E167" s="112"/>
-      <c r="F167" s="113"/>
+        <f>master!C146</f>
+        <v>テストクラスを作成する単位</v>
+      </c>
+      <c r="D167" s="110" t="s">
+        <v>269</v>
+      </c>
+      <c r="E167" s="111"/>
+      <c r="F167" s="112"/>
       <c r="G167" s="58" t="s">
         <v>313</v>
       </c>
@@ -11056,18 +10973,18 @@
       <c r="M167" s="6"/>
       <c r="N167" s="6"/>
     </row>
-    <row r="168" spans="1:14" ht="50.4">
+    <row r="168" spans="1:14" ht="113.4">
       <c r="A168" s="11"/>
-      <c r="B168" s="119"/>
+      <c r="B168" s="117"/>
       <c r="C168" s="58" t="str">
-        <f>master!C146</f>
-        <v>テストクラスを作成する単位</v>
-      </c>
-      <c r="D168" s="111" t="s">
-        <v>269</v>
-      </c>
-      <c r="E168" s="112"/>
-      <c r="F168" s="113"/>
+        <f>master!C147</f>
+        <v>JUnitで単体テスト</v>
+      </c>
+      <c r="D168" s="110" t="s">
+        <v>270</v>
+      </c>
+      <c r="E168" s="111"/>
+      <c r="F168" s="112"/>
       <c r="G168" s="58" t="s">
         <v>314</v>
       </c>
@@ -11076,159 +10993,159 @@
         <v>24</v>
       </c>
       <c r="J168" s="61">
-        <v>2.0833333333333333E-3</v>
+        <v>3.472222222222222E-3</v>
       </c>
       <c r="K168" s="62"/>
       <c r="L168" s="6"/>
       <c r="M168" s="6"/>
       <c r="N168" s="6"/>
     </row>
-    <row r="169" spans="1:14" ht="113.4">
+    <row r="169" spans="1:14" ht="25.2">
       <c r="A169" s="11"/>
-      <c r="B169" s="118"/>
+      <c r="B169" s="116" t="str">
+        <f>master!B148</f>
+        <v>ハンズオン</v>
+      </c>
       <c r="C169" s="58" t="str">
-        <f>master!C147</f>
-        <v>JUnitで単体テスト</v>
-      </c>
-      <c r="D169" s="111" t="s">
-        <v>270</v>
-      </c>
-      <c r="E169" s="112"/>
-      <c r="F169" s="113"/>
+        <f>master!C148</f>
+        <v>バイブコーディングで単体テスト – はじめに</v>
+      </c>
+      <c r="D169" s="110" t="s">
+        <v>271</v>
+      </c>
+      <c r="E169" s="111"/>
+      <c r="F169" s="112"/>
       <c r="G169" s="58" t="s">
-        <v>315</v>
+        <v>311</v>
       </c>
       <c r="H169" s="59"/>
       <c r="I169" s="60" t="s">
         <v>24</v>
       </c>
       <c r="J169" s="61">
-        <v>3.472222222222222E-3</v>
+        <v>6.9444444444444447E-4</v>
       </c>
       <c r="K169" s="62"/>
       <c r="L169" s="6"/>
       <c r="M169" s="6"/>
       <c r="N169" s="6"/>
     </row>
-    <row r="170" spans="1:14" ht="25.2">
+    <row r="170" spans="1:14" ht="50.4">
       <c r="A170" s="11"/>
-      <c r="B170" s="117" t="str">
-        <f>master!B148</f>
-        <v>ハンズオン</v>
-      </c>
+      <c r="B170" s="118"/>
       <c r="C170" s="58" t="str">
-        <f>master!C148</f>
-        <v>バイブコーディングで単体テスト – はじめに</v>
-      </c>
-      <c r="D170" s="111" t="s">
-        <v>271</v>
-      </c>
-      <c r="E170" s="112"/>
-      <c r="F170" s="113"/>
+        <f>master!C149</f>
+        <v>バイブコーディング単体テスト①テスト項目表を作る</v>
+      </c>
+      <c r="D170" s="110" t="s">
+        <v>272</v>
+      </c>
+      <c r="E170" s="111"/>
+      <c r="F170" s="112"/>
       <c r="G170" s="58" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="H170" s="59"/>
       <c r="I170" s="60" t="s">
         <v>24</v>
       </c>
       <c r="J170" s="61">
-        <v>6.9444444444444447E-4</v>
+        <v>3.472222222222222E-3</v>
       </c>
       <c r="K170" s="62"/>
       <c r="L170" s="6"/>
       <c r="M170" s="6"/>
       <c r="N170" s="6"/>
     </row>
-    <row r="171" spans="1:14" ht="50.4">
+    <row r="171" spans="1:14" ht="88.2">
       <c r="A171" s="11"/>
-      <c r="B171" s="119"/>
-      <c r="C171" s="58" t="str">
-        <f>master!C149</f>
-        <v>バイブコーディング単体テスト①テスト項目表を作る</v>
-      </c>
-      <c r="D171" s="111" t="s">
-        <v>272</v>
-      </c>
-      <c r="E171" s="112"/>
-      <c r="F171" s="113"/>
+      <c r="B171" s="118"/>
+      <c r="C171" s="58"/>
+      <c r="D171" s="110" t="s">
+        <v>183</v>
+      </c>
+      <c r="E171" s="111"/>
+      <c r="F171" s="112"/>
       <c r="G171" s="58" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="H171" s="59"/>
       <c r="I171" s="60" t="s">
         <v>24</v>
       </c>
       <c r="J171" s="61">
-        <v>3.472222222222222E-3</v>
+        <v>6.9444444444444441E-3</v>
       </c>
       <c r="K171" s="62"/>
       <c r="L171" s="6"/>
       <c r="M171" s="6"/>
       <c r="N171" s="6"/>
     </row>
-    <row r="172" spans="1:14" ht="88.2">
+    <row r="172" spans="1:14" ht="50.4">
       <c r="A172" s="11"/>
-      <c r="B172" s="119"/>
-      <c r="C172" s="58"/>
-      <c r="D172" s="111" t="s">
-        <v>183</v>
-      </c>
-      <c r="E172" s="112"/>
-      <c r="F172" s="113"/>
+      <c r="B172" s="118"/>
+      <c r="C172" s="76" t="str">
+        <f>master!C150</f>
+        <v>バイブコーディング単体テスト②Repositoryのテストを作る</v>
+      </c>
+      <c r="D172" s="110" t="s">
+        <v>273</v>
+      </c>
+      <c r="E172" s="111"/>
+      <c r="F172" s="112"/>
       <c r="G172" s="58" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
       <c r="H172" s="59"/>
       <c r="I172" s="60" t="s">
         <v>24</v>
       </c>
       <c r="J172" s="61">
-        <v>6.9444444444444441E-3</v>
+        <v>3.472222222222222E-3</v>
       </c>
       <c r="K172" s="62"/>
       <c r="L172" s="6"/>
       <c r="M172" s="6"/>
       <c r="N172" s="6"/>
     </row>
-    <row r="173" spans="1:14" ht="50.4">
+    <row r="173" spans="1:14" ht="88.2">
       <c r="A173" s="11"/>
-      <c r="B173" s="119"/>
-      <c r="C173" s="76" t="str">
-        <f>master!C150</f>
-        <v>バイブコーディング単体テスト②Repositoryのテストを作る</v>
-      </c>
-      <c r="D173" s="111" t="s">
-        <v>273</v>
-      </c>
-      <c r="E173" s="112"/>
-      <c r="F173" s="113"/>
+      <c r="B173" s="118"/>
+      <c r="C173" s="77"/>
+      <c r="D173" s="110" t="s">
+        <v>183</v>
+      </c>
+      <c r="E173" s="111"/>
+      <c r="F173" s="112"/>
       <c r="G173" s="58" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="H173" s="59"/>
       <c r="I173" s="60" t="s">
         <v>24</v>
       </c>
       <c r="J173" s="61">
-        <v>3.472222222222222E-3</v>
+        <v>6.9444444444444441E-3</v>
       </c>
       <c r="K173" s="62"/>
       <c r="L173" s="6"/>
       <c r="M173" s="6"/>
       <c r="N173" s="6"/>
     </row>
-    <row r="174" spans="1:14" ht="88.2">
+    <row r="174" spans="1:14" ht="138.6">
       <c r="A174" s="11"/>
-      <c r="B174" s="119"/>
-      <c r="C174" s="77"/>
-      <c r="D174" s="111" t="s">
-        <v>183</v>
-      </c>
-      <c r="E174" s="112"/>
-      <c r="F174" s="113"/>
+      <c r="B174" s="118"/>
+      <c r="C174" s="58" t="str">
+        <f>master!C151</f>
+        <v>[解説] Repositoryのテストクラス（抜粋）</v>
+      </c>
+      <c r="D174" s="110" t="s">
+        <v>275</v>
+      </c>
+      <c r="E174" s="111"/>
+      <c r="F174" s="112"/>
       <c r="G174" s="58" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="H174" s="59"/>
       <c r="I174" s="60" t="s">
@@ -11242,18 +11159,18 @@
       <c r="M174" s="6"/>
       <c r="N174" s="6"/>
     </row>
-    <row r="175" spans="1:14" ht="138.6">
+    <row r="175" spans="1:14" ht="50.4">
       <c r="A175" s="11"/>
-      <c r="B175" s="119"/>
-      <c r="C175" s="58" t="str">
-        <f>master!C151</f>
-        <v>[解説] Repositoryのテストクラス（抜粋）</v>
-      </c>
-      <c r="D175" s="111" t="s">
-        <v>275</v>
-      </c>
-      <c r="E175" s="112"/>
-      <c r="F175" s="113"/>
+      <c r="B175" s="118"/>
+      <c r="C175" s="76" t="str">
+        <f>master!C152</f>
+        <v>バイブコーディング単体テスト③Serviceのテストを作る</v>
+      </c>
+      <c r="D175" s="110" t="s">
+        <v>273</v>
+      </c>
+      <c r="E175" s="111"/>
+      <c r="F175" s="112"/>
       <c r="G175" s="58" t="s">
         <v>313</v>
       </c>
@@ -11262,51 +11179,51 @@
         <v>24</v>
       </c>
       <c r="J175" s="61">
-        <v>6.9444444444444441E-3</v>
+        <v>3.472222222222222E-3</v>
       </c>
       <c r="K175" s="62"/>
       <c r="L175" s="6"/>
       <c r="M175" s="6"/>
       <c r="N175" s="6"/>
     </row>
-    <row r="176" spans="1:14" ht="50.4">
+    <row r="176" spans="1:14" ht="88.2">
       <c r="A176" s="11"/>
-      <c r="B176" s="119"/>
-      <c r="C176" s="76" t="str">
-        <f>master!C152</f>
-        <v>バイブコーディング単体テスト③Serviceのテストを作る</v>
-      </c>
-      <c r="D176" s="111" t="s">
-        <v>273</v>
-      </c>
-      <c r="E176" s="112"/>
-      <c r="F176" s="113"/>
+      <c r="B176" s="118"/>
+      <c r="C176" s="77"/>
+      <c r="D176" s="110" t="s">
+        <v>183</v>
+      </c>
+      <c r="E176" s="111"/>
+      <c r="F176" s="112"/>
       <c r="G176" s="58" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="H176" s="59"/>
       <c r="I176" s="60" t="s">
         <v>24</v>
       </c>
       <c r="J176" s="61">
-        <v>3.472222222222222E-3</v>
+        <v>6.9444444444444441E-3</v>
       </c>
       <c r="K176" s="62"/>
       <c r="L176" s="6"/>
       <c r="M176" s="6"/>
       <c r="N176" s="6"/>
     </row>
-    <row r="177" spans="1:14" ht="88.2">
+    <row r="177" spans="1:14" ht="138.6">
       <c r="A177" s="11"/>
-      <c r="B177" s="119"/>
-      <c r="C177" s="77"/>
-      <c r="D177" s="111" t="s">
-        <v>183</v>
-      </c>
-      <c r="E177" s="112"/>
-      <c r="F177" s="113"/>
+      <c r="B177" s="118"/>
+      <c r="C177" s="58" t="str">
+        <f>master!C153</f>
+        <v>[解説] Serviceのテストクラス（抜粋）</v>
+      </c>
+      <c r="D177" s="110" t="s">
+        <v>274</v>
+      </c>
+      <c r="E177" s="111"/>
+      <c r="F177" s="112"/>
       <c r="G177" s="58" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="H177" s="59"/>
       <c r="I177" s="60" t="s">
@@ -11320,18 +11237,18 @@
       <c r="M177" s="6"/>
       <c r="N177" s="6"/>
     </row>
-    <row r="178" spans="1:14" ht="138.6">
+    <row r="178" spans="1:14" ht="50.4">
       <c r="A178" s="11"/>
-      <c r="B178" s="119"/>
-      <c r="C178" s="58" t="str">
-        <f>master!C153</f>
-        <v>[解説] Serviceのテストクラス（抜粋）</v>
-      </c>
-      <c r="D178" s="111" t="s">
-        <v>274</v>
-      </c>
-      <c r="E178" s="112"/>
-      <c r="F178" s="113"/>
+      <c r="B178" s="118"/>
+      <c r="C178" s="76" t="str">
+        <f>master!C154</f>
+        <v>バイブコーディング単体テスト④Controllerのテストを作る</v>
+      </c>
+      <c r="D178" s="110" t="s">
+        <v>273</v>
+      </c>
+      <c r="E178" s="111"/>
+      <c r="F178" s="112"/>
       <c r="G178" s="58" t="s">
         <v>313</v>
       </c>
@@ -11340,49 +11257,49 @@
         <v>24</v>
       </c>
       <c r="J178" s="61">
-        <v>6.9444444444444441E-3</v>
+        <v>3.472222222222222E-3</v>
       </c>
       <c r="K178" s="62"/>
       <c r="L178" s="6"/>
       <c r="M178" s="6"/>
       <c r="N178" s="6"/>
     </row>
-    <row r="179" spans="1:14" ht="50.4">
+    <row r="179" spans="1:14" ht="88.2">
       <c r="A179" s="11"/>
-      <c r="B179" s="119"/>
-      <c r="C179" s="76" t="str">
-        <f>master!C154</f>
-        <v>バイブコーディング単体テスト④Controllerのテストを作る</v>
-      </c>
-      <c r="D179" s="111" t="s">
-        <v>273</v>
-      </c>
-      <c r="E179" s="112"/>
-      <c r="F179" s="113"/>
+      <c r="B179" s="118"/>
+      <c r="C179" s="77"/>
+      <c r="D179" s="110" t="s">
+        <v>183</v>
+      </c>
+      <c r="E179" s="111"/>
+      <c r="F179" s="112"/>
       <c r="G179" s="58" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="H179" s="59"/>
       <c r="I179" s="60" t="s">
         <v>24</v>
       </c>
       <c r="J179" s="61">
-        <v>3.472222222222222E-3</v>
+        <v>6.9444444444444441E-3</v>
       </c>
       <c r="K179" s="62"/>
       <c r="L179" s="6"/>
       <c r="M179" s="6"/>
       <c r="N179" s="6"/>
     </row>
-    <row r="180" spans="1:14" ht="88.2">
+    <row r="180" spans="1:14" ht="163.80000000000001">
       <c r="A180" s="11"/>
-      <c r="B180" s="119"/>
-      <c r="C180" s="77"/>
-      <c r="D180" s="111" t="s">
-        <v>183</v>
-      </c>
-      <c r="E180" s="112"/>
-      <c r="F180" s="113"/>
+      <c r="B180" s="117"/>
+      <c r="C180" s="58" t="str">
+        <f>master!C155</f>
+        <v>[解説] Controllerのテストクラス（抜粋）</v>
+      </c>
+      <c r="D180" s="110" t="s">
+        <v>276</v>
+      </c>
+      <c r="E180" s="111"/>
+      <c r="F180" s="112"/>
       <c r="G180" s="58" t="s">
         <v>316</v>
       </c>
@@ -11398,218 +11315,228 @@
       <c r="M180" s="6"/>
       <c r="N180" s="6"/>
     </row>
-    <row r="181" spans="1:14" ht="163.80000000000001">
+    <row r="181" spans="1:14" ht="165" customHeight="1">
       <c r="A181" s="11"/>
-      <c r="B181" s="118"/>
+      <c r="B181" s="116" t="str">
+        <f>master!B156</f>
+        <v>課題2の実施</v>
+      </c>
       <c r="C181" s="58" t="str">
-        <f>master!C155</f>
-        <v>[解説] Controllerのテストクラス（抜粋）</v>
-      </c>
-      <c r="D181" s="111" t="s">
-        <v>276</v>
-      </c>
-      <c r="E181" s="112"/>
-      <c r="F181" s="113"/>
+        <f>master!C156</f>
+        <v>ここから各自で演習を始めましょう。</v>
+      </c>
+      <c r="D181" s="110" t="s">
+        <v>277</v>
+      </c>
+      <c r="E181" s="111"/>
+      <c r="F181" s="112"/>
       <c r="G181" s="58" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="H181" s="59"/>
       <c r="I181" s="60" t="s">
         <v>24</v>
       </c>
-      <c r="J181" s="61">
-        <v>6.9444444444444441E-3</v>
+      <c r="J181" s="61" t="s">
+        <v>343</v>
       </c>
       <c r="K181" s="62"/>
       <c r="L181" s="6"/>
       <c r="M181" s="6"/>
       <c r="N181" s="6"/>
     </row>
-    <row r="182" spans="1:14" ht="165" customHeight="1">
+    <row r="182" spans="1:14" ht="151.19999999999999">
       <c r="A182" s="11"/>
-      <c r="B182" s="117" t="str">
-        <f>master!B156</f>
-        <v>課題2の実施</v>
-      </c>
+      <c r="B182" s="117"/>
       <c r="C182" s="58" t="str">
-        <f>master!C156</f>
-        <v>ここから各自で演習を始めましょう。</v>
-      </c>
-      <c r="D182" s="111" t="s">
-        <v>277</v>
-      </c>
-      <c r="E182" s="112"/>
-      <c r="F182" s="113"/>
+        <f>master!C157</f>
+        <v>[終了条件] 講師配布のテストプログラム(JUnit)が成功すること</v>
+      </c>
+      <c r="D182" s="110" t="s">
+        <v>342</v>
+      </c>
+      <c r="E182" s="111"/>
+      <c r="F182" s="112"/>
       <c r="G182" s="58" t="s">
-        <v>317</v>
+        <v>341</v>
       </c>
       <c r="H182" s="59"/>
       <c r="I182" s="60" t="s">
-        <v>24</v>
+        <v>49</v>
       </c>
       <c r="J182" s="61" t="s">
-        <v>348</v>
-      </c>
-      <c r="K182" s="62"/>
+        <v>343</v>
+      </c>
+      <c r="K182" s="62" t="s">
+        <v>447</v>
+      </c>
       <c r="L182" s="6"/>
       <c r="M182" s="6"/>
       <c r="N182" s="6"/>
     </row>
-    <row r="183" spans="1:14" ht="151.19999999999999">
+    <row r="183" spans="1:14" ht="163.80000000000001">
       <c r="A183" s="11"/>
-      <c r="B183" s="118"/>
+      <c r="B183" s="116" t="str">
+        <f>master!B159</f>
+        <v>追加課題</v>
+      </c>
       <c r="C183" s="58" t="str">
-        <f>master!C157</f>
-        <v>[終了条件] 講師配布のテストプログラム(JUnit)が成功すること</v>
-      </c>
-      <c r="D183" s="111" t="s">
-        <v>347</v>
-      </c>
-      <c r="E183" s="112"/>
-      <c r="F183" s="113"/>
+        <f>master!C159</f>
+        <v>演習課題の概要</v>
+      </c>
+      <c r="D183" s="110" t="s">
+        <v>279</v>
+      </c>
+      <c r="E183" s="111"/>
+      <c r="F183" s="112"/>
       <c r="G183" s="58" t="s">
-        <v>346</v>
+        <v>337</v>
       </c>
       <c r="H183" s="59"/>
       <c r="I183" s="60" t="s">
-        <v>24</v>
-      </c>
-      <c r="J183" s="61">
-        <v>8.3333333333333329E-2</v>
-      </c>
-      <c r="K183" s="62"/>
+        <v>49</v>
+      </c>
+      <c r="J183" s="61" t="s">
+        <v>343</v>
+      </c>
+      <c r="K183" s="62" t="s">
+        <v>446</v>
+      </c>
       <c r="L183" s="6"/>
       <c r="M183" s="6"/>
       <c r="N183" s="6"/>
     </row>
-    <row r="184" spans="1:14" ht="163.80000000000001">
+    <row r="184" spans="1:14" ht="25.2">
       <c r="A184" s="11"/>
-      <c r="B184" s="117" t="str">
-        <f>master!B159</f>
-        <v>追加課題</v>
-      </c>
+      <c r="B184" s="118"/>
       <c r="C184" s="58" t="str">
-        <f>master!C159</f>
-        <v>演習課題の概要</v>
-      </c>
-      <c r="D184" s="111" t="s">
-        <v>279</v>
-      </c>
-      <c r="E184" s="112"/>
-      <c r="F184" s="113"/>
+        <f>master!C160</f>
+        <v>追加課題①：送料の表示機能</v>
+      </c>
+      <c r="D184" s="110" t="s">
+        <v>281</v>
+      </c>
+      <c r="E184" s="111"/>
+      <c r="F184" s="112"/>
       <c r="G184" s="58" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="H184" s="59"/>
       <c r="I184" s="60" t="s">
-        <v>24</v>
+        <v>49</v>
       </c>
       <c r="J184" s="61" t="s">
-        <v>348</v>
-      </c>
-      <c r="K184" s="62"/>
+        <v>343</v>
+      </c>
+      <c r="K184" s="62" t="s">
+        <v>446</v>
+      </c>
       <c r="L184" s="6"/>
       <c r="M184" s="6"/>
       <c r="N184" s="6"/>
     </row>
     <row r="185" spans="1:14" ht="25.2">
       <c r="A185" s="11"/>
-      <c r="B185" s="119"/>
+      <c r="B185" s="118"/>
       <c r="C185" s="58" t="str">
-        <f>master!C160</f>
-        <v>追加課題①：送料の表示機能</v>
-      </c>
-      <c r="D185" s="111" t="s">
+        <f>master!C161</f>
+        <v>追加課題②：クーポン機能</v>
+      </c>
+      <c r="D185" s="110" t="s">
         <v>281</v>
       </c>
-      <c r="E185" s="112"/>
-      <c r="F185" s="113"/>
+      <c r="E185" s="111"/>
+      <c r="F185" s="112"/>
       <c r="G185" s="58" t="s">
-        <v>341</v>
+        <v>338</v>
       </c>
       <c r="H185" s="59"/>
       <c r="I185" s="60" t="s">
-        <v>24</v>
+        <v>49</v>
       </c>
       <c r="J185" s="61" t="s">
-        <v>348</v>
-      </c>
-      <c r="K185" s="62"/>
+        <v>343</v>
+      </c>
+      <c r="K185" s="62" t="s">
+        <v>446</v>
+      </c>
       <c r="L185" s="6"/>
       <c r="M185" s="6"/>
       <c r="N185" s="6"/>
     </row>
     <row r="186" spans="1:14" ht="25.2">
       <c r="A186" s="11"/>
-      <c r="B186" s="119"/>
+      <c r="B186" s="117"/>
       <c r="C186" s="58" t="str">
-        <f>master!C161</f>
-        <v>追加課題②：クーポン機能</v>
-      </c>
-      <c r="D186" s="111" t="s">
+        <f>master!C162</f>
+        <v>追加課題③：ユーザーアカウント機能</v>
+      </c>
+      <c r="D186" s="110" t="s">
         <v>281</v>
       </c>
-      <c r="E186" s="112"/>
-      <c r="F186" s="113"/>
+      <c r="E186" s="111"/>
+      <c r="F186" s="112"/>
       <c r="G186" s="58" t="s">
-        <v>341</v>
+        <v>338</v>
       </c>
       <c r="H186" s="59"/>
       <c r="I186" s="60" t="s">
-        <v>24</v>
+        <v>49</v>
       </c>
       <c r="J186" s="61" t="s">
-        <v>348</v>
-      </c>
-      <c r="K186" s="62"/>
+        <v>343</v>
+      </c>
+      <c r="K186" s="62" t="s">
+        <v>446</v>
+      </c>
       <c r="L186" s="6"/>
       <c r="M186" s="6"/>
       <c r="N186" s="6"/>
     </row>
-    <row r="187" spans="1:14" ht="25.2">
+    <row r="187" spans="1:14" ht="176.4">
       <c r="A187" s="11"/>
-      <c r="B187" s="118"/>
+      <c r="B187" s="116" t="str">
+        <f>master!B164</f>
+        <v>課題の振り返り</v>
+      </c>
       <c r="C187" s="58" t="str">
-        <f>master!C162</f>
-        <v>追加課題③：ユーザーアカウント機能</v>
-      </c>
-      <c r="D187" s="111" t="s">
-        <v>281</v>
-      </c>
-      <c r="E187" s="112"/>
-      <c r="F187" s="113"/>
+        <f>master!C164</f>
+        <v>サンプルのAPとの自分のAPとの比較</v>
+      </c>
+      <c r="D187" s="110" t="s">
+        <v>339</v>
+      </c>
+      <c r="E187" s="111"/>
+      <c r="F187" s="112"/>
       <c r="G187" s="58" t="s">
-        <v>341</v>
+        <v>448</v>
       </c>
       <c r="H187" s="59"/>
       <c r="I187" s="60" t="s">
         <v>24</v>
       </c>
-      <c r="J187" s="61" t="s">
-        <v>348</v>
+      <c r="J187" s="61">
+        <v>2.0833333333333332E-2</v>
       </c>
       <c r="K187" s="62"/>
       <c r="L187" s="6"/>
       <c r="M187" s="6"/>
       <c r="N187" s="6"/>
     </row>
-    <row r="188" spans="1:14" ht="176.4">
+    <row r="188" spans="1:14" ht="63">
       <c r="A188" s="11"/>
-      <c r="B188" s="117" t="str">
-        <f>master!B164</f>
-        <v>課題の振り返り</v>
-      </c>
+      <c r="B188" s="117"/>
       <c r="C188" s="58" t="str">
-        <f>master!C164</f>
-        <v>サンプルのAPとの自分のAPとの比較</v>
-      </c>
-      <c r="D188" s="111" t="s">
-        <v>343</v>
-      </c>
-      <c r="E188" s="112"/>
-      <c r="F188" s="113"/>
+        <f>master!C165</f>
+        <v>レポートの作成</v>
+      </c>
+      <c r="D188" s="110" t="s">
+        <v>340</v>
+      </c>
+      <c r="E188" s="111"/>
+      <c r="F188" s="112"/>
       <c r="G188" s="58" t="s">
-        <v>344</v>
+        <v>449</v>
       </c>
       <c r="H188" s="59"/>
       <c r="I188" s="60" t="s">
@@ -11623,146 +11550,120 @@
       <c r="M188" s="6"/>
       <c r="N188" s="6"/>
     </row>
-    <row r="189" spans="1:14" ht="63">
-      <c r="A189" s="11"/>
-      <c r="B189" s="118"/>
-      <c r="C189" s="58" t="str">
-        <f>master!C165</f>
-        <v>レポートの作成</v>
-      </c>
-      <c r="D189" s="111" t="s">
-        <v>345</v>
-      </c>
-      <c r="E189" s="112"/>
-      <c r="F189" s="113"/>
-      <c r="G189" s="58" t="s">
-        <v>342</v>
-      </c>
-      <c r="H189" s="59"/>
-      <c r="I189" s="60" t="s">
-        <v>24</v>
-      </c>
-      <c r="J189" s="61">
-        <v>2.0833333333333332E-2</v>
-      </c>
-      <c r="K189" s="62"/>
-      <c r="L189" s="6"/>
-      <c r="M189" s="6"/>
-      <c r="N189" s="6"/>
-    </row>
-    <row r="190" spans="1:14" ht="15" customHeight="1">
-      <c r="J190" s="43"/>
-    </row>
-    <row r="191" spans="1:14" ht="15" customHeight="1"/>
+    <row r="189" spans="1:14" ht="15" customHeight="1">
+      <c r="J189" s="43"/>
+    </row>
+    <row r="190" spans="1:14" ht="15" customHeight="1"/>
   </sheetData>
   <mergeCells count="203">
-    <mergeCell ref="D153:F153"/>
-    <mergeCell ref="B138:B140"/>
-    <mergeCell ref="B163:B164"/>
+    <mergeCell ref="D152:F152"/>
+    <mergeCell ref="B137:B139"/>
+    <mergeCell ref="B162:B163"/>
+    <mergeCell ref="D164:F164"/>
+    <mergeCell ref="D187:F187"/>
+    <mergeCell ref="D184:F184"/>
+    <mergeCell ref="D183:F183"/>
     <mergeCell ref="D165:F165"/>
-    <mergeCell ref="D188:F188"/>
-    <mergeCell ref="D185:F185"/>
-    <mergeCell ref="D184:F184"/>
     <mergeCell ref="D166:F166"/>
     <mergeCell ref="D167:F167"/>
+    <mergeCell ref="D180:F180"/>
+    <mergeCell ref="D181:F181"/>
     <mergeCell ref="D168:F168"/>
-    <mergeCell ref="D181:F181"/>
-    <mergeCell ref="D182:F182"/>
     <mergeCell ref="D169:F169"/>
-    <mergeCell ref="D170:F170"/>
-    <mergeCell ref="D178:F178"/>
-    <mergeCell ref="D172:F172"/>
+    <mergeCell ref="D177:F177"/>
+    <mergeCell ref="D171:F171"/>
+    <mergeCell ref="D173:F173"/>
     <mergeCell ref="D174:F174"/>
-    <mergeCell ref="D175:F175"/>
-    <mergeCell ref="B170:B181"/>
-    <mergeCell ref="B166:B169"/>
-    <mergeCell ref="B141:B144"/>
-    <mergeCell ref="B145:B162"/>
+    <mergeCell ref="B169:B180"/>
+    <mergeCell ref="B165:B168"/>
+    <mergeCell ref="B140:B143"/>
+    <mergeCell ref="B144:B161"/>
+    <mergeCell ref="D139:F139"/>
     <mergeCell ref="D140:F140"/>
     <mergeCell ref="D141:F141"/>
     <mergeCell ref="D142:F142"/>
-    <mergeCell ref="D143:F143"/>
+    <mergeCell ref="D144:F144"/>
     <mergeCell ref="D145:F145"/>
     <mergeCell ref="D146:F146"/>
     <mergeCell ref="D147:F147"/>
     <mergeCell ref="D148:F148"/>
-    <mergeCell ref="D149:F149"/>
+    <mergeCell ref="D160:F160"/>
     <mergeCell ref="D161:F161"/>
-    <mergeCell ref="D162:F162"/>
-    <mergeCell ref="D144:F144"/>
+    <mergeCell ref="D143:F143"/>
+    <mergeCell ref="D155:F155"/>
     <mergeCell ref="D156:F156"/>
     <mergeCell ref="D157:F157"/>
     <mergeCell ref="D158:F158"/>
     <mergeCell ref="D159:F159"/>
-    <mergeCell ref="D160:F160"/>
-    <mergeCell ref="D155:F155"/>
     <mergeCell ref="D154:F154"/>
+    <mergeCell ref="D153:F153"/>
+    <mergeCell ref="D149:F149"/>
     <mergeCell ref="D150:F150"/>
     <mergeCell ref="D151:F151"/>
-    <mergeCell ref="D152:F152"/>
-    <mergeCell ref="D139:F139"/>
     <mergeCell ref="D138:F138"/>
-    <mergeCell ref="D112:F112"/>
+    <mergeCell ref="D137:F137"/>
     <mergeCell ref="D111:F111"/>
     <mergeCell ref="D110:F110"/>
-    <mergeCell ref="D113:F113"/>
+    <mergeCell ref="D109:F109"/>
+    <mergeCell ref="D112:F112"/>
+    <mergeCell ref="D103:F103"/>
+    <mergeCell ref="D99:F99"/>
+    <mergeCell ref="D123:F123"/>
+    <mergeCell ref="D136:F136"/>
+    <mergeCell ref="D101:F101"/>
+    <mergeCell ref="D102:F102"/>
     <mergeCell ref="D104:F104"/>
-    <mergeCell ref="D100:F100"/>
-    <mergeCell ref="D124:F124"/>
-    <mergeCell ref="D137:F137"/>
-    <mergeCell ref="D102:F102"/>
-    <mergeCell ref="D103:F103"/>
     <mergeCell ref="D105:F105"/>
     <mergeCell ref="D106:F106"/>
     <mergeCell ref="D107:F107"/>
-    <mergeCell ref="D108:F108"/>
+    <mergeCell ref="D78:F78"/>
+    <mergeCell ref="D80:F80"/>
+    <mergeCell ref="D74:F74"/>
+    <mergeCell ref="D85:F85"/>
+    <mergeCell ref="D90:F90"/>
+    <mergeCell ref="D82:F82"/>
+    <mergeCell ref="D83:F83"/>
+    <mergeCell ref="B71:B90"/>
+    <mergeCell ref="D84:F84"/>
+    <mergeCell ref="D86:F86"/>
+    <mergeCell ref="D87:F87"/>
+    <mergeCell ref="D88:F88"/>
+    <mergeCell ref="D89:F89"/>
+    <mergeCell ref="D77:F77"/>
     <mergeCell ref="D79:F79"/>
     <mergeCell ref="D81:F81"/>
     <mergeCell ref="D75:F75"/>
-    <mergeCell ref="D86:F86"/>
-    <mergeCell ref="D91:F91"/>
-    <mergeCell ref="D83:F83"/>
-    <mergeCell ref="D84:F84"/>
-    <mergeCell ref="B72:B91"/>
-    <mergeCell ref="D85:F85"/>
-    <mergeCell ref="D87:F87"/>
-    <mergeCell ref="D88:F88"/>
-    <mergeCell ref="D89:F89"/>
-    <mergeCell ref="D90:F90"/>
-    <mergeCell ref="D78:F78"/>
-    <mergeCell ref="D80:F80"/>
-    <mergeCell ref="D82:F82"/>
-    <mergeCell ref="D76:F76"/>
-    <mergeCell ref="D74:F74"/>
-    <mergeCell ref="B56:B58"/>
+    <mergeCell ref="D73:F73"/>
+    <mergeCell ref="B55:B57"/>
+    <mergeCell ref="D69:F69"/>
     <mergeCell ref="D70:F70"/>
     <mergeCell ref="D71:F71"/>
     <mergeCell ref="D72:F72"/>
-    <mergeCell ref="D73:F73"/>
-    <mergeCell ref="D63:F63"/>
+    <mergeCell ref="D62:F62"/>
+    <mergeCell ref="D56:F56"/>
     <mergeCell ref="D57:F57"/>
     <mergeCell ref="D58:F58"/>
     <mergeCell ref="D59:F59"/>
+    <mergeCell ref="D66:F66"/>
+    <mergeCell ref="D67:F67"/>
     <mergeCell ref="D60:F60"/>
-    <mergeCell ref="D67:F67"/>
-    <mergeCell ref="D68:F68"/>
     <mergeCell ref="D61:F61"/>
-    <mergeCell ref="D62:F62"/>
+    <mergeCell ref="D63:F63"/>
     <mergeCell ref="D64:F64"/>
     <mergeCell ref="D65:F65"/>
-    <mergeCell ref="D66:F66"/>
-    <mergeCell ref="D69:F69"/>
-    <mergeCell ref="D56:F56"/>
-    <mergeCell ref="B63:B71"/>
-    <mergeCell ref="B59:B62"/>
-    <mergeCell ref="B23:B28"/>
-    <mergeCell ref="B29:B36"/>
-    <mergeCell ref="B37:B55"/>
+    <mergeCell ref="D68:F68"/>
+    <mergeCell ref="D55:F55"/>
+    <mergeCell ref="B62:B70"/>
+    <mergeCell ref="B58:B61"/>
+    <mergeCell ref="B22:B27"/>
+    <mergeCell ref="B28:B35"/>
+    <mergeCell ref="B36:B54"/>
+    <mergeCell ref="D49:F49"/>
     <mergeCell ref="D50:F50"/>
     <mergeCell ref="D51:F51"/>
     <mergeCell ref="D52:F52"/>
     <mergeCell ref="D53:F53"/>
-    <mergeCell ref="D54:F54"/>
+    <mergeCell ref="D37:F37"/>
     <mergeCell ref="D38:F38"/>
     <mergeCell ref="D39:F39"/>
     <mergeCell ref="D40:F40"/>
@@ -11771,55 +11672,53 @@
     <mergeCell ref="D43:F43"/>
     <mergeCell ref="D44:F44"/>
     <mergeCell ref="D45:F45"/>
-    <mergeCell ref="D46:F46"/>
-    <mergeCell ref="I20:J20"/>
-    <mergeCell ref="H20:H21"/>
+    <mergeCell ref="I19:J19"/>
+    <mergeCell ref="H19:H20"/>
     <mergeCell ref="B4:E4"/>
     <mergeCell ref="B5:K5"/>
-    <mergeCell ref="D20:F21"/>
-    <mergeCell ref="G20:G21"/>
-    <mergeCell ref="B20:B21"/>
-    <mergeCell ref="C20:C21"/>
-    <mergeCell ref="K20:K21"/>
+    <mergeCell ref="D19:F20"/>
+    <mergeCell ref="G19:G20"/>
+    <mergeCell ref="B19:B20"/>
+    <mergeCell ref="C19:C20"/>
+    <mergeCell ref="K19:K20"/>
     <mergeCell ref="D7:E7"/>
+    <mergeCell ref="D162:F162"/>
     <mergeCell ref="D163:F163"/>
-    <mergeCell ref="D164:F164"/>
+    <mergeCell ref="D21:F21"/>
+    <mergeCell ref="D35:F35"/>
     <mergeCell ref="D22:F22"/>
-    <mergeCell ref="D36:F36"/>
+    <mergeCell ref="D28:F28"/>
     <mergeCell ref="D23:F23"/>
-    <mergeCell ref="D29:F29"/>
+    <mergeCell ref="D25:F25"/>
+    <mergeCell ref="D27:F27"/>
+    <mergeCell ref="D34:F34"/>
     <mergeCell ref="D24:F24"/>
     <mergeCell ref="D26:F26"/>
-    <mergeCell ref="D28:F28"/>
-    <mergeCell ref="D35:F35"/>
-    <mergeCell ref="D25:F25"/>
-    <mergeCell ref="D27:F27"/>
+    <mergeCell ref="D29:F29"/>
     <mergeCell ref="D30:F30"/>
     <mergeCell ref="D31:F31"/>
     <mergeCell ref="D32:F32"/>
     <mergeCell ref="D33:F33"/>
-    <mergeCell ref="D34:F34"/>
+    <mergeCell ref="D46:F46"/>
     <mergeCell ref="D47:F47"/>
     <mergeCell ref="D48:F48"/>
-    <mergeCell ref="D49:F49"/>
-    <mergeCell ref="D55:F55"/>
-    <mergeCell ref="D37:F37"/>
-    <mergeCell ref="D92:F92"/>
-    <mergeCell ref="D77:F77"/>
-    <mergeCell ref="D187:F187"/>
+    <mergeCell ref="D54:F54"/>
+    <mergeCell ref="D36:F36"/>
+    <mergeCell ref="D91:F91"/>
+    <mergeCell ref="D76:F76"/>
     <mergeCell ref="D186:F186"/>
-    <mergeCell ref="D189:F189"/>
-    <mergeCell ref="B188:B189"/>
-    <mergeCell ref="D171:F171"/>
-    <mergeCell ref="D173:F173"/>
+    <mergeCell ref="D185:F185"/>
+    <mergeCell ref="D188:F188"/>
+    <mergeCell ref="B187:B188"/>
+    <mergeCell ref="D170:F170"/>
+    <mergeCell ref="D172:F172"/>
+    <mergeCell ref="D175:F175"/>
     <mergeCell ref="D176:F176"/>
-    <mergeCell ref="D177:F177"/>
+    <mergeCell ref="D178:F178"/>
     <mergeCell ref="D179:F179"/>
-    <mergeCell ref="D180:F180"/>
-    <mergeCell ref="B184:B187"/>
-    <mergeCell ref="D183:F183"/>
-    <mergeCell ref="B182:B183"/>
-    <mergeCell ref="D121:F121"/>
+    <mergeCell ref="B183:B186"/>
+    <mergeCell ref="D182:F182"/>
+    <mergeCell ref="B181:B182"/>
     <mergeCell ref="D120:F120"/>
     <mergeCell ref="D119:F119"/>
     <mergeCell ref="D118:F118"/>
@@ -11827,38 +11726,39 @@
     <mergeCell ref="D116:F116"/>
     <mergeCell ref="D115:F115"/>
     <mergeCell ref="D114:F114"/>
+    <mergeCell ref="D113:F113"/>
+    <mergeCell ref="D92:F92"/>
     <mergeCell ref="D93:F93"/>
     <mergeCell ref="D94:F94"/>
     <mergeCell ref="D95:F95"/>
     <mergeCell ref="D96:F96"/>
     <mergeCell ref="D97:F97"/>
     <mergeCell ref="D98:F98"/>
-    <mergeCell ref="D99:F99"/>
-    <mergeCell ref="D101:F101"/>
-    <mergeCell ref="D123:F123"/>
-    <mergeCell ref="B120:B124"/>
-    <mergeCell ref="B114:B119"/>
-    <mergeCell ref="B109:B113"/>
-    <mergeCell ref="B100:B108"/>
-    <mergeCell ref="B95:B99"/>
-    <mergeCell ref="B92:B94"/>
+    <mergeCell ref="D100:F100"/>
+    <mergeCell ref="D122:F122"/>
+    <mergeCell ref="B119:B123"/>
+    <mergeCell ref="B113:B118"/>
+    <mergeCell ref="B108:B112"/>
+    <mergeCell ref="B99:B107"/>
+    <mergeCell ref="B94:B98"/>
+    <mergeCell ref="B91:B93"/>
+    <mergeCell ref="D124:F124"/>
+    <mergeCell ref="D135:F135"/>
+    <mergeCell ref="D133:F133"/>
+    <mergeCell ref="D131:F131"/>
+    <mergeCell ref="D132:F132"/>
+    <mergeCell ref="D129:F129"/>
+    <mergeCell ref="D130:F130"/>
+    <mergeCell ref="D127:F127"/>
+    <mergeCell ref="D128:F128"/>
     <mergeCell ref="D125:F125"/>
-    <mergeCell ref="D136:F136"/>
+    <mergeCell ref="D126:F126"/>
     <mergeCell ref="D134:F134"/>
-    <mergeCell ref="D132:F132"/>
-    <mergeCell ref="D133:F133"/>
-    <mergeCell ref="D130:F130"/>
-    <mergeCell ref="D131:F131"/>
-    <mergeCell ref="D128:F128"/>
-    <mergeCell ref="D129:F129"/>
-    <mergeCell ref="D126:F126"/>
-    <mergeCell ref="D127:F127"/>
-    <mergeCell ref="D135:F135"/>
-    <mergeCell ref="B133:B136"/>
-    <mergeCell ref="B128:B132"/>
-    <mergeCell ref="B125:B127"/>
-    <mergeCell ref="D109:F109"/>
-    <mergeCell ref="D122:F122"/>
+    <mergeCell ref="B132:B135"/>
+    <mergeCell ref="B127:B131"/>
+    <mergeCell ref="B124:B126"/>
+    <mergeCell ref="D108:F108"/>
+    <mergeCell ref="D121:F121"/>
   </mergeCells>
   <phoneticPr fontId="3"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -11871,7 +11771,7 @@
           <x14:formula1>
             <xm:f>master!#REF!</xm:f>
           </x14:formula1>
-          <xm:sqref>H22:H189</xm:sqref>
+          <xm:sqref>H21:H188</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -11904,7 +11804,7 @@
     </row>
     <row r="3" spans="2:3">
       <c r="B3" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="C3" t="s">
         <v>54</v>
@@ -12085,7 +11985,7 @@
     </row>
     <row r="37" spans="2:3">
       <c r="B37" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="C37" t="s">
         <v>164</v>
@@ -12174,7 +12074,7 @@
     </row>
     <row r="53" spans="2:3">
       <c r="B53" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="C53" t="s">
         <v>148</v>
@@ -12247,7 +12147,7 @@
     </row>
     <row r="67" spans="2:3">
       <c r="B67" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="C67" t="s">
         <v>161</v>
@@ -12262,182 +12162,182 @@
         <v>163</v>
       </c>
       <c r="C69" t="s">
-        <v>349</v>
+        <v>344</v>
       </c>
     </row>
     <row r="70" spans="2:3">
       <c r="C70" t="s">
-        <v>350</v>
+        <v>345</v>
       </c>
     </row>
     <row r="71" spans="2:3">
       <c r="C71" t="s">
-        <v>351</v>
+        <v>346</v>
       </c>
     </row>
     <row r="72" spans="2:3">
       <c r="B72" t="s">
-        <v>352</v>
+        <v>347</v>
       </c>
       <c r="C72" t="s">
-        <v>349</v>
+        <v>344</v>
       </c>
     </row>
     <row r="73" spans="2:3">
       <c r="C73" t="s">
-        <v>353</v>
+        <v>348</v>
       </c>
     </row>
     <row r="74" spans="2:3">
       <c r="C74" t="s">
-        <v>354</v>
+        <v>349</v>
       </c>
     </row>
     <row r="75" spans="2:3">
       <c r="C75" t="s">
-        <v>355</v>
+        <v>350</v>
       </c>
     </row>
     <row r="76" spans="2:3">
       <c r="C76" t="s">
-        <v>356</v>
+        <v>351</v>
       </c>
     </row>
     <row r="77" spans="2:3">
       <c r="B77" t="s">
-        <v>357</v>
+        <v>352</v>
       </c>
       <c r="C77" t="s">
-        <v>349</v>
+        <v>344</v>
       </c>
     </row>
     <row r="78" spans="2:3">
       <c r="C78" t="s">
-        <v>358</v>
+        <v>353</v>
       </c>
     </row>
     <row r="79" spans="2:3">
       <c r="C79" t="s">
-        <v>359</v>
+        <v>354</v>
       </c>
     </row>
     <row r="80" spans="2:3">
       <c r="C80" t="s">
-        <v>360</v>
+        <v>355</v>
       </c>
     </row>
     <row r="81" spans="2:3">
       <c r="C81" t="s">
-        <v>361</v>
+        <v>356</v>
       </c>
     </row>
     <row r="82" spans="2:3">
       <c r="C82" t="s">
-        <v>362</v>
+        <v>357</v>
       </c>
     </row>
     <row r="83" spans="2:3">
       <c r="C83" t="s">
-        <v>363</v>
+        <v>358</v>
       </c>
     </row>
     <row r="84" spans="2:3">
       <c r="C84" t="s">
-        <v>364</v>
+        <v>359</v>
       </c>
     </row>
     <row r="85" spans="2:3">
       <c r="C85" t="s">
-        <v>365</v>
+        <v>360</v>
       </c>
     </row>
     <row r="86" spans="2:3">
       <c r="B86" t="s">
-        <v>366</v>
+        <v>361</v>
       </c>
       <c r="C86" t="s">
-        <v>349</v>
+        <v>344</v>
       </c>
     </row>
     <row r="87" spans="2:3">
       <c r="C87" t="s">
-        <v>382</v>
+        <v>377</v>
       </c>
     </row>
     <row r="88" spans="2:3">
       <c r="C88" t="s">
-        <v>381</v>
+        <v>376</v>
       </c>
     </row>
     <row r="89" spans="2:3">
       <c r="C89" t="s">
-        <v>380</v>
+        <v>375</v>
       </c>
     </row>
     <row r="90" spans="2:3">
       <c r="C90" t="s">
-        <v>379</v>
+        <v>374</v>
       </c>
     </row>
     <row r="91" spans="2:3">
       <c r="B91" t="s">
-        <v>367</v>
+        <v>362</v>
       </c>
       <c r="C91" t="s">
-        <v>349</v>
+        <v>344</v>
       </c>
     </row>
     <row r="92" spans="2:3">
       <c r="C92" t="s">
-        <v>368</v>
+        <v>363</v>
       </c>
     </row>
     <row r="93" spans="2:3">
       <c r="C93" t="s">
-        <v>378</v>
+        <v>373</v>
       </c>
     </row>
     <row r="94" spans="2:3">
       <c r="C94" t="s">
-        <v>377</v>
+        <v>372</v>
       </c>
     </row>
     <row r="95" spans="2:3">
       <c r="C95" t="s">
-        <v>376</v>
+        <v>371</v>
       </c>
     </row>
     <row r="96" spans="2:3">
       <c r="C96" t="s">
-        <v>369</v>
+        <v>364</v>
       </c>
     </row>
     <row r="97" spans="2:3">
       <c r="B97" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="C97" t="s">
-        <v>372</v>
+        <v>367</v>
       </c>
     </row>
     <row r="98" spans="2:3">
       <c r="C98" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
     </row>
     <row r="99" spans="2:3">
       <c r="C99" t="s">
-        <v>373</v>
+        <v>368</v>
       </c>
     </row>
     <row r="100" spans="2:3">
       <c r="C100" t="s">
-        <v>374</v>
+        <v>369</v>
       </c>
     </row>
     <row r="101" spans="2:3">
       <c r="C101" t="s">
-        <v>375</v>
+        <v>370</v>
       </c>
     </row>
     <row r="102" spans="2:3">
@@ -12446,71 +12346,71 @@
     </row>
     <row r="103" spans="2:3">
       <c r="B103" t="s">
-        <v>383</v>
+        <v>378</v>
       </c>
       <c r="C103" t="s">
-        <v>349</v>
+        <v>344</v>
       </c>
     </row>
     <row r="104" spans="2:3">
       <c r="C104" s="82" t="s">
-        <v>386</v>
+        <v>381</v>
       </c>
     </row>
     <row r="105" spans="2:3">
       <c r="C105" s="82" t="s">
-        <v>387</v>
+        <v>382</v>
       </c>
     </row>
     <row r="106" spans="2:3">
       <c r="B106" t="s">
-        <v>384</v>
+        <v>379</v>
       </c>
       <c r="C106" s="83" t="s">
-        <v>388</v>
+        <v>383</v>
       </c>
     </row>
     <row r="107" spans="2:3">
       <c r="C107" s="79" t="s">
-        <v>389</v>
+        <v>384</v>
       </c>
     </row>
     <row r="108" spans="2:3">
       <c r="C108" s="79" t="s">
-        <v>390</v>
+        <v>385</v>
       </c>
     </row>
     <row r="109" spans="2:3">
       <c r="C109" s="79" t="s">
-        <v>391</v>
+        <v>386</v>
       </c>
     </row>
     <row r="110" spans="2:3">
       <c r="C110" s="79" t="s">
-        <v>392</v>
+        <v>387</v>
       </c>
     </row>
     <row r="111" spans="2:3">
       <c r="B111" t="s">
-        <v>385</v>
+        <v>380</v>
       </c>
       <c r="C111" s="79" t="s">
-        <v>388</v>
+        <v>383</v>
       </c>
     </row>
     <row r="112" spans="2:3">
       <c r="C112" s="79" t="s">
-        <v>393</v>
+        <v>388</v>
       </c>
     </row>
     <row r="113" spans="2:3">
       <c r="C113" s="79" t="s">
-        <v>394</v>
+        <v>389</v>
       </c>
     </row>
     <row r="114" spans="2:3">
       <c r="C114" s="79" t="s">
-        <v>395</v>
+        <v>390</v>
       </c>
     </row>
     <row r="115" spans="2:3">
@@ -12519,7 +12419,7 @@
     </row>
     <row r="116" spans="2:3">
       <c r="B116" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="C116" s="79" t="s">
         <v>54</v>
@@ -12653,7 +12553,7 @@
     </row>
     <row r="141" spans="2:3">
       <c r="B141" s="79" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="C141" s="79" t="s">
         <v>217</v>
@@ -12670,7 +12570,7 @@
     </row>
     <row r="144" spans="2:3">
       <c r="B144" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="C144" t="s">
         <v>164</v>
@@ -12693,7 +12593,7 @@
     </row>
     <row r="148" spans="2:3">
       <c r="B148" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="C148" s="79" t="s">
         <v>255</v>
@@ -12736,7 +12636,7 @@
     </row>
     <row r="156" spans="2:3">
       <c r="B156" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="C156" s="79" t="s">
         <v>259</v>
@@ -12781,7 +12681,7 @@
     </row>
     <row r="164" spans="2:3">
       <c r="B164" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="C164" s="79" t="s">
         <v>283</v>

--- a/IG/7日版/AI Native-バイブコーディング_IG.xlsx
+++ b/IG/7日版/AI Native-バイブコーディング_IG.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\myrepo\ai_navive\IG\7日版\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A591C377-0B6F-4D87-915E-0593B7387203}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF3BFF64-4658-4051-8FB2-0177D9297528}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="860" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="860" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="スケジュール（3日）" sheetId="33" r:id="rId1"/>
@@ -3707,9 +3707,6 @@
     <t>ステージングの取り消し</t>
   </si>
   <si>
-    <t>コミットの取り消し</t>
-  </si>
-  <si>
     <t>リモートリポジトリの操作</t>
   </si>
   <si>
@@ -4552,6 +4549,16 @@
     <t xml:space="preserve">・AI-09
 ・AI-10
 </t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>コミットの打ち消し</t>
+    <rPh sb="5" eb="6">
+      <t>ウ</t>
+    </rPh>
+    <rPh sb="7" eb="8">
+      <t>ケ</t>
+    </rPh>
     <phoneticPr fontId="3"/>
   </si>
 </sst>
@@ -5246,6 +5253,15 @@
     <xf numFmtId="0" fontId="17" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -5264,6 +5280,12 @@
     <xf numFmtId="0" fontId="13" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="11" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -5298,6 +5320,42 @@
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="255"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -5306,33 +5364,6 @@
     <xf numFmtId="0" fontId="5" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="255"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="11" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -5340,30 +5371,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -5738,15 +5745,15 @@
   <sheetData>
     <row r="2" spans="1:8" ht="27">
       <c r="A2" s="13"/>
-      <c r="B2" s="90" t="str">
+      <c r="B2" s="93" t="str">
         <f>"コースプラン/インストラクションガイド 「"&amp;master!$B$1&amp;"_IG」"</f>
         <v>コースプラン/インストラクションガイド 「AI Native-バイブコーディング_IG」</v>
       </c>
-      <c r="C2" s="90"/>
-      <c r="D2" s="90"/>
-      <c r="E2" s="90"/>
-      <c r="F2" s="90"/>
-      <c r="G2" s="90"/>
+      <c r="C2" s="93"/>
+      <c r="D2" s="93"/>
+      <c r="E2" s="93"/>
+      <c r="F2" s="93"/>
+      <c r="G2" s="93"/>
     </row>
     <row r="3" spans="1:8" ht="27.6" thickBot="1">
       <c r="A3" s="13"/>
@@ -5759,10 +5766,10 @@
     </row>
     <row r="4" spans="1:8" ht="27.6" thickBot="1">
       <c r="A4" s="13"/>
-      <c r="B4" s="91" t="s">
+      <c r="B4" s="94" t="s">
         <v>11</v>
       </c>
-      <c r="C4" s="92"/>
+      <c r="C4" s="95"/>
       <c r="D4" s="13"/>
       <c r="E4" s="13"/>
       <c r="F4" s="13"/>
@@ -5770,18 +5777,18 @@
     </row>
     <row r="5" spans="1:8" ht="27.6" thickBot="1">
       <c r="A5" s="13"/>
-      <c r="B5" s="93"/>
-      <c r="C5" s="94"/>
+      <c r="B5" s="96"/>
+      <c r="C5" s="97"/>
       <c r="D5" s="13"/>
       <c r="E5" s="13"/>
       <c r="F5" s="13"/>
       <c r="G5" s="13"/>
     </row>
     <row r="7" spans="1:8" ht="16.2">
-      <c r="B7" s="95" t="s">
+      <c r="B7" s="98" t="s">
         <v>2</v>
       </c>
-      <c r="C7" s="95"/>
+      <c r="C7" s="98"/>
     </row>
     <row r="8" spans="1:8">
       <c r="E8" s="15"/>
@@ -5820,7 +5827,7 @@
       <c r="F10" s="34">
         <v>0.39583333333333331</v>
       </c>
-      <c r="G10" s="127" t="s">
+      <c r="G10" s="90" t="s">
         <v>3</v>
       </c>
     </row>
@@ -6227,7 +6234,7 @@
         <v>0.6875</v>
       </c>
       <c r="C38" s="66" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="D38" s="39"/>
       <c r="E38" s="51"/>
@@ -6268,10 +6275,10 @@
         <v>0.71875</v>
       </c>
       <c r="C41" s="55" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="D41" s="39"/>
-      <c r="E41" s="125"/>
+      <c r="E41" s="99"/>
       <c r="F41" s="39"/>
       <c r="G41" s="51"/>
       <c r="H41" s="6"/>
@@ -6281,11 +6288,11 @@
       <c r="B42" s="64"/>
       <c r="C42" s="52"/>
       <c r="D42" s="39"/>
-      <c r="E42" s="126"/>
+      <c r="E42" s="100"/>
       <c r="F42" s="37">
         <v>0.72916666666666663</v>
       </c>
-      <c r="G42" s="128" t="s">
+      <c r="G42" s="91" t="s">
         <v>52</v>
       </c>
       <c r="H42" s="6"/>
@@ -6305,7 +6312,7 @@
         <v>52</v>
       </c>
       <c r="F43" s="38"/>
-      <c r="G43" s="129"/>
+      <c r="G43" s="92"/>
     </row>
     <row r="44" spans="1:8" ht="15.6" thickBot="1">
       <c r="A44" s="6"/>
@@ -6372,10 +6379,10 @@
       <c r="K3" s="9"/>
     </row>
     <row r="4" spans="1:12" ht="16.2">
-      <c r="B4" s="99" t="s">
+      <c r="B4" s="104" t="s">
         <v>4</v>
       </c>
-      <c r="C4" s="99"/>
+      <c r="C4" s="104"/>
       <c r="D4" s="8"/>
       <c r="E4" s="8"/>
       <c r="F4" s="8"/>
@@ -6386,16 +6393,16 @@
       <c r="K4" s="9"/>
     </row>
     <row r="5" spans="1:12" ht="36" customHeight="1">
-      <c r="B5" s="100"/>
-      <c r="C5" s="100"/>
-      <c r="D5" s="100"/>
-      <c r="E5" s="100"/>
-      <c r="F5" s="100"/>
-      <c r="G5" s="100"/>
-      <c r="H5" s="100"/>
-      <c r="I5" s="100"/>
-      <c r="J5" s="100"/>
-      <c r="K5" s="100"/>
+      <c r="B5" s="105"/>
+      <c r="C5" s="105"/>
+      <c r="D5" s="105"/>
+      <c r="E5" s="105"/>
+      <c r="F5" s="105"/>
+      <c r="G5" s="105"/>
+      <c r="H5" s="105"/>
+      <c r="I5" s="105"/>
+      <c r="J5" s="105"/>
+      <c r="K5" s="105"/>
     </row>
     <row r="6" spans="1:12">
       <c r="B6" s="10"/>
@@ -6410,10 +6417,10 @@
       <c r="C7" s="30" t="s">
         <v>15</v>
       </c>
-      <c r="D7" s="101" t="s">
+      <c r="D7" s="106" t="s">
         <v>20</v>
       </c>
-      <c r="E7" s="101"/>
+      <c r="E7" s="106"/>
       <c r="F7" s="30" t="s">
         <v>10</v>
       </c>
@@ -6445,46 +6452,46 @@
     </row>
     <row r="10" spans="1:12">
       <c r="A10" s="10"/>
-      <c r="B10" s="97"/>
-      <c r="C10" s="97" t="s">
+      <c r="B10" s="102"/>
+      <c r="C10" s="102" t="s">
         <v>7</v>
       </c>
-      <c r="D10" s="97" t="s">
+      <c r="D10" s="102" t="s">
         <v>8</v>
       </c>
-      <c r="E10" s="97"/>
-      <c r="F10" s="97"/>
-      <c r="G10" s="97" t="s">
+      <c r="E10" s="102"/>
+      <c r="F10" s="102"/>
+      <c r="G10" s="102" t="s">
         <v>9</v>
       </c>
-      <c r="H10" s="102" t="s">
+      <c r="H10" s="107" t="s">
         <v>23</v>
       </c>
-      <c r="I10" s="96" t="s">
+      <c r="I10" s="101" t="s">
         <v>31</v>
       </c>
-      <c r="J10" s="96"/>
-      <c r="K10" s="96" t="s">
+      <c r="J10" s="101"/>
+      <c r="K10" s="101" t="s">
         <v>30</v>
       </c>
       <c r="L10" s="10"/>
     </row>
     <row r="11" spans="1:12">
       <c r="A11" s="10"/>
-      <c r="B11" s="97"/>
-      <c r="C11" s="97"/>
-      <c r="D11" s="97"/>
-      <c r="E11" s="97"/>
-      <c r="F11" s="97"/>
-      <c r="G11" s="97"/>
-      <c r="H11" s="103"/>
+      <c r="B11" s="102"/>
+      <c r="C11" s="102"/>
+      <c r="D11" s="102"/>
+      <c r="E11" s="102"/>
+      <c r="F11" s="102"/>
+      <c r="G11" s="102"/>
+      <c r="H11" s="108"/>
       <c r="I11" s="25" t="s">
         <v>25</v>
       </c>
       <c r="J11" s="25" t="s">
         <v>6</v>
       </c>
-      <c r="K11" s="97"/>
+      <c r="K11" s="102"/>
       <c r="L11" s="10"/>
     </row>
     <row r="12" spans="1:12" ht="63">
@@ -6493,11 +6500,11 @@
       <c r="C12" s="19" t="s">
         <v>330</v>
       </c>
-      <c r="D12" s="98" t="s">
+      <c r="D12" s="103" t="s">
         <v>50</v>
       </c>
-      <c r="E12" s="98"/>
-      <c r="F12" s="98"/>
+      <c r="E12" s="103"/>
+      <c r="F12" s="103"/>
       <c r="G12" s="87" t="s">
         <v>51</v>
       </c>
@@ -6517,11 +6524,11 @@
       <c r="C13" s="19" t="s">
         <v>331</v>
       </c>
-      <c r="D13" s="98" t="s">
+      <c r="D13" s="103" t="s">
         <v>328</v>
       </c>
-      <c r="E13" s="98"/>
-      <c r="F13" s="98"/>
+      <c r="E13" s="103"/>
+      <c r="F13" s="103"/>
       <c r="G13" s="87" t="s">
         <v>329</v>
       </c>
@@ -6621,12 +6628,12 @@
       <c r="M3" s="9"/>
     </row>
     <row r="4" spans="2:14" ht="16.2">
-      <c r="B4" s="99" t="s">
+      <c r="B4" s="104" t="s">
         <v>4</v>
       </c>
-      <c r="C4" s="99"/>
-      <c r="D4" s="99"/>
-      <c r="E4" s="99"/>
+      <c r="C4" s="104"/>
+      <c r="D4" s="104"/>
+      <c r="E4" s="104"/>
       <c r="F4" s="8"/>
       <c r="G4" s="8"/>
       <c r="H4" s="7"/>
@@ -6637,16 +6644,16 @@
       <c r="M4" s="9"/>
     </row>
     <row r="5" spans="2:14" ht="36" customHeight="1">
-      <c r="B5" s="121"/>
-      <c r="C5" s="121"/>
-      <c r="D5" s="121"/>
-      <c r="E5" s="121"/>
-      <c r="F5" s="121"/>
-      <c r="G5" s="121"/>
-      <c r="H5" s="121"/>
-      <c r="I5" s="121"/>
-      <c r="J5" s="121"/>
-      <c r="K5" s="121"/>
+      <c r="B5" s="129"/>
+      <c r="C5" s="129"/>
+      <c r="D5" s="129"/>
+      <c r="E5" s="129"/>
+      <c r="F5" s="129"/>
+      <c r="G5" s="129"/>
+      <c r="H5" s="129"/>
+      <c r="I5" s="129"/>
+      <c r="J5" s="129"/>
+      <c r="K5" s="129"/>
       <c r="L5" s="26"/>
       <c r="M5" s="27"/>
     </row>
@@ -6666,10 +6673,10 @@
       <c r="C7" s="30" t="s">
         <v>15</v>
       </c>
-      <c r="D7" s="101" t="s">
+      <c r="D7" s="106" t="s">
         <v>20</v>
       </c>
-      <c r="E7" s="101"/>
+      <c r="E7" s="106"/>
       <c r="F7" s="30" t="s">
         <v>10</v>
       </c>
@@ -6820,7 +6827,7 @@
         <v>93</v>
       </c>
       <c r="C14" s="57" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="D14" s="42" t="s">
         <v>19</v>
@@ -6842,7 +6849,7 @@
         <v>94</v>
       </c>
       <c r="C15" s="57" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="D15" s="42" t="s">
         <v>19</v>
@@ -6905,28 +6912,28 @@
     </row>
     <row r="19" spans="1:14" ht="24" customHeight="1">
       <c r="A19" s="10"/>
-      <c r="B19" s="97" t="s">
+      <c r="B19" s="102" t="s">
         <v>5</v>
       </c>
-      <c r="C19" s="97" t="s">
+      <c r="C19" s="102" t="s">
         <v>7</v>
       </c>
-      <c r="D19" s="97" t="s">
+      <c r="D19" s="102" t="s">
         <v>8</v>
       </c>
-      <c r="E19" s="97"/>
-      <c r="F19" s="97"/>
-      <c r="G19" s="97" t="s">
+      <c r="E19" s="102"/>
+      <c r="F19" s="102"/>
+      <c r="G19" s="102" t="s">
         <v>9</v>
       </c>
-      <c r="H19" s="96" t="s">
+      <c r="H19" s="101" t="s">
         <v>23</v>
       </c>
-      <c r="I19" s="119" t="s">
+      <c r="I19" s="127" t="s">
         <v>31</v>
       </c>
-      <c r="J19" s="120"/>
-      <c r="K19" s="96" t="s">
+      <c r="J19" s="128"/>
+      <c r="K19" s="101" t="s">
         <v>32</v>
       </c>
       <c r="L19" s="6"/>
@@ -6935,20 +6942,20 @@
     </row>
     <row r="20" spans="1:14">
       <c r="A20" s="10"/>
-      <c r="B20" s="97"/>
-      <c r="C20" s="97"/>
-      <c r="D20" s="97"/>
-      <c r="E20" s="97"/>
-      <c r="F20" s="97"/>
-      <c r="G20" s="97"/>
-      <c r="H20" s="96"/>
+      <c r="B20" s="102"/>
+      <c r="C20" s="102"/>
+      <c r="D20" s="102"/>
+      <c r="E20" s="102"/>
+      <c r="F20" s="102"/>
+      <c r="G20" s="102"/>
+      <c r="H20" s="101"/>
       <c r="I20" s="25" t="s">
         <v>25</v>
       </c>
       <c r="J20" s="25" t="s">
         <v>6</v>
       </c>
-      <c r="K20" s="97"/>
+      <c r="K20" s="102"/>
       <c r="L20" s="6"/>
       <c r="M20" s="6"/>
       <c r="N20" s="6"/>
@@ -6963,11 +6970,11 @@
         <f>master!C3</f>
         <v>講義の目的</v>
       </c>
-      <c r="D21" s="104" t="s">
+      <c r="D21" s="109" t="s">
         <v>95</v>
       </c>
-      <c r="E21" s="105"/>
-      <c r="F21" s="106"/>
+      <c r="E21" s="110"/>
+      <c r="F21" s="111"/>
       <c r="G21" s="48" t="s">
         <v>96</v>
       </c>
@@ -6985,7 +6992,7 @@
     </row>
     <row r="22" spans="1:14" ht="138.6" customHeight="1">
       <c r="A22" s="10"/>
-      <c r="B22" s="107" t="str">
+      <c r="B22" s="124" t="str">
         <f>master!B4</f>
         <v>Webアプリケーションとは</v>
       </c>
@@ -6993,11 +7000,11 @@
         <f>master!C4</f>
         <v>Webアプリケーションとは</v>
       </c>
-      <c r="D22" s="104" t="s">
+      <c r="D22" s="109" t="s">
         <v>97</v>
       </c>
-      <c r="E22" s="105"/>
-      <c r="F22" s="106"/>
+      <c r="E22" s="110"/>
+      <c r="F22" s="111"/>
       <c r="G22" s="48" t="s">
         <v>40</v>
       </c>
@@ -7015,16 +7022,16 @@
     </row>
     <row r="23" spans="1:14" ht="75.599999999999994">
       <c r="A23" s="11"/>
-      <c r="B23" s="108"/>
+      <c r="B23" s="125"/>
       <c r="C23" s="48" t="str">
         <f>master!C5</f>
         <v>Webアプリケーションの種類</v>
       </c>
-      <c r="D23" s="104" t="s">
+      <c r="D23" s="109" t="s">
         <v>98</v>
       </c>
-      <c r="E23" s="105"/>
-      <c r="F23" s="106"/>
+      <c r="E23" s="110"/>
+      <c r="F23" s="111"/>
       <c r="G23" s="48" t="s">
         <v>44</v>
       </c>
@@ -7042,16 +7049,16 @@
     </row>
     <row r="24" spans="1:14" ht="37.799999999999997">
       <c r="A24" s="11"/>
-      <c r="B24" s="108"/>
+      <c r="B24" s="125"/>
       <c r="C24" s="48" t="str">
         <f>master!C6</f>
         <v>アプリケーションとは</v>
       </c>
-      <c r="D24" s="104" t="s">
+      <c r="D24" s="109" t="s">
         <v>99</v>
       </c>
-      <c r="E24" s="105"/>
-      <c r="F24" s="106"/>
+      <c r="E24" s="110"/>
+      <c r="F24" s="111"/>
       <c r="G24" s="48" t="s">
         <v>42</v>
       </c>
@@ -7069,16 +7076,16 @@
     </row>
     <row r="25" spans="1:14" ht="63">
       <c r="A25" s="11"/>
-      <c r="B25" s="108"/>
+      <c r="B25" s="125"/>
       <c r="C25" s="48" t="str">
         <f>master!C7</f>
         <v>Web画面アプリケーション</v>
       </c>
-      <c r="D25" s="104" t="s">
+      <c r="D25" s="109" t="s">
         <v>100</v>
       </c>
-      <c r="E25" s="105"/>
-      <c r="F25" s="106"/>
+      <c r="E25" s="110"/>
+      <c r="F25" s="111"/>
       <c r="G25" s="48" t="s">
         <v>41</v>
       </c>
@@ -7096,13 +7103,13 @@
     </row>
     <row r="26" spans="1:14" ht="63">
       <c r="A26" s="11"/>
-      <c r="B26" s="108"/>
+      <c r="B26" s="125"/>
       <c r="C26" s="48"/>
-      <c r="D26" s="104" t="s">
+      <c r="D26" s="109" t="s">
         <v>101</v>
       </c>
-      <c r="E26" s="105"/>
-      <c r="F26" s="106"/>
+      <c r="E26" s="110"/>
+      <c r="F26" s="111"/>
       <c r="G26" s="48" t="s">
         <v>41</v>
       </c>
@@ -7120,16 +7127,16 @@
     </row>
     <row r="27" spans="1:14" ht="113.4">
       <c r="A27" s="11"/>
-      <c r="B27" s="109"/>
+      <c r="B27" s="126"/>
       <c r="C27" s="48" t="str">
         <f>master!C8</f>
         <v>ブラウザからのリクエスト種類</v>
       </c>
-      <c r="D27" s="104" t="s">
+      <c r="D27" s="109" t="s">
         <v>102</v>
       </c>
-      <c r="E27" s="105"/>
-      <c r="F27" s="106"/>
+      <c r="E27" s="110"/>
+      <c r="F27" s="111"/>
       <c r="G27" s="48" t="s">
         <v>45</v>
       </c>
@@ -7147,7 +7154,7 @@
     </row>
     <row r="28" spans="1:14" ht="102" customHeight="1">
       <c r="A28" s="11"/>
-      <c r="B28" s="107" t="str">
+      <c r="B28" s="124" t="str">
         <f>master!B9</f>
         <v>データベースとは</v>
       </c>
@@ -7155,11 +7162,11 @@
         <f>master!C9</f>
         <v>データベースとは</v>
       </c>
-      <c r="D28" s="104" t="s">
+      <c r="D28" s="109" t="s">
         <v>103</v>
       </c>
-      <c r="E28" s="105"/>
-      <c r="F28" s="106"/>
+      <c r="E28" s="110"/>
+      <c r="F28" s="111"/>
       <c r="G28" s="48" t="s">
         <v>42</v>
       </c>
@@ -7177,16 +7184,16 @@
     </row>
     <row r="29" spans="1:14" ht="88.2">
       <c r="A29" s="11"/>
-      <c r="B29" s="108"/>
+      <c r="B29" s="125"/>
       <c r="C29" s="48" t="str">
         <f>master!C10</f>
         <v>リレーショナルデータベース</v>
       </c>
-      <c r="D29" s="104" t="s">
+      <c r="D29" s="109" t="s">
         <v>104</v>
       </c>
-      <c r="E29" s="105"/>
-      <c r="F29" s="106"/>
+      <c r="E29" s="110"/>
+      <c r="F29" s="111"/>
       <c r="G29" s="48" t="s">
         <v>46</v>
       </c>
@@ -7204,16 +7211,16 @@
     </row>
     <row r="30" spans="1:14" ht="25.2">
       <c r="A30" s="11"/>
-      <c r="B30" s="108"/>
+      <c r="B30" s="125"/>
       <c r="C30" s="48" t="str">
         <f>master!C11</f>
         <v>データベースの役割</v>
       </c>
-      <c r="D30" s="104" t="s">
+      <c r="D30" s="109" t="s">
         <v>105</v>
       </c>
-      <c r="E30" s="105"/>
-      <c r="F30" s="106"/>
+      <c r="E30" s="110"/>
+      <c r="F30" s="111"/>
       <c r="G30" s="48" t="s">
         <v>47</v>
       </c>
@@ -7233,16 +7240,16 @@
     </row>
     <row r="31" spans="1:14" ht="75.599999999999994">
       <c r="A31" s="11"/>
-      <c r="B31" s="108"/>
+      <c r="B31" s="125"/>
       <c r="C31" s="48" t="str">
         <f>master!C12</f>
         <v>2.1.テーブル</v>
       </c>
-      <c r="D31" s="104" t="s">
+      <c r="D31" s="109" t="s">
         <v>106</v>
       </c>
-      <c r="E31" s="105"/>
-      <c r="F31" s="106"/>
+      <c r="E31" s="110"/>
+      <c r="F31" s="111"/>
       <c r="G31" s="48" t="s">
         <v>44</v>
       </c>
@@ -7260,16 +7267,16 @@
     </row>
     <row r="32" spans="1:14" ht="100.8">
       <c r="A32" s="11"/>
-      <c r="B32" s="108"/>
+      <c r="B32" s="125"/>
       <c r="C32" s="48" t="str">
         <f>master!C13</f>
         <v>2.2.データ型１</v>
       </c>
-      <c r="D32" s="104" t="s">
+      <c r="D32" s="109" t="s">
         <v>107</v>
       </c>
-      <c r="E32" s="105"/>
-      <c r="F32" s="106"/>
+      <c r="E32" s="110"/>
+      <c r="F32" s="111"/>
       <c r="G32" s="48" t="s">
         <v>48</v>
       </c>
@@ -7287,16 +7294,16 @@
     </row>
     <row r="33" spans="1:14" ht="37.799999999999997">
       <c r="A33" s="11"/>
-      <c r="B33" s="108"/>
+      <c r="B33" s="125"/>
       <c r="C33" s="48" t="str">
         <f>master!C14</f>
         <v>2.2.データ型２</v>
       </c>
-      <c r="D33" s="104" t="s">
+      <c r="D33" s="109" t="s">
         <v>108</v>
       </c>
-      <c r="E33" s="105"/>
-      <c r="F33" s="106"/>
+      <c r="E33" s="110"/>
+      <c r="F33" s="111"/>
       <c r="G33" s="48" t="s">
         <v>42</v>
       </c>
@@ -7314,16 +7321,16 @@
     </row>
     <row r="34" spans="1:14" ht="37.799999999999997">
       <c r="A34" s="11"/>
-      <c r="B34" s="108"/>
+      <c r="B34" s="125"/>
       <c r="C34" s="48" t="str">
         <f>master!C15</f>
         <v>2.3.リレーション</v>
       </c>
-      <c r="D34" s="104" t="s">
+      <c r="D34" s="109" t="s">
         <v>109</v>
       </c>
-      <c r="E34" s="105"/>
-      <c r="F34" s="106"/>
+      <c r="E34" s="110"/>
+      <c r="F34" s="111"/>
       <c r="G34" s="48" t="s">
         <v>42</v>
       </c>
@@ -7341,16 +7348,16 @@
     </row>
     <row r="35" spans="1:14" ht="37.799999999999997">
       <c r="A35" s="11"/>
-      <c r="B35" s="109"/>
+      <c r="B35" s="126"/>
       <c r="C35" s="48" t="str">
         <f>master!C16</f>
         <v>2.4.データを結合して取得（Join）</v>
       </c>
-      <c r="D35" s="104" t="s">
+      <c r="D35" s="109" t="s">
         <v>110</v>
       </c>
-      <c r="E35" s="105"/>
-      <c r="F35" s="106"/>
+      <c r="E35" s="110"/>
+      <c r="F35" s="111"/>
       <c r="G35" s="48" t="s">
         <v>42</v>
       </c>
@@ -7368,7 +7375,7 @@
     </row>
     <row r="36" spans="1:14" ht="88.2">
       <c r="A36" s="11"/>
-      <c r="B36" s="107" t="str">
+      <c r="B36" s="124" t="str">
         <f>master!B17</f>
         <v>Java言語、Springフレームワークとは</v>
       </c>
@@ -7376,11 +7383,11 @@
         <f>master!C17</f>
         <v>Webアプリケーションを作成するためのプログラミング言語</v>
       </c>
-      <c r="D36" s="104" t="s">
+      <c r="D36" s="109" t="s">
         <v>111</v>
       </c>
-      <c r="E36" s="105"/>
-      <c r="F36" s="106"/>
+      <c r="E36" s="110"/>
+      <c r="F36" s="111"/>
       <c r="G36" s="48" t="s">
         <v>46</v>
       </c>
@@ -7398,16 +7405,16 @@
     </row>
     <row r="37" spans="1:14" ht="75.599999999999994">
       <c r="A37" s="11"/>
-      <c r="B37" s="108"/>
+      <c r="B37" s="125"/>
       <c r="C37" s="48" t="str">
         <f>master!C18</f>
         <v>Java</v>
       </c>
-      <c r="D37" s="104" t="s">
+      <c r="D37" s="109" t="s">
         <v>112</v>
       </c>
-      <c r="E37" s="105"/>
-      <c r="F37" s="106"/>
+      <c r="E37" s="110"/>
+      <c r="F37" s="111"/>
       <c r="G37" s="48" t="s">
         <v>44</v>
       </c>
@@ -7425,16 +7432,16 @@
     </row>
     <row r="38" spans="1:14" ht="75.599999999999994">
       <c r="A38" s="11"/>
-      <c r="B38" s="108"/>
+      <c r="B38" s="125"/>
       <c r="C38" s="48" t="str">
         <f>master!C19</f>
         <v>Java言語の構成要素</v>
       </c>
-      <c r="D38" s="104" t="s">
+      <c r="D38" s="109" t="s">
         <v>113</v>
       </c>
-      <c r="E38" s="105"/>
-      <c r="F38" s="106"/>
+      <c r="E38" s="110"/>
+      <c r="F38" s="111"/>
       <c r="G38" s="48" t="s">
         <v>44</v>
       </c>
@@ -7452,16 +7459,16 @@
     </row>
     <row r="39" spans="1:14" ht="50.4">
       <c r="A39" s="11"/>
-      <c r="B39" s="108"/>
+      <c r="B39" s="125"/>
       <c r="C39" s="48" t="str">
         <f>master!C20</f>
         <v>Webアプリケーションを構成するクラス</v>
       </c>
-      <c r="D39" s="104" t="s">
+      <c r="D39" s="109" t="s">
         <v>114</v>
       </c>
-      <c r="E39" s="105"/>
-      <c r="F39" s="106"/>
+      <c r="E39" s="110"/>
+      <c r="F39" s="111"/>
       <c r="G39" s="48" t="s">
         <v>43</v>
       </c>
@@ -7479,16 +7486,16 @@
     </row>
     <row r="40" spans="1:14" ht="88.2">
       <c r="A40" s="11"/>
-      <c r="B40" s="108"/>
+      <c r="B40" s="125"/>
       <c r="C40" s="48" t="str">
         <f>master!C21</f>
         <v>Nレイヤーアーキテクチャ</v>
       </c>
-      <c r="D40" s="104" t="s">
+      <c r="D40" s="109" t="s">
         <v>116</v>
       </c>
-      <c r="E40" s="105"/>
-      <c r="F40" s="106"/>
+      <c r="E40" s="110"/>
+      <c r="F40" s="111"/>
       <c r="G40" s="48" t="s">
         <v>46</v>
       </c>
@@ -7508,16 +7515,16 @@
     </row>
     <row r="41" spans="1:14" ht="201.6">
       <c r="A41" s="11"/>
-      <c r="B41" s="108"/>
+      <c r="B41" s="125"/>
       <c r="C41" s="48" t="str">
         <f>master!C22</f>
         <v>View と Controller と Service と Repository</v>
       </c>
-      <c r="D41" s="104" t="s">
+      <c r="D41" s="109" t="s">
         <v>117</v>
       </c>
-      <c r="E41" s="105"/>
-      <c r="F41" s="106"/>
+      <c r="E41" s="110"/>
+      <c r="F41" s="111"/>
       <c r="G41" s="48" t="s">
         <v>118</v>
       </c>
@@ -7535,16 +7542,16 @@
     </row>
     <row r="42" spans="1:14" ht="37.799999999999997">
       <c r="A42" s="11"/>
-      <c r="B42" s="108"/>
+      <c r="B42" s="125"/>
       <c r="C42" s="48" t="str">
         <f>master!C23</f>
         <v>Nレイヤーアーキテクチャ</v>
       </c>
-      <c r="D42" s="104" t="s">
+      <c r="D42" s="109" t="s">
         <v>119</v>
       </c>
-      <c r="E42" s="105"/>
-      <c r="F42" s="106"/>
+      <c r="E42" s="110"/>
+      <c r="F42" s="111"/>
       <c r="G42" s="48" t="s">
         <v>42</v>
       </c>
@@ -7562,16 +7569,16 @@
     </row>
     <row r="43" spans="1:14" ht="163.80000000000001">
       <c r="A43" s="11"/>
-      <c r="B43" s="108"/>
+      <c r="B43" s="125"/>
       <c r="C43" s="48" t="str">
         <f>master!C24</f>
         <v>Webアプリケーション フレームワーク</v>
       </c>
-      <c r="D43" s="104" t="s">
+      <c r="D43" s="109" t="s">
         <v>120</v>
       </c>
-      <c r="E43" s="105"/>
-      <c r="F43" s="106"/>
+      <c r="E43" s="110"/>
+      <c r="F43" s="111"/>
       <c r="G43" s="48" t="s">
         <v>121</v>
       </c>
@@ -7589,16 +7596,16 @@
     </row>
     <row r="44" spans="1:14" ht="25.2">
       <c r="A44" s="11"/>
-      <c r="B44" s="108"/>
+      <c r="B44" s="125"/>
       <c r="C44" s="48" t="str">
         <f>master!C25</f>
         <v>Java向けWebアプリケーションフレームワーク</v>
       </c>
-      <c r="D44" s="104" t="s">
+      <c r="D44" s="109" t="s">
         <v>122</v>
       </c>
-      <c r="E44" s="105"/>
-      <c r="F44" s="106"/>
+      <c r="E44" s="110"/>
+      <c r="F44" s="111"/>
       <c r="G44" s="48" t="s">
         <v>47</v>
       </c>
@@ -7616,16 +7623,16 @@
     </row>
     <row r="45" spans="1:14" ht="189">
       <c r="A45" s="11"/>
-      <c r="B45" s="108"/>
+      <c r="B45" s="125"/>
       <c r="C45" s="48" t="str">
         <f>master!C26</f>
         <v>Springフレームワーク</v>
       </c>
-      <c r="D45" s="104" t="s">
+      <c r="D45" s="109" t="s">
         <v>123</v>
       </c>
-      <c r="E45" s="105"/>
-      <c r="F45" s="106"/>
+      <c r="E45" s="110"/>
+      <c r="F45" s="111"/>
       <c r="G45" s="48" t="s">
         <v>124</v>
       </c>
@@ -7643,16 +7650,16 @@
     </row>
     <row r="46" spans="1:14" ht="88.2">
       <c r="A46" s="11"/>
-      <c r="B46" s="108"/>
+      <c r="B46" s="125"/>
       <c r="C46" s="48" t="str">
         <f>master!C27</f>
         <v>Springフレームワーク：DIコンテナとは</v>
       </c>
-      <c r="D46" s="104" t="s">
+      <c r="D46" s="109" t="s">
         <v>125</v>
       </c>
-      <c r="E46" s="105"/>
-      <c r="F46" s="106"/>
+      <c r="E46" s="110"/>
+      <c r="F46" s="111"/>
       <c r="G46" s="48" t="s">
         <v>46</v>
       </c>
@@ -7672,16 +7679,16 @@
     </row>
     <row r="47" spans="1:14" ht="63">
       <c r="A47" s="11"/>
-      <c r="B47" s="108"/>
+      <c r="B47" s="125"/>
       <c r="C47" s="48" t="str">
         <f>master!C28</f>
         <v>DIコンテナ：DIコンテナが部品を注入する</v>
       </c>
-      <c r="D47" s="104" t="s">
+      <c r="D47" s="109" t="s">
         <v>126</v>
       </c>
-      <c r="E47" s="105"/>
-      <c r="F47" s="106"/>
+      <c r="E47" s="110"/>
+      <c r="F47" s="111"/>
       <c r="G47" s="48" t="s">
         <v>41</v>
       </c>
@@ -7699,16 +7706,16 @@
     </row>
     <row r="48" spans="1:14" ht="100.8">
       <c r="A48" s="11"/>
-      <c r="B48" s="108"/>
+      <c r="B48" s="125"/>
       <c r="C48" s="48" t="str">
         <f>master!C29</f>
         <v>DIコンテナ：DIコンテナによる部品と注入対象になるための目印</v>
       </c>
-      <c r="D48" s="104" t="s">
+      <c r="D48" s="109" t="s">
         <v>127</v>
       </c>
-      <c r="E48" s="105"/>
-      <c r="F48" s="106"/>
+      <c r="E48" s="110"/>
+      <c r="F48" s="111"/>
       <c r="G48" s="48" t="s">
         <v>48</v>
       </c>
@@ -7726,16 +7733,16 @@
     </row>
     <row r="49" spans="1:14" ht="100.8">
       <c r="A49" s="11"/>
-      <c r="B49" s="108"/>
+      <c r="B49" s="125"/>
       <c r="C49" s="48" t="str">
         <f>master!C30</f>
         <v>Springフレームワークにおける部品の設定</v>
       </c>
-      <c r="D49" s="104" t="s">
+      <c r="D49" s="109" t="s">
         <v>128</v>
       </c>
-      <c r="E49" s="105"/>
-      <c r="F49" s="106"/>
+      <c r="E49" s="110"/>
+      <c r="F49" s="111"/>
       <c r="G49" s="48" t="s">
         <v>48</v>
       </c>
@@ -7753,16 +7760,16 @@
     </row>
     <row r="50" spans="1:14" ht="88.2">
       <c r="A50" s="11"/>
-      <c r="B50" s="108"/>
+      <c r="B50" s="125"/>
       <c r="C50" s="48" t="str">
         <f>master!C31</f>
         <v>Spring Boot</v>
       </c>
-      <c r="D50" s="104" t="s">
+      <c r="D50" s="109" t="s">
         <v>129</v>
       </c>
-      <c r="E50" s="105"/>
-      <c r="F50" s="106"/>
+      <c r="E50" s="110"/>
+      <c r="F50" s="111"/>
       <c r="G50" s="48" t="s">
         <v>46</v>
       </c>
@@ -7780,16 +7787,16 @@
     </row>
     <row r="51" spans="1:14" ht="63">
       <c r="A51" s="11"/>
-      <c r="B51" s="108"/>
+      <c r="B51" s="125"/>
       <c r="C51" s="48" t="str">
         <f>master!C32</f>
         <v>Spring Boot：オートコンフィグレーション</v>
       </c>
-      <c r="D51" s="104" t="s">
+      <c r="D51" s="109" t="s">
         <v>130</v>
       </c>
-      <c r="E51" s="105"/>
-      <c r="F51" s="106"/>
+      <c r="E51" s="110"/>
+      <c r="F51" s="111"/>
       <c r="G51" s="48" t="s">
         <v>41</v>
       </c>
@@ -7807,16 +7814,16 @@
     </row>
     <row r="52" spans="1:14" ht="50.4">
       <c r="A52" s="11"/>
-      <c r="B52" s="108"/>
+      <c r="B52" s="125"/>
       <c r="C52" s="48" t="str">
         <f>master!C33</f>
         <v>Spring Boot：Starters</v>
       </c>
-      <c r="D52" s="104" t="s">
+      <c r="D52" s="109" t="s">
         <v>131</v>
       </c>
-      <c r="E52" s="105"/>
-      <c r="F52" s="106"/>
+      <c r="E52" s="110"/>
+      <c r="F52" s="111"/>
       <c r="G52" s="48" t="s">
         <v>43</v>
       </c>
@@ -7834,16 +7841,16 @@
     </row>
     <row r="53" spans="1:14" ht="88.2">
       <c r="A53" s="11"/>
-      <c r="B53" s="108"/>
+      <c r="B53" s="125"/>
       <c r="C53" s="48" t="str">
         <f>master!C34</f>
         <v>Spring Boot：組込みWebAPサーバ</v>
       </c>
-      <c r="D53" s="104" t="s">
+      <c r="D53" s="109" t="s">
         <v>132</v>
       </c>
-      <c r="E53" s="105"/>
-      <c r="F53" s="106"/>
+      <c r="E53" s="110"/>
+      <c r="F53" s="111"/>
       <c r="G53" s="48" t="s">
         <v>46</v>
       </c>
@@ -7861,14 +7868,14 @@
     </row>
     <row r="54" spans="1:14" ht="25.2">
       <c r="A54" s="11"/>
-      <c r="B54" s="109"/>
+      <c r="B54" s="126"/>
       <c r="C54" s="48" t="str">
         <f>master!C35</f>
         <v>おすすめ書籍：『プロになるためのSpring入門』</v>
       </c>
-      <c r="D54" s="104"/>
-      <c r="E54" s="105"/>
-      <c r="F54" s="106"/>
+      <c r="D54" s="109"/>
+      <c r="E54" s="110"/>
+      <c r="F54" s="111"/>
       <c r="G54" s="48" t="s">
         <v>47</v>
       </c>
@@ -7886,7 +7893,7 @@
     </row>
     <row r="55" spans="1:14" ht="37.799999999999997">
       <c r="A55" s="11"/>
-      <c r="B55" s="113" t="str">
+      <c r="B55" s="121" t="str">
         <f>master!B37</f>
         <v>課題1の導入</v>
       </c>
@@ -7894,11 +7901,11 @@
         <f>master!C37</f>
         <v>演習課題の概要</v>
       </c>
-      <c r="D55" s="110" t="s">
+      <c r="D55" s="115" t="s">
         <v>165</v>
       </c>
-      <c r="E55" s="111"/>
-      <c r="F55" s="112"/>
+      <c r="E55" s="116"/>
+      <c r="F55" s="117"/>
       <c r="G55" s="58" t="s">
         <v>288</v>
       </c>
@@ -7916,16 +7923,16 @@
     </row>
     <row r="56" spans="1:14" ht="37.799999999999997">
       <c r="A56" s="11"/>
-      <c r="B56" s="114"/>
+      <c r="B56" s="122"/>
       <c r="C56" s="58" t="str">
         <f>master!C38</f>
         <v>作成物</v>
       </c>
-      <c r="D56" s="110" t="s">
+      <c r="D56" s="115" t="s">
         <v>166</v>
       </c>
-      <c r="E56" s="111"/>
-      <c r="F56" s="112"/>
+      <c r="E56" s="116"/>
+      <c r="F56" s="117"/>
       <c r="G56" s="58" t="s">
         <v>288</v>
       </c>
@@ -7943,16 +7950,16 @@
     </row>
     <row r="57" spans="1:14" ht="75.599999999999994">
       <c r="A57" s="11"/>
-      <c r="B57" s="115"/>
+      <c r="B57" s="123"/>
       <c r="C57" s="58" t="str">
         <f>master!C39</f>
         <v>演習課題の進め方</v>
       </c>
-      <c r="D57" s="110" t="s">
+      <c r="D57" s="115" t="s">
         <v>167</v>
       </c>
-      <c r="E57" s="111"/>
-      <c r="F57" s="112"/>
+      <c r="E57" s="116"/>
+      <c r="F57" s="117"/>
       <c r="G57" s="58" t="s">
         <v>289</v>
       </c>
@@ -7970,7 +7977,7 @@
     </row>
     <row r="58" spans="1:14" ht="15" customHeight="1">
       <c r="A58" s="11"/>
-      <c r="B58" s="113" t="str">
+      <c r="B58" s="121" t="str">
         <f>master!B40</f>
         <v>Spring Bootプロジェクトの_x000B_準備、起動確認</v>
       </c>
@@ -7978,9 +7985,9 @@
         <f>master!C40</f>
         <v>前提条件</v>
       </c>
-      <c r="D58" s="110"/>
-      <c r="E58" s="111"/>
-      <c r="F58" s="112"/>
+      <c r="D58" s="115"/>
+      <c r="E58" s="116"/>
+      <c r="F58" s="117"/>
       <c r="G58" s="58" t="s">
         <v>290</v>
       </c>
@@ -7998,16 +8005,16 @@
     </row>
     <row r="59" spans="1:14" ht="37.799999999999997">
       <c r="A59" s="11"/>
-      <c r="B59" s="114"/>
+      <c r="B59" s="122"/>
       <c r="C59" s="58" t="str">
         <f>master!C41</f>
         <v>Spring Bootプロジェクトの準備</v>
       </c>
-      <c r="D59" s="110" t="s">
+      <c r="D59" s="115" t="s">
         <v>168</v>
       </c>
-      <c r="E59" s="111"/>
-      <c r="F59" s="112"/>
+      <c r="E59" s="116"/>
+      <c r="F59" s="117"/>
       <c r="G59" s="58" t="s">
         <v>288</v>
       </c>
@@ -8025,16 +8032,16 @@
     </row>
     <row r="60" spans="1:14" ht="25.2">
       <c r="A60" s="11"/>
-      <c r="B60" s="114"/>
+      <c r="B60" s="122"/>
       <c r="C60" s="58" t="str">
         <f>master!C42</f>
         <v>（補足）Spring Bootプロジェクトの準備</v>
       </c>
-      <c r="D60" s="110" t="s">
+      <c r="D60" s="115" t="s">
         <v>169</v>
       </c>
-      <c r="E60" s="111"/>
-      <c r="F60" s="112"/>
+      <c r="E60" s="116"/>
+      <c r="F60" s="117"/>
       <c r="G60" s="58" t="s">
         <v>291</v>
       </c>
@@ -8052,16 +8059,16 @@
     </row>
     <row r="61" spans="1:14" ht="88.2">
       <c r="A61" s="11"/>
-      <c r="B61" s="115"/>
+      <c r="B61" s="123"/>
       <c r="C61" s="58" t="str">
         <f>master!C43</f>
         <v>Spring Bootアプリケーションの起動確認</v>
       </c>
-      <c r="D61" s="110" t="s">
+      <c r="D61" s="115" t="s">
         <v>191</v>
       </c>
-      <c r="E61" s="111"/>
-      <c r="F61" s="112"/>
+      <c r="E61" s="116"/>
+      <c r="F61" s="117"/>
       <c r="G61" s="58" t="s">
         <v>292</v>
       </c>
@@ -8079,7 +8086,7 @@
     </row>
     <row r="62" spans="1:14" ht="190.2" customHeight="1">
       <c r="A62" s="11"/>
-      <c r="B62" s="113" t="str">
+      <c r="B62" s="121" t="str">
         <f>master!B44</f>
         <v>ECサイト Webアプリの要件</v>
       </c>
@@ -8087,11 +8094,11 @@
         <f>master!C44</f>
         <v>ECサイト Webアプリの要件 – はじめに</v>
       </c>
-      <c r="D62" s="110" t="s">
+      <c r="D62" s="115" t="s">
         <v>170</v>
       </c>
-      <c r="E62" s="111"/>
-      <c r="F62" s="112"/>
+      <c r="E62" s="116"/>
+      <c r="F62" s="117"/>
       <c r="G62" s="58" t="s">
         <v>293</v>
       </c>
@@ -8109,16 +8116,16 @@
     </row>
     <row r="63" spans="1:14" ht="151.19999999999999">
       <c r="A63" s="11"/>
-      <c r="B63" s="114"/>
+      <c r="B63" s="122"/>
       <c r="C63" s="58" t="str">
         <f>master!C45</f>
         <v>ECサイト Webアプリの要件➊ 画面</v>
       </c>
-      <c r="D63" s="110" t="s">
+      <c r="D63" s="115" t="s">
         <v>172</v>
       </c>
-      <c r="E63" s="111"/>
-      <c r="F63" s="112"/>
+      <c r="E63" s="116"/>
+      <c r="F63" s="117"/>
       <c r="G63" s="58" t="s">
         <v>294</v>
       </c>
@@ -8136,16 +8143,16 @@
     </row>
     <row r="64" spans="1:14" ht="214.2">
       <c r="A64" s="11"/>
-      <c r="B64" s="114"/>
+      <c r="B64" s="122"/>
       <c r="C64" s="58" t="str">
         <f>master!C46</f>
         <v>ECサイト Webアプリの要件➋ 機能</v>
       </c>
-      <c r="D64" s="110" t="s">
+      <c r="D64" s="115" t="s">
         <v>173</v>
       </c>
-      <c r="E64" s="111"/>
-      <c r="F64" s="112"/>
+      <c r="E64" s="116"/>
+      <c r="F64" s="117"/>
       <c r="G64" s="58" t="s">
         <v>295</v>
       </c>
@@ -8163,16 +8170,16 @@
     </row>
     <row r="65" spans="1:14" ht="63">
       <c r="A65" s="11"/>
-      <c r="B65" s="114"/>
+      <c r="B65" s="122"/>
       <c r="C65" s="58" t="str">
         <f>master!C47</f>
         <v>ECサイト Webアプリの要件➌ 画面遷移</v>
       </c>
-      <c r="D65" s="110" t="s">
+      <c r="D65" s="115" t="s">
         <v>174</v>
       </c>
-      <c r="E65" s="111"/>
-      <c r="F65" s="112"/>
+      <c r="E65" s="116"/>
+      <c r="F65" s="117"/>
       <c r="G65" s="58" t="s">
         <v>296</v>
       </c>
@@ -8190,16 +8197,16 @@
     </row>
     <row r="66" spans="1:14" ht="163.80000000000001">
       <c r="A66" s="11"/>
-      <c r="B66" s="114"/>
+      <c r="B66" s="122"/>
       <c r="C66" s="58" t="str">
         <f>master!C48</f>
         <v>ECサイト Webアプリの要件❹ データ設計</v>
       </c>
-      <c r="D66" s="110" t="s">
+      <c r="D66" s="115" t="s">
         <v>176</v>
       </c>
-      <c r="E66" s="111"/>
-      <c r="F66" s="112"/>
+      <c r="E66" s="116"/>
+      <c r="F66" s="117"/>
       <c r="G66" s="58" t="s">
         <v>297</v>
       </c>
@@ -8217,16 +8224,16 @@
     </row>
     <row r="67" spans="1:14" ht="50.4">
       <c r="A67" s="11"/>
-      <c r="B67" s="114"/>
+      <c r="B67" s="122"/>
       <c r="C67" s="58" t="str">
         <f>master!C49</f>
         <v>ECサイト Webアプリの要件❺ 初期データ</v>
       </c>
-      <c r="D67" s="110" t="s">
+      <c r="D67" s="115" t="s">
         <v>177</v>
       </c>
-      <c r="E67" s="111"/>
-      <c r="F67" s="112"/>
+      <c r="E67" s="116"/>
+      <c r="F67" s="117"/>
       <c r="G67" s="58" t="s">
         <v>293</v>
       </c>
@@ -8244,16 +8251,16 @@
     </row>
     <row r="68" spans="1:14" ht="37.799999999999997">
       <c r="A68" s="11"/>
-      <c r="B68" s="114"/>
+      <c r="B68" s="122"/>
       <c r="C68" s="58" t="str">
         <f>master!C50</f>
         <v>ECサイト Webアプリの要件❻ ディレクトリ構成</v>
       </c>
-      <c r="D68" s="110" t="s">
+      <c r="D68" s="115" t="s">
         <v>178</v>
       </c>
-      <c r="E68" s="111"/>
-      <c r="F68" s="112"/>
+      <c r="E68" s="116"/>
+      <c r="F68" s="117"/>
       <c r="G68" s="58" t="s">
         <v>288</v>
       </c>
@@ -8271,16 +8278,16 @@
     </row>
     <row r="69" spans="1:14" ht="37.799999999999997">
       <c r="A69" s="11"/>
-      <c r="B69" s="114"/>
+      <c r="B69" s="122"/>
       <c r="C69" s="58" t="str">
         <f>master!C51</f>
         <v>ECサイト Webアプリの要件❼ パッケージ構成</v>
       </c>
-      <c r="D69" s="110" t="s">
+      <c r="D69" s="115" t="s">
         <v>180</v>
       </c>
-      <c r="E69" s="111"/>
-      <c r="F69" s="112"/>
+      <c r="E69" s="116"/>
+      <c r="F69" s="117"/>
       <c r="G69" s="58" t="s">
         <v>288</v>
       </c>
@@ -8298,16 +8305,16 @@
     </row>
     <row r="70" spans="1:14" ht="37.799999999999997">
       <c r="A70" s="11"/>
-      <c r="B70" s="115"/>
+      <c r="B70" s="123"/>
       <c r="C70" s="58" t="str">
         <f>master!C52</f>
         <v>ECサイト Webアプリの要件❽ リソース構成</v>
       </c>
-      <c r="D70" s="110" t="s">
+      <c r="D70" s="115" t="s">
         <v>179</v>
       </c>
-      <c r="E70" s="111"/>
-      <c r="F70" s="112"/>
+      <c r="E70" s="116"/>
+      <c r="F70" s="117"/>
       <c r="G70" s="58" t="s">
         <v>288</v>
       </c>
@@ -8325,7 +8332,7 @@
     </row>
     <row r="71" spans="1:14" ht="25.2">
       <c r="A71" s="11"/>
-      <c r="B71" s="113" t="str">
+      <c r="B71" s="121" t="str">
         <f>master!B53</f>
         <v>ハンズオン</v>
       </c>
@@ -8333,11 +8340,11 @@
         <f>master!C53</f>
         <v>バイブコーディング – はじめに</v>
       </c>
-      <c r="D71" s="110" t="s">
+      <c r="D71" s="115" t="s">
         <v>181</v>
       </c>
-      <c r="E71" s="111"/>
-      <c r="F71" s="112"/>
+      <c r="E71" s="116"/>
+      <c r="F71" s="117"/>
       <c r="G71" s="58" t="s">
         <v>291</v>
       </c>
@@ -8355,16 +8362,16 @@
     </row>
     <row r="72" spans="1:14" ht="138.6">
       <c r="A72" s="11"/>
-      <c r="B72" s="114"/>
+      <c r="B72" s="122"/>
       <c r="C72" s="58" t="str">
         <f>master!C54</f>
         <v>[構造理解] Webアプリケーションで必要なもの</v>
       </c>
-      <c r="D72" s="110" t="s">
+      <c r="D72" s="115" t="s">
         <v>182</v>
       </c>
-      <c r="E72" s="111"/>
-      <c r="F72" s="112"/>
+      <c r="E72" s="116"/>
+      <c r="F72" s="117"/>
       <c r="G72" s="58" t="s">
         <v>298</v>
       </c>
@@ -8382,16 +8389,16 @@
     </row>
     <row r="73" spans="1:14" ht="50.4">
       <c r="A73" s="11"/>
-      <c r="B73" s="114"/>
+      <c r="B73" s="122"/>
       <c r="C73" s="76" t="str">
         <f>master!C55</f>
         <v>バイブコーディング➊ 画面モックアップを作ってデザインを決める</v>
       </c>
-      <c r="D73" s="110" t="s">
+      <c r="D73" s="115" t="s">
         <v>192</v>
       </c>
-      <c r="E73" s="111"/>
-      <c r="F73" s="112"/>
+      <c r="E73" s="116"/>
+      <c r="F73" s="117"/>
       <c r="G73" s="58" t="s">
         <v>293</v>
       </c>
@@ -8409,13 +8416,13 @@
     </row>
     <row r="74" spans="1:14" ht="88.2" customHeight="1">
       <c r="A74" s="11"/>
-      <c r="B74" s="114"/>
+      <c r="B74" s="122"/>
       <c r="C74" s="77"/>
-      <c r="D74" s="110" t="s">
+      <c r="D74" s="115" t="s">
         <v>183</v>
       </c>
-      <c r="E74" s="111"/>
-      <c r="F74" s="112"/>
+      <c r="E74" s="116"/>
+      <c r="F74" s="117"/>
       <c r="G74" s="58" t="s">
         <v>292</v>
       </c>
@@ -8429,16 +8436,16 @@
     </row>
     <row r="75" spans="1:14" ht="50.4">
       <c r="A75" s="11"/>
-      <c r="B75" s="114"/>
+      <c r="B75" s="122"/>
       <c r="C75" s="76" t="str">
         <f>master!C56</f>
         <v>バイブコーディング➋ データベースのテーブルを準備する</v>
       </c>
-      <c r="D75" s="110" t="s">
+      <c r="D75" s="115" t="s">
         <v>196</v>
       </c>
-      <c r="E75" s="111"/>
-      <c r="F75" s="112"/>
+      <c r="E75" s="116"/>
+      <c r="F75" s="117"/>
       <c r="G75" s="58" t="s">
         <v>293</v>
       </c>
@@ -8456,13 +8463,13 @@
     </row>
     <row r="76" spans="1:14" ht="88.2">
       <c r="A76" s="11"/>
-      <c r="B76" s="114"/>
+      <c r="B76" s="122"/>
       <c r="C76" s="77"/>
-      <c r="D76" s="110" t="s">
+      <c r="D76" s="115" t="s">
         <v>183</v>
       </c>
-      <c r="E76" s="111"/>
-      <c r="F76" s="112"/>
+      <c r="E76" s="116"/>
+      <c r="F76" s="117"/>
       <c r="G76" s="58" t="s">
         <v>292</v>
       </c>
@@ -8476,16 +8483,16 @@
     </row>
     <row r="77" spans="1:14" ht="50.4">
       <c r="A77" s="11"/>
-      <c r="B77" s="114"/>
+      <c r="B77" s="122"/>
       <c r="C77" s="76" t="str">
         <f>master!C57</f>
         <v>バイブコーディング➌ データベースのデータを準備する</v>
       </c>
-      <c r="D77" s="110" t="s">
+      <c r="D77" s="115" t="s">
         <v>195</v>
       </c>
-      <c r="E77" s="111"/>
-      <c r="F77" s="112"/>
+      <c r="E77" s="116"/>
+      <c r="F77" s="117"/>
       <c r="G77" s="58" t="s">
         <v>293</v>
       </c>
@@ -8503,13 +8510,13 @@
     </row>
     <row r="78" spans="1:14" ht="88.2">
       <c r="A78" s="11"/>
-      <c r="B78" s="114"/>
+      <c r="B78" s="122"/>
       <c r="C78" s="77"/>
-      <c r="D78" s="110" t="s">
+      <c r="D78" s="115" t="s">
         <v>183</v>
       </c>
-      <c r="E78" s="111"/>
-      <c r="F78" s="112"/>
+      <c r="E78" s="116"/>
+      <c r="F78" s="117"/>
       <c r="G78" s="58" t="s">
         <v>292</v>
       </c>
@@ -8523,16 +8530,16 @@
     </row>
     <row r="79" spans="1:14" ht="63">
       <c r="A79" s="11"/>
-      <c r="B79" s="114"/>
+      <c r="B79" s="122"/>
       <c r="C79" s="76" t="str">
         <f>master!C58</f>
         <v>バイブコーディング❹ データベース処理とビジネスロジックを作る</v>
       </c>
-      <c r="D79" s="110" t="s">
+      <c r="D79" s="115" t="s">
         <v>194</v>
       </c>
-      <c r="E79" s="111"/>
-      <c r="F79" s="112"/>
+      <c r="E79" s="116"/>
+      <c r="F79" s="117"/>
       <c r="G79" s="58" t="s">
         <v>296</v>
       </c>
@@ -8550,13 +8557,13 @@
     </row>
     <row r="80" spans="1:14" ht="88.2">
       <c r="A80" s="11"/>
-      <c r="B80" s="114"/>
+      <c r="B80" s="122"/>
       <c r="C80" s="77"/>
-      <c r="D80" s="110" t="s">
+      <c r="D80" s="115" t="s">
         <v>183</v>
       </c>
-      <c r="E80" s="111"/>
-      <c r="F80" s="112"/>
+      <c r="E80" s="116"/>
+      <c r="F80" s="117"/>
       <c r="G80" s="58" t="s">
         <v>292</v>
       </c>
@@ -8570,16 +8577,16 @@
     </row>
     <row r="81" spans="1:14" ht="50.4">
       <c r="A81" s="11"/>
-      <c r="B81" s="114"/>
+      <c r="B81" s="122"/>
       <c r="C81" s="58" t="str">
         <f>master!C59</f>
         <v>[解説] RepositoryクラスとSQLの例（抜粋）</v>
       </c>
-      <c r="D81" s="110" t="s">
+      <c r="D81" s="115" t="s">
         <v>184</v>
       </c>
-      <c r="E81" s="111"/>
-      <c r="F81" s="112"/>
+      <c r="E81" s="116"/>
+      <c r="F81" s="117"/>
       <c r="G81" s="58" t="s">
         <v>293</v>
       </c>
@@ -8597,16 +8604,16 @@
     </row>
     <row r="82" spans="1:14" ht="50.4">
       <c r="A82" s="11"/>
-      <c r="B82" s="114"/>
+      <c r="B82" s="122"/>
       <c r="C82" s="58" t="str">
         <f>master!C60</f>
         <v>[解説] Entity/Modelクラスの例（抜粋）</v>
       </c>
-      <c r="D82" s="110" t="s">
+      <c r="D82" s="115" t="s">
         <v>185</v>
       </c>
-      <c r="E82" s="111"/>
-      <c r="F82" s="112"/>
+      <c r="E82" s="116"/>
+      <c r="F82" s="117"/>
       <c r="G82" s="58" t="s">
         <v>293</v>
       </c>
@@ -8624,16 +8631,16 @@
     </row>
     <row r="83" spans="1:14" ht="37.799999999999997">
       <c r="A83" s="11"/>
-      <c r="B83" s="114"/>
+      <c r="B83" s="122"/>
       <c r="C83" s="58" t="str">
         <f>master!C61</f>
         <v>[解説] Serviceクラスの例（抜粋）</v>
       </c>
-      <c r="D83" s="110" t="s">
+      <c r="D83" s="115" t="s">
         <v>186</v>
       </c>
-      <c r="E83" s="111"/>
-      <c r="F83" s="112"/>
+      <c r="E83" s="116"/>
+      <c r="F83" s="117"/>
       <c r="G83" s="58" t="s">
         <v>288</v>
       </c>
@@ -8651,16 +8658,16 @@
     </row>
     <row r="84" spans="1:14" ht="50.4">
       <c r="A84" s="11"/>
-      <c r="B84" s="114"/>
+      <c r="B84" s="122"/>
       <c r="C84" s="76" t="str">
         <f>master!C62</f>
         <v>バイブコーディング❺ モックアップをもとに画面表示/処理を作る</v>
       </c>
-      <c r="D84" s="110" t="s">
+      <c r="D84" s="115" t="s">
         <v>193</v>
       </c>
-      <c r="E84" s="111"/>
-      <c r="F84" s="112"/>
+      <c r="E84" s="116"/>
+      <c r="F84" s="117"/>
       <c r="G84" s="58" t="s">
         <v>293</v>
       </c>
@@ -8678,13 +8685,13 @@
     </row>
     <row r="85" spans="1:14" ht="88.2">
       <c r="A85" s="11"/>
-      <c r="B85" s="114"/>
+      <c r="B85" s="122"/>
       <c r="C85" s="77"/>
-      <c r="D85" s="110" t="s">
+      <c r="D85" s="115" t="s">
         <v>183</v>
       </c>
-      <c r="E85" s="111"/>
-      <c r="F85" s="112"/>
+      <c r="E85" s="116"/>
+      <c r="F85" s="117"/>
       <c r="G85" s="58" t="s">
         <v>292</v>
       </c>
@@ -8698,16 +8705,16 @@
     </row>
     <row r="86" spans="1:14" ht="37.799999999999997">
       <c r="A86" s="11"/>
-      <c r="B86" s="114"/>
+      <c r="B86" s="122"/>
       <c r="C86" s="58" t="str">
         <f>master!C63</f>
         <v>[解説] Controllerクラスの例（抜粋）</v>
       </c>
-      <c r="D86" s="110" t="s">
+      <c r="D86" s="115" t="s">
         <v>187</v>
       </c>
-      <c r="E86" s="111"/>
-      <c r="F86" s="112"/>
+      <c r="E86" s="116"/>
+      <c r="F86" s="117"/>
       <c r="G86" s="58" t="s">
         <v>288</v>
       </c>
@@ -8725,16 +8732,16 @@
     </row>
     <row r="87" spans="1:14" ht="37.799999999999997">
       <c r="A87" s="11"/>
-      <c r="B87" s="114"/>
+      <c r="B87" s="122"/>
       <c r="C87" s="58" t="str">
         <f>master!C64</f>
         <v>[解説] Thymeleafテンプレートの例（抜粋）</v>
       </c>
-      <c r="D87" s="110" t="s">
+      <c r="D87" s="115" t="s">
         <v>188</v>
       </c>
-      <c r="E87" s="111"/>
-      <c r="F87" s="112"/>
+      <c r="E87" s="116"/>
+      <c r="F87" s="117"/>
       <c r="G87" s="58" t="s">
         <v>288</v>
       </c>
@@ -8752,16 +8759,16 @@
     </row>
     <row r="88" spans="1:14" ht="37.799999999999997">
       <c r="A88" s="11"/>
-      <c r="B88" s="114"/>
+      <c r="B88" s="122"/>
       <c r="C88" s="58" t="str">
         <f>master!C65</f>
         <v>[解説] Formクラスの例（抜粋）</v>
       </c>
-      <c r="D88" s="110" t="s">
+      <c r="D88" s="115" t="s">
         <v>189</v>
       </c>
-      <c r="E88" s="111"/>
-      <c r="F88" s="112"/>
+      <c r="E88" s="116"/>
+      <c r="F88" s="117"/>
       <c r="G88" s="58" t="s">
         <v>288</v>
       </c>
@@ -8779,16 +8786,16 @@
     </row>
     <row r="89" spans="1:14" ht="75.599999999999994">
       <c r="A89" s="11"/>
-      <c r="B89" s="114"/>
+      <c r="B89" s="122"/>
       <c r="C89" s="76" t="str">
         <f>master!C66</f>
         <v>バイブコーディング❻ 動作を確認する</v>
       </c>
-      <c r="D89" s="110" t="s">
+      <c r="D89" s="115" t="s">
         <v>190</v>
       </c>
-      <c r="E89" s="111"/>
-      <c r="F89" s="112"/>
+      <c r="E89" s="116"/>
+      <c r="F89" s="117"/>
       <c r="G89" s="58" t="s">
         <v>289</v>
       </c>
@@ -8806,13 +8813,13 @@
     </row>
     <row r="90" spans="1:14" ht="63">
       <c r="A90" s="11"/>
-      <c r="B90" s="115"/>
+      <c r="B90" s="123"/>
       <c r="C90" s="77"/>
-      <c r="D90" s="110" t="s">
+      <c r="D90" s="115" t="s">
         <v>197</v>
       </c>
-      <c r="E90" s="111"/>
-      <c r="F90" s="112"/>
+      <c r="E90" s="116"/>
+      <c r="F90" s="117"/>
       <c r="G90" s="58" t="s">
         <v>296</v>
       </c>
@@ -8830,7 +8837,7 @@
     </row>
     <row r="91" spans="1:14" ht="50.4">
       <c r="A91" s="11"/>
-      <c r="B91" s="107" t="str">
+      <c r="B91" s="124" t="str">
         <f>master!B69</f>
         <v>Gitとは</v>
       </c>
@@ -8838,11 +8845,11 @@
         <f>master!C69</f>
         <v>はじめに</v>
       </c>
-      <c r="D91" s="104" t="s">
-        <v>418</v>
-      </c>
-      <c r="E91" s="105"/>
-      <c r="F91" s="106"/>
+      <c r="D91" s="109" t="s">
+        <v>417</v>
+      </c>
+      <c r="E91" s="110"/>
+      <c r="F91" s="111"/>
       <c r="G91" s="48" t="s">
         <v>335</v>
       </c>
@@ -8860,16 +8867,16 @@
     </row>
     <row r="92" spans="1:14" ht="37.799999999999997">
       <c r="A92" s="11"/>
-      <c r="B92" s="108"/>
+      <c r="B92" s="125"/>
       <c r="C92" s="48" t="str">
         <f>master!C70</f>
         <v>バージョン管理とは</v>
       </c>
-      <c r="D92" s="104" t="s">
-        <v>393</v>
-      </c>
-      <c r="E92" s="105"/>
-      <c r="F92" s="106"/>
+      <c r="D92" s="109" t="s">
+        <v>392</v>
+      </c>
+      <c r="E92" s="110"/>
+      <c r="F92" s="111"/>
       <c r="G92" s="48" t="s">
         <v>334</v>
       </c>
@@ -8887,18 +8894,18 @@
     </row>
     <row r="93" spans="1:14" ht="151.19999999999999">
       <c r="A93" s="11"/>
-      <c r="B93" s="109"/>
+      <c r="B93" s="126"/>
       <c r="C93" s="48" t="str">
         <f>master!C71</f>
         <v>Gitの概要</v>
       </c>
-      <c r="D93" s="104" t="s">
+      <c r="D93" s="109" t="s">
+        <v>393</v>
+      </c>
+      <c r="E93" s="110"/>
+      <c r="F93" s="111"/>
+      <c r="G93" s="48" t="s">
         <v>394</v>
-      </c>
-      <c r="E93" s="105"/>
-      <c r="F93" s="106"/>
-      <c r="G93" s="48" t="s">
-        <v>395</v>
       </c>
       <c r="H93" s="12"/>
       <c r="I93" s="46" t="s">
@@ -8914,7 +8921,7 @@
     </row>
     <row r="94" spans="1:14" ht="75.599999999999994">
       <c r="A94" s="11"/>
-      <c r="B94" s="107" t="str">
+      <c r="B94" s="124" t="str">
         <f>master!B72</f>
         <v>Gitの基本構成</v>
       </c>
@@ -8922,13 +8929,13 @@
         <f>master!C72</f>
         <v>はじめに</v>
       </c>
-      <c r="D94" s="104" t="s">
-        <v>417</v>
-      </c>
-      <c r="E94" s="105"/>
-      <c r="F94" s="106"/>
+      <c r="D94" s="109" t="s">
+        <v>416</v>
+      </c>
+      <c r="E94" s="110"/>
+      <c r="F94" s="111"/>
       <c r="G94" s="48" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="H94" s="12"/>
       <c r="I94" s="46" t="s">
@@ -8944,16 +8951,16 @@
     </row>
     <row r="95" spans="1:14" ht="37.799999999999997">
       <c r="A95" s="11"/>
-      <c r="B95" s="108"/>
+      <c r="B95" s="125"/>
       <c r="C95" s="48" t="str">
         <f>master!C73</f>
         <v>ワーキングツリー</v>
       </c>
-      <c r="D95" s="104" t="s">
-        <v>397</v>
-      </c>
-      <c r="E95" s="105"/>
-      <c r="F95" s="106"/>
+      <c r="D95" s="109" t="s">
+        <v>396</v>
+      </c>
+      <c r="E95" s="110"/>
+      <c r="F95" s="111"/>
       <c r="G95" s="48" t="s">
         <v>334</v>
       </c>
@@ -8971,16 +8978,16 @@
     </row>
     <row r="96" spans="1:14" ht="37.799999999999997">
       <c r="A96" s="11"/>
-      <c r="B96" s="108"/>
+      <c r="B96" s="125"/>
       <c r="C96" s="48" t="str">
         <f>master!C74</f>
         <v>ステージングエリア</v>
       </c>
-      <c r="D96" s="104" t="s">
-        <v>398</v>
-      </c>
-      <c r="E96" s="105"/>
-      <c r="F96" s="106"/>
+      <c r="D96" s="109" t="s">
+        <v>397</v>
+      </c>
+      <c r="E96" s="110"/>
+      <c r="F96" s="111"/>
       <c r="G96" s="48" t="s">
         <v>334</v>
       </c>
@@ -8998,16 +9005,16 @@
     </row>
     <row r="97" spans="1:14" ht="37.799999999999997">
       <c r="A97" s="11"/>
-      <c r="B97" s="108"/>
+      <c r="B97" s="125"/>
       <c r="C97" s="48" t="str">
         <f>master!C75</f>
         <v>ローカルリポジトリ</v>
       </c>
-      <c r="D97" s="104" t="s">
-        <v>399</v>
-      </c>
-      <c r="E97" s="105"/>
-      <c r="F97" s="106"/>
+      <c r="D97" s="109" t="s">
+        <v>398</v>
+      </c>
+      <c r="E97" s="110"/>
+      <c r="F97" s="111"/>
       <c r="G97" s="48" t="s">
         <v>334</v>
       </c>
@@ -9025,16 +9032,16 @@
     </row>
     <row r="98" spans="1:14" ht="50.4">
       <c r="A98" s="11"/>
-      <c r="B98" s="109"/>
+      <c r="B98" s="126"/>
       <c r="C98" s="48" t="str">
         <f>master!C76</f>
         <v>リモートリポジトリ</v>
       </c>
-      <c r="D98" s="104" t="s">
-        <v>400</v>
-      </c>
-      <c r="E98" s="105"/>
-      <c r="F98" s="106"/>
+      <c r="D98" s="109" t="s">
+        <v>399</v>
+      </c>
+      <c r="E98" s="110"/>
+      <c r="F98" s="111"/>
       <c r="G98" s="48" t="s">
         <v>335</v>
       </c>
@@ -9052,7 +9059,7 @@
     </row>
     <row r="99" spans="1:14" ht="88.2">
       <c r="A99" s="11"/>
-      <c r="B99" s="107" t="str">
+      <c r="B99" s="124" t="str">
         <f>master!B77</f>
         <v>ローカルリポジトリの操作</v>
       </c>
@@ -9060,13 +9067,13 @@
         <f>master!C77</f>
         <v>はじめに</v>
       </c>
-      <c r="D99" s="104" t="s">
-        <v>416</v>
-      </c>
-      <c r="E99" s="105"/>
-      <c r="F99" s="106"/>
+      <c r="D99" s="109" t="s">
+        <v>415</v>
+      </c>
+      <c r="E99" s="110"/>
+      <c r="F99" s="111"/>
       <c r="G99" s="48" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="H99" s="12"/>
       <c r="I99" s="46" t="s">
@@ -9082,16 +9089,16 @@
     </row>
     <row r="100" spans="1:14" ht="37.799999999999997">
       <c r="A100" s="11"/>
-      <c r="B100" s="108"/>
+      <c r="B100" s="125"/>
       <c r="C100" s="48" t="str">
         <f>master!C78</f>
         <v>リポジトリの作成</v>
       </c>
-      <c r="D100" s="104" t="s">
-        <v>402</v>
-      </c>
-      <c r="E100" s="105"/>
-      <c r="F100" s="106"/>
+      <c r="D100" s="109" t="s">
+        <v>401</v>
+      </c>
+      <c r="E100" s="110"/>
+      <c r="F100" s="111"/>
       <c r="G100" s="48" t="s">
         <v>334</v>
       </c>
@@ -9109,16 +9116,16 @@
     </row>
     <row r="101" spans="1:14" ht="37.799999999999997" customHeight="1">
       <c r="A101" s="11"/>
-      <c r="B101" s="108"/>
+      <c r="B101" s="125"/>
       <c r="C101" s="48" t="str">
         <f>master!C79</f>
         <v>ファイルの変更</v>
       </c>
-      <c r="D101" s="104" t="s">
-        <v>403</v>
-      </c>
-      <c r="E101" s="105"/>
-      <c r="F101" s="106"/>
+      <c r="D101" s="109" t="s">
+        <v>402</v>
+      </c>
+      <c r="E101" s="110"/>
+      <c r="F101" s="111"/>
       <c r="G101" s="48" t="s">
         <v>334</v>
       </c>
@@ -9136,16 +9143,16 @@
     </row>
     <row r="102" spans="1:14" ht="37.799999999999997">
       <c r="A102" s="11"/>
-      <c r="B102" s="108"/>
+      <c r="B102" s="125"/>
       <c r="C102" s="48" t="str">
         <f>master!C80</f>
         <v>変更内容の確認</v>
       </c>
-      <c r="D102" s="104" t="s">
-        <v>404</v>
-      </c>
-      <c r="E102" s="105"/>
-      <c r="F102" s="106"/>
+      <c r="D102" s="109" t="s">
+        <v>403</v>
+      </c>
+      <c r="E102" s="110"/>
+      <c r="F102" s="111"/>
       <c r="G102" s="48" t="s">
         <v>334</v>
       </c>
@@ -9163,16 +9170,16 @@
     </row>
     <row r="103" spans="1:14" ht="37.799999999999997">
       <c r="A103" s="11"/>
-      <c r="B103" s="108"/>
+      <c r="B103" s="125"/>
       <c r="C103" s="48" t="str">
         <f>master!C81</f>
         <v>変更内容のステージ</v>
       </c>
-      <c r="D103" s="104" t="s">
-        <v>405</v>
-      </c>
-      <c r="E103" s="105"/>
-      <c r="F103" s="106"/>
+      <c r="D103" s="109" t="s">
+        <v>404</v>
+      </c>
+      <c r="E103" s="110"/>
+      <c r="F103" s="111"/>
       <c r="G103" s="48" t="s">
         <v>334</v>
       </c>
@@ -9190,16 +9197,16 @@
     </row>
     <row r="104" spans="1:14" ht="37.799999999999997">
       <c r="A104" s="11"/>
-      <c r="B104" s="108"/>
+      <c r="B104" s="125"/>
       <c r="C104" s="48" t="str">
         <f>master!C82</f>
         <v>変更内容のコミット</v>
       </c>
-      <c r="D104" s="104" t="s">
-        <v>406</v>
-      </c>
-      <c r="E104" s="105"/>
-      <c r="F104" s="106"/>
+      <c r="D104" s="109" t="s">
+        <v>405</v>
+      </c>
+      <c r="E104" s="110"/>
+      <c r="F104" s="111"/>
       <c r="G104" s="48" t="s">
         <v>334</v>
       </c>
@@ -9217,16 +9224,16 @@
     </row>
     <row r="105" spans="1:14" ht="37.799999999999997">
       <c r="A105" s="11"/>
-      <c r="B105" s="108"/>
+      <c r="B105" s="125"/>
       <c r="C105" s="48" t="str">
         <f>master!C83</f>
         <v>ワーキングツリーの変更の取り消し</v>
       </c>
-      <c r="D105" s="104" t="s">
-        <v>407</v>
-      </c>
-      <c r="E105" s="105"/>
-      <c r="F105" s="106"/>
+      <c r="D105" s="109" t="s">
+        <v>406</v>
+      </c>
+      <c r="E105" s="110"/>
+      <c r="F105" s="111"/>
       <c r="G105" s="48" t="s">
         <v>334</v>
       </c>
@@ -9244,16 +9251,16 @@
     </row>
     <row r="106" spans="1:14" ht="37.799999999999997">
       <c r="A106" s="11"/>
-      <c r="B106" s="108"/>
+      <c r="B106" s="125"/>
       <c r="C106" s="48" t="str">
         <f>master!C84</f>
         <v>ステージングの取り消し</v>
       </c>
-      <c r="D106" s="104" t="s">
-        <v>408</v>
-      </c>
-      <c r="E106" s="105"/>
-      <c r="F106" s="106"/>
+      <c r="D106" s="109" t="s">
+        <v>407</v>
+      </c>
+      <c r="E106" s="110"/>
+      <c r="F106" s="111"/>
       <c r="G106" s="48" t="s">
         <v>334</v>
       </c>
@@ -9271,16 +9278,16 @@
     </row>
     <row r="107" spans="1:14" ht="37.799999999999997">
       <c r="A107" s="11"/>
-      <c r="B107" s="109"/>
+      <c r="B107" s="126"/>
       <c r="C107" s="48" t="str">
         <f>master!C85</f>
-        <v>コミットの取り消し</v>
-      </c>
-      <c r="D107" s="104" t="s">
-        <v>409</v>
-      </c>
-      <c r="E107" s="105"/>
-      <c r="F107" s="106"/>
+        <v>コミットの打ち消し</v>
+      </c>
+      <c r="D107" s="109" t="s">
+        <v>408</v>
+      </c>
+      <c r="E107" s="110"/>
+      <c r="F107" s="111"/>
       <c r="G107" s="48" t="s">
         <v>334</v>
       </c>
@@ -9298,7 +9305,7 @@
     </row>
     <row r="108" spans="1:14" ht="75.599999999999994">
       <c r="A108" s="11"/>
-      <c r="B108" s="107" t="str">
+      <c r="B108" s="124" t="str">
         <f>master!B86</f>
         <v>リモートリポジトリの操作</v>
       </c>
@@ -9306,13 +9313,13 @@
         <f>master!C86</f>
         <v>はじめに</v>
       </c>
-      <c r="D108" s="104" t="s">
-        <v>414</v>
-      </c>
-      <c r="E108" s="105"/>
-      <c r="F108" s="106"/>
+      <c r="D108" s="109" t="s">
+        <v>413</v>
+      </c>
+      <c r="E108" s="110"/>
+      <c r="F108" s="111"/>
       <c r="G108" s="48" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="H108" s="12"/>
       <c r="I108" s="46" t="s">
@@ -9322,7 +9329,7 @@
         <v>0</v>
       </c>
       <c r="K108" s="89" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="L108" s="6"/>
       <c r="M108" s="6"/>
@@ -9330,16 +9337,16 @@
     </row>
     <row r="109" spans="1:14" ht="37.799999999999997">
       <c r="A109" s="11"/>
-      <c r="B109" s="108"/>
+      <c r="B109" s="125"/>
       <c r="C109" s="48" t="str">
         <f>master!C87</f>
         <v>リポジトリの取得</v>
       </c>
-      <c r="D109" s="104" t="s">
-        <v>410</v>
-      </c>
-      <c r="E109" s="105"/>
-      <c r="F109" s="106"/>
+      <c r="D109" s="109" t="s">
+        <v>409</v>
+      </c>
+      <c r="E109" s="110"/>
+      <c r="F109" s="111"/>
       <c r="G109" s="48" t="s">
         <v>334</v>
       </c>
@@ -9351,7 +9358,7 @@
         <v>0</v>
       </c>
       <c r="K109" s="89" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="L109" s="6"/>
       <c r="M109" s="6"/>
@@ -9359,16 +9366,16 @@
     </row>
     <row r="110" spans="1:14" ht="37.799999999999997">
       <c r="A110" s="11"/>
-      <c r="B110" s="108"/>
+      <c r="B110" s="125"/>
       <c r="C110" s="48" t="str">
         <f>master!C88</f>
         <v>リモートからの取得</v>
       </c>
-      <c r="D110" s="104" t="s">
-        <v>411</v>
-      </c>
-      <c r="E110" s="105"/>
-      <c r="F110" s="106"/>
+      <c r="D110" s="109" t="s">
+        <v>410</v>
+      </c>
+      <c r="E110" s="110"/>
+      <c r="F110" s="111"/>
       <c r="G110" s="48" t="s">
         <v>334</v>
       </c>
@@ -9380,7 +9387,7 @@
         <v>0</v>
       </c>
       <c r="K110" s="89" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="L110" s="6"/>
       <c r="M110" s="6"/>
@@ -9388,16 +9395,16 @@
     </row>
     <row r="111" spans="1:14" ht="37.799999999999997">
       <c r="A111" s="11"/>
-      <c r="B111" s="108"/>
+      <c r="B111" s="125"/>
       <c r="C111" s="48" t="str">
         <f>master!C89</f>
         <v>リモートからの取得と反映</v>
       </c>
-      <c r="D111" s="104" t="s">
-        <v>413</v>
-      </c>
-      <c r="E111" s="105"/>
-      <c r="F111" s="106"/>
+      <c r="D111" s="109" t="s">
+        <v>412</v>
+      </c>
+      <c r="E111" s="110"/>
+      <c r="F111" s="111"/>
       <c r="G111" s="48" t="s">
         <v>334</v>
       </c>
@@ -9409,7 +9416,7 @@
         <v>0</v>
       </c>
       <c r="K111" s="89" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="L111" s="6"/>
       <c r="M111" s="6"/>
@@ -9417,16 +9424,16 @@
     </row>
     <row r="112" spans="1:14" ht="37.799999999999997">
       <c r="A112" s="11"/>
-      <c r="B112" s="109"/>
+      <c r="B112" s="126"/>
       <c r="C112" s="48" t="str">
         <f>master!C90</f>
         <v>リモートへの反映</v>
       </c>
-      <c r="D112" s="104" t="s">
-        <v>412</v>
-      </c>
-      <c r="E112" s="105"/>
-      <c r="F112" s="106"/>
+      <c r="D112" s="109" t="s">
+        <v>411</v>
+      </c>
+      <c r="E112" s="110"/>
+      <c r="F112" s="111"/>
       <c r="G112" s="48" t="s">
         <v>334</v>
       </c>
@@ -9438,7 +9445,7 @@
         <v>0</v>
       </c>
       <c r="K112" s="89" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="L112" s="6"/>
       <c r="M112" s="6"/>
@@ -9446,7 +9453,7 @@
     </row>
     <row r="113" spans="1:14" ht="88.2">
       <c r="A113" s="11"/>
-      <c r="B113" s="107" t="str">
+      <c r="B113" s="124" t="str">
         <f>master!B91</f>
         <v>ブランチの操作</v>
       </c>
@@ -9454,13 +9461,13 @@
         <f>master!C91</f>
         <v>はじめに</v>
       </c>
-      <c r="D113" s="104" t="s">
-        <v>415</v>
-      </c>
-      <c r="E113" s="105"/>
-      <c r="F113" s="106"/>
+      <c r="D113" s="109" t="s">
+        <v>414</v>
+      </c>
+      <c r="E113" s="110"/>
+      <c r="F113" s="111"/>
       <c r="G113" s="48" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="H113" s="12"/>
       <c r="I113" s="46" t="s">
@@ -9470,7 +9477,7 @@
         <v>0</v>
       </c>
       <c r="K113" s="89" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="L113" s="6"/>
       <c r="M113" s="6"/>
@@ -9478,16 +9485,16 @@
     </row>
     <row r="114" spans="1:14" ht="37.799999999999997">
       <c r="A114" s="11"/>
-      <c r="B114" s="108"/>
+      <c r="B114" s="125"/>
       <c r="C114" s="48" t="str">
         <f>master!C92</f>
         <v>ブランチとは</v>
       </c>
-      <c r="D114" s="104" t="s">
-        <v>419</v>
-      </c>
-      <c r="E114" s="105"/>
-      <c r="F114" s="106"/>
+      <c r="D114" s="109" t="s">
+        <v>418</v>
+      </c>
+      <c r="E114" s="110"/>
+      <c r="F114" s="111"/>
       <c r="G114" s="48" t="s">
         <v>334</v>
       </c>
@@ -9505,16 +9512,16 @@
     </row>
     <row r="115" spans="1:14" ht="37.799999999999997">
       <c r="A115" s="11"/>
-      <c r="B115" s="108"/>
+      <c r="B115" s="125"/>
       <c r="C115" s="48" t="str">
         <f>master!C93</f>
         <v>ブランチの作成</v>
       </c>
-      <c r="D115" s="104" t="s">
-        <v>420</v>
-      </c>
-      <c r="E115" s="105"/>
-      <c r="F115" s="106"/>
+      <c r="D115" s="109" t="s">
+        <v>419</v>
+      </c>
+      <c r="E115" s="110"/>
+      <c r="F115" s="111"/>
       <c r="G115" s="48" t="s">
         <v>334</v>
       </c>
@@ -9532,16 +9539,16 @@
     </row>
     <row r="116" spans="1:14" ht="37.799999999999997">
       <c r="A116" s="11"/>
-      <c r="B116" s="108"/>
+      <c r="B116" s="125"/>
       <c r="C116" s="48" t="str">
         <f>master!C94</f>
         <v>ブランチの切り替え</v>
       </c>
-      <c r="D116" s="104" t="s">
-        <v>421</v>
-      </c>
-      <c r="E116" s="105"/>
-      <c r="F116" s="106"/>
+      <c r="D116" s="109" t="s">
+        <v>420</v>
+      </c>
+      <c r="E116" s="110"/>
+      <c r="F116" s="111"/>
       <c r="G116" s="48" t="s">
         <v>334</v>
       </c>
@@ -9559,16 +9566,16 @@
     </row>
     <row r="117" spans="1:14" ht="37.799999999999997">
       <c r="A117" s="11"/>
-      <c r="B117" s="108"/>
+      <c r="B117" s="125"/>
       <c r="C117" s="48" t="str">
         <f>master!C95</f>
         <v>ブランチのマージ</v>
       </c>
-      <c r="D117" s="104" t="s">
-        <v>422</v>
-      </c>
-      <c r="E117" s="105"/>
-      <c r="F117" s="106"/>
+      <c r="D117" s="109" t="s">
+        <v>421</v>
+      </c>
+      <c r="E117" s="110"/>
+      <c r="F117" s="111"/>
       <c r="G117" s="48" t="s">
         <v>334</v>
       </c>
@@ -9586,16 +9593,16 @@
     </row>
     <row r="118" spans="1:14" ht="100.8">
       <c r="A118" s="11"/>
-      <c r="B118" s="109"/>
+      <c r="B118" s="126"/>
       <c r="C118" s="48" t="str">
         <f>master!C96</f>
         <v>コンフリクトの解消</v>
       </c>
-      <c r="D118" s="104" t="s">
-        <v>424</v>
-      </c>
-      <c r="E118" s="105"/>
-      <c r="F118" s="106"/>
+      <c r="D118" s="109" t="s">
+        <v>423</v>
+      </c>
+      <c r="E118" s="110"/>
+      <c r="F118" s="111"/>
       <c r="G118" s="48" t="s">
         <v>333</v>
       </c>
@@ -9613,7 +9620,7 @@
     </row>
     <row r="119" spans="1:14" ht="75.599999999999994">
       <c r="A119" s="11"/>
-      <c r="B119" s="107" t="str">
+      <c r="B119" s="124" t="str">
         <f>master!B97</f>
         <v>VSCodeによるGitの操作</v>
       </c>
@@ -9621,13 +9628,13 @@
         <f>master!C97</f>
         <v>はじめに</v>
       </c>
-      <c r="D119" s="104" t="s">
-        <v>423</v>
-      </c>
-      <c r="E119" s="105"/>
-      <c r="F119" s="106"/>
+      <c r="D119" s="109" t="s">
+        <v>422</v>
+      </c>
+      <c r="E119" s="110"/>
+      <c r="F119" s="111"/>
       <c r="G119" s="48" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="H119" s="12"/>
       <c r="I119" s="46" t="s">
@@ -9643,18 +9650,18 @@
     </row>
     <row r="120" spans="1:14" ht="25.2">
       <c r="A120" s="11"/>
-      <c r="B120" s="108"/>
+      <c r="B120" s="125"/>
       <c r="C120" s="48" t="str">
         <f>master!C98</f>
         <v>VSCodeのソース管理機能</v>
       </c>
-      <c r="D120" s="104" t="s">
+      <c r="D120" s="109" t="s">
+        <v>424</v>
+      </c>
+      <c r="E120" s="110"/>
+      <c r="F120" s="111"/>
+      <c r="G120" s="48" t="s">
         <v>425</v>
-      </c>
-      <c r="E120" s="105"/>
-      <c r="F120" s="106"/>
-      <c r="G120" s="48" t="s">
-        <v>426</v>
       </c>
       <c r="H120" s="12"/>
       <c r="I120" s="46" t="s">
@@ -9670,18 +9677,18 @@
     </row>
     <row r="121" spans="1:14" ht="126">
       <c r="A121" s="11"/>
-      <c r="B121" s="108"/>
+      <c r="B121" s="125"/>
       <c r="C121" s="48" t="str">
         <f>master!C99</f>
         <v>ローカルリポジトリの操作</v>
       </c>
-      <c r="D121" s="104" t="s">
-        <v>437</v>
-      </c>
-      <c r="E121" s="105"/>
-      <c r="F121" s="106"/>
+      <c r="D121" s="109" t="s">
+        <v>436</v>
+      </c>
+      <c r="E121" s="110"/>
+      <c r="F121" s="111"/>
       <c r="G121" s="48" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="H121" s="12"/>
       <c r="I121" s="46" t="s">
@@ -9697,16 +9704,16 @@
     </row>
     <row r="122" spans="1:14" ht="63">
       <c r="A122" s="11"/>
-      <c r="B122" s="108"/>
+      <c r="B122" s="125"/>
       <c r="C122" s="48" t="str">
         <f>master!C100</f>
         <v>リモートリポジトリの操作</v>
       </c>
-      <c r="D122" s="104" t="s">
-        <v>427</v>
-      </c>
-      <c r="E122" s="105"/>
-      <c r="F122" s="106"/>
+      <c r="D122" s="109" t="s">
+        <v>426</v>
+      </c>
+      <c r="E122" s="110"/>
+      <c r="F122" s="111"/>
       <c r="G122" s="48" t="s">
         <v>336</v>
       </c>
@@ -9718,7 +9725,7 @@
         <v>0</v>
       </c>
       <c r="K122" s="89" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="L122" s="6"/>
       <c r="M122" s="6"/>
@@ -9726,18 +9733,18 @@
     </row>
     <row r="123" spans="1:14" ht="113.4">
       <c r="A123" s="11"/>
-      <c r="B123" s="109"/>
+      <c r="B123" s="126"/>
       <c r="C123" s="48" t="str">
         <f>master!C101</f>
         <v>ブランチの操作</v>
       </c>
-      <c r="D123" s="104" t="s">
+      <c r="D123" s="109" t="s">
+        <v>437</v>
+      </c>
+      <c r="E123" s="110"/>
+      <c r="F123" s="111"/>
+      <c r="G123" s="48" t="s">
         <v>438</v>
-      </c>
-      <c r="E123" s="105"/>
-      <c r="F123" s="106"/>
-      <c r="G123" s="48" t="s">
-        <v>439</v>
       </c>
       <c r="H123" s="12"/>
       <c r="I123" s="46" t="s">
@@ -9747,7 +9754,7 @@
         <v>0</v>
       </c>
       <c r="K123" s="89" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="L123" s="6"/>
       <c r="M123" s="6"/>
@@ -9755,7 +9762,7 @@
     </row>
     <row r="124" spans="1:14" ht="25.2">
       <c r="A124" s="11"/>
-      <c r="B124" s="113" t="str">
+      <c r="B124" s="121" t="str">
         <f>master!B103</f>
         <v>演習について</v>
       </c>
@@ -9763,9 +9770,9 @@
         <f>master!C103</f>
         <v>はじめに</v>
       </c>
-      <c r="D124" s="110"/>
-      <c r="E124" s="111"/>
-      <c r="F124" s="112"/>
+      <c r="D124" s="115"/>
+      <c r="E124" s="116"/>
+      <c r="F124" s="117"/>
       <c r="G124" s="58" t="s">
         <v>338</v>
       </c>
@@ -9783,18 +9790,18 @@
     </row>
     <row r="125" spans="1:14" ht="50.4">
       <c r="A125" s="11"/>
-      <c r="B125" s="114"/>
+      <c r="B125" s="122"/>
       <c r="C125" s="58" t="str">
         <f>master!C104</f>
         <v>演習の構成</v>
       </c>
-      <c r="D125" s="110" t="s">
-        <v>429</v>
-      </c>
-      <c r="E125" s="111"/>
-      <c r="F125" s="112"/>
+      <c r="D125" s="115" t="s">
+        <v>428</v>
+      </c>
+      <c r="E125" s="116"/>
+      <c r="F125" s="117"/>
       <c r="G125" s="58" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="H125" s="59"/>
       <c r="I125" s="60" t="s">
@@ -9810,18 +9817,18 @@
     </row>
     <row r="126" spans="1:14" ht="50.4">
       <c r="A126" s="11"/>
-      <c r="B126" s="115"/>
+      <c r="B126" s="123"/>
       <c r="C126" s="58" t="str">
         <f>master!C105</f>
         <v>演習で利用するソフトウェア</v>
       </c>
-      <c r="D126" s="110" t="s">
-        <v>430</v>
-      </c>
-      <c r="E126" s="111"/>
-      <c r="F126" s="112"/>
+      <c r="D126" s="115" t="s">
+        <v>429</v>
+      </c>
+      <c r="E126" s="116"/>
+      <c r="F126" s="117"/>
       <c r="G126" s="58" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="H126" s="59"/>
       <c r="I126" s="60" t="s">
@@ -9831,7 +9838,7 @@
         <v>6.9444444444444447E-4</v>
       </c>
       <c r="K126" s="62" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="L126" s="6"/>
       <c r="M126" s="6"/>
@@ -9839,7 +9846,7 @@
     </row>
     <row r="127" spans="1:14" ht="176.4">
       <c r="A127" s="11"/>
-      <c r="B127" s="113" t="str">
+      <c r="B127" s="121" t="str">
         <f>master!B106</f>
         <v>VS Codeによるローカルリポジトリの操作</v>
       </c>
@@ -9847,13 +9854,13 @@
         <f>master!C106</f>
         <v>演習の前に</v>
       </c>
-      <c r="D127" s="110" t="s">
-        <v>434</v>
-      </c>
-      <c r="E127" s="111"/>
-      <c r="F127" s="112"/>
+      <c r="D127" s="115" t="s">
+        <v>433</v>
+      </c>
+      <c r="E127" s="116"/>
+      <c r="F127" s="117"/>
       <c r="G127" s="58" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="H127" s="59"/>
       <c r="I127" s="60" t="s">
@@ -9869,18 +9876,18 @@
     </row>
     <row r="128" spans="1:14" ht="37.799999999999997">
       <c r="A128" s="11"/>
-      <c r="B128" s="114"/>
+      <c r="B128" s="122"/>
       <c r="C128" s="58" t="str">
         <f>master!C107</f>
         <v>VS Codeによるリポジトリの作成</v>
       </c>
-      <c r="D128" s="110" t="s">
+      <c r="D128" s="115" t="s">
+        <v>430</v>
+      </c>
+      <c r="E128" s="116"/>
+      <c r="F128" s="117"/>
+      <c r="G128" s="58" t="s">
         <v>431</v>
-      </c>
-      <c r="E128" s="111"/>
-      <c r="F128" s="112"/>
-      <c r="G128" s="58" t="s">
-        <v>432</v>
       </c>
       <c r="H128" s="59"/>
       <c r="I128" s="60" t="s">
@@ -9896,18 +9903,18 @@
     </row>
     <row r="129" spans="1:14" ht="37.799999999999997">
       <c r="A129" s="11"/>
-      <c r="B129" s="114"/>
+      <c r="B129" s="122"/>
       <c r="C129" s="58" t="str">
         <f>master!C108</f>
         <v>VS Codeによる変更内容の確認</v>
       </c>
-      <c r="D129" s="110" t="s">
+      <c r="D129" s="115" t="s">
+        <v>430</v>
+      </c>
+      <c r="E129" s="116"/>
+      <c r="F129" s="117"/>
+      <c r="G129" s="58" t="s">
         <v>431</v>
-      </c>
-      <c r="E129" s="111"/>
-      <c r="F129" s="112"/>
-      <c r="G129" s="58" t="s">
-        <v>432</v>
       </c>
       <c r="H129" s="59"/>
       <c r="I129" s="60" t="s">
@@ -9923,18 +9930,18 @@
     </row>
     <row r="130" spans="1:14" ht="37.799999999999997">
       <c r="A130" s="11"/>
-      <c r="B130" s="114"/>
+      <c r="B130" s="122"/>
       <c r="C130" s="58" t="str">
         <f>master!C109</f>
         <v>VS Codeによる変更内容のステージング</v>
       </c>
-      <c r="D130" s="110" t="s">
+      <c r="D130" s="115" t="s">
+        <v>430</v>
+      </c>
+      <c r="E130" s="116"/>
+      <c r="F130" s="117"/>
+      <c r="G130" s="58" t="s">
         <v>431</v>
-      </c>
-      <c r="E130" s="111"/>
-      <c r="F130" s="112"/>
-      <c r="G130" s="58" t="s">
-        <v>432</v>
       </c>
       <c r="H130" s="59"/>
       <c r="I130" s="60" t="s">
@@ -9950,18 +9957,18 @@
     </row>
     <row r="131" spans="1:14" ht="37.799999999999997">
       <c r="A131" s="11"/>
-      <c r="B131" s="115"/>
+      <c r="B131" s="123"/>
       <c r="C131" s="58" t="str">
         <f>master!C110</f>
         <v>VS Codeによる変更内容のコミット</v>
       </c>
-      <c r="D131" s="110" t="s">
+      <c r="D131" s="115" t="s">
+        <v>430</v>
+      </c>
+      <c r="E131" s="116"/>
+      <c r="F131" s="117"/>
+      <c r="G131" s="58" t="s">
         <v>431</v>
-      </c>
-      <c r="E131" s="111"/>
-      <c r="F131" s="112"/>
-      <c r="G131" s="58" t="s">
-        <v>432</v>
       </c>
       <c r="H131" s="59"/>
       <c r="I131" s="60" t="s">
@@ -9977,7 +9984,7 @@
     </row>
     <row r="132" spans="1:14" ht="163.80000000000001">
       <c r="A132" s="11"/>
-      <c r="B132" s="113" t="str">
+      <c r="B132" s="121" t="str">
         <f>master!B111</f>
         <v>VS Codeによるブランチの操作</v>
       </c>
@@ -9985,11 +9992,11 @@
         <f>master!C111</f>
         <v>演習の前に</v>
       </c>
-      <c r="D132" s="110" t="s">
-        <v>435</v>
-      </c>
-      <c r="E132" s="111"/>
-      <c r="F132" s="112"/>
+      <c r="D132" s="115" t="s">
+        <v>434</v>
+      </c>
+      <c r="E132" s="116"/>
+      <c r="F132" s="117"/>
       <c r="G132" s="58" t="s">
         <v>337</v>
       </c>
@@ -10001,7 +10008,7 @@
         <v>0</v>
       </c>
       <c r="K132" s="62" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="L132" s="6"/>
       <c r="M132" s="6"/>
@@ -10009,18 +10016,18 @@
     </row>
     <row r="133" spans="1:14" ht="37.799999999999997">
       <c r="A133" s="11"/>
-      <c r="B133" s="114"/>
+      <c r="B133" s="122"/>
       <c r="C133" s="58" t="str">
         <f>master!C112</f>
         <v>VS Codeによるブランチの作成</v>
       </c>
-      <c r="D133" s="110" t="s">
+      <c r="D133" s="115" t="s">
+        <v>430</v>
+      </c>
+      <c r="E133" s="116"/>
+      <c r="F133" s="117"/>
+      <c r="G133" s="58" t="s">
         <v>431</v>
-      </c>
-      <c r="E133" s="111"/>
-      <c r="F133" s="112"/>
-      <c r="G133" s="58" t="s">
-        <v>432</v>
       </c>
       <c r="H133" s="59"/>
       <c r="I133" s="60" t="s">
@@ -10030,7 +10037,7 @@
         <v>0</v>
       </c>
       <c r="K133" s="62" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="L133" s="6"/>
       <c r="M133" s="6"/>
@@ -10038,18 +10045,18 @@
     </row>
     <row r="134" spans="1:14" ht="37.799999999999997">
       <c r="A134" s="11"/>
-      <c r="B134" s="114"/>
+      <c r="B134" s="122"/>
       <c r="C134" s="58" t="str">
         <f>master!C113</f>
         <v>VS Codeによるブランチの切り替え</v>
       </c>
-      <c r="D134" s="110" t="s">
+      <c r="D134" s="115" t="s">
+        <v>430</v>
+      </c>
+      <c r="E134" s="116"/>
+      <c r="F134" s="117"/>
+      <c r="G134" s="58" t="s">
         <v>431</v>
-      </c>
-      <c r="E134" s="111"/>
-      <c r="F134" s="112"/>
-      <c r="G134" s="58" t="s">
-        <v>432</v>
       </c>
       <c r="H134" s="59"/>
       <c r="I134" s="60" t="s">
@@ -10059,7 +10066,7 @@
         <v>0</v>
       </c>
       <c r="K134" s="62" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="L134" s="6"/>
       <c r="M134" s="6"/>
@@ -10067,18 +10074,18 @@
     </row>
     <row r="135" spans="1:14" ht="37.799999999999997">
       <c r="A135" s="11"/>
-      <c r="B135" s="115"/>
+      <c r="B135" s="123"/>
       <c r="C135" s="58" t="str">
         <f>master!C114</f>
         <v>VS Codeによるブランチのマージ</v>
       </c>
-      <c r="D135" s="110" t="s">
+      <c r="D135" s="115" t="s">
+        <v>430</v>
+      </c>
+      <c r="E135" s="116"/>
+      <c r="F135" s="117"/>
+      <c r="G135" s="58" t="s">
         <v>431</v>
-      </c>
-      <c r="E135" s="111"/>
-      <c r="F135" s="112"/>
-      <c r="G135" s="58" t="s">
-        <v>432</v>
       </c>
       <c r="H135" s="59"/>
       <c r="I135" s="60" t="s">
@@ -10088,7 +10095,7 @@
         <v>0</v>
       </c>
       <c r="K135" s="62" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="L135" s="6"/>
       <c r="M135" s="6"/>
@@ -10104,17 +10111,17 @@
         <f>master!C67</f>
         <v>ここから各自で演習を始めましょう。</v>
       </c>
-      <c r="D136" s="110" t="s">
+      <c r="D136" s="115" t="s">
         <v>198</v>
       </c>
-      <c r="E136" s="111"/>
-      <c r="F136" s="112"/>
+      <c r="E136" s="116"/>
+      <c r="F136" s="117"/>
       <c r="G136" s="58" t="s">
         <v>295</v>
       </c>
       <c r="H136" s="59"/>
       <c r="I136" s="60" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="J136" s="61" t="s">
         <v>343</v>
@@ -10126,7 +10133,7 @@
     </row>
     <row r="137" spans="1:14" ht="50.4">
       <c r="A137" s="11"/>
-      <c r="B137" s="122" t="str">
+      <c r="B137" s="112" t="str">
         <f>master!B116</f>
         <v>単体テストとJunitの導入</v>
       </c>
@@ -10134,11 +10141,11 @@
         <f>master!C116</f>
         <v>講義の目的</v>
       </c>
-      <c r="D137" s="104" t="s">
+      <c r="D137" s="109" t="s">
         <v>227</v>
       </c>
-      <c r="E137" s="105"/>
-      <c r="F137" s="106"/>
+      <c r="E137" s="110"/>
+      <c r="F137" s="111"/>
       <c r="G137" s="48" t="s">
         <v>299</v>
       </c>
@@ -10156,14 +10163,14 @@
     </row>
     <row r="138" spans="1:14" ht="25.2">
       <c r="A138" s="11"/>
-      <c r="B138" s="123"/>
+      <c r="B138" s="113"/>
       <c r="C138" s="78" t="str">
         <f>master!C117</f>
         <v>TERASOLUNA 開発手順　 ※再掲</v>
       </c>
-      <c r="D138" s="104"/>
-      <c r="E138" s="105"/>
-      <c r="F138" s="106"/>
+      <c r="D138" s="109"/>
+      <c r="E138" s="110"/>
+      <c r="F138" s="111"/>
       <c r="G138" s="48" t="s">
         <v>300</v>
       </c>
@@ -10181,16 +10188,16 @@
     </row>
     <row r="139" spans="1:14" ht="25.2">
       <c r="A139" s="11"/>
-      <c r="B139" s="124"/>
+      <c r="B139" s="114"/>
       <c r="C139" s="78" t="str">
         <f>master!C118</f>
         <v>V字モデル　 ※再掲</v>
       </c>
-      <c r="D139" s="104" t="s">
+      <c r="D139" s="109" t="s">
         <v>228</v>
       </c>
-      <c r="E139" s="105"/>
-      <c r="F139" s="106"/>
+      <c r="E139" s="110"/>
+      <c r="F139" s="111"/>
       <c r="G139" s="48" t="s">
         <v>300</v>
       </c>
@@ -10208,7 +10215,7 @@
     </row>
     <row r="140" spans="1:14" ht="50.4">
       <c r="A140" s="11"/>
-      <c r="B140" s="122" t="str">
+      <c r="B140" s="112" t="str">
         <f>master!B119</f>
         <v>テストとは</v>
       </c>
@@ -10216,11 +10223,11 @@
         <f>master!C119</f>
         <v>テストとは</v>
       </c>
-      <c r="D140" s="104" t="s">
+      <c r="D140" s="109" t="s">
         <v>229</v>
       </c>
-      <c r="E140" s="105"/>
-      <c r="F140" s="106"/>
+      <c r="E140" s="110"/>
+      <c r="F140" s="111"/>
       <c r="G140" s="48" t="s">
         <v>299</v>
       </c>
@@ -10238,16 +10245,16 @@
     </row>
     <row r="141" spans="1:14" ht="315">
       <c r="A141" s="11"/>
-      <c r="B141" s="123"/>
+      <c r="B141" s="113"/>
       <c r="C141" s="78" t="str">
         <f>master!C120</f>
         <v>テストの目的</v>
       </c>
-      <c r="D141" s="104" t="s">
+      <c r="D141" s="109" t="s">
         <v>230</v>
       </c>
-      <c r="E141" s="105"/>
-      <c r="F141" s="106"/>
+      <c r="E141" s="110"/>
+      <c r="F141" s="111"/>
       <c r="G141" s="48" t="s">
         <v>301</v>
       </c>
@@ -10265,16 +10272,16 @@
     </row>
     <row r="142" spans="1:14" ht="25.2">
       <c r="A142" s="11"/>
-      <c r="B142" s="123"/>
+      <c r="B142" s="113"/>
       <c r="C142" s="78" t="str">
         <f>master!C121</f>
         <v>テストを実施しなかった場合…</v>
       </c>
-      <c r="D142" s="104" t="s">
+      <c r="D142" s="109" t="s">
         <v>231</v>
       </c>
-      <c r="E142" s="105"/>
-      <c r="F142" s="106"/>
+      <c r="E142" s="110"/>
+      <c r="F142" s="111"/>
       <c r="G142" s="48" t="s">
         <v>300</v>
       </c>
@@ -10292,16 +10299,16 @@
     </row>
     <row r="143" spans="1:14" ht="100.8">
       <c r="A143" s="11"/>
-      <c r="B143" s="124"/>
+      <c r="B143" s="114"/>
       <c r="C143" s="78" t="str">
         <f>master!C122</f>
         <v>コラム：テストとデバッグ</v>
       </c>
-      <c r="D143" s="104" t="s">
+      <c r="D143" s="109" t="s">
         <v>232</v>
       </c>
-      <c r="E143" s="105"/>
-      <c r="F143" s="106"/>
+      <c r="E143" s="110"/>
+      <c r="F143" s="111"/>
       <c r="G143" s="48" t="s">
         <v>302</v>
       </c>
@@ -10319,7 +10326,7 @@
     </row>
     <row r="144" spans="1:14" ht="50.4">
       <c r="A144" s="11"/>
-      <c r="B144" s="122" t="str">
+      <c r="B144" s="112" t="str">
         <f>master!B123</f>
         <v>単体テストとは</v>
       </c>
@@ -10327,11 +10334,11 @@
         <f>master!C123</f>
         <v>単体テスト（Unit Test）とは</v>
       </c>
-      <c r="D144" s="104" t="s">
+      <c r="D144" s="109" t="s">
         <v>233</v>
       </c>
-      <c r="E144" s="105"/>
-      <c r="F144" s="106"/>
+      <c r="E144" s="110"/>
+      <c r="F144" s="111"/>
       <c r="G144" s="48" t="s">
         <v>299</v>
       </c>
@@ -10349,14 +10356,14 @@
     </row>
     <row r="145" spans="1:14" ht="25.2">
       <c r="A145" s="11"/>
-      <c r="B145" s="123"/>
+      <c r="B145" s="113"/>
       <c r="C145" s="78" t="str">
         <f>master!C124</f>
         <v xml:space="preserve">V字モデル　– 製造/単体テスト –　※再掲 </v>
       </c>
-      <c r="D145" s="104"/>
-      <c r="E145" s="105"/>
-      <c r="F145" s="106"/>
+      <c r="D145" s="109"/>
+      <c r="E145" s="110"/>
+      <c r="F145" s="111"/>
       <c r="G145" s="48" t="s">
         <v>300</v>
       </c>
@@ -10374,16 +10381,16 @@
     </row>
     <row r="146" spans="1:14" ht="302.39999999999998">
       <c r="A146" s="11"/>
-      <c r="B146" s="123"/>
+      <c r="B146" s="113"/>
       <c r="C146" s="78" t="str">
         <f>master!C125</f>
         <v>テスト設計の流れ</v>
       </c>
-      <c r="D146" s="104" t="s">
+      <c r="D146" s="109" t="s">
         <v>234</v>
       </c>
-      <c r="E146" s="105"/>
-      <c r="F146" s="106"/>
+      <c r="E146" s="110"/>
+      <c r="F146" s="111"/>
       <c r="G146" s="48" t="s">
         <v>303</v>
       </c>
@@ -10401,16 +10408,16 @@
     </row>
     <row r="147" spans="1:14" ht="37.799999999999997">
       <c r="A147" s="11"/>
-      <c r="B147" s="123"/>
+      <c r="B147" s="113"/>
       <c r="C147" s="78" t="str">
         <f>master!C126</f>
         <v>テスト設計の例</v>
       </c>
-      <c r="D147" s="104" t="s">
+      <c r="D147" s="109" t="s">
         <v>235</v>
       </c>
-      <c r="E147" s="105"/>
-      <c r="F147" s="106"/>
+      <c r="E147" s="110"/>
+      <c r="F147" s="111"/>
       <c r="G147" s="48" t="s">
         <v>304</v>
       </c>
@@ -10428,16 +10435,16 @@
     </row>
     <row r="148" spans="1:14" ht="75.599999999999994">
       <c r="A148" s="11"/>
-      <c r="B148" s="123"/>
+      <c r="B148" s="113"/>
       <c r="C148" s="78" t="str">
         <f>master!C127</f>
         <v>単体テスト（Unit Test）とは</v>
       </c>
-      <c r="D148" s="104" t="s">
+      <c r="D148" s="109" t="s">
         <v>236</v>
       </c>
-      <c r="E148" s="105"/>
-      <c r="F148" s="106"/>
+      <c r="E148" s="110"/>
+      <c r="F148" s="111"/>
       <c r="G148" s="48" t="s">
         <v>305</v>
       </c>
@@ -10455,16 +10462,16 @@
     </row>
     <row r="149" spans="1:14" ht="113.4">
       <c r="A149" s="11"/>
-      <c r="B149" s="123"/>
+      <c r="B149" s="113"/>
       <c r="C149" s="78" t="str">
         <f>master!C128</f>
         <v>テスト技法 – ブラックボックステスト技法 –</v>
       </c>
-      <c r="D149" s="104" t="s">
+      <c r="D149" s="109" t="s">
         <v>237</v>
       </c>
-      <c r="E149" s="105"/>
-      <c r="F149" s="106"/>
+      <c r="E149" s="110"/>
+      <c r="F149" s="111"/>
       <c r="G149" s="48" t="s">
         <v>306</v>
       </c>
@@ -10482,16 +10489,16 @@
     </row>
     <row r="150" spans="1:14" ht="201.6">
       <c r="A150" s="11"/>
-      <c r="B150" s="123"/>
+      <c r="B150" s="113"/>
       <c r="C150" s="78" t="str">
         <f>master!C129</f>
         <v>ブラックボックステスト：同値分割法</v>
       </c>
-      <c r="D150" s="104" t="s">
+      <c r="D150" s="109" t="s">
         <v>240</v>
       </c>
-      <c r="E150" s="105"/>
-      <c r="F150" s="106"/>
+      <c r="E150" s="110"/>
+      <c r="F150" s="111"/>
       <c r="G150" s="48" t="s">
         <v>307</v>
       </c>
@@ -10509,16 +10516,16 @@
     </row>
     <row r="151" spans="1:14" ht="113.4">
       <c r="A151" s="11"/>
-      <c r="B151" s="123"/>
+      <c r="B151" s="113"/>
       <c r="C151" s="78" t="str">
         <f>master!C130</f>
         <v>ブラックボックステスト：境界値分析</v>
       </c>
-      <c r="D151" s="104" t="s">
+      <c r="D151" s="109" t="s">
         <v>239</v>
       </c>
-      <c r="E151" s="105"/>
-      <c r="F151" s="106"/>
+      <c r="E151" s="110"/>
+      <c r="F151" s="111"/>
       <c r="G151" s="48" t="s">
         <v>306</v>
       </c>
@@ -10536,16 +10543,16 @@
     </row>
     <row r="152" spans="1:14" ht="176.4">
       <c r="A152" s="11"/>
-      <c r="B152" s="123"/>
+      <c r="B152" s="113"/>
       <c r="C152" s="78" t="str">
         <f>master!C131</f>
         <v>ブラックボックステスト：ディシジョンテーブルテスト</v>
       </c>
-      <c r="D152" s="104" t="s">
+      <c r="D152" s="109" t="s">
         <v>238</v>
       </c>
-      <c r="E152" s="105"/>
-      <c r="F152" s="106"/>
+      <c r="E152" s="110"/>
+      <c r="F152" s="111"/>
       <c r="G152" s="48" t="s">
         <v>308</v>
       </c>
@@ -10563,16 +10570,16 @@
     </row>
     <row r="153" spans="1:14" ht="37.799999999999997">
       <c r="A153" s="11"/>
-      <c r="B153" s="123"/>
+      <c r="B153" s="113"/>
       <c r="C153" s="78" t="str">
         <f>master!C132</f>
         <v>ブラックボックステスト：状態遷移テスト</v>
       </c>
-      <c r="D153" s="104" t="s">
+      <c r="D153" s="109" t="s">
         <v>241</v>
       </c>
-      <c r="E153" s="105"/>
-      <c r="F153" s="106"/>
+      <c r="E153" s="110"/>
+      <c r="F153" s="111"/>
       <c r="G153" s="48" t="s">
         <v>304</v>
       </c>
@@ -10590,16 +10597,16 @@
     </row>
     <row r="154" spans="1:14" ht="88.2">
       <c r="A154" s="11"/>
-      <c r="B154" s="123"/>
+      <c r="B154" s="113"/>
       <c r="C154" s="78" t="str">
         <f>master!C133</f>
         <v>テスト技法 – ホワイトボックステスト技法 –</v>
       </c>
-      <c r="D154" s="104" t="s">
+      <c r="D154" s="109" t="s">
         <v>242</v>
       </c>
-      <c r="E154" s="105"/>
-      <c r="F154" s="106"/>
+      <c r="E154" s="110"/>
+      <c r="F154" s="111"/>
       <c r="G154" s="48" t="s">
         <v>309</v>
       </c>
@@ -10617,16 +10624,16 @@
     </row>
     <row r="155" spans="1:14" ht="151.19999999999999">
       <c r="A155" s="11"/>
-      <c r="B155" s="123"/>
+      <c r="B155" s="113"/>
       <c r="C155" s="78" t="str">
         <f>master!C134</f>
         <v>ホワイトボックステストの評価基準</v>
       </c>
-      <c r="D155" s="104" t="s">
+      <c r="D155" s="109" t="s">
         <v>243</v>
       </c>
-      <c r="E155" s="105"/>
-      <c r="F155" s="106"/>
+      <c r="E155" s="110"/>
+      <c r="F155" s="111"/>
       <c r="G155" s="48" t="s">
         <v>310</v>
       </c>
@@ -10644,16 +10651,16 @@
     </row>
     <row r="156" spans="1:14" ht="37.799999999999997">
       <c r="A156" s="11"/>
-      <c r="B156" s="123"/>
+      <c r="B156" s="113"/>
       <c r="C156" s="78" t="str">
         <f>master!C135</f>
         <v>ホワイトボックステスト：ステートメントテスト</v>
       </c>
-      <c r="D156" s="104" t="s">
+      <c r="D156" s="109" t="s">
         <v>244</v>
       </c>
-      <c r="E156" s="105"/>
-      <c r="F156" s="106"/>
+      <c r="E156" s="110"/>
+      <c r="F156" s="111"/>
       <c r="G156" s="48" t="s">
         <v>304</v>
       </c>
@@ -10671,16 +10678,16 @@
     </row>
     <row r="157" spans="1:14" ht="37.799999999999997">
       <c r="A157" s="11"/>
-      <c r="B157" s="123"/>
+      <c r="B157" s="113"/>
       <c r="C157" s="78" t="str">
         <f>master!C136</f>
         <v>ホワイトボックステスト：ブランチテスト</v>
       </c>
-      <c r="D157" s="104" t="s">
+      <c r="D157" s="109" t="s">
         <v>245</v>
       </c>
-      <c r="E157" s="105"/>
-      <c r="F157" s="106"/>
+      <c r="E157" s="110"/>
+      <c r="F157" s="111"/>
       <c r="G157" s="48" t="s">
         <v>304</v>
       </c>
@@ -10698,16 +10705,16 @@
     </row>
     <row r="158" spans="1:14" ht="37.799999999999997">
       <c r="A158" s="11"/>
-      <c r="B158" s="123"/>
+      <c r="B158" s="113"/>
       <c r="C158" s="78" t="str">
         <f>master!C137</f>
         <v>ホワイトボックステスト：コンディションテスト</v>
       </c>
-      <c r="D158" s="104" t="s">
+      <c r="D158" s="109" t="s">
         <v>246</v>
       </c>
-      <c r="E158" s="105"/>
-      <c r="F158" s="106"/>
+      <c r="E158" s="110"/>
+      <c r="F158" s="111"/>
       <c r="G158" s="48" t="s">
         <v>304</v>
       </c>
@@ -10725,16 +10732,16 @@
     </row>
     <row r="159" spans="1:14" ht="37.799999999999997">
       <c r="A159" s="11"/>
-      <c r="B159" s="123"/>
+      <c r="B159" s="113"/>
       <c r="C159" s="78" t="str">
         <f>master!C138</f>
         <v>テスト技法 – 経験ベースの技法 –</v>
       </c>
-      <c r="D159" s="104" t="s">
+      <c r="D159" s="109" t="s">
         <v>247</v>
       </c>
-      <c r="E159" s="105"/>
-      <c r="F159" s="106"/>
+      <c r="E159" s="110"/>
+      <c r="F159" s="111"/>
       <c r="G159" s="48" t="s">
         <v>304</v>
       </c>
@@ -10752,16 +10759,16 @@
     </row>
     <row r="160" spans="1:14" ht="100.8">
       <c r="A160" s="11"/>
-      <c r="B160" s="123"/>
+      <c r="B160" s="113"/>
       <c r="C160" s="78" t="str">
         <f>master!C139</f>
         <v>スタブとドライバ</v>
       </c>
-      <c r="D160" s="104" t="s">
+      <c r="D160" s="109" t="s">
         <v>248</v>
       </c>
-      <c r="E160" s="105"/>
-      <c r="F160" s="106"/>
+      <c r="E160" s="110"/>
+      <c r="F160" s="111"/>
       <c r="G160" s="48" t="s">
         <v>302</v>
       </c>
@@ -10779,16 +10786,16 @@
     </row>
     <row r="161" spans="1:14" ht="75.599999999999994">
       <c r="A161" s="11"/>
-      <c r="B161" s="124"/>
+      <c r="B161" s="114"/>
       <c r="C161" s="78" t="str">
         <f>master!C140</f>
         <v>スタブとモック</v>
       </c>
-      <c r="D161" s="104" t="s">
+      <c r="D161" s="109" t="s">
         <v>249</v>
       </c>
-      <c r="E161" s="105"/>
-      <c r="F161" s="106"/>
+      <c r="E161" s="110"/>
+      <c r="F161" s="111"/>
       <c r="G161" s="48" t="s">
         <v>305</v>
       </c>
@@ -10806,7 +10813,7 @@
     </row>
     <row r="162" spans="1:14" ht="37.799999999999997">
       <c r="A162" s="11"/>
-      <c r="B162" s="122" t="str">
+      <c r="B162" s="112" t="str">
         <f>master!B141</f>
         <v>JUnit</v>
       </c>
@@ -10814,11 +10821,11 @@
         <f>master!C141</f>
         <v>JUnitとは</v>
       </c>
-      <c r="D162" s="104" t="s">
+      <c r="D162" s="109" t="s">
         <v>250</v>
       </c>
-      <c r="E162" s="105"/>
-      <c r="F162" s="106"/>
+      <c r="E162" s="110"/>
+      <c r="F162" s="111"/>
       <c r="G162" s="48" t="s">
         <v>304</v>
       </c>
@@ -10836,14 +10843,14 @@
     </row>
     <row r="163" spans="1:14" ht="25.2">
       <c r="A163" s="11"/>
-      <c r="B163" s="124"/>
+      <c r="B163" s="114"/>
       <c r="C163" s="78" t="str">
         <f>master!C142</f>
         <v>参考文献</v>
       </c>
-      <c r="D163" s="104"/>
-      <c r="E163" s="105"/>
-      <c r="F163" s="106"/>
+      <c r="D163" s="109"/>
+      <c r="E163" s="110"/>
+      <c r="F163" s="111"/>
       <c r="G163" s="48" t="s">
         <v>300</v>
       </c>
@@ -10869,11 +10876,11 @@
         <f>master!C67</f>
         <v>ここから各自で演習を始めましょう。</v>
       </c>
-      <c r="D164" s="110" t="s">
+      <c r="D164" s="115" t="s">
         <v>251</v>
       </c>
-      <c r="E164" s="111"/>
-      <c r="F164" s="112"/>
+      <c r="E164" s="116"/>
+      <c r="F164" s="117"/>
       <c r="G164" s="58" t="s">
         <v>42</v>
       </c>
@@ -10891,7 +10898,7 @@
     </row>
     <row r="165" spans="1:14" ht="25.2">
       <c r="A165" s="11"/>
-      <c r="B165" s="116" t="str">
+      <c r="B165" s="118" t="str">
         <f>master!B144</f>
         <v>課題2の導入</v>
       </c>
@@ -10899,11 +10906,11 @@
         <f>master!C144</f>
         <v>演習課題の概要</v>
       </c>
-      <c r="D165" s="110" t="s">
+      <c r="D165" s="115" t="s">
         <v>267</v>
       </c>
-      <c r="E165" s="111"/>
-      <c r="F165" s="112"/>
+      <c r="E165" s="116"/>
+      <c r="F165" s="117"/>
       <c r="G165" s="58" t="s">
         <v>311</v>
       </c>
@@ -10921,16 +10928,16 @@
     </row>
     <row r="166" spans="1:14" ht="138.6">
       <c r="A166" s="11"/>
-      <c r="B166" s="118"/>
+      <c r="B166" s="119"/>
       <c r="C166" s="58" t="str">
         <f>master!C145</f>
         <v>[構造理解] Webアプリケーションで必要なもの  ※再掲</v>
       </c>
-      <c r="D166" s="110" t="s">
+      <c r="D166" s="115" t="s">
         <v>268</v>
       </c>
-      <c r="E166" s="111"/>
-      <c r="F166" s="112"/>
+      <c r="E166" s="116"/>
+      <c r="F166" s="117"/>
       <c r="G166" s="58" t="s">
         <v>312</v>
       </c>
@@ -10948,16 +10955,16 @@
     </row>
     <row r="167" spans="1:14" ht="50.4">
       <c r="A167" s="11"/>
-      <c r="B167" s="118"/>
+      <c r="B167" s="119"/>
       <c r="C167" s="58" t="str">
         <f>master!C146</f>
         <v>テストクラスを作成する単位</v>
       </c>
-      <c r="D167" s="110" t="s">
+      <c r="D167" s="115" t="s">
         <v>269</v>
       </c>
-      <c r="E167" s="111"/>
-      <c r="F167" s="112"/>
+      <c r="E167" s="116"/>
+      <c r="F167" s="117"/>
       <c r="G167" s="58" t="s">
         <v>313</v>
       </c>
@@ -10975,16 +10982,16 @@
     </row>
     <row r="168" spans="1:14" ht="113.4">
       <c r="A168" s="11"/>
-      <c r="B168" s="117"/>
+      <c r="B168" s="120"/>
       <c r="C168" s="58" t="str">
         <f>master!C147</f>
         <v>JUnitで単体テスト</v>
       </c>
-      <c r="D168" s="110" t="s">
+      <c r="D168" s="115" t="s">
         <v>270</v>
       </c>
-      <c r="E168" s="111"/>
-      <c r="F168" s="112"/>
+      <c r="E168" s="116"/>
+      <c r="F168" s="117"/>
       <c r="G168" s="58" t="s">
         <v>314</v>
       </c>
@@ -11002,7 +11009,7 @@
     </row>
     <row r="169" spans="1:14" ht="25.2">
       <c r="A169" s="11"/>
-      <c r="B169" s="116" t="str">
+      <c r="B169" s="118" t="str">
         <f>master!B148</f>
         <v>ハンズオン</v>
       </c>
@@ -11010,11 +11017,11 @@
         <f>master!C148</f>
         <v>バイブコーディングで単体テスト – はじめに</v>
       </c>
-      <c r="D169" s="110" t="s">
+      <c r="D169" s="115" t="s">
         <v>271</v>
       </c>
-      <c r="E169" s="111"/>
-      <c r="F169" s="112"/>
+      <c r="E169" s="116"/>
+      <c r="F169" s="117"/>
       <c r="G169" s="58" t="s">
         <v>311</v>
       </c>
@@ -11032,16 +11039,16 @@
     </row>
     <row r="170" spans="1:14" ht="50.4">
       <c r="A170" s="11"/>
-      <c r="B170" s="118"/>
+      <c r="B170" s="119"/>
       <c r="C170" s="58" t="str">
         <f>master!C149</f>
         <v>バイブコーディング単体テスト①テスト項目表を作る</v>
       </c>
-      <c r="D170" s="110" t="s">
+      <c r="D170" s="115" t="s">
         <v>272</v>
       </c>
-      <c r="E170" s="111"/>
-      <c r="F170" s="112"/>
+      <c r="E170" s="116"/>
+      <c r="F170" s="117"/>
       <c r="G170" s="58" t="s">
         <v>313</v>
       </c>
@@ -11059,13 +11066,13 @@
     </row>
     <row r="171" spans="1:14" ht="88.2">
       <c r="A171" s="11"/>
-      <c r="B171" s="118"/>
+      <c r="B171" s="119"/>
       <c r="C171" s="58"/>
-      <c r="D171" s="110" t="s">
+      <c r="D171" s="115" t="s">
         <v>183</v>
       </c>
-      <c r="E171" s="111"/>
-      <c r="F171" s="112"/>
+      <c r="E171" s="116"/>
+      <c r="F171" s="117"/>
       <c r="G171" s="58" t="s">
         <v>315</v>
       </c>
@@ -11083,16 +11090,16 @@
     </row>
     <row r="172" spans="1:14" ht="50.4">
       <c r="A172" s="11"/>
-      <c r="B172" s="118"/>
+      <c r="B172" s="119"/>
       <c r="C172" s="76" t="str">
         <f>master!C150</f>
         <v>バイブコーディング単体テスト②Repositoryのテストを作る</v>
       </c>
-      <c r="D172" s="110" t="s">
+      <c r="D172" s="115" t="s">
         <v>273</v>
       </c>
-      <c r="E172" s="111"/>
-      <c r="F172" s="112"/>
+      <c r="E172" s="116"/>
+      <c r="F172" s="117"/>
       <c r="G172" s="58" t="s">
         <v>313</v>
       </c>
@@ -11110,13 +11117,13 @@
     </row>
     <row r="173" spans="1:14" ht="88.2">
       <c r="A173" s="11"/>
-      <c r="B173" s="118"/>
+      <c r="B173" s="119"/>
       <c r="C173" s="77"/>
-      <c r="D173" s="110" t="s">
+      <c r="D173" s="115" t="s">
         <v>183</v>
       </c>
-      <c r="E173" s="111"/>
-      <c r="F173" s="112"/>
+      <c r="E173" s="116"/>
+      <c r="F173" s="117"/>
       <c r="G173" s="58" t="s">
         <v>315</v>
       </c>
@@ -11134,16 +11141,16 @@
     </row>
     <row r="174" spans="1:14" ht="138.6">
       <c r="A174" s="11"/>
-      <c r="B174" s="118"/>
+      <c r="B174" s="119"/>
       <c r="C174" s="58" t="str">
         <f>master!C151</f>
         <v>[解説] Repositoryのテストクラス（抜粋）</v>
       </c>
-      <c r="D174" s="110" t="s">
+      <c r="D174" s="115" t="s">
         <v>275</v>
       </c>
-      <c r="E174" s="111"/>
-      <c r="F174" s="112"/>
+      <c r="E174" s="116"/>
+      <c r="F174" s="117"/>
       <c r="G174" s="58" t="s">
         <v>312</v>
       </c>
@@ -11161,16 +11168,16 @@
     </row>
     <row r="175" spans="1:14" ht="50.4">
       <c r="A175" s="11"/>
-      <c r="B175" s="118"/>
+      <c r="B175" s="119"/>
       <c r="C175" s="76" t="str">
         <f>master!C152</f>
         <v>バイブコーディング単体テスト③Serviceのテストを作る</v>
       </c>
-      <c r="D175" s="110" t="s">
+      <c r="D175" s="115" t="s">
         <v>273</v>
       </c>
-      <c r="E175" s="111"/>
-      <c r="F175" s="112"/>
+      <c r="E175" s="116"/>
+      <c r="F175" s="117"/>
       <c r="G175" s="58" t="s">
         <v>313</v>
       </c>
@@ -11188,13 +11195,13 @@
     </row>
     <row r="176" spans="1:14" ht="88.2">
       <c r="A176" s="11"/>
-      <c r="B176" s="118"/>
+      <c r="B176" s="119"/>
       <c r="C176" s="77"/>
-      <c r="D176" s="110" t="s">
+      <c r="D176" s="115" t="s">
         <v>183</v>
       </c>
-      <c r="E176" s="111"/>
-      <c r="F176" s="112"/>
+      <c r="E176" s="116"/>
+      <c r="F176" s="117"/>
       <c r="G176" s="58" t="s">
         <v>315</v>
       </c>
@@ -11212,16 +11219,16 @@
     </row>
     <row r="177" spans="1:14" ht="138.6">
       <c r="A177" s="11"/>
-      <c r="B177" s="118"/>
+      <c r="B177" s="119"/>
       <c r="C177" s="58" t="str">
         <f>master!C153</f>
         <v>[解説] Serviceのテストクラス（抜粋）</v>
       </c>
-      <c r="D177" s="110" t="s">
+      <c r="D177" s="115" t="s">
         <v>274</v>
       </c>
-      <c r="E177" s="111"/>
-      <c r="F177" s="112"/>
+      <c r="E177" s="116"/>
+      <c r="F177" s="117"/>
       <c r="G177" s="58" t="s">
         <v>312</v>
       </c>
@@ -11239,16 +11246,16 @@
     </row>
     <row r="178" spans="1:14" ht="50.4">
       <c r="A178" s="11"/>
-      <c r="B178" s="118"/>
+      <c r="B178" s="119"/>
       <c r="C178" s="76" t="str">
         <f>master!C154</f>
         <v>バイブコーディング単体テスト④Controllerのテストを作る</v>
       </c>
-      <c r="D178" s="110" t="s">
+      <c r="D178" s="115" t="s">
         <v>273</v>
       </c>
-      <c r="E178" s="111"/>
-      <c r="F178" s="112"/>
+      <c r="E178" s="116"/>
+      <c r="F178" s="117"/>
       <c r="G178" s="58" t="s">
         <v>313</v>
       </c>
@@ -11266,13 +11273,13 @@
     </row>
     <row r="179" spans="1:14" ht="88.2">
       <c r="A179" s="11"/>
-      <c r="B179" s="118"/>
+      <c r="B179" s="119"/>
       <c r="C179" s="77"/>
-      <c r="D179" s="110" t="s">
+      <c r="D179" s="115" t="s">
         <v>183</v>
       </c>
-      <c r="E179" s="111"/>
-      <c r="F179" s="112"/>
+      <c r="E179" s="116"/>
+      <c r="F179" s="117"/>
       <c r="G179" s="58" t="s">
         <v>315</v>
       </c>
@@ -11290,16 +11297,16 @@
     </row>
     <row r="180" spans="1:14" ht="163.80000000000001">
       <c r="A180" s="11"/>
-      <c r="B180" s="117"/>
+      <c r="B180" s="120"/>
       <c r="C180" s="58" t="str">
         <f>master!C155</f>
         <v>[解説] Controllerのテストクラス（抜粋）</v>
       </c>
-      <c r="D180" s="110" t="s">
+      <c r="D180" s="115" t="s">
         <v>276</v>
       </c>
-      <c r="E180" s="111"/>
-      <c r="F180" s="112"/>
+      <c r="E180" s="116"/>
+      <c r="F180" s="117"/>
       <c r="G180" s="58" t="s">
         <v>316</v>
       </c>
@@ -11317,7 +11324,7 @@
     </row>
     <row r="181" spans="1:14" ht="165" customHeight="1">
       <c r="A181" s="11"/>
-      <c r="B181" s="116" t="str">
+      <c r="B181" s="118" t="str">
         <f>master!B156</f>
         <v>課題2の実施</v>
       </c>
@@ -11325,11 +11332,11 @@
         <f>master!C156</f>
         <v>ここから各自で演習を始めましょう。</v>
       </c>
-      <c r="D181" s="110" t="s">
+      <c r="D181" s="115" t="s">
         <v>277</v>
       </c>
-      <c r="E181" s="111"/>
-      <c r="F181" s="112"/>
+      <c r="E181" s="116"/>
+      <c r="F181" s="117"/>
       <c r="G181" s="58" t="s">
         <v>316</v>
       </c>
@@ -11347,16 +11354,16 @@
     </row>
     <row r="182" spans="1:14" ht="151.19999999999999">
       <c r="A182" s="11"/>
-      <c r="B182" s="117"/>
+      <c r="B182" s="120"/>
       <c r="C182" s="58" t="str">
         <f>master!C157</f>
         <v>[終了条件] 講師配布のテストプログラム(JUnit)が成功すること</v>
       </c>
-      <c r="D182" s="110" t="s">
+      <c r="D182" s="115" t="s">
         <v>342</v>
       </c>
-      <c r="E182" s="111"/>
-      <c r="F182" s="112"/>
+      <c r="E182" s="116"/>
+      <c r="F182" s="117"/>
       <c r="G182" s="58" t="s">
         <v>341</v>
       </c>
@@ -11368,7 +11375,7 @@
         <v>343</v>
       </c>
       <c r="K182" s="62" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="L182" s="6"/>
       <c r="M182" s="6"/>
@@ -11376,7 +11383,7 @@
     </row>
     <row r="183" spans="1:14" ht="163.80000000000001">
       <c r="A183" s="11"/>
-      <c r="B183" s="116" t="str">
+      <c r="B183" s="118" t="str">
         <f>master!B159</f>
         <v>追加課題</v>
       </c>
@@ -11384,11 +11391,11 @@
         <f>master!C159</f>
         <v>演習課題の概要</v>
       </c>
-      <c r="D183" s="110" t="s">
+      <c r="D183" s="115" t="s">
         <v>279</v>
       </c>
-      <c r="E183" s="111"/>
-      <c r="F183" s="112"/>
+      <c r="E183" s="116"/>
+      <c r="F183" s="117"/>
       <c r="G183" s="58" t="s">
         <v>337</v>
       </c>
@@ -11400,7 +11407,7 @@
         <v>343</v>
       </c>
       <c r="K183" s="62" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="L183" s="6"/>
       <c r="M183" s="6"/>
@@ -11408,16 +11415,16 @@
     </row>
     <row r="184" spans="1:14" ht="25.2">
       <c r="A184" s="11"/>
-      <c r="B184" s="118"/>
+      <c r="B184" s="119"/>
       <c r="C184" s="58" t="str">
         <f>master!C160</f>
         <v>追加課題①：送料の表示機能</v>
       </c>
-      <c r="D184" s="110" t="s">
+      <c r="D184" s="115" t="s">
         <v>281</v>
       </c>
-      <c r="E184" s="111"/>
-      <c r="F184" s="112"/>
+      <c r="E184" s="116"/>
+      <c r="F184" s="117"/>
       <c r="G184" s="58" t="s">
         <v>338</v>
       </c>
@@ -11429,7 +11436,7 @@
         <v>343</v>
       </c>
       <c r="K184" s="62" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="L184" s="6"/>
       <c r="M184" s="6"/>
@@ -11437,16 +11444,16 @@
     </row>
     <row r="185" spans="1:14" ht="25.2">
       <c r="A185" s="11"/>
-      <c r="B185" s="118"/>
+      <c r="B185" s="119"/>
       <c r="C185" s="58" t="str">
         <f>master!C161</f>
         <v>追加課題②：クーポン機能</v>
       </c>
-      <c r="D185" s="110" t="s">
+      <c r="D185" s="115" t="s">
         <v>281</v>
       </c>
-      <c r="E185" s="111"/>
-      <c r="F185" s="112"/>
+      <c r="E185" s="116"/>
+      <c r="F185" s="117"/>
       <c r="G185" s="58" t="s">
         <v>338</v>
       </c>
@@ -11458,7 +11465,7 @@
         <v>343</v>
       </c>
       <c r="K185" s="62" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="L185" s="6"/>
       <c r="M185" s="6"/>
@@ -11466,16 +11473,16 @@
     </row>
     <row r="186" spans="1:14" ht="25.2">
       <c r="A186" s="11"/>
-      <c r="B186" s="117"/>
+      <c r="B186" s="120"/>
       <c r="C186" s="58" t="str">
         <f>master!C162</f>
         <v>追加課題③：ユーザーアカウント機能</v>
       </c>
-      <c r="D186" s="110" t="s">
+      <c r="D186" s="115" t="s">
         <v>281</v>
       </c>
-      <c r="E186" s="111"/>
-      <c r="F186" s="112"/>
+      <c r="E186" s="116"/>
+      <c r="F186" s="117"/>
       <c r="G186" s="58" t="s">
         <v>338</v>
       </c>
@@ -11487,7 +11494,7 @@
         <v>343</v>
       </c>
       <c r="K186" s="62" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="L186" s="6"/>
       <c r="M186" s="6"/>
@@ -11495,7 +11502,7 @@
     </row>
     <row r="187" spans="1:14" ht="176.4">
       <c r="A187" s="11"/>
-      <c r="B187" s="116" t="str">
+      <c r="B187" s="118" t="str">
         <f>master!B164</f>
         <v>課題の振り返り</v>
       </c>
@@ -11503,13 +11510,13 @@
         <f>master!C164</f>
         <v>サンプルのAPとの自分のAPとの比較</v>
       </c>
-      <c r="D187" s="110" t="s">
+      <c r="D187" s="115" t="s">
         <v>339</v>
       </c>
-      <c r="E187" s="111"/>
-      <c r="F187" s="112"/>
+      <c r="E187" s="116"/>
+      <c r="F187" s="117"/>
       <c r="G187" s="58" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="H187" s="59"/>
       <c r="I187" s="60" t="s">
@@ -11525,18 +11532,18 @@
     </row>
     <row r="188" spans="1:14" ht="63">
       <c r="A188" s="11"/>
-      <c r="B188" s="117"/>
+      <c r="B188" s="120"/>
       <c r="C188" s="58" t="str">
         <f>master!C165</f>
         <v>レポートの作成</v>
       </c>
-      <c r="D188" s="110" t="s">
+      <c r="D188" s="115" t="s">
         <v>340</v>
       </c>
-      <c r="E188" s="111"/>
-      <c r="F188" s="112"/>
+      <c r="E188" s="116"/>
+      <c r="F188" s="117"/>
       <c r="G188" s="58" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="H188" s="59"/>
       <c r="I188" s="60" t="s">
@@ -11556,6 +11563,185 @@
     <row r="190" spans="1:14" ht="15" customHeight="1"/>
   </sheetData>
   <mergeCells count="203">
+    <mergeCell ref="B119:B123"/>
+    <mergeCell ref="B113:B118"/>
+    <mergeCell ref="B108:B112"/>
+    <mergeCell ref="B99:B107"/>
+    <mergeCell ref="B94:B98"/>
+    <mergeCell ref="B91:B93"/>
+    <mergeCell ref="D124:F124"/>
+    <mergeCell ref="D135:F135"/>
+    <mergeCell ref="D133:F133"/>
+    <mergeCell ref="D131:F131"/>
+    <mergeCell ref="D132:F132"/>
+    <mergeCell ref="D129:F129"/>
+    <mergeCell ref="D130:F130"/>
+    <mergeCell ref="D127:F127"/>
+    <mergeCell ref="D128:F128"/>
+    <mergeCell ref="D125:F125"/>
+    <mergeCell ref="D126:F126"/>
+    <mergeCell ref="D134:F134"/>
+    <mergeCell ref="B132:B135"/>
+    <mergeCell ref="B127:B131"/>
+    <mergeCell ref="B124:B126"/>
+    <mergeCell ref="D108:F108"/>
+    <mergeCell ref="D121:F121"/>
+    <mergeCell ref="D92:F92"/>
+    <mergeCell ref="D93:F93"/>
+    <mergeCell ref="D94:F94"/>
+    <mergeCell ref="D95:F95"/>
+    <mergeCell ref="D96:F96"/>
+    <mergeCell ref="D97:F97"/>
+    <mergeCell ref="D98:F98"/>
+    <mergeCell ref="D100:F100"/>
+    <mergeCell ref="D122:F122"/>
+    <mergeCell ref="D186:F186"/>
+    <mergeCell ref="D185:F185"/>
+    <mergeCell ref="D188:F188"/>
+    <mergeCell ref="B187:B188"/>
+    <mergeCell ref="D170:F170"/>
+    <mergeCell ref="D172:F172"/>
+    <mergeCell ref="D175:F175"/>
+    <mergeCell ref="D176:F176"/>
+    <mergeCell ref="D178:F178"/>
+    <mergeCell ref="D179:F179"/>
+    <mergeCell ref="B183:B186"/>
+    <mergeCell ref="D182:F182"/>
+    <mergeCell ref="B181:B182"/>
+    <mergeCell ref="D162:F162"/>
+    <mergeCell ref="D163:F163"/>
+    <mergeCell ref="D21:F21"/>
+    <mergeCell ref="D35:F35"/>
+    <mergeCell ref="D22:F22"/>
+    <mergeCell ref="D28:F28"/>
+    <mergeCell ref="D23:F23"/>
+    <mergeCell ref="D25:F25"/>
+    <mergeCell ref="D27:F27"/>
+    <mergeCell ref="D34:F34"/>
+    <mergeCell ref="D24:F24"/>
+    <mergeCell ref="D26:F26"/>
+    <mergeCell ref="D29:F29"/>
+    <mergeCell ref="D30:F30"/>
+    <mergeCell ref="D31:F31"/>
+    <mergeCell ref="D32:F32"/>
+    <mergeCell ref="D33:F33"/>
+    <mergeCell ref="D46:F46"/>
+    <mergeCell ref="D47:F47"/>
+    <mergeCell ref="D48:F48"/>
+    <mergeCell ref="D54:F54"/>
+    <mergeCell ref="D36:F36"/>
+    <mergeCell ref="D91:F91"/>
+    <mergeCell ref="D76:F76"/>
+    <mergeCell ref="I19:J19"/>
+    <mergeCell ref="H19:H20"/>
+    <mergeCell ref="B4:E4"/>
+    <mergeCell ref="B5:K5"/>
+    <mergeCell ref="D19:F20"/>
+    <mergeCell ref="G19:G20"/>
+    <mergeCell ref="B19:B20"/>
+    <mergeCell ref="C19:C20"/>
+    <mergeCell ref="K19:K20"/>
+    <mergeCell ref="D7:E7"/>
+    <mergeCell ref="B22:B27"/>
+    <mergeCell ref="B28:B35"/>
+    <mergeCell ref="B36:B54"/>
+    <mergeCell ref="D49:F49"/>
+    <mergeCell ref="D50:F50"/>
+    <mergeCell ref="D51:F51"/>
+    <mergeCell ref="D52:F52"/>
+    <mergeCell ref="D53:F53"/>
+    <mergeCell ref="D37:F37"/>
+    <mergeCell ref="D38:F38"/>
+    <mergeCell ref="D39:F39"/>
+    <mergeCell ref="D40:F40"/>
+    <mergeCell ref="D41:F41"/>
+    <mergeCell ref="D42:F42"/>
+    <mergeCell ref="D43:F43"/>
+    <mergeCell ref="D44:F44"/>
+    <mergeCell ref="D45:F45"/>
+    <mergeCell ref="B55:B57"/>
+    <mergeCell ref="D69:F69"/>
+    <mergeCell ref="D70:F70"/>
+    <mergeCell ref="D71:F71"/>
+    <mergeCell ref="D72:F72"/>
+    <mergeCell ref="D62:F62"/>
+    <mergeCell ref="D56:F56"/>
+    <mergeCell ref="D57:F57"/>
+    <mergeCell ref="D58:F58"/>
+    <mergeCell ref="D59:F59"/>
+    <mergeCell ref="D66:F66"/>
+    <mergeCell ref="D67:F67"/>
+    <mergeCell ref="D60:F60"/>
+    <mergeCell ref="D61:F61"/>
+    <mergeCell ref="D63:F63"/>
+    <mergeCell ref="D64:F64"/>
+    <mergeCell ref="D65:F65"/>
+    <mergeCell ref="D68:F68"/>
+    <mergeCell ref="D55:F55"/>
+    <mergeCell ref="B62:B70"/>
+    <mergeCell ref="B58:B61"/>
+    <mergeCell ref="D78:F78"/>
+    <mergeCell ref="D80:F80"/>
+    <mergeCell ref="D74:F74"/>
+    <mergeCell ref="D85:F85"/>
+    <mergeCell ref="D90:F90"/>
+    <mergeCell ref="D82:F82"/>
+    <mergeCell ref="D83:F83"/>
+    <mergeCell ref="B71:B90"/>
+    <mergeCell ref="D84:F84"/>
+    <mergeCell ref="D86:F86"/>
+    <mergeCell ref="D87:F87"/>
+    <mergeCell ref="D88:F88"/>
+    <mergeCell ref="D89:F89"/>
+    <mergeCell ref="D77:F77"/>
+    <mergeCell ref="D79:F79"/>
+    <mergeCell ref="D81:F81"/>
+    <mergeCell ref="D75:F75"/>
+    <mergeCell ref="D73:F73"/>
+    <mergeCell ref="D138:F138"/>
+    <mergeCell ref="D137:F137"/>
+    <mergeCell ref="D111:F111"/>
+    <mergeCell ref="D110:F110"/>
+    <mergeCell ref="D109:F109"/>
+    <mergeCell ref="D112:F112"/>
+    <mergeCell ref="D103:F103"/>
+    <mergeCell ref="D99:F99"/>
+    <mergeCell ref="D123:F123"/>
+    <mergeCell ref="D136:F136"/>
+    <mergeCell ref="D101:F101"/>
+    <mergeCell ref="D102:F102"/>
+    <mergeCell ref="D104:F104"/>
+    <mergeCell ref="D105:F105"/>
+    <mergeCell ref="D106:F106"/>
+    <mergeCell ref="D107:F107"/>
+    <mergeCell ref="D120:F120"/>
+    <mergeCell ref="D119:F119"/>
+    <mergeCell ref="D118:F118"/>
+    <mergeCell ref="D117:F117"/>
+    <mergeCell ref="D116:F116"/>
+    <mergeCell ref="D115:F115"/>
+    <mergeCell ref="D114:F114"/>
+    <mergeCell ref="D113:F113"/>
+    <mergeCell ref="D141:F141"/>
+    <mergeCell ref="D142:F142"/>
+    <mergeCell ref="D144:F144"/>
+    <mergeCell ref="D145:F145"/>
+    <mergeCell ref="D146:F146"/>
+    <mergeCell ref="D147:F147"/>
+    <mergeCell ref="D148:F148"/>
+    <mergeCell ref="D160:F160"/>
+    <mergeCell ref="D161:F161"/>
+    <mergeCell ref="D143:F143"/>
+    <mergeCell ref="D155:F155"/>
+    <mergeCell ref="D156:F156"/>
+    <mergeCell ref="D157:F157"/>
+    <mergeCell ref="D158:F158"/>
+    <mergeCell ref="D159:F159"/>
+    <mergeCell ref="D154:F154"/>
+    <mergeCell ref="D153:F153"/>
+    <mergeCell ref="D149:F149"/>
+    <mergeCell ref="D150:F150"/>
+    <mergeCell ref="D151:F151"/>
     <mergeCell ref="D152:F152"/>
     <mergeCell ref="B137:B139"/>
     <mergeCell ref="B162:B163"/>
@@ -11580,185 +11766,6 @@
     <mergeCell ref="B144:B161"/>
     <mergeCell ref="D139:F139"/>
     <mergeCell ref="D140:F140"/>
-    <mergeCell ref="D141:F141"/>
-    <mergeCell ref="D142:F142"/>
-    <mergeCell ref="D144:F144"/>
-    <mergeCell ref="D145:F145"/>
-    <mergeCell ref="D146:F146"/>
-    <mergeCell ref="D147:F147"/>
-    <mergeCell ref="D148:F148"/>
-    <mergeCell ref="D160:F160"/>
-    <mergeCell ref="D161:F161"/>
-    <mergeCell ref="D143:F143"/>
-    <mergeCell ref="D155:F155"/>
-    <mergeCell ref="D156:F156"/>
-    <mergeCell ref="D157:F157"/>
-    <mergeCell ref="D158:F158"/>
-    <mergeCell ref="D159:F159"/>
-    <mergeCell ref="D154:F154"/>
-    <mergeCell ref="D153:F153"/>
-    <mergeCell ref="D149:F149"/>
-    <mergeCell ref="D150:F150"/>
-    <mergeCell ref="D151:F151"/>
-    <mergeCell ref="D138:F138"/>
-    <mergeCell ref="D137:F137"/>
-    <mergeCell ref="D111:F111"/>
-    <mergeCell ref="D110:F110"/>
-    <mergeCell ref="D109:F109"/>
-    <mergeCell ref="D112:F112"/>
-    <mergeCell ref="D103:F103"/>
-    <mergeCell ref="D99:F99"/>
-    <mergeCell ref="D123:F123"/>
-    <mergeCell ref="D136:F136"/>
-    <mergeCell ref="D101:F101"/>
-    <mergeCell ref="D102:F102"/>
-    <mergeCell ref="D104:F104"/>
-    <mergeCell ref="D105:F105"/>
-    <mergeCell ref="D106:F106"/>
-    <mergeCell ref="D107:F107"/>
-    <mergeCell ref="D78:F78"/>
-    <mergeCell ref="D80:F80"/>
-    <mergeCell ref="D74:F74"/>
-    <mergeCell ref="D85:F85"/>
-    <mergeCell ref="D90:F90"/>
-    <mergeCell ref="D82:F82"/>
-    <mergeCell ref="D83:F83"/>
-    <mergeCell ref="B71:B90"/>
-    <mergeCell ref="D84:F84"/>
-    <mergeCell ref="D86:F86"/>
-    <mergeCell ref="D87:F87"/>
-    <mergeCell ref="D88:F88"/>
-    <mergeCell ref="D89:F89"/>
-    <mergeCell ref="D77:F77"/>
-    <mergeCell ref="D79:F79"/>
-    <mergeCell ref="D81:F81"/>
-    <mergeCell ref="D75:F75"/>
-    <mergeCell ref="D73:F73"/>
-    <mergeCell ref="B55:B57"/>
-    <mergeCell ref="D69:F69"/>
-    <mergeCell ref="D70:F70"/>
-    <mergeCell ref="D71:F71"/>
-    <mergeCell ref="D72:F72"/>
-    <mergeCell ref="D62:F62"/>
-    <mergeCell ref="D56:F56"/>
-    <mergeCell ref="D57:F57"/>
-    <mergeCell ref="D58:F58"/>
-    <mergeCell ref="D59:F59"/>
-    <mergeCell ref="D66:F66"/>
-    <mergeCell ref="D67:F67"/>
-    <mergeCell ref="D60:F60"/>
-    <mergeCell ref="D61:F61"/>
-    <mergeCell ref="D63:F63"/>
-    <mergeCell ref="D64:F64"/>
-    <mergeCell ref="D65:F65"/>
-    <mergeCell ref="D68:F68"/>
-    <mergeCell ref="D55:F55"/>
-    <mergeCell ref="B62:B70"/>
-    <mergeCell ref="B58:B61"/>
-    <mergeCell ref="B22:B27"/>
-    <mergeCell ref="B28:B35"/>
-    <mergeCell ref="B36:B54"/>
-    <mergeCell ref="D49:F49"/>
-    <mergeCell ref="D50:F50"/>
-    <mergeCell ref="D51:F51"/>
-    <mergeCell ref="D52:F52"/>
-    <mergeCell ref="D53:F53"/>
-    <mergeCell ref="D37:F37"/>
-    <mergeCell ref="D38:F38"/>
-    <mergeCell ref="D39:F39"/>
-    <mergeCell ref="D40:F40"/>
-    <mergeCell ref="D41:F41"/>
-    <mergeCell ref="D42:F42"/>
-    <mergeCell ref="D43:F43"/>
-    <mergeCell ref="D44:F44"/>
-    <mergeCell ref="D45:F45"/>
-    <mergeCell ref="I19:J19"/>
-    <mergeCell ref="H19:H20"/>
-    <mergeCell ref="B4:E4"/>
-    <mergeCell ref="B5:K5"/>
-    <mergeCell ref="D19:F20"/>
-    <mergeCell ref="G19:G20"/>
-    <mergeCell ref="B19:B20"/>
-    <mergeCell ref="C19:C20"/>
-    <mergeCell ref="K19:K20"/>
-    <mergeCell ref="D7:E7"/>
-    <mergeCell ref="D162:F162"/>
-    <mergeCell ref="D163:F163"/>
-    <mergeCell ref="D21:F21"/>
-    <mergeCell ref="D35:F35"/>
-    <mergeCell ref="D22:F22"/>
-    <mergeCell ref="D28:F28"/>
-    <mergeCell ref="D23:F23"/>
-    <mergeCell ref="D25:F25"/>
-    <mergeCell ref="D27:F27"/>
-    <mergeCell ref="D34:F34"/>
-    <mergeCell ref="D24:F24"/>
-    <mergeCell ref="D26:F26"/>
-    <mergeCell ref="D29:F29"/>
-    <mergeCell ref="D30:F30"/>
-    <mergeCell ref="D31:F31"/>
-    <mergeCell ref="D32:F32"/>
-    <mergeCell ref="D33:F33"/>
-    <mergeCell ref="D46:F46"/>
-    <mergeCell ref="D47:F47"/>
-    <mergeCell ref="D48:F48"/>
-    <mergeCell ref="D54:F54"/>
-    <mergeCell ref="D36:F36"/>
-    <mergeCell ref="D91:F91"/>
-    <mergeCell ref="D76:F76"/>
-    <mergeCell ref="D186:F186"/>
-    <mergeCell ref="D185:F185"/>
-    <mergeCell ref="D188:F188"/>
-    <mergeCell ref="B187:B188"/>
-    <mergeCell ref="D170:F170"/>
-    <mergeCell ref="D172:F172"/>
-    <mergeCell ref="D175:F175"/>
-    <mergeCell ref="D176:F176"/>
-    <mergeCell ref="D178:F178"/>
-    <mergeCell ref="D179:F179"/>
-    <mergeCell ref="B183:B186"/>
-    <mergeCell ref="D182:F182"/>
-    <mergeCell ref="B181:B182"/>
-    <mergeCell ref="D120:F120"/>
-    <mergeCell ref="D119:F119"/>
-    <mergeCell ref="D118:F118"/>
-    <mergeCell ref="D117:F117"/>
-    <mergeCell ref="D116:F116"/>
-    <mergeCell ref="D115:F115"/>
-    <mergeCell ref="D114:F114"/>
-    <mergeCell ref="D113:F113"/>
-    <mergeCell ref="D92:F92"/>
-    <mergeCell ref="D93:F93"/>
-    <mergeCell ref="D94:F94"/>
-    <mergeCell ref="D95:F95"/>
-    <mergeCell ref="D96:F96"/>
-    <mergeCell ref="D97:F97"/>
-    <mergeCell ref="D98:F98"/>
-    <mergeCell ref="D100:F100"/>
-    <mergeCell ref="D122:F122"/>
-    <mergeCell ref="B119:B123"/>
-    <mergeCell ref="B113:B118"/>
-    <mergeCell ref="B108:B112"/>
-    <mergeCell ref="B99:B107"/>
-    <mergeCell ref="B94:B98"/>
-    <mergeCell ref="B91:B93"/>
-    <mergeCell ref="D124:F124"/>
-    <mergeCell ref="D135:F135"/>
-    <mergeCell ref="D133:F133"/>
-    <mergeCell ref="D131:F131"/>
-    <mergeCell ref="D132:F132"/>
-    <mergeCell ref="D129:F129"/>
-    <mergeCell ref="D130:F130"/>
-    <mergeCell ref="D127:F127"/>
-    <mergeCell ref="D128:F128"/>
-    <mergeCell ref="D125:F125"/>
-    <mergeCell ref="D126:F126"/>
-    <mergeCell ref="D134:F134"/>
-    <mergeCell ref="B132:B135"/>
-    <mergeCell ref="B127:B131"/>
-    <mergeCell ref="B124:B126"/>
-    <mergeCell ref="D108:F108"/>
-    <mergeCell ref="D121:F121"/>
   </mergeCells>
   <phoneticPr fontId="3"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -12248,12 +12255,12 @@
     </row>
     <row r="85" spans="2:3">
       <c r="C85" t="s">
-        <v>360</v>
+        <v>449</v>
       </c>
     </row>
     <row r="86" spans="2:3">
       <c r="B86" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="C86" t="s">
         <v>344</v>
@@ -12261,27 +12268,27 @@
     </row>
     <row r="87" spans="2:3">
       <c r="C87" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="88" spans="2:3">
       <c r="C88" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
     </row>
     <row r="89" spans="2:3">
       <c r="C89" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="90" spans="2:3">
       <c r="C90" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
     </row>
     <row r="91" spans="2:3">
       <c r="B91" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="C91" t="s">
         <v>344</v>
@@ -12289,55 +12296,55 @@
     </row>
     <row r="92" spans="2:3">
       <c r="C92" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
     </row>
     <row r="93" spans="2:3">
       <c r="C93" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
     </row>
     <row r="94" spans="2:3">
       <c r="C94" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
     </row>
     <row r="95" spans="2:3">
       <c r="C95" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
     </row>
     <row r="96" spans="2:3">
       <c r="C96" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
     </row>
     <row r="97" spans="2:3">
       <c r="B97" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="C97" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
     </row>
     <row r="98" spans="2:3">
       <c r="C98" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
     </row>
     <row r="99" spans="2:3">
       <c r="C99" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
     </row>
     <row r="100" spans="2:3">
       <c r="C100" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
     </row>
     <row r="101" spans="2:3">
       <c r="C101" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
     </row>
     <row r="102" spans="2:3">
@@ -12346,7 +12353,7 @@
     </row>
     <row r="103" spans="2:3">
       <c r="B103" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="C103" t="s">
         <v>344</v>
@@ -12354,63 +12361,63 @@
     </row>
     <row r="104" spans="2:3">
       <c r="C104" s="82" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
     </row>
     <row r="105" spans="2:3">
       <c r="C105" s="82" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
     </row>
     <row r="106" spans="2:3">
       <c r="B106" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="C106" s="83" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
     </row>
     <row r="107" spans="2:3">
       <c r="C107" s="79" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
     </row>
     <row r="108" spans="2:3">
       <c r="C108" s="79" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
     </row>
     <row r="109" spans="2:3">
       <c r="C109" s="79" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
     </row>
     <row r="110" spans="2:3">
       <c r="C110" s="79" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
     </row>
     <row r="111" spans="2:3">
       <c r="B111" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="C111" s="79" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
     </row>
     <row r="112" spans="2:3">
       <c r="C112" s="79" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
     </row>
     <row r="113" spans="2:3">
       <c r="C113" s="79" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
     </row>
     <row r="114" spans="2:3">
       <c r="C114" s="79" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
     </row>
     <row r="115" spans="2:3">

--- a/IG/7日版/AI Native-バイブコーディング_IG.xlsx
+++ b/IG/7日版/AI Native-バイブコーディング_IG.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\myrepo\ai_navive\IG\7日版\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF3BFF64-4658-4051-8FB2-0177D9297528}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D5F55BDF-1974-4C36-BE82-916AD66BB9EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="860" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'スケジュール（3日）'!$A$1:$H$44</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="2">講義!$A$1:$L$189</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="2">講義!$A$1:$L$190</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="1">特記イベント!$A$1:$L$14</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -88,7 +88,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="828" uniqueCount="450">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="832" uniqueCount="452">
   <si>
     <t>1 日目</t>
     <rPh sb="2" eb="3">
@@ -3089,23 +3089,6 @@
     <phoneticPr fontId="3"/>
   </si>
   <si>
-    <t>レポートの作成</t>
-    <rPh sb="5" eb="7">
-      <t>サクセイ</t>
-    </rPh>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
-    <t>サンプルのAPとの自分のAPとの比較</t>
-    <rPh sb="9" eb="11">
-      <t>ジブン</t>
-    </rPh>
-    <rPh sb="16" eb="18">
-      <t>ヒカク</t>
-    </rPh>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
     <t>AI-09</t>
   </si>
   <si>
@@ -3303,19 +3286,6 @@
     </rPh>
     <rPh sb="4" eb="6">
       <t>ジッシ</t>
-    </rPh>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
-    <t>課題の振り返り</t>
-    <rPh sb="0" eb="2">
-      <t>カダイ</t>
-    </rPh>
-    <rPh sb="3" eb="4">
-      <t>フ</t>
-    </rPh>
-    <rPh sb="5" eb="6">
-      <t>カエ</t>
     </rPh>
     <phoneticPr fontId="3"/>
   </si>
@@ -3427,94 +3397,6 @@
   <si>
     <t xml:space="preserve">・AI-08
 </t>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">サンプルAPと自分のAPを比較し、違いを検討する。
-■環境構築
-1. zipを解凍する。
-2. 解凍したフォルダをVSコードで開く。
-3. アプリケーションを実行する。
-4. アプリケーションやソースコードを確認し、違いを確認する。
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Meiryo UI"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>※ポートの衝突を防ぐため、以下のコマンドで実行することを推奨する。</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="Meiryo UI"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t xml:space="preserve">
-　「mvn spring-boot:run -Dspring-boot.run.arguments=--server.port=8081」
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Meiryo UI"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t xml:space="preserve">
-※ソースコードの比較は「Compare Folders」を使った方がよい。
-※ソースコードの違いについては、生成AIを活用して内容を確認すること。</t>
-    </r>
-    <rPh sb="7" eb="9">
-      <t>ジブン</t>
-    </rPh>
-    <rPh sb="13" eb="15">
-      <t>ヒカク</t>
-    </rPh>
-    <rPh sb="17" eb="18">
-      <t>チガ</t>
-    </rPh>
-    <rPh sb="20" eb="22">
-      <t>ケントウ</t>
-    </rPh>
-    <rPh sb="80" eb="82">
-      <t>ジッコウ</t>
-    </rPh>
-    <rPh sb="109" eb="110">
-      <t>チガ</t>
-    </rPh>
-    <rPh sb="112" eb="114">
-      <t>カクニン</t>
-    </rPh>
-    <rPh sb="232" eb="234">
-      <t>ヒカク</t>
-    </rPh>
-    <rPh sb="253" eb="254">
-      <t>ツカ</t>
-    </rPh>
-    <rPh sb="256" eb="257">
-      <t>ホウ</t>
-    </rPh>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
-    <t>振り返りレポートを作成することを説明する。
-①自身のAPとサンプルAPの違い
-②自身のAPをどのように改善できるか
-③気づいたこと・学んだこと</t>
-    <rPh sb="9" eb="11">
-      <t>サクセイ</t>
-    </rPh>
-    <rPh sb="16" eb="18">
-      <t>セツメイ</t>
-    </rPh>
     <phoneticPr fontId="3"/>
   </si>
   <si>
@@ -4558,6 +4440,162 @@
     </rPh>
     <rPh sb="7" eb="8">
       <t>ケ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>分析結果の共有</t>
+    <rPh sb="0" eb="2">
+      <t>ブンセキ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ケッカ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>キョウユウ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>アプリケーションの比較・分析</t>
+    <rPh sb="9" eb="11">
+      <t>ヒカク</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>ブンセキ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>演習の振り返り</t>
+    <rPh sb="0" eb="2">
+      <t>エンシュウ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>フ</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>カエ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>分析結果を共有することを説明する。
+①自身のAPと配布のAPの違い
+②自身のAPをどのように改善できるか
+③気づいたこと・学んだこと</t>
+    <rPh sb="0" eb="2">
+      <t>ブンセキ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ケッカ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>キョウユウ</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>セツメイ</t>
+    </rPh>
+    <rPh sb="25" eb="27">
+      <t>ハイフ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>改善点の整理</t>
+    <rPh sb="0" eb="3">
+      <t>カイゼンテン</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>セイリ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>比較・分析した結果をもとに、自身のアプリケーションの改善点を整理することを説明する。
+・実装方法
+・可読性
+・保守性など</t>
+    <rPh sb="37" eb="39">
+      <t>セツメイ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">自身のAPと配布のAPを比較し、違いを分析することを説明する。
+■環境構築
+1. zipを解凍する。
+2. 解凍したフォルダをVSコードで開く。
+3. アプリケーションを実行する。
+4. アプリケーションやソースコードを確認し、違いを確認する。
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Meiryo UI"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>※ポートの衝突を防ぐため、以下のコマンドで実行することを推奨する。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Meiryo UI"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t xml:space="preserve">
+　「mvn spring-boot:run -Dspring-boot.run.arguments=--server.port=8081」
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Meiryo UI"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t xml:space="preserve">
+※ソースコードの比較は「Compare Folders」を使った方がよい。
+※ソースコードの違いについては、生成AIを活用して内容を確認すること。</t>
+    </r>
+    <rPh sb="6" eb="8">
+      <t>ハイフ</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>ヒカク</t>
+    </rPh>
+    <rPh sb="16" eb="17">
+      <t>チガ</t>
+    </rPh>
+    <rPh sb="19" eb="21">
+      <t>ブンセキ</t>
+    </rPh>
+    <rPh sb="26" eb="28">
+      <t>セツメイ</t>
+    </rPh>
+    <rPh sb="86" eb="88">
+      <t>ジッコウ</t>
+    </rPh>
+    <rPh sb="115" eb="116">
+      <t>チガ</t>
+    </rPh>
+    <rPh sb="118" eb="120">
+      <t>カクニン</t>
+    </rPh>
+    <rPh sb="238" eb="240">
+      <t>ヒカク</t>
+    </rPh>
+    <rPh sb="259" eb="260">
+      <t>ツカ</t>
+    </rPh>
+    <rPh sb="262" eb="263">
+      <t>ホウ</t>
     </rPh>
     <phoneticPr fontId="3"/>
   </si>
@@ -5310,6 +5348,33 @@
     <xf numFmtId="0" fontId="11" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -5319,33 +5384,6 @@
     <xf numFmtId="0" fontId="5" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="9" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="255"/>
     </xf>
@@ -5364,14 +5402,14 @@
     <xf numFmtId="0" fontId="5" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="255"/>
     </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="11" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -5801,11 +5839,11 @@
       </c>
       <c r="D9" s="21"/>
       <c r="E9" s="21" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="F9" s="21"/>
       <c r="G9" s="21" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="14.25" customHeight="1">
@@ -6234,7 +6272,7 @@
         <v>0.6875</v>
       </c>
       <c r="C38" s="66" t="s">
-        <v>444</v>
+        <v>439</v>
       </c>
       <c r="D38" s="39"/>
       <c r="E38" s="51"/>
@@ -6243,7 +6281,7 @@
       </c>
       <c r="G38" s="51" t="str">
         <f>master!B164</f>
-        <v>課題の振り返り</v>
+        <v>演習の振り返り</v>
       </c>
       <c r="H38" s="6"/>
     </row>
@@ -6275,7 +6313,7 @@
         <v>0.71875</v>
       </c>
       <c r="C41" s="55" t="s">
-        <v>444</v>
+        <v>439</v>
       </c>
       <c r="D41" s="39"/>
       <c r="E41" s="99"/>
@@ -6498,7 +6536,7 @@
       <c r="A12" s="10"/>
       <c r="B12" s="19"/>
       <c r="C12" s="19" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
       <c r="D12" s="103" t="s">
         <v>50</v>
@@ -6522,15 +6560,15 @@
       <c r="A13" s="10"/>
       <c r="B13" s="19"/>
       <c r="C13" s="19" t="s">
-        <v>331</v>
+        <v>328</v>
       </c>
       <c r="D13" s="103" t="s">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="E13" s="103"/>
       <c r="F13" s="103"/>
       <c r="G13" s="87" t="s">
-        <v>329</v>
+        <v>326</v>
       </c>
       <c r="H13" s="19"/>
       <c r="I13" s="47" t="s">
@@ -6578,7 +6616,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A2:N190"/>
+  <dimension ref="A2:N191"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="4.33203125" style="1" customWidth="1"/>
@@ -6644,16 +6682,16 @@
       <c r="M4" s="9"/>
     </row>
     <row r="5" spans="2:14" ht="36" customHeight="1">
-      <c r="B5" s="129"/>
-      <c r="C5" s="129"/>
-      <c r="D5" s="129"/>
-      <c r="E5" s="129"/>
-      <c r="F5" s="129"/>
-      <c r="G5" s="129"/>
-      <c r="H5" s="129"/>
-      <c r="I5" s="129"/>
-      <c r="J5" s="129"/>
-      <c r="K5" s="129"/>
+      <c r="B5" s="127"/>
+      <c r="C5" s="127"/>
+      <c r="D5" s="127"/>
+      <c r="E5" s="127"/>
+      <c r="F5" s="127"/>
+      <c r="G5" s="127"/>
+      <c r="H5" s="127"/>
+      <c r="I5" s="127"/>
+      <c r="J5" s="127"/>
+      <c r="K5" s="127"/>
       <c r="L5" s="26"/>
       <c r="M5" s="27"/>
     </row>
@@ -6802,7 +6840,7 @@
     </row>
     <row r="13" spans="2:14">
       <c r="B13" s="31" t="s">
-        <v>332</v>
+        <v>329</v>
       </c>
       <c r="C13" s="57" t="s">
         <v>37</v>
@@ -6827,7 +6865,7 @@
         <v>93</v>
       </c>
       <c r="C14" s="57" t="s">
-        <v>390</v>
+        <v>385</v>
       </c>
       <c r="D14" s="42" t="s">
         <v>19</v>
@@ -6849,7 +6887,7 @@
         <v>94</v>
       </c>
       <c r="C15" s="57" t="s">
-        <v>391</v>
+        <v>386</v>
       </c>
       <c r="D15" s="42" t="s">
         <v>19</v>
@@ -6868,10 +6906,10 @@
     </row>
     <row r="16" spans="2:14">
       <c r="B16" s="31" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="C16" s="57" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="D16" s="42" t="s">
         <v>19</v>
@@ -6890,10 +6928,10 @@
     </row>
     <row r="17" spans="1:14">
       <c r="B17" s="31" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="C17" s="57" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="D17" s="42" t="s">
         <v>19</v>
@@ -6929,10 +6967,10 @@
       <c r="H19" s="101" t="s">
         <v>23</v>
       </c>
-      <c r="I19" s="127" t="s">
+      <c r="I19" s="128" t="s">
         <v>31</v>
       </c>
-      <c r="J19" s="128"/>
+      <c r="J19" s="129"/>
       <c r="K19" s="101" t="s">
         <v>32</v>
       </c>
@@ -6970,11 +7008,11 @@
         <f>master!C3</f>
         <v>講義の目的</v>
       </c>
-      <c r="D21" s="109" t="s">
+      <c r="D21" s="118" t="s">
         <v>95</v>
       </c>
-      <c r="E21" s="110"/>
-      <c r="F21" s="111"/>
+      <c r="E21" s="119"/>
+      <c r="F21" s="120"/>
       <c r="G21" s="48" t="s">
         <v>96</v>
       </c>
@@ -7000,11 +7038,11 @@
         <f>master!C4</f>
         <v>Webアプリケーションとは</v>
       </c>
-      <c r="D22" s="109" t="s">
+      <c r="D22" s="118" t="s">
         <v>97</v>
       </c>
-      <c r="E22" s="110"/>
-      <c r="F22" s="111"/>
+      <c r="E22" s="119"/>
+      <c r="F22" s="120"/>
       <c r="G22" s="48" t="s">
         <v>40</v>
       </c>
@@ -7027,11 +7065,11 @@
         <f>master!C5</f>
         <v>Webアプリケーションの種類</v>
       </c>
-      <c r="D23" s="109" t="s">
+      <c r="D23" s="118" t="s">
         <v>98</v>
       </c>
-      <c r="E23" s="110"/>
-      <c r="F23" s="111"/>
+      <c r="E23" s="119"/>
+      <c r="F23" s="120"/>
       <c r="G23" s="48" t="s">
         <v>44</v>
       </c>
@@ -7054,11 +7092,11 @@
         <f>master!C6</f>
         <v>アプリケーションとは</v>
       </c>
-      <c r="D24" s="109" t="s">
+      <c r="D24" s="118" t="s">
         <v>99</v>
       </c>
-      <c r="E24" s="110"/>
-      <c r="F24" s="111"/>
+      <c r="E24" s="119"/>
+      <c r="F24" s="120"/>
       <c r="G24" s="48" t="s">
         <v>42</v>
       </c>
@@ -7081,11 +7119,11 @@
         <f>master!C7</f>
         <v>Web画面アプリケーション</v>
       </c>
-      <c r="D25" s="109" t="s">
+      <c r="D25" s="118" t="s">
         <v>100</v>
       </c>
-      <c r="E25" s="110"/>
-      <c r="F25" s="111"/>
+      <c r="E25" s="119"/>
+      <c r="F25" s="120"/>
       <c r="G25" s="48" t="s">
         <v>41</v>
       </c>
@@ -7105,11 +7143,11 @@
       <c r="A26" s="11"/>
       <c r="B26" s="125"/>
       <c r="C26" s="48"/>
-      <c r="D26" s="109" t="s">
+      <c r="D26" s="118" t="s">
         <v>101</v>
       </c>
-      <c r="E26" s="110"/>
-      <c r="F26" s="111"/>
+      <c r="E26" s="119"/>
+      <c r="F26" s="120"/>
       <c r="G26" s="48" t="s">
         <v>41</v>
       </c>
@@ -7132,11 +7170,11 @@
         <f>master!C8</f>
         <v>ブラウザからのリクエスト種類</v>
       </c>
-      <c r="D27" s="109" t="s">
+      <c r="D27" s="118" t="s">
         <v>102</v>
       </c>
-      <c r="E27" s="110"/>
-      <c r="F27" s="111"/>
+      <c r="E27" s="119"/>
+      <c r="F27" s="120"/>
       <c r="G27" s="48" t="s">
         <v>45</v>
       </c>
@@ -7162,11 +7200,11 @@
         <f>master!C9</f>
         <v>データベースとは</v>
       </c>
-      <c r="D28" s="109" t="s">
+      <c r="D28" s="118" t="s">
         <v>103</v>
       </c>
-      <c r="E28" s="110"/>
-      <c r="F28" s="111"/>
+      <c r="E28" s="119"/>
+      <c r="F28" s="120"/>
       <c r="G28" s="48" t="s">
         <v>42</v>
       </c>
@@ -7189,11 +7227,11 @@
         <f>master!C10</f>
         <v>リレーショナルデータベース</v>
       </c>
-      <c r="D29" s="109" t="s">
+      <c r="D29" s="118" t="s">
         <v>104</v>
       </c>
-      <c r="E29" s="110"/>
-      <c r="F29" s="111"/>
+      <c r="E29" s="119"/>
+      <c r="F29" s="120"/>
       <c r="G29" s="48" t="s">
         <v>46</v>
       </c>
@@ -7216,11 +7254,11 @@
         <f>master!C11</f>
         <v>データベースの役割</v>
       </c>
-      <c r="D30" s="109" t="s">
+      <c r="D30" s="118" t="s">
         <v>105</v>
       </c>
-      <c r="E30" s="110"/>
-      <c r="F30" s="111"/>
+      <c r="E30" s="119"/>
+      <c r="F30" s="120"/>
       <c r="G30" s="48" t="s">
         <v>47</v>
       </c>
@@ -7245,11 +7283,11 @@
         <f>master!C12</f>
         <v>2.1.テーブル</v>
       </c>
-      <c r="D31" s="109" t="s">
+      <c r="D31" s="118" t="s">
         <v>106</v>
       </c>
-      <c r="E31" s="110"/>
-      <c r="F31" s="111"/>
+      <c r="E31" s="119"/>
+      <c r="F31" s="120"/>
       <c r="G31" s="48" t="s">
         <v>44</v>
       </c>
@@ -7272,11 +7310,11 @@
         <f>master!C13</f>
         <v>2.2.データ型１</v>
       </c>
-      <c r="D32" s="109" t="s">
+      <c r="D32" s="118" t="s">
         <v>107</v>
       </c>
-      <c r="E32" s="110"/>
-      <c r="F32" s="111"/>
+      <c r="E32" s="119"/>
+      <c r="F32" s="120"/>
       <c r="G32" s="48" t="s">
         <v>48</v>
       </c>
@@ -7299,11 +7337,11 @@
         <f>master!C14</f>
         <v>2.2.データ型２</v>
       </c>
-      <c r="D33" s="109" t="s">
+      <c r="D33" s="118" t="s">
         <v>108</v>
       </c>
-      <c r="E33" s="110"/>
-      <c r="F33" s="111"/>
+      <c r="E33" s="119"/>
+      <c r="F33" s="120"/>
       <c r="G33" s="48" t="s">
         <v>42</v>
       </c>
@@ -7326,11 +7364,11 @@
         <f>master!C15</f>
         <v>2.3.リレーション</v>
       </c>
-      <c r="D34" s="109" t="s">
+      <c r="D34" s="118" t="s">
         <v>109</v>
       </c>
-      <c r="E34" s="110"/>
-      <c r="F34" s="111"/>
+      <c r="E34" s="119"/>
+      <c r="F34" s="120"/>
       <c r="G34" s="48" t="s">
         <v>42</v>
       </c>
@@ -7353,11 +7391,11 @@
         <f>master!C16</f>
         <v>2.4.データを結合して取得（Join）</v>
       </c>
-      <c r="D35" s="109" t="s">
+      <c r="D35" s="118" t="s">
         <v>110</v>
       </c>
-      <c r="E35" s="110"/>
-      <c r="F35" s="111"/>
+      <c r="E35" s="119"/>
+      <c r="F35" s="120"/>
       <c r="G35" s="48" t="s">
         <v>42</v>
       </c>
@@ -7383,11 +7421,11 @@
         <f>master!C17</f>
         <v>Webアプリケーションを作成するためのプログラミング言語</v>
       </c>
-      <c r="D36" s="109" t="s">
+      <c r="D36" s="118" t="s">
         <v>111</v>
       </c>
-      <c r="E36" s="110"/>
-      <c r="F36" s="111"/>
+      <c r="E36" s="119"/>
+      <c r="F36" s="120"/>
       <c r="G36" s="48" t="s">
         <v>46</v>
       </c>
@@ -7410,11 +7448,11 @@
         <f>master!C18</f>
         <v>Java</v>
       </c>
-      <c r="D37" s="109" t="s">
+      <c r="D37" s="118" t="s">
         <v>112</v>
       </c>
-      <c r="E37" s="110"/>
-      <c r="F37" s="111"/>
+      <c r="E37" s="119"/>
+      <c r="F37" s="120"/>
       <c r="G37" s="48" t="s">
         <v>44</v>
       </c>
@@ -7437,11 +7475,11 @@
         <f>master!C19</f>
         <v>Java言語の構成要素</v>
       </c>
-      <c r="D38" s="109" t="s">
+      <c r="D38" s="118" t="s">
         <v>113</v>
       </c>
-      <c r="E38" s="110"/>
-      <c r="F38" s="111"/>
+      <c r="E38" s="119"/>
+      <c r="F38" s="120"/>
       <c r="G38" s="48" t="s">
         <v>44</v>
       </c>
@@ -7464,11 +7502,11 @@
         <f>master!C20</f>
         <v>Webアプリケーションを構成するクラス</v>
       </c>
-      <c r="D39" s="109" t="s">
+      <c r="D39" s="118" t="s">
         <v>114</v>
       </c>
-      <c r="E39" s="110"/>
-      <c r="F39" s="111"/>
+      <c r="E39" s="119"/>
+      <c r="F39" s="120"/>
       <c r="G39" s="48" t="s">
         <v>43</v>
       </c>
@@ -7491,11 +7529,11 @@
         <f>master!C21</f>
         <v>Nレイヤーアーキテクチャ</v>
       </c>
-      <c r="D40" s="109" t="s">
+      <c r="D40" s="118" t="s">
         <v>116</v>
       </c>
-      <c r="E40" s="110"/>
-      <c r="F40" s="111"/>
+      <c r="E40" s="119"/>
+      <c r="F40" s="120"/>
       <c r="G40" s="48" t="s">
         <v>46</v>
       </c>
@@ -7520,11 +7558,11 @@
         <f>master!C22</f>
         <v>View と Controller と Service と Repository</v>
       </c>
-      <c r="D41" s="109" t="s">
+      <c r="D41" s="118" t="s">
         <v>117</v>
       </c>
-      <c r="E41" s="110"/>
-      <c r="F41" s="111"/>
+      <c r="E41" s="119"/>
+      <c r="F41" s="120"/>
       <c r="G41" s="48" t="s">
         <v>118</v>
       </c>
@@ -7547,11 +7585,11 @@
         <f>master!C23</f>
         <v>Nレイヤーアーキテクチャ</v>
       </c>
-      <c r="D42" s="109" t="s">
+      <c r="D42" s="118" t="s">
         <v>119</v>
       </c>
-      <c r="E42" s="110"/>
-      <c r="F42" s="111"/>
+      <c r="E42" s="119"/>
+      <c r="F42" s="120"/>
       <c r="G42" s="48" t="s">
         <v>42</v>
       </c>
@@ -7574,11 +7612,11 @@
         <f>master!C24</f>
         <v>Webアプリケーション フレームワーク</v>
       </c>
-      <c r="D43" s="109" t="s">
+      <c r="D43" s="118" t="s">
         <v>120</v>
       </c>
-      <c r="E43" s="110"/>
-      <c r="F43" s="111"/>
+      <c r="E43" s="119"/>
+      <c r="F43" s="120"/>
       <c r="G43" s="48" t="s">
         <v>121</v>
       </c>
@@ -7601,11 +7639,11 @@
         <f>master!C25</f>
         <v>Java向けWebアプリケーションフレームワーク</v>
       </c>
-      <c r="D44" s="109" t="s">
+      <c r="D44" s="118" t="s">
         <v>122</v>
       </c>
-      <c r="E44" s="110"/>
-      <c r="F44" s="111"/>
+      <c r="E44" s="119"/>
+      <c r="F44" s="120"/>
       <c r="G44" s="48" t="s">
         <v>47</v>
       </c>
@@ -7628,11 +7666,11 @@
         <f>master!C26</f>
         <v>Springフレームワーク</v>
       </c>
-      <c r="D45" s="109" t="s">
+      <c r="D45" s="118" t="s">
         <v>123</v>
       </c>
-      <c r="E45" s="110"/>
-      <c r="F45" s="111"/>
+      <c r="E45" s="119"/>
+      <c r="F45" s="120"/>
       <c r="G45" s="48" t="s">
         <v>124</v>
       </c>
@@ -7655,11 +7693,11 @@
         <f>master!C27</f>
         <v>Springフレームワーク：DIコンテナとは</v>
       </c>
-      <c r="D46" s="109" t="s">
+      <c r="D46" s="118" t="s">
         <v>125</v>
       </c>
-      <c r="E46" s="110"/>
-      <c r="F46" s="111"/>
+      <c r="E46" s="119"/>
+      <c r="F46" s="120"/>
       <c r="G46" s="48" t="s">
         <v>46</v>
       </c>
@@ -7684,11 +7722,11 @@
         <f>master!C28</f>
         <v>DIコンテナ：DIコンテナが部品を注入する</v>
       </c>
-      <c r="D47" s="109" t="s">
+      <c r="D47" s="118" t="s">
         <v>126</v>
       </c>
-      <c r="E47" s="110"/>
-      <c r="F47" s="111"/>
+      <c r="E47" s="119"/>
+      <c r="F47" s="120"/>
       <c r="G47" s="48" t="s">
         <v>41</v>
       </c>
@@ -7711,11 +7749,11 @@
         <f>master!C29</f>
         <v>DIコンテナ：DIコンテナによる部品と注入対象になるための目印</v>
       </c>
-      <c r="D48" s="109" t="s">
+      <c r="D48" s="118" t="s">
         <v>127</v>
       </c>
-      <c r="E48" s="110"/>
-      <c r="F48" s="111"/>
+      <c r="E48" s="119"/>
+      <c r="F48" s="120"/>
       <c r="G48" s="48" t="s">
         <v>48</v>
       </c>
@@ -7738,11 +7776,11 @@
         <f>master!C30</f>
         <v>Springフレームワークにおける部品の設定</v>
       </c>
-      <c r="D49" s="109" t="s">
+      <c r="D49" s="118" t="s">
         <v>128</v>
       </c>
-      <c r="E49" s="110"/>
-      <c r="F49" s="111"/>
+      <c r="E49" s="119"/>
+      <c r="F49" s="120"/>
       <c r="G49" s="48" t="s">
         <v>48</v>
       </c>
@@ -7765,11 +7803,11 @@
         <f>master!C31</f>
         <v>Spring Boot</v>
       </c>
-      <c r="D50" s="109" t="s">
+      <c r="D50" s="118" t="s">
         <v>129</v>
       </c>
-      <c r="E50" s="110"/>
-      <c r="F50" s="111"/>
+      <c r="E50" s="119"/>
+      <c r="F50" s="120"/>
       <c r="G50" s="48" t="s">
         <v>46</v>
       </c>
@@ -7792,11 +7830,11 @@
         <f>master!C32</f>
         <v>Spring Boot：オートコンフィグレーション</v>
       </c>
-      <c r="D51" s="109" t="s">
+      <c r="D51" s="118" t="s">
         <v>130</v>
       </c>
-      <c r="E51" s="110"/>
-      <c r="F51" s="111"/>
+      <c r="E51" s="119"/>
+      <c r="F51" s="120"/>
       <c r="G51" s="48" t="s">
         <v>41</v>
       </c>
@@ -7819,11 +7857,11 @@
         <f>master!C33</f>
         <v>Spring Boot：Starters</v>
       </c>
-      <c r="D52" s="109" t="s">
+      <c r="D52" s="118" t="s">
         <v>131</v>
       </c>
-      <c r="E52" s="110"/>
-      <c r="F52" s="111"/>
+      <c r="E52" s="119"/>
+      <c r="F52" s="120"/>
       <c r="G52" s="48" t="s">
         <v>43</v>
       </c>
@@ -7846,11 +7884,11 @@
         <f>master!C34</f>
         <v>Spring Boot：組込みWebAPサーバ</v>
       </c>
-      <c r="D53" s="109" t="s">
+      <c r="D53" s="118" t="s">
         <v>132</v>
       </c>
-      <c r="E53" s="110"/>
-      <c r="F53" s="111"/>
+      <c r="E53" s="119"/>
+      <c r="F53" s="120"/>
       <c r="G53" s="48" t="s">
         <v>46</v>
       </c>
@@ -7873,9 +7911,9 @@
         <f>master!C35</f>
         <v>おすすめ書籍：『プロになるためのSpring入門』</v>
       </c>
-      <c r="D54" s="109"/>
-      <c r="E54" s="110"/>
-      <c r="F54" s="111"/>
+      <c r="D54" s="118"/>
+      <c r="E54" s="119"/>
+      <c r="F54" s="120"/>
       <c r="G54" s="48" t="s">
         <v>47</v>
       </c>
@@ -7901,13 +7939,13 @@
         <f>master!C37</f>
         <v>演習課題の概要</v>
       </c>
-      <c r="D55" s="115" t="s">
+      <c r="D55" s="112" t="s">
         <v>165</v>
       </c>
-      <c r="E55" s="116"/>
-      <c r="F55" s="117"/>
+      <c r="E55" s="113"/>
+      <c r="F55" s="114"/>
       <c r="G55" s="58" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="H55" s="59"/>
       <c r="I55" s="60" t="s">
@@ -7928,13 +7966,13 @@
         <f>master!C38</f>
         <v>作成物</v>
       </c>
-      <c r="D56" s="115" t="s">
+      <c r="D56" s="112" t="s">
         <v>166</v>
       </c>
-      <c r="E56" s="116"/>
-      <c r="F56" s="117"/>
+      <c r="E56" s="113"/>
+      <c r="F56" s="114"/>
       <c r="G56" s="58" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="H56" s="59"/>
       <c r="I56" s="60" t="s">
@@ -7955,13 +7993,13 @@
         <f>master!C39</f>
         <v>演習課題の進め方</v>
       </c>
-      <c r="D57" s="115" t="s">
+      <c r="D57" s="112" t="s">
         <v>167</v>
       </c>
-      <c r="E57" s="116"/>
-      <c r="F57" s="117"/>
+      <c r="E57" s="113"/>
+      <c r="F57" s="114"/>
       <c r="G57" s="58" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="H57" s="59"/>
       <c r="I57" s="60" t="s">
@@ -7985,11 +8023,11 @@
         <f>master!C40</f>
         <v>前提条件</v>
       </c>
-      <c r="D58" s="115"/>
-      <c r="E58" s="116"/>
-      <c r="F58" s="117"/>
+      <c r="D58" s="112"/>
+      <c r="E58" s="113"/>
+      <c r="F58" s="114"/>
       <c r="G58" s="58" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="H58" s="59"/>
       <c r="I58" s="60" t="s">
@@ -8010,13 +8048,13 @@
         <f>master!C41</f>
         <v>Spring Bootプロジェクトの準備</v>
       </c>
-      <c r="D59" s="115" t="s">
+      <c r="D59" s="112" t="s">
         <v>168</v>
       </c>
-      <c r="E59" s="116"/>
-      <c r="F59" s="117"/>
+      <c r="E59" s="113"/>
+      <c r="F59" s="114"/>
       <c r="G59" s="58" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="H59" s="59"/>
       <c r="I59" s="60" t="s">
@@ -8037,13 +8075,13 @@
         <f>master!C42</f>
         <v>（補足）Spring Bootプロジェクトの準備</v>
       </c>
-      <c r="D60" s="115" t="s">
+      <c r="D60" s="112" t="s">
         <v>169</v>
       </c>
-      <c r="E60" s="116"/>
-      <c r="F60" s="117"/>
+      <c r="E60" s="113"/>
+      <c r="F60" s="114"/>
       <c r="G60" s="58" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="H60" s="59"/>
       <c r="I60" s="60" t="s">
@@ -8064,13 +8102,13 @@
         <f>master!C43</f>
         <v>Spring Bootアプリケーションの起動確認</v>
       </c>
-      <c r="D61" s="115" t="s">
+      <c r="D61" s="112" t="s">
         <v>191</v>
       </c>
-      <c r="E61" s="116"/>
-      <c r="F61" s="117"/>
+      <c r="E61" s="113"/>
+      <c r="F61" s="114"/>
       <c r="G61" s="58" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="H61" s="59"/>
       <c r="I61" s="60" t="s">
@@ -8094,13 +8132,13 @@
         <f>master!C44</f>
         <v>ECサイト Webアプリの要件 – はじめに</v>
       </c>
-      <c r="D62" s="115" t="s">
+      <c r="D62" s="112" t="s">
         <v>170</v>
       </c>
-      <c r="E62" s="116"/>
-      <c r="F62" s="117"/>
+      <c r="E62" s="113"/>
+      <c r="F62" s="114"/>
       <c r="G62" s="58" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="H62" s="59"/>
       <c r="I62" s="60" t="s">
@@ -8121,13 +8159,13 @@
         <f>master!C45</f>
         <v>ECサイト Webアプリの要件➊ 画面</v>
       </c>
-      <c r="D63" s="115" t="s">
+      <c r="D63" s="112" t="s">
         <v>172</v>
       </c>
-      <c r="E63" s="116"/>
-      <c r="F63" s="117"/>
+      <c r="E63" s="113"/>
+      <c r="F63" s="114"/>
       <c r="G63" s="58" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="H63" s="59"/>
       <c r="I63" s="60" t="s">
@@ -8148,13 +8186,13 @@
         <f>master!C46</f>
         <v>ECサイト Webアプリの要件➋ 機能</v>
       </c>
-      <c r="D64" s="115" t="s">
+      <c r="D64" s="112" t="s">
         <v>173</v>
       </c>
-      <c r="E64" s="116"/>
-      <c r="F64" s="117"/>
+      <c r="E64" s="113"/>
+      <c r="F64" s="114"/>
       <c r="G64" s="58" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="H64" s="59"/>
       <c r="I64" s="60" t="s">
@@ -8175,13 +8213,13 @@
         <f>master!C47</f>
         <v>ECサイト Webアプリの要件➌ 画面遷移</v>
       </c>
-      <c r="D65" s="115" t="s">
+      <c r="D65" s="112" t="s">
         <v>174</v>
       </c>
-      <c r="E65" s="116"/>
-      <c r="F65" s="117"/>
+      <c r="E65" s="113"/>
+      <c r="F65" s="114"/>
       <c r="G65" s="58" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="H65" s="59"/>
       <c r="I65" s="60" t="s">
@@ -8202,13 +8240,13 @@
         <f>master!C48</f>
         <v>ECサイト Webアプリの要件❹ データ設計</v>
       </c>
-      <c r="D66" s="115" t="s">
+      <c r="D66" s="112" t="s">
         <v>176</v>
       </c>
-      <c r="E66" s="116"/>
-      <c r="F66" s="117"/>
+      <c r="E66" s="113"/>
+      <c r="F66" s="114"/>
       <c r="G66" s="58" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="H66" s="59"/>
       <c r="I66" s="60" t="s">
@@ -8229,13 +8267,13 @@
         <f>master!C49</f>
         <v>ECサイト Webアプリの要件❺ 初期データ</v>
       </c>
-      <c r="D67" s="115" t="s">
+      <c r="D67" s="112" t="s">
         <v>177</v>
       </c>
-      <c r="E67" s="116"/>
-      <c r="F67" s="117"/>
+      <c r="E67" s="113"/>
+      <c r="F67" s="114"/>
       <c r="G67" s="58" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="H67" s="59"/>
       <c r="I67" s="60" t="s">
@@ -8256,13 +8294,13 @@
         <f>master!C50</f>
         <v>ECサイト Webアプリの要件❻ ディレクトリ構成</v>
       </c>
-      <c r="D68" s="115" t="s">
+      <c r="D68" s="112" t="s">
         <v>178</v>
       </c>
-      <c r="E68" s="116"/>
-      <c r="F68" s="117"/>
+      <c r="E68" s="113"/>
+      <c r="F68" s="114"/>
       <c r="G68" s="58" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="H68" s="59"/>
       <c r="I68" s="60" t="s">
@@ -8283,13 +8321,13 @@
         <f>master!C51</f>
         <v>ECサイト Webアプリの要件❼ パッケージ構成</v>
       </c>
-      <c r="D69" s="115" t="s">
+      <c r="D69" s="112" t="s">
         <v>180</v>
       </c>
-      <c r="E69" s="116"/>
-      <c r="F69" s="117"/>
+      <c r="E69" s="113"/>
+      <c r="F69" s="114"/>
       <c r="G69" s="58" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="H69" s="59"/>
       <c r="I69" s="60" t="s">
@@ -8310,13 +8348,13 @@
         <f>master!C52</f>
         <v>ECサイト Webアプリの要件❽ リソース構成</v>
       </c>
-      <c r="D70" s="115" t="s">
+      <c r="D70" s="112" t="s">
         <v>179</v>
       </c>
-      <c r="E70" s="116"/>
-      <c r="F70" s="117"/>
+      <c r="E70" s="113"/>
+      <c r="F70" s="114"/>
       <c r="G70" s="58" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="H70" s="59"/>
       <c r="I70" s="60" t="s">
@@ -8340,13 +8378,13 @@
         <f>master!C53</f>
         <v>バイブコーディング – はじめに</v>
       </c>
-      <c r="D71" s="115" t="s">
+      <c r="D71" s="112" t="s">
         <v>181</v>
       </c>
-      <c r="E71" s="116"/>
-      <c r="F71" s="117"/>
+      <c r="E71" s="113"/>
+      <c r="F71" s="114"/>
       <c r="G71" s="58" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="H71" s="59"/>
       <c r="I71" s="60" t="s">
@@ -8367,13 +8405,13 @@
         <f>master!C54</f>
         <v>[構造理解] Webアプリケーションで必要なもの</v>
       </c>
-      <c r="D72" s="115" t="s">
+      <c r="D72" s="112" t="s">
         <v>182</v>
       </c>
-      <c r="E72" s="116"/>
-      <c r="F72" s="117"/>
+      <c r="E72" s="113"/>
+      <c r="F72" s="114"/>
       <c r="G72" s="58" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="H72" s="59"/>
       <c r="I72" s="60" t="s">
@@ -8394,13 +8432,13 @@
         <f>master!C55</f>
         <v>バイブコーディング➊ 画面モックアップを作ってデザインを決める</v>
       </c>
-      <c r="D73" s="115" t="s">
+      <c r="D73" s="112" t="s">
         <v>192</v>
       </c>
-      <c r="E73" s="116"/>
-      <c r="F73" s="117"/>
+      <c r="E73" s="113"/>
+      <c r="F73" s="114"/>
       <c r="G73" s="58" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="H73" s="59"/>
       <c r="I73" s="60" t="s">
@@ -8418,13 +8456,13 @@
       <c r="A74" s="11"/>
       <c r="B74" s="122"/>
       <c r="C74" s="77"/>
-      <c r="D74" s="115" t="s">
+      <c r="D74" s="112" t="s">
         <v>183</v>
       </c>
-      <c r="E74" s="116"/>
-      <c r="F74" s="117"/>
+      <c r="E74" s="113"/>
+      <c r="F74" s="114"/>
       <c r="G74" s="58" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="H74" s="59"/>
       <c r="I74" s="60"/>
@@ -8441,13 +8479,13 @@
         <f>master!C56</f>
         <v>バイブコーディング➋ データベースのテーブルを準備する</v>
       </c>
-      <c r="D75" s="115" t="s">
+      <c r="D75" s="112" t="s">
         <v>196</v>
       </c>
-      <c r="E75" s="116"/>
-      <c r="F75" s="117"/>
+      <c r="E75" s="113"/>
+      <c r="F75" s="114"/>
       <c r="G75" s="58" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="H75" s="59"/>
       <c r="I75" s="60" t="s">
@@ -8465,13 +8503,13 @@
       <c r="A76" s="11"/>
       <c r="B76" s="122"/>
       <c r="C76" s="77"/>
-      <c r="D76" s="115" t="s">
+      <c r="D76" s="112" t="s">
         <v>183</v>
       </c>
-      <c r="E76" s="116"/>
-      <c r="F76" s="117"/>
+      <c r="E76" s="113"/>
+      <c r="F76" s="114"/>
       <c r="G76" s="58" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="H76" s="59"/>
       <c r="I76" s="60"/>
@@ -8488,13 +8526,13 @@
         <f>master!C57</f>
         <v>バイブコーディング➌ データベースのデータを準備する</v>
       </c>
-      <c r="D77" s="115" t="s">
+      <c r="D77" s="112" t="s">
         <v>195</v>
       </c>
-      <c r="E77" s="116"/>
-      <c r="F77" s="117"/>
+      <c r="E77" s="113"/>
+      <c r="F77" s="114"/>
       <c r="G77" s="58" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="H77" s="59"/>
       <c r="I77" s="60" t="s">
@@ -8512,13 +8550,13 @@
       <c r="A78" s="11"/>
       <c r="B78" s="122"/>
       <c r="C78" s="77"/>
-      <c r="D78" s="115" t="s">
+      <c r="D78" s="112" t="s">
         <v>183</v>
       </c>
-      <c r="E78" s="116"/>
-      <c r="F78" s="117"/>
+      <c r="E78" s="113"/>
+      <c r="F78" s="114"/>
       <c r="G78" s="58" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="H78" s="59"/>
       <c r="I78" s="60"/>
@@ -8535,13 +8573,13 @@
         <f>master!C58</f>
         <v>バイブコーディング❹ データベース処理とビジネスロジックを作る</v>
       </c>
-      <c r="D79" s="115" t="s">
+      <c r="D79" s="112" t="s">
         <v>194</v>
       </c>
-      <c r="E79" s="116"/>
-      <c r="F79" s="117"/>
+      <c r="E79" s="113"/>
+      <c r="F79" s="114"/>
       <c r="G79" s="58" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="H79" s="59"/>
       <c r="I79" s="60" t="s">
@@ -8559,13 +8597,13 @@
       <c r="A80" s="11"/>
       <c r="B80" s="122"/>
       <c r="C80" s="77"/>
-      <c r="D80" s="115" t="s">
+      <c r="D80" s="112" t="s">
         <v>183</v>
       </c>
-      <c r="E80" s="116"/>
-      <c r="F80" s="117"/>
+      <c r="E80" s="113"/>
+      <c r="F80" s="114"/>
       <c r="G80" s="58" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="H80" s="59"/>
       <c r="I80" s="60"/>
@@ -8582,13 +8620,13 @@
         <f>master!C59</f>
         <v>[解説] RepositoryクラスとSQLの例（抜粋）</v>
       </c>
-      <c r="D81" s="115" t="s">
+      <c r="D81" s="112" t="s">
         <v>184</v>
       </c>
-      <c r="E81" s="116"/>
-      <c r="F81" s="117"/>
+      <c r="E81" s="113"/>
+      <c r="F81" s="114"/>
       <c r="G81" s="58" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="H81" s="59"/>
       <c r="I81" s="60" t="s">
@@ -8609,13 +8647,13 @@
         <f>master!C60</f>
         <v>[解説] Entity/Modelクラスの例（抜粋）</v>
       </c>
-      <c r="D82" s="115" t="s">
+      <c r="D82" s="112" t="s">
         <v>185</v>
       </c>
-      <c r="E82" s="116"/>
-      <c r="F82" s="117"/>
+      <c r="E82" s="113"/>
+      <c r="F82" s="114"/>
       <c r="G82" s="58" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="H82" s="59"/>
       <c r="I82" s="60" t="s">
@@ -8636,13 +8674,13 @@
         <f>master!C61</f>
         <v>[解説] Serviceクラスの例（抜粋）</v>
       </c>
-      <c r="D83" s="115" t="s">
+      <c r="D83" s="112" t="s">
         <v>186</v>
       </c>
-      <c r="E83" s="116"/>
-      <c r="F83" s="117"/>
+      <c r="E83" s="113"/>
+      <c r="F83" s="114"/>
       <c r="G83" s="58" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="H83" s="59"/>
       <c r="I83" s="60" t="s">
@@ -8663,13 +8701,13 @@
         <f>master!C62</f>
         <v>バイブコーディング❺ モックアップをもとに画面表示/処理を作る</v>
       </c>
-      <c r="D84" s="115" t="s">
+      <c r="D84" s="112" t="s">
         <v>193</v>
       </c>
-      <c r="E84" s="116"/>
-      <c r="F84" s="117"/>
+      <c r="E84" s="113"/>
+      <c r="F84" s="114"/>
       <c r="G84" s="58" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="H84" s="59"/>
       <c r="I84" s="60" t="s">
@@ -8687,13 +8725,13 @@
       <c r="A85" s="11"/>
       <c r="B85" s="122"/>
       <c r="C85" s="77"/>
-      <c r="D85" s="115" t="s">
+      <c r="D85" s="112" t="s">
         <v>183</v>
       </c>
-      <c r="E85" s="116"/>
-      <c r="F85" s="117"/>
+      <c r="E85" s="113"/>
+      <c r="F85" s="114"/>
       <c r="G85" s="58" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="H85" s="59"/>
       <c r="I85" s="60"/>
@@ -8710,13 +8748,13 @@
         <f>master!C63</f>
         <v>[解説] Controllerクラスの例（抜粋）</v>
       </c>
-      <c r="D86" s="115" t="s">
+      <c r="D86" s="112" t="s">
         <v>187</v>
       </c>
-      <c r="E86" s="116"/>
-      <c r="F86" s="117"/>
+      <c r="E86" s="113"/>
+      <c r="F86" s="114"/>
       <c r="G86" s="58" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="H86" s="59"/>
       <c r="I86" s="60" t="s">
@@ -8737,13 +8775,13 @@
         <f>master!C64</f>
         <v>[解説] Thymeleafテンプレートの例（抜粋）</v>
       </c>
-      <c r="D87" s="115" t="s">
+      <c r="D87" s="112" t="s">
         <v>188</v>
       </c>
-      <c r="E87" s="116"/>
-      <c r="F87" s="117"/>
+      <c r="E87" s="113"/>
+      <c r="F87" s="114"/>
       <c r="G87" s="58" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="H87" s="59"/>
       <c r="I87" s="60" t="s">
@@ -8764,13 +8802,13 @@
         <f>master!C65</f>
         <v>[解説] Formクラスの例（抜粋）</v>
       </c>
-      <c r="D88" s="115" t="s">
+      <c r="D88" s="112" t="s">
         <v>189</v>
       </c>
-      <c r="E88" s="116"/>
-      <c r="F88" s="117"/>
+      <c r="E88" s="113"/>
+      <c r="F88" s="114"/>
       <c r="G88" s="58" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="H88" s="59"/>
       <c r="I88" s="60" t="s">
@@ -8791,13 +8829,13 @@
         <f>master!C66</f>
         <v>バイブコーディング❻ 動作を確認する</v>
       </c>
-      <c r="D89" s="115" t="s">
+      <c r="D89" s="112" t="s">
         <v>190</v>
       </c>
-      <c r="E89" s="116"/>
-      <c r="F89" s="117"/>
+      <c r="E89" s="113"/>
+      <c r="F89" s="114"/>
       <c r="G89" s="58" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="H89" s="59"/>
       <c r="I89" s="60" t="s">
@@ -8815,13 +8853,13 @@
       <c r="A90" s="11"/>
       <c r="B90" s="123"/>
       <c r="C90" s="77"/>
-      <c r="D90" s="115" t="s">
+      <c r="D90" s="112" t="s">
         <v>197</v>
       </c>
-      <c r="E90" s="116"/>
-      <c r="F90" s="117"/>
+      <c r="E90" s="113"/>
+      <c r="F90" s="114"/>
       <c r="G90" s="58" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="H90" s="59"/>
       <c r="I90" s="60" t="s">
@@ -8845,13 +8883,13 @@
         <f>master!C69</f>
         <v>はじめに</v>
       </c>
-      <c r="D91" s="109" t="s">
-        <v>417</v>
-      </c>
-      <c r="E91" s="110"/>
-      <c r="F91" s="111"/>
+      <c r="D91" s="118" t="s">
+        <v>412</v>
+      </c>
+      <c r="E91" s="119"/>
+      <c r="F91" s="120"/>
       <c r="G91" s="48" t="s">
-        <v>335</v>
+        <v>332</v>
       </c>
       <c r="H91" s="12"/>
       <c r="I91" s="46" t="s">
@@ -8872,13 +8910,13 @@
         <f>master!C70</f>
         <v>バージョン管理とは</v>
       </c>
-      <c r="D92" s="109" t="s">
-        <v>392</v>
-      </c>
-      <c r="E92" s="110"/>
-      <c r="F92" s="111"/>
+      <c r="D92" s="118" t="s">
+        <v>387</v>
+      </c>
+      <c r="E92" s="119"/>
+      <c r="F92" s="120"/>
       <c r="G92" s="48" t="s">
-        <v>334</v>
+        <v>331</v>
       </c>
       <c r="H92" s="12"/>
       <c r="I92" s="46" t="s">
@@ -8899,13 +8937,13 @@
         <f>master!C71</f>
         <v>Gitの概要</v>
       </c>
-      <c r="D93" s="109" t="s">
-        <v>393</v>
-      </c>
-      <c r="E93" s="110"/>
-      <c r="F93" s="111"/>
+      <c r="D93" s="118" t="s">
+        <v>388</v>
+      </c>
+      <c r="E93" s="119"/>
+      <c r="F93" s="120"/>
       <c r="G93" s="48" t="s">
-        <v>394</v>
+        <v>389</v>
       </c>
       <c r="H93" s="12"/>
       <c r="I93" s="46" t="s">
@@ -8929,13 +8967,13 @@
         <f>master!C72</f>
         <v>はじめに</v>
       </c>
-      <c r="D94" s="109" t="s">
-        <v>416</v>
-      </c>
-      <c r="E94" s="110"/>
-      <c r="F94" s="111"/>
+      <c r="D94" s="118" t="s">
+        <v>411</v>
+      </c>
+      <c r="E94" s="119"/>
+      <c r="F94" s="120"/>
       <c r="G94" s="48" t="s">
-        <v>395</v>
+        <v>390</v>
       </c>
       <c r="H94" s="12"/>
       <c r="I94" s="46" t="s">
@@ -8956,13 +8994,13 @@
         <f>master!C73</f>
         <v>ワーキングツリー</v>
       </c>
-      <c r="D95" s="109" t="s">
-        <v>396</v>
-      </c>
-      <c r="E95" s="110"/>
-      <c r="F95" s="111"/>
+      <c r="D95" s="118" t="s">
+        <v>391</v>
+      </c>
+      <c r="E95" s="119"/>
+      <c r="F95" s="120"/>
       <c r="G95" s="48" t="s">
-        <v>334</v>
+        <v>331</v>
       </c>
       <c r="H95" s="12"/>
       <c r="I95" s="46" t="s">
@@ -8983,13 +9021,13 @@
         <f>master!C74</f>
         <v>ステージングエリア</v>
       </c>
-      <c r="D96" s="109" t="s">
-        <v>397</v>
-      </c>
-      <c r="E96" s="110"/>
-      <c r="F96" s="111"/>
+      <c r="D96" s="118" t="s">
+        <v>392</v>
+      </c>
+      <c r="E96" s="119"/>
+      <c r="F96" s="120"/>
       <c r="G96" s="48" t="s">
-        <v>334</v>
+        <v>331</v>
       </c>
       <c r="H96" s="12"/>
       <c r="I96" s="46" t="s">
@@ -9010,13 +9048,13 @@
         <f>master!C75</f>
         <v>ローカルリポジトリ</v>
       </c>
-      <c r="D97" s="109" t="s">
-        <v>398</v>
-      </c>
-      <c r="E97" s="110"/>
-      <c r="F97" s="111"/>
+      <c r="D97" s="118" t="s">
+        <v>393</v>
+      </c>
+      <c r="E97" s="119"/>
+      <c r="F97" s="120"/>
       <c r="G97" s="48" t="s">
-        <v>334</v>
+        <v>331</v>
       </c>
       <c r="H97" s="12"/>
       <c r="I97" s="46" t="s">
@@ -9037,13 +9075,13 @@
         <f>master!C76</f>
         <v>リモートリポジトリ</v>
       </c>
-      <c r="D98" s="109" t="s">
-        <v>399</v>
-      </c>
-      <c r="E98" s="110"/>
-      <c r="F98" s="111"/>
+      <c r="D98" s="118" t="s">
+        <v>394</v>
+      </c>
+      <c r="E98" s="119"/>
+      <c r="F98" s="120"/>
       <c r="G98" s="48" t="s">
-        <v>335</v>
+        <v>332</v>
       </c>
       <c r="H98" s="12"/>
       <c r="I98" s="46" t="s">
@@ -9067,13 +9105,13 @@
         <f>master!C77</f>
         <v>はじめに</v>
       </c>
-      <c r="D99" s="109" t="s">
-        <v>415</v>
-      </c>
-      <c r="E99" s="110"/>
-      <c r="F99" s="111"/>
+      <c r="D99" s="118" t="s">
+        <v>410</v>
+      </c>
+      <c r="E99" s="119"/>
+      <c r="F99" s="120"/>
       <c r="G99" s="48" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
       <c r="H99" s="12"/>
       <c r="I99" s="46" t="s">
@@ -9094,13 +9132,13 @@
         <f>master!C78</f>
         <v>リポジトリの作成</v>
       </c>
-      <c r="D100" s="109" t="s">
-        <v>401</v>
-      </c>
-      <c r="E100" s="110"/>
-      <c r="F100" s="111"/>
+      <c r="D100" s="118" t="s">
+        <v>396</v>
+      </c>
+      <c r="E100" s="119"/>
+      <c r="F100" s="120"/>
       <c r="G100" s="48" t="s">
-        <v>334</v>
+        <v>331</v>
       </c>
       <c r="H100" s="12"/>
       <c r="I100" s="46" t="s">
@@ -9121,13 +9159,13 @@
         <f>master!C79</f>
         <v>ファイルの変更</v>
       </c>
-      <c r="D101" s="109" t="s">
-        <v>402</v>
-      </c>
-      <c r="E101" s="110"/>
-      <c r="F101" s="111"/>
+      <c r="D101" s="118" t="s">
+        <v>397</v>
+      </c>
+      <c r="E101" s="119"/>
+      <c r="F101" s="120"/>
       <c r="G101" s="48" t="s">
-        <v>334</v>
+        <v>331</v>
       </c>
       <c r="H101" s="12"/>
       <c r="I101" s="46" t="s">
@@ -9148,13 +9186,13 @@
         <f>master!C80</f>
         <v>変更内容の確認</v>
       </c>
-      <c r="D102" s="109" t="s">
-        <v>403</v>
-      </c>
-      <c r="E102" s="110"/>
-      <c r="F102" s="111"/>
+      <c r="D102" s="118" t="s">
+        <v>398</v>
+      </c>
+      <c r="E102" s="119"/>
+      <c r="F102" s="120"/>
       <c r="G102" s="48" t="s">
-        <v>334</v>
+        <v>331</v>
       </c>
       <c r="H102" s="12"/>
       <c r="I102" s="46" t="s">
@@ -9175,13 +9213,13 @@
         <f>master!C81</f>
         <v>変更内容のステージ</v>
       </c>
-      <c r="D103" s="109" t="s">
-        <v>404</v>
-      </c>
-      <c r="E103" s="110"/>
-      <c r="F103" s="111"/>
+      <c r="D103" s="118" t="s">
+        <v>399</v>
+      </c>
+      <c r="E103" s="119"/>
+      <c r="F103" s="120"/>
       <c r="G103" s="48" t="s">
-        <v>334</v>
+        <v>331</v>
       </c>
       <c r="H103" s="12"/>
       <c r="I103" s="46" t="s">
@@ -9202,13 +9240,13 @@
         <f>master!C82</f>
         <v>変更内容のコミット</v>
       </c>
-      <c r="D104" s="109" t="s">
-        <v>405</v>
-      </c>
-      <c r="E104" s="110"/>
-      <c r="F104" s="111"/>
+      <c r="D104" s="118" t="s">
+        <v>400</v>
+      </c>
+      <c r="E104" s="119"/>
+      <c r="F104" s="120"/>
       <c r="G104" s="48" t="s">
-        <v>334</v>
+        <v>331</v>
       </c>
       <c r="H104" s="12"/>
       <c r="I104" s="46" t="s">
@@ -9229,13 +9267,13 @@
         <f>master!C83</f>
         <v>ワーキングツリーの変更の取り消し</v>
       </c>
-      <c r="D105" s="109" t="s">
-        <v>406</v>
-      </c>
-      <c r="E105" s="110"/>
-      <c r="F105" s="111"/>
+      <c r="D105" s="118" t="s">
+        <v>401</v>
+      </c>
+      <c r="E105" s="119"/>
+      <c r="F105" s="120"/>
       <c r="G105" s="48" t="s">
-        <v>334</v>
+        <v>331</v>
       </c>
       <c r="H105" s="12"/>
       <c r="I105" s="46" t="s">
@@ -9256,13 +9294,13 @@
         <f>master!C84</f>
         <v>ステージングの取り消し</v>
       </c>
-      <c r="D106" s="109" t="s">
-        <v>407</v>
-      </c>
-      <c r="E106" s="110"/>
-      <c r="F106" s="111"/>
+      <c r="D106" s="118" t="s">
+        <v>402</v>
+      </c>
+      <c r="E106" s="119"/>
+      <c r="F106" s="120"/>
       <c r="G106" s="48" t="s">
-        <v>334</v>
+        <v>331</v>
       </c>
       <c r="H106" s="12"/>
       <c r="I106" s="46" t="s">
@@ -9283,13 +9321,13 @@
         <f>master!C85</f>
         <v>コミットの打ち消し</v>
       </c>
-      <c r="D107" s="109" t="s">
-        <v>408</v>
-      </c>
-      <c r="E107" s="110"/>
-      <c r="F107" s="111"/>
+      <c r="D107" s="118" t="s">
+        <v>403</v>
+      </c>
+      <c r="E107" s="119"/>
+      <c r="F107" s="120"/>
       <c r="G107" s="48" t="s">
-        <v>334</v>
+        <v>331</v>
       </c>
       <c r="H107" s="12"/>
       <c r="I107" s="46" t="s">
@@ -9313,13 +9351,13 @@
         <f>master!C86</f>
         <v>はじめに</v>
       </c>
-      <c r="D108" s="109" t="s">
-        <v>413</v>
-      </c>
-      <c r="E108" s="110"/>
-      <c r="F108" s="111"/>
+      <c r="D108" s="118" t="s">
+        <v>408</v>
+      </c>
+      <c r="E108" s="119"/>
+      <c r="F108" s="120"/>
       <c r="G108" s="48" t="s">
-        <v>395</v>
+        <v>390</v>
       </c>
       <c r="H108" s="12"/>
       <c r="I108" s="46" t="s">
@@ -9329,7 +9367,7 @@
         <v>0</v>
       </c>
       <c r="K108" s="89" t="s">
-        <v>441</v>
+        <v>436</v>
       </c>
       <c r="L108" s="6"/>
       <c r="M108" s="6"/>
@@ -9342,13 +9380,13 @@
         <f>master!C87</f>
         <v>リポジトリの取得</v>
       </c>
-      <c r="D109" s="109" t="s">
-        <v>409</v>
-      </c>
-      <c r="E109" s="110"/>
-      <c r="F109" s="111"/>
+      <c r="D109" s="118" t="s">
+        <v>404</v>
+      </c>
+      <c r="E109" s="119"/>
+      <c r="F109" s="120"/>
       <c r="G109" s="48" t="s">
-        <v>334</v>
+        <v>331</v>
       </c>
       <c r="H109" s="12"/>
       <c r="I109" s="46" t="s">
@@ -9358,7 +9396,7 @@
         <v>0</v>
       </c>
       <c r="K109" s="89" t="s">
-        <v>441</v>
+        <v>436</v>
       </c>
       <c r="L109" s="6"/>
       <c r="M109" s="6"/>
@@ -9371,13 +9409,13 @@
         <f>master!C88</f>
         <v>リモートからの取得</v>
       </c>
-      <c r="D110" s="109" t="s">
-        <v>410</v>
-      </c>
-      <c r="E110" s="110"/>
-      <c r="F110" s="111"/>
+      <c r="D110" s="118" t="s">
+        <v>405</v>
+      </c>
+      <c r="E110" s="119"/>
+      <c r="F110" s="120"/>
       <c r="G110" s="48" t="s">
-        <v>334</v>
+        <v>331</v>
       </c>
       <c r="H110" s="12"/>
       <c r="I110" s="46" t="s">
@@ -9387,7 +9425,7 @@
         <v>0</v>
       </c>
       <c r="K110" s="89" t="s">
-        <v>441</v>
+        <v>436</v>
       </c>
       <c r="L110" s="6"/>
       <c r="M110" s="6"/>
@@ -9400,13 +9438,13 @@
         <f>master!C89</f>
         <v>リモートからの取得と反映</v>
       </c>
-      <c r="D111" s="109" t="s">
-        <v>412</v>
-      </c>
-      <c r="E111" s="110"/>
-      <c r="F111" s="111"/>
+      <c r="D111" s="118" t="s">
+        <v>407</v>
+      </c>
+      <c r="E111" s="119"/>
+      <c r="F111" s="120"/>
       <c r="G111" s="48" t="s">
-        <v>334</v>
+        <v>331</v>
       </c>
       <c r="H111" s="12"/>
       <c r="I111" s="46" t="s">
@@ -9416,7 +9454,7 @@
         <v>0</v>
       </c>
       <c r="K111" s="89" t="s">
-        <v>441</v>
+        <v>436</v>
       </c>
       <c r="L111" s="6"/>
       <c r="M111" s="6"/>
@@ -9429,13 +9467,13 @@
         <f>master!C90</f>
         <v>リモートへの反映</v>
       </c>
-      <c r="D112" s="109" t="s">
-        <v>411</v>
-      </c>
-      <c r="E112" s="110"/>
-      <c r="F112" s="111"/>
+      <c r="D112" s="118" t="s">
+        <v>406</v>
+      </c>
+      <c r="E112" s="119"/>
+      <c r="F112" s="120"/>
       <c r="G112" s="48" t="s">
-        <v>334</v>
+        <v>331</v>
       </c>
       <c r="H112" s="12"/>
       <c r="I112" s="46" t="s">
@@ -9445,7 +9483,7 @@
         <v>0</v>
       </c>
       <c r="K112" s="89" t="s">
-        <v>441</v>
+        <v>436</v>
       </c>
       <c r="L112" s="6"/>
       <c r="M112" s="6"/>
@@ -9461,13 +9499,13 @@
         <f>master!C91</f>
         <v>はじめに</v>
       </c>
-      <c r="D113" s="109" t="s">
-        <v>414</v>
-      </c>
-      <c r="E113" s="110"/>
-      <c r="F113" s="111"/>
+      <c r="D113" s="118" t="s">
+        <v>409</v>
+      </c>
+      <c r="E113" s="119"/>
+      <c r="F113" s="120"/>
       <c r="G113" s="48" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
       <c r="H113" s="12"/>
       <c r="I113" s="46" t="s">
@@ -9477,7 +9515,7 @@
         <v>0</v>
       </c>
       <c r="K113" s="89" t="s">
-        <v>439</v>
+        <v>434</v>
       </c>
       <c r="L113" s="6"/>
       <c r="M113" s="6"/>
@@ -9490,13 +9528,13 @@
         <f>master!C92</f>
         <v>ブランチとは</v>
       </c>
-      <c r="D114" s="109" t="s">
-        <v>418</v>
-      </c>
-      <c r="E114" s="110"/>
-      <c r="F114" s="111"/>
+      <c r="D114" s="118" t="s">
+        <v>413</v>
+      </c>
+      <c r="E114" s="119"/>
+      <c r="F114" s="120"/>
       <c r="G114" s="48" t="s">
-        <v>334</v>
+        <v>331</v>
       </c>
       <c r="H114" s="12"/>
       <c r="I114" s="46" t="s">
@@ -9517,13 +9555,13 @@
         <f>master!C93</f>
         <v>ブランチの作成</v>
       </c>
-      <c r="D115" s="109" t="s">
-        <v>419</v>
-      </c>
-      <c r="E115" s="110"/>
-      <c r="F115" s="111"/>
+      <c r="D115" s="118" t="s">
+        <v>414</v>
+      </c>
+      <c r="E115" s="119"/>
+      <c r="F115" s="120"/>
       <c r="G115" s="48" t="s">
-        <v>334</v>
+        <v>331</v>
       </c>
       <c r="H115" s="12"/>
       <c r="I115" s="46" t="s">
@@ -9544,13 +9582,13 @@
         <f>master!C94</f>
         <v>ブランチの切り替え</v>
       </c>
-      <c r="D116" s="109" t="s">
-        <v>420</v>
-      </c>
-      <c r="E116" s="110"/>
-      <c r="F116" s="111"/>
+      <c r="D116" s="118" t="s">
+        <v>415</v>
+      </c>
+      <c r="E116" s="119"/>
+      <c r="F116" s="120"/>
       <c r="G116" s="48" t="s">
-        <v>334</v>
+        <v>331</v>
       </c>
       <c r="H116" s="12"/>
       <c r="I116" s="46" t="s">
@@ -9571,13 +9609,13 @@
         <f>master!C95</f>
         <v>ブランチのマージ</v>
       </c>
-      <c r="D117" s="109" t="s">
-        <v>421</v>
-      </c>
-      <c r="E117" s="110"/>
-      <c r="F117" s="111"/>
+      <c r="D117" s="118" t="s">
+        <v>416</v>
+      </c>
+      <c r="E117" s="119"/>
+      <c r="F117" s="120"/>
       <c r="G117" s="48" t="s">
-        <v>334</v>
+        <v>331</v>
       </c>
       <c r="H117" s="12"/>
       <c r="I117" s="46" t="s">
@@ -9598,13 +9636,13 @@
         <f>master!C96</f>
         <v>コンフリクトの解消</v>
       </c>
-      <c r="D118" s="109" t="s">
-        <v>423</v>
-      </c>
-      <c r="E118" s="110"/>
-      <c r="F118" s="111"/>
+      <c r="D118" s="118" t="s">
+        <v>418</v>
+      </c>
+      <c r="E118" s="119"/>
+      <c r="F118" s="120"/>
       <c r="G118" s="48" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="H118" s="12"/>
       <c r="I118" s="46" t="s">
@@ -9628,13 +9666,13 @@
         <f>master!C97</f>
         <v>はじめに</v>
       </c>
-      <c r="D119" s="109" t="s">
-        <v>422</v>
-      </c>
-      <c r="E119" s="110"/>
-      <c r="F119" s="111"/>
+      <c r="D119" s="118" t="s">
+        <v>417</v>
+      </c>
+      <c r="E119" s="119"/>
+      <c r="F119" s="120"/>
       <c r="G119" s="48" t="s">
-        <v>395</v>
+        <v>390</v>
       </c>
       <c r="H119" s="12"/>
       <c r="I119" s="46" t="s">
@@ -9655,13 +9693,13 @@
         <f>master!C98</f>
         <v>VSCodeのソース管理機能</v>
       </c>
-      <c r="D120" s="109" t="s">
-        <v>424</v>
-      </c>
-      <c r="E120" s="110"/>
-      <c r="F120" s="111"/>
+      <c r="D120" s="118" t="s">
+        <v>419</v>
+      </c>
+      <c r="E120" s="119"/>
+      <c r="F120" s="120"/>
       <c r="G120" s="48" t="s">
-        <v>425</v>
+        <v>420</v>
       </c>
       <c r="H120" s="12"/>
       <c r="I120" s="46" t="s">
@@ -9682,13 +9720,13 @@
         <f>master!C99</f>
         <v>ローカルリポジトリの操作</v>
       </c>
-      <c r="D121" s="109" t="s">
-        <v>436</v>
-      </c>
-      <c r="E121" s="110"/>
-      <c r="F121" s="111"/>
+      <c r="D121" s="118" t="s">
+        <v>431</v>
+      </c>
+      <c r="E121" s="119"/>
+      <c r="F121" s="120"/>
       <c r="G121" s="48" t="s">
-        <v>435</v>
+        <v>430</v>
       </c>
       <c r="H121" s="12"/>
       <c r="I121" s="46" t="s">
@@ -9709,13 +9747,13 @@
         <f>master!C100</f>
         <v>リモートリポジトリの操作</v>
       </c>
-      <c r="D122" s="109" t="s">
-        <v>426</v>
-      </c>
-      <c r="E122" s="110"/>
-      <c r="F122" s="111"/>
+      <c r="D122" s="118" t="s">
+        <v>421</v>
+      </c>
+      <c r="E122" s="119"/>
+      <c r="F122" s="120"/>
       <c r="G122" s="48" t="s">
-        <v>336</v>
+        <v>333</v>
       </c>
       <c r="H122" s="12"/>
       <c r="I122" s="46" t="s">
@@ -9725,7 +9763,7 @@
         <v>0</v>
       </c>
       <c r="K122" s="89" t="s">
-        <v>441</v>
+        <v>436</v>
       </c>
       <c r="L122" s="6"/>
       <c r="M122" s="6"/>
@@ -9738,13 +9776,13 @@
         <f>master!C101</f>
         <v>ブランチの操作</v>
       </c>
-      <c r="D123" s="109" t="s">
-        <v>437</v>
-      </c>
-      <c r="E123" s="110"/>
-      <c r="F123" s="111"/>
+      <c r="D123" s="118" t="s">
+        <v>432</v>
+      </c>
+      <c r="E123" s="119"/>
+      <c r="F123" s="120"/>
       <c r="G123" s="48" t="s">
-        <v>438</v>
+        <v>433</v>
       </c>
       <c r="H123" s="12"/>
       <c r="I123" s="46" t="s">
@@ -9754,7 +9792,7 @@
         <v>0</v>
       </c>
       <c r="K123" s="89" t="s">
-        <v>440</v>
+        <v>435</v>
       </c>
       <c r="L123" s="6"/>
       <c r="M123" s="6"/>
@@ -9770,11 +9808,11 @@
         <f>master!C103</f>
         <v>はじめに</v>
       </c>
-      <c r="D124" s="115"/>
-      <c r="E124" s="116"/>
-      <c r="F124" s="117"/>
+      <c r="D124" s="112"/>
+      <c r="E124" s="113"/>
+      <c r="F124" s="114"/>
       <c r="G124" s="58" t="s">
-        <v>338</v>
+        <v>335</v>
       </c>
       <c r="H124" s="59"/>
       <c r="I124" s="60" t="s">
@@ -9795,13 +9833,13 @@
         <f>master!C104</f>
         <v>演習の構成</v>
       </c>
-      <c r="D125" s="115" t="s">
-        <v>428</v>
-      </c>
-      <c r="E125" s="116"/>
-      <c r="F125" s="117"/>
+      <c r="D125" s="112" t="s">
+        <v>423</v>
+      </c>
+      <c r="E125" s="113"/>
+      <c r="F125" s="114"/>
       <c r="G125" s="58" t="s">
-        <v>427</v>
+        <v>422</v>
       </c>
       <c r="H125" s="59"/>
       <c r="I125" s="60" t="s">
@@ -9822,13 +9860,13 @@
         <f>master!C105</f>
         <v>演習で利用するソフトウェア</v>
       </c>
-      <c r="D126" s="115" t="s">
-        <v>429</v>
-      </c>
-      <c r="E126" s="116"/>
-      <c r="F126" s="117"/>
+      <c r="D126" s="112" t="s">
+        <v>424</v>
+      </c>
+      <c r="E126" s="113"/>
+      <c r="F126" s="114"/>
       <c r="G126" s="58" t="s">
-        <v>427</v>
+        <v>422</v>
       </c>
       <c r="H126" s="59"/>
       <c r="I126" s="60" t="s">
@@ -9838,7 +9876,7 @@
         <v>6.9444444444444447E-4</v>
       </c>
       <c r="K126" s="62" t="s">
-        <v>442</v>
+        <v>437</v>
       </c>
       <c r="L126" s="6"/>
       <c r="M126" s="6"/>
@@ -9854,13 +9892,13 @@
         <f>master!C106</f>
         <v>演習の前に</v>
       </c>
-      <c r="D127" s="115" t="s">
-        <v>433</v>
-      </c>
-      <c r="E127" s="116"/>
-      <c r="F127" s="117"/>
+      <c r="D127" s="112" t="s">
+        <v>428</v>
+      </c>
+      <c r="E127" s="113"/>
+      <c r="F127" s="114"/>
       <c r="G127" s="58" t="s">
-        <v>432</v>
+        <v>427</v>
       </c>
       <c r="H127" s="59"/>
       <c r="I127" s="60" t="s">
@@ -9881,13 +9919,13 @@
         <f>master!C107</f>
         <v>VS Codeによるリポジトリの作成</v>
       </c>
-      <c r="D128" s="115" t="s">
-        <v>430</v>
-      </c>
-      <c r="E128" s="116"/>
-      <c r="F128" s="117"/>
+      <c r="D128" s="112" t="s">
+        <v>425</v>
+      </c>
+      <c r="E128" s="113"/>
+      <c r="F128" s="114"/>
       <c r="G128" s="58" t="s">
-        <v>431</v>
+        <v>426</v>
       </c>
       <c r="H128" s="59"/>
       <c r="I128" s="60" t="s">
@@ -9908,13 +9946,13 @@
         <f>master!C108</f>
         <v>VS Codeによる変更内容の確認</v>
       </c>
-      <c r="D129" s="115" t="s">
-        <v>430</v>
-      </c>
-      <c r="E129" s="116"/>
-      <c r="F129" s="117"/>
+      <c r="D129" s="112" t="s">
+        <v>425</v>
+      </c>
+      <c r="E129" s="113"/>
+      <c r="F129" s="114"/>
       <c r="G129" s="58" t="s">
-        <v>431</v>
+        <v>426</v>
       </c>
       <c r="H129" s="59"/>
       <c r="I129" s="60" t="s">
@@ -9935,13 +9973,13 @@
         <f>master!C109</f>
         <v>VS Codeによる変更内容のステージング</v>
       </c>
-      <c r="D130" s="115" t="s">
-        <v>430</v>
-      </c>
-      <c r="E130" s="116"/>
-      <c r="F130" s="117"/>
+      <c r="D130" s="112" t="s">
+        <v>425</v>
+      </c>
+      <c r="E130" s="113"/>
+      <c r="F130" s="114"/>
       <c r="G130" s="58" t="s">
-        <v>431</v>
+        <v>426</v>
       </c>
       <c r="H130" s="59"/>
       <c r="I130" s="60" t="s">
@@ -9962,13 +10000,13 @@
         <f>master!C110</f>
         <v>VS Codeによる変更内容のコミット</v>
       </c>
-      <c r="D131" s="115" t="s">
-        <v>430</v>
-      </c>
-      <c r="E131" s="116"/>
-      <c r="F131" s="117"/>
+      <c r="D131" s="112" t="s">
+        <v>425</v>
+      </c>
+      <c r="E131" s="113"/>
+      <c r="F131" s="114"/>
       <c r="G131" s="58" t="s">
-        <v>431</v>
+        <v>426</v>
       </c>
       <c r="H131" s="59"/>
       <c r="I131" s="60" t="s">
@@ -9992,13 +10030,13 @@
         <f>master!C111</f>
         <v>演習の前に</v>
       </c>
-      <c r="D132" s="115" t="s">
-        <v>434</v>
-      </c>
-      <c r="E132" s="116"/>
-      <c r="F132" s="117"/>
+      <c r="D132" s="112" t="s">
+        <v>429</v>
+      </c>
+      <c r="E132" s="113"/>
+      <c r="F132" s="114"/>
       <c r="G132" s="58" t="s">
-        <v>337</v>
+        <v>334</v>
       </c>
       <c r="H132" s="59"/>
       <c r="I132" s="60" t="s">
@@ -10008,7 +10046,7 @@
         <v>0</v>
       </c>
       <c r="K132" s="62" t="s">
-        <v>440</v>
+        <v>435</v>
       </c>
       <c r="L132" s="6"/>
       <c r="M132" s="6"/>
@@ -10021,13 +10059,13 @@
         <f>master!C112</f>
         <v>VS Codeによるブランチの作成</v>
       </c>
-      <c r="D133" s="115" t="s">
-        <v>430</v>
-      </c>
-      <c r="E133" s="116"/>
-      <c r="F133" s="117"/>
+      <c r="D133" s="112" t="s">
+        <v>425</v>
+      </c>
+      <c r="E133" s="113"/>
+      <c r="F133" s="114"/>
       <c r="G133" s="58" t="s">
-        <v>431</v>
+        <v>426</v>
       </c>
       <c r="H133" s="59"/>
       <c r="I133" s="60" t="s">
@@ -10037,7 +10075,7 @@
         <v>0</v>
       </c>
       <c r="K133" s="62" t="s">
-        <v>440</v>
+        <v>435</v>
       </c>
       <c r="L133" s="6"/>
       <c r="M133" s="6"/>
@@ -10050,13 +10088,13 @@
         <f>master!C113</f>
         <v>VS Codeによるブランチの切り替え</v>
       </c>
-      <c r="D134" s="115" t="s">
-        <v>430</v>
-      </c>
-      <c r="E134" s="116"/>
-      <c r="F134" s="117"/>
+      <c r="D134" s="112" t="s">
+        <v>425</v>
+      </c>
+      <c r="E134" s="113"/>
+      <c r="F134" s="114"/>
       <c r="G134" s="58" t="s">
-        <v>431</v>
+        <v>426</v>
       </c>
       <c r="H134" s="59"/>
       <c r="I134" s="60" t="s">
@@ -10066,7 +10104,7 @@
         <v>0</v>
       </c>
       <c r="K134" s="62" t="s">
-        <v>440</v>
+        <v>435</v>
       </c>
       <c r="L134" s="6"/>
       <c r="M134" s="6"/>
@@ -10079,13 +10117,13 @@
         <f>master!C114</f>
         <v>VS Codeによるブランチのマージ</v>
       </c>
-      <c r="D135" s="115" t="s">
-        <v>430</v>
-      </c>
-      <c r="E135" s="116"/>
-      <c r="F135" s="117"/>
+      <c r="D135" s="112" t="s">
+        <v>425</v>
+      </c>
+      <c r="E135" s="113"/>
+      <c r="F135" s="114"/>
       <c r="G135" s="58" t="s">
-        <v>431</v>
+        <v>426</v>
       </c>
       <c r="H135" s="59"/>
       <c r="I135" s="60" t="s">
@@ -10095,7 +10133,7 @@
         <v>0</v>
       </c>
       <c r="K135" s="62" t="s">
-        <v>440</v>
+        <v>435</v>
       </c>
       <c r="L135" s="6"/>
       <c r="M135" s="6"/>
@@ -10111,20 +10149,20 @@
         <f>master!C67</f>
         <v>ここから各自で演習を始めましょう。</v>
       </c>
-      <c r="D136" s="115" t="s">
+      <c r="D136" s="112" t="s">
         <v>198</v>
       </c>
-      <c r="E136" s="116"/>
-      <c r="F136" s="117"/>
+      <c r="E136" s="113"/>
+      <c r="F136" s="114"/>
       <c r="G136" s="58" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="H136" s="59"/>
       <c r="I136" s="60" t="s">
-        <v>443</v>
+        <v>438</v>
       </c>
       <c r="J136" s="61" t="s">
-        <v>343</v>
+        <v>338</v>
       </c>
       <c r="K136" s="62"/>
       <c r="L136" s="6"/>
@@ -10133,7 +10171,7 @@
     </row>
     <row r="137" spans="1:14" ht="50.4">
       <c r="A137" s="11"/>
-      <c r="B137" s="112" t="str">
+      <c r="B137" s="109" t="str">
         <f>master!B116</f>
         <v>単体テストとJunitの導入</v>
       </c>
@@ -10141,13 +10179,13 @@
         <f>master!C116</f>
         <v>講義の目的</v>
       </c>
-      <c r="D137" s="109" t="s">
+      <c r="D137" s="118" t="s">
         <v>227</v>
       </c>
-      <c r="E137" s="110"/>
-      <c r="F137" s="111"/>
+      <c r="E137" s="119"/>
+      <c r="F137" s="120"/>
       <c r="G137" s="48" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="H137" s="12"/>
       <c r="I137" s="46" t="s">
@@ -10163,16 +10201,16 @@
     </row>
     <row r="138" spans="1:14" ht="25.2">
       <c r="A138" s="11"/>
-      <c r="B138" s="113"/>
+      <c r="B138" s="110"/>
       <c r="C138" s="78" t="str">
         <f>master!C117</f>
         <v>TERASOLUNA 開発手順　 ※再掲</v>
       </c>
-      <c r="D138" s="109"/>
-      <c r="E138" s="110"/>
-      <c r="F138" s="111"/>
+      <c r="D138" s="118"/>
+      <c r="E138" s="119"/>
+      <c r="F138" s="120"/>
       <c r="G138" s="48" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="H138" s="12"/>
       <c r="I138" s="46" t="s">
@@ -10188,18 +10226,18 @@
     </row>
     <row r="139" spans="1:14" ht="25.2">
       <c r="A139" s="11"/>
-      <c r="B139" s="114"/>
+      <c r="B139" s="111"/>
       <c r="C139" s="78" t="str">
         <f>master!C118</f>
         <v>V字モデル　 ※再掲</v>
       </c>
-      <c r="D139" s="109" t="s">
+      <c r="D139" s="118" t="s">
         <v>228</v>
       </c>
-      <c r="E139" s="110"/>
-      <c r="F139" s="111"/>
+      <c r="E139" s="119"/>
+      <c r="F139" s="120"/>
       <c r="G139" s="48" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="H139" s="12"/>
       <c r="I139" s="46" t="s">
@@ -10215,7 +10253,7 @@
     </row>
     <row r="140" spans="1:14" ht="50.4">
       <c r="A140" s="11"/>
-      <c r="B140" s="112" t="str">
+      <c r="B140" s="109" t="str">
         <f>master!B119</f>
         <v>テストとは</v>
       </c>
@@ -10223,13 +10261,13 @@
         <f>master!C119</f>
         <v>テストとは</v>
       </c>
-      <c r="D140" s="109" t="s">
+      <c r="D140" s="118" t="s">
         <v>229</v>
       </c>
-      <c r="E140" s="110"/>
-      <c r="F140" s="111"/>
+      <c r="E140" s="119"/>
+      <c r="F140" s="120"/>
       <c r="G140" s="48" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="H140" s="12"/>
       <c r="I140" s="46" t="s">
@@ -10245,18 +10283,18 @@
     </row>
     <row r="141" spans="1:14" ht="315">
       <c r="A141" s="11"/>
-      <c r="B141" s="113"/>
+      <c r="B141" s="110"/>
       <c r="C141" s="78" t="str">
         <f>master!C120</f>
         <v>テストの目的</v>
       </c>
-      <c r="D141" s="109" t="s">
+      <c r="D141" s="118" t="s">
         <v>230</v>
       </c>
-      <c r="E141" s="110"/>
-      <c r="F141" s="111"/>
+      <c r="E141" s="119"/>
+      <c r="F141" s="120"/>
       <c r="G141" s="48" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="H141" s="12"/>
       <c r="I141" s="46" t="s">
@@ -10272,18 +10310,18 @@
     </row>
     <row r="142" spans="1:14" ht="25.2">
       <c r="A142" s="11"/>
-      <c r="B142" s="113"/>
+      <c r="B142" s="110"/>
       <c r="C142" s="78" t="str">
         <f>master!C121</f>
         <v>テストを実施しなかった場合…</v>
       </c>
-      <c r="D142" s="109" t="s">
+      <c r="D142" s="118" t="s">
         <v>231</v>
       </c>
-      <c r="E142" s="110"/>
-      <c r="F142" s="111"/>
+      <c r="E142" s="119"/>
+      <c r="F142" s="120"/>
       <c r="G142" s="48" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="H142" s="12"/>
       <c r="I142" s="46" t="s">
@@ -10299,18 +10337,18 @@
     </row>
     <row r="143" spans="1:14" ht="100.8">
       <c r="A143" s="11"/>
-      <c r="B143" s="114"/>
+      <c r="B143" s="111"/>
       <c r="C143" s="78" t="str">
         <f>master!C122</f>
         <v>コラム：テストとデバッグ</v>
       </c>
-      <c r="D143" s="109" t="s">
+      <c r="D143" s="118" t="s">
         <v>232</v>
       </c>
-      <c r="E143" s="110"/>
-      <c r="F143" s="111"/>
+      <c r="E143" s="119"/>
+      <c r="F143" s="120"/>
       <c r="G143" s="48" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="H143" s="12"/>
       <c r="I143" s="46" t="s">
@@ -10326,7 +10364,7 @@
     </row>
     <row r="144" spans="1:14" ht="50.4">
       <c r="A144" s="11"/>
-      <c r="B144" s="112" t="str">
+      <c r="B144" s="109" t="str">
         <f>master!B123</f>
         <v>単体テストとは</v>
       </c>
@@ -10334,13 +10372,13 @@
         <f>master!C123</f>
         <v>単体テスト（Unit Test）とは</v>
       </c>
-      <c r="D144" s="109" t="s">
+      <c r="D144" s="118" t="s">
         <v>233</v>
       </c>
-      <c r="E144" s="110"/>
-      <c r="F144" s="111"/>
+      <c r="E144" s="119"/>
+      <c r="F144" s="120"/>
       <c r="G144" s="48" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="H144" s="12"/>
       <c r="I144" s="46" t="s">
@@ -10356,16 +10394,16 @@
     </row>
     <row r="145" spans="1:14" ht="25.2">
       <c r="A145" s="11"/>
-      <c r="B145" s="113"/>
+      <c r="B145" s="110"/>
       <c r="C145" s="78" t="str">
         <f>master!C124</f>
         <v xml:space="preserve">V字モデル　– 製造/単体テスト –　※再掲 </v>
       </c>
-      <c r="D145" s="109"/>
-      <c r="E145" s="110"/>
-      <c r="F145" s="111"/>
+      <c r="D145" s="118"/>
+      <c r="E145" s="119"/>
+      <c r="F145" s="120"/>
       <c r="G145" s="48" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="H145" s="12"/>
       <c r="I145" s="46" t="s">
@@ -10381,18 +10419,18 @@
     </row>
     <row r="146" spans="1:14" ht="302.39999999999998">
       <c r="A146" s="11"/>
-      <c r="B146" s="113"/>
+      <c r="B146" s="110"/>
       <c r="C146" s="78" t="str">
         <f>master!C125</f>
         <v>テスト設計の流れ</v>
       </c>
-      <c r="D146" s="109" t="s">
+      <c r="D146" s="118" t="s">
         <v>234</v>
       </c>
-      <c r="E146" s="110"/>
-      <c r="F146" s="111"/>
+      <c r="E146" s="119"/>
+      <c r="F146" s="120"/>
       <c r="G146" s="48" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="H146" s="12"/>
       <c r="I146" s="46" t="s">
@@ -10408,18 +10446,18 @@
     </row>
     <row r="147" spans="1:14" ht="37.799999999999997">
       <c r="A147" s="11"/>
-      <c r="B147" s="113"/>
+      <c r="B147" s="110"/>
       <c r="C147" s="78" t="str">
         <f>master!C126</f>
         <v>テスト設計の例</v>
       </c>
-      <c r="D147" s="109" t="s">
+      <c r="D147" s="118" t="s">
         <v>235</v>
       </c>
-      <c r="E147" s="110"/>
-      <c r="F147" s="111"/>
+      <c r="E147" s="119"/>
+      <c r="F147" s="120"/>
       <c r="G147" s="48" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="H147" s="12"/>
       <c r="I147" s="46" t="s">
@@ -10435,18 +10473,18 @@
     </row>
     <row r="148" spans="1:14" ht="75.599999999999994">
       <c r="A148" s="11"/>
-      <c r="B148" s="113"/>
+      <c r="B148" s="110"/>
       <c r="C148" s="78" t="str">
         <f>master!C127</f>
         <v>単体テスト（Unit Test）とは</v>
       </c>
-      <c r="D148" s="109" t="s">
+      <c r="D148" s="118" t="s">
         <v>236</v>
       </c>
-      <c r="E148" s="110"/>
-      <c r="F148" s="111"/>
+      <c r="E148" s="119"/>
+      <c r="F148" s="120"/>
       <c r="G148" s="48" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="H148" s="12"/>
       <c r="I148" s="46" t="s">
@@ -10462,18 +10500,18 @@
     </row>
     <row r="149" spans="1:14" ht="113.4">
       <c r="A149" s="11"/>
-      <c r="B149" s="113"/>
+      <c r="B149" s="110"/>
       <c r="C149" s="78" t="str">
         <f>master!C128</f>
         <v>テスト技法 – ブラックボックステスト技法 –</v>
       </c>
-      <c r="D149" s="109" t="s">
+      <c r="D149" s="118" t="s">
         <v>237</v>
       </c>
-      <c r="E149" s="110"/>
-      <c r="F149" s="111"/>
+      <c r="E149" s="119"/>
+      <c r="F149" s="120"/>
       <c r="G149" s="48" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="H149" s="12"/>
       <c r="I149" s="46" t="s">
@@ -10489,18 +10527,18 @@
     </row>
     <row r="150" spans="1:14" ht="201.6">
       <c r="A150" s="11"/>
-      <c r="B150" s="113"/>
+      <c r="B150" s="110"/>
       <c r="C150" s="78" t="str">
         <f>master!C129</f>
         <v>ブラックボックステスト：同値分割法</v>
       </c>
-      <c r="D150" s="109" t="s">
+      <c r="D150" s="118" t="s">
         <v>240</v>
       </c>
-      <c r="E150" s="110"/>
-      <c r="F150" s="111"/>
+      <c r="E150" s="119"/>
+      <c r="F150" s="120"/>
       <c r="G150" s="48" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="H150" s="12"/>
       <c r="I150" s="46" t="s">
@@ -10516,18 +10554,18 @@
     </row>
     <row r="151" spans="1:14" ht="113.4">
       <c r="A151" s="11"/>
-      <c r="B151" s="113"/>
+      <c r="B151" s="110"/>
       <c r="C151" s="78" t="str">
         <f>master!C130</f>
         <v>ブラックボックステスト：境界値分析</v>
       </c>
-      <c r="D151" s="109" t="s">
+      <c r="D151" s="118" t="s">
         <v>239</v>
       </c>
-      <c r="E151" s="110"/>
-      <c r="F151" s="111"/>
+      <c r="E151" s="119"/>
+      <c r="F151" s="120"/>
       <c r="G151" s="48" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="H151" s="12"/>
       <c r="I151" s="46" t="s">
@@ -10543,18 +10581,18 @@
     </row>
     <row r="152" spans="1:14" ht="176.4">
       <c r="A152" s="11"/>
-      <c r="B152" s="113"/>
+      <c r="B152" s="110"/>
       <c r="C152" s="78" t="str">
         <f>master!C131</f>
         <v>ブラックボックステスト：ディシジョンテーブルテスト</v>
       </c>
-      <c r="D152" s="109" t="s">
+      <c r="D152" s="118" t="s">
         <v>238</v>
       </c>
-      <c r="E152" s="110"/>
-      <c r="F152" s="111"/>
+      <c r="E152" s="119"/>
+      <c r="F152" s="120"/>
       <c r="G152" s="48" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="H152" s="12"/>
       <c r="I152" s="46" t="s">
@@ -10570,18 +10608,18 @@
     </row>
     <row r="153" spans="1:14" ht="37.799999999999997">
       <c r="A153" s="11"/>
-      <c r="B153" s="113"/>
+      <c r="B153" s="110"/>
       <c r="C153" s="78" t="str">
         <f>master!C132</f>
         <v>ブラックボックステスト：状態遷移テスト</v>
       </c>
-      <c r="D153" s="109" t="s">
+      <c r="D153" s="118" t="s">
         <v>241</v>
       </c>
-      <c r="E153" s="110"/>
-      <c r="F153" s="111"/>
+      <c r="E153" s="119"/>
+      <c r="F153" s="120"/>
       <c r="G153" s="48" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="H153" s="12"/>
       <c r="I153" s="46" t="s">
@@ -10597,18 +10635,18 @@
     </row>
     <row r="154" spans="1:14" ht="88.2">
       <c r="A154" s="11"/>
-      <c r="B154" s="113"/>
+      <c r="B154" s="110"/>
       <c r="C154" s="78" t="str">
         <f>master!C133</f>
         <v>テスト技法 – ホワイトボックステスト技法 –</v>
       </c>
-      <c r="D154" s="109" t="s">
+      <c r="D154" s="118" t="s">
         <v>242</v>
       </c>
-      <c r="E154" s="110"/>
-      <c r="F154" s="111"/>
+      <c r="E154" s="119"/>
+      <c r="F154" s="120"/>
       <c r="G154" s="48" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="H154" s="12"/>
       <c r="I154" s="46" t="s">
@@ -10624,18 +10662,18 @@
     </row>
     <row r="155" spans="1:14" ht="151.19999999999999">
       <c r="A155" s="11"/>
-      <c r="B155" s="113"/>
+      <c r="B155" s="110"/>
       <c r="C155" s="78" t="str">
         <f>master!C134</f>
         <v>ホワイトボックステストの評価基準</v>
       </c>
-      <c r="D155" s="109" t="s">
+      <c r="D155" s="118" t="s">
         <v>243</v>
       </c>
-      <c r="E155" s="110"/>
-      <c r="F155" s="111"/>
+      <c r="E155" s="119"/>
+      <c r="F155" s="120"/>
       <c r="G155" s="48" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="H155" s="12"/>
       <c r="I155" s="46" t="s">
@@ -10651,18 +10689,18 @@
     </row>
     <row r="156" spans="1:14" ht="37.799999999999997">
       <c r="A156" s="11"/>
-      <c r="B156" s="113"/>
+      <c r="B156" s="110"/>
       <c r="C156" s="78" t="str">
         <f>master!C135</f>
         <v>ホワイトボックステスト：ステートメントテスト</v>
       </c>
-      <c r="D156" s="109" t="s">
+      <c r="D156" s="118" t="s">
         <v>244</v>
       </c>
-      <c r="E156" s="110"/>
-      <c r="F156" s="111"/>
+      <c r="E156" s="119"/>
+      <c r="F156" s="120"/>
       <c r="G156" s="48" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="H156" s="12"/>
       <c r="I156" s="46" t="s">
@@ -10678,18 +10716,18 @@
     </row>
     <row r="157" spans="1:14" ht="37.799999999999997">
       <c r="A157" s="11"/>
-      <c r="B157" s="113"/>
+      <c r="B157" s="110"/>
       <c r="C157" s="78" t="str">
         <f>master!C136</f>
         <v>ホワイトボックステスト：ブランチテスト</v>
       </c>
-      <c r="D157" s="109" t="s">
+      <c r="D157" s="118" t="s">
         <v>245</v>
       </c>
-      <c r="E157" s="110"/>
-      <c r="F157" s="111"/>
+      <c r="E157" s="119"/>
+      <c r="F157" s="120"/>
       <c r="G157" s="48" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="H157" s="12"/>
       <c r="I157" s="46" t="s">
@@ -10705,18 +10743,18 @@
     </row>
     <row r="158" spans="1:14" ht="37.799999999999997">
       <c r="A158" s="11"/>
-      <c r="B158" s="113"/>
+      <c r="B158" s="110"/>
       <c r="C158" s="78" t="str">
         <f>master!C137</f>
         <v>ホワイトボックステスト：コンディションテスト</v>
       </c>
-      <c r="D158" s="109" t="s">
+      <c r="D158" s="118" t="s">
         <v>246</v>
       </c>
-      <c r="E158" s="110"/>
-      <c r="F158" s="111"/>
+      <c r="E158" s="119"/>
+      <c r="F158" s="120"/>
       <c r="G158" s="48" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="H158" s="12"/>
       <c r="I158" s="46" t="s">
@@ -10732,18 +10770,18 @@
     </row>
     <row r="159" spans="1:14" ht="37.799999999999997">
       <c r="A159" s="11"/>
-      <c r="B159" s="113"/>
+      <c r="B159" s="110"/>
       <c r="C159" s="78" t="str">
         <f>master!C138</f>
         <v>テスト技法 – 経験ベースの技法 –</v>
       </c>
-      <c r="D159" s="109" t="s">
+      <c r="D159" s="118" t="s">
         <v>247</v>
       </c>
-      <c r="E159" s="110"/>
-      <c r="F159" s="111"/>
+      <c r="E159" s="119"/>
+      <c r="F159" s="120"/>
       <c r="G159" s="48" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="H159" s="12"/>
       <c r="I159" s="46" t="s">
@@ -10759,18 +10797,18 @@
     </row>
     <row r="160" spans="1:14" ht="100.8">
       <c r="A160" s="11"/>
-      <c r="B160" s="113"/>
+      <c r="B160" s="110"/>
       <c r="C160" s="78" t="str">
         <f>master!C139</f>
         <v>スタブとドライバ</v>
       </c>
-      <c r="D160" s="109" t="s">
+      <c r="D160" s="118" t="s">
         <v>248</v>
       </c>
-      <c r="E160" s="110"/>
-      <c r="F160" s="111"/>
+      <c r="E160" s="119"/>
+      <c r="F160" s="120"/>
       <c r="G160" s="48" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="H160" s="12"/>
       <c r="I160" s="46" t="s">
@@ -10786,18 +10824,18 @@
     </row>
     <row r="161" spans="1:14" ht="75.599999999999994">
       <c r="A161" s="11"/>
-      <c r="B161" s="114"/>
+      <c r="B161" s="111"/>
       <c r="C161" s="78" t="str">
         <f>master!C140</f>
         <v>スタブとモック</v>
       </c>
-      <c r="D161" s="109" t="s">
+      <c r="D161" s="118" t="s">
         <v>249</v>
       </c>
-      <c r="E161" s="110"/>
-      <c r="F161" s="111"/>
+      <c r="E161" s="119"/>
+      <c r="F161" s="120"/>
       <c r="G161" s="48" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="H161" s="12"/>
       <c r="I161" s="46" t="s">
@@ -10813,7 +10851,7 @@
     </row>
     <row r="162" spans="1:14" ht="37.799999999999997">
       <c r="A162" s="11"/>
-      <c r="B162" s="112" t="str">
+      <c r="B162" s="109" t="str">
         <f>master!B141</f>
         <v>JUnit</v>
       </c>
@@ -10821,13 +10859,13 @@
         <f>master!C141</f>
         <v>JUnitとは</v>
       </c>
-      <c r="D162" s="109" t="s">
+      <c r="D162" s="118" t="s">
         <v>250</v>
       </c>
-      <c r="E162" s="110"/>
-      <c r="F162" s="111"/>
+      <c r="E162" s="119"/>
+      <c r="F162" s="120"/>
       <c r="G162" s="48" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="H162" s="12"/>
       <c r="I162" s="46" t="s">
@@ -10843,16 +10881,16 @@
     </row>
     <row r="163" spans="1:14" ht="25.2">
       <c r="A163" s="11"/>
-      <c r="B163" s="114"/>
+      <c r="B163" s="111"/>
       <c r="C163" s="78" t="str">
         <f>master!C142</f>
         <v>参考文献</v>
       </c>
-      <c r="D163" s="109"/>
-      <c r="E163" s="110"/>
-      <c r="F163" s="111"/>
+      <c r="D163" s="118"/>
+      <c r="E163" s="119"/>
+      <c r="F163" s="120"/>
       <c r="G163" s="48" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="H163" s="12"/>
       <c r="I163" s="46" t="s">
@@ -10876,11 +10914,11 @@
         <f>master!C67</f>
         <v>ここから各自で演習を始めましょう。</v>
       </c>
-      <c r="D164" s="115" t="s">
+      <c r="D164" s="112" t="s">
         <v>251</v>
       </c>
-      <c r="E164" s="116"/>
-      <c r="F164" s="117"/>
+      <c r="E164" s="113"/>
+      <c r="F164" s="114"/>
       <c r="G164" s="58" t="s">
         <v>42</v>
       </c>
@@ -10889,7 +10927,7 @@
         <v>24</v>
       </c>
       <c r="J164" s="61" t="s">
-        <v>343</v>
+        <v>338</v>
       </c>
       <c r="K164" s="62"/>
       <c r="L164" s="6"/>
@@ -10898,7 +10936,7 @@
     </row>
     <row r="165" spans="1:14" ht="25.2">
       <c r="A165" s="11"/>
-      <c r="B165" s="118" t="str">
+      <c r="B165" s="115" t="str">
         <f>master!B144</f>
         <v>課題2の導入</v>
       </c>
@@ -10906,13 +10944,13 @@
         <f>master!C144</f>
         <v>演習課題の概要</v>
       </c>
-      <c r="D165" s="115" t="s">
+      <c r="D165" s="112" t="s">
         <v>267</v>
       </c>
-      <c r="E165" s="116"/>
-      <c r="F165" s="117"/>
+      <c r="E165" s="113"/>
+      <c r="F165" s="114"/>
       <c r="G165" s="58" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="H165" s="59"/>
       <c r="I165" s="60" t="s">
@@ -10928,18 +10966,18 @@
     </row>
     <row r="166" spans="1:14" ht="138.6">
       <c r="A166" s="11"/>
-      <c r="B166" s="119"/>
+      <c r="B166" s="116"/>
       <c r="C166" s="58" t="str">
         <f>master!C145</f>
         <v>[構造理解] Webアプリケーションで必要なもの  ※再掲</v>
       </c>
-      <c r="D166" s="115" t="s">
+      <c r="D166" s="112" t="s">
         <v>268</v>
       </c>
-      <c r="E166" s="116"/>
-      <c r="F166" s="117"/>
+      <c r="E166" s="113"/>
+      <c r="F166" s="114"/>
       <c r="G166" s="58" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="H166" s="59"/>
       <c r="I166" s="60" t="s">
@@ -10955,18 +10993,18 @@
     </row>
     <row r="167" spans="1:14" ht="50.4">
       <c r="A167" s="11"/>
-      <c r="B167" s="119"/>
+      <c r="B167" s="116"/>
       <c r="C167" s="58" t="str">
         <f>master!C146</f>
         <v>テストクラスを作成する単位</v>
       </c>
-      <c r="D167" s="115" t="s">
+      <c r="D167" s="112" t="s">
         <v>269</v>
       </c>
-      <c r="E167" s="116"/>
-      <c r="F167" s="117"/>
+      <c r="E167" s="113"/>
+      <c r="F167" s="114"/>
       <c r="G167" s="58" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="H167" s="59"/>
       <c r="I167" s="60" t="s">
@@ -10982,18 +11020,18 @@
     </row>
     <row r="168" spans="1:14" ht="113.4">
       <c r="A168" s="11"/>
-      <c r="B168" s="120"/>
+      <c r="B168" s="117"/>
       <c r="C168" s="58" t="str">
         <f>master!C147</f>
         <v>JUnitで単体テスト</v>
       </c>
-      <c r="D168" s="115" t="s">
+      <c r="D168" s="112" t="s">
         <v>270</v>
       </c>
-      <c r="E168" s="116"/>
-      <c r="F168" s="117"/>
+      <c r="E168" s="113"/>
+      <c r="F168" s="114"/>
       <c r="G168" s="58" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="H168" s="59"/>
       <c r="I168" s="60" t="s">
@@ -11009,7 +11047,7 @@
     </row>
     <row r="169" spans="1:14" ht="25.2">
       <c r="A169" s="11"/>
-      <c r="B169" s="118" t="str">
+      <c r="B169" s="115" t="str">
         <f>master!B148</f>
         <v>ハンズオン</v>
       </c>
@@ -11017,13 +11055,13 @@
         <f>master!C148</f>
         <v>バイブコーディングで単体テスト – はじめに</v>
       </c>
-      <c r="D169" s="115" t="s">
+      <c r="D169" s="112" t="s">
         <v>271</v>
       </c>
-      <c r="E169" s="116"/>
-      <c r="F169" s="117"/>
+      <c r="E169" s="113"/>
+      <c r="F169" s="114"/>
       <c r="G169" s="58" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="H169" s="59"/>
       <c r="I169" s="60" t="s">
@@ -11039,18 +11077,18 @@
     </row>
     <row r="170" spans="1:14" ht="50.4">
       <c r="A170" s="11"/>
-      <c r="B170" s="119"/>
+      <c r="B170" s="116"/>
       <c r="C170" s="58" t="str">
         <f>master!C149</f>
         <v>バイブコーディング単体テスト①テスト項目表を作る</v>
       </c>
-      <c r="D170" s="115" t="s">
+      <c r="D170" s="112" t="s">
         <v>272</v>
       </c>
-      <c r="E170" s="116"/>
-      <c r="F170" s="117"/>
+      <c r="E170" s="113"/>
+      <c r="F170" s="114"/>
       <c r="G170" s="58" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="H170" s="59"/>
       <c r="I170" s="60" t="s">
@@ -11066,15 +11104,15 @@
     </row>
     <row r="171" spans="1:14" ht="88.2">
       <c r="A171" s="11"/>
-      <c r="B171" s="119"/>
+      <c r="B171" s="116"/>
       <c r="C171" s="58"/>
-      <c r="D171" s="115" t="s">
+      <c r="D171" s="112" t="s">
         <v>183</v>
       </c>
-      <c r="E171" s="116"/>
-      <c r="F171" s="117"/>
+      <c r="E171" s="113"/>
+      <c r="F171" s="114"/>
       <c r="G171" s="58" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="H171" s="59"/>
       <c r="I171" s="60" t="s">
@@ -11090,18 +11128,18 @@
     </row>
     <row r="172" spans="1:14" ht="50.4">
       <c r="A172" s="11"/>
-      <c r="B172" s="119"/>
+      <c r="B172" s="116"/>
       <c r="C172" s="76" t="str">
         <f>master!C150</f>
         <v>バイブコーディング単体テスト②Repositoryのテストを作る</v>
       </c>
-      <c r="D172" s="115" t="s">
+      <c r="D172" s="112" t="s">
         <v>273</v>
       </c>
-      <c r="E172" s="116"/>
-      <c r="F172" s="117"/>
+      <c r="E172" s="113"/>
+      <c r="F172" s="114"/>
       <c r="G172" s="58" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="H172" s="59"/>
       <c r="I172" s="60" t="s">
@@ -11117,15 +11155,15 @@
     </row>
     <row r="173" spans="1:14" ht="88.2">
       <c r="A173" s="11"/>
-      <c r="B173" s="119"/>
+      <c r="B173" s="116"/>
       <c r="C173" s="77"/>
-      <c r="D173" s="115" t="s">
+      <c r="D173" s="112" t="s">
         <v>183</v>
       </c>
-      <c r="E173" s="116"/>
-      <c r="F173" s="117"/>
+      <c r="E173" s="113"/>
+      <c r="F173" s="114"/>
       <c r="G173" s="58" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="H173" s="59"/>
       <c r="I173" s="60" t="s">
@@ -11141,18 +11179,18 @@
     </row>
     <row r="174" spans="1:14" ht="138.6">
       <c r="A174" s="11"/>
-      <c r="B174" s="119"/>
+      <c r="B174" s="116"/>
       <c r="C174" s="58" t="str">
         <f>master!C151</f>
         <v>[解説] Repositoryのテストクラス（抜粋）</v>
       </c>
-      <c r="D174" s="115" t="s">
+      <c r="D174" s="112" t="s">
         <v>275</v>
       </c>
-      <c r="E174" s="116"/>
-      <c r="F174" s="117"/>
+      <c r="E174" s="113"/>
+      <c r="F174" s="114"/>
       <c r="G174" s="58" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="H174" s="59"/>
       <c r="I174" s="60" t="s">
@@ -11168,18 +11206,18 @@
     </row>
     <row r="175" spans="1:14" ht="50.4">
       <c r="A175" s="11"/>
-      <c r="B175" s="119"/>
+      <c r="B175" s="116"/>
       <c r="C175" s="76" t="str">
         <f>master!C152</f>
         <v>バイブコーディング単体テスト③Serviceのテストを作る</v>
       </c>
-      <c r="D175" s="115" t="s">
+      <c r="D175" s="112" t="s">
         <v>273</v>
       </c>
-      <c r="E175" s="116"/>
-      <c r="F175" s="117"/>
+      <c r="E175" s="113"/>
+      <c r="F175" s="114"/>
       <c r="G175" s="58" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="H175" s="59"/>
       <c r="I175" s="60" t="s">
@@ -11195,15 +11233,15 @@
     </row>
     <row r="176" spans="1:14" ht="88.2">
       <c r="A176" s="11"/>
-      <c r="B176" s="119"/>
+      <c r="B176" s="116"/>
       <c r="C176" s="77"/>
-      <c r="D176" s="115" t="s">
+      <c r="D176" s="112" t="s">
         <v>183</v>
       </c>
-      <c r="E176" s="116"/>
-      <c r="F176" s="117"/>
+      <c r="E176" s="113"/>
+      <c r="F176" s="114"/>
       <c r="G176" s="58" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="H176" s="59"/>
       <c r="I176" s="60" t="s">
@@ -11219,18 +11257,18 @@
     </row>
     <row r="177" spans="1:14" ht="138.6">
       <c r="A177" s="11"/>
-      <c r="B177" s="119"/>
+      <c r="B177" s="116"/>
       <c r="C177" s="58" t="str">
         <f>master!C153</f>
         <v>[解説] Serviceのテストクラス（抜粋）</v>
       </c>
-      <c r="D177" s="115" t="s">
+      <c r="D177" s="112" t="s">
         <v>274</v>
       </c>
-      <c r="E177" s="116"/>
-      <c r="F177" s="117"/>
+      <c r="E177" s="113"/>
+      <c r="F177" s="114"/>
       <c r="G177" s="58" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="H177" s="59"/>
       <c r="I177" s="60" t="s">
@@ -11246,18 +11284,18 @@
     </row>
     <row r="178" spans="1:14" ht="50.4">
       <c r="A178" s="11"/>
-      <c r="B178" s="119"/>
+      <c r="B178" s="116"/>
       <c r="C178" s="76" t="str">
         <f>master!C154</f>
         <v>バイブコーディング単体テスト④Controllerのテストを作る</v>
       </c>
-      <c r="D178" s="115" t="s">
+      <c r="D178" s="112" t="s">
         <v>273</v>
       </c>
-      <c r="E178" s="116"/>
-      <c r="F178" s="117"/>
+      <c r="E178" s="113"/>
+      <c r="F178" s="114"/>
       <c r="G178" s="58" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="H178" s="59"/>
       <c r="I178" s="60" t="s">
@@ -11273,15 +11311,15 @@
     </row>
     <row r="179" spans="1:14" ht="88.2">
       <c r="A179" s="11"/>
-      <c r="B179" s="119"/>
+      <c r="B179" s="116"/>
       <c r="C179" s="77"/>
-      <c r="D179" s="115" t="s">
+      <c r="D179" s="112" t="s">
         <v>183</v>
       </c>
-      <c r="E179" s="116"/>
-      <c r="F179" s="117"/>
+      <c r="E179" s="113"/>
+      <c r="F179" s="114"/>
       <c r="G179" s="58" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="H179" s="59"/>
       <c r="I179" s="60" t="s">
@@ -11297,18 +11335,18 @@
     </row>
     <row r="180" spans="1:14" ht="163.80000000000001">
       <c r="A180" s="11"/>
-      <c r="B180" s="120"/>
+      <c r="B180" s="117"/>
       <c r="C180" s="58" t="str">
         <f>master!C155</f>
         <v>[解説] Controllerのテストクラス（抜粋）</v>
       </c>
-      <c r="D180" s="115" t="s">
+      <c r="D180" s="112" t="s">
         <v>276</v>
       </c>
-      <c r="E180" s="116"/>
-      <c r="F180" s="117"/>
+      <c r="E180" s="113"/>
+      <c r="F180" s="114"/>
       <c r="G180" s="58" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="H180" s="59"/>
       <c r="I180" s="60" t="s">
@@ -11324,7 +11362,7 @@
     </row>
     <row r="181" spans="1:14" ht="165" customHeight="1">
       <c r="A181" s="11"/>
-      <c r="B181" s="118" t="str">
+      <c r="B181" s="115" t="str">
         <f>master!B156</f>
         <v>課題2の実施</v>
       </c>
@@ -11332,20 +11370,20 @@
         <f>master!C156</f>
         <v>ここから各自で演習を始めましょう。</v>
       </c>
-      <c r="D181" s="115" t="s">
+      <c r="D181" s="112" t="s">
         <v>277</v>
       </c>
-      <c r="E181" s="116"/>
-      <c r="F181" s="117"/>
+      <c r="E181" s="113"/>
+      <c r="F181" s="114"/>
       <c r="G181" s="58" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="H181" s="59"/>
       <c r="I181" s="60" t="s">
         <v>24</v>
       </c>
       <c r="J181" s="61" t="s">
-        <v>343</v>
+        <v>338</v>
       </c>
       <c r="K181" s="62"/>
       <c r="L181" s="6"/>
@@ -11354,28 +11392,28 @@
     </row>
     <row r="182" spans="1:14" ht="151.19999999999999">
       <c r="A182" s="11"/>
-      <c r="B182" s="120"/>
+      <c r="B182" s="117"/>
       <c r="C182" s="58" t="str">
         <f>master!C157</f>
         <v>[終了条件] 講師配布のテストプログラム(JUnit)が成功すること</v>
       </c>
-      <c r="D182" s="115" t="s">
-        <v>342</v>
-      </c>
-      <c r="E182" s="116"/>
-      <c r="F182" s="117"/>
+      <c r="D182" s="112" t="s">
+        <v>337</v>
+      </c>
+      <c r="E182" s="113"/>
+      <c r="F182" s="114"/>
       <c r="G182" s="58" t="s">
-        <v>341</v>
+        <v>336</v>
       </c>
       <c r="H182" s="59"/>
       <c r="I182" s="60" t="s">
         <v>49</v>
       </c>
       <c r="J182" s="61" t="s">
-        <v>343</v>
+        <v>338</v>
       </c>
       <c r="K182" s="62" t="s">
-        <v>446</v>
+        <v>441</v>
       </c>
       <c r="L182" s="6"/>
       <c r="M182" s="6"/>
@@ -11383,7 +11421,7 @@
     </row>
     <row r="183" spans="1:14" ht="163.80000000000001">
       <c r="A183" s="11"/>
-      <c r="B183" s="118" t="str">
+      <c r="B183" s="115" t="str">
         <f>master!B159</f>
         <v>追加課題</v>
       </c>
@@ -11391,23 +11429,23 @@
         <f>master!C159</f>
         <v>演習課題の概要</v>
       </c>
-      <c r="D183" s="115" t="s">
+      <c r="D183" s="112" t="s">
         <v>279</v>
       </c>
-      <c r="E183" s="116"/>
-      <c r="F183" s="117"/>
+      <c r="E183" s="113"/>
+      <c r="F183" s="114"/>
       <c r="G183" s="58" t="s">
-        <v>337</v>
+        <v>334</v>
       </c>
       <c r="H183" s="59"/>
       <c r="I183" s="60" t="s">
         <v>49</v>
       </c>
       <c r="J183" s="61" t="s">
-        <v>343</v>
+        <v>338</v>
       </c>
       <c r="K183" s="62" t="s">
-        <v>445</v>
+        <v>440</v>
       </c>
       <c r="L183" s="6"/>
       <c r="M183" s="6"/>
@@ -11415,28 +11453,28 @@
     </row>
     <row r="184" spans="1:14" ht="25.2">
       <c r="A184" s="11"/>
-      <c r="B184" s="119"/>
+      <c r="B184" s="116"/>
       <c r="C184" s="58" t="str">
         <f>master!C160</f>
         <v>追加課題①：送料の表示機能</v>
       </c>
-      <c r="D184" s="115" t="s">
+      <c r="D184" s="112" t="s">
         <v>281</v>
       </c>
-      <c r="E184" s="116"/>
-      <c r="F184" s="117"/>
+      <c r="E184" s="113"/>
+      <c r="F184" s="114"/>
       <c r="G184" s="58" t="s">
-        <v>338</v>
+        <v>335</v>
       </c>
       <c r="H184" s="59"/>
       <c r="I184" s="60" t="s">
         <v>49</v>
       </c>
       <c r="J184" s="61" t="s">
-        <v>343</v>
+        <v>338</v>
       </c>
       <c r="K184" s="62" t="s">
-        <v>445</v>
+        <v>440</v>
       </c>
       <c r="L184" s="6"/>
       <c r="M184" s="6"/>
@@ -11444,28 +11482,28 @@
     </row>
     <row r="185" spans="1:14" ht="25.2">
       <c r="A185" s="11"/>
-      <c r="B185" s="119"/>
+      <c r="B185" s="116"/>
       <c r="C185" s="58" t="str">
         <f>master!C161</f>
         <v>追加課題②：クーポン機能</v>
       </c>
-      <c r="D185" s="115" t="s">
+      <c r="D185" s="112" t="s">
         <v>281</v>
       </c>
-      <c r="E185" s="116"/>
-      <c r="F185" s="117"/>
+      <c r="E185" s="113"/>
+      <c r="F185" s="114"/>
       <c r="G185" s="58" t="s">
-        <v>338</v>
+        <v>335</v>
       </c>
       <c r="H185" s="59"/>
       <c r="I185" s="60" t="s">
         <v>49</v>
       </c>
       <c r="J185" s="61" t="s">
-        <v>343</v>
+        <v>338</v>
       </c>
       <c r="K185" s="62" t="s">
-        <v>445</v>
+        <v>440</v>
       </c>
       <c r="L185" s="6"/>
       <c r="M185" s="6"/>
@@ -11473,28 +11511,28 @@
     </row>
     <row r="186" spans="1:14" ht="25.2">
       <c r="A186" s="11"/>
-      <c r="B186" s="120"/>
+      <c r="B186" s="117"/>
       <c r="C186" s="58" t="str">
         <f>master!C162</f>
         <v>追加課題③：ユーザーアカウント機能</v>
       </c>
-      <c r="D186" s="115" t="s">
+      <c r="D186" s="112" t="s">
         <v>281</v>
       </c>
-      <c r="E186" s="116"/>
-      <c r="F186" s="117"/>
+      <c r="E186" s="113"/>
+      <c r="F186" s="114"/>
       <c r="G186" s="58" t="s">
-        <v>338</v>
+        <v>335</v>
       </c>
       <c r="H186" s="59"/>
       <c r="I186" s="60" t="s">
         <v>49</v>
       </c>
       <c r="J186" s="61" t="s">
-        <v>343</v>
+        <v>338</v>
       </c>
       <c r="K186" s="62" t="s">
-        <v>445</v>
+        <v>440</v>
       </c>
       <c r="L186" s="6"/>
       <c r="M186" s="6"/>
@@ -11502,21 +11540,21 @@
     </row>
     <row r="187" spans="1:14" ht="176.4">
       <c r="A187" s="11"/>
-      <c r="B187" s="118" t="str">
+      <c r="B187" s="115" t="str">
         <f>master!B164</f>
-        <v>課題の振り返り</v>
+        <v>演習の振り返り</v>
       </c>
       <c r="C187" s="58" t="str">
         <f>master!C164</f>
-        <v>サンプルのAPとの自分のAPとの比較</v>
-      </c>
-      <c r="D187" s="115" t="s">
-        <v>339</v>
-      </c>
-      <c r="E187" s="116"/>
-      <c r="F187" s="117"/>
+        <v>アプリケーションの比較・分析</v>
+      </c>
+      <c r="D187" s="112" t="s">
+        <v>451</v>
+      </c>
+      <c r="E187" s="113"/>
+      <c r="F187" s="114"/>
       <c r="G187" s="58" t="s">
-        <v>447</v>
+        <v>442</v>
       </c>
       <c r="H187" s="59"/>
       <c r="I187" s="60" t="s">
@@ -11532,18 +11570,18 @@
     </row>
     <row r="188" spans="1:14" ht="63">
       <c r="A188" s="11"/>
-      <c r="B188" s="120"/>
+      <c r="B188" s="116"/>
       <c r="C188" s="58" t="str">
         <f>master!C165</f>
-        <v>レポートの作成</v>
-      </c>
-      <c r="D188" s="115" t="s">
-        <v>340</v>
-      </c>
-      <c r="E188" s="116"/>
-      <c r="F188" s="117"/>
+        <v>改善点の整理</v>
+      </c>
+      <c r="D188" s="112" t="s">
+        <v>450</v>
+      </c>
+      <c r="E188" s="113"/>
+      <c r="F188" s="114"/>
       <c r="G188" s="58" t="s">
-        <v>448</v>
+        <v>443</v>
       </c>
       <c r="H188" s="59"/>
       <c r="I188" s="60" t="s">
@@ -11557,16 +11595,40 @@
       <c r="M188" s="6"/>
       <c r="N188" s="6"/>
     </row>
-    <row r="189" spans="1:14" ht="15" customHeight="1">
-      <c r="J189" s="43"/>
-    </row>
-    <row r="190" spans="1:14" ht="15" customHeight="1"/>
+    <row r="189" spans="1:14" ht="63">
+      <c r="A189" s="11"/>
+      <c r="B189" s="117"/>
+      <c r="C189" s="58" t="str">
+        <f>master!C166</f>
+        <v>分析結果の共有</v>
+      </c>
+      <c r="D189" s="112" t="s">
+        <v>448</v>
+      </c>
+      <c r="E189" s="113"/>
+      <c r="F189" s="114"/>
+      <c r="G189" s="58" t="s">
+        <v>443</v>
+      </c>
+      <c r="H189" s="59"/>
+      <c r="I189" s="60" t="s">
+        <v>24</v>
+      </c>
+      <c r="J189" s="61">
+        <v>2.0833333333333332E-2</v>
+      </c>
+      <c r="K189" s="62"/>
+      <c r="L189" s="6"/>
+      <c r="M189" s="6"/>
+      <c r="N189" s="6"/>
+    </row>
+    <row r="190" spans="1:14" ht="15" customHeight="1">
+      <c r="J190" s="43"/>
+    </row>
+    <row r="191" spans="1:14" ht="15" customHeight="1"/>
   </sheetData>
-  <mergeCells count="203">
-    <mergeCell ref="B119:B123"/>
-    <mergeCell ref="B113:B118"/>
-    <mergeCell ref="B108:B112"/>
-    <mergeCell ref="B99:B107"/>
+  <mergeCells count="204">
+    <mergeCell ref="D188:F188"/>
     <mergeCell ref="B94:B98"/>
     <mergeCell ref="B91:B93"/>
     <mergeCell ref="D124:F124"/>
@@ -11587,6 +11649,38 @@
     <mergeCell ref="D108:F108"/>
     <mergeCell ref="D121:F121"/>
     <mergeCell ref="D92:F92"/>
+    <mergeCell ref="D99:F99"/>
+    <mergeCell ref="D123:F123"/>
+    <mergeCell ref="D136:F136"/>
+    <mergeCell ref="D101:F101"/>
+    <mergeCell ref="D102:F102"/>
+    <mergeCell ref="B119:B123"/>
+    <mergeCell ref="B113:B118"/>
+    <mergeCell ref="B108:B112"/>
+    <mergeCell ref="B99:B107"/>
+    <mergeCell ref="D162:F162"/>
+    <mergeCell ref="D163:F163"/>
+    <mergeCell ref="D138:F138"/>
+    <mergeCell ref="D137:F137"/>
+    <mergeCell ref="D111:F111"/>
+    <mergeCell ref="D110:F110"/>
+    <mergeCell ref="D109:F109"/>
+    <mergeCell ref="D112:F112"/>
+    <mergeCell ref="D103:F103"/>
+    <mergeCell ref="D31:F31"/>
+    <mergeCell ref="D32:F32"/>
+    <mergeCell ref="D33:F33"/>
+    <mergeCell ref="D189:F189"/>
+    <mergeCell ref="B187:B189"/>
+    <mergeCell ref="D170:F170"/>
+    <mergeCell ref="D172:F172"/>
+    <mergeCell ref="D175:F175"/>
+    <mergeCell ref="D176:F176"/>
+    <mergeCell ref="D178:F178"/>
+    <mergeCell ref="D179:F179"/>
+    <mergeCell ref="B183:B186"/>
+    <mergeCell ref="D182:F182"/>
+    <mergeCell ref="B181:B182"/>
     <mergeCell ref="D93:F93"/>
     <mergeCell ref="D94:F94"/>
     <mergeCell ref="D95:F95"/>
@@ -11597,43 +11691,30 @@
     <mergeCell ref="D122:F122"/>
     <mergeCell ref="D186:F186"/>
     <mergeCell ref="D185:F185"/>
-    <mergeCell ref="D188:F188"/>
-    <mergeCell ref="B187:B188"/>
-    <mergeCell ref="D170:F170"/>
-    <mergeCell ref="D172:F172"/>
-    <mergeCell ref="D175:F175"/>
-    <mergeCell ref="D176:F176"/>
-    <mergeCell ref="D178:F178"/>
-    <mergeCell ref="D179:F179"/>
-    <mergeCell ref="B183:B186"/>
-    <mergeCell ref="D182:F182"/>
-    <mergeCell ref="B181:B182"/>
-    <mergeCell ref="D162:F162"/>
-    <mergeCell ref="D163:F163"/>
+    <mergeCell ref="D91:F91"/>
+    <mergeCell ref="D76:F76"/>
+    <mergeCell ref="I19:J19"/>
+    <mergeCell ref="H19:H20"/>
+    <mergeCell ref="D78:F78"/>
+    <mergeCell ref="D80:F80"/>
+    <mergeCell ref="D74:F74"/>
+    <mergeCell ref="D85:F85"/>
+    <mergeCell ref="D90:F90"/>
+    <mergeCell ref="D82:F82"/>
+    <mergeCell ref="D83:F83"/>
+    <mergeCell ref="D87:F87"/>
+    <mergeCell ref="D88:F88"/>
+    <mergeCell ref="D89:F89"/>
+    <mergeCell ref="D77:F77"/>
+    <mergeCell ref="D79:F79"/>
+    <mergeCell ref="D81:F81"/>
+    <mergeCell ref="D75:F75"/>
+    <mergeCell ref="D73:F73"/>
     <mergeCell ref="D21:F21"/>
     <mergeCell ref="D35:F35"/>
     <mergeCell ref="D22:F22"/>
     <mergeCell ref="D28:F28"/>
     <mergeCell ref="D23:F23"/>
-    <mergeCell ref="D25:F25"/>
-    <mergeCell ref="D27:F27"/>
-    <mergeCell ref="D34:F34"/>
-    <mergeCell ref="D24:F24"/>
-    <mergeCell ref="D26:F26"/>
-    <mergeCell ref="D29:F29"/>
-    <mergeCell ref="D30:F30"/>
-    <mergeCell ref="D31:F31"/>
-    <mergeCell ref="D32:F32"/>
-    <mergeCell ref="D33:F33"/>
-    <mergeCell ref="D46:F46"/>
-    <mergeCell ref="D47:F47"/>
-    <mergeCell ref="D48:F48"/>
-    <mergeCell ref="D54:F54"/>
-    <mergeCell ref="D36:F36"/>
-    <mergeCell ref="D91:F91"/>
-    <mergeCell ref="D76:F76"/>
-    <mergeCell ref="I19:J19"/>
-    <mergeCell ref="H19:H20"/>
     <mergeCell ref="B4:E4"/>
     <mergeCell ref="B5:K5"/>
     <mergeCell ref="D19:F20"/>
@@ -11643,6 +11724,10 @@
     <mergeCell ref="K19:K20"/>
     <mergeCell ref="D7:E7"/>
     <mergeCell ref="B22:B27"/>
+    <mergeCell ref="D25:F25"/>
+    <mergeCell ref="D27:F27"/>
+    <mergeCell ref="D24:F24"/>
+    <mergeCell ref="D26:F26"/>
     <mergeCell ref="B28:B35"/>
     <mergeCell ref="B36:B54"/>
     <mergeCell ref="D49:F49"/>
@@ -11659,6 +11744,14 @@
     <mergeCell ref="D43:F43"/>
     <mergeCell ref="D44:F44"/>
     <mergeCell ref="D45:F45"/>
+    <mergeCell ref="D46:F46"/>
+    <mergeCell ref="D47:F47"/>
+    <mergeCell ref="D48:F48"/>
+    <mergeCell ref="D54:F54"/>
+    <mergeCell ref="D36:F36"/>
+    <mergeCell ref="D34:F34"/>
+    <mergeCell ref="D29:F29"/>
+    <mergeCell ref="D30:F30"/>
     <mergeCell ref="B55:B57"/>
     <mergeCell ref="D69:F69"/>
     <mergeCell ref="D70:F70"/>
@@ -11680,36 +11773,9 @@
     <mergeCell ref="D55:F55"/>
     <mergeCell ref="B62:B70"/>
     <mergeCell ref="B58:B61"/>
-    <mergeCell ref="D78:F78"/>
-    <mergeCell ref="D80:F80"/>
-    <mergeCell ref="D74:F74"/>
-    <mergeCell ref="D85:F85"/>
-    <mergeCell ref="D90:F90"/>
-    <mergeCell ref="D82:F82"/>
-    <mergeCell ref="D83:F83"/>
     <mergeCell ref="B71:B90"/>
     <mergeCell ref="D84:F84"/>
     <mergeCell ref="D86:F86"/>
-    <mergeCell ref="D87:F87"/>
-    <mergeCell ref="D88:F88"/>
-    <mergeCell ref="D89:F89"/>
-    <mergeCell ref="D77:F77"/>
-    <mergeCell ref="D79:F79"/>
-    <mergeCell ref="D81:F81"/>
-    <mergeCell ref="D75:F75"/>
-    <mergeCell ref="D73:F73"/>
-    <mergeCell ref="D138:F138"/>
-    <mergeCell ref="D137:F137"/>
-    <mergeCell ref="D111:F111"/>
-    <mergeCell ref="D110:F110"/>
-    <mergeCell ref="D109:F109"/>
-    <mergeCell ref="D112:F112"/>
-    <mergeCell ref="D103:F103"/>
-    <mergeCell ref="D99:F99"/>
-    <mergeCell ref="D123:F123"/>
-    <mergeCell ref="D136:F136"/>
-    <mergeCell ref="D101:F101"/>
-    <mergeCell ref="D102:F102"/>
     <mergeCell ref="D104:F104"/>
     <mergeCell ref="D105:F105"/>
     <mergeCell ref="D106:F106"/>
@@ -11722,7 +11788,6 @@
     <mergeCell ref="D115:F115"/>
     <mergeCell ref="D114:F114"/>
     <mergeCell ref="D113:F113"/>
-    <mergeCell ref="D141:F141"/>
     <mergeCell ref="D142:F142"/>
     <mergeCell ref="D144:F144"/>
     <mergeCell ref="D145:F145"/>
@@ -11766,6 +11831,7 @@
     <mergeCell ref="B144:B161"/>
     <mergeCell ref="D139:F139"/>
     <mergeCell ref="D140:F140"/>
+    <mergeCell ref="D141:F141"/>
   </mergeCells>
   <phoneticPr fontId="3"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -11778,7 +11844,7 @@
           <x14:formula1>
             <xm:f>master!#REF!</xm:f>
           </x14:formula1>
-          <xm:sqref>H21:H188</xm:sqref>
+          <xm:sqref>H21:H189</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -11788,7 +11854,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="B1:C166"/>
+  <dimension ref="B1:C167"/>
   <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="13.2"/>
   <cols>
     <col min="1" max="1" width="4.6640625" customWidth="1"/>
@@ -11811,7 +11877,7 @@
     </row>
     <row r="3" spans="2:3">
       <c r="B3" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="C3" t="s">
         <v>54</v>
@@ -11992,7 +12058,7 @@
     </row>
     <row r="37" spans="2:3">
       <c r="B37" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="C37" t="s">
         <v>164</v>
@@ -12081,7 +12147,7 @@
     </row>
     <row r="53" spans="2:3">
       <c r="B53" t="s">
-        <v>323</v>
+        <v>320</v>
       </c>
       <c r="C53" t="s">
         <v>148</v>
@@ -12154,7 +12220,7 @@
     </row>
     <row r="67" spans="2:3">
       <c r="B67" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="C67" t="s">
         <v>161</v>
@@ -12169,182 +12235,182 @@
         <v>163</v>
       </c>
       <c r="C69" t="s">
-        <v>344</v>
+        <v>339</v>
       </c>
     </row>
     <row r="70" spans="2:3">
       <c r="C70" t="s">
-        <v>345</v>
+        <v>340</v>
       </c>
     </row>
     <row r="71" spans="2:3">
       <c r="C71" t="s">
-        <v>346</v>
+        <v>341</v>
       </c>
     </row>
     <row r="72" spans="2:3">
       <c r="B72" t="s">
-        <v>347</v>
+        <v>342</v>
       </c>
       <c r="C72" t="s">
-        <v>344</v>
+        <v>339</v>
       </c>
     </row>
     <row r="73" spans="2:3">
       <c r="C73" t="s">
-        <v>348</v>
+        <v>343</v>
       </c>
     </row>
     <row r="74" spans="2:3">
       <c r="C74" t="s">
-        <v>349</v>
+        <v>344</v>
       </c>
     </row>
     <row r="75" spans="2:3">
       <c r="C75" t="s">
-        <v>350</v>
+        <v>345</v>
       </c>
     </row>
     <row r="76" spans="2:3">
       <c r="C76" t="s">
-        <v>351</v>
+        <v>346</v>
       </c>
     </row>
     <row r="77" spans="2:3">
       <c r="B77" t="s">
-        <v>352</v>
+        <v>347</v>
       </c>
       <c r="C77" t="s">
-        <v>344</v>
+        <v>339</v>
       </c>
     </row>
     <row r="78" spans="2:3">
       <c r="C78" t="s">
-        <v>353</v>
+        <v>348</v>
       </c>
     </row>
     <row r="79" spans="2:3">
       <c r="C79" t="s">
-        <v>354</v>
+        <v>349</v>
       </c>
     </row>
     <row r="80" spans="2:3">
       <c r="C80" t="s">
-        <v>355</v>
+        <v>350</v>
       </c>
     </row>
     <row r="81" spans="2:3">
       <c r="C81" t="s">
-        <v>356</v>
+        <v>351</v>
       </c>
     </row>
     <row r="82" spans="2:3">
       <c r="C82" t="s">
-        <v>357</v>
+        <v>352</v>
       </c>
     </row>
     <row r="83" spans="2:3">
       <c r="C83" t="s">
-        <v>358</v>
+        <v>353</v>
       </c>
     </row>
     <row r="84" spans="2:3">
       <c r="C84" t="s">
-        <v>359</v>
+        <v>354</v>
       </c>
     </row>
     <row r="85" spans="2:3">
       <c r="C85" t="s">
-        <v>449</v>
+        <v>444</v>
       </c>
     </row>
     <row r="86" spans="2:3">
       <c r="B86" t="s">
-        <v>360</v>
+        <v>355</v>
       </c>
       <c r="C86" t="s">
-        <v>344</v>
+        <v>339</v>
       </c>
     </row>
     <row r="87" spans="2:3">
       <c r="C87" t="s">
-        <v>376</v>
+        <v>371</v>
       </c>
     </row>
     <row r="88" spans="2:3">
       <c r="C88" t="s">
-        <v>375</v>
+        <v>370</v>
       </c>
     </row>
     <row r="89" spans="2:3">
       <c r="C89" t="s">
-        <v>374</v>
+        <v>369</v>
       </c>
     </row>
     <row r="90" spans="2:3">
       <c r="C90" t="s">
-        <v>373</v>
+        <v>368</v>
       </c>
     </row>
     <row r="91" spans="2:3">
       <c r="B91" t="s">
-        <v>361</v>
+        <v>356</v>
       </c>
       <c r="C91" t="s">
-        <v>344</v>
+        <v>339</v>
       </c>
     </row>
     <row r="92" spans="2:3">
       <c r="C92" t="s">
-        <v>362</v>
+        <v>357</v>
       </c>
     </row>
     <row r="93" spans="2:3">
       <c r="C93" t="s">
-        <v>372</v>
+        <v>367</v>
       </c>
     </row>
     <row r="94" spans="2:3">
       <c r="C94" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
     </row>
     <row r="95" spans="2:3">
       <c r="C95" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
     </row>
     <row r="96" spans="2:3">
       <c r="C96" t="s">
-        <v>363</v>
+        <v>358</v>
       </c>
     </row>
     <row r="97" spans="2:3">
       <c r="B97" t="s">
-        <v>364</v>
+        <v>359</v>
       </c>
       <c r="C97" t="s">
-        <v>366</v>
+        <v>361</v>
       </c>
     </row>
     <row r="98" spans="2:3">
       <c r="C98" t="s">
-        <v>365</v>
+        <v>360</v>
       </c>
     </row>
     <row r="99" spans="2:3">
       <c r="C99" t="s">
-        <v>367</v>
+        <v>362</v>
       </c>
     </row>
     <row r="100" spans="2:3">
       <c r="C100" t="s">
-        <v>368</v>
+        <v>363</v>
       </c>
     </row>
     <row r="101" spans="2:3">
       <c r="C101" t="s">
-        <v>369</v>
+        <v>364</v>
       </c>
     </row>
     <row r="102" spans="2:3">
@@ -12353,71 +12419,71 @@
     </row>
     <row r="103" spans="2:3">
       <c r="B103" t="s">
-        <v>377</v>
+        <v>372</v>
       </c>
       <c r="C103" t="s">
-        <v>344</v>
+        <v>339</v>
       </c>
     </row>
     <row r="104" spans="2:3">
       <c r="C104" s="82" t="s">
-        <v>380</v>
+        <v>375</v>
       </c>
     </row>
     <row r="105" spans="2:3">
       <c r="C105" s="82" t="s">
-        <v>381</v>
+        <v>376</v>
       </c>
     </row>
     <row r="106" spans="2:3">
       <c r="B106" t="s">
-        <v>378</v>
+        <v>373</v>
       </c>
       <c r="C106" s="83" t="s">
-        <v>382</v>
+        <v>377</v>
       </c>
     </row>
     <row r="107" spans="2:3">
       <c r="C107" s="79" t="s">
-        <v>383</v>
+        <v>378</v>
       </c>
     </row>
     <row r="108" spans="2:3">
       <c r="C108" s="79" t="s">
-        <v>384</v>
+        <v>379</v>
       </c>
     </row>
     <row r="109" spans="2:3">
       <c r="C109" s="79" t="s">
-        <v>385</v>
+        <v>380</v>
       </c>
     </row>
     <row r="110" spans="2:3">
       <c r="C110" s="79" t="s">
-        <v>386</v>
+        <v>381</v>
       </c>
     </row>
     <row r="111" spans="2:3">
       <c r="B111" t="s">
-        <v>379</v>
+        <v>374</v>
       </c>
       <c r="C111" s="79" t="s">
-        <v>382</v>
+        <v>377</v>
       </c>
     </row>
     <row r="112" spans="2:3">
       <c r="C112" s="79" t="s">
-        <v>387</v>
+        <v>382</v>
       </c>
     </row>
     <row r="113" spans="2:3">
       <c r="C113" s="79" t="s">
-        <v>388</v>
+        <v>383</v>
       </c>
     </row>
     <row r="114" spans="2:3">
       <c r="C114" s="79" t="s">
-        <v>389</v>
+        <v>384</v>
       </c>
     </row>
     <row r="115" spans="2:3">
@@ -12426,7 +12492,7 @@
     </row>
     <row r="116" spans="2:3">
       <c r="B116" t="s">
-        <v>326</v>
+        <v>323</v>
       </c>
       <c r="C116" s="79" t="s">
         <v>54</v>
@@ -12560,7 +12626,7 @@
     </row>
     <row r="141" spans="2:3">
       <c r="B141" s="79" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="C141" s="79" t="s">
         <v>217</v>
@@ -12577,7 +12643,7 @@
     </row>
     <row r="144" spans="2:3">
       <c r="B144" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
       <c r="C144" t="s">
         <v>164</v>
@@ -12600,7 +12666,7 @@
     </row>
     <row r="148" spans="2:3">
       <c r="B148" t="s">
-        <v>323</v>
+        <v>320</v>
       </c>
       <c r="C148" s="79" t="s">
         <v>255</v>
@@ -12643,7 +12709,7 @@
     </row>
     <row r="156" spans="2:3">
       <c r="B156" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="C156" s="79" t="s">
         <v>259</v>
@@ -12688,20 +12754,25 @@
     </row>
     <row r="164" spans="2:3">
       <c r="B164" t="s">
-        <v>322</v>
+        <v>447</v>
       </c>
       <c r="C164" s="79" t="s">
-        <v>283</v>
+        <v>446</v>
       </c>
     </row>
     <row r="165" spans="2:3">
       <c r="C165" s="79" t="s">
-        <v>282</v>
+        <v>449</v>
       </c>
     </row>
     <row r="166" spans="2:3">
-      <c r="B166" s="81"/>
-      <c r="C166" s="81"/>
+      <c r="C166" s="79" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="167" spans="2:3">
+      <c r="B167" s="81"/>
+      <c r="C167" s="81"/>
     </row>
   </sheetData>
   <phoneticPr fontId="3"/>

--- a/IG/7日版/AI Native-バイブコーディング_IG.xlsx
+++ b/IG/7日版/AI Native-バイブコーディング_IG.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\myrepo\ai_navive\IG\7日版\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D5F55BDF-1974-4C36-BE82-916AD66BB9EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B6CD91C-A346-4657-8A05-5214E23A9A56}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="860" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="860" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="スケジュール（3日）" sheetId="33" r:id="rId1"/>
@@ -88,7 +88,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="832" uniqueCount="452">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="832" uniqueCount="447">
   <si>
     <t>1 日目</t>
     <rPh sb="2" eb="3">
@@ -3647,47 +3647,7 @@
     <phoneticPr fontId="3"/>
   </si>
   <si>
-    <t>リポジトリの取得</t>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
-    <t>演習について</t>
-  </si>
-  <si>
-    <t>VS Codeによるローカルリポジトリの操作</t>
-  </si>
-  <si>
-    <t>VS Codeによるブランチの操作</t>
-  </si>
-  <si>
-    <t>演習の構成</t>
-  </si>
-  <si>
-    <t>演習で利用するソフトウェア</t>
-  </si>
-  <si>
     <t>演習の前に</t>
-  </si>
-  <si>
-    <t>VS Codeによるリポジトリの作成</t>
-  </si>
-  <si>
-    <t>VS Codeによる変更内容の確認</t>
-  </si>
-  <si>
-    <t>VS Codeによる変更内容のステージング</t>
-  </si>
-  <si>
-    <t>VS Codeによる変更内容のコミット</t>
-  </si>
-  <si>
-    <t>VS Codeによるブランチの作成</t>
-  </si>
-  <si>
-    <t>VS Codeによるブランチの切り替え</t>
-  </si>
-  <si>
-    <t>VS Codeによるブランチのマージ</t>
   </si>
   <si>
     <t>Git入門.docx</t>
@@ -4597,6 +4557,40 @@
     <rPh sb="262" eb="263">
       <t>ホウ</t>
     </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>リポジトリの複製</t>
+    <rPh sb="6" eb="8">
+      <t>フクセイ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>変更内容のステージング</t>
+  </si>
+  <si>
+    <t>ブランチの作成</t>
+  </si>
+  <si>
+    <t>ブランチの切り替え</t>
+  </si>
+  <si>
+    <t>ブランチのマージ</t>
+  </si>
+  <si>
+    <t>演習の概要について</t>
+    <rPh sb="3" eb="5">
+      <t>ガイヨウ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>構成</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>利用するソフトウェア</t>
     <phoneticPr fontId="3"/>
   </si>
 </sst>
@@ -5348,6 +5342,60 @@
     <xf numFmtId="0" fontId="11" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
     </xf>
@@ -5356,60 +5404,6 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -6272,7 +6266,7 @@
         <v>0.6875</v>
       </c>
       <c r="C38" s="66" t="s">
-        <v>439</v>
+        <v>426</v>
       </c>
       <c r="D38" s="39"/>
       <c r="E38" s="51"/>
@@ -6313,7 +6307,7 @@
         <v>0.71875</v>
       </c>
       <c r="C41" s="55" t="s">
-        <v>439</v>
+        <v>426</v>
       </c>
       <c r="D41" s="39"/>
       <c r="E41" s="99"/>
@@ -6682,16 +6676,16 @@
       <c r="M4" s="9"/>
     </row>
     <row r="5" spans="2:14" ht="36" customHeight="1">
-      <c r="B5" s="127"/>
-      <c r="C5" s="127"/>
-      <c r="D5" s="127"/>
-      <c r="E5" s="127"/>
-      <c r="F5" s="127"/>
-      <c r="G5" s="127"/>
-      <c r="H5" s="127"/>
-      <c r="I5" s="127"/>
-      <c r="J5" s="127"/>
-      <c r="K5" s="127"/>
+      <c r="B5" s="126"/>
+      <c r="C5" s="126"/>
+      <c r="D5" s="126"/>
+      <c r="E5" s="126"/>
+      <c r="F5" s="126"/>
+      <c r="G5" s="126"/>
+      <c r="H5" s="126"/>
+      <c r="I5" s="126"/>
+      <c r="J5" s="126"/>
+      <c r="K5" s="126"/>
       <c r="L5" s="26"/>
       <c r="M5" s="27"/>
     </row>
@@ -6865,7 +6859,7 @@
         <v>93</v>
       </c>
       <c r="C14" s="57" t="s">
-        <v>385</v>
+        <v>372</v>
       </c>
       <c r="D14" s="42" t="s">
         <v>19</v>
@@ -6887,7 +6881,7 @@
         <v>94</v>
       </c>
       <c r="C15" s="57" t="s">
-        <v>386</v>
+        <v>373</v>
       </c>
       <c r="D15" s="42" t="s">
         <v>19</v>
@@ -6967,10 +6961,10 @@
       <c r="H19" s="101" t="s">
         <v>23</v>
       </c>
-      <c r="I19" s="128" t="s">
+      <c r="I19" s="124" t="s">
         <v>31</v>
       </c>
-      <c r="J19" s="129"/>
+      <c r="J19" s="125"/>
       <c r="K19" s="101" t="s">
         <v>32</v>
       </c>
@@ -7030,7 +7024,7 @@
     </row>
     <row r="22" spans="1:14" ht="138.6" customHeight="1">
       <c r="A22" s="10"/>
-      <c r="B22" s="124" t="str">
+      <c r="B22" s="112" t="str">
         <f>master!B4</f>
         <v>Webアプリケーションとは</v>
       </c>
@@ -7060,7 +7054,7 @@
     </row>
     <row r="23" spans="1:14" ht="75.599999999999994">
       <c r="A23" s="11"/>
-      <c r="B23" s="125"/>
+      <c r="B23" s="113"/>
       <c r="C23" s="48" t="str">
         <f>master!C5</f>
         <v>Webアプリケーションの種類</v>
@@ -7087,7 +7081,7 @@
     </row>
     <row r="24" spans="1:14" ht="37.799999999999997">
       <c r="A24" s="11"/>
-      <c r="B24" s="125"/>
+      <c r="B24" s="113"/>
       <c r="C24" s="48" t="str">
         <f>master!C6</f>
         <v>アプリケーションとは</v>
@@ -7114,7 +7108,7 @@
     </row>
     <row r="25" spans="1:14" ht="63">
       <c r="A25" s="11"/>
-      <c r="B25" s="125"/>
+      <c r="B25" s="113"/>
       <c r="C25" s="48" t="str">
         <f>master!C7</f>
         <v>Web画面アプリケーション</v>
@@ -7141,7 +7135,7 @@
     </row>
     <row r="26" spans="1:14" ht="63">
       <c r="A26" s="11"/>
-      <c r="B26" s="125"/>
+      <c r="B26" s="113"/>
       <c r="C26" s="48"/>
       <c r="D26" s="118" t="s">
         <v>101</v>
@@ -7165,7 +7159,7 @@
     </row>
     <row r="27" spans="1:14" ht="113.4">
       <c r="A27" s="11"/>
-      <c r="B27" s="126"/>
+      <c r="B27" s="114"/>
       <c r="C27" s="48" t="str">
         <f>master!C8</f>
         <v>ブラウザからのリクエスト種類</v>
@@ -7192,7 +7186,7 @@
     </row>
     <row r="28" spans="1:14" ht="102" customHeight="1">
       <c r="A28" s="11"/>
-      <c r="B28" s="124" t="str">
+      <c r="B28" s="112" t="str">
         <f>master!B9</f>
         <v>データベースとは</v>
       </c>
@@ -7222,7 +7216,7 @@
     </row>
     <row r="29" spans="1:14" ht="88.2">
       <c r="A29" s="11"/>
-      <c r="B29" s="125"/>
+      <c r="B29" s="113"/>
       <c r="C29" s="48" t="str">
         <f>master!C10</f>
         <v>リレーショナルデータベース</v>
@@ -7249,7 +7243,7 @@
     </row>
     <row r="30" spans="1:14" ht="25.2">
       <c r="A30" s="11"/>
-      <c r="B30" s="125"/>
+      <c r="B30" s="113"/>
       <c r="C30" s="48" t="str">
         <f>master!C11</f>
         <v>データベースの役割</v>
@@ -7278,7 +7272,7 @@
     </row>
     <row r="31" spans="1:14" ht="75.599999999999994">
       <c r="A31" s="11"/>
-      <c r="B31" s="125"/>
+      <c r="B31" s="113"/>
       <c r="C31" s="48" t="str">
         <f>master!C12</f>
         <v>2.1.テーブル</v>
@@ -7305,7 +7299,7 @@
     </row>
     <row r="32" spans="1:14" ht="100.8">
       <c r="A32" s="11"/>
-      <c r="B32" s="125"/>
+      <c r="B32" s="113"/>
       <c r="C32" s="48" t="str">
         <f>master!C13</f>
         <v>2.2.データ型１</v>
@@ -7332,7 +7326,7 @@
     </row>
     <row r="33" spans="1:14" ht="37.799999999999997">
       <c r="A33" s="11"/>
-      <c r="B33" s="125"/>
+      <c r="B33" s="113"/>
       <c r="C33" s="48" t="str">
         <f>master!C14</f>
         <v>2.2.データ型２</v>
@@ -7359,7 +7353,7 @@
     </row>
     <row r="34" spans="1:14" ht="37.799999999999997">
       <c r="A34" s="11"/>
-      <c r="B34" s="125"/>
+      <c r="B34" s="113"/>
       <c r="C34" s="48" t="str">
         <f>master!C15</f>
         <v>2.3.リレーション</v>
@@ -7386,7 +7380,7 @@
     </row>
     <row r="35" spans="1:14" ht="37.799999999999997">
       <c r="A35" s="11"/>
-      <c r="B35" s="126"/>
+      <c r="B35" s="114"/>
       <c r="C35" s="48" t="str">
         <f>master!C16</f>
         <v>2.4.データを結合して取得（Join）</v>
@@ -7413,7 +7407,7 @@
     </row>
     <row r="36" spans="1:14" ht="88.2">
       <c r="A36" s="11"/>
-      <c r="B36" s="124" t="str">
+      <c r="B36" s="112" t="str">
         <f>master!B17</f>
         <v>Java言語、Springフレームワークとは</v>
       </c>
@@ -7443,7 +7437,7 @@
     </row>
     <row r="37" spans="1:14" ht="75.599999999999994">
       <c r="A37" s="11"/>
-      <c r="B37" s="125"/>
+      <c r="B37" s="113"/>
       <c r="C37" s="48" t="str">
         <f>master!C18</f>
         <v>Java</v>
@@ -7470,7 +7464,7 @@
     </row>
     <row r="38" spans="1:14" ht="75.599999999999994">
       <c r="A38" s="11"/>
-      <c r="B38" s="125"/>
+      <c r="B38" s="113"/>
       <c r="C38" s="48" t="str">
         <f>master!C19</f>
         <v>Java言語の構成要素</v>
@@ -7497,7 +7491,7 @@
     </row>
     <row r="39" spans="1:14" ht="50.4">
       <c r="A39" s="11"/>
-      <c r="B39" s="125"/>
+      <c r="B39" s="113"/>
       <c r="C39" s="48" t="str">
         <f>master!C20</f>
         <v>Webアプリケーションを構成するクラス</v>
@@ -7524,7 +7518,7 @@
     </row>
     <row r="40" spans="1:14" ht="88.2">
       <c r="A40" s="11"/>
-      <c r="B40" s="125"/>
+      <c r="B40" s="113"/>
       <c r="C40" s="48" t="str">
         <f>master!C21</f>
         <v>Nレイヤーアーキテクチャ</v>
@@ -7553,7 +7547,7 @@
     </row>
     <row r="41" spans="1:14" ht="201.6">
       <c r="A41" s="11"/>
-      <c r="B41" s="125"/>
+      <c r="B41" s="113"/>
       <c r="C41" s="48" t="str">
         <f>master!C22</f>
         <v>View と Controller と Service と Repository</v>
@@ -7580,7 +7574,7 @@
     </row>
     <row r="42" spans="1:14" ht="37.799999999999997">
       <c r="A42" s="11"/>
-      <c r="B42" s="125"/>
+      <c r="B42" s="113"/>
       <c r="C42" s="48" t="str">
         <f>master!C23</f>
         <v>Nレイヤーアーキテクチャ</v>
@@ -7607,7 +7601,7 @@
     </row>
     <row r="43" spans="1:14" ht="163.80000000000001">
       <c r="A43" s="11"/>
-      <c r="B43" s="125"/>
+      <c r="B43" s="113"/>
       <c r="C43" s="48" t="str">
         <f>master!C24</f>
         <v>Webアプリケーション フレームワーク</v>
@@ -7634,7 +7628,7 @@
     </row>
     <row r="44" spans="1:14" ht="25.2">
       <c r="A44" s="11"/>
-      <c r="B44" s="125"/>
+      <c r="B44" s="113"/>
       <c r="C44" s="48" t="str">
         <f>master!C25</f>
         <v>Java向けWebアプリケーションフレームワーク</v>
@@ -7661,7 +7655,7 @@
     </row>
     <row r="45" spans="1:14" ht="189">
       <c r="A45" s="11"/>
-      <c r="B45" s="125"/>
+      <c r="B45" s="113"/>
       <c r="C45" s="48" t="str">
         <f>master!C26</f>
         <v>Springフレームワーク</v>
@@ -7688,7 +7682,7 @@
     </row>
     <row r="46" spans="1:14" ht="88.2">
       <c r="A46" s="11"/>
-      <c r="B46" s="125"/>
+      <c r="B46" s="113"/>
       <c r="C46" s="48" t="str">
         <f>master!C27</f>
         <v>Springフレームワーク：DIコンテナとは</v>
@@ -7717,7 +7711,7 @@
     </row>
     <row r="47" spans="1:14" ht="63">
       <c r="A47" s="11"/>
-      <c r="B47" s="125"/>
+      <c r="B47" s="113"/>
       <c r="C47" s="48" t="str">
         <f>master!C28</f>
         <v>DIコンテナ：DIコンテナが部品を注入する</v>
@@ -7744,7 +7738,7 @@
     </row>
     <row r="48" spans="1:14" ht="100.8">
       <c r="A48" s="11"/>
-      <c r="B48" s="125"/>
+      <c r="B48" s="113"/>
       <c r="C48" s="48" t="str">
         <f>master!C29</f>
         <v>DIコンテナ：DIコンテナによる部品と注入対象になるための目印</v>
@@ -7771,7 +7765,7 @@
     </row>
     <row r="49" spans="1:14" ht="100.8">
       <c r="A49" s="11"/>
-      <c r="B49" s="125"/>
+      <c r="B49" s="113"/>
       <c r="C49" s="48" t="str">
         <f>master!C30</f>
         <v>Springフレームワークにおける部品の設定</v>
@@ -7798,7 +7792,7 @@
     </row>
     <row r="50" spans="1:14" ht="88.2">
       <c r="A50" s="11"/>
-      <c r="B50" s="125"/>
+      <c r="B50" s="113"/>
       <c r="C50" s="48" t="str">
         <f>master!C31</f>
         <v>Spring Boot</v>
@@ -7825,7 +7819,7 @@
     </row>
     <row r="51" spans="1:14" ht="63">
       <c r="A51" s="11"/>
-      <c r="B51" s="125"/>
+      <c r="B51" s="113"/>
       <c r="C51" s="48" t="str">
         <f>master!C32</f>
         <v>Spring Boot：オートコンフィグレーション</v>
@@ -7852,7 +7846,7 @@
     </row>
     <row r="52" spans="1:14" ht="50.4">
       <c r="A52" s="11"/>
-      <c r="B52" s="125"/>
+      <c r="B52" s="113"/>
       <c r="C52" s="48" t="str">
         <f>master!C33</f>
         <v>Spring Boot：Starters</v>
@@ -7879,7 +7873,7 @@
     </row>
     <row r="53" spans="1:14" ht="88.2">
       <c r="A53" s="11"/>
-      <c r="B53" s="125"/>
+      <c r="B53" s="113"/>
       <c r="C53" s="48" t="str">
         <f>master!C34</f>
         <v>Spring Boot：組込みWebAPサーバ</v>
@@ -7906,7 +7900,7 @@
     </row>
     <row r="54" spans="1:14" ht="25.2">
       <c r="A54" s="11"/>
-      <c r="B54" s="126"/>
+      <c r="B54" s="114"/>
       <c r="C54" s="48" t="str">
         <f>master!C35</f>
         <v>おすすめ書籍：『プロになるためのSpring入門』</v>
@@ -7931,7 +7925,7 @@
     </row>
     <row r="55" spans="1:14" ht="37.799999999999997">
       <c r="A55" s="11"/>
-      <c r="B55" s="121" t="str">
+      <c r="B55" s="115" t="str">
         <f>master!B37</f>
         <v>課題1の導入</v>
       </c>
@@ -7939,11 +7933,11 @@
         <f>master!C37</f>
         <v>演習課題の概要</v>
       </c>
-      <c r="D55" s="112" t="s">
+      <c r="D55" s="109" t="s">
         <v>165</v>
       </c>
-      <c r="E55" s="113"/>
-      <c r="F55" s="114"/>
+      <c r="E55" s="110"/>
+      <c r="F55" s="111"/>
       <c r="G55" s="58" t="s">
         <v>286</v>
       </c>
@@ -7961,16 +7955,16 @@
     </row>
     <row r="56" spans="1:14" ht="37.799999999999997">
       <c r="A56" s="11"/>
-      <c r="B56" s="122"/>
+      <c r="B56" s="116"/>
       <c r="C56" s="58" t="str">
         <f>master!C38</f>
         <v>作成物</v>
       </c>
-      <c r="D56" s="112" t="s">
+      <c r="D56" s="109" t="s">
         <v>166</v>
       </c>
-      <c r="E56" s="113"/>
-      <c r="F56" s="114"/>
+      <c r="E56" s="110"/>
+      <c r="F56" s="111"/>
       <c r="G56" s="58" t="s">
         <v>286</v>
       </c>
@@ -7988,16 +7982,16 @@
     </row>
     <row r="57" spans="1:14" ht="75.599999999999994">
       <c r="A57" s="11"/>
-      <c r="B57" s="123"/>
+      <c r="B57" s="117"/>
       <c r="C57" s="58" t="str">
         <f>master!C39</f>
         <v>演習課題の進め方</v>
       </c>
-      <c r="D57" s="112" t="s">
+      <c r="D57" s="109" t="s">
         <v>167</v>
       </c>
-      <c r="E57" s="113"/>
-      <c r="F57" s="114"/>
+      <c r="E57" s="110"/>
+      <c r="F57" s="111"/>
       <c r="G57" s="58" t="s">
         <v>287</v>
       </c>
@@ -8015,7 +8009,7 @@
     </row>
     <row r="58" spans="1:14" ht="15" customHeight="1">
       <c r="A58" s="11"/>
-      <c r="B58" s="121" t="str">
+      <c r="B58" s="115" t="str">
         <f>master!B40</f>
         <v>Spring Bootプロジェクトの_x000B_準備、起動確認</v>
       </c>
@@ -8023,9 +8017,9 @@
         <f>master!C40</f>
         <v>前提条件</v>
       </c>
-      <c r="D58" s="112"/>
-      <c r="E58" s="113"/>
-      <c r="F58" s="114"/>
+      <c r="D58" s="109"/>
+      <c r="E58" s="110"/>
+      <c r="F58" s="111"/>
       <c r="G58" s="58" t="s">
         <v>288</v>
       </c>
@@ -8043,16 +8037,16 @@
     </row>
     <row r="59" spans="1:14" ht="37.799999999999997">
       <c r="A59" s="11"/>
-      <c r="B59" s="122"/>
+      <c r="B59" s="116"/>
       <c r="C59" s="58" t="str">
         <f>master!C41</f>
         <v>Spring Bootプロジェクトの準備</v>
       </c>
-      <c r="D59" s="112" t="s">
+      <c r="D59" s="109" t="s">
         <v>168</v>
       </c>
-      <c r="E59" s="113"/>
-      <c r="F59" s="114"/>
+      <c r="E59" s="110"/>
+      <c r="F59" s="111"/>
       <c r="G59" s="58" t="s">
         <v>286</v>
       </c>
@@ -8070,16 +8064,16 @@
     </row>
     <row r="60" spans="1:14" ht="25.2">
       <c r="A60" s="11"/>
-      <c r="B60" s="122"/>
+      <c r="B60" s="116"/>
       <c r="C60" s="58" t="str">
         <f>master!C42</f>
         <v>（補足）Spring Bootプロジェクトの準備</v>
       </c>
-      <c r="D60" s="112" t="s">
+      <c r="D60" s="109" t="s">
         <v>169</v>
       </c>
-      <c r="E60" s="113"/>
-      <c r="F60" s="114"/>
+      <c r="E60" s="110"/>
+      <c r="F60" s="111"/>
       <c r="G60" s="58" t="s">
         <v>289</v>
       </c>
@@ -8097,16 +8091,16 @@
     </row>
     <row r="61" spans="1:14" ht="88.2">
       <c r="A61" s="11"/>
-      <c r="B61" s="123"/>
+      <c r="B61" s="117"/>
       <c r="C61" s="58" t="str">
         <f>master!C43</f>
         <v>Spring Bootアプリケーションの起動確認</v>
       </c>
-      <c r="D61" s="112" t="s">
+      <c r="D61" s="109" t="s">
         <v>191</v>
       </c>
-      <c r="E61" s="113"/>
-      <c r="F61" s="114"/>
+      <c r="E61" s="110"/>
+      <c r="F61" s="111"/>
       <c r="G61" s="58" t="s">
         <v>290</v>
       </c>
@@ -8124,7 +8118,7 @@
     </row>
     <row r="62" spans="1:14" ht="190.2" customHeight="1">
       <c r="A62" s="11"/>
-      <c r="B62" s="121" t="str">
+      <c r="B62" s="115" t="str">
         <f>master!B44</f>
         <v>ECサイト Webアプリの要件</v>
       </c>
@@ -8132,11 +8126,11 @@
         <f>master!C44</f>
         <v>ECサイト Webアプリの要件 – はじめに</v>
       </c>
-      <c r="D62" s="112" t="s">
+      <c r="D62" s="109" t="s">
         <v>170</v>
       </c>
-      <c r="E62" s="113"/>
-      <c r="F62" s="114"/>
+      <c r="E62" s="110"/>
+      <c r="F62" s="111"/>
       <c r="G62" s="58" t="s">
         <v>291</v>
       </c>
@@ -8154,16 +8148,16 @@
     </row>
     <row r="63" spans="1:14" ht="151.19999999999999">
       <c r="A63" s="11"/>
-      <c r="B63" s="122"/>
+      <c r="B63" s="116"/>
       <c r="C63" s="58" t="str">
         <f>master!C45</f>
         <v>ECサイト Webアプリの要件➊ 画面</v>
       </c>
-      <c r="D63" s="112" t="s">
+      <c r="D63" s="109" t="s">
         <v>172</v>
       </c>
-      <c r="E63" s="113"/>
-      <c r="F63" s="114"/>
+      <c r="E63" s="110"/>
+      <c r="F63" s="111"/>
       <c r="G63" s="58" t="s">
         <v>292</v>
       </c>
@@ -8181,16 +8175,16 @@
     </row>
     <row r="64" spans="1:14" ht="214.2">
       <c r="A64" s="11"/>
-      <c r="B64" s="122"/>
+      <c r="B64" s="116"/>
       <c r="C64" s="58" t="str">
         <f>master!C46</f>
         <v>ECサイト Webアプリの要件➋ 機能</v>
       </c>
-      <c r="D64" s="112" t="s">
+      <c r="D64" s="109" t="s">
         <v>173</v>
       </c>
-      <c r="E64" s="113"/>
-      <c r="F64" s="114"/>
+      <c r="E64" s="110"/>
+      <c r="F64" s="111"/>
       <c r="G64" s="58" t="s">
         <v>293</v>
       </c>
@@ -8208,16 +8202,16 @@
     </row>
     <row r="65" spans="1:14" ht="63">
       <c r="A65" s="11"/>
-      <c r="B65" s="122"/>
+      <c r="B65" s="116"/>
       <c r="C65" s="58" t="str">
         <f>master!C47</f>
         <v>ECサイト Webアプリの要件➌ 画面遷移</v>
       </c>
-      <c r="D65" s="112" t="s">
+      <c r="D65" s="109" t="s">
         <v>174</v>
       </c>
-      <c r="E65" s="113"/>
-      <c r="F65" s="114"/>
+      <c r="E65" s="110"/>
+      <c r="F65" s="111"/>
       <c r="G65" s="58" t="s">
         <v>294</v>
       </c>
@@ -8235,16 +8229,16 @@
     </row>
     <row r="66" spans="1:14" ht="163.80000000000001">
       <c r="A66" s="11"/>
-      <c r="B66" s="122"/>
+      <c r="B66" s="116"/>
       <c r="C66" s="58" t="str">
         <f>master!C48</f>
         <v>ECサイト Webアプリの要件❹ データ設計</v>
       </c>
-      <c r="D66" s="112" t="s">
+      <c r="D66" s="109" t="s">
         <v>176</v>
       </c>
-      <c r="E66" s="113"/>
-      <c r="F66" s="114"/>
+      <c r="E66" s="110"/>
+      <c r="F66" s="111"/>
       <c r="G66" s="58" t="s">
         <v>295</v>
       </c>
@@ -8262,16 +8256,16 @@
     </row>
     <row r="67" spans="1:14" ht="50.4">
       <c r="A67" s="11"/>
-      <c r="B67" s="122"/>
+      <c r="B67" s="116"/>
       <c r="C67" s="58" t="str">
         <f>master!C49</f>
         <v>ECサイト Webアプリの要件❺ 初期データ</v>
       </c>
-      <c r="D67" s="112" t="s">
+      <c r="D67" s="109" t="s">
         <v>177</v>
       </c>
-      <c r="E67" s="113"/>
-      <c r="F67" s="114"/>
+      <c r="E67" s="110"/>
+      <c r="F67" s="111"/>
       <c r="G67" s="58" t="s">
         <v>291</v>
       </c>
@@ -8289,16 +8283,16 @@
     </row>
     <row r="68" spans="1:14" ht="37.799999999999997">
       <c r="A68" s="11"/>
-      <c r="B68" s="122"/>
+      <c r="B68" s="116"/>
       <c r="C68" s="58" t="str">
         <f>master!C50</f>
         <v>ECサイト Webアプリの要件❻ ディレクトリ構成</v>
       </c>
-      <c r="D68" s="112" t="s">
+      <c r="D68" s="109" t="s">
         <v>178</v>
       </c>
-      <c r="E68" s="113"/>
-      <c r="F68" s="114"/>
+      <c r="E68" s="110"/>
+      <c r="F68" s="111"/>
       <c r="G68" s="58" t="s">
         <v>286</v>
       </c>
@@ -8316,16 +8310,16 @@
     </row>
     <row r="69" spans="1:14" ht="37.799999999999997">
       <c r="A69" s="11"/>
-      <c r="B69" s="122"/>
+      <c r="B69" s="116"/>
       <c r="C69" s="58" t="str">
         <f>master!C51</f>
         <v>ECサイト Webアプリの要件❼ パッケージ構成</v>
       </c>
-      <c r="D69" s="112" t="s">
+      <c r="D69" s="109" t="s">
         <v>180</v>
       </c>
-      <c r="E69" s="113"/>
-      <c r="F69" s="114"/>
+      <c r="E69" s="110"/>
+      <c r="F69" s="111"/>
       <c r="G69" s="58" t="s">
         <v>286</v>
       </c>
@@ -8343,16 +8337,16 @@
     </row>
     <row r="70" spans="1:14" ht="37.799999999999997">
       <c r="A70" s="11"/>
-      <c r="B70" s="123"/>
+      <c r="B70" s="117"/>
       <c r="C70" s="58" t="str">
         <f>master!C52</f>
         <v>ECサイト Webアプリの要件❽ リソース構成</v>
       </c>
-      <c r="D70" s="112" t="s">
+      <c r="D70" s="109" t="s">
         <v>179</v>
       </c>
-      <c r="E70" s="113"/>
-      <c r="F70" s="114"/>
+      <c r="E70" s="110"/>
+      <c r="F70" s="111"/>
       <c r="G70" s="58" t="s">
         <v>286</v>
       </c>
@@ -8370,7 +8364,7 @@
     </row>
     <row r="71" spans="1:14" ht="25.2">
       <c r="A71" s="11"/>
-      <c r="B71" s="121" t="str">
+      <c r="B71" s="115" t="str">
         <f>master!B53</f>
         <v>ハンズオン</v>
       </c>
@@ -8378,11 +8372,11 @@
         <f>master!C53</f>
         <v>バイブコーディング – はじめに</v>
       </c>
-      <c r="D71" s="112" t="s">
+      <c r="D71" s="109" t="s">
         <v>181</v>
       </c>
-      <c r="E71" s="113"/>
-      <c r="F71" s="114"/>
+      <c r="E71" s="110"/>
+      <c r="F71" s="111"/>
       <c r="G71" s="58" t="s">
         <v>289</v>
       </c>
@@ -8400,16 +8394,16 @@
     </row>
     <row r="72" spans="1:14" ht="138.6">
       <c r="A72" s="11"/>
-      <c r="B72" s="122"/>
+      <c r="B72" s="116"/>
       <c r="C72" s="58" t="str">
         <f>master!C54</f>
         <v>[構造理解] Webアプリケーションで必要なもの</v>
       </c>
-      <c r="D72" s="112" t="s">
+      <c r="D72" s="109" t="s">
         <v>182</v>
       </c>
-      <c r="E72" s="113"/>
-      <c r="F72" s="114"/>
+      <c r="E72" s="110"/>
+      <c r="F72" s="111"/>
       <c r="G72" s="58" t="s">
         <v>296</v>
       </c>
@@ -8427,16 +8421,16 @@
     </row>
     <row r="73" spans="1:14" ht="50.4">
       <c r="A73" s="11"/>
-      <c r="B73" s="122"/>
+      <c r="B73" s="116"/>
       <c r="C73" s="76" t="str">
         <f>master!C55</f>
         <v>バイブコーディング➊ 画面モックアップを作ってデザインを決める</v>
       </c>
-      <c r="D73" s="112" t="s">
+      <c r="D73" s="109" t="s">
         <v>192</v>
       </c>
-      <c r="E73" s="113"/>
-      <c r="F73" s="114"/>
+      <c r="E73" s="110"/>
+      <c r="F73" s="111"/>
       <c r="G73" s="58" t="s">
         <v>291</v>
       </c>
@@ -8454,13 +8448,13 @@
     </row>
     <row r="74" spans="1:14" ht="88.2" customHeight="1">
       <c r="A74" s="11"/>
-      <c r="B74" s="122"/>
+      <c r="B74" s="116"/>
       <c r="C74" s="77"/>
-      <c r="D74" s="112" t="s">
+      <c r="D74" s="109" t="s">
         <v>183</v>
       </c>
-      <c r="E74" s="113"/>
-      <c r="F74" s="114"/>
+      <c r="E74" s="110"/>
+      <c r="F74" s="111"/>
       <c r="G74" s="58" t="s">
         <v>290</v>
       </c>
@@ -8474,16 +8468,16 @@
     </row>
     <row r="75" spans="1:14" ht="50.4">
       <c r="A75" s="11"/>
-      <c r="B75" s="122"/>
+      <c r="B75" s="116"/>
       <c r="C75" s="76" t="str">
         <f>master!C56</f>
         <v>バイブコーディング➋ データベースのテーブルを準備する</v>
       </c>
-      <c r="D75" s="112" t="s">
+      <c r="D75" s="109" t="s">
         <v>196</v>
       </c>
-      <c r="E75" s="113"/>
-      <c r="F75" s="114"/>
+      <c r="E75" s="110"/>
+      <c r="F75" s="111"/>
       <c r="G75" s="58" t="s">
         <v>291</v>
       </c>
@@ -8501,13 +8495,13 @@
     </row>
     <row r="76" spans="1:14" ht="88.2">
       <c r="A76" s="11"/>
-      <c r="B76" s="122"/>
+      <c r="B76" s="116"/>
       <c r="C76" s="77"/>
-      <c r="D76" s="112" t="s">
+      <c r="D76" s="109" t="s">
         <v>183</v>
       </c>
-      <c r="E76" s="113"/>
-      <c r="F76" s="114"/>
+      <c r="E76" s="110"/>
+      <c r="F76" s="111"/>
       <c r="G76" s="58" t="s">
         <v>290</v>
       </c>
@@ -8521,16 +8515,16 @@
     </row>
     <row r="77" spans="1:14" ht="50.4">
       <c r="A77" s="11"/>
-      <c r="B77" s="122"/>
+      <c r="B77" s="116"/>
       <c r="C77" s="76" t="str">
         <f>master!C57</f>
         <v>バイブコーディング➌ データベースのデータを準備する</v>
       </c>
-      <c r="D77" s="112" t="s">
+      <c r="D77" s="109" t="s">
         <v>195</v>
       </c>
-      <c r="E77" s="113"/>
-      <c r="F77" s="114"/>
+      <c r="E77" s="110"/>
+      <c r="F77" s="111"/>
       <c r="G77" s="58" t="s">
         <v>291</v>
       </c>
@@ -8548,13 +8542,13 @@
     </row>
     <row r="78" spans="1:14" ht="88.2">
       <c r="A78" s="11"/>
-      <c r="B78" s="122"/>
+      <c r="B78" s="116"/>
       <c r="C78" s="77"/>
-      <c r="D78" s="112" t="s">
+      <c r="D78" s="109" t="s">
         <v>183</v>
       </c>
-      <c r="E78" s="113"/>
-      <c r="F78" s="114"/>
+      <c r="E78" s="110"/>
+      <c r="F78" s="111"/>
       <c r="G78" s="58" t="s">
         <v>290</v>
       </c>
@@ -8568,16 +8562,16 @@
     </row>
     <row r="79" spans="1:14" ht="63">
       <c r="A79" s="11"/>
-      <c r="B79" s="122"/>
+      <c r="B79" s="116"/>
       <c r="C79" s="76" t="str">
         <f>master!C58</f>
         <v>バイブコーディング❹ データベース処理とビジネスロジックを作る</v>
       </c>
-      <c r="D79" s="112" t="s">
+      <c r="D79" s="109" t="s">
         <v>194</v>
       </c>
-      <c r="E79" s="113"/>
-      <c r="F79" s="114"/>
+      <c r="E79" s="110"/>
+      <c r="F79" s="111"/>
       <c r="G79" s="58" t="s">
         <v>294</v>
       </c>
@@ -8595,13 +8589,13 @@
     </row>
     <row r="80" spans="1:14" ht="88.2">
       <c r="A80" s="11"/>
-      <c r="B80" s="122"/>
+      <c r="B80" s="116"/>
       <c r="C80" s="77"/>
-      <c r="D80" s="112" t="s">
+      <c r="D80" s="109" t="s">
         <v>183</v>
       </c>
-      <c r="E80" s="113"/>
-      <c r="F80" s="114"/>
+      <c r="E80" s="110"/>
+      <c r="F80" s="111"/>
       <c r="G80" s="58" t="s">
         <v>290</v>
       </c>
@@ -8615,16 +8609,16 @@
     </row>
     <row r="81" spans="1:14" ht="50.4">
       <c r="A81" s="11"/>
-      <c r="B81" s="122"/>
+      <c r="B81" s="116"/>
       <c r="C81" s="58" t="str">
         <f>master!C59</f>
         <v>[解説] RepositoryクラスとSQLの例（抜粋）</v>
       </c>
-      <c r="D81" s="112" t="s">
+      <c r="D81" s="109" t="s">
         <v>184</v>
       </c>
-      <c r="E81" s="113"/>
-      <c r="F81" s="114"/>
+      <c r="E81" s="110"/>
+      <c r="F81" s="111"/>
       <c r="G81" s="58" t="s">
         <v>291</v>
       </c>
@@ -8642,16 +8636,16 @@
     </row>
     <row r="82" spans="1:14" ht="50.4">
       <c r="A82" s="11"/>
-      <c r="B82" s="122"/>
+      <c r="B82" s="116"/>
       <c r="C82" s="58" t="str">
         <f>master!C60</f>
         <v>[解説] Entity/Modelクラスの例（抜粋）</v>
       </c>
-      <c r="D82" s="112" t="s">
+      <c r="D82" s="109" t="s">
         <v>185</v>
       </c>
-      <c r="E82" s="113"/>
-      <c r="F82" s="114"/>
+      <c r="E82" s="110"/>
+      <c r="F82" s="111"/>
       <c r="G82" s="58" t="s">
         <v>291</v>
       </c>
@@ -8669,16 +8663,16 @@
     </row>
     <row r="83" spans="1:14" ht="37.799999999999997">
       <c r="A83" s="11"/>
-      <c r="B83" s="122"/>
+      <c r="B83" s="116"/>
       <c r="C83" s="58" t="str">
         <f>master!C61</f>
         <v>[解説] Serviceクラスの例（抜粋）</v>
       </c>
-      <c r="D83" s="112" t="s">
+      <c r="D83" s="109" t="s">
         <v>186</v>
       </c>
-      <c r="E83" s="113"/>
-      <c r="F83" s="114"/>
+      <c r="E83" s="110"/>
+      <c r="F83" s="111"/>
       <c r="G83" s="58" t="s">
         <v>286</v>
       </c>
@@ -8696,16 +8690,16 @@
     </row>
     <row r="84" spans="1:14" ht="50.4">
       <c r="A84" s="11"/>
-      <c r="B84" s="122"/>
+      <c r="B84" s="116"/>
       <c r="C84" s="76" t="str">
         <f>master!C62</f>
         <v>バイブコーディング❺ モックアップをもとに画面表示/処理を作る</v>
       </c>
-      <c r="D84" s="112" t="s">
+      <c r="D84" s="109" t="s">
         <v>193</v>
       </c>
-      <c r="E84" s="113"/>
-      <c r="F84" s="114"/>
+      <c r="E84" s="110"/>
+      <c r="F84" s="111"/>
       <c r="G84" s="58" t="s">
         <v>291</v>
       </c>
@@ -8723,13 +8717,13 @@
     </row>
     <row r="85" spans="1:14" ht="88.2">
       <c r="A85" s="11"/>
-      <c r="B85" s="122"/>
+      <c r="B85" s="116"/>
       <c r="C85" s="77"/>
-      <c r="D85" s="112" t="s">
+      <c r="D85" s="109" t="s">
         <v>183</v>
       </c>
-      <c r="E85" s="113"/>
-      <c r="F85" s="114"/>
+      <c r="E85" s="110"/>
+      <c r="F85" s="111"/>
       <c r="G85" s="58" t="s">
         <v>290</v>
       </c>
@@ -8743,16 +8737,16 @@
     </row>
     <row r="86" spans="1:14" ht="37.799999999999997">
       <c r="A86" s="11"/>
-      <c r="B86" s="122"/>
+      <c r="B86" s="116"/>
       <c r="C86" s="58" t="str">
         <f>master!C63</f>
         <v>[解説] Controllerクラスの例（抜粋）</v>
       </c>
-      <c r="D86" s="112" t="s">
+      <c r="D86" s="109" t="s">
         <v>187</v>
       </c>
-      <c r="E86" s="113"/>
-      <c r="F86" s="114"/>
+      <c r="E86" s="110"/>
+      <c r="F86" s="111"/>
       <c r="G86" s="58" t="s">
         <v>286</v>
       </c>
@@ -8770,16 +8764,16 @@
     </row>
     <row r="87" spans="1:14" ht="37.799999999999997">
       <c r="A87" s="11"/>
-      <c r="B87" s="122"/>
+      <c r="B87" s="116"/>
       <c r="C87" s="58" t="str">
         <f>master!C64</f>
         <v>[解説] Thymeleafテンプレートの例（抜粋）</v>
       </c>
-      <c r="D87" s="112" t="s">
+      <c r="D87" s="109" t="s">
         <v>188</v>
       </c>
-      <c r="E87" s="113"/>
-      <c r="F87" s="114"/>
+      <c r="E87" s="110"/>
+      <c r="F87" s="111"/>
       <c r="G87" s="58" t="s">
         <v>286</v>
       </c>
@@ -8797,16 +8791,16 @@
     </row>
     <row r="88" spans="1:14" ht="37.799999999999997">
       <c r="A88" s="11"/>
-      <c r="B88" s="122"/>
+      <c r="B88" s="116"/>
       <c r="C88" s="58" t="str">
         <f>master!C65</f>
         <v>[解説] Formクラスの例（抜粋）</v>
       </c>
-      <c r="D88" s="112" t="s">
+      <c r="D88" s="109" t="s">
         <v>189</v>
       </c>
-      <c r="E88" s="113"/>
-      <c r="F88" s="114"/>
+      <c r="E88" s="110"/>
+      <c r="F88" s="111"/>
       <c r="G88" s="58" t="s">
         <v>286</v>
       </c>
@@ -8824,16 +8818,16 @@
     </row>
     <row r="89" spans="1:14" ht="75.599999999999994">
       <c r="A89" s="11"/>
-      <c r="B89" s="122"/>
+      <c r="B89" s="116"/>
       <c r="C89" s="76" t="str">
         <f>master!C66</f>
         <v>バイブコーディング❻ 動作を確認する</v>
       </c>
-      <c r="D89" s="112" t="s">
+      <c r="D89" s="109" t="s">
         <v>190</v>
       </c>
-      <c r="E89" s="113"/>
-      <c r="F89" s="114"/>
+      <c r="E89" s="110"/>
+      <c r="F89" s="111"/>
       <c r="G89" s="58" t="s">
         <v>287</v>
       </c>
@@ -8851,13 +8845,13 @@
     </row>
     <row r="90" spans="1:14" ht="63">
       <c r="A90" s="11"/>
-      <c r="B90" s="123"/>
+      <c r="B90" s="117"/>
       <c r="C90" s="77"/>
-      <c r="D90" s="112" t="s">
+      <c r="D90" s="109" t="s">
         <v>197</v>
       </c>
-      <c r="E90" s="113"/>
-      <c r="F90" s="114"/>
+      <c r="E90" s="110"/>
+      <c r="F90" s="111"/>
       <c r="G90" s="58" t="s">
         <v>294</v>
       </c>
@@ -8875,7 +8869,7 @@
     </row>
     <row r="91" spans="1:14" ht="50.4">
       <c r="A91" s="11"/>
-      <c r="B91" s="124" t="str">
+      <c r="B91" s="112" t="str">
         <f>master!B69</f>
         <v>Gitとは</v>
       </c>
@@ -8884,7 +8878,7 @@
         <v>はじめに</v>
       </c>
       <c r="D91" s="118" t="s">
-        <v>412</v>
+        <v>399</v>
       </c>
       <c r="E91" s="119"/>
       <c r="F91" s="120"/>
@@ -8905,13 +8899,13 @@
     </row>
     <row r="92" spans="1:14" ht="37.799999999999997">
       <c r="A92" s="11"/>
-      <c r="B92" s="125"/>
+      <c r="B92" s="113"/>
       <c r="C92" s="48" t="str">
         <f>master!C70</f>
         <v>バージョン管理とは</v>
       </c>
       <c r="D92" s="118" t="s">
-        <v>387</v>
+        <v>374</v>
       </c>
       <c r="E92" s="119"/>
       <c r="F92" s="120"/>
@@ -8932,18 +8926,18 @@
     </row>
     <row r="93" spans="1:14" ht="151.19999999999999">
       <c r="A93" s="11"/>
-      <c r="B93" s="126"/>
+      <c r="B93" s="114"/>
       <c r="C93" s="48" t="str">
         <f>master!C71</f>
         <v>Gitの概要</v>
       </c>
       <c r="D93" s="118" t="s">
-        <v>388</v>
+        <v>375</v>
       </c>
       <c r="E93" s="119"/>
       <c r="F93" s="120"/>
       <c r="G93" s="48" t="s">
-        <v>389</v>
+        <v>376</v>
       </c>
       <c r="H93" s="12"/>
       <c r="I93" s="46" t="s">
@@ -8959,7 +8953,7 @@
     </row>
     <row r="94" spans="1:14" ht="75.599999999999994">
       <c r="A94" s="11"/>
-      <c r="B94" s="124" t="str">
+      <c r="B94" s="112" t="str">
         <f>master!B72</f>
         <v>Gitの基本構成</v>
       </c>
@@ -8968,12 +8962,12 @@
         <v>はじめに</v>
       </c>
       <c r="D94" s="118" t="s">
-        <v>411</v>
+        <v>398</v>
       </c>
       <c r="E94" s="119"/>
       <c r="F94" s="120"/>
       <c r="G94" s="48" t="s">
-        <v>390</v>
+        <v>377</v>
       </c>
       <c r="H94" s="12"/>
       <c r="I94" s="46" t="s">
@@ -8989,13 +8983,13 @@
     </row>
     <row r="95" spans="1:14" ht="37.799999999999997">
       <c r="A95" s="11"/>
-      <c r="B95" s="125"/>
+      <c r="B95" s="113"/>
       <c r="C95" s="48" t="str">
         <f>master!C73</f>
         <v>ワーキングツリー</v>
       </c>
       <c r="D95" s="118" t="s">
-        <v>391</v>
+        <v>378</v>
       </c>
       <c r="E95" s="119"/>
       <c r="F95" s="120"/>
@@ -9016,13 +9010,13 @@
     </row>
     <row r="96" spans="1:14" ht="37.799999999999997">
       <c r="A96" s="11"/>
-      <c r="B96" s="125"/>
+      <c r="B96" s="113"/>
       <c r="C96" s="48" t="str">
         <f>master!C74</f>
         <v>ステージングエリア</v>
       </c>
       <c r="D96" s="118" t="s">
-        <v>392</v>
+        <v>379</v>
       </c>
       <c r="E96" s="119"/>
       <c r="F96" s="120"/>
@@ -9043,13 +9037,13 @@
     </row>
     <row r="97" spans="1:14" ht="37.799999999999997">
       <c r="A97" s="11"/>
-      <c r="B97" s="125"/>
+      <c r="B97" s="113"/>
       <c r="C97" s="48" t="str">
         <f>master!C75</f>
         <v>ローカルリポジトリ</v>
       </c>
       <c r="D97" s="118" t="s">
-        <v>393</v>
+        <v>380</v>
       </c>
       <c r="E97" s="119"/>
       <c r="F97" s="120"/>
@@ -9070,13 +9064,13 @@
     </row>
     <row r="98" spans="1:14" ht="50.4">
       <c r="A98" s="11"/>
-      <c r="B98" s="126"/>
+      <c r="B98" s="114"/>
       <c r="C98" s="48" t="str">
         <f>master!C76</f>
         <v>リモートリポジトリ</v>
       </c>
       <c r="D98" s="118" t="s">
-        <v>394</v>
+        <v>381</v>
       </c>
       <c r="E98" s="119"/>
       <c r="F98" s="120"/>
@@ -9097,7 +9091,7 @@
     </row>
     <row r="99" spans="1:14" ht="88.2">
       <c r="A99" s="11"/>
-      <c r="B99" s="124" t="str">
+      <c r="B99" s="112" t="str">
         <f>master!B77</f>
         <v>ローカルリポジトリの操作</v>
       </c>
@@ -9106,12 +9100,12 @@
         <v>はじめに</v>
       </c>
       <c r="D99" s="118" t="s">
-        <v>410</v>
+        <v>397</v>
       </c>
       <c r="E99" s="119"/>
       <c r="F99" s="120"/>
       <c r="G99" s="48" t="s">
-        <v>395</v>
+        <v>382</v>
       </c>
       <c r="H99" s="12"/>
       <c r="I99" s="46" t="s">
@@ -9127,13 +9121,13 @@
     </row>
     <row r="100" spans="1:14" ht="37.799999999999997">
       <c r="A100" s="11"/>
-      <c r="B100" s="125"/>
+      <c r="B100" s="113"/>
       <c r="C100" s="48" t="str">
         <f>master!C78</f>
         <v>リポジトリの作成</v>
       </c>
       <c r="D100" s="118" t="s">
-        <v>396</v>
+        <v>383</v>
       </c>
       <c r="E100" s="119"/>
       <c r="F100" s="120"/>
@@ -9154,13 +9148,13 @@
     </row>
     <row r="101" spans="1:14" ht="37.799999999999997" customHeight="1">
       <c r="A101" s="11"/>
-      <c r="B101" s="125"/>
+      <c r="B101" s="113"/>
       <c r="C101" s="48" t="str">
         <f>master!C79</f>
         <v>ファイルの変更</v>
       </c>
       <c r="D101" s="118" t="s">
-        <v>397</v>
+        <v>384</v>
       </c>
       <c r="E101" s="119"/>
       <c r="F101" s="120"/>
@@ -9181,13 +9175,13 @@
     </row>
     <row r="102" spans="1:14" ht="37.799999999999997">
       <c r="A102" s="11"/>
-      <c r="B102" s="125"/>
+      <c r="B102" s="113"/>
       <c r="C102" s="48" t="str">
         <f>master!C80</f>
         <v>変更内容の確認</v>
       </c>
       <c r="D102" s="118" t="s">
-        <v>398</v>
+        <v>385</v>
       </c>
       <c r="E102" s="119"/>
       <c r="F102" s="120"/>
@@ -9208,13 +9202,13 @@
     </row>
     <row r="103" spans="1:14" ht="37.799999999999997">
       <c r="A103" s="11"/>
-      <c r="B103" s="125"/>
+      <c r="B103" s="113"/>
       <c r="C103" s="48" t="str">
         <f>master!C81</f>
         <v>変更内容のステージ</v>
       </c>
       <c r="D103" s="118" t="s">
-        <v>399</v>
+        <v>386</v>
       </c>
       <c r="E103" s="119"/>
       <c r="F103" s="120"/>
@@ -9235,13 +9229,13 @@
     </row>
     <row r="104" spans="1:14" ht="37.799999999999997">
       <c r="A104" s="11"/>
-      <c r="B104" s="125"/>
+      <c r="B104" s="113"/>
       <c r="C104" s="48" t="str">
         <f>master!C82</f>
         <v>変更内容のコミット</v>
       </c>
       <c r="D104" s="118" t="s">
-        <v>400</v>
+        <v>387</v>
       </c>
       <c r="E104" s="119"/>
       <c r="F104" s="120"/>
@@ -9262,13 +9256,13 @@
     </row>
     <row r="105" spans="1:14" ht="37.799999999999997">
       <c r="A105" s="11"/>
-      <c r="B105" s="125"/>
+      <c r="B105" s="113"/>
       <c r="C105" s="48" t="str">
         <f>master!C83</f>
         <v>ワーキングツリーの変更の取り消し</v>
       </c>
       <c r="D105" s="118" t="s">
-        <v>401</v>
+        <v>388</v>
       </c>
       <c r="E105" s="119"/>
       <c r="F105" s="120"/>
@@ -9289,13 +9283,13 @@
     </row>
     <row r="106" spans="1:14" ht="37.799999999999997">
       <c r="A106" s="11"/>
-      <c r="B106" s="125"/>
+      <c r="B106" s="113"/>
       <c r="C106" s="48" t="str">
         <f>master!C84</f>
         <v>ステージングの取り消し</v>
       </c>
       <c r="D106" s="118" t="s">
-        <v>402</v>
+        <v>389</v>
       </c>
       <c r="E106" s="119"/>
       <c r="F106" s="120"/>
@@ -9316,13 +9310,13 @@
     </row>
     <row r="107" spans="1:14" ht="37.799999999999997">
       <c r="A107" s="11"/>
-      <c r="B107" s="126"/>
+      <c r="B107" s="114"/>
       <c r="C107" s="48" t="str">
         <f>master!C85</f>
         <v>コミットの打ち消し</v>
       </c>
       <c r="D107" s="118" t="s">
-        <v>403</v>
+        <v>390</v>
       </c>
       <c r="E107" s="119"/>
       <c r="F107" s="120"/>
@@ -9343,7 +9337,7 @@
     </row>
     <row r="108" spans="1:14" ht="75.599999999999994">
       <c r="A108" s="11"/>
-      <c r="B108" s="124" t="str">
+      <c r="B108" s="112" t="str">
         <f>master!B86</f>
         <v>リモートリポジトリの操作</v>
       </c>
@@ -9352,12 +9346,12 @@
         <v>はじめに</v>
       </c>
       <c r="D108" s="118" t="s">
-        <v>408</v>
+        <v>395</v>
       </c>
       <c r="E108" s="119"/>
       <c r="F108" s="120"/>
       <c r="G108" s="48" t="s">
-        <v>390</v>
+        <v>377</v>
       </c>
       <c r="H108" s="12"/>
       <c r="I108" s="46" t="s">
@@ -9367,7 +9361,7 @@
         <v>0</v>
       </c>
       <c r="K108" s="89" t="s">
-        <v>436</v>
+        <v>423</v>
       </c>
       <c r="L108" s="6"/>
       <c r="M108" s="6"/>
@@ -9375,13 +9369,13 @@
     </row>
     <row r="109" spans="1:14" ht="37.799999999999997">
       <c r="A109" s="11"/>
-      <c r="B109" s="125"/>
+      <c r="B109" s="113"/>
       <c r="C109" s="48" t="str">
         <f>master!C87</f>
-        <v>リポジトリの取得</v>
+        <v>リポジトリの複製</v>
       </c>
       <c r="D109" s="118" t="s">
-        <v>404</v>
+        <v>391</v>
       </c>
       <c r="E109" s="119"/>
       <c r="F109" s="120"/>
@@ -9396,7 +9390,7 @@
         <v>0</v>
       </c>
       <c r="K109" s="89" t="s">
-        <v>436</v>
+        <v>423</v>
       </c>
       <c r="L109" s="6"/>
       <c r="M109" s="6"/>
@@ -9404,13 +9398,13 @@
     </row>
     <row r="110" spans="1:14" ht="37.799999999999997">
       <c r="A110" s="11"/>
-      <c r="B110" s="125"/>
+      <c r="B110" s="113"/>
       <c r="C110" s="48" t="str">
         <f>master!C88</f>
         <v>リモートからの取得</v>
       </c>
       <c r="D110" s="118" t="s">
-        <v>405</v>
+        <v>392</v>
       </c>
       <c r="E110" s="119"/>
       <c r="F110" s="120"/>
@@ -9425,7 +9419,7 @@
         <v>0</v>
       </c>
       <c r="K110" s="89" t="s">
-        <v>436</v>
+        <v>423</v>
       </c>
       <c r="L110" s="6"/>
       <c r="M110" s="6"/>
@@ -9433,13 +9427,13 @@
     </row>
     <row r="111" spans="1:14" ht="37.799999999999997">
       <c r="A111" s="11"/>
-      <c r="B111" s="125"/>
+      <c r="B111" s="113"/>
       <c r="C111" s="48" t="str">
         <f>master!C89</f>
         <v>リモートからの取得と反映</v>
       </c>
       <c r="D111" s="118" t="s">
-        <v>407</v>
+        <v>394</v>
       </c>
       <c r="E111" s="119"/>
       <c r="F111" s="120"/>
@@ -9454,7 +9448,7 @@
         <v>0</v>
       </c>
       <c r="K111" s="89" t="s">
-        <v>436</v>
+        <v>423</v>
       </c>
       <c r="L111" s="6"/>
       <c r="M111" s="6"/>
@@ -9462,13 +9456,13 @@
     </row>
     <row r="112" spans="1:14" ht="37.799999999999997">
       <c r="A112" s="11"/>
-      <c r="B112" s="126"/>
+      <c r="B112" s="114"/>
       <c r="C112" s="48" t="str">
         <f>master!C90</f>
         <v>リモートへの反映</v>
       </c>
       <c r="D112" s="118" t="s">
-        <v>406</v>
+        <v>393</v>
       </c>
       <c r="E112" s="119"/>
       <c r="F112" s="120"/>
@@ -9483,7 +9477,7 @@
         <v>0</v>
       </c>
       <c r="K112" s="89" t="s">
-        <v>436</v>
+        <v>423</v>
       </c>
       <c r="L112" s="6"/>
       <c r="M112" s="6"/>
@@ -9491,7 +9485,7 @@
     </row>
     <row r="113" spans="1:14" ht="88.2">
       <c r="A113" s="11"/>
-      <c r="B113" s="124" t="str">
+      <c r="B113" s="112" t="str">
         <f>master!B91</f>
         <v>ブランチの操作</v>
       </c>
@@ -9500,12 +9494,12 @@
         <v>はじめに</v>
       </c>
       <c r="D113" s="118" t="s">
-        <v>409</v>
+        <v>396</v>
       </c>
       <c r="E113" s="119"/>
       <c r="F113" s="120"/>
       <c r="G113" s="48" t="s">
-        <v>395</v>
+        <v>382</v>
       </c>
       <c r="H113" s="12"/>
       <c r="I113" s="46" t="s">
@@ -9515,7 +9509,7 @@
         <v>0</v>
       </c>
       <c r="K113" s="89" t="s">
-        <v>434</v>
+        <v>421</v>
       </c>
       <c r="L113" s="6"/>
       <c r="M113" s="6"/>
@@ -9523,13 +9517,13 @@
     </row>
     <row r="114" spans="1:14" ht="37.799999999999997">
       <c r="A114" s="11"/>
-      <c r="B114" s="125"/>
+      <c r="B114" s="113"/>
       <c r="C114" s="48" t="str">
         <f>master!C92</f>
         <v>ブランチとは</v>
       </c>
       <c r="D114" s="118" t="s">
-        <v>413</v>
+        <v>400</v>
       </c>
       <c r="E114" s="119"/>
       <c r="F114" s="120"/>
@@ -9550,13 +9544,13 @@
     </row>
     <row r="115" spans="1:14" ht="37.799999999999997">
       <c r="A115" s="11"/>
-      <c r="B115" s="125"/>
+      <c r="B115" s="113"/>
       <c r="C115" s="48" t="str">
         <f>master!C93</f>
         <v>ブランチの作成</v>
       </c>
       <c r="D115" s="118" t="s">
-        <v>414</v>
+        <v>401</v>
       </c>
       <c r="E115" s="119"/>
       <c r="F115" s="120"/>
@@ -9577,13 +9571,13 @@
     </row>
     <row r="116" spans="1:14" ht="37.799999999999997">
       <c r="A116" s="11"/>
-      <c r="B116" s="125"/>
+      <c r="B116" s="113"/>
       <c r="C116" s="48" t="str">
         <f>master!C94</f>
         <v>ブランチの切り替え</v>
       </c>
       <c r="D116" s="118" t="s">
-        <v>415</v>
+        <v>402</v>
       </c>
       <c r="E116" s="119"/>
       <c r="F116" s="120"/>
@@ -9604,13 +9598,13 @@
     </row>
     <row r="117" spans="1:14" ht="37.799999999999997">
       <c r="A117" s="11"/>
-      <c r="B117" s="125"/>
+      <c r="B117" s="113"/>
       <c r="C117" s="48" t="str">
         <f>master!C95</f>
         <v>ブランチのマージ</v>
       </c>
       <c r="D117" s="118" t="s">
-        <v>416</v>
+        <v>403</v>
       </c>
       <c r="E117" s="119"/>
       <c r="F117" s="120"/>
@@ -9631,13 +9625,13 @@
     </row>
     <row r="118" spans="1:14" ht="100.8">
       <c r="A118" s="11"/>
-      <c r="B118" s="126"/>
+      <c r="B118" s="114"/>
       <c r="C118" s="48" t="str">
         <f>master!C96</f>
         <v>コンフリクトの解消</v>
       </c>
       <c r="D118" s="118" t="s">
-        <v>418</v>
+        <v>405</v>
       </c>
       <c r="E118" s="119"/>
       <c r="F118" s="120"/>
@@ -9658,7 +9652,7 @@
     </row>
     <row r="119" spans="1:14" ht="75.599999999999994">
       <c r="A119" s="11"/>
-      <c r="B119" s="124" t="str">
+      <c r="B119" s="112" t="str">
         <f>master!B97</f>
         <v>VSCodeによるGitの操作</v>
       </c>
@@ -9667,12 +9661,12 @@
         <v>はじめに</v>
       </c>
       <c r="D119" s="118" t="s">
-        <v>417</v>
+        <v>404</v>
       </c>
       <c r="E119" s="119"/>
       <c r="F119" s="120"/>
       <c r="G119" s="48" t="s">
-        <v>390</v>
+        <v>377</v>
       </c>
       <c r="H119" s="12"/>
       <c r="I119" s="46" t="s">
@@ -9688,18 +9682,18 @@
     </row>
     <row r="120" spans="1:14" ht="25.2">
       <c r="A120" s="11"/>
-      <c r="B120" s="125"/>
+      <c r="B120" s="113"/>
       <c r="C120" s="48" t="str">
         <f>master!C98</f>
         <v>VSCodeのソース管理機能</v>
       </c>
       <c r="D120" s="118" t="s">
-        <v>419</v>
+        <v>406</v>
       </c>
       <c r="E120" s="119"/>
       <c r="F120" s="120"/>
       <c r="G120" s="48" t="s">
-        <v>420</v>
+        <v>407</v>
       </c>
       <c r="H120" s="12"/>
       <c r="I120" s="46" t="s">
@@ -9715,18 +9709,18 @@
     </row>
     <row r="121" spans="1:14" ht="126">
       <c r="A121" s="11"/>
-      <c r="B121" s="125"/>
+      <c r="B121" s="113"/>
       <c r="C121" s="48" t="str">
         <f>master!C99</f>
         <v>ローカルリポジトリの操作</v>
       </c>
       <c r="D121" s="118" t="s">
-        <v>431</v>
+        <v>418</v>
       </c>
       <c r="E121" s="119"/>
       <c r="F121" s="120"/>
       <c r="G121" s="48" t="s">
-        <v>430</v>
+        <v>417</v>
       </c>
       <c r="H121" s="12"/>
       <c r="I121" s="46" t="s">
@@ -9742,13 +9736,13 @@
     </row>
     <row r="122" spans="1:14" ht="63">
       <c r="A122" s="11"/>
-      <c r="B122" s="125"/>
+      <c r="B122" s="113"/>
       <c r="C122" s="48" t="str">
         <f>master!C100</f>
         <v>リモートリポジトリの操作</v>
       </c>
       <c r="D122" s="118" t="s">
-        <v>421</v>
+        <v>408</v>
       </c>
       <c r="E122" s="119"/>
       <c r="F122" s="120"/>
@@ -9763,7 +9757,7 @@
         <v>0</v>
       </c>
       <c r="K122" s="89" t="s">
-        <v>436</v>
+        <v>423</v>
       </c>
       <c r="L122" s="6"/>
       <c r="M122" s="6"/>
@@ -9771,18 +9765,18 @@
     </row>
     <row r="123" spans="1:14" ht="113.4">
       <c r="A123" s="11"/>
-      <c r="B123" s="126"/>
+      <c r="B123" s="114"/>
       <c r="C123" s="48" t="str">
         <f>master!C101</f>
         <v>ブランチの操作</v>
       </c>
       <c r="D123" s="118" t="s">
-        <v>432</v>
+        <v>419</v>
       </c>
       <c r="E123" s="119"/>
       <c r="F123" s="120"/>
       <c r="G123" s="48" t="s">
-        <v>433</v>
+        <v>420</v>
       </c>
       <c r="H123" s="12"/>
       <c r="I123" s="46" t="s">
@@ -9792,7 +9786,7 @@
         <v>0</v>
       </c>
       <c r="K123" s="89" t="s">
-        <v>435</v>
+        <v>422</v>
       </c>
       <c r="L123" s="6"/>
       <c r="M123" s="6"/>
@@ -9800,17 +9794,17 @@
     </row>
     <row r="124" spans="1:14" ht="25.2">
       <c r="A124" s="11"/>
-      <c r="B124" s="121" t="str">
+      <c r="B124" s="115" t="str">
         <f>master!B103</f>
-        <v>演習について</v>
+        <v>演習の概要について</v>
       </c>
       <c r="C124" s="58" t="str">
         <f>master!C103</f>
         <v>はじめに</v>
       </c>
-      <c r="D124" s="112"/>
-      <c r="E124" s="113"/>
-      <c r="F124" s="114"/>
+      <c r="D124" s="109"/>
+      <c r="E124" s="110"/>
+      <c r="F124" s="111"/>
       <c r="G124" s="58" t="s">
         <v>335</v>
       </c>
@@ -9828,18 +9822,18 @@
     </row>
     <row r="125" spans="1:14" ht="50.4">
       <c r="A125" s="11"/>
-      <c r="B125" s="122"/>
+      <c r="B125" s="116"/>
       <c r="C125" s="58" t="str">
         <f>master!C104</f>
-        <v>演習の構成</v>
-      </c>
-      <c r="D125" s="112" t="s">
-        <v>423</v>
-      </c>
-      <c r="E125" s="113"/>
-      <c r="F125" s="114"/>
+        <v>構成</v>
+      </c>
+      <c r="D125" s="109" t="s">
+        <v>410</v>
+      </c>
+      <c r="E125" s="110"/>
+      <c r="F125" s="111"/>
       <c r="G125" s="58" t="s">
-        <v>422</v>
+        <v>409</v>
       </c>
       <c r="H125" s="59"/>
       <c r="I125" s="60" t="s">
@@ -9855,18 +9849,18 @@
     </row>
     <row r="126" spans="1:14" ht="50.4">
       <c r="A126" s="11"/>
-      <c r="B126" s="123"/>
+      <c r="B126" s="117"/>
       <c r="C126" s="58" t="str">
         <f>master!C105</f>
-        <v>演習で利用するソフトウェア</v>
-      </c>
-      <c r="D126" s="112" t="s">
-        <v>424</v>
-      </c>
-      <c r="E126" s="113"/>
-      <c r="F126" s="114"/>
+        <v>利用するソフトウェア</v>
+      </c>
+      <c r="D126" s="109" t="s">
+        <v>411</v>
+      </c>
+      <c r="E126" s="110"/>
+      <c r="F126" s="111"/>
       <c r="G126" s="58" t="s">
-        <v>422</v>
+        <v>409</v>
       </c>
       <c r="H126" s="59"/>
       <c r="I126" s="60" t="s">
@@ -9876,7 +9870,7 @@
         <v>6.9444444444444447E-4</v>
       </c>
       <c r="K126" s="62" t="s">
-        <v>437</v>
+        <v>424</v>
       </c>
       <c r="L126" s="6"/>
       <c r="M126" s="6"/>
@@ -9884,21 +9878,21 @@
     </row>
     <row r="127" spans="1:14" ht="176.4">
       <c r="A127" s="11"/>
-      <c r="B127" s="121" t="str">
+      <c r="B127" s="115" t="str">
         <f>master!B106</f>
-        <v>VS Codeによるローカルリポジトリの操作</v>
+        <v>ローカルリポジトリの操作</v>
       </c>
       <c r="C127" s="58" t="str">
         <f>master!C106</f>
         <v>演習の前に</v>
       </c>
-      <c r="D127" s="112" t="s">
-        <v>428</v>
-      </c>
-      <c r="E127" s="113"/>
-      <c r="F127" s="114"/>
+      <c r="D127" s="109" t="s">
+        <v>415</v>
+      </c>
+      <c r="E127" s="110"/>
+      <c r="F127" s="111"/>
       <c r="G127" s="58" t="s">
-        <v>427</v>
+        <v>414</v>
       </c>
       <c r="H127" s="59"/>
       <c r="I127" s="60" t="s">
@@ -9914,18 +9908,18 @@
     </row>
     <row r="128" spans="1:14" ht="37.799999999999997">
       <c r="A128" s="11"/>
-      <c r="B128" s="122"/>
+      <c r="B128" s="116"/>
       <c r="C128" s="58" t="str">
         <f>master!C107</f>
-        <v>VS Codeによるリポジトリの作成</v>
-      </c>
-      <c r="D128" s="112" t="s">
-        <v>425</v>
-      </c>
-      <c r="E128" s="113"/>
-      <c r="F128" s="114"/>
+        <v>リポジトリの作成</v>
+      </c>
+      <c r="D128" s="109" t="s">
+        <v>412</v>
+      </c>
+      <c r="E128" s="110"/>
+      <c r="F128" s="111"/>
       <c r="G128" s="58" t="s">
-        <v>426</v>
+        <v>413</v>
       </c>
       <c r="H128" s="59"/>
       <c r="I128" s="60" t="s">
@@ -9941,18 +9935,18 @@
     </row>
     <row r="129" spans="1:14" ht="37.799999999999997">
       <c r="A129" s="11"/>
-      <c r="B129" s="122"/>
+      <c r="B129" s="116"/>
       <c r="C129" s="58" t="str">
         <f>master!C108</f>
-        <v>VS Codeによる変更内容の確認</v>
-      </c>
-      <c r="D129" s="112" t="s">
-        <v>425</v>
-      </c>
-      <c r="E129" s="113"/>
-      <c r="F129" s="114"/>
+        <v>変更内容の確認</v>
+      </c>
+      <c r="D129" s="109" t="s">
+        <v>412</v>
+      </c>
+      <c r="E129" s="110"/>
+      <c r="F129" s="111"/>
       <c r="G129" s="58" t="s">
-        <v>426</v>
+        <v>413</v>
       </c>
       <c r="H129" s="59"/>
       <c r="I129" s="60" t="s">
@@ -9968,18 +9962,18 @@
     </row>
     <row r="130" spans="1:14" ht="37.799999999999997">
       <c r="A130" s="11"/>
-      <c r="B130" s="122"/>
+      <c r="B130" s="116"/>
       <c r="C130" s="58" t="str">
         <f>master!C109</f>
-        <v>VS Codeによる変更内容のステージング</v>
-      </c>
-      <c r="D130" s="112" t="s">
-        <v>425</v>
-      </c>
-      <c r="E130" s="113"/>
-      <c r="F130" s="114"/>
+        <v>変更内容のステージング</v>
+      </c>
+      <c r="D130" s="109" t="s">
+        <v>412</v>
+      </c>
+      <c r="E130" s="110"/>
+      <c r="F130" s="111"/>
       <c r="G130" s="58" t="s">
-        <v>426</v>
+        <v>413</v>
       </c>
       <c r="H130" s="59"/>
       <c r="I130" s="60" t="s">
@@ -9995,18 +9989,18 @@
     </row>
     <row r="131" spans="1:14" ht="37.799999999999997">
       <c r="A131" s="11"/>
-      <c r="B131" s="123"/>
+      <c r="B131" s="117"/>
       <c r="C131" s="58" t="str">
         <f>master!C110</f>
-        <v>VS Codeによる変更内容のコミット</v>
-      </c>
-      <c r="D131" s="112" t="s">
-        <v>425</v>
-      </c>
-      <c r="E131" s="113"/>
-      <c r="F131" s="114"/>
+        <v>変更内容のコミット</v>
+      </c>
+      <c r="D131" s="109" t="s">
+        <v>412</v>
+      </c>
+      <c r="E131" s="110"/>
+      <c r="F131" s="111"/>
       <c r="G131" s="58" t="s">
-        <v>426</v>
+        <v>413</v>
       </c>
       <c r="H131" s="59"/>
       <c r="I131" s="60" t="s">
@@ -10022,19 +10016,19 @@
     </row>
     <row r="132" spans="1:14" ht="163.80000000000001">
       <c r="A132" s="11"/>
-      <c r="B132" s="121" t="str">
+      <c r="B132" s="115" t="str">
         <f>master!B111</f>
-        <v>VS Codeによるブランチの操作</v>
+        <v>ブランチの操作</v>
       </c>
       <c r="C132" s="58" t="str">
         <f>master!C111</f>
         <v>演習の前に</v>
       </c>
-      <c r="D132" s="112" t="s">
-        <v>429</v>
-      </c>
-      <c r="E132" s="113"/>
-      <c r="F132" s="114"/>
+      <c r="D132" s="109" t="s">
+        <v>416</v>
+      </c>
+      <c r="E132" s="110"/>
+      <c r="F132" s="111"/>
       <c r="G132" s="58" t="s">
         <v>334</v>
       </c>
@@ -10046,7 +10040,7 @@
         <v>0</v>
       </c>
       <c r="K132" s="62" t="s">
-        <v>435</v>
+        <v>422</v>
       </c>
       <c r="L132" s="6"/>
       <c r="M132" s="6"/>
@@ -10054,18 +10048,18 @@
     </row>
     <row r="133" spans="1:14" ht="37.799999999999997">
       <c r="A133" s="11"/>
-      <c r="B133" s="122"/>
+      <c r="B133" s="116"/>
       <c r="C133" s="58" t="str">
         <f>master!C112</f>
-        <v>VS Codeによるブランチの作成</v>
-      </c>
-      <c r="D133" s="112" t="s">
-        <v>425</v>
-      </c>
-      <c r="E133" s="113"/>
-      <c r="F133" s="114"/>
+        <v>ブランチの作成</v>
+      </c>
+      <c r="D133" s="109" t="s">
+        <v>412</v>
+      </c>
+      <c r="E133" s="110"/>
+      <c r="F133" s="111"/>
       <c r="G133" s="58" t="s">
-        <v>426</v>
+        <v>413</v>
       </c>
       <c r="H133" s="59"/>
       <c r="I133" s="60" t="s">
@@ -10075,7 +10069,7 @@
         <v>0</v>
       </c>
       <c r="K133" s="62" t="s">
-        <v>435</v>
+        <v>422</v>
       </c>
       <c r="L133" s="6"/>
       <c r="M133" s="6"/>
@@ -10083,18 +10077,18 @@
     </row>
     <row r="134" spans="1:14" ht="37.799999999999997">
       <c r="A134" s="11"/>
-      <c r="B134" s="122"/>
+      <c r="B134" s="116"/>
       <c r="C134" s="58" t="str">
         <f>master!C113</f>
-        <v>VS Codeによるブランチの切り替え</v>
-      </c>
-      <c r="D134" s="112" t="s">
-        <v>425</v>
-      </c>
-      <c r="E134" s="113"/>
-      <c r="F134" s="114"/>
+        <v>ブランチの切り替え</v>
+      </c>
+      <c r="D134" s="109" t="s">
+        <v>412</v>
+      </c>
+      <c r="E134" s="110"/>
+      <c r="F134" s="111"/>
       <c r="G134" s="58" t="s">
-        <v>426</v>
+        <v>413</v>
       </c>
       <c r="H134" s="59"/>
       <c r="I134" s="60" t="s">
@@ -10104,7 +10098,7 @@
         <v>0</v>
       </c>
       <c r="K134" s="62" t="s">
-        <v>435</v>
+        <v>422</v>
       </c>
       <c r="L134" s="6"/>
       <c r="M134" s="6"/>
@@ -10112,18 +10106,18 @@
     </row>
     <row r="135" spans="1:14" ht="37.799999999999997">
       <c r="A135" s="11"/>
-      <c r="B135" s="123"/>
+      <c r="B135" s="117"/>
       <c r="C135" s="58" t="str">
         <f>master!C114</f>
-        <v>VS Codeによるブランチのマージ</v>
-      </c>
-      <c r="D135" s="112" t="s">
-        <v>425</v>
-      </c>
-      <c r="E135" s="113"/>
-      <c r="F135" s="114"/>
+        <v>ブランチのマージ</v>
+      </c>
+      <c r="D135" s="109" t="s">
+        <v>412</v>
+      </c>
+      <c r="E135" s="110"/>
+      <c r="F135" s="111"/>
       <c r="G135" s="58" t="s">
-        <v>426</v>
+        <v>413</v>
       </c>
       <c r="H135" s="59"/>
       <c r="I135" s="60" t="s">
@@ -10133,7 +10127,7 @@
         <v>0</v>
       </c>
       <c r="K135" s="62" t="s">
-        <v>435</v>
+        <v>422</v>
       </c>
       <c r="L135" s="6"/>
       <c r="M135" s="6"/>
@@ -10149,17 +10143,17 @@
         <f>master!C67</f>
         <v>ここから各自で演習を始めましょう。</v>
       </c>
-      <c r="D136" s="112" t="s">
+      <c r="D136" s="109" t="s">
         <v>198</v>
       </c>
-      <c r="E136" s="113"/>
-      <c r="F136" s="114"/>
+      <c r="E136" s="110"/>
+      <c r="F136" s="111"/>
       <c r="G136" s="58" t="s">
         <v>293</v>
       </c>
       <c r="H136" s="59"/>
       <c r="I136" s="60" t="s">
-        <v>438</v>
+        <v>425</v>
       </c>
       <c r="J136" s="61" t="s">
         <v>338</v>
@@ -10171,7 +10165,7 @@
     </row>
     <row r="137" spans="1:14" ht="50.4">
       <c r="A137" s="11"/>
-      <c r="B137" s="109" t="str">
+      <c r="B137" s="127" t="str">
         <f>master!B116</f>
         <v>単体テストとJunitの導入</v>
       </c>
@@ -10201,7 +10195,7 @@
     </row>
     <row r="138" spans="1:14" ht="25.2">
       <c r="A138" s="11"/>
-      <c r="B138" s="110"/>
+      <c r="B138" s="128"/>
       <c r="C138" s="78" t="str">
         <f>master!C117</f>
         <v>TERASOLUNA 開発手順　 ※再掲</v>
@@ -10226,7 +10220,7 @@
     </row>
     <row r="139" spans="1:14" ht="25.2">
       <c r="A139" s="11"/>
-      <c r="B139" s="111"/>
+      <c r="B139" s="129"/>
       <c r="C139" s="78" t="str">
         <f>master!C118</f>
         <v>V字モデル　 ※再掲</v>
@@ -10253,7 +10247,7 @@
     </row>
     <row r="140" spans="1:14" ht="50.4">
       <c r="A140" s="11"/>
-      <c r="B140" s="109" t="str">
+      <c r="B140" s="127" t="str">
         <f>master!B119</f>
         <v>テストとは</v>
       </c>
@@ -10283,7 +10277,7 @@
     </row>
     <row r="141" spans="1:14" ht="315">
       <c r="A141" s="11"/>
-      <c r="B141" s="110"/>
+      <c r="B141" s="128"/>
       <c r="C141" s="78" t="str">
         <f>master!C120</f>
         <v>テストの目的</v>
@@ -10310,7 +10304,7 @@
     </row>
     <row r="142" spans="1:14" ht="25.2">
       <c r="A142" s="11"/>
-      <c r="B142" s="110"/>
+      <c r="B142" s="128"/>
       <c r="C142" s="78" t="str">
         <f>master!C121</f>
         <v>テストを実施しなかった場合…</v>
@@ -10337,7 +10331,7 @@
     </row>
     <row r="143" spans="1:14" ht="100.8">
       <c r="A143" s="11"/>
-      <c r="B143" s="111"/>
+      <c r="B143" s="129"/>
       <c r="C143" s="78" t="str">
         <f>master!C122</f>
         <v>コラム：テストとデバッグ</v>
@@ -10364,7 +10358,7 @@
     </row>
     <row r="144" spans="1:14" ht="50.4">
       <c r="A144" s="11"/>
-      <c r="B144" s="109" t="str">
+      <c r="B144" s="127" t="str">
         <f>master!B123</f>
         <v>単体テストとは</v>
       </c>
@@ -10394,7 +10388,7 @@
     </row>
     <row r="145" spans="1:14" ht="25.2">
       <c r="A145" s="11"/>
-      <c r="B145" s="110"/>
+      <c r="B145" s="128"/>
       <c r="C145" s="78" t="str">
         <f>master!C124</f>
         <v xml:space="preserve">V字モデル　– 製造/単体テスト –　※再掲 </v>
@@ -10419,7 +10413,7 @@
     </row>
     <row r="146" spans="1:14" ht="302.39999999999998">
       <c r="A146" s="11"/>
-      <c r="B146" s="110"/>
+      <c r="B146" s="128"/>
       <c r="C146" s="78" t="str">
         <f>master!C125</f>
         <v>テスト設計の流れ</v>
@@ -10446,7 +10440,7 @@
     </row>
     <row r="147" spans="1:14" ht="37.799999999999997">
       <c r="A147" s="11"/>
-      <c r="B147" s="110"/>
+      <c r="B147" s="128"/>
       <c r="C147" s="78" t="str">
         <f>master!C126</f>
         <v>テスト設計の例</v>
@@ -10473,7 +10467,7 @@
     </row>
     <row r="148" spans="1:14" ht="75.599999999999994">
       <c r="A148" s="11"/>
-      <c r="B148" s="110"/>
+      <c r="B148" s="128"/>
       <c r="C148" s="78" t="str">
         <f>master!C127</f>
         <v>単体テスト（Unit Test）とは</v>
@@ -10500,7 +10494,7 @@
     </row>
     <row r="149" spans="1:14" ht="113.4">
       <c r="A149" s="11"/>
-      <c r="B149" s="110"/>
+      <c r="B149" s="128"/>
       <c r="C149" s="78" t="str">
         <f>master!C128</f>
         <v>テスト技法 – ブラックボックステスト技法 –</v>
@@ -10527,7 +10521,7 @@
     </row>
     <row r="150" spans="1:14" ht="201.6">
       <c r="A150" s="11"/>
-      <c r="B150" s="110"/>
+      <c r="B150" s="128"/>
       <c r="C150" s="78" t="str">
         <f>master!C129</f>
         <v>ブラックボックステスト：同値分割法</v>
@@ -10554,7 +10548,7 @@
     </row>
     <row r="151" spans="1:14" ht="113.4">
       <c r="A151" s="11"/>
-      <c r="B151" s="110"/>
+      <c r="B151" s="128"/>
       <c r="C151" s="78" t="str">
         <f>master!C130</f>
         <v>ブラックボックステスト：境界値分析</v>
@@ -10581,7 +10575,7 @@
     </row>
     <row r="152" spans="1:14" ht="176.4">
       <c r="A152" s="11"/>
-      <c r="B152" s="110"/>
+      <c r="B152" s="128"/>
       <c r="C152" s="78" t="str">
         <f>master!C131</f>
         <v>ブラックボックステスト：ディシジョンテーブルテスト</v>
@@ -10608,7 +10602,7 @@
     </row>
     <row r="153" spans="1:14" ht="37.799999999999997">
       <c r="A153" s="11"/>
-      <c r="B153" s="110"/>
+      <c r="B153" s="128"/>
       <c r="C153" s="78" t="str">
         <f>master!C132</f>
         <v>ブラックボックステスト：状態遷移テスト</v>
@@ -10635,7 +10629,7 @@
     </row>
     <row r="154" spans="1:14" ht="88.2">
       <c r="A154" s="11"/>
-      <c r="B154" s="110"/>
+      <c r="B154" s="128"/>
       <c r="C154" s="78" t="str">
         <f>master!C133</f>
         <v>テスト技法 – ホワイトボックステスト技法 –</v>
@@ -10662,7 +10656,7 @@
     </row>
     <row r="155" spans="1:14" ht="151.19999999999999">
       <c r="A155" s="11"/>
-      <c r="B155" s="110"/>
+      <c r="B155" s="128"/>
       <c r="C155" s="78" t="str">
         <f>master!C134</f>
         <v>ホワイトボックステストの評価基準</v>
@@ -10689,7 +10683,7 @@
     </row>
     <row r="156" spans="1:14" ht="37.799999999999997">
       <c r="A156" s="11"/>
-      <c r="B156" s="110"/>
+      <c r="B156" s="128"/>
       <c r="C156" s="78" t="str">
         <f>master!C135</f>
         <v>ホワイトボックステスト：ステートメントテスト</v>
@@ -10716,7 +10710,7 @@
     </row>
     <row r="157" spans="1:14" ht="37.799999999999997">
       <c r="A157" s="11"/>
-      <c r="B157" s="110"/>
+      <c r="B157" s="128"/>
       <c r="C157" s="78" t="str">
         <f>master!C136</f>
         <v>ホワイトボックステスト：ブランチテスト</v>
@@ -10743,7 +10737,7 @@
     </row>
     <row r="158" spans="1:14" ht="37.799999999999997">
       <c r="A158" s="11"/>
-      <c r="B158" s="110"/>
+      <c r="B158" s="128"/>
       <c r="C158" s="78" t="str">
         <f>master!C137</f>
         <v>ホワイトボックステスト：コンディションテスト</v>
@@ -10770,7 +10764,7 @@
     </row>
     <row r="159" spans="1:14" ht="37.799999999999997">
       <c r="A159" s="11"/>
-      <c r="B159" s="110"/>
+      <c r="B159" s="128"/>
       <c r="C159" s="78" t="str">
         <f>master!C138</f>
         <v>テスト技法 – 経験ベースの技法 –</v>
@@ -10797,7 +10791,7 @@
     </row>
     <row r="160" spans="1:14" ht="100.8">
       <c r="A160" s="11"/>
-      <c r="B160" s="110"/>
+      <c r="B160" s="128"/>
       <c r="C160" s="78" t="str">
         <f>master!C139</f>
         <v>スタブとドライバ</v>
@@ -10824,7 +10818,7 @@
     </row>
     <row r="161" spans="1:14" ht="75.599999999999994">
       <c r="A161" s="11"/>
-      <c r="B161" s="111"/>
+      <c r="B161" s="129"/>
       <c r="C161" s="78" t="str">
         <f>master!C140</f>
         <v>スタブとモック</v>
@@ -10851,7 +10845,7 @@
     </row>
     <row r="162" spans="1:14" ht="37.799999999999997">
       <c r="A162" s="11"/>
-      <c r="B162" s="109" t="str">
+      <c r="B162" s="127" t="str">
         <f>master!B141</f>
         <v>JUnit</v>
       </c>
@@ -10881,7 +10875,7 @@
     </row>
     <row r="163" spans="1:14" ht="25.2">
       <c r="A163" s="11"/>
-      <c r="B163" s="111"/>
+      <c r="B163" s="129"/>
       <c r="C163" s="78" t="str">
         <f>master!C142</f>
         <v>参考文献</v>
@@ -10914,11 +10908,11 @@
         <f>master!C67</f>
         <v>ここから各自で演習を始めましょう。</v>
       </c>
-      <c r="D164" s="112" t="s">
+      <c r="D164" s="109" t="s">
         <v>251</v>
       </c>
-      <c r="E164" s="113"/>
-      <c r="F164" s="114"/>
+      <c r="E164" s="110"/>
+      <c r="F164" s="111"/>
       <c r="G164" s="58" t="s">
         <v>42</v>
       </c>
@@ -10936,7 +10930,7 @@
     </row>
     <row r="165" spans="1:14" ht="25.2">
       <c r="A165" s="11"/>
-      <c r="B165" s="115" t="str">
+      <c r="B165" s="121" t="str">
         <f>master!B144</f>
         <v>課題2の導入</v>
       </c>
@@ -10944,11 +10938,11 @@
         <f>master!C144</f>
         <v>演習課題の概要</v>
       </c>
-      <c r="D165" s="112" t="s">
+      <c r="D165" s="109" t="s">
         <v>267</v>
       </c>
-      <c r="E165" s="113"/>
-      <c r="F165" s="114"/>
+      <c r="E165" s="110"/>
+      <c r="F165" s="111"/>
       <c r="G165" s="58" t="s">
         <v>309</v>
       </c>
@@ -10966,16 +10960,16 @@
     </row>
     <row r="166" spans="1:14" ht="138.6">
       <c r="A166" s="11"/>
-      <c r="B166" s="116"/>
+      <c r="B166" s="122"/>
       <c r="C166" s="58" t="str">
         <f>master!C145</f>
         <v>[構造理解] Webアプリケーションで必要なもの  ※再掲</v>
       </c>
-      <c r="D166" s="112" t="s">
+      <c r="D166" s="109" t="s">
         <v>268</v>
       </c>
-      <c r="E166" s="113"/>
-      <c r="F166" s="114"/>
+      <c r="E166" s="110"/>
+      <c r="F166" s="111"/>
       <c r="G166" s="58" t="s">
         <v>310</v>
       </c>
@@ -10993,16 +10987,16 @@
     </row>
     <row r="167" spans="1:14" ht="50.4">
       <c r="A167" s="11"/>
-      <c r="B167" s="116"/>
+      <c r="B167" s="122"/>
       <c r="C167" s="58" t="str">
         <f>master!C146</f>
         <v>テストクラスを作成する単位</v>
       </c>
-      <c r="D167" s="112" t="s">
+      <c r="D167" s="109" t="s">
         <v>269</v>
       </c>
-      <c r="E167" s="113"/>
-      <c r="F167" s="114"/>
+      <c r="E167" s="110"/>
+      <c r="F167" s="111"/>
       <c r="G167" s="58" t="s">
         <v>311</v>
       </c>
@@ -11020,16 +11014,16 @@
     </row>
     <row r="168" spans="1:14" ht="113.4">
       <c r="A168" s="11"/>
-      <c r="B168" s="117"/>
+      <c r="B168" s="123"/>
       <c r="C168" s="58" t="str">
         <f>master!C147</f>
         <v>JUnitで単体テスト</v>
       </c>
-      <c r="D168" s="112" t="s">
+      <c r="D168" s="109" t="s">
         <v>270</v>
       </c>
-      <c r="E168" s="113"/>
-      <c r="F168" s="114"/>
+      <c r="E168" s="110"/>
+      <c r="F168" s="111"/>
       <c r="G168" s="58" t="s">
         <v>312</v>
       </c>
@@ -11047,7 +11041,7 @@
     </row>
     <row r="169" spans="1:14" ht="25.2">
       <c r="A169" s="11"/>
-      <c r="B169" s="115" t="str">
+      <c r="B169" s="121" t="str">
         <f>master!B148</f>
         <v>ハンズオン</v>
       </c>
@@ -11055,11 +11049,11 @@
         <f>master!C148</f>
         <v>バイブコーディングで単体テスト – はじめに</v>
       </c>
-      <c r="D169" s="112" t="s">
+      <c r="D169" s="109" t="s">
         <v>271</v>
       </c>
-      <c r="E169" s="113"/>
-      <c r="F169" s="114"/>
+      <c r="E169" s="110"/>
+      <c r="F169" s="111"/>
       <c r="G169" s="58" t="s">
         <v>309</v>
       </c>
@@ -11077,16 +11071,16 @@
     </row>
     <row r="170" spans="1:14" ht="50.4">
       <c r="A170" s="11"/>
-      <c r="B170" s="116"/>
+      <c r="B170" s="122"/>
       <c r="C170" s="58" t="str">
         <f>master!C149</f>
         <v>バイブコーディング単体テスト①テスト項目表を作る</v>
       </c>
-      <c r="D170" s="112" t="s">
+      <c r="D170" s="109" t="s">
         <v>272</v>
       </c>
-      <c r="E170" s="113"/>
-      <c r="F170" s="114"/>
+      <c r="E170" s="110"/>
+      <c r="F170" s="111"/>
       <c r="G170" s="58" t="s">
         <v>311</v>
       </c>
@@ -11104,13 +11098,13 @@
     </row>
     <row r="171" spans="1:14" ht="88.2">
       <c r="A171" s="11"/>
-      <c r="B171" s="116"/>
+      <c r="B171" s="122"/>
       <c r="C171" s="58"/>
-      <c r="D171" s="112" t="s">
+      <c r="D171" s="109" t="s">
         <v>183</v>
       </c>
-      <c r="E171" s="113"/>
-      <c r="F171" s="114"/>
+      <c r="E171" s="110"/>
+      <c r="F171" s="111"/>
       <c r="G171" s="58" t="s">
         <v>313</v>
       </c>
@@ -11128,16 +11122,16 @@
     </row>
     <row r="172" spans="1:14" ht="50.4">
       <c r="A172" s="11"/>
-      <c r="B172" s="116"/>
+      <c r="B172" s="122"/>
       <c r="C172" s="76" t="str">
         <f>master!C150</f>
         <v>バイブコーディング単体テスト②Repositoryのテストを作る</v>
       </c>
-      <c r="D172" s="112" t="s">
+      <c r="D172" s="109" t="s">
         <v>273</v>
       </c>
-      <c r="E172" s="113"/>
-      <c r="F172" s="114"/>
+      <c r="E172" s="110"/>
+      <c r="F172" s="111"/>
       <c r="G172" s="58" t="s">
         <v>311</v>
       </c>
@@ -11155,13 +11149,13 @@
     </row>
     <row r="173" spans="1:14" ht="88.2">
       <c r="A173" s="11"/>
-      <c r="B173" s="116"/>
+      <c r="B173" s="122"/>
       <c r="C173" s="77"/>
-      <c r="D173" s="112" t="s">
+      <c r="D173" s="109" t="s">
         <v>183</v>
       </c>
-      <c r="E173" s="113"/>
-      <c r="F173" s="114"/>
+      <c r="E173" s="110"/>
+      <c r="F173" s="111"/>
       <c r="G173" s="58" t="s">
         <v>313</v>
       </c>
@@ -11179,16 +11173,16 @@
     </row>
     <row r="174" spans="1:14" ht="138.6">
       <c r="A174" s="11"/>
-      <c r="B174" s="116"/>
+      <c r="B174" s="122"/>
       <c r="C174" s="58" t="str">
         <f>master!C151</f>
         <v>[解説] Repositoryのテストクラス（抜粋）</v>
       </c>
-      <c r="D174" s="112" t="s">
+      <c r="D174" s="109" t="s">
         <v>275</v>
       </c>
-      <c r="E174" s="113"/>
-      <c r="F174" s="114"/>
+      <c r="E174" s="110"/>
+      <c r="F174" s="111"/>
       <c r="G174" s="58" t="s">
         <v>310</v>
       </c>
@@ -11206,16 +11200,16 @@
     </row>
     <row r="175" spans="1:14" ht="50.4">
       <c r="A175" s="11"/>
-      <c r="B175" s="116"/>
+      <c r="B175" s="122"/>
       <c r="C175" s="76" t="str">
         <f>master!C152</f>
         <v>バイブコーディング単体テスト③Serviceのテストを作る</v>
       </c>
-      <c r="D175" s="112" t="s">
+      <c r="D175" s="109" t="s">
         <v>273</v>
       </c>
-      <c r="E175" s="113"/>
-      <c r="F175" s="114"/>
+      <c r="E175" s="110"/>
+      <c r="F175" s="111"/>
       <c r="G175" s="58" t="s">
         <v>311</v>
       </c>
@@ -11233,13 +11227,13 @@
     </row>
     <row r="176" spans="1:14" ht="88.2">
       <c r="A176" s="11"/>
-      <c r="B176" s="116"/>
+      <c r="B176" s="122"/>
       <c r="C176" s="77"/>
-      <c r="D176" s="112" t="s">
+      <c r="D176" s="109" t="s">
         <v>183</v>
       </c>
-      <c r="E176" s="113"/>
-      <c r="F176" s="114"/>
+      <c r="E176" s="110"/>
+      <c r="F176" s="111"/>
       <c r="G176" s="58" t="s">
         <v>313</v>
       </c>
@@ -11257,16 +11251,16 @@
     </row>
     <row r="177" spans="1:14" ht="138.6">
       <c r="A177" s="11"/>
-      <c r="B177" s="116"/>
+      <c r="B177" s="122"/>
       <c r="C177" s="58" t="str">
         <f>master!C153</f>
         <v>[解説] Serviceのテストクラス（抜粋）</v>
       </c>
-      <c r="D177" s="112" t="s">
+      <c r="D177" s="109" t="s">
         <v>274</v>
       </c>
-      <c r="E177" s="113"/>
-      <c r="F177" s="114"/>
+      <c r="E177" s="110"/>
+      <c r="F177" s="111"/>
       <c r="G177" s="58" t="s">
         <v>310</v>
       </c>
@@ -11284,16 +11278,16 @@
     </row>
     <row r="178" spans="1:14" ht="50.4">
       <c r="A178" s="11"/>
-      <c r="B178" s="116"/>
+      <c r="B178" s="122"/>
       <c r="C178" s="76" t="str">
         <f>master!C154</f>
         <v>バイブコーディング単体テスト④Controllerのテストを作る</v>
       </c>
-      <c r="D178" s="112" t="s">
+      <c r="D178" s="109" t="s">
         <v>273</v>
       </c>
-      <c r="E178" s="113"/>
-      <c r="F178" s="114"/>
+      <c r="E178" s="110"/>
+      <c r="F178" s="111"/>
       <c r="G178" s="58" t="s">
         <v>311</v>
       </c>
@@ -11311,13 +11305,13 @@
     </row>
     <row r="179" spans="1:14" ht="88.2">
       <c r="A179" s="11"/>
-      <c r="B179" s="116"/>
+      <c r="B179" s="122"/>
       <c r="C179" s="77"/>
-      <c r="D179" s="112" t="s">
+      <c r="D179" s="109" t="s">
         <v>183</v>
       </c>
-      <c r="E179" s="113"/>
-      <c r="F179" s="114"/>
+      <c r="E179" s="110"/>
+      <c r="F179" s="111"/>
       <c r="G179" s="58" t="s">
         <v>313</v>
       </c>
@@ -11335,16 +11329,16 @@
     </row>
     <row r="180" spans="1:14" ht="163.80000000000001">
       <c r="A180" s="11"/>
-      <c r="B180" s="117"/>
+      <c r="B180" s="123"/>
       <c r="C180" s="58" t="str">
         <f>master!C155</f>
         <v>[解説] Controllerのテストクラス（抜粋）</v>
       </c>
-      <c r="D180" s="112" t="s">
+      <c r="D180" s="109" t="s">
         <v>276</v>
       </c>
-      <c r="E180" s="113"/>
-      <c r="F180" s="114"/>
+      <c r="E180" s="110"/>
+      <c r="F180" s="111"/>
       <c r="G180" s="58" t="s">
         <v>314</v>
       </c>
@@ -11362,7 +11356,7 @@
     </row>
     <row r="181" spans="1:14" ht="165" customHeight="1">
       <c r="A181" s="11"/>
-      <c r="B181" s="115" t="str">
+      <c r="B181" s="121" t="str">
         <f>master!B156</f>
         <v>課題2の実施</v>
       </c>
@@ -11370,11 +11364,11 @@
         <f>master!C156</f>
         <v>ここから各自で演習を始めましょう。</v>
       </c>
-      <c r="D181" s="112" t="s">
+      <c r="D181" s="109" t="s">
         <v>277</v>
       </c>
-      <c r="E181" s="113"/>
-      <c r="F181" s="114"/>
+      <c r="E181" s="110"/>
+      <c r="F181" s="111"/>
       <c r="G181" s="58" t="s">
         <v>314</v>
       </c>
@@ -11392,16 +11386,16 @@
     </row>
     <row r="182" spans="1:14" ht="151.19999999999999">
       <c r="A182" s="11"/>
-      <c r="B182" s="117"/>
+      <c r="B182" s="123"/>
       <c r="C182" s="58" t="str">
         <f>master!C157</f>
         <v>[終了条件] 講師配布のテストプログラム(JUnit)が成功すること</v>
       </c>
-      <c r="D182" s="112" t="s">
+      <c r="D182" s="109" t="s">
         <v>337</v>
       </c>
-      <c r="E182" s="113"/>
-      <c r="F182" s="114"/>
+      <c r="E182" s="110"/>
+      <c r="F182" s="111"/>
       <c r="G182" s="58" t="s">
         <v>336</v>
       </c>
@@ -11413,7 +11407,7 @@
         <v>338</v>
       </c>
       <c r="K182" s="62" t="s">
-        <v>441</v>
+        <v>428</v>
       </c>
       <c r="L182" s="6"/>
       <c r="M182" s="6"/>
@@ -11421,7 +11415,7 @@
     </row>
     <row r="183" spans="1:14" ht="163.80000000000001">
       <c r="A183" s="11"/>
-      <c r="B183" s="115" t="str">
+      <c r="B183" s="121" t="str">
         <f>master!B159</f>
         <v>追加課題</v>
       </c>
@@ -11429,11 +11423,11 @@
         <f>master!C159</f>
         <v>演習課題の概要</v>
       </c>
-      <c r="D183" s="112" t="s">
+      <c r="D183" s="109" t="s">
         <v>279</v>
       </c>
-      <c r="E183" s="113"/>
-      <c r="F183" s="114"/>
+      <c r="E183" s="110"/>
+      <c r="F183" s="111"/>
       <c r="G183" s="58" t="s">
         <v>334</v>
       </c>
@@ -11445,7 +11439,7 @@
         <v>338</v>
       </c>
       <c r="K183" s="62" t="s">
-        <v>440</v>
+        <v>427</v>
       </c>
       <c r="L183" s="6"/>
       <c r="M183" s="6"/>
@@ -11453,16 +11447,16 @@
     </row>
     <row r="184" spans="1:14" ht="25.2">
       <c r="A184" s="11"/>
-      <c r="B184" s="116"/>
+      <c r="B184" s="122"/>
       <c r="C184" s="58" t="str">
         <f>master!C160</f>
         <v>追加課題①：送料の表示機能</v>
       </c>
-      <c r="D184" s="112" t="s">
+      <c r="D184" s="109" t="s">
         <v>281</v>
       </c>
-      <c r="E184" s="113"/>
-      <c r="F184" s="114"/>
+      <c r="E184" s="110"/>
+      <c r="F184" s="111"/>
       <c r="G184" s="58" t="s">
         <v>335</v>
       </c>
@@ -11474,7 +11468,7 @@
         <v>338</v>
       </c>
       <c r="K184" s="62" t="s">
-        <v>440</v>
+        <v>427</v>
       </c>
       <c r="L184" s="6"/>
       <c r="M184" s="6"/>
@@ -11482,16 +11476,16 @@
     </row>
     <row r="185" spans="1:14" ht="25.2">
       <c r="A185" s="11"/>
-      <c r="B185" s="116"/>
+      <c r="B185" s="122"/>
       <c r="C185" s="58" t="str">
         <f>master!C161</f>
         <v>追加課題②：クーポン機能</v>
       </c>
-      <c r="D185" s="112" t="s">
+      <c r="D185" s="109" t="s">
         <v>281</v>
       </c>
-      <c r="E185" s="113"/>
-      <c r="F185" s="114"/>
+      <c r="E185" s="110"/>
+      <c r="F185" s="111"/>
       <c r="G185" s="58" t="s">
         <v>335</v>
       </c>
@@ -11503,7 +11497,7 @@
         <v>338</v>
       </c>
       <c r="K185" s="62" t="s">
-        <v>440</v>
+        <v>427</v>
       </c>
       <c r="L185" s="6"/>
       <c r="M185" s="6"/>
@@ -11511,16 +11505,16 @@
     </row>
     <row r="186" spans="1:14" ht="25.2">
       <c r="A186" s="11"/>
-      <c r="B186" s="117"/>
+      <c r="B186" s="123"/>
       <c r="C186" s="58" t="str">
         <f>master!C162</f>
         <v>追加課題③：ユーザーアカウント機能</v>
       </c>
-      <c r="D186" s="112" t="s">
+      <c r="D186" s="109" t="s">
         <v>281</v>
       </c>
-      <c r="E186" s="113"/>
-      <c r="F186" s="114"/>
+      <c r="E186" s="110"/>
+      <c r="F186" s="111"/>
       <c r="G186" s="58" t="s">
         <v>335</v>
       </c>
@@ -11532,7 +11526,7 @@
         <v>338</v>
       </c>
       <c r="K186" s="62" t="s">
-        <v>440</v>
+        <v>427</v>
       </c>
       <c r="L186" s="6"/>
       <c r="M186" s="6"/>
@@ -11540,7 +11534,7 @@
     </row>
     <row r="187" spans="1:14" ht="176.4">
       <c r="A187" s="11"/>
-      <c r="B187" s="115" t="str">
+      <c r="B187" s="121" t="str">
         <f>master!B164</f>
         <v>演習の振り返り</v>
       </c>
@@ -11548,13 +11542,13 @@
         <f>master!C164</f>
         <v>アプリケーションの比較・分析</v>
       </c>
-      <c r="D187" s="112" t="s">
-        <v>451</v>
-      </c>
-      <c r="E187" s="113"/>
-      <c r="F187" s="114"/>
+      <c r="D187" s="109" t="s">
+        <v>438</v>
+      </c>
+      <c r="E187" s="110"/>
+      <c r="F187" s="111"/>
       <c r="G187" s="58" t="s">
-        <v>442</v>
+        <v>429</v>
       </c>
       <c r="H187" s="59"/>
       <c r="I187" s="60" t="s">
@@ -11570,18 +11564,18 @@
     </row>
     <row r="188" spans="1:14" ht="63">
       <c r="A188" s="11"/>
-      <c r="B188" s="116"/>
+      <c r="B188" s="122"/>
       <c r="C188" s="58" t="str">
         <f>master!C165</f>
         <v>改善点の整理</v>
       </c>
-      <c r="D188" s="112" t="s">
-        <v>450</v>
-      </c>
-      <c r="E188" s="113"/>
-      <c r="F188" s="114"/>
+      <c r="D188" s="109" t="s">
+        <v>437</v>
+      </c>
+      <c r="E188" s="110"/>
+      <c r="F188" s="111"/>
       <c r="G188" s="58" t="s">
-        <v>443</v>
+        <v>430</v>
       </c>
       <c r="H188" s="59"/>
       <c r="I188" s="60" t="s">
@@ -11597,18 +11591,18 @@
     </row>
     <row r="189" spans="1:14" ht="63">
       <c r="A189" s="11"/>
-      <c r="B189" s="117"/>
+      <c r="B189" s="123"/>
       <c r="C189" s="58" t="str">
         <f>master!C166</f>
         <v>分析結果の共有</v>
       </c>
-      <c r="D189" s="112" t="s">
-        <v>448</v>
-      </c>
-      <c r="E189" s="113"/>
-      <c r="F189" s="114"/>
+      <c r="D189" s="109" t="s">
+        <v>435</v>
+      </c>
+      <c r="E189" s="110"/>
+      <c r="F189" s="111"/>
       <c r="G189" s="58" t="s">
-        <v>443</v>
+        <v>430</v>
       </c>
       <c r="H189" s="59"/>
       <c r="I189" s="60" t="s">
@@ -11628,6 +11622,186 @@
     <row r="191" spans="1:14" ht="15" customHeight="1"/>
   </sheetData>
   <mergeCells count="204">
+    <mergeCell ref="B137:B139"/>
+    <mergeCell ref="B162:B163"/>
+    <mergeCell ref="D164:F164"/>
+    <mergeCell ref="D187:F187"/>
+    <mergeCell ref="D184:F184"/>
+    <mergeCell ref="D183:F183"/>
+    <mergeCell ref="D165:F165"/>
+    <mergeCell ref="D166:F166"/>
+    <mergeCell ref="D167:F167"/>
+    <mergeCell ref="D180:F180"/>
+    <mergeCell ref="D181:F181"/>
+    <mergeCell ref="D168:F168"/>
+    <mergeCell ref="D169:F169"/>
+    <mergeCell ref="D177:F177"/>
+    <mergeCell ref="D171:F171"/>
+    <mergeCell ref="D173:F173"/>
+    <mergeCell ref="D174:F174"/>
+    <mergeCell ref="B169:B180"/>
+    <mergeCell ref="B165:B168"/>
+    <mergeCell ref="B140:B143"/>
+    <mergeCell ref="B144:B161"/>
+    <mergeCell ref="D139:F139"/>
+    <mergeCell ref="D140:F140"/>
+    <mergeCell ref="D141:F141"/>
+    <mergeCell ref="D160:F160"/>
+    <mergeCell ref="D161:F161"/>
+    <mergeCell ref="D143:F143"/>
+    <mergeCell ref="D155:F155"/>
+    <mergeCell ref="D156:F156"/>
+    <mergeCell ref="D157:F157"/>
+    <mergeCell ref="D158:F158"/>
+    <mergeCell ref="D159:F159"/>
+    <mergeCell ref="D154:F154"/>
+    <mergeCell ref="D153:F153"/>
+    <mergeCell ref="D149:F149"/>
+    <mergeCell ref="D150:F150"/>
+    <mergeCell ref="D151:F151"/>
+    <mergeCell ref="D152:F152"/>
+    <mergeCell ref="D115:F115"/>
+    <mergeCell ref="D114:F114"/>
+    <mergeCell ref="D113:F113"/>
+    <mergeCell ref="D142:F142"/>
+    <mergeCell ref="D144:F144"/>
+    <mergeCell ref="D145:F145"/>
+    <mergeCell ref="D146:F146"/>
+    <mergeCell ref="D147:F147"/>
+    <mergeCell ref="D148:F148"/>
+    <mergeCell ref="B55:B57"/>
+    <mergeCell ref="D69:F69"/>
+    <mergeCell ref="D70:F70"/>
+    <mergeCell ref="D71:F71"/>
+    <mergeCell ref="D72:F72"/>
+    <mergeCell ref="D62:F62"/>
+    <mergeCell ref="D56:F56"/>
+    <mergeCell ref="D57:F57"/>
+    <mergeCell ref="D58:F58"/>
+    <mergeCell ref="D59:F59"/>
+    <mergeCell ref="D66:F66"/>
+    <mergeCell ref="D67:F67"/>
+    <mergeCell ref="D60:F60"/>
+    <mergeCell ref="D61:F61"/>
+    <mergeCell ref="D63:F63"/>
+    <mergeCell ref="D64:F64"/>
+    <mergeCell ref="D65:F65"/>
+    <mergeCell ref="D68:F68"/>
+    <mergeCell ref="D55:F55"/>
+    <mergeCell ref="B62:B70"/>
+    <mergeCell ref="B58:B61"/>
+    <mergeCell ref="B71:B90"/>
+    <mergeCell ref="D84:F84"/>
+    <mergeCell ref="D86:F86"/>
+    <mergeCell ref="B28:B35"/>
+    <mergeCell ref="B36:B54"/>
+    <mergeCell ref="D49:F49"/>
+    <mergeCell ref="D50:F50"/>
+    <mergeCell ref="D51:F51"/>
+    <mergeCell ref="D52:F52"/>
+    <mergeCell ref="D53:F53"/>
+    <mergeCell ref="D37:F37"/>
+    <mergeCell ref="D38:F38"/>
+    <mergeCell ref="D39:F39"/>
+    <mergeCell ref="D40:F40"/>
+    <mergeCell ref="D41:F41"/>
+    <mergeCell ref="D42:F42"/>
+    <mergeCell ref="D43:F43"/>
+    <mergeCell ref="D44:F44"/>
+    <mergeCell ref="D45:F45"/>
+    <mergeCell ref="D46:F46"/>
+    <mergeCell ref="D47:F47"/>
+    <mergeCell ref="D48:F48"/>
+    <mergeCell ref="D54:F54"/>
+    <mergeCell ref="D36:F36"/>
+    <mergeCell ref="D34:F34"/>
+    <mergeCell ref="D29:F29"/>
+    <mergeCell ref="D30:F30"/>
+    <mergeCell ref="B4:E4"/>
+    <mergeCell ref="B5:K5"/>
+    <mergeCell ref="D19:F20"/>
+    <mergeCell ref="G19:G20"/>
+    <mergeCell ref="B19:B20"/>
+    <mergeCell ref="C19:C20"/>
+    <mergeCell ref="K19:K20"/>
+    <mergeCell ref="D7:E7"/>
+    <mergeCell ref="B22:B27"/>
+    <mergeCell ref="D25:F25"/>
+    <mergeCell ref="D27:F27"/>
+    <mergeCell ref="D24:F24"/>
+    <mergeCell ref="D26:F26"/>
+    <mergeCell ref="D91:F91"/>
+    <mergeCell ref="D76:F76"/>
+    <mergeCell ref="I19:J19"/>
+    <mergeCell ref="H19:H20"/>
+    <mergeCell ref="D78:F78"/>
+    <mergeCell ref="D80:F80"/>
+    <mergeCell ref="D74:F74"/>
+    <mergeCell ref="D85:F85"/>
+    <mergeCell ref="D90:F90"/>
+    <mergeCell ref="D82:F82"/>
+    <mergeCell ref="D83:F83"/>
+    <mergeCell ref="D87:F87"/>
+    <mergeCell ref="D88:F88"/>
+    <mergeCell ref="D89:F89"/>
+    <mergeCell ref="D77:F77"/>
+    <mergeCell ref="D79:F79"/>
+    <mergeCell ref="D81:F81"/>
+    <mergeCell ref="D75:F75"/>
+    <mergeCell ref="D73:F73"/>
+    <mergeCell ref="D21:F21"/>
+    <mergeCell ref="D35:F35"/>
+    <mergeCell ref="D22:F22"/>
+    <mergeCell ref="D28:F28"/>
+    <mergeCell ref="D23:F23"/>
+    <mergeCell ref="D31:F31"/>
+    <mergeCell ref="D32:F32"/>
+    <mergeCell ref="D33:F33"/>
+    <mergeCell ref="D189:F189"/>
+    <mergeCell ref="B187:B189"/>
+    <mergeCell ref="D170:F170"/>
+    <mergeCell ref="D172:F172"/>
+    <mergeCell ref="D175:F175"/>
+    <mergeCell ref="D176:F176"/>
+    <mergeCell ref="D178:F178"/>
+    <mergeCell ref="D179:F179"/>
+    <mergeCell ref="B183:B186"/>
+    <mergeCell ref="D182:F182"/>
+    <mergeCell ref="B181:B182"/>
+    <mergeCell ref="D93:F93"/>
+    <mergeCell ref="D94:F94"/>
+    <mergeCell ref="D95:F95"/>
+    <mergeCell ref="D96:F96"/>
+    <mergeCell ref="D97:F97"/>
+    <mergeCell ref="D98:F98"/>
+    <mergeCell ref="D100:F100"/>
+    <mergeCell ref="D122:F122"/>
+    <mergeCell ref="D186:F186"/>
+    <mergeCell ref="D185:F185"/>
+    <mergeCell ref="D101:F101"/>
+    <mergeCell ref="D102:F102"/>
+    <mergeCell ref="B119:B123"/>
+    <mergeCell ref="B113:B118"/>
+    <mergeCell ref="B108:B112"/>
+    <mergeCell ref="B99:B107"/>
+    <mergeCell ref="D162:F162"/>
+    <mergeCell ref="D163:F163"/>
+    <mergeCell ref="D138:F138"/>
+    <mergeCell ref="D137:F137"/>
+    <mergeCell ref="D111:F111"/>
+    <mergeCell ref="D110:F110"/>
+    <mergeCell ref="D109:F109"/>
+    <mergeCell ref="D112:F112"/>
+    <mergeCell ref="D103:F103"/>
+    <mergeCell ref="D104:F104"/>
+    <mergeCell ref="D105:F105"/>
+    <mergeCell ref="D106:F106"/>
+    <mergeCell ref="D107:F107"/>
+    <mergeCell ref="D120:F120"/>
+    <mergeCell ref="D119:F119"/>
+    <mergeCell ref="D118:F118"/>
+    <mergeCell ref="D117:F117"/>
+    <mergeCell ref="D116:F116"/>
     <mergeCell ref="D188:F188"/>
     <mergeCell ref="B94:B98"/>
     <mergeCell ref="B91:B93"/>
@@ -11652,186 +11826,6 @@
     <mergeCell ref="D99:F99"/>
     <mergeCell ref="D123:F123"/>
     <mergeCell ref="D136:F136"/>
-    <mergeCell ref="D101:F101"/>
-    <mergeCell ref="D102:F102"/>
-    <mergeCell ref="B119:B123"/>
-    <mergeCell ref="B113:B118"/>
-    <mergeCell ref="B108:B112"/>
-    <mergeCell ref="B99:B107"/>
-    <mergeCell ref="D162:F162"/>
-    <mergeCell ref="D163:F163"/>
-    <mergeCell ref="D138:F138"/>
-    <mergeCell ref="D137:F137"/>
-    <mergeCell ref="D111:F111"/>
-    <mergeCell ref="D110:F110"/>
-    <mergeCell ref="D109:F109"/>
-    <mergeCell ref="D112:F112"/>
-    <mergeCell ref="D103:F103"/>
-    <mergeCell ref="D31:F31"/>
-    <mergeCell ref="D32:F32"/>
-    <mergeCell ref="D33:F33"/>
-    <mergeCell ref="D189:F189"/>
-    <mergeCell ref="B187:B189"/>
-    <mergeCell ref="D170:F170"/>
-    <mergeCell ref="D172:F172"/>
-    <mergeCell ref="D175:F175"/>
-    <mergeCell ref="D176:F176"/>
-    <mergeCell ref="D178:F178"/>
-    <mergeCell ref="D179:F179"/>
-    <mergeCell ref="B183:B186"/>
-    <mergeCell ref="D182:F182"/>
-    <mergeCell ref="B181:B182"/>
-    <mergeCell ref="D93:F93"/>
-    <mergeCell ref="D94:F94"/>
-    <mergeCell ref="D95:F95"/>
-    <mergeCell ref="D96:F96"/>
-    <mergeCell ref="D97:F97"/>
-    <mergeCell ref="D98:F98"/>
-    <mergeCell ref="D100:F100"/>
-    <mergeCell ref="D122:F122"/>
-    <mergeCell ref="D186:F186"/>
-    <mergeCell ref="D185:F185"/>
-    <mergeCell ref="D91:F91"/>
-    <mergeCell ref="D76:F76"/>
-    <mergeCell ref="I19:J19"/>
-    <mergeCell ref="H19:H20"/>
-    <mergeCell ref="D78:F78"/>
-    <mergeCell ref="D80:F80"/>
-    <mergeCell ref="D74:F74"/>
-    <mergeCell ref="D85:F85"/>
-    <mergeCell ref="D90:F90"/>
-    <mergeCell ref="D82:F82"/>
-    <mergeCell ref="D83:F83"/>
-    <mergeCell ref="D87:F87"/>
-    <mergeCell ref="D88:F88"/>
-    <mergeCell ref="D89:F89"/>
-    <mergeCell ref="D77:F77"/>
-    <mergeCell ref="D79:F79"/>
-    <mergeCell ref="D81:F81"/>
-    <mergeCell ref="D75:F75"/>
-    <mergeCell ref="D73:F73"/>
-    <mergeCell ref="D21:F21"/>
-    <mergeCell ref="D35:F35"/>
-    <mergeCell ref="D22:F22"/>
-    <mergeCell ref="D28:F28"/>
-    <mergeCell ref="D23:F23"/>
-    <mergeCell ref="B4:E4"/>
-    <mergeCell ref="B5:K5"/>
-    <mergeCell ref="D19:F20"/>
-    <mergeCell ref="G19:G20"/>
-    <mergeCell ref="B19:B20"/>
-    <mergeCell ref="C19:C20"/>
-    <mergeCell ref="K19:K20"/>
-    <mergeCell ref="D7:E7"/>
-    <mergeCell ref="B22:B27"/>
-    <mergeCell ref="D25:F25"/>
-    <mergeCell ref="D27:F27"/>
-    <mergeCell ref="D24:F24"/>
-    <mergeCell ref="D26:F26"/>
-    <mergeCell ref="B28:B35"/>
-    <mergeCell ref="B36:B54"/>
-    <mergeCell ref="D49:F49"/>
-    <mergeCell ref="D50:F50"/>
-    <mergeCell ref="D51:F51"/>
-    <mergeCell ref="D52:F52"/>
-    <mergeCell ref="D53:F53"/>
-    <mergeCell ref="D37:F37"/>
-    <mergeCell ref="D38:F38"/>
-    <mergeCell ref="D39:F39"/>
-    <mergeCell ref="D40:F40"/>
-    <mergeCell ref="D41:F41"/>
-    <mergeCell ref="D42:F42"/>
-    <mergeCell ref="D43:F43"/>
-    <mergeCell ref="D44:F44"/>
-    <mergeCell ref="D45:F45"/>
-    <mergeCell ref="D46:F46"/>
-    <mergeCell ref="D47:F47"/>
-    <mergeCell ref="D48:F48"/>
-    <mergeCell ref="D54:F54"/>
-    <mergeCell ref="D36:F36"/>
-    <mergeCell ref="D34:F34"/>
-    <mergeCell ref="D29:F29"/>
-    <mergeCell ref="D30:F30"/>
-    <mergeCell ref="B55:B57"/>
-    <mergeCell ref="D69:F69"/>
-    <mergeCell ref="D70:F70"/>
-    <mergeCell ref="D71:F71"/>
-    <mergeCell ref="D72:F72"/>
-    <mergeCell ref="D62:F62"/>
-    <mergeCell ref="D56:F56"/>
-    <mergeCell ref="D57:F57"/>
-    <mergeCell ref="D58:F58"/>
-    <mergeCell ref="D59:F59"/>
-    <mergeCell ref="D66:F66"/>
-    <mergeCell ref="D67:F67"/>
-    <mergeCell ref="D60:F60"/>
-    <mergeCell ref="D61:F61"/>
-    <mergeCell ref="D63:F63"/>
-    <mergeCell ref="D64:F64"/>
-    <mergeCell ref="D65:F65"/>
-    <mergeCell ref="D68:F68"/>
-    <mergeCell ref="D55:F55"/>
-    <mergeCell ref="B62:B70"/>
-    <mergeCell ref="B58:B61"/>
-    <mergeCell ref="B71:B90"/>
-    <mergeCell ref="D84:F84"/>
-    <mergeCell ref="D86:F86"/>
-    <mergeCell ref="D104:F104"/>
-    <mergeCell ref="D105:F105"/>
-    <mergeCell ref="D106:F106"/>
-    <mergeCell ref="D107:F107"/>
-    <mergeCell ref="D120:F120"/>
-    <mergeCell ref="D119:F119"/>
-    <mergeCell ref="D118:F118"/>
-    <mergeCell ref="D117:F117"/>
-    <mergeCell ref="D116:F116"/>
-    <mergeCell ref="D115:F115"/>
-    <mergeCell ref="D114:F114"/>
-    <mergeCell ref="D113:F113"/>
-    <mergeCell ref="D142:F142"/>
-    <mergeCell ref="D144:F144"/>
-    <mergeCell ref="D145:F145"/>
-    <mergeCell ref="D146:F146"/>
-    <mergeCell ref="D147:F147"/>
-    <mergeCell ref="D148:F148"/>
-    <mergeCell ref="D160:F160"/>
-    <mergeCell ref="D161:F161"/>
-    <mergeCell ref="D143:F143"/>
-    <mergeCell ref="D155:F155"/>
-    <mergeCell ref="D156:F156"/>
-    <mergeCell ref="D157:F157"/>
-    <mergeCell ref="D158:F158"/>
-    <mergeCell ref="D159:F159"/>
-    <mergeCell ref="D154:F154"/>
-    <mergeCell ref="D153:F153"/>
-    <mergeCell ref="D149:F149"/>
-    <mergeCell ref="D150:F150"/>
-    <mergeCell ref="D151:F151"/>
-    <mergeCell ref="D152:F152"/>
-    <mergeCell ref="B137:B139"/>
-    <mergeCell ref="B162:B163"/>
-    <mergeCell ref="D164:F164"/>
-    <mergeCell ref="D187:F187"/>
-    <mergeCell ref="D184:F184"/>
-    <mergeCell ref="D183:F183"/>
-    <mergeCell ref="D165:F165"/>
-    <mergeCell ref="D166:F166"/>
-    <mergeCell ref="D167:F167"/>
-    <mergeCell ref="D180:F180"/>
-    <mergeCell ref="D181:F181"/>
-    <mergeCell ref="D168:F168"/>
-    <mergeCell ref="D169:F169"/>
-    <mergeCell ref="D177:F177"/>
-    <mergeCell ref="D171:F171"/>
-    <mergeCell ref="D173:F173"/>
-    <mergeCell ref="D174:F174"/>
-    <mergeCell ref="B169:B180"/>
-    <mergeCell ref="B165:B168"/>
-    <mergeCell ref="B140:B143"/>
-    <mergeCell ref="B144:B161"/>
-    <mergeCell ref="D139:F139"/>
-    <mergeCell ref="D140:F140"/>
-    <mergeCell ref="D141:F141"/>
   </mergeCells>
   <phoneticPr fontId="3"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -12321,7 +12315,7 @@
     </row>
     <row r="85" spans="2:3">
       <c r="C85" t="s">
-        <v>444</v>
+        <v>431</v>
       </c>
     </row>
     <row r="86" spans="2:3">
@@ -12334,7 +12328,7 @@
     </row>
     <row r="87" spans="2:3">
       <c r="C87" t="s">
-        <v>371</v>
+        <v>439</v>
       </c>
     </row>
     <row r="88" spans="2:3">
@@ -12419,7 +12413,7 @@
     </row>
     <row r="103" spans="2:3">
       <c r="B103" t="s">
-        <v>372</v>
+        <v>444</v>
       </c>
       <c r="C103" t="s">
         <v>339</v>
@@ -12427,63 +12421,63 @@
     </row>
     <row r="104" spans="2:3">
       <c r="C104" s="82" t="s">
-        <v>375</v>
+        <v>445</v>
       </c>
     </row>
     <row r="105" spans="2:3">
       <c r="C105" s="82" t="s">
-        <v>376</v>
+        <v>446</v>
       </c>
     </row>
     <row r="106" spans="2:3">
       <c r="B106" t="s">
-        <v>373</v>
+        <v>362</v>
       </c>
       <c r="C106" s="83" t="s">
-        <v>377</v>
+        <v>371</v>
       </c>
     </row>
     <row r="107" spans="2:3">
       <c r="C107" s="79" t="s">
-        <v>378</v>
+        <v>348</v>
       </c>
     </row>
     <row r="108" spans="2:3">
       <c r="C108" s="79" t="s">
-        <v>379</v>
+        <v>350</v>
       </c>
     </row>
     <row r="109" spans="2:3">
       <c r="C109" s="79" t="s">
-        <v>380</v>
+        <v>440</v>
       </c>
     </row>
     <row r="110" spans="2:3">
       <c r="C110" s="79" t="s">
-        <v>381</v>
+        <v>352</v>
       </c>
     </row>
     <row r="111" spans="2:3">
       <c r="B111" t="s">
-        <v>374</v>
+        <v>356</v>
       </c>
       <c r="C111" s="79" t="s">
-        <v>377</v>
+        <v>371</v>
       </c>
     </row>
     <row r="112" spans="2:3">
       <c r="C112" s="79" t="s">
-        <v>382</v>
+        <v>441</v>
       </c>
     </row>
     <row r="113" spans="2:3">
       <c r="C113" s="79" t="s">
-        <v>383</v>
+        <v>442</v>
       </c>
     </row>
     <row r="114" spans="2:3">
       <c r="C114" s="79" t="s">
-        <v>384</v>
+        <v>443</v>
       </c>
     </row>
     <row r="115" spans="2:3">
@@ -12754,20 +12748,20 @@
     </row>
     <row r="164" spans="2:3">
       <c r="B164" t="s">
-        <v>447</v>
+        <v>434</v>
       </c>
       <c r="C164" s="79" t="s">
-        <v>446</v>
+        <v>433</v>
       </c>
     </row>
     <row r="165" spans="2:3">
       <c r="C165" s="79" t="s">
-        <v>449</v>
+        <v>436</v>
       </c>
     </row>
     <row r="166" spans="2:3">
       <c r="C166" s="79" t="s">
-        <v>445</v>
+        <v>432</v>
       </c>
     </row>
     <row r="167" spans="2:3">

--- a/IG/7日版/AI Native-バイブコーディング_IG.xlsx
+++ b/IG/7日版/AI Native-バイブコーディング_IG.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\myrepo\ai_navive\IG\7日版\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B6CD91C-A346-4657-8A05-5214E23A9A56}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9CBE823B-10FF-4CDD-A4B6-3FBA9545E40E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="860" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -347,16 +347,6 @@
     <phoneticPr fontId="3"/>
   </si>
   <si>
-    <t>オリエンテーション用資材</t>
-    <rPh sb="9" eb="10">
-      <t>ヨウ</t>
-    </rPh>
-    <rPh sb="10" eb="12">
-      <t>シザイ</t>
-    </rPh>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
     <t>【AI Native研修-バイブコーディング①】WebとDBとJavaとSpring.pptx</t>
     <phoneticPr fontId="3"/>
   </si>
@@ -427,15 +417,6 @@
   </si>
   <si>
     <t>✕</t>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
-    <t>・教材のダウンロード
-・本科目の概要説明
-　科目の位置づけや目的、全体スケジュールの説明</t>
-    <rPh sb="1" eb="3">
-      <t>キョウザイ</t>
-    </rPh>
     <phoneticPr fontId="3"/>
   </si>
   <si>
@@ -3090,10 +3071,6 @@
   </si>
   <si>
     <t>AI-09</t>
-  </si>
-  <si>
-    <t>【AI Native研修-バイブコーディング】演習振り返り.pptx</t>
-    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>サンプルAP</t>
@@ -4591,6 +4568,32 @@
   </si>
   <si>
     <t>利用するソフトウェア</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>【AI Native研修-バイブコーディング】演習振り返り.docx</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>【AI Native研修-バイブコーディング】研修の概要.pptx</t>
+    <rPh sb="10" eb="12">
+      <t>ケンシュウ</t>
+    </rPh>
+    <rPh sb="23" eb="25">
+      <t>ケンシュウ</t>
+    </rPh>
+    <rPh sb="26" eb="28">
+      <t>ガイヨウ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>・教材のダウンロード
+・本科目の概要説明
+　科目の位置づけや目的、全体の説明</t>
+    <rPh sb="1" eb="3">
+      <t>キョウザイ</t>
+    </rPh>
     <phoneticPr fontId="3"/>
   </si>
 </sst>
@@ -5833,11 +5836,11 @@
       </c>
       <c r="D9" s="21"/>
       <c r="E9" s="21" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="F9" s="21"/>
       <c r="G9" s="21" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="14.25" customHeight="1">
@@ -5994,7 +5997,7 @@
         <v>0.5</v>
       </c>
       <c r="C20" s="37" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D20" s="63"/>
       <c r="E20" s="51"/>
@@ -6266,7 +6269,7 @@
         <v>0.6875</v>
       </c>
       <c r="C38" s="66" t="s">
-        <v>426</v>
+        <v>423</v>
       </c>
       <c r="D38" s="39"/>
       <c r="E38" s="51"/>
@@ -6307,7 +6310,7 @@
         <v>0.71875</v>
       </c>
       <c r="C41" s="55" t="s">
-        <v>426</v>
+        <v>423</v>
       </c>
       <c r="D41" s="39"/>
       <c r="E41" s="99"/>
@@ -6325,7 +6328,7 @@
         <v>0.72916666666666663</v>
       </c>
       <c r="G42" s="91" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="H42" s="6"/>
     </row>
@@ -6335,13 +6338,13 @@
         <v>0.73958333333333337</v>
       </c>
       <c r="C43" s="73" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D43" s="74">
         <v>0.73958333333333337</v>
       </c>
       <c r="E43" s="73" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="F43" s="38"/>
       <c r="G43" s="92"/>
@@ -6467,7 +6470,7 @@
         <v>17</v>
       </c>
       <c r="C8" s="32" t="s">
-        <v>33</v>
+        <v>445</v>
       </c>
       <c r="D8" s="42" t="s">
         <v>19</v>
@@ -6530,15 +6533,15 @@
       <c r="A12" s="10"/>
       <c r="B12" s="19"/>
       <c r="C12" s="19" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
       <c r="D12" s="103" t="s">
-        <v>50</v>
+        <v>446</v>
       </c>
       <c r="E12" s="103"/>
       <c r="F12" s="103"/>
       <c r="G12" s="87" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="H12" s="19"/>
       <c r="I12" s="47" t="s">
@@ -6554,15 +6557,15 @@
       <c r="A13" s="10"/>
       <c r="B13" s="19"/>
       <c r="C13" s="19" t="s">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="D13" s="103" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="E13" s="103"/>
       <c r="F13" s="103"/>
       <c r="G13" s="87" t="s">
-        <v>326</v>
+        <v>323</v>
       </c>
       <c r="H13" s="19"/>
       <c r="I13" s="47" t="s">
@@ -6724,10 +6727,10 @@
     </row>
     <row r="8" spans="2:14">
       <c r="B8" s="31" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C8" s="57" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D8" s="42" t="s">
         <v>19</v>
@@ -6746,10 +6749,10 @@
     </row>
     <row r="9" spans="2:14">
       <c r="B9" s="31" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C9" s="57" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D9" s="42" t="s">
         <v>19</v>
@@ -6768,10 +6771,10 @@
     </row>
     <row r="10" spans="2:14">
       <c r="B10" s="31" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="C10" s="33" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D10" s="42" t="s">
         <v>19</v>
@@ -6790,10 +6793,10 @@
     </row>
     <row r="11" spans="2:14">
       <c r="B11" s="31" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="C11" s="57" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="D11" s="42" t="s">
         <v>19</v>
@@ -6812,10 +6815,10 @@
     </row>
     <row r="12" spans="2:14">
       <c r="B12" s="31" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="C12" s="33" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="D12" s="42" t="s">
         <v>19</v>
@@ -6834,10 +6837,10 @@
     </row>
     <row r="13" spans="2:14">
       <c r="B13" s="31" t="s">
-        <v>329</v>
+        <v>326</v>
       </c>
       <c r="C13" s="57" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D13" s="42" t="s">
         <v>19</v>
@@ -6856,10 +6859,10 @@
     </row>
     <row r="14" spans="2:14">
       <c r="B14" s="31" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="C14" s="57" t="s">
-        <v>372</v>
+        <v>369</v>
       </c>
       <c r="D14" s="42" t="s">
         <v>19</v>
@@ -6878,10 +6881,10 @@
     </row>
     <row r="15" spans="2:14">
       <c r="B15" s="31" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="C15" s="57" t="s">
-        <v>373</v>
+        <v>370</v>
       </c>
       <c r="D15" s="42" t="s">
         <v>19</v>
@@ -6900,10 +6903,10 @@
     </row>
     <row r="16" spans="2:14">
       <c r="B16" s="31" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="C16" s="57" t="s">
-        <v>283</v>
+        <v>444</v>
       </c>
       <c r="D16" s="42" t="s">
         <v>19</v>
@@ -6922,10 +6925,10 @@
     </row>
     <row r="17" spans="1:14">
       <c r="B17" s="31" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="C17" s="57" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="D17" s="42" t="s">
         <v>19</v>
@@ -7003,12 +7006,12 @@
         <v>講義の目的</v>
       </c>
       <c r="D21" s="118" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="E21" s="119"/>
       <c r="F21" s="120"/>
       <c r="G21" s="48" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="H21" s="12"/>
       <c r="I21" s="46" t="s">
@@ -7033,12 +7036,12 @@
         <v>Webアプリケーションとは</v>
       </c>
       <c r="D22" s="118" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="E22" s="119"/>
       <c r="F22" s="120"/>
       <c r="G22" s="48" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="H22" s="12"/>
       <c r="I22" s="46" t="s">
@@ -7060,12 +7063,12 @@
         <v>Webアプリケーションの種類</v>
       </c>
       <c r="D23" s="118" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="E23" s="119"/>
       <c r="F23" s="120"/>
       <c r="G23" s="48" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H23" s="12"/>
       <c r="I23" s="46" t="s">
@@ -7087,12 +7090,12 @@
         <v>アプリケーションとは</v>
       </c>
       <c r="D24" s="118" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="E24" s="119"/>
       <c r="F24" s="120"/>
       <c r="G24" s="48" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="H24" s="12"/>
       <c r="I24" s="46" t="s">
@@ -7114,12 +7117,12 @@
         <v>Web画面アプリケーション</v>
       </c>
       <c r="D25" s="118" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="E25" s="119"/>
       <c r="F25" s="120"/>
       <c r="G25" s="48" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="H25" s="12"/>
       <c r="I25" s="46" t="s">
@@ -7138,12 +7141,12 @@
       <c r="B26" s="113"/>
       <c r="C26" s="48"/>
       <c r="D26" s="118" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="E26" s="119"/>
       <c r="F26" s="120"/>
       <c r="G26" s="48" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="H26" s="12"/>
       <c r="I26" s="46" t="s">
@@ -7165,12 +7168,12 @@
         <v>ブラウザからのリクエスト種類</v>
       </c>
       <c r="D27" s="118" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="E27" s="119"/>
       <c r="F27" s="120"/>
       <c r="G27" s="48" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="H27" s="12"/>
       <c r="I27" s="46" t="s">
@@ -7195,12 +7198,12 @@
         <v>データベースとは</v>
       </c>
       <c r="D28" s="118" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="E28" s="119"/>
       <c r="F28" s="120"/>
       <c r="G28" s="48" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="H28" s="12"/>
       <c r="I28" s="46" t="s">
@@ -7222,12 +7225,12 @@
         <v>リレーショナルデータベース</v>
       </c>
       <c r="D29" s="118" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="E29" s="119"/>
       <c r="F29" s="120"/>
       <c r="G29" s="48" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="H29" s="12"/>
       <c r="I29" s="46" t="s">
@@ -7249,12 +7252,12 @@
         <v>データベースの役割</v>
       </c>
       <c r="D30" s="118" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="E30" s="119"/>
       <c r="F30" s="120"/>
       <c r="G30" s="48" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="H30" s="12"/>
       <c r="I30" s="46" t="s">
@@ -7264,7 +7267,7 @@
         <v>3.472222222222222E-3</v>
       </c>
       <c r="K30" s="40" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="L30" s="6"/>
       <c r="M30" s="6"/>
@@ -7278,12 +7281,12 @@
         <v>2.1.テーブル</v>
       </c>
       <c r="D31" s="118" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="E31" s="119"/>
       <c r="F31" s="120"/>
       <c r="G31" s="48" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H31" s="12"/>
       <c r="I31" s="46" t="s">
@@ -7305,12 +7308,12 @@
         <v>2.2.データ型１</v>
       </c>
       <c r="D32" s="118" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="E32" s="119"/>
       <c r="F32" s="120"/>
       <c r="G32" s="48" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="H32" s="12"/>
       <c r="I32" s="46" t="s">
@@ -7332,12 +7335,12 @@
         <v>2.2.データ型２</v>
       </c>
       <c r="D33" s="118" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="E33" s="119"/>
       <c r="F33" s="120"/>
       <c r="G33" s="48" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="H33" s="12"/>
       <c r="I33" s="46" t="s">
@@ -7359,12 +7362,12 @@
         <v>2.3.リレーション</v>
       </c>
       <c r="D34" s="118" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="E34" s="119"/>
       <c r="F34" s="120"/>
       <c r="G34" s="48" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="H34" s="12"/>
       <c r="I34" s="46" t="s">
@@ -7386,12 +7389,12 @@
         <v>2.4.データを結合して取得（Join）</v>
       </c>
       <c r="D35" s="118" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="E35" s="119"/>
       <c r="F35" s="120"/>
       <c r="G35" s="48" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="H35" s="12"/>
       <c r="I35" s="46" t="s">
@@ -7416,12 +7419,12 @@
         <v>Webアプリケーションを作成するためのプログラミング言語</v>
       </c>
       <c r="D36" s="118" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="E36" s="119"/>
       <c r="F36" s="120"/>
       <c r="G36" s="48" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="H36" s="12"/>
       <c r="I36" s="46" t="s">
@@ -7443,12 +7446,12 @@
         <v>Java</v>
       </c>
       <c r="D37" s="118" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="E37" s="119"/>
       <c r="F37" s="120"/>
       <c r="G37" s="48" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H37" s="12"/>
       <c r="I37" s="46" t="s">
@@ -7470,12 +7473,12 @@
         <v>Java言語の構成要素</v>
       </c>
       <c r="D38" s="118" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="E38" s="119"/>
       <c r="F38" s="120"/>
       <c r="G38" s="48" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H38" s="12"/>
       <c r="I38" s="46" t="s">
@@ -7497,12 +7500,12 @@
         <v>Webアプリケーションを構成するクラス</v>
       </c>
       <c r="D39" s="118" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="E39" s="119"/>
       <c r="F39" s="120"/>
       <c r="G39" s="48" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="H39" s="12"/>
       <c r="I39" s="46" t="s">
@@ -7524,12 +7527,12 @@
         <v>Nレイヤーアーキテクチャ</v>
       </c>
       <c r="D40" s="118" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="E40" s="119"/>
       <c r="F40" s="120"/>
       <c r="G40" s="48" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="H40" s="12"/>
       <c r="I40" s="46" t="s">
@@ -7539,7 +7542,7 @@
         <v>3.472222222222222E-3</v>
       </c>
       <c r="K40" s="40" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="L40" s="6"/>
       <c r="M40" s="6"/>
@@ -7553,16 +7556,16 @@
         <v>View と Controller と Service と Repository</v>
       </c>
       <c r="D41" s="118" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="E41" s="119"/>
       <c r="F41" s="120"/>
       <c r="G41" s="48" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="H41" s="12"/>
       <c r="I41" s="46" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="J41" s="44">
         <v>3.472222222222222E-3</v>
@@ -7580,12 +7583,12 @@
         <v>Nレイヤーアーキテクチャ</v>
       </c>
       <c r="D42" s="118" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="E42" s="119"/>
       <c r="F42" s="120"/>
       <c r="G42" s="48" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="H42" s="12"/>
       <c r="I42" s="46" t="s">
@@ -7607,12 +7610,12 @@
         <v>Webアプリケーション フレームワーク</v>
       </c>
       <c r="D43" s="118" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="E43" s="119"/>
       <c r="F43" s="120"/>
       <c r="G43" s="48" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="H43" s="12"/>
       <c r="I43" s="46" t="s">
@@ -7634,12 +7637,12 @@
         <v>Java向けWebアプリケーションフレームワーク</v>
       </c>
       <c r="D44" s="118" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="E44" s="119"/>
       <c r="F44" s="120"/>
       <c r="G44" s="48" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="H44" s="12"/>
       <c r="I44" s="46" t="s">
@@ -7661,12 +7664,12 @@
         <v>Springフレームワーク</v>
       </c>
       <c r="D45" s="118" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="E45" s="119"/>
       <c r="F45" s="120"/>
       <c r="G45" s="48" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="H45" s="12"/>
       <c r="I45" s="46" t="s">
@@ -7688,12 +7691,12 @@
         <v>Springフレームワーク：DIコンテナとは</v>
       </c>
       <c r="D46" s="118" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="E46" s="119"/>
       <c r="F46" s="120"/>
       <c r="G46" s="48" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="H46" s="12"/>
       <c r="I46" s="46" t="s">
@@ -7703,7 +7706,7 @@
         <v>3.472222222222222E-3</v>
       </c>
       <c r="K46" s="40" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="L46" s="6"/>
       <c r="M46" s="6"/>
@@ -7717,12 +7720,12 @@
         <v>DIコンテナ：DIコンテナが部品を注入する</v>
       </c>
       <c r="D47" s="118" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="E47" s="119"/>
       <c r="F47" s="120"/>
       <c r="G47" s="48" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="H47" s="12"/>
       <c r="I47" s="46" t="s">
@@ -7744,12 +7747,12 @@
         <v>DIコンテナ：DIコンテナによる部品と注入対象になるための目印</v>
       </c>
       <c r="D48" s="118" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="E48" s="119"/>
       <c r="F48" s="120"/>
       <c r="G48" s="48" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="H48" s="12"/>
       <c r="I48" s="46" t="s">
@@ -7771,12 +7774,12 @@
         <v>Springフレームワークにおける部品の設定</v>
       </c>
       <c r="D49" s="118" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="E49" s="119"/>
       <c r="F49" s="120"/>
       <c r="G49" s="48" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="H49" s="12"/>
       <c r="I49" s="46" t="s">
@@ -7798,12 +7801,12 @@
         <v>Spring Boot</v>
       </c>
       <c r="D50" s="118" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="E50" s="119"/>
       <c r="F50" s="120"/>
       <c r="G50" s="48" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="H50" s="12"/>
       <c r="I50" s="46" t="s">
@@ -7825,12 +7828,12 @@
         <v>Spring Boot：オートコンフィグレーション</v>
       </c>
       <c r="D51" s="118" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="E51" s="119"/>
       <c r="F51" s="120"/>
       <c r="G51" s="48" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="H51" s="12"/>
       <c r="I51" s="46" t="s">
@@ -7852,12 +7855,12 @@
         <v>Spring Boot：Starters</v>
       </c>
       <c r="D52" s="118" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="E52" s="119"/>
       <c r="F52" s="120"/>
       <c r="G52" s="48" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="H52" s="12"/>
       <c r="I52" s="46" t="s">
@@ -7879,12 +7882,12 @@
         <v>Spring Boot：組込みWebAPサーバ</v>
       </c>
       <c r="D53" s="118" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="E53" s="119"/>
       <c r="F53" s="120"/>
       <c r="G53" s="48" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="H53" s="12"/>
       <c r="I53" s="46" t="s">
@@ -7909,7 +7912,7 @@
       <c r="E54" s="119"/>
       <c r="F54" s="120"/>
       <c r="G54" s="48" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="H54" s="12"/>
       <c r="I54" s="46" t="s">
@@ -7934,12 +7937,12 @@
         <v>演習課題の概要</v>
       </c>
       <c r="D55" s="109" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="E55" s="110"/>
       <c r="F55" s="111"/>
       <c r="G55" s="58" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="H55" s="59"/>
       <c r="I55" s="60" t="s">
@@ -7961,12 +7964,12 @@
         <v>作成物</v>
       </c>
       <c r="D56" s="109" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="E56" s="110"/>
       <c r="F56" s="111"/>
       <c r="G56" s="58" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="H56" s="59"/>
       <c r="I56" s="60" t="s">
@@ -7988,12 +7991,12 @@
         <v>演習課題の進め方</v>
       </c>
       <c r="D57" s="109" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="E57" s="110"/>
       <c r="F57" s="111"/>
       <c r="G57" s="58" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="H57" s="59"/>
       <c r="I57" s="60" t="s">
@@ -8021,7 +8024,7 @@
       <c r="E58" s="110"/>
       <c r="F58" s="111"/>
       <c r="G58" s="58" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="H58" s="59"/>
       <c r="I58" s="60" t="s">
@@ -8043,12 +8046,12 @@
         <v>Spring Bootプロジェクトの準備</v>
       </c>
       <c r="D59" s="109" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="E59" s="110"/>
       <c r="F59" s="111"/>
       <c r="G59" s="58" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="H59" s="59"/>
       <c r="I59" s="60" t="s">
@@ -8070,16 +8073,16 @@
         <v>（補足）Spring Bootプロジェクトの準備</v>
       </c>
       <c r="D60" s="109" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="E60" s="110"/>
       <c r="F60" s="111"/>
       <c r="G60" s="58" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="H60" s="59"/>
       <c r="I60" s="60" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="J60" s="61">
         <v>0</v>
@@ -8097,16 +8100,16 @@
         <v>Spring Bootアプリケーションの起動確認</v>
       </c>
       <c r="D61" s="109" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="E61" s="110"/>
       <c r="F61" s="111"/>
       <c r="G61" s="58" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c r="H61" s="59"/>
       <c r="I61" s="60" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="J61" s="61">
         <v>6.9444444444444441E-3</v>
@@ -8127,12 +8130,12 @@
         <v>ECサイト Webアプリの要件 – はじめに</v>
       </c>
       <c r="D62" s="109" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="E62" s="110"/>
       <c r="F62" s="111"/>
       <c r="G62" s="58" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="H62" s="59"/>
       <c r="I62" s="60" t="s">
@@ -8154,12 +8157,12 @@
         <v>ECサイト Webアプリの要件➊ 画面</v>
       </c>
       <c r="D63" s="109" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="E63" s="110"/>
       <c r="F63" s="111"/>
       <c r="G63" s="58" t="s">
-        <v>292</v>
+        <v>289</v>
       </c>
       <c r="H63" s="59"/>
       <c r="I63" s="60" t="s">
@@ -8181,12 +8184,12 @@
         <v>ECサイト Webアプリの要件➋ 機能</v>
       </c>
       <c r="D64" s="109" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="E64" s="110"/>
       <c r="F64" s="111"/>
       <c r="G64" s="58" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="H64" s="59"/>
       <c r="I64" s="60" t="s">
@@ -8208,12 +8211,12 @@
         <v>ECサイト Webアプリの要件➌ 画面遷移</v>
       </c>
       <c r="D65" s="109" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="E65" s="110"/>
       <c r="F65" s="111"/>
       <c r="G65" s="58" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="H65" s="59"/>
       <c r="I65" s="60" t="s">
@@ -8235,12 +8238,12 @@
         <v>ECサイト Webアプリの要件❹ データ設計</v>
       </c>
       <c r="D66" s="109" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="E66" s="110"/>
       <c r="F66" s="111"/>
       <c r="G66" s="58" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="H66" s="59"/>
       <c r="I66" s="60" t="s">
@@ -8262,12 +8265,12 @@
         <v>ECサイト Webアプリの要件❺ 初期データ</v>
       </c>
       <c r="D67" s="109" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="E67" s="110"/>
       <c r="F67" s="111"/>
       <c r="G67" s="58" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="H67" s="59"/>
       <c r="I67" s="60" t="s">
@@ -8289,12 +8292,12 @@
         <v>ECサイト Webアプリの要件❻ ディレクトリ構成</v>
       </c>
       <c r="D68" s="109" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="E68" s="110"/>
       <c r="F68" s="111"/>
       <c r="G68" s="58" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="H68" s="59"/>
       <c r="I68" s="60" t="s">
@@ -8316,12 +8319,12 @@
         <v>ECサイト Webアプリの要件❼ パッケージ構成</v>
       </c>
       <c r="D69" s="109" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="E69" s="110"/>
       <c r="F69" s="111"/>
       <c r="G69" s="58" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="H69" s="59"/>
       <c r="I69" s="60" t="s">
@@ -8343,12 +8346,12 @@
         <v>ECサイト Webアプリの要件❽ リソース構成</v>
       </c>
       <c r="D70" s="109" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="E70" s="110"/>
       <c r="F70" s="111"/>
       <c r="G70" s="58" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="H70" s="59"/>
       <c r="I70" s="60" t="s">
@@ -8373,12 +8376,12 @@
         <v>バイブコーディング – はじめに</v>
       </c>
       <c r="D71" s="109" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="E71" s="110"/>
       <c r="F71" s="111"/>
       <c r="G71" s="58" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="H71" s="59"/>
       <c r="I71" s="60" t="s">
@@ -8400,12 +8403,12 @@
         <v>[構造理解] Webアプリケーションで必要なもの</v>
       </c>
       <c r="D72" s="109" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="E72" s="110"/>
       <c r="F72" s="111"/>
       <c r="G72" s="58" t="s">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="H72" s="59"/>
       <c r="I72" s="60" t="s">
@@ -8427,12 +8430,12 @@
         <v>バイブコーディング➊ 画面モックアップを作ってデザインを決める</v>
       </c>
       <c r="D73" s="109" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="E73" s="110"/>
       <c r="F73" s="111"/>
       <c r="G73" s="58" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="H73" s="59"/>
       <c r="I73" s="60" t="s">
@@ -8451,12 +8454,12 @@
       <c r="B74" s="116"/>
       <c r="C74" s="77"/>
       <c r="D74" s="109" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="E74" s="110"/>
       <c r="F74" s="111"/>
       <c r="G74" s="58" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c r="H74" s="59"/>
       <c r="I74" s="60"/>
@@ -8474,12 +8477,12 @@
         <v>バイブコーディング➋ データベースのテーブルを準備する</v>
       </c>
       <c r="D75" s="109" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="E75" s="110"/>
       <c r="F75" s="111"/>
       <c r="G75" s="58" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="H75" s="59"/>
       <c r="I75" s="60" t="s">
@@ -8498,12 +8501,12 @@
       <c r="B76" s="116"/>
       <c r="C76" s="77"/>
       <c r="D76" s="109" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="E76" s="110"/>
       <c r="F76" s="111"/>
       <c r="G76" s="58" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c r="H76" s="59"/>
       <c r="I76" s="60"/>
@@ -8521,12 +8524,12 @@
         <v>バイブコーディング➌ データベースのデータを準備する</v>
       </c>
       <c r="D77" s="109" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="E77" s="110"/>
       <c r="F77" s="111"/>
       <c r="G77" s="58" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="H77" s="59"/>
       <c r="I77" s="60" t="s">
@@ -8545,12 +8548,12 @@
       <c r="B78" s="116"/>
       <c r="C78" s="77"/>
       <c r="D78" s="109" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="E78" s="110"/>
       <c r="F78" s="111"/>
       <c r="G78" s="58" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c r="H78" s="59"/>
       <c r="I78" s="60"/>
@@ -8568,12 +8571,12 @@
         <v>バイブコーディング❹ データベース処理とビジネスロジックを作る</v>
       </c>
       <c r="D79" s="109" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="E79" s="110"/>
       <c r="F79" s="111"/>
       <c r="G79" s="58" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="H79" s="59"/>
       <c r="I79" s="60" t="s">
@@ -8592,12 +8595,12 @@
       <c r="B80" s="116"/>
       <c r="C80" s="77"/>
       <c r="D80" s="109" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="E80" s="110"/>
       <c r="F80" s="111"/>
       <c r="G80" s="58" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c r="H80" s="59"/>
       <c r="I80" s="60"/>
@@ -8615,12 +8618,12 @@
         <v>[解説] RepositoryクラスとSQLの例（抜粋）</v>
       </c>
       <c r="D81" s="109" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="E81" s="110"/>
       <c r="F81" s="111"/>
       <c r="G81" s="58" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="H81" s="59"/>
       <c r="I81" s="60" t="s">
@@ -8642,12 +8645,12 @@
         <v>[解説] Entity/Modelクラスの例（抜粋）</v>
       </c>
       <c r="D82" s="109" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="E82" s="110"/>
       <c r="F82" s="111"/>
       <c r="G82" s="58" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="H82" s="59"/>
       <c r="I82" s="60" t="s">
@@ -8669,12 +8672,12 @@
         <v>[解説] Serviceクラスの例（抜粋）</v>
       </c>
       <c r="D83" s="109" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="E83" s="110"/>
       <c r="F83" s="111"/>
       <c r="G83" s="58" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="H83" s="59"/>
       <c r="I83" s="60" t="s">
@@ -8696,12 +8699,12 @@
         <v>バイブコーディング❺ モックアップをもとに画面表示/処理を作る</v>
       </c>
       <c r="D84" s="109" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="E84" s="110"/>
       <c r="F84" s="111"/>
       <c r="G84" s="58" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="H84" s="59"/>
       <c r="I84" s="60" t="s">
@@ -8720,12 +8723,12 @@
       <c r="B85" s="116"/>
       <c r="C85" s="77"/>
       <c r="D85" s="109" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="E85" s="110"/>
       <c r="F85" s="111"/>
       <c r="G85" s="58" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c r="H85" s="59"/>
       <c r="I85" s="60"/>
@@ -8743,12 +8746,12 @@
         <v>[解説] Controllerクラスの例（抜粋）</v>
       </c>
       <c r="D86" s="109" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="E86" s="110"/>
       <c r="F86" s="111"/>
       <c r="G86" s="58" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="H86" s="59"/>
       <c r="I86" s="60" t="s">
@@ -8770,12 +8773,12 @@
         <v>[解説] Thymeleafテンプレートの例（抜粋）</v>
       </c>
       <c r="D87" s="109" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="E87" s="110"/>
       <c r="F87" s="111"/>
       <c r="G87" s="58" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="H87" s="59"/>
       <c r="I87" s="60" t="s">
@@ -8797,12 +8800,12 @@
         <v>[解説] Formクラスの例（抜粋）</v>
       </c>
       <c r="D88" s="109" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="E88" s="110"/>
       <c r="F88" s="111"/>
       <c r="G88" s="58" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="H88" s="59"/>
       <c r="I88" s="60" t="s">
@@ -8824,12 +8827,12 @@
         <v>バイブコーディング❻ 動作を確認する</v>
       </c>
       <c r="D89" s="109" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="E89" s="110"/>
       <c r="F89" s="111"/>
       <c r="G89" s="58" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="H89" s="59"/>
       <c r="I89" s="60" t="s">
@@ -8848,12 +8851,12 @@
       <c r="B90" s="117"/>
       <c r="C90" s="77"/>
       <c r="D90" s="109" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="E90" s="110"/>
       <c r="F90" s="111"/>
       <c r="G90" s="58" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="H90" s="59"/>
       <c r="I90" s="60" t="s">
@@ -8878,12 +8881,12 @@
         <v>はじめに</v>
       </c>
       <c r="D91" s="118" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
       <c r="E91" s="119"/>
       <c r="F91" s="120"/>
       <c r="G91" s="48" t="s">
-        <v>332</v>
+        <v>329</v>
       </c>
       <c r="H91" s="12"/>
       <c r="I91" s="46" t="s">
@@ -8905,12 +8908,12 @@
         <v>バージョン管理とは</v>
       </c>
       <c r="D92" s="118" t="s">
-        <v>374</v>
+        <v>371</v>
       </c>
       <c r="E92" s="119"/>
       <c r="F92" s="120"/>
       <c r="G92" s="48" t="s">
-        <v>331</v>
+        <v>328</v>
       </c>
       <c r="H92" s="12"/>
       <c r="I92" s="46" t="s">
@@ -8932,12 +8935,12 @@
         <v>Gitの概要</v>
       </c>
       <c r="D93" s="118" t="s">
-        <v>375</v>
+        <v>372</v>
       </c>
       <c r="E93" s="119"/>
       <c r="F93" s="120"/>
       <c r="G93" s="48" t="s">
-        <v>376</v>
+        <v>373</v>
       </c>
       <c r="H93" s="12"/>
       <c r="I93" s="46" t="s">
@@ -8962,12 +8965,12 @@
         <v>はじめに</v>
       </c>
       <c r="D94" s="118" t="s">
-        <v>398</v>
+        <v>395</v>
       </c>
       <c r="E94" s="119"/>
       <c r="F94" s="120"/>
       <c r="G94" s="48" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="H94" s="12"/>
       <c r="I94" s="46" t="s">
@@ -8989,12 +8992,12 @@
         <v>ワーキングツリー</v>
       </c>
       <c r="D95" s="118" t="s">
-        <v>378</v>
+        <v>375</v>
       </c>
       <c r="E95" s="119"/>
       <c r="F95" s="120"/>
       <c r="G95" s="48" t="s">
-        <v>331</v>
+        <v>328</v>
       </c>
       <c r="H95" s="12"/>
       <c r="I95" s="46" t="s">
@@ -9016,12 +9019,12 @@
         <v>ステージングエリア</v>
       </c>
       <c r="D96" s="118" t="s">
-        <v>379</v>
+        <v>376</v>
       </c>
       <c r="E96" s="119"/>
       <c r="F96" s="120"/>
       <c r="G96" s="48" t="s">
-        <v>331</v>
+        <v>328</v>
       </c>
       <c r="H96" s="12"/>
       <c r="I96" s="46" t="s">
@@ -9043,12 +9046,12 @@
         <v>ローカルリポジトリ</v>
       </c>
       <c r="D97" s="118" t="s">
-        <v>380</v>
+        <v>377</v>
       </c>
       <c r="E97" s="119"/>
       <c r="F97" s="120"/>
       <c r="G97" s="48" t="s">
-        <v>331</v>
+        <v>328</v>
       </c>
       <c r="H97" s="12"/>
       <c r="I97" s="46" t="s">
@@ -9070,12 +9073,12 @@
         <v>リモートリポジトリ</v>
       </c>
       <c r="D98" s="118" t="s">
-        <v>381</v>
+        <v>378</v>
       </c>
       <c r="E98" s="119"/>
       <c r="F98" s="120"/>
       <c r="G98" s="48" t="s">
-        <v>332</v>
+        <v>329</v>
       </c>
       <c r="H98" s="12"/>
       <c r="I98" s="46" t="s">
@@ -9100,12 +9103,12 @@
         <v>はじめに</v>
       </c>
       <c r="D99" s="118" t="s">
-        <v>397</v>
+        <v>394</v>
       </c>
       <c r="E99" s="119"/>
       <c r="F99" s="120"/>
       <c r="G99" s="48" t="s">
-        <v>382</v>
+        <v>379</v>
       </c>
       <c r="H99" s="12"/>
       <c r="I99" s="46" t="s">
@@ -9127,12 +9130,12 @@
         <v>リポジトリの作成</v>
       </c>
       <c r="D100" s="118" t="s">
-        <v>383</v>
+        <v>380</v>
       </c>
       <c r="E100" s="119"/>
       <c r="F100" s="120"/>
       <c r="G100" s="48" t="s">
-        <v>331</v>
+        <v>328</v>
       </c>
       <c r="H100" s="12"/>
       <c r="I100" s="46" t="s">
@@ -9154,12 +9157,12 @@
         <v>ファイルの変更</v>
       </c>
       <c r="D101" s="118" t="s">
-        <v>384</v>
+        <v>381</v>
       </c>
       <c r="E101" s="119"/>
       <c r="F101" s="120"/>
       <c r="G101" s="48" t="s">
-        <v>331</v>
+        <v>328</v>
       </c>
       <c r="H101" s="12"/>
       <c r="I101" s="46" t="s">
@@ -9181,12 +9184,12 @@
         <v>変更内容の確認</v>
       </c>
       <c r="D102" s="118" t="s">
-        <v>385</v>
+        <v>382</v>
       </c>
       <c r="E102" s="119"/>
       <c r="F102" s="120"/>
       <c r="G102" s="48" t="s">
-        <v>331</v>
+        <v>328</v>
       </c>
       <c r="H102" s="12"/>
       <c r="I102" s="46" t="s">
@@ -9208,12 +9211,12 @@
         <v>変更内容のステージ</v>
       </c>
       <c r="D103" s="118" t="s">
-        <v>386</v>
+        <v>383</v>
       </c>
       <c r="E103" s="119"/>
       <c r="F103" s="120"/>
       <c r="G103" s="48" t="s">
-        <v>331</v>
+        <v>328</v>
       </c>
       <c r="H103" s="12"/>
       <c r="I103" s="46" t="s">
@@ -9235,12 +9238,12 @@
         <v>変更内容のコミット</v>
       </c>
       <c r="D104" s="118" t="s">
-        <v>387</v>
+        <v>384</v>
       </c>
       <c r="E104" s="119"/>
       <c r="F104" s="120"/>
       <c r="G104" s="48" t="s">
-        <v>331</v>
+        <v>328</v>
       </c>
       <c r="H104" s="12"/>
       <c r="I104" s="46" t="s">
@@ -9262,12 +9265,12 @@
         <v>ワーキングツリーの変更の取り消し</v>
       </c>
       <c r="D105" s="118" t="s">
-        <v>388</v>
+        <v>385</v>
       </c>
       <c r="E105" s="119"/>
       <c r="F105" s="120"/>
       <c r="G105" s="48" t="s">
-        <v>331</v>
+        <v>328</v>
       </c>
       <c r="H105" s="12"/>
       <c r="I105" s="46" t="s">
@@ -9289,12 +9292,12 @@
         <v>ステージングの取り消し</v>
       </c>
       <c r="D106" s="118" t="s">
-        <v>389</v>
+        <v>386</v>
       </c>
       <c r="E106" s="119"/>
       <c r="F106" s="120"/>
       <c r="G106" s="48" t="s">
-        <v>331</v>
+        <v>328</v>
       </c>
       <c r="H106" s="12"/>
       <c r="I106" s="46" t="s">
@@ -9316,12 +9319,12 @@
         <v>コミットの打ち消し</v>
       </c>
       <c r="D107" s="118" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="E107" s="119"/>
       <c r="F107" s="120"/>
       <c r="G107" s="48" t="s">
-        <v>331</v>
+        <v>328</v>
       </c>
       <c r="H107" s="12"/>
       <c r="I107" s="46" t="s">
@@ -9346,22 +9349,22 @@
         <v>はじめに</v>
       </c>
       <c r="D108" s="118" t="s">
-        <v>395</v>
+        <v>392</v>
       </c>
       <c r="E108" s="119"/>
       <c r="F108" s="120"/>
       <c r="G108" s="48" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="H108" s="12"/>
       <c r="I108" s="46" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="J108" s="44">
         <v>0</v>
       </c>
       <c r="K108" s="89" t="s">
-        <v>423</v>
+        <v>420</v>
       </c>
       <c r="L108" s="6"/>
       <c r="M108" s="6"/>
@@ -9375,22 +9378,22 @@
         <v>リポジトリの複製</v>
       </c>
       <c r="D109" s="118" t="s">
-        <v>391</v>
+        <v>388</v>
       </c>
       <c r="E109" s="119"/>
       <c r="F109" s="120"/>
       <c r="G109" s="48" t="s">
-        <v>331</v>
+        <v>328</v>
       </c>
       <c r="H109" s="12"/>
       <c r="I109" s="46" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="J109" s="44">
         <v>0</v>
       </c>
       <c r="K109" s="89" t="s">
-        <v>423</v>
+        <v>420</v>
       </c>
       <c r="L109" s="6"/>
       <c r="M109" s="6"/>
@@ -9404,22 +9407,22 @@
         <v>リモートからの取得</v>
       </c>
       <c r="D110" s="118" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
       <c r="E110" s="119"/>
       <c r="F110" s="120"/>
       <c r="G110" s="48" t="s">
-        <v>331</v>
+        <v>328</v>
       </c>
       <c r="H110" s="12"/>
       <c r="I110" s="46" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="J110" s="44">
         <v>0</v>
       </c>
       <c r="K110" s="89" t="s">
-        <v>423</v>
+        <v>420</v>
       </c>
       <c r="L110" s="6"/>
       <c r="M110" s="6"/>
@@ -9433,22 +9436,22 @@
         <v>リモートからの取得と反映</v>
       </c>
       <c r="D111" s="118" t="s">
-        <v>394</v>
+        <v>391</v>
       </c>
       <c r="E111" s="119"/>
       <c r="F111" s="120"/>
       <c r="G111" s="48" t="s">
-        <v>331</v>
+        <v>328</v>
       </c>
       <c r="H111" s="12"/>
       <c r="I111" s="46" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="J111" s="44">
         <v>0</v>
       </c>
       <c r="K111" s="89" t="s">
-        <v>423</v>
+        <v>420</v>
       </c>
       <c r="L111" s="6"/>
       <c r="M111" s="6"/>
@@ -9462,22 +9465,22 @@
         <v>リモートへの反映</v>
       </c>
       <c r="D112" s="118" t="s">
-        <v>393</v>
+        <v>390</v>
       </c>
       <c r="E112" s="119"/>
       <c r="F112" s="120"/>
       <c r="G112" s="48" t="s">
-        <v>331</v>
+        <v>328</v>
       </c>
       <c r="H112" s="12"/>
       <c r="I112" s="46" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="J112" s="44">
         <v>0</v>
       </c>
       <c r="K112" s="89" t="s">
-        <v>423</v>
+        <v>420</v>
       </c>
       <c r="L112" s="6"/>
       <c r="M112" s="6"/>
@@ -9494,22 +9497,22 @@
         <v>はじめに</v>
       </c>
       <c r="D113" s="118" t="s">
-        <v>396</v>
+        <v>393</v>
       </c>
       <c r="E113" s="119"/>
       <c r="F113" s="120"/>
       <c r="G113" s="48" t="s">
-        <v>382</v>
+        <v>379</v>
       </c>
       <c r="H113" s="12"/>
       <c r="I113" s="46" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="J113" s="44">
         <v>0</v>
       </c>
       <c r="K113" s="89" t="s">
-        <v>421</v>
+        <v>418</v>
       </c>
       <c r="L113" s="6"/>
       <c r="M113" s="6"/>
@@ -9523,16 +9526,16 @@
         <v>ブランチとは</v>
       </c>
       <c r="D114" s="118" t="s">
-        <v>400</v>
+        <v>397</v>
       </c>
       <c r="E114" s="119"/>
       <c r="F114" s="120"/>
       <c r="G114" s="48" t="s">
-        <v>331</v>
+        <v>328</v>
       </c>
       <c r="H114" s="12"/>
       <c r="I114" s="46" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="J114" s="44">
         <v>0</v>
@@ -9550,16 +9553,16 @@
         <v>ブランチの作成</v>
       </c>
       <c r="D115" s="118" t="s">
-        <v>401</v>
+        <v>398</v>
       </c>
       <c r="E115" s="119"/>
       <c r="F115" s="120"/>
       <c r="G115" s="48" t="s">
-        <v>331</v>
+        <v>328</v>
       </c>
       <c r="H115" s="12"/>
       <c r="I115" s="46" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="J115" s="44">
         <v>0</v>
@@ -9577,16 +9580,16 @@
         <v>ブランチの切り替え</v>
       </c>
       <c r="D116" s="118" t="s">
-        <v>402</v>
+        <v>399</v>
       </c>
       <c r="E116" s="119"/>
       <c r="F116" s="120"/>
       <c r="G116" s="48" t="s">
-        <v>331</v>
+        <v>328</v>
       </c>
       <c r="H116" s="12"/>
       <c r="I116" s="46" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="J116" s="44">
         <v>0</v>
@@ -9604,16 +9607,16 @@
         <v>ブランチのマージ</v>
       </c>
       <c r="D117" s="118" t="s">
-        <v>403</v>
+        <v>400</v>
       </c>
       <c r="E117" s="119"/>
       <c r="F117" s="120"/>
       <c r="G117" s="48" t="s">
-        <v>331</v>
+        <v>328</v>
       </c>
       <c r="H117" s="12"/>
       <c r="I117" s="46" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="J117" s="44">
         <v>0</v>
@@ -9631,16 +9634,16 @@
         <v>コンフリクトの解消</v>
       </c>
       <c r="D118" s="118" t="s">
-        <v>405</v>
+        <v>402</v>
       </c>
       <c r="E118" s="119"/>
       <c r="F118" s="120"/>
       <c r="G118" s="48" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
       <c r="H118" s="12"/>
       <c r="I118" s="46" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="J118" s="44">
         <v>0</v>
@@ -9661,12 +9664,12 @@
         <v>はじめに</v>
       </c>
       <c r="D119" s="118" t="s">
-        <v>404</v>
+        <v>401</v>
       </c>
       <c r="E119" s="119"/>
       <c r="F119" s="120"/>
       <c r="G119" s="48" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="H119" s="12"/>
       <c r="I119" s="46" t="s">
@@ -9688,12 +9691,12 @@
         <v>VSCodeのソース管理機能</v>
       </c>
       <c r="D120" s="118" t="s">
-        <v>406</v>
+        <v>403</v>
       </c>
       <c r="E120" s="119"/>
       <c r="F120" s="120"/>
       <c r="G120" s="48" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="H120" s="12"/>
       <c r="I120" s="46" t="s">
@@ -9715,16 +9718,16 @@
         <v>ローカルリポジトリの操作</v>
       </c>
       <c r="D121" s="118" t="s">
-        <v>418</v>
+        <v>415</v>
       </c>
       <c r="E121" s="119"/>
       <c r="F121" s="120"/>
       <c r="G121" s="48" t="s">
-        <v>417</v>
+        <v>414</v>
       </c>
       <c r="H121" s="12"/>
       <c r="I121" s="46" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="J121" s="44">
         <v>0</v>
@@ -9742,22 +9745,22 @@
         <v>リモートリポジトリの操作</v>
       </c>
       <c r="D122" s="118" t="s">
-        <v>408</v>
+        <v>405</v>
       </c>
       <c r="E122" s="119"/>
       <c r="F122" s="120"/>
       <c r="G122" s="48" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="H122" s="12"/>
       <c r="I122" s="46" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="J122" s="44">
         <v>0</v>
       </c>
       <c r="K122" s="89" t="s">
-        <v>423</v>
+        <v>420</v>
       </c>
       <c r="L122" s="6"/>
       <c r="M122" s="6"/>
@@ -9771,22 +9774,22 @@
         <v>ブランチの操作</v>
       </c>
       <c r="D123" s="118" t="s">
-        <v>419</v>
+        <v>416</v>
       </c>
       <c r="E123" s="119"/>
       <c r="F123" s="120"/>
       <c r="G123" s="48" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
       <c r="H123" s="12"/>
       <c r="I123" s="46" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="J123" s="44">
         <v>0</v>
       </c>
       <c r="K123" s="89" t="s">
-        <v>422</v>
+        <v>419</v>
       </c>
       <c r="L123" s="6"/>
       <c r="M123" s="6"/>
@@ -9806,7 +9809,7 @@
       <c r="E124" s="110"/>
       <c r="F124" s="111"/>
       <c r="G124" s="58" t="s">
-        <v>335</v>
+        <v>332</v>
       </c>
       <c r="H124" s="59"/>
       <c r="I124" s="60" t="s">
@@ -9828,12 +9831,12 @@
         <v>構成</v>
       </c>
       <c r="D125" s="109" t="s">
-        <v>410</v>
+        <v>407</v>
       </c>
       <c r="E125" s="110"/>
       <c r="F125" s="111"/>
       <c r="G125" s="58" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="H125" s="59"/>
       <c r="I125" s="60" t="s">
@@ -9855,12 +9858,12 @@
         <v>利用するソフトウェア</v>
       </c>
       <c r="D126" s="109" t="s">
-        <v>411</v>
+        <v>408</v>
       </c>
       <c r="E126" s="110"/>
       <c r="F126" s="111"/>
       <c r="G126" s="58" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="H126" s="59"/>
       <c r="I126" s="60" t="s">
@@ -9870,7 +9873,7 @@
         <v>6.9444444444444447E-4</v>
       </c>
       <c r="K126" s="62" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="L126" s="6"/>
       <c r="M126" s="6"/>
@@ -9887,12 +9890,12 @@
         <v>演習の前に</v>
       </c>
       <c r="D127" s="109" t="s">
-        <v>415</v>
+        <v>412</v>
       </c>
       <c r="E127" s="110"/>
       <c r="F127" s="111"/>
       <c r="G127" s="58" t="s">
-        <v>414</v>
+        <v>411</v>
       </c>
       <c r="H127" s="59"/>
       <c r="I127" s="60" t="s">
@@ -9914,12 +9917,12 @@
         <v>リポジトリの作成</v>
       </c>
       <c r="D128" s="109" t="s">
-        <v>412</v>
+        <v>409</v>
       </c>
       <c r="E128" s="110"/>
       <c r="F128" s="111"/>
       <c r="G128" s="58" t="s">
-        <v>413</v>
+        <v>410</v>
       </c>
       <c r="H128" s="59"/>
       <c r="I128" s="60" t="s">
@@ -9941,12 +9944,12 @@
         <v>変更内容の確認</v>
       </c>
       <c r="D129" s="109" t="s">
-        <v>412</v>
+        <v>409</v>
       </c>
       <c r="E129" s="110"/>
       <c r="F129" s="111"/>
       <c r="G129" s="58" t="s">
-        <v>413</v>
+        <v>410</v>
       </c>
       <c r="H129" s="59"/>
       <c r="I129" s="60" t="s">
@@ -9968,12 +9971,12 @@
         <v>変更内容のステージング</v>
       </c>
       <c r="D130" s="109" t="s">
-        <v>412</v>
+        <v>409</v>
       </c>
       <c r="E130" s="110"/>
       <c r="F130" s="111"/>
       <c r="G130" s="58" t="s">
-        <v>413</v>
+        <v>410</v>
       </c>
       <c r="H130" s="59"/>
       <c r="I130" s="60" t="s">
@@ -9995,12 +9998,12 @@
         <v>変更内容のコミット</v>
       </c>
       <c r="D131" s="109" t="s">
-        <v>412</v>
+        <v>409</v>
       </c>
       <c r="E131" s="110"/>
       <c r="F131" s="111"/>
       <c r="G131" s="58" t="s">
-        <v>413</v>
+        <v>410</v>
       </c>
       <c r="H131" s="59"/>
       <c r="I131" s="60" t="s">
@@ -10025,22 +10028,22 @@
         <v>演習の前に</v>
       </c>
       <c r="D132" s="109" t="s">
-        <v>416</v>
+        <v>413</v>
       </c>
       <c r="E132" s="110"/>
       <c r="F132" s="111"/>
       <c r="G132" s="58" t="s">
-        <v>334</v>
+        <v>331</v>
       </c>
       <c r="H132" s="59"/>
       <c r="I132" s="60" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="J132" s="61">
         <v>0</v>
       </c>
       <c r="K132" s="62" t="s">
-        <v>422</v>
+        <v>419</v>
       </c>
       <c r="L132" s="6"/>
       <c r="M132" s="6"/>
@@ -10054,22 +10057,22 @@
         <v>ブランチの作成</v>
       </c>
       <c r="D133" s="109" t="s">
-        <v>412</v>
+        <v>409</v>
       </c>
       <c r="E133" s="110"/>
       <c r="F133" s="111"/>
       <c r="G133" s="58" t="s">
-        <v>413</v>
+        <v>410</v>
       </c>
       <c r="H133" s="59"/>
       <c r="I133" s="60" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="J133" s="61">
         <v>0</v>
       </c>
       <c r="K133" s="62" t="s">
-        <v>422</v>
+        <v>419</v>
       </c>
       <c r="L133" s="6"/>
       <c r="M133" s="6"/>
@@ -10083,22 +10086,22 @@
         <v>ブランチの切り替え</v>
       </c>
       <c r="D134" s="109" t="s">
-        <v>412</v>
+        <v>409</v>
       </c>
       <c r="E134" s="110"/>
       <c r="F134" s="111"/>
       <c r="G134" s="58" t="s">
-        <v>413</v>
+        <v>410</v>
       </c>
       <c r="H134" s="59"/>
       <c r="I134" s="60" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="J134" s="61">
         <v>0</v>
       </c>
       <c r="K134" s="62" t="s">
-        <v>422</v>
+        <v>419</v>
       </c>
       <c r="L134" s="6"/>
       <c r="M134" s="6"/>
@@ -10112,22 +10115,22 @@
         <v>ブランチのマージ</v>
       </c>
       <c r="D135" s="109" t="s">
-        <v>412</v>
+        <v>409</v>
       </c>
       <c r="E135" s="110"/>
       <c r="F135" s="111"/>
       <c r="G135" s="58" t="s">
-        <v>413</v>
+        <v>410</v>
       </c>
       <c r="H135" s="59"/>
       <c r="I135" s="60" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="J135" s="61">
         <v>0</v>
       </c>
       <c r="K135" s="62" t="s">
-        <v>422</v>
+        <v>419</v>
       </c>
       <c r="L135" s="6"/>
       <c r="M135" s="6"/>
@@ -10144,19 +10147,19 @@
         <v>ここから各自で演習を始めましょう。</v>
       </c>
       <c r="D136" s="109" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="E136" s="110"/>
       <c r="F136" s="111"/>
       <c r="G136" s="58" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="H136" s="59"/>
       <c r="I136" s="60" t="s">
-        <v>425</v>
+        <v>422</v>
       </c>
       <c r="J136" s="61" t="s">
-        <v>338</v>
+        <v>335</v>
       </c>
       <c r="K136" s="62"/>
       <c r="L136" s="6"/>
@@ -10174,12 +10177,12 @@
         <v>講義の目的</v>
       </c>
       <c r="D137" s="118" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="E137" s="119"/>
       <c r="F137" s="120"/>
       <c r="G137" s="48" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="H137" s="12"/>
       <c r="I137" s="46" t="s">
@@ -10204,7 +10207,7 @@
       <c r="E138" s="119"/>
       <c r="F138" s="120"/>
       <c r="G138" s="48" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="H138" s="12"/>
       <c r="I138" s="46" t="s">
@@ -10226,12 +10229,12 @@
         <v>V字モデル　 ※再掲</v>
       </c>
       <c r="D139" s="118" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="E139" s="119"/>
       <c r="F139" s="120"/>
       <c r="G139" s="48" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="H139" s="12"/>
       <c r="I139" s="46" t="s">
@@ -10256,12 +10259,12 @@
         <v>テストとは</v>
       </c>
       <c r="D140" s="118" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="E140" s="119"/>
       <c r="F140" s="120"/>
       <c r="G140" s="48" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="H140" s="12"/>
       <c r="I140" s="46" t="s">
@@ -10283,12 +10286,12 @@
         <v>テストの目的</v>
       </c>
       <c r="D141" s="118" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="E141" s="119"/>
       <c r="F141" s="120"/>
       <c r="G141" s="48" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="H141" s="12"/>
       <c r="I141" s="46" t="s">
@@ -10310,12 +10313,12 @@
         <v>テストを実施しなかった場合…</v>
       </c>
       <c r="D142" s="118" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="E142" s="119"/>
       <c r="F142" s="120"/>
       <c r="G142" s="48" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="H142" s="12"/>
       <c r="I142" s="46" t="s">
@@ -10337,12 +10340,12 @@
         <v>コラム：テストとデバッグ</v>
       </c>
       <c r="D143" s="118" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="E143" s="119"/>
       <c r="F143" s="120"/>
       <c r="G143" s="48" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="H143" s="12"/>
       <c r="I143" s="46" t="s">
@@ -10367,12 +10370,12 @@
         <v>単体テスト（Unit Test）とは</v>
       </c>
       <c r="D144" s="118" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="E144" s="119"/>
       <c r="F144" s="120"/>
       <c r="G144" s="48" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="H144" s="12"/>
       <c r="I144" s="46" t="s">
@@ -10397,7 +10400,7 @@
       <c r="E145" s="119"/>
       <c r="F145" s="120"/>
       <c r="G145" s="48" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="H145" s="12"/>
       <c r="I145" s="46" t="s">
@@ -10419,12 +10422,12 @@
         <v>テスト設計の流れ</v>
       </c>
       <c r="D146" s="118" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="E146" s="119"/>
       <c r="F146" s="120"/>
       <c r="G146" s="48" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="H146" s="12"/>
       <c r="I146" s="46" t="s">
@@ -10446,12 +10449,12 @@
         <v>テスト設計の例</v>
       </c>
       <c r="D147" s="118" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="E147" s="119"/>
       <c r="F147" s="120"/>
       <c r="G147" s="48" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="H147" s="12"/>
       <c r="I147" s="46" t="s">
@@ -10473,12 +10476,12 @@
         <v>単体テスト（Unit Test）とは</v>
       </c>
       <c r="D148" s="118" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="E148" s="119"/>
       <c r="F148" s="120"/>
       <c r="G148" s="48" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="H148" s="12"/>
       <c r="I148" s="46" t="s">
@@ -10500,12 +10503,12 @@
         <v>テスト技法 – ブラックボックステスト技法 –</v>
       </c>
       <c r="D149" s="118" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="E149" s="119"/>
       <c r="F149" s="120"/>
       <c r="G149" s="48" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="H149" s="12"/>
       <c r="I149" s="46" t="s">
@@ -10527,12 +10530,12 @@
         <v>ブラックボックステスト：同値分割法</v>
       </c>
       <c r="D150" s="118" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="E150" s="119"/>
       <c r="F150" s="120"/>
       <c r="G150" s="48" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="H150" s="12"/>
       <c r="I150" s="46" t="s">
@@ -10554,12 +10557,12 @@
         <v>ブラックボックステスト：境界値分析</v>
       </c>
       <c r="D151" s="118" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="E151" s="119"/>
       <c r="F151" s="120"/>
       <c r="G151" s="48" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="H151" s="12"/>
       <c r="I151" s="46" t="s">
@@ -10581,12 +10584,12 @@
         <v>ブラックボックステスト：ディシジョンテーブルテスト</v>
       </c>
       <c r="D152" s="118" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="E152" s="119"/>
       <c r="F152" s="120"/>
       <c r="G152" s="48" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="H152" s="12"/>
       <c r="I152" s="46" t="s">
@@ -10608,12 +10611,12 @@
         <v>ブラックボックステスト：状態遷移テスト</v>
       </c>
       <c r="D153" s="118" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="E153" s="119"/>
       <c r="F153" s="120"/>
       <c r="G153" s="48" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="H153" s="12"/>
       <c r="I153" s="46" t="s">
@@ -10635,12 +10638,12 @@
         <v>テスト技法 – ホワイトボックステスト技法 –</v>
       </c>
       <c r="D154" s="118" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="E154" s="119"/>
       <c r="F154" s="120"/>
       <c r="G154" s="48" t="s">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="H154" s="12"/>
       <c r="I154" s="46" t="s">
@@ -10662,12 +10665,12 @@
         <v>ホワイトボックステストの評価基準</v>
       </c>
       <c r="D155" s="118" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="E155" s="119"/>
       <c r="F155" s="120"/>
       <c r="G155" s="48" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="H155" s="12"/>
       <c r="I155" s="46" t="s">
@@ -10689,12 +10692,12 @@
         <v>ホワイトボックステスト：ステートメントテスト</v>
       </c>
       <c r="D156" s="118" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="E156" s="119"/>
       <c r="F156" s="120"/>
       <c r="G156" s="48" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="H156" s="12"/>
       <c r="I156" s="46" t="s">
@@ -10716,12 +10719,12 @@
         <v>ホワイトボックステスト：ブランチテスト</v>
       </c>
       <c r="D157" s="118" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="E157" s="119"/>
       <c r="F157" s="120"/>
       <c r="G157" s="48" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="H157" s="12"/>
       <c r="I157" s="46" t="s">
@@ -10743,12 +10746,12 @@
         <v>ホワイトボックステスト：コンディションテスト</v>
       </c>
       <c r="D158" s="118" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="E158" s="119"/>
       <c r="F158" s="120"/>
       <c r="G158" s="48" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="H158" s="12"/>
       <c r="I158" s="46" t="s">
@@ -10770,12 +10773,12 @@
         <v>テスト技法 – 経験ベースの技法 –</v>
       </c>
       <c r="D159" s="118" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="E159" s="119"/>
       <c r="F159" s="120"/>
       <c r="G159" s="48" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="H159" s="12"/>
       <c r="I159" s="46" t="s">
@@ -10797,12 +10800,12 @@
         <v>スタブとドライバ</v>
       </c>
       <c r="D160" s="118" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="E160" s="119"/>
       <c r="F160" s="120"/>
       <c r="G160" s="48" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="H160" s="12"/>
       <c r="I160" s="46" t="s">
@@ -10824,12 +10827,12 @@
         <v>スタブとモック</v>
       </c>
       <c r="D161" s="118" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="E161" s="119"/>
       <c r="F161" s="120"/>
       <c r="G161" s="48" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="H161" s="12"/>
       <c r="I161" s="46" t="s">
@@ -10854,12 +10857,12 @@
         <v>JUnitとは</v>
       </c>
       <c r="D162" s="118" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="E162" s="119"/>
       <c r="F162" s="120"/>
       <c r="G162" s="48" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="H162" s="12"/>
       <c r="I162" s="46" t="s">
@@ -10884,7 +10887,7 @@
       <c r="E163" s="119"/>
       <c r="F163" s="120"/>
       <c r="G163" s="48" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="H163" s="12"/>
       <c r="I163" s="46" t="s">
@@ -10909,19 +10912,19 @@
         <v>ここから各自で演習を始めましょう。</v>
       </c>
       <c r="D164" s="109" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="E164" s="110"/>
       <c r="F164" s="111"/>
       <c r="G164" s="58" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="H164" s="59"/>
       <c r="I164" s="60" t="s">
         <v>24</v>
       </c>
       <c r="J164" s="61" t="s">
-        <v>338</v>
+        <v>335</v>
       </c>
       <c r="K164" s="62"/>
       <c r="L164" s="6"/>
@@ -10939,12 +10942,12 @@
         <v>演習課題の概要</v>
       </c>
       <c r="D165" s="109" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="E165" s="110"/>
       <c r="F165" s="111"/>
       <c r="G165" s="58" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="H165" s="59"/>
       <c r="I165" s="60" t="s">
@@ -10966,12 +10969,12 @@
         <v>[構造理解] Webアプリケーションで必要なもの  ※再掲</v>
       </c>
       <c r="D166" s="109" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="E166" s="110"/>
       <c r="F166" s="111"/>
       <c r="G166" s="58" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="H166" s="59"/>
       <c r="I166" s="60" t="s">
@@ -10993,12 +10996,12 @@
         <v>テストクラスを作成する単位</v>
       </c>
       <c r="D167" s="109" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="E167" s="110"/>
       <c r="F167" s="111"/>
       <c r="G167" s="58" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="H167" s="59"/>
       <c r="I167" s="60" t="s">
@@ -11020,12 +11023,12 @@
         <v>JUnitで単体テスト</v>
       </c>
       <c r="D168" s="109" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="E168" s="110"/>
       <c r="F168" s="111"/>
       <c r="G168" s="58" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
       <c r="H168" s="59"/>
       <c r="I168" s="60" t="s">
@@ -11050,12 +11053,12 @@
         <v>バイブコーディングで単体テスト – はじめに</v>
       </c>
       <c r="D169" s="109" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="E169" s="110"/>
       <c r="F169" s="111"/>
       <c r="G169" s="58" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="H169" s="59"/>
       <c r="I169" s="60" t="s">
@@ -11077,12 +11080,12 @@
         <v>バイブコーディング単体テスト①テスト項目表を作る</v>
       </c>
       <c r="D170" s="109" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="E170" s="110"/>
       <c r="F170" s="111"/>
       <c r="G170" s="58" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="H170" s="59"/>
       <c r="I170" s="60" t="s">
@@ -11101,12 +11104,12 @@
       <c r="B171" s="122"/>
       <c r="C171" s="58"/>
       <c r="D171" s="109" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="E171" s="110"/>
       <c r="F171" s="111"/>
       <c r="G171" s="58" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="H171" s="59"/>
       <c r="I171" s="60" t="s">
@@ -11128,12 +11131,12 @@
         <v>バイブコーディング単体テスト②Repositoryのテストを作る</v>
       </c>
       <c r="D172" s="109" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="E172" s="110"/>
       <c r="F172" s="111"/>
       <c r="G172" s="58" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="H172" s="59"/>
       <c r="I172" s="60" t="s">
@@ -11152,12 +11155,12 @@
       <c r="B173" s="122"/>
       <c r="C173" s="77"/>
       <c r="D173" s="109" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="E173" s="110"/>
       <c r="F173" s="111"/>
       <c r="G173" s="58" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="H173" s="59"/>
       <c r="I173" s="60" t="s">
@@ -11179,12 +11182,12 @@
         <v>[解説] Repositoryのテストクラス（抜粋）</v>
       </c>
       <c r="D174" s="109" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="E174" s="110"/>
       <c r="F174" s="111"/>
       <c r="G174" s="58" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="H174" s="59"/>
       <c r="I174" s="60" t="s">
@@ -11206,12 +11209,12 @@
         <v>バイブコーディング単体テスト③Serviceのテストを作る</v>
       </c>
       <c r="D175" s="109" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="E175" s="110"/>
       <c r="F175" s="111"/>
       <c r="G175" s="58" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="H175" s="59"/>
       <c r="I175" s="60" t="s">
@@ -11230,12 +11233,12 @@
       <c r="B176" s="122"/>
       <c r="C176" s="77"/>
       <c r="D176" s="109" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="E176" s="110"/>
       <c r="F176" s="111"/>
       <c r="G176" s="58" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="H176" s="59"/>
       <c r="I176" s="60" t="s">
@@ -11257,12 +11260,12 @@
         <v>[解説] Serviceのテストクラス（抜粋）</v>
       </c>
       <c r="D177" s="109" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="E177" s="110"/>
       <c r="F177" s="111"/>
       <c r="G177" s="58" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="H177" s="59"/>
       <c r="I177" s="60" t="s">
@@ -11284,12 +11287,12 @@
         <v>バイブコーディング単体テスト④Controllerのテストを作る</v>
       </c>
       <c r="D178" s="109" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="E178" s="110"/>
       <c r="F178" s="111"/>
       <c r="G178" s="58" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="H178" s="59"/>
       <c r="I178" s="60" t="s">
@@ -11308,12 +11311,12 @@
       <c r="B179" s="122"/>
       <c r="C179" s="77"/>
       <c r="D179" s="109" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="E179" s="110"/>
       <c r="F179" s="111"/>
       <c r="G179" s="58" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="H179" s="59"/>
       <c r="I179" s="60" t="s">
@@ -11335,12 +11338,12 @@
         <v>[解説] Controllerのテストクラス（抜粋）</v>
       </c>
       <c r="D180" s="109" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="E180" s="110"/>
       <c r="F180" s="111"/>
       <c r="G180" s="58" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="H180" s="59"/>
       <c r="I180" s="60" t="s">
@@ -11365,19 +11368,19 @@
         <v>ここから各自で演習を始めましょう。</v>
       </c>
       <c r="D181" s="109" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="E181" s="110"/>
       <c r="F181" s="111"/>
       <c r="G181" s="58" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="H181" s="59"/>
       <c r="I181" s="60" t="s">
         <v>24</v>
       </c>
       <c r="J181" s="61" t="s">
-        <v>338</v>
+        <v>335</v>
       </c>
       <c r="K181" s="62"/>
       <c r="L181" s="6"/>
@@ -11392,22 +11395,22 @@
         <v>[終了条件] 講師配布のテストプログラム(JUnit)が成功すること</v>
       </c>
       <c r="D182" s="109" t="s">
-        <v>337</v>
+        <v>334</v>
       </c>
       <c r="E182" s="110"/>
       <c r="F182" s="111"/>
       <c r="G182" s="58" t="s">
-        <v>336</v>
+        <v>333</v>
       </c>
       <c r="H182" s="59"/>
       <c r="I182" s="60" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="J182" s="61" t="s">
-        <v>338</v>
+        <v>335</v>
       </c>
       <c r="K182" s="62" t="s">
-        <v>428</v>
+        <v>425</v>
       </c>
       <c r="L182" s="6"/>
       <c r="M182" s="6"/>
@@ -11424,22 +11427,22 @@
         <v>演習課題の概要</v>
       </c>
       <c r="D183" s="109" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="E183" s="110"/>
       <c r="F183" s="111"/>
       <c r="G183" s="58" t="s">
-        <v>334</v>
+        <v>331</v>
       </c>
       <c r="H183" s="59"/>
       <c r="I183" s="60" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="J183" s="61" t="s">
-        <v>338</v>
+        <v>335</v>
       </c>
       <c r="K183" s="62" t="s">
-        <v>427</v>
+        <v>424</v>
       </c>
       <c r="L183" s="6"/>
       <c r="M183" s="6"/>
@@ -11453,22 +11456,22 @@
         <v>追加課題①：送料の表示機能</v>
       </c>
       <c r="D184" s="109" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="E184" s="110"/>
       <c r="F184" s="111"/>
       <c r="G184" s="58" t="s">
-        <v>335</v>
+        <v>332</v>
       </c>
       <c r="H184" s="59"/>
       <c r="I184" s="60" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="J184" s="61" t="s">
-        <v>338</v>
+        <v>335</v>
       </c>
       <c r="K184" s="62" t="s">
-        <v>427</v>
+        <v>424</v>
       </c>
       <c r="L184" s="6"/>
       <c r="M184" s="6"/>
@@ -11482,22 +11485,22 @@
         <v>追加課題②：クーポン機能</v>
       </c>
       <c r="D185" s="109" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="E185" s="110"/>
       <c r="F185" s="111"/>
       <c r="G185" s="58" t="s">
-        <v>335</v>
+        <v>332</v>
       </c>
       <c r="H185" s="59"/>
       <c r="I185" s="60" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="J185" s="61" t="s">
-        <v>338</v>
+        <v>335</v>
       </c>
       <c r="K185" s="62" t="s">
-        <v>427</v>
+        <v>424</v>
       </c>
       <c r="L185" s="6"/>
       <c r="M185" s="6"/>
@@ -11511,22 +11514,22 @@
         <v>追加課題③：ユーザーアカウント機能</v>
       </c>
       <c r="D186" s="109" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="E186" s="110"/>
       <c r="F186" s="111"/>
       <c r="G186" s="58" t="s">
-        <v>335</v>
+        <v>332</v>
       </c>
       <c r="H186" s="59"/>
       <c r="I186" s="60" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="J186" s="61" t="s">
-        <v>338</v>
+        <v>335</v>
       </c>
       <c r="K186" s="62" t="s">
-        <v>427</v>
+        <v>424</v>
       </c>
       <c r="L186" s="6"/>
       <c r="M186" s="6"/>
@@ -11543,12 +11546,12 @@
         <v>アプリケーションの比較・分析</v>
       </c>
       <c r="D187" s="109" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="E187" s="110"/>
       <c r="F187" s="111"/>
       <c r="G187" s="58" t="s">
-        <v>429</v>
+        <v>426</v>
       </c>
       <c r="H187" s="59"/>
       <c r="I187" s="60" t="s">
@@ -11570,12 +11573,12 @@
         <v>改善点の整理</v>
       </c>
       <c r="D188" s="109" t="s">
-        <v>437</v>
+        <v>434</v>
       </c>
       <c r="E188" s="110"/>
       <c r="F188" s="111"/>
       <c r="G188" s="58" t="s">
-        <v>430</v>
+        <v>427</v>
       </c>
       <c r="H188" s="59"/>
       <c r="I188" s="60" t="s">
@@ -11597,12 +11600,12 @@
         <v>分析結果の共有</v>
       </c>
       <c r="D189" s="109" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="E189" s="110"/>
       <c r="F189" s="111"/>
       <c r="G189" s="58" t="s">
-        <v>430</v>
+        <v>427</v>
       </c>
       <c r="H189" s="59"/>
       <c r="I189" s="60" t="s">
@@ -11858,7 +11861,7 @@
   <sheetData>
     <row r="1" spans="2:3">
       <c r="B1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="2" spans="2:3">
@@ -11871,179 +11874,179 @@
     </row>
     <row r="3" spans="2:3">
       <c r="B3" t="s">
-        <v>321</v>
+        <v>318</v>
       </c>
       <c r="C3" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
     </row>
     <row r="4" spans="2:3">
       <c r="B4" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C4" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
     </row>
     <row r="5" spans="2:3">
       <c r="C5" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
     </row>
     <row r="6" spans="2:3">
       <c r="C6" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
     </row>
     <row r="7" spans="2:3">
       <c r="C7" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
     </row>
     <row r="8" spans="2:3">
       <c r="C8" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
     </row>
     <row r="9" spans="2:3">
       <c r="B9" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C9" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="10" spans="2:3">
       <c r="C10" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="11" spans="2:3">
       <c r="C11" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="12" spans="2:3">
       <c r="C12" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
     </row>
     <row r="13" spans="2:3">
       <c r="C13" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
     </row>
     <row r="14" spans="2:3">
       <c r="C14" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
     </row>
     <row r="15" spans="2:3">
       <c r="C15" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
     </row>
     <row r="16" spans="2:3">
       <c r="C16" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
     </row>
     <row r="17" spans="2:3">
       <c r="B17" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="C17" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
     </row>
     <row r="18" spans="2:3">
       <c r="C18" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
     </row>
     <row r="19" spans="2:3">
       <c r="C19" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
     </row>
     <row r="20" spans="2:3">
       <c r="C20" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
     </row>
     <row r="21" spans="2:3">
       <c r="C21" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
     </row>
     <row r="22" spans="2:3">
       <c r="C22" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
     </row>
     <row r="23" spans="2:3">
       <c r="C23" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
     </row>
     <row r="24" spans="2:3">
       <c r="C24" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
     </row>
     <row r="25" spans="2:3">
       <c r="C25" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
     </row>
     <row r="26" spans="2:3">
       <c r="C26" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
     </row>
     <row r="27" spans="2:3">
       <c r="C27" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
     </row>
     <row r="28" spans="2:3">
       <c r="C28" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
     </row>
     <row r="29" spans="2:3">
       <c r="C29" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
     </row>
     <row r="30" spans="2:3">
       <c r="C30" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
     </row>
     <row r="31" spans="2:3">
       <c r="C31" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
     </row>
     <row r="32" spans="2:3">
       <c r="C32" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
     </row>
     <row r="33" spans="2:3">
       <c r="C33" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="34" spans="2:3">
       <c r="C34" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
     </row>
     <row r="35" spans="2:3">
       <c r="C35" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
     </row>
     <row r="36" spans="2:3">
@@ -12052,172 +12055,172 @@
     </row>
     <row r="37" spans="2:3">
       <c r="B37" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="C37" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
     </row>
     <row r="38" spans="2:3">
       <c r="C38" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
     </row>
     <row r="39" spans="2:3">
       <c r="C39" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
     </row>
     <row r="40" spans="2:3">
       <c r="B40" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="C40" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
     </row>
     <row r="41" spans="2:3">
       <c r="C41" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
     </row>
     <row r="42" spans="2:3">
       <c r="C42" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
     </row>
     <row r="43" spans="2:3">
       <c r="C43" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
     </row>
     <row r="44" spans="2:3">
       <c r="B44" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="C44" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
     </row>
     <row r="45" spans="2:3">
       <c r="C45" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
     </row>
     <row r="46" spans="2:3">
       <c r="C46" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
     </row>
     <row r="47" spans="2:3">
       <c r="C47" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
     </row>
     <row r="48" spans="2:3">
       <c r="C48" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
     </row>
     <row r="49" spans="2:3">
       <c r="C49" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
     </row>
     <row r="50" spans="2:3">
       <c r="C50" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
     </row>
     <row r="51" spans="2:3">
       <c r="C51" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
     </row>
     <row r="52" spans="2:3">
       <c r="C52" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
     </row>
     <row r="53" spans="2:3">
       <c r="B53" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="C53" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
     </row>
     <row r="54" spans="2:3">
       <c r="C54" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="55" spans="2:3">
       <c r="C55" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
     </row>
     <row r="56" spans="2:3">
       <c r="C56" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
     </row>
     <row r="57" spans="2:3">
       <c r="C57" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
     </row>
     <row r="58" spans="2:3">
       <c r="C58" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
     </row>
     <row r="59" spans="2:3">
       <c r="C59" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
     </row>
     <row r="60" spans="2:3">
       <c r="C60" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
     </row>
     <row r="61" spans="2:3">
       <c r="C61" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
     </row>
     <row r="62" spans="2:3">
       <c r="C62" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
     </row>
     <row r="63" spans="2:3">
       <c r="C63" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
     </row>
     <row r="64" spans="2:3">
       <c r="C64" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
     </row>
     <row r="65" spans="2:3">
       <c r="C65" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
     </row>
     <row r="66" spans="2:3">
       <c r="C66" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
     </row>
     <row r="67" spans="2:3">
       <c r="B67" t="s">
-        <v>319</v>
+        <v>316</v>
       </c>
       <c r="C67" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
     </row>
     <row r="68" spans="2:3">
@@ -12226,185 +12229,185 @@
     </row>
     <row r="69" spans="2:3">
       <c r="B69" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="C69" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
     </row>
     <row r="70" spans="2:3">
       <c r="C70" t="s">
-        <v>340</v>
+        <v>337</v>
       </c>
     </row>
     <row r="71" spans="2:3">
       <c r="C71" t="s">
-        <v>341</v>
+        <v>338</v>
       </c>
     </row>
     <row r="72" spans="2:3">
       <c r="B72" t="s">
-        <v>342</v>
+        <v>339</v>
       </c>
       <c r="C72" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
     </row>
     <row r="73" spans="2:3">
       <c r="C73" t="s">
-        <v>343</v>
+        <v>340</v>
       </c>
     </row>
     <row r="74" spans="2:3">
       <c r="C74" t="s">
-        <v>344</v>
+        <v>341</v>
       </c>
     </row>
     <row r="75" spans="2:3">
       <c r="C75" t="s">
-        <v>345</v>
+        <v>342</v>
       </c>
     </row>
     <row r="76" spans="2:3">
       <c r="C76" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
     </row>
     <row r="77" spans="2:3">
       <c r="B77" t="s">
-        <v>347</v>
+        <v>344</v>
       </c>
       <c r="C77" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
     </row>
     <row r="78" spans="2:3">
       <c r="C78" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
     </row>
     <row r="79" spans="2:3">
       <c r="C79" t="s">
-        <v>349</v>
+        <v>346</v>
       </c>
     </row>
     <row r="80" spans="2:3">
       <c r="C80" t="s">
-        <v>350</v>
+        <v>347</v>
       </c>
     </row>
     <row r="81" spans="2:3">
       <c r="C81" t="s">
-        <v>351</v>
+        <v>348</v>
       </c>
     </row>
     <row r="82" spans="2:3">
       <c r="C82" t="s">
-        <v>352</v>
+        <v>349</v>
       </c>
     </row>
     <row r="83" spans="2:3">
       <c r="C83" t="s">
-        <v>353</v>
+        <v>350</v>
       </c>
     </row>
     <row r="84" spans="2:3">
       <c r="C84" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
     </row>
     <row r="85" spans="2:3">
       <c r="C85" t="s">
-        <v>431</v>
+        <v>428</v>
       </c>
     </row>
     <row r="86" spans="2:3">
       <c r="B86" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
       <c r="C86" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
     </row>
     <row r="87" spans="2:3">
       <c r="C87" t="s">
-        <v>439</v>
+        <v>436</v>
       </c>
     </row>
     <row r="88" spans="2:3">
       <c r="C88" t="s">
-        <v>370</v>
+        <v>367</v>
       </c>
     </row>
     <row r="89" spans="2:3">
       <c r="C89" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
     </row>
     <row r="90" spans="2:3">
       <c r="C90" t="s">
-        <v>368</v>
+        <v>365</v>
       </c>
     </row>
     <row r="91" spans="2:3">
       <c r="B91" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="C91" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
     </row>
     <row r="92" spans="2:3">
       <c r="C92" t="s">
-        <v>357</v>
+        <v>354</v>
       </c>
     </row>
     <row r="93" spans="2:3">
       <c r="C93" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
     </row>
     <row r="94" spans="2:3">
       <c r="C94" t="s">
-        <v>366</v>
+        <v>363</v>
       </c>
     </row>
     <row r="95" spans="2:3">
       <c r="C95" t="s">
-        <v>365</v>
+        <v>362</v>
       </c>
     </row>
     <row r="96" spans="2:3">
       <c r="C96" t="s">
-        <v>358</v>
+        <v>355</v>
       </c>
     </row>
     <row r="97" spans="2:3">
       <c r="B97" t="s">
-        <v>359</v>
+        <v>356</v>
       </c>
       <c r="C97" t="s">
-        <v>361</v>
+        <v>358</v>
       </c>
     </row>
     <row r="98" spans="2:3">
       <c r="C98" t="s">
-        <v>360</v>
+        <v>357</v>
       </c>
     </row>
     <row r="99" spans="2:3">
       <c r="C99" t="s">
-        <v>362</v>
+        <v>359</v>
       </c>
     </row>
     <row r="100" spans="2:3">
       <c r="C100" t="s">
-        <v>363</v>
+        <v>360</v>
       </c>
     </row>
     <row r="101" spans="2:3">
       <c r="C101" t="s">
-        <v>364</v>
+        <v>361</v>
       </c>
     </row>
     <row r="102" spans="2:3">
@@ -12413,71 +12416,71 @@
     </row>
     <row r="103" spans="2:3">
       <c r="B103" t="s">
-        <v>444</v>
+        <v>441</v>
       </c>
       <c r="C103" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
     </row>
     <row r="104" spans="2:3">
       <c r="C104" s="82" t="s">
-        <v>445</v>
+        <v>442</v>
       </c>
     </row>
     <row r="105" spans="2:3">
       <c r="C105" s="82" t="s">
-        <v>446</v>
+        <v>443</v>
       </c>
     </row>
     <row r="106" spans="2:3">
       <c r="B106" t="s">
-        <v>362</v>
+        <v>359</v>
       </c>
       <c r="C106" s="83" t="s">
-        <v>371</v>
+        <v>368</v>
       </c>
     </row>
     <row r="107" spans="2:3">
       <c r="C107" s="79" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
     </row>
     <row r="108" spans="2:3">
       <c r="C108" s="79" t="s">
-        <v>350</v>
+        <v>347</v>
       </c>
     </row>
     <row r="109" spans="2:3">
       <c r="C109" s="79" t="s">
-        <v>440</v>
+        <v>437</v>
       </c>
     </row>
     <row r="110" spans="2:3">
       <c r="C110" s="79" t="s">
-        <v>352</v>
+        <v>349</v>
       </c>
     </row>
     <row r="111" spans="2:3">
       <c r="B111" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="C111" s="79" t="s">
-        <v>371</v>
+        <v>368</v>
       </c>
     </row>
     <row r="112" spans="2:3">
       <c r="C112" s="79" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
     </row>
     <row r="113" spans="2:3">
       <c r="C113" s="79" t="s">
-        <v>442</v>
+        <v>439</v>
       </c>
     </row>
     <row r="114" spans="2:3">
       <c r="C114" s="79" t="s">
-        <v>443</v>
+        <v>440</v>
       </c>
     </row>
     <row r="115" spans="2:3">
@@ -12486,149 +12489,149 @@
     </row>
     <row r="116" spans="2:3">
       <c r="B116" t="s">
-        <v>323</v>
+        <v>320</v>
       </c>
       <c r="C116" s="79" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
     </row>
     <row r="117" spans="2:3">
       <c r="C117" s="82" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
     </row>
     <row r="118" spans="2:3">
       <c r="C118" s="82" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
     </row>
     <row r="119" spans="2:3">
       <c r="B119" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="C119" s="82" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
     </row>
     <row r="120" spans="2:3">
       <c r="C120" s="82" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
     </row>
     <row r="121" spans="2:3">
       <c r="C121" s="83" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
     </row>
     <row r="122" spans="2:3">
       <c r="C122" s="79" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
     </row>
     <row r="123" spans="2:3">
       <c r="B123" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="C123" s="79" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
     </row>
     <row r="124" spans="2:3">
       <c r="C124" s="79" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
     </row>
     <row r="125" spans="2:3">
       <c r="C125" s="79" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
     </row>
     <row r="126" spans="2:3">
       <c r="C126" s="79" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
     </row>
     <row r="127" spans="2:3">
       <c r="C127" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
     </row>
     <row r="128" spans="2:3">
       <c r="C128" s="79" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
     </row>
     <row r="129" spans="2:3">
       <c r="C129" s="79" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
     </row>
     <row r="130" spans="2:3">
       <c r="C130" s="79" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="131" spans="2:3">
       <c r="C131" s="79" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
     </row>
     <row r="132" spans="2:3">
       <c r="C132" s="79" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
     </row>
     <row r="133" spans="2:3">
       <c r="C133" s="79" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
     </row>
     <row r="134" spans="2:3">
       <c r="C134" s="79" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
     </row>
     <row r="135" spans="2:3">
       <c r="C135" s="79" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
     </row>
     <row r="136" spans="2:3">
       <c r="C136" s="79" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
     </row>
     <row r="137" spans="2:3">
       <c r="C137" s="79" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
     </row>
     <row r="138" spans="2:3">
       <c r="C138" s="79" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
     </row>
     <row r="139" spans="2:3">
       <c r="C139" s="79" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
     </row>
     <row r="140" spans="2:3">
       <c r="C140" s="79" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
     </row>
     <row r="141" spans="2:3">
       <c r="B141" s="79" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="C141" s="79" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
     </row>
     <row r="142" spans="2:3">
       <c r="C142" s="79" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
     </row>
     <row r="143" spans="2:3">
@@ -12637,81 +12640,81 @@
     </row>
     <row r="144" spans="2:3">
       <c r="B144" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="C144" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
     </row>
     <row r="145" spans="2:3">
       <c r="C145" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
     </row>
     <row r="146" spans="2:3">
       <c r="C146" s="79" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
     </row>
     <row r="147" spans="2:3">
       <c r="C147" s="79" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
     </row>
     <row r="148" spans="2:3">
       <c r="B148" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="C148" s="79" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
     </row>
     <row r="149" spans="2:3">
       <c r="C149" s="79" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
     </row>
     <row r="150" spans="2:3">
       <c r="C150" s="79" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
     </row>
     <row r="151" spans="2:3">
       <c r="C151" s="79" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
     </row>
     <row r="152" spans="2:3">
       <c r="C152" s="79" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
     </row>
     <row r="153" spans="2:3">
       <c r="C153" s="79" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
     </row>
     <row r="154" spans="2:3">
       <c r="C154" s="79" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
     </row>
     <row r="155" spans="2:3">
       <c r="C155" s="79" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
     </row>
     <row r="156" spans="2:3">
       <c r="B156" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="C156" s="79" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
     </row>
     <row r="157" spans="2:3">
       <c r="C157" s="79" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
     </row>
     <row r="158" spans="2:3">
@@ -12720,26 +12723,26 @@
     </row>
     <row r="159" spans="2:3">
       <c r="B159" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="C159" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
     </row>
     <row r="160" spans="2:3">
       <c r="B160" s="79"/>
       <c r="C160" s="79" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
     </row>
     <row r="161" spans="2:3">
       <c r="C161" s="79" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
     </row>
     <row r="162" spans="2:3">
       <c r="C162" s="79" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
     </row>
     <row r="163" spans="2:3">
@@ -12748,20 +12751,20 @@
     </row>
     <row r="164" spans="2:3">
       <c r="B164" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="C164" s="79" t="s">
-        <v>433</v>
+        <v>430</v>
       </c>
     </row>
     <row r="165" spans="2:3">
       <c r="C165" s="79" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
     </row>
     <row r="166" spans="2:3">
       <c r="C166" s="79" t="s">
-        <v>432</v>
+        <v>429</v>
       </c>
     </row>
     <row r="167" spans="2:3">

--- a/IG/7日版/AI Native-バイブコーディング_IG.xlsx
+++ b/IG/7日版/AI Native-バイブコーディング_IG.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\myrepo\ai_navive\IG\7日版\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9CBE823B-10FF-4CDD-A4B6-3FBA9545E40E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C868B2B-729A-429E-80B2-167328CFE7E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="860" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4768,7 +4768,7 @@
       <charset val="128"/>
     </font>
   </fonts>
-  <fills count="11">
+  <fills count="12">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -4826,6 +4826,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="0" tint="-0.14999847407452621"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -5017,7 +5023,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="130">
+  <cellXfs count="138">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -5345,6 +5351,15 @@
     <xf numFmtId="0" fontId="11" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -5354,6 +5369,33 @@
     <xf numFmtId="0" fontId="5" fillId="9" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="255"/>
     </xf>
@@ -5363,32 +5405,8 @@
     <xf numFmtId="0" fontId="5" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="255"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -5396,17 +5414,29 @@
     <xf numFmtId="0" fontId="11" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="20" fontId="5" fillId="11" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="20" fontId="5" fillId="11" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -6679,16 +6709,16 @@
       <c r="M4" s="9"/>
     </row>
     <row r="5" spans="2:14" ht="36" customHeight="1">
-      <c r="B5" s="126"/>
-      <c r="C5" s="126"/>
-      <c r="D5" s="126"/>
-      <c r="E5" s="126"/>
-      <c r="F5" s="126"/>
-      <c r="G5" s="126"/>
-      <c r="H5" s="126"/>
-      <c r="I5" s="126"/>
-      <c r="J5" s="126"/>
-      <c r="K5" s="126"/>
+      <c r="B5" s="127"/>
+      <c r="C5" s="127"/>
+      <c r="D5" s="127"/>
+      <c r="E5" s="127"/>
+      <c r="F5" s="127"/>
+      <c r="G5" s="127"/>
+      <c r="H5" s="127"/>
+      <c r="I5" s="127"/>
+      <c r="J5" s="127"/>
+      <c r="K5" s="127"/>
       <c r="L5" s="26"/>
       <c r="M5" s="27"/>
     </row>
@@ -6964,10 +6994,10 @@
       <c r="H19" s="101" t="s">
         <v>23</v>
       </c>
-      <c r="I19" s="124" t="s">
+      <c r="I19" s="128" t="s">
         <v>31</v>
       </c>
-      <c r="J19" s="125"/>
+      <c r="J19" s="129"/>
       <c r="K19" s="101" t="s">
         <v>32</v>
       </c>
@@ -7027,7 +7057,7 @@
     </row>
     <row r="22" spans="1:14" ht="138.6" customHeight="1">
       <c r="A22" s="10"/>
-      <c r="B22" s="112" t="str">
+      <c r="B22" s="124" t="str">
         <f>master!B4</f>
         <v>Webアプリケーションとは</v>
       </c>
@@ -7057,7 +7087,7 @@
     </row>
     <row r="23" spans="1:14" ht="75.599999999999994">
       <c r="A23" s="11"/>
-      <c r="B23" s="113"/>
+      <c r="B23" s="125"/>
       <c r="C23" s="48" t="str">
         <f>master!C5</f>
         <v>Webアプリケーションの種類</v>
@@ -7084,7 +7114,7 @@
     </row>
     <row r="24" spans="1:14" ht="37.799999999999997">
       <c r="A24" s="11"/>
-      <c r="B24" s="113"/>
+      <c r="B24" s="125"/>
       <c r="C24" s="48" t="str">
         <f>master!C6</f>
         <v>アプリケーションとは</v>
@@ -7111,7 +7141,7 @@
     </row>
     <row r="25" spans="1:14" ht="63">
       <c r="A25" s="11"/>
-      <c r="B25" s="113"/>
+      <c r="B25" s="125"/>
       <c r="C25" s="48" t="str">
         <f>master!C7</f>
         <v>Web画面アプリケーション</v>
@@ -7138,7 +7168,7 @@
     </row>
     <row r="26" spans="1:14" ht="63">
       <c r="A26" s="11"/>
-      <c r="B26" s="113"/>
+      <c r="B26" s="125"/>
       <c r="C26" s="48"/>
       <c r="D26" s="118" t="s">
         <v>99</v>
@@ -7162,7 +7192,7 @@
     </row>
     <row r="27" spans="1:14" ht="113.4">
       <c r="A27" s="11"/>
-      <c r="B27" s="114"/>
+      <c r="B27" s="126"/>
       <c r="C27" s="48" t="str">
         <f>master!C8</f>
         <v>ブラウザからのリクエスト種類</v>
@@ -7189,7 +7219,7 @@
     </row>
     <row r="28" spans="1:14" ht="102" customHeight="1">
       <c r="A28" s="11"/>
-      <c r="B28" s="112" t="str">
+      <c r="B28" s="124" t="str">
         <f>master!B9</f>
         <v>データベースとは</v>
       </c>
@@ -7219,7 +7249,7 @@
     </row>
     <row r="29" spans="1:14" ht="88.2">
       <c r="A29" s="11"/>
-      <c r="B29" s="113"/>
+      <c r="B29" s="125"/>
       <c r="C29" s="48" t="str">
         <f>master!C10</f>
         <v>リレーショナルデータベース</v>
@@ -7246,7 +7276,7 @@
     </row>
     <row r="30" spans="1:14" ht="25.2">
       <c r="A30" s="11"/>
-      <c r="B30" s="113"/>
+      <c r="B30" s="125"/>
       <c r="C30" s="48" t="str">
         <f>master!C11</f>
         <v>データベースの役割</v>
@@ -7275,7 +7305,7 @@
     </row>
     <row r="31" spans="1:14" ht="75.599999999999994">
       <c r="A31" s="11"/>
-      <c r="B31" s="113"/>
+      <c r="B31" s="125"/>
       <c r="C31" s="48" t="str">
         <f>master!C12</f>
         <v>2.1.テーブル</v>
@@ -7302,7 +7332,7 @@
     </row>
     <row r="32" spans="1:14" ht="100.8">
       <c r="A32" s="11"/>
-      <c r="B32" s="113"/>
+      <c r="B32" s="125"/>
       <c r="C32" s="48" t="str">
         <f>master!C13</f>
         <v>2.2.データ型１</v>
@@ -7329,7 +7359,7 @@
     </row>
     <row r="33" spans="1:14" ht="37.799999999999997">
       <c r="A33" s="11"/>
-      <c r="B33" s="113"/>
+      <c r="B33" s="125"/>
       <c r="C33" s="48" t="str">
         <f>master!C14</f>
         <v>2.2.データ型２</v>
@@ -7356,7 +7386,7 @@
     </row>
     <row r="34" spans="1:14" ht="37.799999999999997">
       <c r="A34" s="11"/>
-      <c r="B34" s="113"/>
+      <c r="B34" s="125"/>
       <c r="C34" s="48" t="str">
         <f>master!C15</f>
         <v>2.3.リレーション</v>
@@ -7383,7 +7413,7 @@
     </row>
     <row r="35" spans="1:14" ht="37.799999999999997">
       <c r="A35" s="11"/>
-      <c r="B35" s="114"/>
+      <c r="B35" s="126"/>
       <c r="C35" s="48" t="str">
         <f>master!C16</f>
         <v>2.4.データを結合して取得（Join）</v>
@@ -7410,7 +7440,7 @@
     </row>
     <row r="36" spans="1:14" ht="88.2">
       <c r="A36" s="11"/>
-      <c r="B36" s="112" t="str">
+      <c r="B36" s="124" t="str">
         <f>master!B17</f>
         <v>Java言語、Springフレームワークとは</v>
       </c>
@@ -7440,7 +7470,7 @@
     </row>
     <row r="37" spans="1:14" ht="75.599999999999994">
       <c r="A37" s="11"/>
-      <c r="B37" s="113"/>
+      <c r="B37" s="125"/>
       <c r="C37" s="48" t="str">
         <f>master!C18</f>
         <v>Java</v>
@@ -7467,7 +7497,7 @@
     </row>
     <row r="38" spans="1:14" ht="75.599999999999994">
       <c r="A38" s="11"/>
-      <c r="B38" s="113"/>
+      <c r="B38" s="125"/>
       <c r="C38" s="48" t="str">
         <f>master!C19</f>
         <v>Java言語の構成要素</v>
@@ -7494,7 +7524,7 @@
     </row>
     <row r="39" spans="1:14" ht="50.4">
       <c r="A39" s="11"/>
-      <c r="B39" s="113"/>
+      <c r="B39" s="125"/>
       <c r="C39" s="48" t="str">
         <f>master!C20</f>
         <v>Webアプリケーションを構成するクラス</v>
@@ -7521,7 +7551,7 @@
     </row>
     <row r="40" spans="1:14" ht="88.2">
       <c r="A40" s="11"/>
-      <c r="B40" s="113"/>
+      <c r="B40" s="125"/>
       <c r="C40" s="48" t="str">
         <f>master!C21</f>
         <v>Nレイヤーアーキテクチャ</v>
@@ -7550,7 +7580,7 @@
     </row>
     <row r="41" spans="1:14" ht="201.6">
       <c r="A41" s="11"/>
-      <c r="B41" s="113"/>
+      <c r="B41" s="125"/>
       <c r="C41" s="48" t="str">
         <f>master!C22</f>
         <v>View と Controller と Service と Repository</v>
@@ -7577,7 +7607,7 @@
     </row>
     <row r="42" spans="1:14" ht="37.799999999999997">
       <c r="A42" s="11"/>
-      <c r="B42" s="113"/>
+      <c r="B42" s="125"/>
       <c r="C42" s="48" t="str">
         <f>master!C23</f>
         <v>Nレイヤーアーキテクチャ</v>
@@ -7604,7 +7634,7 @@
     </row>
     <row r="43" spans="1:14" ht="163.80000000000001">
       <c r="A43" s="11"/>
-      <c r="B43" s="113"/>
+      <c r="B43" s="125"/>
       <c r="C43" s="48" t="str">
         <f>master!C24</f>
         <v>Webアプリケーション フレームワーク</v>
@@ -7631,7 +7661,7 @@
     </row>
     <row r="44" spans="1:14" ht="25.2">
       <c r="A44" s="11"/>
-      <c r="B44" s="113"/>
+      <c r="B44" s="125"/>
       <c r="C44" s="48" t="str">
         <f>master!C25</f>
         <v>Java向けWebアプリケーションフレームワーク</v>
@@ -7658,7 +7688,7 @@
     </row>
     <row r="45" spans="1:14" ht="189">
       <c r="A45" s="11"/>
-      <c r="B45" s="113"/>
+      <c r="B45" s="125"/>
       <c r="C45" s="48" t="str">
         <f>master!C26</f>
         <v>Springフレームワーク</v>
@@ -7685,7 +7715,7 @@
     </row>
     <row r="46" spans="1:14" ht="88.2">
       <c r="A46" s="11"/>
-      <c r="B46" s="113"/>
+      <c r="B46" s="125"/>
       <c r="C46" s="48" t="str">
         <f>master!C27</f>
         <v>Springフレームワーク：DIコンテナとは</v>
@@ -7714,7 +7744,7 @@
     </row>
     <row r="47" spans="1:14" ht="63">
       <c r="A47" s="11"/>
-      <c r="B47" s="113"/>
+      <c r="B47" s="125"/>
       <c r="C47" s="48" t="str">
         <f>master!C28</f>
         <v>DIコンテナ：DIコンテナが部品を注入する</v>
@@ -7741,7 +7771,7 @@
     </row>
     <row r="48" spans="1:14" ht="100.8">
       <c r="A48" s="11"/>
-      <c r="B48" s="113"/>
+      <c r="B48" s="125"/>
       <c r="C48" s="48" t="str">
         <f>master!C29</f>
         <v>DIコンテナ：DIコンテナによる部品と注入対象になるための目印</v>
@@ -7768,7 +7798,7 @@
     </row>
     <row r="49" spans="1:14" ht="100.8">
       <c r="A49" s="11"/>
-      <c r="B49" s="113"/>
+      <c r="B49" s="125"/>
       <c r="C49" s="48" t="str">
         <f>master!C30</f>
         <v>Springフレームワークにおける部品の設定</v>
@@ -7795,7 +7825,7 @@
     </row>
     <row r="50" spans="1:14" ht="88.2">
       <c r="A50" s="11"/>
-      <c r="B50" s="113"/>
+      <c r="B50" s="125"/>
       <c r="C50" s="48" t="str">
         <f>master!C31</f>
         <v>Spring Boot</v>
@@ -7822,7 +7852,7 @@
     </row>
     <row r="51" spans="1:14" ht="63">
       <c r="A51" s="11"/>
-      <c r="B51" s="113"/>
+      <c r="B51" s="125"/>
       <c r="C51" s="48" t="str">
         <f>master!C32</f>
         <v>Spring Boot：オートコンフィグレーション</v>
@@ -7849,7 +7879,7 @@
     </row>
     <row r="52" spans="1:14" ht="50.4">
       <c r="A52" s="11"/>
-      <c r="B52" s="113"/>
+      <c r="B52" s="125"/>
       <c r="C52" s="48" t="str">
         <f>master!C33</f>
         <v>Spring Boot：Starters</v>
@@ -7876,7 +7906,7 @@
     </row>
     <row r="53" spans="1:14" ht="88.2">
       <c r="A53" s="11"/>
-      <c r="B53" s="113"/>
+      <c r="B53" s="125"/>
       <c r="C53" s="48" t="str">
         <f>master!C34</f>
         <v>Spring Boot：組込みWebAPサーバ</v>
@@ -7903,7 +7933,7 @@
     </row>
     <row r="54" spans="1:14" ht="25.2">
       <c r="A54" s="11"/>
-      <c r="B54" s="114"/>
+      <c r="B54" s="126"/>
       <c r="C54" s="48" t="str">
         <f>master!C35</f>
         <v>おすすめ書籍：『プロになるためのSpring入門』</v>
@@ -7928,7 +7958,7 @@
     </row>
     <row r="55" spans="1:14" ht="37.799999999999997">
       <c r="A55" s="11"/>
-      <c r="B55" s="115" t="str">
+      <c r="B55" s="121" t="str">
         <f>master!B37</f>
         <v>課題1の導入</v>
       </c>
@@ -7936,11 +7966,11 @@
         <f>master!C37</f>
         <v>演習課題の概要</v>
       </c>
-      <c r="D55" s="109" t="s">
+      <c r="D55" s="112" t="s">
         <v>163</v>
       </c>
-      <c r="E55" s="110"/>
-      <c r="F55" s="111"/>
+      <c r="E55" s="113"/>
+      <c r="F55" s="114"/>
       <c r="G55" s="58" t="s">
         <v>283</v>
       </c>
@@ -7958,16 +7988,16 @@
     </row>
     <row r="56" spans="1:14" ht="37.799999999999997">
       <c r="A56" s="11"/>
-      <c r="B56" s="116"/>
+      <c r="B56" s="122"/>
       <c r="C56" s="58" t="str">
         <f>master!C38</f>
         <v>作成物</v>
       </c>
-      <c r="D56" s="109" t="s">
+      <c r="D56" s="112" t="s">
         <v>164</v>
       </c>
-      <c r="E56" s="110"/>
-      <c r="F56" s="111"/>
+      <c r="E56" s="113"/>
+      <c r="F56" s="114"/>
       <c r="G56" s="58" t="s">
         <v>283</v>
       </c>
@@ -7985,16 +8015,16 @@
     </row>
     <row r="57" spans="1:14" ht="75.599999999999994">
       <c r="A57" s="11"/>
-      <c r="B57" s="117"/>
+      <c r="B57" s="123"/>
       <c r="C57" s="58" t="str">
         <f>master!C39</f>
         <v>演習課題の進め方</v>
       </c>
-      <c r="D57" s="109" t="s">
+      <c r="D57" s="112" t="s">
         <v>165</v>
       </c>
-      <c r="E57" s="110"/>
-      <c r="F57" s="111"/>
+      <c r="E57" s="113"/>
+      <c r="F57" s="114"/>
       <c r="G57" s="58" t="s">
         <v>284</v>
       </c>
@@ -8012,7 +8042,7 @@
     </row>
     <row r="58" spans="1:14" ht="15" customHeight="1">
       <c r="A58" s="11"/>
-      <c r="B58" s="115" t="str">
+      <c r="B58" s="121" t="str">
         <f>master!B40</f>
         <v>Spring Bootプロジェクトの_x000B_準備、起動確認</v>
       </c>
@@ -8020,9 +8050,9 @@
         <f>master!C40</f>
         <v>前提条件</v>
       </c>
-      <c r="D58" s="109"/>
-      <c r="E58" s="110"/>
-      <c r="F58" s="111"/>
+      <c r="D58" s="112"/>
+      <c r="E58" s="113"/>
+      <c r="F58" s="114"/>
       <c r="G58" s="58" t="s">
         <v>285</v>
       </c>
@@ -8040,16 +8070,16 @@
     </row>
     <row r="59" spans="1:14" ht="37.799999999999997">
       <c r="A59" s="11"/>
-      <c r="B59" s="116"/>
+      <c r="B59" s="122"/>
       <c r="C59" s="58" t="str">
         <f>master!C41</f>
         <v>Spring Bootプロジェクトの準備</v>
       </c>
-      <c r="D59" s="109" t="s">
+      <c r="D59" s="112" t="s">
         <v>166</v>
       </c>
-      <c r="E59" s="110"/>
-      <c r="F59" s="111"/>
+      <c r="E59" s="113"/>
+      <c r="F59" s="114"/>
       <c r="G59" s="58" t="s">
         <v>283</v>
       </c>
@@ -8067,16 +8097,16 @@
     </row>
     <row r="60" spans="1:14" ht="25.2">
       <c r="A60" s="11"/>
-      <c r="B60" s="116"/>
+      <c r="B60" s="122"/>
       <c r="C60" s="58" t="str">
         <f>master!C42</f>
         <v>（補足）Spring Bootプロジェクトの準備</v>
       </c>
-      <c r="D60" s="109" t="s">
+      <c r="D60" s="112" t="s">
         <v>167</v>
       </c>
-      <c r="E60" s="110"/>
-      <c r="F60" s="111"/>
+      <c r="E60" s="113"/>
+      <c r="F60" s="114"/>
       <c r="G60" s="58" t="s">
         <v>286</v>
       </c>
@@ -8094,16 +8124,16 @@
     </row>
     <row r="61" spans="1:14" ht="88.2">
       <c r="A61" s="11"/>
-      <c r="B61" s="117"/>
+      <c r="B61" s="123"/>
       <c r="C61" s="58" t="str">
         <f>master!C43</f>
         <v>Spring Bootアプリケーションの起動確認</v>
       </c>
-      <c r="D61" s="109" t="s">
+      <c r="D61" s="112" t="s">
         <v>189</v>
       </c>
-      <c r="E61" s="110"/>
-      <c r="F61" s="111"/>
+      <c r="E61" s="113"/>
+      <c r="F61" s="114"/>
       <c r="G61" s="58" t="s">
         <v>287</v>
       </c>
@@ -8119,9 +8149,9 @@
       <c r="M61" s="6"/>
       <c r="N61" s="6"/>
     </row>
-    <row r="62" spans="1:14" ht="190.2" customHeight="1">
+    <row r="62" spans="1:14" ht="50.4">
       <c r="A62" s="11"/>
-      <c r="B62" s="115" t="str">
+      <c r="B62" s="121" t="str">
         <f>master!B44</f>
         <v>ECサイト Webアプリの要件</v>
       </c>
@@ -8129,11 +8159,11 @@
         <f>master!C44</f>
         <v>ECサイト Webアプリの要件 – はじめに</v>
       </c>
-      <c r="D62" s="109" t="s">
+      <c r="D62" s="112" t="s">
         <v>168</v>
       </c>
-      <c r="E62" s="110"/>
-      <c r="F62" s="111"/>
+      <c r="E62" s="113"/>
+      <c r="F62" s="114"/>
       <c r="G62" s="58" t="s">
         <v>288</v>
       </c>
@@ -8151,16 +8181,16 @@
     </row>
     <row r="63" spans="1:14" ht="151.19999999999999">
       <c r="A63" s="11"/>
-      <c r="B63" s="116"/>
+      <c r="B63" s="122"/>
       <c r="C63" s="58" t="str">
         <f>master!C45</f>
         <v>ECサイト Webアプリの要件➊ 画面</v>
       </c>
-      <c r="D63" s="109" t="s">
+      <c r="D63" s="112" t="s">
         <v>170</v>
       </c>
-      <c r="E63" s="110"/>
-      <c r="F63" s="111"/>
+      <c r="E63" s="113"/>
+      <c r="F63" s="114"/>
       <c r="G63" s="58" t="s">
         <v>289</v>
       </c>
@@ -8178,16 +8208,16 @@
     </row>
     <row r="64" spans="1:14" ht="214.2">
       <c r="A64" s="11"/>
-      <c r="B64" s="116"/>
+      <c r="B64" s="122"/>
       <c r="C64" s="58" t="str">
         <f>master!C46</f>
         <v>ECサイト Webアプリの要件➋ 機能</v>
       </c>
-      <c r="D64" s="109" t="s">
+      <c r="D64" s="112" t="s">
         <v>171</v>
       </c>
-      <c r="E64" s="110"/>
-      <c r="F64" s="111"/>
+      <c r="E64" s="113"/>
+      <c r="F64" s="114"/>
       <c r="G64" s="58" t="s">
         <v>290</v>
       </c>
@@ -8205,16 +8235,16 @@
     </row>
     <row r="65" spans="1:14" ht="63">
       <c r="A65" s="11"/>
-      <c r="B65" s="116"/>
+      <c r="B65" s="122"/>
       <c r="C65" s="58" t="str">
         <f>master!C47</f>
         <v>ECサイト Webアプリの要件➌ 画面遷移</v>
       </c>
-      <c r="D65" s="109" t="s">
+      <c r="D65" s="112" t="s">
         <v>172</v>
       </c>
-      <c r="E65" s="110"/>
-      <c r="F65" s="111"/>
+      <c r="E65" s="113"/>
+      <c r="F65" s="114"/>
       <c r="G65" s="58" t="s">
         <v>291</v>
       </c>
@@ -8232,16 +8262,16 @@
     </row>
     <row r="66" spans="1:14" ht="163.80000000000001">
       <c r="A66" s="11"/>
-      <c r="B66" s="116"/>
+      <c r="B66" s="122"/>
       <c r="C66" s="58" t="str">
         <f>master!C48</f>
         <v>ECサイト Webアプリの要件❹ データ設計</v>
       </c>
-      <c r="D66" s="109" t="s">
+      <c r="D66" s="112" t="s">
         <v>174</v>
       </c>
-      <c r="E66" s="110"/>
-      <c r="F66" s="111"/>
+      <c r="E66" s="113"/>
+      <c r="F66" s="114"/>
       <c r="G66" s="58" t="s">
         <v>292</v>
       </c>
@@ -8259,16 +8289,16 @@
     </row>
     <row r="67" spans="1:14" ht="50.4">
       <c r="A67" s="11"/>
-      <c r="B67" s="116"/>
+      <c r="B67" s="122"/>
       <c r="C67" s="58" t="str">
         <f>master!C49</f>
         <v>ECサイト Webアプリの要件❺ 初期データ</v>
       </c>
-      <c r="D67" s="109" t="s">
+      <c r="D67" s="112" t="s">
         <v>175</v>
       </c>
-      <c r="E67" s="110"/>
-      <c r="F67" s="111"/>
+      <c r="E67" s="113"/>
+      <c r="F67" s="114"/>
       <c r="G67" s="58" t="s">
         <v>288</v>
       </c>
@@ -8286,16 +8316,16 @@
     </row>
     <row r="68" spans="1:14" ht="37.799999999999997">
       <c r="A68" s="11"/>
-      <c r="B68" s="116"/>
+      <c r="B68" s="122"/>
       <c r="C68" s="58" t="str">
         <f>master!C50</f>
         <v>ECサイト Webアプリの要件❻ ディレクトリ構成</v>
       </c>
-      <c r="D68" s="109" t="s">
+      <c r="D68" s="112" t="s">
         <v>176</v>
       </c>
-      <c r="E68" s="110"/>
-      <c r="F68" s="111"/>
+      <c r="E68" s="113"/>
+      <c r="F68" s="114"/>
       <c r="G68" s="58" t="s">
         <v>283</v>
       </c>
@@ -8313,16 +8343,16 @@
     </row>
     <row r="69" spans="1:14" ht="37.799999999999997">
       <c r="A69" s="11"/>
-      <c r="B69" s="116"/>
+      <c r="B69" s="122"/>
       <c r="C69" s="58" t="str">
         <f>master!C51</f>
         <v>ECサイト Webアプリの要件❼ パッケージ構成</v>
       </c>
-      <c r="D69" s="109" t="s">
+      <c r="D69" s="112" t="s">
         <v>178</v>
       </c>
-      <c r="E69" s="110"/>
-      <c r="F69" s="111"/>
+      <c r="E69" s="113"/>
+      <c r="F69" s="114"/>
       <c r="G69" s="58" t="s">
         <v>283</v>
       </c>
@@ -8340,16 +8370,16 @@
     </row>
     <row r="70" spans="1:14" ht="37.799999999999997">
       <c r="A70" s="11"/>
-      <c r="B70" s="117"/>
+      <c r="B70" s="123"/>
       <c r="C70" s="58" t="str">
         <f>master!C52</f>
         <v>ECサイト Webアプリの要件❽ リソース構成</v>
       </c>
-      <c r="D70" s="109" t="s">
+      <c r="D70" s="112" t="s">
         <v>177</v>
       </c>
-      <c r="E70" s="110"/>
-      <c r="F70" s="111"/>
+      <c r="E70" s="113"/>
+      <c r="F70" s="114"/>
       <c r="G70" s="58" t="s">
         <v>283</v>
       </c>
@@ -8367,7 +8397,7 @@
     </row>
     <row r="71" spans="1:14" ht="25.2">
       <c r="A71" s="11"/>
-      <c r="B71" s="115" t="str">
+      <c r="B71" s="121" t="str">
         <f>master!B53</f>
         <v>ハンズオン</v>
       </c>
@@ -8375,11 +8405,11 @@
         <f>master!C53</f>
         <v>バイブコーディング – はじめに</v>
       </c>
-      <c r="D71" s="109" t="s">
+      <c r="D71" s="112" t="s">
         <v>179</v>
       </c>
-      <c r="E71" s="110"/>
-      <c r="F71" s="111"/>
+      <c r="E71" s="113"/>
+      <c r="F71" s="114"/>
       <c r="G71" s="58" t="s">
         <v>286</v>
       </c>
@@ -8397,16 +8427,16 @@
     </row>
     <row r="72" spans="1:14" ht="138.6">
       <c r="A72" s="11"/>
-      <c r="B72" s="116"/>
+      <c r="B72" s="122"/>
       <c r="C72" s="58" t="str">
         <f>master!C54</f>
         <v>[構造理解] Webアプリケーションで必要なもの</v>
       </c>
-      <c r="D72" s="109" t="s">
+      <c r="D72" s="112" t="s">
         <v>180</v>
       </c>
-      <c r="E72" s="110"/>
-      <c r="F72" s="111"/>
+      <c r="E72" s="113"/>
+      <c r="F72" s="114"/>
       <c r="G72" s="58" t="s">
         <v>293</v>
       </c>
@@ -8424,16 +8454,16 @@
     </row>
     <row r="73" spans="1:14" ht="50.4">
       <c r="A73" s="11"/>
-      <c r="B73" s="116"/>
+      <c r="B73" s="122"/>
       <c r="C73" s="76" t="str">
         <f>master!C55</f>
         <v>バイブコーディング➊ 画面モックアップを作ってデザインを決める</v>
       </c>
-      <c r="D73" s="109" t="s">
+      <c r="D73" s="112" t="s">
         <v>190</v>
       </c>
-      <c r="E73" s="110"/>
-      <c r="F73" s="111"/>
+      <c r="E73" s="113"/>
+      <c r="F73" s="114"/>
       <c r="G73" s="58" t="s">
         <v>288</v>
       </c>
@@ -8442,7 +8472,7 @@
         <v>24</v>
       </c>
       <c r="J73" s="61">
-        <v>1.3888888888888888E-2</v>
+        <v>1.3888888888888889E-3</v>
       </c>
       <c r="K73" s="62"/>
       <c r="L73" s="6"/>
@@ -8451,36 +8481,38 @@
     </row>
     <row r="74" spans="1:14" ht="88.2" customHeight="1">
       <c r="A74" s="11"/>
-      <c r="B74" s="116"/>
+      <c r="B74" s="122"/>
       <c r="C74" s="77"/>
-      <c r="D74" s="109" t="s">
+      <c r="D74" s="131" t="s">
         <v>181</v>
       </c>
-      <c r="E74" s="110"/>
-      <c r="F74" s="111"/>
-      <c r="G74" s="58" t="s">
+      <c r="E74" s="132"/>
+      <c r="F74" s="133"/>
+      <c r="G74" s="130" t="s">
         <v>287</v>
       </c>
-      <c r="H74" s="59"/>
-      <c r="I74" s="60"/>
-      <c r="J74" s="61"/>
-      <c r="K74" s="62"/>
+      <c r="H74" s="134"/>
+      <c r="I74" s="135"/>
+      <c r="J74" s="136">
+        <v>3.472222222222222E-3</v>
+      </c>
+      <c r="K74" s="137"/>
       <c r="L74" s="6"/>
       <c r="M74" s="6"/>
       <c r="N74" s="6"/>
     </row>
     <row r="75" spans="1:14" ht="50.4">
       <c r="A75" s="11"/>
-      <c r="B75" s="116"/>
+      <c r="B75" s="122"/>
       <c r="C75" s="76" t="str">
         <f>master!C56</f>
         <v>バイブコーディング➋ データベースのテーブルを準備する</v>
       </c>
-      <c r="D75" s="109" t="s">
+      <c r="D75" s="112" t="s">
         <v>194</v>
       </c>
-      <c r="E75" s="110"/>
-      <c r="F75" s="111"/>
+      <c r="E75" s="113"/>
+      <c r="F75" s="114"/>
       <c r="G75" s="58" t="s">
         <v>288</v>
       </c>
@@ -8498,36 +8530,38 @@
     </row>
     <row r="76" spans="1:14" ht="88.2">
       <c r="A76" s="11"/>
-      <c r="B76" s="116"/>
+      <c r="B76" s="122"/>
       <c r="C76" s="77"/>
-      <c r="D76" s="109" t="s">
+      <c r="D76" s="131" t="s">
         <v>181</v>
       </c>
-      <c r="E76" s="110"/>
-      <c r="F76" s="111"/>
-      <c r="G76" s="58" t="s">
+      <c r="E76" s="132"/>
+      <c r="F76" s="133"/>
+      <c r="G76" s="130" t="s">
         <v>287</v>
       </c>
-      <c r="H76" s="59"/>
-      <c r="I76" s="60"/>
-      <c r="J76" s="61"/>
-      <c r="K76" s="62"/>
+      <c r="H76" s="134"/>
+      <c r="I76" s="135"/>
+      <c r="J76" s="136">
+        <v>3.472222222222222E-3</v>
+      </c>
+      <c r="K76" s="137"/>
       <c r="L76" s="6"/>
       <c r="M76" s="6"/>
       <c r="N76" s="6"/>
     </row>
     <row r="77" spans="1:14" ht="50.4">
       <c r="A77" s="11"/>
-      <c r="B77" s="116"/>
+      <c r="B77" s="122"/>
       <c r="C77" s="76" t="str">
         <f>master!C57</f>
         <v>バイブコーディング➌ データベースのデータを準備する</v>
       </c>
-      <c r="D77" s="109" t="s">
+      <c r="D77" s="112" t="s">
         <v>193</v>
       </c>
-      <c r="E77" s="110"/>
-      <c r="F77" s="111"/>
+      <c r="E77" s="113"/>
+      <c r="F77" s="114"/>
       <c r="G77" s="58" t="s">
         <v>288</v>
       </c>
@@ -8545,36 +8579,38 @@
     </row>
     <row r="78" spans="1:14" ht="88.2">
       <c r="A78" s="11"/>
-      <c r="B78" s="116"/>
+      <c r="B78" s="122"/>
       <c r="C78" s="77"/>
-      <c r="D78" s="109" t="s">
+      <c r="D78" s="131" t="s">
         <v>181</v>
       </c>
-      <c r="E78" s="110"/>
-      <c r="F78" s="111"/>
-      <c r="G78" s="58" t="s">
+      <c r="E78" s="132"/>
+      <c r="F78" s="133"/>
+      <c r="G78" s="130" t="s">
         <v>287</v>
       </c>
-      <c r="H78" s="59"/>
-      <c r="I78" s="60"/>
-      <c r="J78" s="61"/>
-      <c r="K78" s="62"/>
+      <c r="H78" s="134"/>
+      <c r="I78" s="135"/>
+      <c r="J78" s="136">
+        <v>3.472222222222222E-3</v>
+      </c>
+      <c r="K78" s="137"/>
       <c r="L78" s="6"/>
       <c r="M78" s="6"/>
       <c r="N78" s="6"/>
     </row>
     <row r="79" spans="1:14" ht="63">
       <c r="A79" s="11"/>
-      <c r="B79" s="116"/>
+      <c r="B79" s="122"/>
       <c r="C79" s="76" t="str">
         <f>master!C58</f>
         <v>バイブコーディング❹ データベース処理とビジネスロジックを作る</v>
       </c>
-      <c r="D79" s="109" t="s">
+      <c r="D79" s="112" t="s">
         <v>192</v>
       </c>
-      <c r="E79" s="110"/>
-      <c r="F79" s="111"/>
+      <c r="E79" s="113"/>
+      <c r="F79" s="114"/>
       <c r="G79" s="58" t="s">
         <v>291</v>
       </c>
@@ -8583,7 +8619,7 @@
         <v>24</v>
       </c>
       <c r="J79" s="61">
-        <v>3.472222222222222E-3</v>
+        <v>1.3888888888888889E-3</v>
       </c>
       <c r="K79" s="62"/>
       <c r="L79" s="6"/>
@@ -8592,36 +8628,38 @@
     </row>
     <row r="80" spans="1:14" ht="88.2">
       <c r="A80" s="11"/>
-      <c r="B80" s="116"/>
+      <c r="B80" s="122"/>
       <c r="C80" s="77"/>
-      <c r="D80" s="109" t="s">
+      <c r="D80" s="131" t="s">
         <v>181</v>
       </c>
-      <c r="E80" s="110"/>
-      <c r="F80" s="111"/>
-      <c r="G80" s="58" t="s">
+      <c r="E80" s="132"/>
+      <c r="F80" s="133"/>
+      <c r="G80" s="130" t="s">
         <v>287</v>
       </c>
-      <c r="H80" s="59"/>
-      <c r="I80" s="60"/>
-      <c r="J80" s="61"/>
-      <c r="K80" s="62"/>
+      <c r="H80" s="134"/>
+      <c r="I80" s="135"/>
+      <c r="J80" s="136">
+        <v>3.472222222222222E-3</v>
+      </c>
+      <c r="K80" s="137"/>
       <c r="L80" s="6"/>
       <c r="M80" s="6"/>
       <c r="N80" s="6"/>
     </row>
     <row r="81" spans="1:14" ht="50.4">
       <c r="A81" s="11"/>
-      <c r="B81" s="116"/>
+      <c r="B81" s="122"/>
       <c r="C81" s="58" t="str">
         <f>master!C59</f>
         <v>[解説] RepositoryクラスとSQLの例（抜粋）</v>
       </c>
-      <c r="D81" s="109" t="s">
+      <c r="D81" s="112" t="s">
         <v>182</v>
       </c>
-      <c r="E81" s="110"/>
-      <c r="F81" s="111"/>
+      <c r="E81" s="113"/>
+      <c r="F81" s="114"/>
       <c r="G81" s="58" t="s">
         <v>288</v>
       </c>
@@ -8639,16 +8677,16 @@
     </row>
     <row r="82" spans="1:14" ht="50.4">
       <c r="A82" s="11"/>
-      <c r="B82" s="116"/>
+      <c r="B82" s="122"/>
       <c r="C82" s="58" t="str">
         <f>master!C60</f>
         <v>[解説] Entity/Modelクラスの例（抜粋）</v>
       </c>
-      <c r="D82" s="109" t="s">
+      <c r="D82" s="112" t="s">
         <v>183</v>
       </c>
-      <c r="E82" s="110"/>
-      <c r="F82" s="111"/>
+      <c r="E82" s="113"/>
+      <c r="F82" s="114"/>
       <c r="G82" s="58" t="s">
         <v>288</v>
       </c>
@@ -8666,16 +8704,16 @@
     </row>
     <row r="83" spans="1:14" ht="37.799999999999997">
       <c r="A83" s="11"/>
-      <c r="B83" s="116"/>
+      <c r="B83" s="122"/>
       <c r="C83" s="58" t="str">
         <f>master!C61</f>
         <v>[解説] Serviceクラスの例（抜粋）</v>
       </c>
-      <c r="D83" s="109" t="s">
+      <c r="D83" s="112" t="s">
         <v>184</v>
       </c>
-      <c r="E83" s="110"/>
-      <c r="F83" s="111"/>
+      <c r="E83" s="113"/>
+      <c r="F83" s="114"/>
       <c r="G83" s="58" t="s">
         <v>283</v>
       </c>
@@ -8693,16 +8731,16 @@
     </row>
     <row r="84" spans="1:14" ht="50.4">
       <c r="A84" s="11"/>
-      <c r="B84" s="116"/>
+      <c r="B84" s="122"/>
       <c r="C84" s="76" t="str">
         <f>master!C62</f>
         <v>バイブコーディング❺ モックアップをもとに画面表示/処理を作る</v>
       </c>
-      <c r="D84" s="109" t="s">
+      <c r="D84" s="112" t="s">
         <v>191</v>
       </c>
-      <c r="E84" s="110"/>
-      <c r="F84" s="111"/>
+      <c r="E84" s="113"/>
+      <c r="F84" s="114"/>
       <c r="G84" s="58" t="s">
         <v>288</v>
       </c>
@@ -8711,7 +8749,7 @@
         <v>24</v>
       </c>
       <c r="J84" s="61">
-        <v>6.9444444444444441E-3</v>
+        <v>1.3888888888888889E-3</v>
       </c>
       <c r="K84" s="62"/>
       <c r="L84" s="6"/>
@@ -8720,36 +8758,38 @@
     </row>
     <row r="85" spans="1:14" ht="88.2">
       <c r="A85" s="11"/>
-      <c r="B85" s="116"/>
+      <c r="B85" s="122"/>
       <c r="C85" s="77"/>
-      <c r="D85" s="109" t="s">
+      <c r="D85" s="131" t="s">
         <v>181</v>
       </c>
-      <c r="E85" s="110"/>
-      <c r="F85" s="111"/>
-      <c r="G85" s="58" t="s">
+      <c r="E85" s="132"/>
+      <c r="F85" s="133"/>
+      <c r="G85" s="130" t="s">
         <v>287</v>
       </c>
-      <c r="H85" s="59"/>
-      <c r="I85" s="60"/>
-      <c r="J85" s="61"/>
-      <c r="K85" s="62"/>
+      <c r="H85" s="134"/>
+      <c r="I85" s="135"/>
+      <c r="J85" s="136">
+        <v>3.472222222222222E-3</v>
+      </c>
+      <c r="K85" s="137"/>
       <c r="L85" s="6"/>
       <c r="M85" s="6"/>
       <c r="N85" s="6"/>
     </row>
     <row r="86" spans="1:14" ht="37.799999999999997">
       <c r="A86" s="11"/>
-      <c r="B86" s="116"/>
+      <c r="B86" s="122"/>
       <c r="C86" s="58" t="str">
         <f>master!C63</f>
         <v>[解説] Controllerクラスの例（抜粋）</v>
       </c>
-      <c r="D86" s="109" t="s">
+      <c r="D86" s="112" t="s">
         <v>185</v>
       </c>
-      <c r="E86" s="110"/>
-      <c r="F86" s="111"/>
+      <c r="E86" s="113"/>
+      <c r="F86" s="114"/>
       <c r="G86" s="58" t="s">
         <v>283</v>
       </c>
@@ -8767,16 +8807,16 @@
     </row>
     <row r="87" spans="1:14" ht="37.799999999999997">
       <c r="A87" s="11"/>
-      <c r="B87" s="116"/>
+      <c r="B87" s="122"/>
       <c r="C87" s="58" t="str">
         <f>master!C64</f>
         <v>[解説] Thymeleafテンプレートの例（抜粋）</v>
       </c>
-      <c r="D87" s="109" t="s">
+      <c r="D87" s="112" t="s">
         <v>186</v>
       </c>
-      <c r="E87" s="110"/>
-      <c r="F87" s="111"/>
+      <c r="E87" s="113"/>
+      <c r="F87" s="114"/>
       <c r="G87" s="58" t="s">
         <v>283</v>
       </c>
@@ -8794,16 +8834,16 @@
     </row>
     <row r="88" spans="1:14" ht="37.799999999999997">
       <c r="A88" s="11"/>
-      <c r="B88" s="116"/>
+      <c r="B88" s="122"/>
       <c r="C88" s="58" t="str">
         <f>master!C65</f>
         <v>[解説] Formクラスの例（抜粋）</v>
       </c>
-      <c r="D88" s="109" t="s">
+      <c r="D88" s="112" t="s">
         <v>187</v>
       </c>
-      <c r="E88" s="110"/>
-      <c r="F88" s="111"/>
+      <c r="E88" s="113"/>
+      <c r="F88" s="114"/>
       <c r="G88" s="58" t="s">
         <v>283</v>
       </c>
@@ -8821,16 +8861,16 @@
     </row>
     <row r="89" spans="1:14" ht="75.599999999999994">
       <c r="A89" s="11"/>
-      <c r="B89" s="116"/>
+      <c r="B89" s="122"/>
       <c r="C89" s="76" t="str">
         <f>master!C66</f>
         <v>バイブコーディング❻ 動作を確認する</v>
       </c>
-      <c r="D89" s="109" t="s">
+      <c r="D89" s="112" t="s">
         <v>188</v>
       </c>
-      <c r="E89" s="110"/>
-      <c r="F89" s="111"/>
+      <c r="E89" s="113"/>
+      <c r="F89" s="114"/>
       <c r="G89" s="58" t="s">
         <v>284</v>
       </c>
@@ -8848,31 +8888,31 @@
     </row>
     <row r="90" spans="1:14" ht="63">
       <c r="A90" s="11"/>
-      <c r="B90" s="117"/>
+      <c r="B90" s="123"/>
       <c r="C90" s="77"/>
-      <c r="D90" s="109" t="s">
+      <c r="D90" s="131" t="s">
         <v>195</v>
       </c>
-      <c r="E90" s="110"/>
-      <c r="F90" s="111"/>
-      <c r="G90" s="58" t="s">
+      <c r="E90" s="132"/>
+      <c r="F90" s="133"/>
+      <c r="G90" s="130" t="s">
         <v>291</v>
       </c>
-      <c r="H90" s="59"/>
-      <c r="I90" s="60" t="s">
-        <v>24</v>
-      </c>
-      <c r="J90" s="61">
-        <v>6.9444444444444441E-3</v>
-      </c>
-      <c r="K90" s="62"/>
+      <c r="H90" s="134"/>
+      <c r="I90" s="135" t="s">
+        <v>24</v>
+      </c>
+      <c r="J90" s="136">
+        <v>1.0416666666666666E-2</v>
+      </c>
+      <c r="K90" s="137"/>
       <c r="L90" s="6"/>
       <c r="M90" s="6"/>
       <c r="N90" s="6"/>
     </row>
     <row r="91" spans="1:14" ht="50.4">
       <c r="A91" s="11"/>
-      <c r="B91" s="112" t="str">
+      <c r="B91" s="124" t="str">
         <f>master!B69</f>
         <v>Gitとは</v>
       </c>
@@ -8902,7 +8942,7 @@
     </row>
     <row r="92" spans="1:14" ht="37.799999999999997">
       <c r="A92" s="11"/>
-      <c r="B92" s="113"/>
+      <c r="B92" s="125"/>
       <c r="C92" s="48" t="str">
         <f>master!C70</f>
         <v>バージョン管理とは</v>
@@ -8929,7 +8969,7 @@
     </row>
     <row r="93" spans="1:14" ht="151.19999999999999">
       <c r="A93" s="11"/>
-      <c r="B93" s="114"/>
+      <c r="B93" s="126"/>
       <c r="C93" s="48" t="str">
         <f>master!C71</f>
         <v>Gitの概要</v>
@@ -8956,7 +8996,7 @@
     </row>
     <row r="94" spans="1:14" ht="75.599999999999994">
       <c r="A94" s="11"/>
-      <c r="B94" s="112" t="str">
+      <c r="B94" s="124" t="str">
         <f>master!B72</f>
         <v>Gitの基本構成</v>
       </c>
@@ -8986,7 +9026,7 @@
     </row>
     <row r="95" spans="1:14" ht="37.799999999999997">
       <c r="A95" s="11"/>
-      <c r="B95" s="113"/>
+      <c r="B95" s="125"/>
       <c r="C95" s="48" t="str">
         <f>master!C73</f>
         <v>ワーキングツリー</v>
@@ -9013,7 +9053,7 @@
     </row>
     <row r="96" spans="1:14" ht="37.799999999999997">
       <c r="A96" s="11"/>
-      <c r="B96" s="113"/>
+      <c r="B96" s="125"/>
       <c r="C96" s="48" t="str">
         <f>master!C74</f>
         <v>ステージングエリア</v>
@@ -9040,7 +9080,7 @@
     </row>
     <row r="97" spans="1:14" ht="37.799999999999997">
       <c r="A97" s="11"/>
-      <c r="B97" s="113"/>
+      <c r="B97" s="125"/>
       <c r="C97" s="48" t="str">
         <f>master!C75</f>
         <v>ローカルリポジトリ</v>
@@ -9067,7 +9107,7 @@
     </row>
     <row r="98" spans="1:14" ht="50.4">
       <c r="A98" s="11"/>
-      <c r="B98" s="114"/>
+      <c r="B98" s="126"/>
       <c r="C98" s="48" t="str">
         <f>master!C76</f>
         <v>リモートリポジトリ</v>
@@ -9094,7 +9134,7 @@
     </row>
     <row r="99" spans="1:14" ht="88.2">
       <c r="A99" s="11"/>
-      <c r="B99" s="112" t="str">
+      <c r="B99" s="124" t="str">
         <f>master!B77</f>
         <v>ローカルリポジトリの操作</v>
       </c>
@@ -9124,7 +9164,7 @@
     </row>
     <row r="100" spans="1:14" ht="37.799999999999997">
       <c r="A100" s="11"/>
-      <c r="B100" s="113"/>
+      <c r="B100" s="125"/>
       <c r="C100" s="48" t="str">
         <f>master!C78</f>
         <v>リポジトリの作成</v>
@@ -9151,7 +9191,7 @@
     </row>
     <row r="101" spans="1:14" ht="37.799999999999997" customHeight="1">
       <c r="A101" s="11"/>
-      <c r="B101" s="113"/>
+      <c r="B101" s="125"/>
       <c r="C101" s="48" t="str">
         <f>master!C79</f>
         <v>ファイルの変更</v>
@@ -9178,7 +9218,7 @@
     </row>
     <row r="102" spans="1:14" ht="37.799999999999997">
       <c r="A102" s="11"/>
-      <c r="B102" s="113"/>
+      <c r="B102" s="125"/>
       <c r="C102" s="48" t="str">
         <f>master!C80</f>
         <v>変更内容の確認</v>
@@ -9205,7 +9245,7 @@
     </row>
     <row r="103" spans="1:14" ht="37.799999999999997">
       <c r="A103" s="11"/>
-      <c r="B103" s="113"/>
+      <c r="B103" s="125"/>
       <c r="C103" s="48" t="str">
         <f>master!C81</f>
         <v>変更内容のステージ</v>
@@ -9232,7 +9272,7 @@
     </row>
     <row r="104" spans="1:14" ht="37.799999999999997">
       <c r="A104" s="11"/>
-      <c r="B104" s="113"/>
+      <c r="B104" s="125"/>
       <c r="C104" s="48" t="str">
         <f>master!C82</f>
         <v>変更内容のコミット</v>
@@ -9259,7 +9299,7 @@
     </row>
     <row r="105" spans="1:14" ht="37.799999999999997">
       <c r="A105" s="11"/>
-      <c r="B105" s="113"/>
+      <c r="B105" s="125"/>
       <c r="C105" s="48" t="str">
         <f>master!C83</f>
         <v>ワーキングツリーの変更の取り消し</v>
@@ -9286,7 +9326,7 @@
     </row>
     <row r="106" spans="1:14" ht="37.799999999999997">
       <c r="A106" s="11"/>
-      <c r="B106" s="113"/>
+      <c r="B106" s="125"/>
       <c r="C106" s="48" t="str">
         <f>master!C84</f>
         <v>ステージングの取り消し</v>
@@ -9313,7 +9353,7 @@
     </row>
     <row r="107" spans="1:14" ht="37.799999999999997">
       <c r="A107" s="11"/>
-      <c r="B107" s="114"/>
+      <c r="B107" s="126"/>
       <c r="C107" s="48" t="str">
         <f>master!C85</f>
         <v>コミットの打ち消し</v>
@@ -9340,7 +9380,7 @@
     </row>
     <row r="108" spans="1:14" ht="75.599999999999994">
       <c r="A108" s="11"/>
-      <c r="B108" s="112" t="str">
+      <c r="B108" s="124" t="str">
         <f>master!B86</f>
         <v>リモートリポジトリの操作</v>
       </c>
@@ -9372,7 +9412,7 @@
     </row>
     <row r="109" spans="1:14" ht="37.799999999999997">
       <c r="A109" s="11"/>
-      <c r="B109" s="113"/>
+      <c r="B109" s="125"/>
       <c r="C109" s="48" t="str">
         <f>master!C87</f>
         <v>リポジトリの複製</v>
@@ -9401,7 +9441,7 @@
     </row>
     <row r="110" spans="1:14" ht="37.799999999999997">
       <c r="A110" s="11"/>
-      <c r="B110" s="113"/>
+      <c r="B110" s="125"/>
       <c r="C110" s="48" t="str">
         <f>master!C88</f>
         <v>リモートからの取得</v>
@@ -9430,7 +9470,7 @@
     </row>
     <row r="111" spans="1:14" ht="37.799999999999997">
       <c r="A111" s="11"/>
-      <c r="B111" s="113"/>
+      <c r="B111" s="125"/>
       <c r="C111" s="48" t="str">
         <f>master!C89</f>
         <v>リモートからの取得と反映</v>
@@ -9459,7 +9499,7 @@
     </row>
     <row r="112" spans="1:14" ht="37.799999999999997">
       <c r="A112" s="11"/>
-      <c r="B112" s="114"/>
+      <c r="B112" s="126"/>
       <c r="C112" s="48" t="str">
         <f>master!C90</f>
         <v>リモートへの反映</v>
@@ -9488,7 +9528,7 @@
     </row>
     <row r="113" spans="1:14" ht="88.2">
       <c r="A113" s="11"/>
-      <c r="B113" s="112" t="str">
+      <c r="B113" s="124" t="str">
         <f>master!B91</f>
         <v>ブランチの操作</v>
       </c>
@@ -9520,7 +9560,7 @@
     </row>
     <row r="114" spans="1:14" ht="37.799999999999997">
       <c r="A114" s="11"/>
-      <c r="B114" s="113"/>
+      <c r="B114" s="125"/>
       <c r="C114" s="48" t="str">
         <f>master!C92</f>
         <v>ブランチとは</v>
@@ -9547,7 +9587,7 @@
     </row>
     <row r="115" spans="1:14" ht="37.799999999999997">
       <c r="A115" s="11"/>
-      <c r="B115" s="113"/>
+      <c r="B115" s="125"/>
       <c r="C115" s="48" t="str">
         <f>master!C93</f>
         <v>ブランチの作成</v>
@@ -9574,7 +9614,7 @@
     </row>
     <row r="116" spans="1:14" ht="37.799999999999997">
       <c r="A116" s="11"/>
-      <c r="B116" s="113"/>
+      <c r="B116" s="125"/>
       <c r="C116" s="48" t="str">
         <f>master!C94</f>
         <v>ブランチの切り替え</v>
@@ -9601,7 +9641,7 @@
     </row>
     <row r="117" spans="1:14" ht="37.799999999999997">
       <c r="A117" s="11"/>
-      <c r="B117" s="113"/>
+      <c r="B117" s="125"/>
       <c r="C117" s="48" t="str">
         <f>master!C95</f>
         <v>ブランチのマージ</v>
@@ -9628,7 +9668,7 @@
     </row>
     <row r="118" spans="1:14" ht="100.8">
       <c r="A118" s="11"/>
-      <c r="B118" s="114"/>
+      <c r="B118" s="126"/>
       <c r="C118" s="48" t="str">
         <f>master!C96</f>
         <v>コンフリクトの解消</v>
@@ -9655,7 +9695,7 @@
     </row>
     <row r="119" spans="1:14" ht="75.599999999999994">
       <c r="A119" s="11"/>
-      <c r="B119" s="112" t="str">
+      <c r="B119" s="124" t="str">
         <f>master!B97</f>
         <v>VSCodeによるGitの操作</v>
       </c>
@@ -9685,7 +9725,7 @@
     </row>
     <row r="120" spans="1:14" ht="25.2">
       <c r="A120" s="11"/>
-      <c r="B120" s="113"/>
+      <c r="B120" s="125"/>
       <c r="C120" s="48" t="str">
         <f>master!C98</f>
         <v>VSCodeのソース管理機能</v>
@@ -9712,7 +9752,7 @@
     </row>
     <row r="121" spans="1:14" ht="126">
       <c r="A121" s="11"/>
-      <c r="B121" s="113"/>
+      <c r="B121" s="125"/>
       <c r="C121" s="48" t="str">
         <f>master!C99</f>
         <v>ローカルリポジトリの操作</v>
@@ -9739,7 +9779,7 @@
     </row>
     <row r="122" spans="1:14" ht="63">
       <c r="A122" s="11"/>
-      <c r="B122" s="113"/>
+      <c r="B122" s="125"/>
       <c r="C122" s="48" t="str">
         <f>master!C100</f>
         <v>リモートリポジトリの操作</v>
@@ -9768,7 +9808,7 @@
     </row>
     <row r="123" spans="1:14" ht="113.4">
       <c r="A123" s="11"/>
-      <c r="B123" s="114"/>
+      <c r="B123" s="126"/>
       <c r="C123" s="48" t="str">
         <f>master!C101</f>
         <v>ブランチの操作</v>
@@ -9797,7 +9837,7 @@
     </row>
     <row r="124" spans="1:14" ht="25.2">
       <c r="A124" s="11"/>
-      <c r="B124" s="115" t="str">
+      <c r="B124" s="121" t="str">
         <f>master!B103</f>
         <v>演習の概要について</v>
       </c>
@@ -9805,9 +9845,9 @@
         <f>master!C103</f>
         <v>はじめに</v>
       </c>
-      <c r="D124" s="109"/>
-      <c r="E124" s="110"/>
-      <c r="F124" s="111"/>
+      <c r="D124" s="112"/>
+      <c r="E124" s="113"/>
+      <c r="F124" s="114"/>
       <c r="G124" s="58" t="s">
         <v>332</v>
       </c>
@@ -9825,16 +9865,16 @@
     </row>
     <row r="125" spans="1:14" ht="50.4">
       <c r="A125" s="11"/>
-      <c r="B125" s="116"/>
+      <c r="B125" s="122"/>
       <c r="C125" s="58" t="str">
         <f>master!C104</f>
         <v>構成</v>
       </c>
-      <c r="D125" s="109" t="s">
+      <c r="D125" s="112" t="s">
         <v>407</v>
       </c>
-      <c r="E125" s="110"/>
-      <c r="F125" s="111"/>
+      <c r="E125" s="113"/>
+      <c r="F125" s="114"/>
       <c r="G125" s="58" t="s">
         <v>406</v>
       </c>
@@ -9852,16 +9892,16 @@
     </row>
     <row r="126" spans="1:14" ht="50.4">
       <c r="A126" s="11"/>
-      <c r="B126" s="117"/>
+      <c r="B126" s="123"/>
       <c r="C126" s="58" t="str">
         <f>master!C105</f>
         <v>利用するソフトウェア</v>
       </c>
-      <c r="D126" s="109" t="s">
+      <c r="D126" s="112" t="s">
         <v>408</v>
       </c>
-      <c r="E126" s="110"/>
-      <c r="F126" s="111"/>
+      <c r="E126" s="113"/>
+      <c r="F126" s="114"/>
       <c r="G126" s="58" t="s">
         <v>406</v>
       </c>
@@ -9881,7 +9921,7 @@
     </row>
     <row r="127" spans="1:14" ht="176.4">
       <c r="A127" s="11"/>
-      <c r="B127" s="115" t="str">
+      <c r="B127" s="121" t="str">
         <f>master!B106</f>
         <v>ローカルリポジトリの操作</v>
       </c>
@@ -9889,11 +9929,11 @@
         <f>master!C106</f>
         <v>演習の前に</v>
       </c>
-      <c r="D127" s="109" t="s">
+      <c r="D127" s="112" t="s">
         <v>412</v>
       </c>
-      <c r="E127" s="110"/>
-      <c r="F127" s="111"/>
+      <c r="E127" s="113"/>
+      <c r="F127" s="114"/>
       <c r="G127" s="58" t="s">
         <v>411</v>
       </c>
@@ -9911,16 +9951,16 @@
     </row>
     <row r="128" spans="1:14" ht="37.799999999999997">
       <c r="A128" s="11"/>
-      <c r="B128" s="116"/>
+      <c r="B128" s="122"/>
       <c r="C128" s="58" t="str">
         <f>master!C107</f>
         <v>リポジトリの作成</v>
       </c>
-      <c r="D128" s="109" t="s">
+      <c r="D128" s="112" t="s">
         <v>409</v>
       </c>
-      <c r="E128" s="110"/>
-      <c r="F128" s="111"/>
+      <c r="E128" s="113"/>
+      <c r="F128" s="114"/>
       <c r="G128" s="58" t="s">
         <v>410</v>
       </c>
@@ -9938,16 +9978,16 @@
     </row>
     <row r="129" spans="1:14" ht="37.799999999999997">
       <c r="A129" s="11"/>
-      <c r="B129" s="116"/>
+      <c r="B129" s="122"/>
       <c r="C129" s="58" t="str">
         <f>master!C108</f>
         <v>変更内容の確認</v>
       </c>
-      <c r="D129" s="109" t="s">
+      <c r="D129" s="112" t="s">
         <v>409</v>
       </c>
-      <c r="E129" s="110"/>
-      <c r="F129" s="111"/>
+      <c r="E129" s="113"/>
+      <c r="F129" s="114"/>
       <c r="G129" s="58" t="s">
         <v>410</v>
       </c>
@@ -9965,16 +10005,16 @@
     </row>
     <row r="130" spans="1:14" ht="37.799999999999997">
       <c r="A130" s="11"/>
-      <c r="B130" s="116"/>
+      <c r="B130" s="122"/>
       <c r="C130" s="58" t="str">
         <f>master!C109</f>
         <v>変更内容のステージング</v>
       </c>
-      <c r="D130" s="109" t="s">
+      <c r="D130" s="112" t="s">
         <v>409</v>
       </c>
-      <c r="E130" s="110"/>
-      <c r="F130" s="111"/>
+      <c r="E130" s="113"/>
+      <c r="F130" s="114"/>
       <c r="G130" s="58" t="s">
         <v>410</v>
       </c>
@@ -9992,16 +10032,16 @@
     </row>
     <row r="131" spans="1:14" ht="37.799999999999997">
       <c r="A131" s="11"/>
-      <c r="B131" s="117"/>
+      <c r="B131" s="123"/>
       <c r="C131" s="58" t="str">
         <f>master!C110</f>
         <v>変更内容のコミット</v>
       </c>
-      <c r="D131" s="109" t="s">
+      <c r="D131" s="112" t="s">
         <v>409</v>
       </c>
-      <c r="E131" s="110"/>
-      <c r="F131" s="111"/>
+      <c r="E131" s="113"/>
+      <c r="F131" s="114"/>
       <c r="G131" s="58" t="s">
         <v>410</v>
       </c>
@@ -10019,7 +10059,7 @@
     </row>
     <row r="132" spans="1:14" ht="163.80000000000001">
       <c r="A132" s="11"/>
-      <c r="B132" s="115" t="str">
+      <c r="B132" s="121" t="str">
         <f>master!B111</f>
         <v>ブランチの操作</v>
       </c>
@@ -10027,11 +10067,11 @@
         <f>master!C111</f>
         <v>演習の前に</v>
       </c>
-      <c r="D132" s="109" t="s">
+      <c r="D132" s="112" t="s">
         <v>413</v>
       </c>
-      <c r="E132" s="110"/>
-      <c r="F132" s="111"/>
+      <c r="E132" s="113"/>
+      <c r="F132" s="114"/>
       <c r="G132" s="58" t="s">
         <v>331</v>
       </c>
@@ -10051,16 +10091,16 @@
     </row>
     <row r="133" spans="1:14" ht="37.799999999999997">
       <c r="A133" s="11"/>
-      <c r="B133" s="116"/>
+      <c r="B133" s="122"/>
       <c r="C133" s="58" t="str">
         <f>master!C112</f>
         <v>ブランチの作成</v>
       </c>
-      <c r="D133" s="109" t="s">
+      <c r="D133" s="112" t="s">
         <v>409</v>
       </c>
-      <c r="E133" s="110"/>
-      <c r="F133" s="111"/>
+      <c r="E133" s="113"/>
+      <c r="F133" s="114"/>
       <c r="G133" s="58" t="s">
         <v>410</v>
       </c>
@@ -10080,16 +10120,16 @@
     </row>
     <row r="134" spans="1:14" ht="37.799999999999997">
       <c r="A134" s="11"/>
-      <c r="B134" s="116"/>
+      <c r="B134" s="122"/>
       <c r="C134" s="58" t="str">
         <f>master!C113</f>
         <v>ブランチの切り替え</v>
       </c>
-      <c r="D134" s="109" t="s">
+      <c r="D134" s="112" t="s">
         <v>409</v>
       </c>
-      <c r="E134" s="110"/>
-      <c r="F134" s="111"/>
+      <c r="E134" s="113"/>
+      <c r="F134" s="114"/>
       <c r="G134" s="58" t="s">
         <v>410</v>
       </c>
@@ -10109,16 +10149,16 @@
     </row>
     <row r="135" spans="1:14" ht="37.799999999999997">
       <c r="A135" s="11"/>
-      <c r="B135" s="117"/>
+      <c r="B135" s="123"/>
       <c r="C135" s="58" t="str">
         <f>master!C114</f>
         <v>ブランチのマージ</v>
       </c>
-      <c r="D135" s="109" t="s">
+      <c r="D135" s="112" t="s">
         <v>409</v>
       </c>
-      <c r="E135" s="110"/>
-      <c r="F135" s="111"/>
+      <c r="E135" s="113"/>
+      <c r="F135" s="114"/>
       <c r="G135" s="58" t="s">
         <v>410</v>
       </c>
@@ -10146,11 +10186,11 @@
         <f>master!C67</f>
         <v>ここから各自で演習を始めましょう。</v>
       </c>
-      <c r="D136" s="109" t="s">
+      <c r="D136" s="112" t="s">
         <v>196</v>
       </c>
-      <c r="E136" s="110"/>
-      <c r="F136" s="111"/>
+      <c r="E136" s="113"/>
+      <c r="F136" s="114"/>
       <c r="G136" s="58" t="s">
         <v>290</v>
       </c>
@@ -10168,7 +10208,7 @@
     </row>
     <row r="137" spans="1:14" ht="50.4">
       <c r="A137" s="11"/>
-      <c r="B137" s="127" t="str">
+      <c r="B137" s="109" t="str">
         <f>master!B116</f>
         <v>単体テストとJunitの導入</v>
       </c>
@@ -10198,7 +10238,7 @@
     </row>
     <row r="138" spans="1:14" ht="25.2">
       <c r="A138" s="11"/>
-      <c r="B138" s="128"/>
+      <c r="B138" s="110"/>
       <c r="C138" s="78" t="str">
         <f>master!C117</f>
         <v>TERASOLUNA 開発手順　 ※再掲</v>
@@ -10223,7 +10263,7 @@
     </row>
     <row r="139" spans="1:14" ht="25.2">
       <c r="A139" s="11"/>
-      <c r="B139" s="129"/>
+      <c r="B139" s="111"/>
       <c r="C139" s="78" t="str">
         <f>master!C118</f>
         <v>V字モデル　 ※再掲</v>
@@ -10250,7 +10290,7 @@
     </row>
     <row r="140" spans="1:14" ht="50.4">
       <c r="A140" s="11"/>
-      <c r="B140" s="127" t="str">
+      <c r="B140" s="109" t="str">
         <f>master!B119</f>
         <v>テストとは</v>
       </c>
@@ -10280,7 +10320,7 @@
     </row>
     <row r="141" spans="1:14" ht="315">
       <c r="A141" s="11"/>
-      <c r="B141" s="128"/>
+      <c r="B141" s="110"/>
       <c r="C141" s="78" t="str">
         <f>master!C120</f>
         <v>テストの目的</v>
@@ -10307,7 +10347,7 @@
     </row>
     <row r="142" spans="1:14" ht="25.2">
       <c r="A142" s="11"/>
-      <c r="B142" s="128"/>
+      <c r="B142" s="110"/>
       <c r="C142" s="78" t="str">
         <f>master!C121</f>
         <v>テストを実施しなかった場合…</v>
@@ -10334,7 +10374,7 @@
     </row>
     <row r="143" spans="1:14" ht="100.8">
       <c r="A143" s="11"/>
-      <c r="B143" s="129"/>
+      <c r="B143" s="111"/>
       <c r="C143" s="78" t="str">
         <f>master!C122</f>
         <v>コラム：テストとデバッグ</v>
@@ -10361,7 +10401,7 @@
     </row>
     <row r="144" spans="1:14" ht="50.4">
       <c r="A144" s="11"/>
-      <c r="B144" s="127" t="str">
+      <c r="B144" s="109" t="str">
         <f>master!B123</f>
         <v>単体テストとは</v>
       </c>
@@ -10391,7 +10431,7 @@
     </row>
     <row r="145" spans="1:14" ht="25.2">
       <c r="A145" s="11"/>
-      <c r="B145" s="128"/>
+      <c r="B145" s="110"/>
       <c r="C145" s="78" t="str">
         <f>master!C124</f>
         <v xml:space="preserve">V字モデル　– 製造/単体テスト –　※再掲 </v>
@@ -10416,7 +10456,7 @@
     </row>
     <row r="146" spans="1:14" ht="302.39999999999998">
       <c r="A146" s="11"/>
-      <c r="B146" s="128"/>
+      <c r="B146" s="110"/>
       <c r="C146" s="78" t="str">
         <f>master!C125</f>
         <v>テスト設計の流れ</v>
@@ -10443,7 +10483,7 @@
     </row>
     <row r="147" spans="1:14" ht="37.799999999999997">
       <c r="A147" s="11"/>
-      <c r="B147" s="128"/>
+      <c r="B147" s="110"/>
       <c r="C147" s="78" t="str">
         <f>master!C126</f>
         <v>テスト設計の例</v>
@@ -10470,7 +10510,7 @@
     </row>
     <row r="148" spans="1:14" ht="75.599999999999994">
       <c r="A148" s="11"/>
-      <c r="B148" s="128"/>
+      <c r="B148" s="110"/>
       <c r="C148" s="78" t="str">
         <f>master!C127</f>
         <v>単体テスト（Unit Test）とは</v>
@@ -10497,7 +10537,7 @@
     </row>
     <row r="149" spans="1:14" ht="113.4">
       <c r="A149" s="11"/>
-      <c r="B149" s="128"/>
+      <c r="B149" s="110"/>
       <c r="C149" s="78" t="str">
         <f>master!C128</f>
         <v>テスト技法 – ブラックボックステスト技法 –</v>
@@ -10524,7 +10564,7 @@
     </row>
     <row r="150" spans="1:14" ht="201.6">
       <c r="A150" s="11"/>
-      <c r="B150" s="128"/>
+      <c r="B150" s="110"/>
       <c r="C150" s="78" t="str">
         <f>master!C129</f>
         <v>ブラックボックステスト：同値分割法</v>
@@ -10551,7 +10591,7 @@
     </row>
     <row r="151" spans="1:14" ht="113.4">
       <c r="A151" s="11"/>
-      <c r="B151" s="128"/>
+      <c r="B151" s="110"/>
       <c r="C151" s="78" t="str">
         <f>master!C130</f>
         <v>ブラックボックステスト：境界値分析</v>
@@ -10578,7 +10618,7 @@
     </row>
     <row r="152" spans="1:14" ht="176.4">
       <c r="A152" s="11"/>
-      <c r="B152" s="128"/>
+      <c r="B152" s="110"/>
       <c r="C152" s="78" t="str">
         <f>master!C131</f>
         <v>ブラックボックステスト：ディシジョンテーブルテスト</v>
@@ -10605,7 +10645,7 @@
     </row>
     <row r="153" spans="1:14" ht="37.799999999999997">
       <c r="A153" s="11"/>
-      <c r="B153" s="128"/>
+      <c r="B153" s="110"/>
       <c r="C153" s="78" t="str">
         <f>master!C132</f>
         <v>ブラックボックステスト：状態遷移テスト</v>
@@ -10632,7 +10672,7 @@
     </row>
     <row r="154" spans="1:14" ht="88.2">
       <c r="A154" s="11"/>
-      <c r="B154" s="128"/>
+      <c r="B154" s="110"/>
       <c r="C154" s="78" t="str">
         <f>master!C133</f>
         <v>テスト技法 – ホワイトボックステスト技法 –</v>
@@ -10659,7 +10699,7 @@
     </row>
     <row r="155" spans="1:14" ht="151.19999999999999">
       <c r="A155" s="11"/>
-      <c r="B155" s="128"/>
+      <c r="B155" s="110"/>
       <c r="C155" s="78" t="str">
         <f>master!C134</f>
         <v>ホワイトボックステストの評価基準</v>
@@ -10686,7 +10726,7 @@
     </row>
     <row r="156" spans="1:14" ht="37.799999999999997">
       <c r="A156" s="11"/>
-      <c r="B156" s="128"/>
+      <c r="B156" s="110"/>
       <c r="C156" s="78" t="str">
         <f>master!C135</f>
         <v>ホワイトボックステスト：ステートメントテスト</v>
@@ -10713,7 +10753,7 @@
     </row>
     <row r="157" spans="1:14" ht="37.799999999999997">
       <c r="A157" s="11"/>
-      <c r="B157" s="128"/>
+      <c r="B157" s="110"/>
       <c r="C157" s="78" t="str">
         <f>master!C136</f>
         <v>ホワイトボックステスト：ブランチテスト</v>
@@ -10740,7 +10780,7 @@
     </row>
     <row r="158" spans="1:14" ht="37.799999999999997">
       <c r="A158" s="11"/>
-      <c r="B158" s="128"/>
+      <c r="B158" s="110"/>
       <c r="C158" s="78" t="str">
         <f>master!C137</f>
         <v>ホワイトボックステスト：コンディションテスト</v>
@@ -10767,7 +10807,7 @@
     </row>
     <row r="159" spans="1:14" ht="37.799999999999997">
       <c r="A159" s="11"/>
-      <c r="B159" s="128"/>
+      <c r="B159" s="110"/>
       <c r="C159" s="78" t="str">
         <f>master!C138</f>
         <v>テスト技法 – 経験ベースの技法 –</v>
@@ -10794,7 +10834,7 @@
     </row>
     <row r="160" spans="1:14" ht="100.8">
       <c r="A160" s="11"/>
-      <c r="B160" s="128"/>
+      <c r="B160" s="110"/>
       <c r="C160" s="78" t="str">
         <f>master!C139</f>
         <v>スタブとドライバ</v>
@@ -10821,7 +10861,7 @@
     </row>
     <row r="161" spans="1:14" ht="75.599999999999994">
       <c r="A161" s="11"/>
-      <c r="B161" s="129"/>
+      <c r="B161" s="111"/>
       <c r="C161" s="78" t="str">
         <f>master!C140</f>
         <v>スタブとモック</v>
@@ -10848,7 +10888,7 @@
     </row>
     <row r="162" spans="1:14" ht="37.799999999999997">
       <c r="A162" s="11"/>
-      <c r="B162" s="127" t="str">
+      <c r="B162" s="109" t="str">
         <f>master!B141</f>
         <v>JUnit</v>
       </c>
@@ -10878,7 +10918,7 @@
     </row>
     <row r="163" spans="1:14" ht="25.2">
       <c r="A163" s="11"/>
-      <c r="B163" s="129"/>
+      <c r="B163" s="111"/>
       <c r="C163" s="78" t="str">
         <f>master!C142</f>
         <v>参考文献</v>
@@ -10911,11 +10951,11 @@
         <f>master!C67</f>
         <v>ここから各自で演習を始めましょう。</v>
       </c>
-      <c r="D164" s="109" t="s">
+      <c r="D164" s="112" t="s">
         <v>249</v>
       </c>
-      <c r="E164" s="110"/>
-      <c r="F164" s="111"/>
+      <c r="E164" s="113"/>
+      <c r="F164" s="114"/>
       <c r="G164" s="58" t="s">
         <v>41</v>
       </c>
@@ -10933,7 +10973,7 @@
     </row>
     <row r="165" spans="1:14" ht="25.2">
       <c r="A165" s="11"/>
-      <c r="B165" s="121" t="str">
+      <c r="B165" s="115" t="str">
         <f>master!B144</f>
         <v>課題2の導入</v>
       </c>
@@ -10941,11 +10981,11 @@
         <f>master!C144</f>
         <v>演習課題の概要</v>
       </c>
-      <c r="D165" s="109" t="s">
+      <c r="D165" s="112" t="s">
         <v>265</v>
       </c>
-      <c r="E165" s="110"/>
-      <c r="F165" s="111"/>
+      <c r="E165" s="113"/>
+      <c r="F165" s="114"/>
       <c r="G165" s="58" t="s">
         <v>306</v>
       </c>
@@ -10963,16 +11003,16 @@
     </row>
     <row r="166" spans="1:14" ht="138.6">
       <c r="A166" s="11"/>
-      <c r="B166" s="122"/>
+      <c r="B166" s="116"/>
       <c r="C166" s="58" t="str">
         <f>master!C145</f>
         <v>[構造理解] Webアプリケーションで必要なもの  ※再掲</v>
       </c>
-      <c r="D166" s="109" t="s">
+      <c r="D166" s="112" t="s">
         <v>266</v>
       </c>
-      <c r="E166" s="110"/>
-      <c r="F166" s="111"/>
+      <c r="E166" s="113"/>
+      <c r="F166" s="114"/>
       <c r="G166" s="58" t="s">
         <v>307</v>
       </c>
@@ -10990,16 +11030,16 @@
     </row>
     <row r="167" spans="1:14" ht="50.4">
       <c r="A167" s="11"/>
-      <c r="B167" s="122"/>
+      <c r="B167" s="116"/>
       <c r="C167" s="58" t="str">
         <f>master!C146</f>
         <v>テストクラスを作成する単位</v>
       </c>
-      <c r="D167" s="109" t="s">
+      <c r="D167" s="112" t="s">
         <v>267</v>
       </c>
-      <c r="E167" s="110"/>
-      <c r="F167" s="111"/>
+      <c r="E167" s="113"/>
+      <c r="F167" s="114"/>
       <c r="G167" s="58" t="s">
         <v>308</v>
       </c>
@@ -11017,16 +11057,16 @@
     </row>
     <row r="168" spans="1:14" ht="113.4">
       <c r="A168" s="11"/>
-      <c r="B168" s="123"/>
+      <c r="B168" s="117"/>
       <c r="C168" s="58" t="str">
         <f>master!C147</f>
         <v>JUnitで単体テスト</v>
       </c>
-      <c r="D168" s="109" t="s">
+      <c r="D168" s="112" t="s">
         <v>268</v>
       </c>
-      <c r="E168" s="110"/>
-      <c r="F168" s="111"/>
+      <c r="E168" s="113"/>
+      <c r="F168" s="114"/>
       <c r="G168" s="58" t="s">
         <v>309</v>
       </c>
@@ -11044,7 +11084,7 @@
     </row>
     <row r="169" spans="1:14" ht="25.2">
       <c r="A169" s="11"/>
-      <c r="B169" s="121" t="str">
+      <c r="B169" s="115" t="str">
         <f>master!B148</f>
         <v>ハンズオン</v>
       </c>
@@ -11052,11 +11092,11 @@
         <f>master!C148</f>
         <v>バイブコーディングで単体テスト – はじめに</v>
       </c>
-      <c r="D169" s="109" t="s">
+      <c r="D169" s="112" t="s">
         <v>269</v>
       </c>
-      <c r="E169" s="110"/>
-      <c r="F169" s="111"/>
+      <c r="E169" s="113"/>
+      <c r="F169" s="114"/>
       <c r="G169" s="58" t="s">
         <v>306</v>
       </c>
@@ -11074,16 +11114,16 @@
     </row>
     <row r="170" spans="1:14" ht="50.4">
       <c r="A170" s="11"/>
-      <c r="B170" s="122"/>
-      <c r="C170" s="58" t="str">
+      <c r="B170" s="116"/>
+      <c r="C170" s="76" t="str">
         <f>master!C149</f>
         <v>バイブコーディング単体テスト①テスト項目表を作る</v>
       </c>
-      <c r="D170" s="109" t="s">
+      <c r="D170" s="112" t="s">
         <v>270</v>
       </c>
-      <c r="E170" s="110"/>
-      <c r="F170" s="111"/>
+      <c r="E170" s="113"/>
+      <c r="F170" s="114"/>
       <c r="G170" s="58" t="s">
         <v>308</v>
       </c>
@@ -11101,40 +11141,40 @@
     </row>
     <row r="171" spans="1:14" ht="88.2">
       <c r="A171" s="11"/>
-      <c r="B171" s="122"/>
-      <c r="C171" s="58"/>
-      <c r="D171" s="109" t="s">
+      <c r="B171" s="116"/>
+      <c r="C171" s="77"/>
+      <c r="D171" s="131" t="s">
         <v>181</v>
       </c>
-      <c r="E171" s="110"/>
-      <c r="F171" s="111"/>
-      <c r="G171" s="58" t="s">
+      <c r="E171" s="132"/>
+      <c r="F171" s="133"/>
+      <c r="G171" s="130" t="s">
         <v>310</v>
       </c>
-      <c r="H171" s="59"/>
-      <c r="I171" s="60" t="s">
-        <v>24</v>
-      </c>
-      <c r="J171" s="61">
+      <c r="H171" s="134"/>
+      <c r="I171" s="135" t="s">
+        <v>24</v>
+      </c>
+      <c r="J171" s="136">
         <v>6.9444444444444441E-3</v>
       </c>
-      <c r="K171" s="62"/>
+      <c r="K171" s="137"/>
       <c r="L171" s="6"/>
       <c r="M171" s="6"/>
       <c r="N171" s="6"/>
     </row>
     <row r="172" spans="1:14" ht="50.4">
       <c r="A172" s="11"/>
-      <c r="B172" s="122"/>
+      <c r="B172" s="116"/>
       <c r="C172" s="76" t="str">
         <f>master!C150</f>
         <v>バイブコーディング単体テスト②Repositoryのテストを作る</v>
       </c>
-      <c r="D172" s="109" t="s">
+      <c r="D172" s="112" t="s">
         <v>271</v>
       </c>
-      <c r="E172" s="110"/>
-      <c r="F172" s="111"/>
+      <c r="E172" s="113"/>
+      <c r="F172" s="114"/>
       <c r="G172" s="58" t="s">
         <v>308</v>
       </c>
@@ -11152,40 +11192,40 @@
     </row>
     <row r="173" spans="1:14" ht="88.2">
       <c r="A173" s="11"/>
-      <c r="B173" s="122"/>
+      <c r="B173" s="116"/>
       <c r="C173" s="77"/>
-      <c r="D173" s="109" t="s">
+      <c r="D173" s="131" t="s">
         <v>181</v>
       </c>
-      <c r="E173" s="110"/>
-      <c r="F173" s="111"/>
-      <c r="G173" s="58" t="s">
+      <c r="E173" s="132"/>
+      <c r="F173" s="133"/>
+      <c r="G173" s="130" t="s">
         <v>310</v>
       </c>
-      <c r="H173" s="59"/>
-      <c r="I173" s="60" t="s">
-        <v>24</v>
-      </c>
-      <c r="J173" s="61">
+      <c r="H173" s="134"/>
+      <c r="I173" s="135" t="s">
+        <v>24</v>
+      </c>
+      <c r="J173" s="136">
         <v>6.9444444444444441E-3</v>
       </c>
-      <c r="K173" s="62"/>
+      <c r="K173" s="137"/>
       <c r="L173" s="6"/>
       <c r="M173" s="6"/>
       <c r="N173" s="6"/>
     </row>
     <row r="174" spans="1:14" ht="138.6">
       <c r="A174" s="11"/>
-      <c r="B174" s="122"/>
+      <c r="B174" s="116"/>
       <c r="C174" s="58" t="str">
         <f>master!C151</f>
         <v>[解説] Repositoryのテストクラス（抜粋）</v>
       </c>
-      <c r="D174" s="109" t="s">
+      <c r="D174" s="112" t="s">
         <v>273</v>
       </c>
-      <c r="E174" s="110"/>
-      <c r="F174" s="111"/>
+      <c r="E174" s="113"/>
+      <c r="F174" s="114"/>
       <c r="G174" s="58" t="s">
         <v>307</v>
       </c>
@@ -11203,16 +11243,16 @@
     </row>
     <row r="175" spans="1:14" ht="50.4">
       <c r="A175" s="11"/>
-      <c r="B175" s="122"/>
+      <c r="B175" s="116"/>
       <c r="C175" s="76" t="str">
         <f>master!C152</f>
         <v>バイブコーディング単体テスト③Serviceのテストを作る</v>
       </c>
-      <c r="D175" s="109" t="s">
+      <c r="D175" s="112" t="s">
         <v>271</v>
       </c>
-      <c r="E175" s="110"/>
-      <c r="F175" s="111"/>
+      <c r="E175" s="113"/>
+      <c r="F175" s="114"/>
       <c r="G175" s="58" t="s">
         <v>308</v>
       </c>
@@ -11230,40 +11270,40 @@
     </row>
     <row r="176" spans="1:14" ht="88.2">
       <c r="A176" s="11"/>
-      <c r="B176" s="122"/>
+      <c r="B176" s="116"/>
       <c r="C176" s="77"/>
-      <c r="D176" s="109" t="s">
+      <c r="D176" s="131" t="s">
         <v>181</v>
       </c>
-      <c r="E176" s="110"/>
-      <c r="F176" s="111"/>
-      <c r="G176" s="58" t="s">
+      <c r="E176" s="132"/>
+      <c r="F176" s="133"/>
+      <c r="G176" s="130" t="s">
         <v>310</v>
       </c>
-      <c r="H176" s="59"/>
-      <c r="I176" s="60" t="s">
-        <v>24</v>
-      </c>
-      <c r="J176" s="61">
+      <c r="H176" s="134"/>
+      <c r="I176" s="135" t="s">
+        <v>24</v>
+      </c>
+      <c r="J176" s="136">
         <v>6.9444444444444441E-3</v>
       </c>
-      <c r="K176" s="62"/>
+      <c r="K176" s="137"/>
       <c r="L176" s="6"/>
       <c r="M176" s="6"/>
       <c r="N176" s="6"/>
     </row>
     <row r="177" spans="1:14" ht="138.6">
       <c r="A177" s="11"/>
-      <c r="B177" s="122"/>
+      <c r="B177" s="116"/>
       <c r="C177" s="58" t="str">
         <f>master!C153</f>
         <v>[解説] Serviceのテストクラス（抜粋）</v>
       </c>
-      <c r="D177" s="109" t="s">
+      <c r="D177" s="112" t="s">
         <v>272</v>
       </c>
-      <c r="E177" s="110"/>
-      <c r="F177" s="111"/>
+      <c r="E177" s="113"/>
+      <c r="F177" s="114"/>
       <c r="G177" s="58" t="s">
         <v>307</v>
       </c>
@@ -11281,16 +11321,16 @@
     </row>
     <row r="178" spans="1:14" ht="50.4">
       <c r="A178" s="11"/>
-      <c r="B178" s="122"/>
+      <c r="B178" s="116"/>
       <c r="C178" s="76" t="str">
         <f>master!C154</f>
         <v>バイブコーディング単体テスト④Controllerのテストを作る</v>
       </c>
-      <c r="D178" s="109" t="s">
+      <c r="D178" s="112" t="s">
         <v>271</v>
       </c>
-      <c r="E178" s="110"/>
-      <c r="F178" s="111"/>
+      <c r="E178" s="113"/>
+      <c r="F178" s="114"/>
       <c r="G178" s="58" t="s">
         <v>308</v>
       </c>
@@ -11308,40 +11348,40 @@
     </row>
     <row r="179" spans="1:14" ht="88.2">
       <c r="A179" s="11"/>
-      <c r="B179" s="122"/>
+      <c r="B179" s="116"/>
       <c r="C179" s="77"/>
-      <c r="D179" s="109" t="s">
+      <c r="D179" s="131" t="s">
         <v>181</v>
       </c>
-      <c r="E179" s="110"/>
-      <c r="F179" s="111"/>
-      <c r="G179" s="58" t="s">
+      <c r="E179" s="132"/>
+      <c r="F179" s="133"/>
+      <c r="G179" s="130" t="s">
         <v>310</v>
       </c>
-      <c r="H179" s="59"/>
-      <c r="I179" s="60" t="s">
-        <v>24</v>
-      </c>
-      <c r="J179" s="61">
+      <c r="H179" s="134"/>
+      <c r="I179" s="135" t="s">
+        <v>24</v>
+      </c>
+      <c r="J179" s="136">
         <v>6.9444444444444441E-3</v>
       </c>
-      <c r="K179" s="62"/>
+      <c r="K179" s="137"/>
       <c r="L179" s="6"/>
       <c r="M179" s="6"/>
       <c r="N179" s="6"/>
     </row>
     <row r="180" spans="1:14" ht="163.80000000000001">
       <c r="A180" s="11"/>
-      <c r="B180" s="123"/>
+      <c r="B180" s="117"/>
       <c r="C180" s="58" t="str">
         <f>master!C155</f>
         <v>[解説] Controllerのテストクラス（抜粋）</v>
       </c>
-      <c r="D180" s="109" t="s">
+      <c r="D180" s="112" t="s">
         <v>274</v>
       </c>
-      <c r="E180" s="110"/>
-      <c r="F180" s="111"/>
+      <c r="E180" s="113"/>
+      <c r="F180" s="114"/>
       <c r="G180" s="58" t="s">
         <v>311</v>
       </c>
@@ -11359,7 +11399,7 @@
     </row>
     <row r="181" spans="1:14" ht="165" customHeight="1">
       <c r="A181" s="11"/>
-      <c r="B181" s="121" t="str">
+      <c r="B181" s="115" t="str">
         <f>master!B156</f>
         <v>課題2の実施</v>
       </c>
@@ -11367,11 +11407,11 @@
         <f>master!C156</f>
         <v>ここから各自で演習を始めましょう。</v>
       </c>
-      <c r="D181" s="109" t="s">
+      <c r="D181" s="112" t="s">
         <v>275</v>
       </c>
-      <c r="E181" s="110"/>
-      <c r="F181" s="111"/>
+      <c r="E181" s="113"/>
+      <c r="F181" s="114"/>
       <c r="G181" s="58" t="s">
         <v>311</v>
       </c>
@@ -11389,16 +11429,16 @@
     </row>
     <row r="182" spans="1:14" ht="151.19999999999999">
       <c r="A182" s="11"/>
-      <c r="B182" s="123"/>
+      <c r="B182" s="117"/>
       <c r="C182" s="58" t="str">
         <f>master!C157</f>
         <v>[終了条件] 講師配布のテストプログラム(JUnit)が成功すること</v>
       </c>
-      <c r="D182" s="109" t="s">
+      <c r="D182" s="112" t="s">
         <v>334</v>
       </c>
-      <c r="E182" s="110"/>
-      <c r="F182" s="111"/>
+      <c r="E182" s="113"/>
+      <c r="F182" s="114"/>
       <c r="G182" s="58" t="s">
         <v>333</v>
       </c>
@@ -11418,7 +11458,7 @@
     </row>
     <row r="183" spans="1:14" ht="163.80000000000001">
       <c r="A183" s="11"/>
-      <c r="B183" s="121" t="str">
+      <c r="B183" s="115" t="str">
         <f>master!B159</f>
         <v>追加課題</v>
       </c>
@@ -11426,11 +11466,11 @@
         <f>master!C159</f>
         <v>演習課題の概要</v>
       </c>
-      <c r="D183" s="109" t="s">
+      <c r="D183" s="112" t="s">
         <v>277</v>
       </c>
-      <c r="E183" s="110"/>
-      <c r="F183" s="111"/>
+      <c r="E183" s="113"/>
+      <c r="F183" s="114"/>
       <c r="G183" s="58" t="s">
         <v>331</v>
       </c>
@@ -11450,16 +11490,16 @@
     </row>
     <row r="184" spans="1:14" ht="25.2">
       <c r="A184" s="11"/>
-      <c r="B184" s="122"/>
+      <c r="B184" s="116"/>
       <c r="C184" s="58" t="str">
         <f>master!C160</f>
         <v>追加課題①：送料の表示機能</v>
       </c>
-      <c r="D184" s="109" t="s">
+      <c r="D184" s="112" t="s">
         <v>279</v>
       </c>
-      <c r="E184" s="110"/>
-      <c r="F184" s="111"/>
+      <c r="E184" s="113"/>
+      <c r="F184" s="114"/>
       <c r="G184" s="58" t="s">
         <v>332</v>
       </c>
@@ -11479,16 +11519,16 @@
     </row>
     <row r="185" spans="1:14" ht="25.2">
       <c r="A185" s="11"/>
-      <c r="B185" s="122"/>
+      <c r="B185" s="116"/>
       <c r="C185" s="58" t="str">
         <f>master!C161</f>
         <v>追加課題②：クーポン機能</v>
       </c>
-      <c r="D185" s="109" t="s">
+      <c r="D185" s="112" t="s">
         <v>279</v>
       </c>
-      <c r="E185" s="110"/>
-      <c r="F185" s="111"/>
+      <c r="E185" s="113"/>
+      <c r="F185" s="114"/>
       <c r="G185" s="58" t="s">
         <v>332</v>
       </c>
@@ -11508,16 +11548,16 @@
     </row>
     <row r="186" spans="1:14" ht="25.2">
       <c r="A186" s="11"/>
-      <c r="B186" s="123"/>
+      <c r="B186" s="117"/>
       <c r="C186" s="58" t="str">
         <f>master!C162</f>
         <v>追加課題③：ユーザーアカウント機能</v>
       </c>
-      <c r="D186" s="109" t="s">
+      <c r="D186" s="112" t="s">
         <v>279</v>
       </c>
-      <c r="E186" s="110"/>
-      <c r="F186" s="111"/>
+      <c r="E186" s="113"/>
+      <c r="F186" s="114"/>
       <c r="G186" s="58" t="s">
         <v>332</v>
       </c>
@@ -11537,7 +11577,7 @@
     </row>
     <row r="187" spans="1:14" ht="176.4">
       <c r="A187" s="11"/>
-      <c r="B187" s="121" t="str">
+      <c r="B187" s="115" t="str">
         <f>master!B164</f>
         <v>演習の振り返り</v>
       </c>
@@ -11545,11 +11585,11 @@
         <f>master!C164</f>
         <v>アプリケーションの比較・分析</v>
       </c>
-      <c r="D187" s="109" t="s">
+      <c r="D187" s="112" t="s">
         <v>435</v>
       </c>
-      <c r="E187" s="110"/>
-      <c r="F187" s="111"/>
+      <c r="E187" s="113"/>
+      <c r="F187" s="114"/>
       <c r="G187" s="58" t="s">
         <v>426</v>
       </c>
@@ -11567,16 +11607,16 @@
     </row>
     <row r="188" spans="1:14" ht="63">
       <c r="A188" s="11"/>
-      <c r="B188" s="122"/>
+      <c r="B188" s="116"/>
       <c r="C188" s="58" t="str">
         <f>master!C165</f>
         <v>改善点の整理</v>
       </c>
-      <c r="D188" s="109" t="s">
+      <c r="D188" s="112" t="s">
         <v>434</v>
       </c>
-      <c r="E188" s="110"/>
-      <c r="F188" s="111"/>
+      <c r="E188" s="113"/>
+      <c r="F188" s="114"/>
       <c r="G188" s="58" t="s">
         <v>427</v>
       </c>
@@ -11594,16 +11634,16 @@
     </row>
     <row r="189" spans="1:14" ht="63">
       <c r="A189" s="11"/>
-      <c r="B189" s="123"/>
+      <c r="B189" s="117"/>
       <c r="C189" s="58" t="str">
         <f>master!C166</f>
         <v>分析結果の共有</v>
       </c>
-      <c r="D189" s="109" t="s">
+      <c r="D189" s="112" t="s">
         <v>432</v>
       </c>
-      <c r="E189" s="110"/>
-      <c r="F189" s="111"/>
+      <c r="E189" s="113"/>
+      <c r="F189" s="114"/>
       <c r="G189" s="58" t="s">
         <v>427</v>
       </c>
@@ -11625,6 +11665,186 @@
     <row r="191" spans="1:14" ht="15" customHeight="1"/>
   </sheetData>
   <mergeCells count="204">
+    <mergeCell ref="D188:F188"/>
+    <mergeCell ref="B94:B98"/>
+    <mergeCell ref="B91:B93"/>
+    <mergeCell ref="D124:F124"/>
+    <mergeCell ref="D135:F135"/>
+    <mergeCell ref="D133:F133"/>
+    <mergeCell ref="D131:F131"/>
+    <mergeCell ref="D132:F132"/>
+    <mergeCell ref="D129:F129"/>
+    <mergeCell ref="D130:F130"/>
+    <mergeCell ref="D127:F127"/>
+    <mergeCell ref="D128:F128"/>
+    <mergeCell ref="D125:F125"/>
+    <mergeCell ref="D126:F126"/>
+    <mergeCell ref="D134:F134"/>
+    <mergeCell ref="B132:B135"/>
+    <mergeCell ref="B127:B131"/>
+    <mergeCell ref="B124:B126"/>
+    <mergeCell ref="D108:F108"/>
+    <mergeCell ref="D121:F121"/>
+    <mergeCell ref="D92:F92"/>
+    <mergeCell ref="D99:F99"/>
+    <mergeCell ref="D123:F123"/>
+    <mergeCell ref="D136:F136"/>
+    <mergeCell ref="D101:F101"/>
+    <mergeCell ref="D102:F102"/>
+    <mergeCell ref="B119:B123"/>
+    <mergeCell ref="B113:B118"/>
+    <mergeCell ref="B108:B112"/>
+    <mergeCell ref="B99:B107"/>
+    <mergeCell ref="D162:F162"/>
+    <mergeCell ref="D163:F163"/>
+    <mergeCell ref="D138:F138"/>
+    <mergeCell ref="D137:F137"/>
+    <mergeCell ref="D111:F111"/>
+    <mergeCell ref="D110:F110"/>
+    <mergeCell ref="D109:F109"/>
+    <mergeCell ref="D112:F112"/>
+    <mergeCell ref="D103:F103"/>
+    <mergeCell ref="D104:F104"/>
+    <mergeCell ref="D105:F105"/>
+    <mergeCell ref="D106:F106"/>
+    <mergeCell ref="D107:F107"/>
+    <mergeCell ref="D120:F120"/>
+    <mergeCell ref="D119:F119"/>
+    <mergeCell ref="D118:F118"/>
+    <mergeCell ref="D117:F117"/>
+    <mergeCell ref="D116:F116"/>
+    <mergeCell ref="D31:F31"/>
+    <mergeCell ref="D32:F32"/>
+    <mergeCell ref="D33:F33"/>
+    <mergeCell ref="D189:F189"/>
+    <mergeCell ref="B187:B189"/>
+    <mergeCell ref="D170:F170"/>
+    <mergeCell ref="D172:F172"/>
+    <mergeCell ref="D175:F175"/>
+    <mergeCell ref="D176:F176"/>
+    <mergeCell ref="D178:F178"/>
+    <mergeCell ref="D179:F179"/>
+    <mergeCell ref="B183:B186"/>
+    <mergeCell ref="D182:F182"/>
+    <mergeCell ref="B181:B182"/>
+    <mergeCell ref="D93:F93"/>
+    <mergeCell ref="D94:F94"/>
+    <mergeCell ref="D95:F95"/>
+    <mergeCell ref="D96:F96"/>
+    <mergeCell ref="D97:F97"/>
+    <mergeCell ref="D98:F98"/>
+    <mergeCell ref="D100:F100"/>
+    <mergeCell ref="D122:F122"/>
+    <mergeCell ref="D186:F186"/>
+    <mergeCell ref="D185:F185"/>
+    <mergeCell ref="D91:F91"/>
+    <mergeCell ref="D76:F76"/>
+    <mergeCell ref="I19:J19"/>
+    <mergeCell ref="H19:H20"/>
+    <mergeCell ref="D78:F78"/>
+    <mergeCell ref="D80:F80"/>
+    <mergeCell ref="D74:F74"/>
+    <mergeCell ref="D85:F85"/>
+    <mergeCell ref="D90:F90"/>
+    <mergeCell ref="D82:F82"/>
+    <mergeCell ref="D83:F83"/>
+    <mergeCell ref="D87:F87"/>
+    <mergeCell ref="D88:F88"/>
+    <mergeCell ref="D89:F89"/>
+    <mergeCell ref="D77:F77"/>
+    <mergeCell ref="D79:F79"/>
+    <mergeCell ref="D81:F81"/>
+    <mergeCell ref="D75:F75"/>
+    <mergeCell ref="D73:F73"/>
+    <mergeCell ref="D21:F21"/>
+    <mergeCell ref="D35:F35"/>
+    <mergeCell ref="D22:F22"/>
+    <mergeCell ref="D28:F28"/>
+    <mergeCell ref="D23:F23"/>
+    <mergeCell ref="B4:E4"/>
+    <mergeCell ref="B5:K5"/>
+    <mergeCell ref="D19:F20"/>
+    <mergeCell ref="G19:G20"/>
+    <mergeCell ref="B19:B20"/>
+    <mergeCell ref="C19:C20"/>
+    <mergeCell ref="K19:K20"/>
+    <mergeCell ref="D7:E7"/>
+    <mergeCell ref="B22:B27"/>
+    <mergeCell ref="D25:F25"/>
+    <mergeCell ref="D27:F27"/>
+    <mergeCell ref="D24:F24"/>
+    <mergeCell ref="D26:F26"/>
+    <mergeCell ref="B28:B35"/>
+    <mergeCell ref="B36:B54"/>
+    <mergeCell ref="D49:F49"/>
+    <mergeCell ref="D50:F50"/>
+    <mergeCell ref="D51:F51"/>
+    <mergeCell ref="D52:F52"/>
+    <mergeCell ref="D53:F53"/>
+    <mergeCell ref="D37:F37"/>
+    <mergeCell ref="D38:F38"/>
+    <mergeCell ref="D39:F39"/>
+    <mergeCell ref="D40:F40"/>
+    <mergeCell ref="D41:F41"/>
+    <mergeCell ref="D42:F42"/>
+    <mergeCell ref="D43:F43"/>
+    <mergeCell ref="D44:F44"/>
+    <mergeCell ref="D45:F45"/>
+    <mergeCell ref="D46:F46"/>
+    <mergeCell ref="D47:F47"/>
+    <mergeCell ref="D48:F48"/>
+    <mergeCell ref="D54:F54"/>
+    <mergeCell ref="D36:F36"/>
+    <mergeCell ref="D34:F34"/>
+    <mergeCell ref="D29:F29"/>
+    <mergeCell ref="D30:F30"/>
+    <mergeCell ref="B55:B57"/>
+    <mergeCell ref="D69:F69"/>
+    <mergeCell ref="D70:F70"/>
+    <mergeCell ref="D71:F71"/>
+    <mergeCell ref="D72:F72"/>
+    <mergeCell ref="D62:F62"/>
+    <mergeCell ref="D56:F56"/>
+    <mergeCell ref="D57:F57"/>
+    <mergeCell ref="D58:F58"/>
+    <mergeCell ref="D59:F59"/>
+    <mergeCell ref="D66:F66"/>
+    <mergeCell ref="D67:F67"/>
+    <mergeCell ref="D60:F60"/>
+    <mergeCell ref="D61:F61"/>
+    <mergeCell ref="D63:F63"/>
+    <mergeCell ref="D64:F64"/>
+    <mergeCell ref="D65:F65"/>
+    <mergeCell ref="D68:F68"/>
+    <mergeCell ref="D55:F55"/>
+    <mergeCell ref="B62:B70"/>
+    <mergeCell ref="B58:B61"/>
+    <mergeCell ref="B71:B90"/>
+    <mergeCell ref="D84:F84"/>
+    <mergeCell ref="D86:F86"/>
+    <mergeCell ref="D115:F115"/>
+    <mergeCell ref="D114:F114"/>
+    <mergeCell ref="D113:F113"/>
+    <mergeCell ref="D142:F142"/>
+    <mergeCell ref="D144:F144"/>
+    <mergeCell ref="D145:F145"/>
+    <mergeCell ref="D146:F146"/>
+    <mergeCell ref="D147:F147"/>
+    <mergeCell ref="D148:F148"/>
+    <mergeCell ref="D160:F160"/>
+    <mergeCell ref="D161:F161"/>
+    <mergeCell ref="D143:F143"/>
+    <mergeCell ref="D155:F155"/>
+    <mergeCell ref="D156:F156"/>
+    <mergeCell ref="D157:F157"/>
+    <mergeCell ref="D158:F158"/>
+    <mergeCell ref="D159:F159"/>
+    <mergeCell ref="D154:F154"/>
+    <mergeCell ref="D153:F153"/>
+    <mergeCell ref="D149:F149"/>
+    <mergeCell ref="D150:F150"/>
+    <mergeCell ref="D151:F151"/>
+    <mergeCell ref="D152:F152"/>
     <mergeCell ref="B137:B139"/>
     <mergeCell ref="B162:B163"/>
     <mergeCell ref="D164:F164"/>
@@ -11649,186 +11869,6 @@
     <mergeCell ref="D139:F139"/>
     <mergeCell ref="D140:F140"/>
     <mergeCell ref="D141:F141"/>
-    <mergeCell ref="D160:F160"/>
-    <mergeCell ref="D161:F161"/>
-    <mergeCell ref="D143:F143"/>
-    <mergeCell ref="D155:F155"/>
-    <mergeCell ref="D156:F156"/>
-    <mergeCell ref="D157:F157"/>
-    <mergeCell ref="D158:F158"/>
-    <mergeCell ref="D159:F159"/>
-    <mergeCell ref="D154:F154"/>
-    <mergeCell ref="D153:F153"/>
-    <mergeCell ref="D149:F149"/>
-    <mergeCell ref="D150:F150"/>
-    <mergeCell ref="D151:F151"/>
-    <mergeCell ref="D152:F152"/>
-    <mergeCell ref="D115:F115"/>
-    <mergeCell ref="D114:F114"/>
-    <mergeCell ref="D113:F113"/>
-    <mergeCell ref="D142:F142"/>
-    <mergeCell ref="D144:F144"/>
-    <mergeCell ref="D145:F145"/>
-    <mergeCell ref="D146:F146"/>
-    <mergeCell ref="D147:F147"/>
-    <mergeCell ref="D148:F148"/>
-    <mergeCell ref="B55:B57"/>
-    <mergeCell ref="D69:F69"/>
-    <mergeCell ref="D70:F70"/>
-    <mergeCell ref="D71:F71"/>
-    <mergeCell ref="D72:F72"/>
-    <mergeCell ref="D62:F62"/>
-    <mergeCell ref="D56:F56"/>
-    <mergeCell ref="D57:F57"/>
-    <mergeCell ref="D58:F58"/>
-    <mergeCell ref="D59:F59"/>
-    <mergeCell ref="D66:F66"/>
-    <mergeCell ref="D67:F67"/>
-    <mergeCell ref="D60:F60"/>
-    <mergeCell ref="D61:F61"/>
-    <mergeCell ref="D63:F63"/>
-    <mergeCell ref="D64:F64"/>
-    <mergeCell ref="D65:F65"/>
-    <mergeCell ref="D68:F68"/>
-    <mergeCell ref="D55:F55"/>
-    <mergeCell ref="B62:B70"/>
-    <mergeCell ref="B58:B61"/>
-    <mergeCell ref="B71:B90"/>
-    <mergeCell ref="D84:F84"/>
-    <mergeCell ref="D86:F86"/>
-    <mergeCell ref="B28:B35"/>
-    <mergeCell ref="B36:B54"/>
-    <mergeCell ref="D49:F49"/>
-    <mergeCell ref="D50:F50"/>
-    <mergeCell ref="D51:F51"/>
-    <mergeCell ref="D52:F52"/>
-    <mergeCell ref="D53:F53"/>
-    <mergeCell ref="D37:F37"/>
-    <mergeCell ref="D38:F38"/>
-    <mergeCell ref="D39:F39"/>
-    <mergeCell ref="D40:F40"/>
-    <mergeCell ref="D41:F41"/>
-    <mergeCell ref="D42:F42"/>
-    <mergeCell ref="D43:F43"/>
-    <mergeCell ref="D44:F44"/>
-    <mergeCell ref="D45:F45"/>
-    <mergeCell ref="D46:F46"/>
-    <mergeCell ref="D47:F47"/>
-    <mergeCell ref="D48:F48"/>
-    <mergeCell ref="D54:F54"/>
-    <mergeCell ref="D36:F36"/>
-    <mergeCell ref="D34:F34"/>
-    <mergeCell ref="D29:F29"/>
-    <mergeCell ref="D30:F30"/>
-    <mergeCell ref="B4:E4"/>
-    <mergeCell ref="B5:K5"/>
-    <mergeCell ref="D19:F20"/>
-    <mergeCell ref="G19:G20"/>
-    <mergeCell ref="B19:B20"/>
-    <mergeCell ref="C19:C20"/>
-    <mergeCell ref="K19:K20"/>
-    <mergeCell ref="D7:E7"/>
-    <mergeCell ref="B22:B27"/>
-    <mergeCell ref="D25:F25"/>
-    <mergeCell ref="D27:F27"/>
-    <mergeCell ref="D24:F24"/>
-    <mergeCell ref="D26:F26"/>
-    <mergeCell ref="D91:F91"/>
-    <mergeCell ref="D76:F76"/>
-    <mergeCell ref="I19:J19"/>
-    <mergeCell ref="H19:H20"/>
-    <mergeCell ref="D78:F78"/>
-    <mergeCell ref="D80:F80"/>
-    <mergeCell ref="D74:F74"/>
-    <mergeCell ref="D85:F85"/>
-    <mergeCell ref="D90:F90"/>
-    <mergeCell ref="D82:F82"/>
-    <mergeCell ref="D83:F83"/>
-    <mergeCell ref="D87:F87"/>
-    <mergeCell ref="D88:F88"/>
-    <mergeCell ref="D89:F89"/>
-    <mergeCell ref="D77:F77"/>
-    <mergeCell ref="D79:F79"/>
-    <mergeCell ref="D81:F81"/>
-    <mergeCell ref="D75:F75"/>
-    <mergeCell ref="D73:F73"/>
-    <mergeCell ref="D21:F21"/>
-    <mergeCell ref="D35:F35"/>
-    <mergeCell ref="D22:F22"/>
-    <mergeCell ref="D28:F28"/>
-    <mergeCell ref="D23:F23"/>
-    <mergeCell ref="D31:F31"/>
-    <mergeCell ref="D32:F32"/>
-    <mergeCell ref="D33:F33"/>
-    <mergeCell ref="D189:F189"/>
-    <mergeCell ref="B187:B189"/>
-    <mergeCell ref="D170:F170"/>
-    <mergeCell ref="D172:F172"/>
-    <mergeCell ref="D175:F175"/>
-    <mergeCell ref="D176:F176"/>
-    <mergeCell ref="D178:F178"/>
-    <mergeCell ref="D179:F179"/>
-    <mergeCell ref="B183:B186"/>
-    <mergeCell ref="D182:F182"/>
-    <mergeCell ref="B181:B182"/>
-    <mergeCell ref="D93:F93"/>
-    <mergeCell ref="D94:F94"/>
-    <mergeCell ref="D95:F95"/>
-    <mergeCell ref="D96:F96"/>
-    <mergeCell ref="D97:F97"/>
-    <mergeCell ref="D98:F98"/>
-    <mergeCell ref="D100:F100"/>
-    <mergeCell ref="D122:F122"/>
-    <mergeCell ref="D186:F186"/>
-    <mergeCell ref="D185:F185"/>
-    <mergeCell ref="D101:F101"/>
-    <mergeCell ref="D102:F102"/>
-    <mergeCell ref="B119:B123"/>
-    <mergeCell ref="B113:B118"/>
-    <mergeCell ref="B108:B112"/>
-    <mergeCell ref="B99:B107"/>
-    <mergeCell ref="D162:F162"/>
-    <mergeCell ref="D163:F163"/>
-    <mergeCell ref="D138:F138"/>
-    <mergeCell ref="D137:F137"/>
-    <mergeCell ref="D111:F111"/>
-    <mergeCell ref="D110:F110"/>
-    <mergeCell ref="D109:F109"/>
-    <mergeCell ref="D112:F112"/>
-    <mergeCell ref="D103:F103"/>
-    <mergeCell ref="D104:F104"/>
-    <mergeCell ref="D105:F105"/>
-    <mergeCell ref="D106:F106"/>
-    <mergeCell ref="D107:F107"/>
-    <mergeCell ref="D120:F120"/>
-    <mergeCell ref="D119:F119"/>
-    <mergeCell ref="D118:F118"/>
-    <mergeCell ref="D117:F117"/>
-    <mergeCell ref="D116:F116"/>
-    <mergeCell ref="D188:F188"/>
-    <mergeCell ref="B94:B98"/>
-    <mergeCell ref="B91:B93"/>
-    <mergeCell ref="D124:F124"/>
-    <mergeCell ref="D135:F135"/>
-    <mergeCell ref="D133:F133"/>
-    <mergeCell ref="D131:F131"/>
-    <mergeCell ref="D132:F132"/>
-    <mergeCell ref="D129:F129"/>
-    <mergeCell ref="D130:F130"/>
-    <mergeCell ref="D127:F127"/>
-    <mergeCell ref="D128:F128"/>
-    <mergeCell ref="D125:F125"/>
-    <mergeCell ref="D126:F126"/>
-    <mergeCell ref="D134:F134"/>
-    <mergeCell ref="B132:B135"/>
-    <mergeCell ref="B127:B131"/>
-    <mergeCell ref="B124:B126"/>
-    <mergeCell ref="D108:F108"/>
-    <mergeCell ref="D121:F121"/>
-    <mergeCell ref="D92:F92"/>
-    <mergeCell ref="D99:F99"/>
-    <mergeCell ref="D123:F123"/>
-    <mergeCell ref="D136:F136"/>
   </mergeCells>
   <phoneticPr fontId="3"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/IG/7日版/AI Native-バイブコーディング_IG.xlsx
+++ b/IG/7日版/AI Native-バイブコーディング_IG.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\myrepo\ai_navive\IG\7日版\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C868B2B-729A-429E-80B2-167328CFE7E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E75C021F-21D7-473D-A269-954F79FD552E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="860" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -88,7 +88,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="832" uniqueCount="447">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="832" uniqueCount="452">
   <si>
     <t>1 日目</t>
     <rPh sb="2" eb="3">
@@ -3624,9 +3624,6 @@
     <phoneticPr fontId="3"/>
   </si>
   <si>
-    <t>演習の前に</t>
-  </si>
-  <si>
     <t>Git入門.docx</t>
   </si>
   <si>
@@ -3645,18 +3642,6 @@
     <rPh sb="59" eb="61">
       <t>セツメイ</t>
     </rPh>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
-    <t>Gitと「バージョン管理を実現するためのツールであり、現在最も広く利用されている分散型バージョン管理システム」のこと。
-Gitの主な特徴
-・ファイルの変更履歴を記録できる。
-・過去の状態に戻すことができる。
-・変更内容の差分を確認できる。
-・複数人で共同作業できる。
-以下のキーワードについて説明する。
-・中央集中型バージョン管理システム
-・分散型バージョン管理システム</t>
     <phoneticPr fontId="3"/>
   </si>
   <si>
@@ -4544,30 +4529,10 @@
     <phoneticPr fontId="3"/>
   </si>
   <si>
-    <t>変更内容のステージング</t>
-  </si>
-  <si>
-    <t>ブランチの作成</t>
-  </si>
-  <si>
-    <t>ブランチの切り替え</t>
-  </si>
-  <si>
-    <t>ブランチのマージ</t>
-  </si>
-  <si>
     <t>演習の概要について</t>
     <rPh sb="3" eb="5">
       <t>ガイヨウ</t>
     </rPh>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
-    <t>構成</t>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
-    <t>利用するソフトウェア</t>
     <phoneticPr fontId="3"/>
   </si>
   <si>
@@ -4595,6 +4560,54 @@
       <t>キョウザイ</t>
     </rPh>
     <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>Gitとは、「バージョン管理を実現するためのツールであり、現在最も広く利用されている分散型バージョン管理システム」のこと。
+Gitの主な特徴
+・ファイルの変更履歴を記録できる。
+・過去の状態に戻すことができる。
+・変更内容の差分を確認できる。
+・複数人で共同作業できる。
+以下のキーワードについて説明する。
+・中央集中型バージョン管理システム
+・分散型バージョン管理システム</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>0.1 はじめに</t>
+  </si>
+  <si>
+    <t>0.2 構成</t>
+  </si>
+  <si>
+    <t>0.3 利用するソフトウェア</t>
+  </si>
+  <si>
+    <t>1.0 演習の前に</t>
+  </si>
+  <si>
+    <t>1.1 リポジトリの作成</t>
+  </si>
+  <si>
+    <t>1.2 変更内容の確認</t>
+  </si>
+  <si>
+    <t>1.3 変更内容のステージ</t>
+  </si>
+  <si>
+    <t>1.4 変更内容のコミット</t>
+  </si>
+  <si>
+    <t>2.0 演習の前に</t>
+  </si>
+  <si>
+    <t>2.1 ブランチの作成</t>
+  </si>
+  <si>
+    <t>2.2 ブランチの切り替え</t>
+  </si>
+  <si>
+    <t>2.3 ブランチのマージ</t>
   </si>
 </sst>
 </file>
@@ -5303,6 +5316,21 @@
     <xf numFmtId="0" fontId="5" fillId="7" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="20" fontId="5" fillId="11" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="20" fontId="5" fillId="11" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -5351,6 +5379,69 @@
     <xf numFmtId="0" fontId="11" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
     </xf>
@@ -5359,84 +5450,6 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="11" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="11" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="20" fontId="5" fillId="11" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="20" fontId="5" fillId="11" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -5810,15 +5823,15 @@
   <sheetData>
     <row r="2" spans="1:8" ht="27">
       <c r="A2" s="13"/>
-      <c r="B2" s="93" t="str">
+      <c r="B2" s="98" t="str">
         <f>"コースプラン/インストラクションガイド 「"&amp;master!$B$1&amp;"_IG」"</f>
         <v>コースプラン/インストラクションガイド 「AI Native-バイブコーディング_IG」</v>
       </c>
-      <c r="C2" s="93"/>
-      <c r="D2" s="93"/>
-      <c r="E2" s="93"/>
-      <c r="F2" s="93"/>
-      <c r="G2" s="93"/>
+      <c r="C2" s="98"/>
+      <c r="D2" s="98"/>
+      <c r="E2" s="98"/>
+      <c r="F2" s="98"/>
+      <c r="G2" s="98"/>
     </row>
     <row r="3" spans="1:8" ht="27.6" thickBot="1">
       <c r="A3" s="13"/>
@@ -5831,10 +5844,10 @@
     </row>
     <row r="4" spans="1:8" ht="27.6" thickBot="1">
       <c r="A4" s="13"/>
-      <c r="B4" s="94" t="s">
+      <c r="B4" s="99" t="s">
         <v>11</v>
       </c>
-      <c r="C4" s="95"/>
+      <c r="C4" s="100"/>
       <c r="D4" s="13"/>
       <c r="E4" s="13"/>
       <c r="F4" s="13"/>
@@ -5842,18 +5855,18 @@
     </row>
     <row r="5" spans="1:8" ht="27.6" thickBot="1">
       <c r="A5" s="13"/>
-      <c r="B5" s="96"/>
-      <c r="C5" s="97"/>
+      <c r="B5" s="101"/>
+      <c r="C5" s="102"/>
       <c r="D5" s="13"/>
       <c r="E5" s="13"/>
       <c r="F5" s="13"/>
       <c r="G5" s="13"/>
     </row>
     <row r="7" spans="1:8" ht="16.2">
-      <c r="B7" s="98" t="s">
+      <c r="B7" s="103" t="s">
         <v>2</v>
       </c>
-      <c r="C7" s="98"/>
+      <c r="C7" s="103"/>
     </row>
     <row r="8" spans="1:8">
       <c r="E8" s="15"/>
@@ -6299,7 +6312,7 @@
         <v>0.6875</v>
       </c>
       <c r="C38" s="66" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="D38" s="39"/>
       <c r="E38" s="51"/>
@@ -6340,10 +6353,10 @@
         <v>0.71875</v>
       </c>
       <c r="C41" s="55" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="D41" s="39"/>
-      <c r="E41" s="99"/>
+      <c r="E41" s="104"/>
       <c r="F41" s="39"/>
       <c r="G41" s="51"/>
       <c r="H41" s="6"/>
@@ -6353,7 +6366,7 @@
       <c r="B42" s="64"/>
       <c r="C42" s="52"/>
       <c r="D42" s="39"/>
-      <c r="E42" s="100"/>
+      <c r="E42" s="105"/>
       <c r="F42" s="37">
         <v>0.72916666666666663</v>
       </c>
@@ -6444,10 +6457,10 @@
       <c r="K3" s="9"/>
     </row>
     <row r="4" spans="1:12" ht="16.2">
-      <c r="B4" s="104" t="s">
+      <c r="B4" s="109" t="s">
         <v>4</v>
       </c>
-      <c r="C4" s="104"/>
+      <c r="C4" s="109"/>
       <c r="D4" s="8"/>
       <c r="E4" s="8"/>
       <c r="F4" s="8"/>
@@ -6458,16 +6471,16 @@
       <c r="K4" s="9"/>
     </row>
     <row r="5" spans="1:12" ht="36" customHeight="1">
-      <c r="B5" s="105"/>
-      <c r="C5" s="105"/>
-      <c r="D5" s="105"/>
-      <c r="E5" s="105"/>
-      <c r="F5" s="105"/>
-      <c r="G5" s="105"/>
-      <c r="H5" s="105"/>
-      <c r="I5" s="105"/>
-      <c r="J5" s="105"/>
-      <c r="K5" s="105"/>
+      <c r="B5" s="110"/>
+      <c r="C5" s="110"/>
+      <c r="D5" s="110"/>
+      <c r="E5" s="110"/>
+      <c r="F5" s="110"/>
+      <c r="G5" s="110"/>
+      <c r="H5" s="110"/>
+      <c r="I5" s="110"/>
+      <c r="J5" s="110"/>
+      <c r="K5" s="110"/>
     </row>
     <row r="6" spans="1:12">
       <c r="B6" s="10"/>
@@ -6482,10 +6495,10 @@
       <c r="C7" s="30" t="s">
         <v>15</v>
       </c>
-      <c r="D7" s="106" t="s">
+      <c r="D7" s="111" t="s">
         <v>20</v>
       </c>
-      <c r="E7" s="106"/>
+      <c r="E7" s="111"/>
       <c r="F7" s="30" t="s">
         <v>10</v>
       </c>
@@ -6500,7 +6513,7 @@
         <v>17</v>
       </c>
       <c r="C8" s="32" t="s">
-        <v>445</v>
+        <v>437</v>
       </c>
       <c r="D8" s="42" t="s">
         <v>19</v>
@@ -6517,46 +6530,46 @@
     </row>
     <row r="10" spans="1:12">
       <c r="A10" s="10"/>
-      <c r="B10" s="102"/>
-      <c r="C10" s="102" t="s">
+      <c r="B10" s="107"/>
+      <c r="C10" s="107" t="s">
         <v>7</v>
       </c>
-      <c r="D10" s="102" t="s">
+      <c r="D10" s="107" t="s">
         <v>8</v>
       </c>
-      <c r="E10" s="102"/>
-      <c r="F10" s="102"/>
-      <c r="G10" s="102" t="s">
+      <c r="E10" s="107"/>
+      <c r="F10" s="107"/>
+      <c r="G10" s="107" t="s">
         <v>9</v>
       </c>
-      <c r="H10" s="107" t="s">
+      <c r="H10" s="112" t="s">
         <v>23</v>
       </c>
-      <c r="I10" s="101" t="s">
+      <c r="I10" s="106" t="s">
         <v>31</v>
       </c>
-      <c r="J10" s="101"/>
-      <c r="K10" s="101" t="s">
+      <c r="J10" s="106"/>
+      <c r="K10" s="106" t="s">
         <v>30</v>
       </c>
       <c r="L10" s="10"/>
     </row>
     <row r="11" spans="1:12">
       <c r="A11" s="10"/>
-      <c r="B11" s="102"/>
-      <c r="C11" s="102"/>
-      <c r="D11" s="102"/>
-      <c r="E11" s="102"/>
-      <c r="F11" s="102"/>
-      <c r="G11" s="102"/>
-      <c r="H11" s="108"/>
+      <c r="B11" s="107"/>
+      <c r="C11" s="107"/>
+      <c r="D11" s="107"/>
+      <c r="E11" s="107"/>
+      <c r="F11" s="107"/>
+      <c r="G11" s="107"/>
+      <c r="H11" s="113"/>
       <c r="I11" s="25" t="s">
         <v>25</v>
       </c>
       <c r="J11" s="25" t="s">
         <v>6</v>
       </c>
-      <c r="K11" s="102"/>
+      <c r="K11" s="107"/>
       <c r="L11" s="10"/>
     </row>
     <row r="12" spans="1:12" ht="63">
@@ -6565,11 +6578,11 @@
       <c r="C12" s="19" t="s">
         <v>324</v>
       </c>
-      <c r="D12" s="103" t="s">
-        <v>446</v>
-      </c>
-      <c r="E12" s="103"/>
-      <c r="F12" s="103"/>
+      <c r="D12" s="108" t="s">
+        <v>438</v>
+      </c>
+      <c r="E12" s="108"/>
+      <c r="F12" s="108"/>
       <c r="G12" s="87" t="s">
         <v>49</v>
       </c>
@@ -6589,11 +6602,11 @@
       <c r="C13" s="19" t="s">
         <v>325</v>
       </c>
-      <c r="D13" s="103" t="s">
+      <c r="D13" s="108" t="s">
         <v>322</v>
       </c>
-      <c r="E13" s="103"/>
-      <c r="F13" s="103"/>
+      <c r="E13" s="108"/>
+      <c r="F13" s="108"/>
       <c r="G13" s="87" t="s">
         <v>323</v>
       </c>
@@ -6693,12 +6706,12 @@
       <c r="M3" s="9"/>
     </row>
     <row r="4" spans="2:14" ht="16.2">
-      <c r="B4" s="104" t="s">
+      <c r="B4" s="109" t="s">
         <v>4</v>
       </c>
-      <c r="C4" s="104"/>
-      <c r="D4" s="104"/>
-      <c r="E4" s="104"/>
+      <c r="C4" s="109"/>
+      <c r="D4" s="109"/>
+      <c r="E4" s="109"/>
       <c r="F4" s="8"/>
       <c r="G4" s="8"/>
       <c r="H4" s="7"/>
@@ -6709,16 +6722,16 @@
       <c r="M4" s="9"/>
     </row>
     <row r="5" spans="2:14" ht="36" customHeight="1">
-      <c r="B5" s="127"/>
-      <c r="C5" s="127"/>
-      <c r="D5" s="127"/>
-      <c r="E5" s="127"/>
-      <c r="F5" s="127"/>
-      <c r="G5" s="127"/>
-      <c r="H5" s="127"/>
-      <c r="I5" s="127"/>
-      <c r="J5" s="127"/>
-      <c r="K5" s="127"/>
+      <c r="B5" s="134"/>
+      <c r="C5" s="134"/>
+      <c r="D5" s="134"/>
+      <c r="E5" s="134"/>
+      <c r="F5" s="134"/>
+      <c r="G5" s="134"/>
+      <c r="H5" s="134"/>
+      <c r="I5" s="134"/>
+      <c r="J5" s="134"/>
+      <c r="K5" s="134"/>
       <c r="L5" s="26"/>
       <c r="M5" s="27"/>
     </row>
@@ -6738,10 +6751,10 @@
       <c r="C7" s="30" t="s">
         <v>15</v>
       </c>
-      <c r="D7" s="106" t="s">
+      <c r="D7" s="111" t="s">
         <v>20</v>
       </c>
-      <c r="E7" s="106"/>
+      <c r="E7" s="111"/>
       <c r="F7" s="30" t="s">
         <v>10</v>
       </c>
@@ -6892,7 +6905,7 @@
         <v>91</v>
       </c>
       <c r="C14" s="57" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="D14" s="42" t="s">
         <v>19</v>
@@ -6914,7 +6927,7 @@
         <v>92</v>
       </c>
       <c r="C15" s="57" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="D15" s="42" t="s">
         <v>19</v>
@@ -6936,7 +6949,7 @@
         <v>280</v>
       </c>
       <c r="C16" s="57" t="s">
-        <v>444</v>
+        <v>436</v>
       </c>
       <c r="D16" s="42" t="s">
         <v>19</v>
@@ -6977,28 +6990,28 @@
     </row>
     <row r="19" spans="1:14" ht="24" customHeight="1">
       <c r="A19" s="10"/>
-      <c r="B19" s="102" t="s">
+      <c r="B19" s="107" t="s">
         <v>5</v>
       </c>
-      <c r="C19" s="102" t="s">
+      <c r="C19" s="107" t="s">
         <v>7</v>
       </c>
-      <c r="D19" s="102" t="s">
+      <c r="D19" s="107" t="s">
         <v>8</v>
       </c>
-      <c r="E19" s="102"/>
-      <c r="F19" s="102"/>
-      <c r="G19" s="102" t="s">
+      <c r="E19" s="107"/>
+      <c r="F19" s="107"/>
+      <c r="G19" s="107" t="s">
         <v>9</v>
       </c>
-      <c r="H19" s="101" t="s">
+      <c r="H19" s="106" t="s">
         <v>23</v>
       </c>
-      <c r="I19" s="128" t="s">
+      <c r="I19" s="132" t="s">
         <v>31</v>
       </c>
-      <c r="J19" s="129"/>
-      <c r="K19" s="101" t="s">
+      <c r="J19" s="133"/>
+      <c r="K19" s="106" t="s">
         <v>32</v>
       </c>
       <c r="L19" s="6"/>
@@ -7007,20 +7020,20 @@
     </row>
     <row r="20" spans="1:14">
       <c r="A20" s="10"/>
-      <c r="B20" s="102"/>
-      <c r="C20" s="102"/>
-      <c r="D20" s="102"/>
-      <c r="E20" s="102"/>
-      <c r="F20" s="102"/>
-      <c r="G20" s="102"/>
-      <c r="H20" s="101"/>
+      <c r="B20" s="107"/>
+      <c r="C20" s="107"/>
+      <c r="D20" s="107"/>
+      <c r="E20" s="107"/>
+      <c r="F20" s="107"/>
+      <c r="G20" s="107"/>
+      <c r="H20" s="106"/>
       <c r="I20" s="25" t="s">
         <v>25</v>
       </c>
       <c r="J20" s="25" t="s">
         <v>6</v>
       </c>
-      <c r="K20" s="102"/>
+      <c r="K20" s="107"/>
       <c r="L20" s="6"/>
       <c r="M20" s="6"/>
       <c r="N20" s="6"/>
@@ -7035,11 +7048,11 @@
         <f>master!C3</f>
         <v>講義の目的</v>
       </c>
-      <c r="D21" s="118" t="s">
+      <c r="D21" s="123" t="s">
         <v>93</v>
       </c>
-      <c r="E21" s="119"/>
-      <c r="F21" s="120"/>
+      <c r="E21" s="124"/>
+      <c r="F21" s="125"/>
       <c r="G21" s="48" t="s">
         <v>94</v>
       </c>
@@ -7057,7 +7070,7 @@
     </row>
     <row r="22" spans="1:14" ht="138.6" customHeight="1">
       <c r="A22" s="10"/>
-      <c r="B22" s="124" t="str">
+      <c r="B22" s="117" t="str">
         <f>master!B4</f>
         <v>Webアプリケーションとは</v>
       </c>
@@ -7065,11 +7078,11 @@
         <f>master!C4</f>
         <v>Webアプリケーションとは</v>
       </c>
-      <c r="D22" s="118" t="s">
+      <c r="D22" s="123" t="s">
         <v>95</v>
       </c>
-      <c r="E22" s="119"/>
-      <c r="F22" s="120"/>
+      <c r="E22" s="124"/>
+      <c r="F22" s="125"/>
       <c r="G22" s="48" t="s">
         <v>39</v>
       </c>
@@ -7087,16 +7100,16 @@
     </row>
     <row r="23" spans="1:14" ht="75.599999999999994">
       <c r="A23" s="11"/>
-      <c r="B23" s="125"/>
+      <c r="B23" s="118"/>
       <c r="C23" s="48" t="str">
         <f>master!C5</f>
         <v>Webアプリケーションの種類</v>
       </c>
-      <c r="D23" s="118" t="s">
+      <c r="D23" s="123" t="s">
         <v>96</v>
       </c>
-      <c r="E23" s="119"/>
-      <c r="F23" s="120"/>
+      <c r="E23" s="124"/>
+      <c r="F23" s="125"/>
       <c r="G23" s="48" t="s">
         <v>43</v>
       </c>
@@ -7114,16 +7127,16 @@
     </row>
     <row r="24" spans="1:14" ht="37.799999999999997">
       <c r="A24" s="11"/>
-      <c r="B24" s="125"/>
+      <c r="B24" s="118"/>
       <c r="C24" s="48" t="str">
         <f>master!C6</f>
         <v>アプリケーションとは</v>
       </c>
-      <c r="D24" s="118" t="s">
+      <c r="D24" s="123" t="s">
         <v>97</v>
       </c>
-      <c r="E24" s="119"/>
-      <c r="F24" s="120"/>
+      <c r="E24" s="124"/>
+      <c r="F24" s="125"/>
       <c r="G24" s="48" t="s">
         <v>41</v>
       </c>
@@ -7141,16 +7154,16 @@
     </row>
     <row r="25" spans="1:14" ht="63">
       <c r="A25" s="11"/>
-      <c r="B25" s="125"/>
+      <c r="B25" s="118"/>
       <c r="C25" s="48" t="str">
         <f>master!C7</f>
         <v>Web画面アプリケーション</v>
       </c>
-      <c r="D25" s="118" t="s">
+      <c r="D25" s="123" t="s">
         <v>98</v>
       </c>
-      <c r="E25" s="119"/>
-      <c r="F25" s="120"/>
+      <c r="E25" s="124"/>
+      <c r="F25" s="125"/>
       <c r="G25" s="48" t="s">
         <v>40</v>
       </c>
@@ -7168,13 +7181,13 @@
     </row>
     <row r="26" spans="1:14" ht="63">
       <c r="A26" s="11"/>
-      <c r="B26" s="125"/>
+      <c r="B26" s="118"/>
       <c r="C26" s="48"/>
-      <c r="D26" s="118" t="s">
+      <c r="D26" s="123" t="s">
         <v>99</v>
       </c>
-      <c r="E26" s="119"/>
-      <c r="F26" s="120"/>
+      <c r="E26" s="124"/>
+      <c r="F26" s="125"/>
       <c r="G26" s="48" t="s">
         <v>40</v>
       </c>
@@ -7192,16 +7205,16 @@
     </row>
     <row r="27" spans="1:14" ht="113.4">
       <c r="A27" s="11"/>
-      <c r="B27" s="126"/>
+      <c r="B27" s="119"/>
       <c r="C27" s="48" t="str">
         <f>master!C8</f>
         <v>ブラウザからのリクエスト種類</v>
       </c>
-      <c r="D27" s="118" t="s">
+      <c r="D27" s="123" t="s">
         <v>100</v>
       </c>
-      <c r="E27" s="119"/>
-      <c r="F27" s="120"/>
+      <c r="E27" s="124"/>
+      <c r="F27" s="125"/>
       <c r="G27" s="48" t="s">
         <v>44</v>
       </c>
@@ -7219,7 +7232,7 @@
     </row>
     <row r="28" spans="1:14" ht="102" customHeight="1">
       <c r="A28" s="11"/>
-      <c r="B28" s="124" t="str">
+      <c r="B28" s="117" t="str">
         <f>master!B9</f>
         <v>データベースとは</v>
       </c>
@@ -7227,11 +7240,11 @@
         <f>master!C9</f>
         <v>データベースとは</v>
       </c>
-      <c r="D28" s="118" t="s">
+      <c r="D28" s="123" t="s">
         <v>101</v>
       </c>
-      <c r="E28" s="119"/>
-      <c r="F28" s="120"/>
+      <c r="E28" s="124"/>
+      <c r="F28" s="125"/>
       <c r="G28" s="48" t="s">
         <v>41</v>
       </c>
@@ -7249,16 +7262,16 @@
     </row>
     <row r="29" spans="1:14" ht="88.2">
       <c r="A29" s="11"/>
-      <c r="B29" s="125"/>
+      <c r="B29" s="118"/>
       <c r="C29" s="48" t="str">
         <f>master!C10</f>
         <v>リレーショナルデータベース</v>
       </c>
-      <c r="D29" s="118" t="s">
+      <c r="D29" s="123" t="s">
         <v>102</v>
       </c>
-      <c r="E29" s="119"/>
-      <c r="F29" s="120"/>
+      <c r="E29" s="124"/>
+      <c r="F29" s="125"/>
       <c r="G29" s="48" t="s">
         <v>45</v>
       </c>
@@ -7276,16 +7289,16 @@
     </row>
     <row r="30" spans="1:14" ht="25.2">
       <c r="A30" s="11"/>
-      <c r="B30" s="125"/>
+      <c r="B30" s="118"/>
       <c r="C30" s="48" t="str">
         <f>master!C11</f>
         <v>データベースの役割</v>
       </c>
-      <c r="D30" s="118" t="s">
+      <c r="D30" s="123" t="s">
         <v>103</v>
       </c>
-      <c r="E30" s="119"/>
-      <c r="F30" s="120"/>
+      <c r="E30" s="124"/>
+      <c r="F30" s="125"/>
       <c r="G30" s="48" t="s">
         <v>46</v>
       </c>
@@ -7305,16 +7318,16 @@
     </row>
     <row r="31" spans="1:14" ht="75.599999999999994">
       <c r="A31" s="11"/>
-      <c r="B31" s="125"/>
+      <c r="B31" s="118"/>
       <c r="C31" s="48" t="str">
         <f>master!C12</f>
         <v>2.1.テーブル</v>
       </c>
-      <c r="D31" s="118" t="s">
+      <c r="D31" s="123" t="s">
         <v>104</v>
       </c>
-      <c r="E31" s="119"/>
-      <c r="F31" s="120"/>
+      <c r="E31" s="124"/>
+      <c r="F31" s="125"/>
       <c r="G31" s="48" t="s">
         <v>43</v>
       </c>
@@ -7332,16 +7345,16 @@
     </row>
     <row r="32" spans="1:14" ht="100.8">
       <c r="A32" s="11"/>
-      <c r="B32" s="125"/>
+      <c r="B32" s="118"/>
       <c r="C32" s="48" t="str">
         <f>master!C13</f>
         <v>2.2.データ型１</v>
       </c>
-      <c r="D32" s="118" t="s">
+      <c r="D32" s="123" t="s">
         <v>105</v>
       </c>
-      <c r="E32" s="119"/>
-      <c r="F32" s="120"/>
+      <c r="E32" s="124"/>
+      <c r="F32" s="125"/>
       <c r="G32" s="48" t="s">
         <v>47</v>
       </c>
@@ -7359,16 +7372,16 @@
     </row>
     <row r="33" spans="1:14" ht="37.799999999999997">
       <c r="A33" s="11"/>
-      <c r="B33" s="125"/>
+      <c r="B33" s="118"/>
       <c r="C33" s="48" t="str">
         <f>master!C14</f>
         <v>2.2.データ型２</v>
       </c>
-      <c r="D33" s="118" t="s">
+      <c r="D33" s="123" t="s">
         <v>106</v>
       </c>
-      <c r="E33" s="119"/>
-      <c r="F33" s="120"/>
+      <c r="E33" s="124"/>
+      <c r="F33" s="125"/>
       <c r="G33" s="48" t="s">
         <v>41</v>
       </c>
@@ -7386,16 +7399,16 @@
     </row>
     <row r="34" spans="1:14" ht="37.799999999999997">
       <c r="A34" s="11"/>
-      <c r="B34" s="125"/>
+      <c r="B34" s="118"/>
       <c r="C34" s="48" t="str">
         <f>master!C15</f>
         <v>2.3.リレーション</v>
       </c>
-      <c r="D34" s="118" t="s">
+      <c r="D34" s="123" t="s">
         <v>107</v>
       </c>
-      <c r="E34" s="119"/>
-      <c r="F34" s="120"/>
+      <c r="E34" s="124"/>
+      <c r="F34" s="125"/>
       <c r="G34" s="48" t="s">
         <v>41</v>
       </c>
@@ -7413,16 +7426,16 @@
     </row>
     <row r="35" spans="1:14" ht="37.799999999999997">
       <c r="A35" s="11"/>
-      <c r="B35" s="126"/>
+      <c r="B35" s="119"/>
       <c r="C35" s="48" t="str">
         <f>master!C16</f>
         <v>2.4.データを結合して取得（Join）</v>
       </c>
-      <c r="D35" s="118" t="s">
+      <c r="D35" s="123" t="s">
         <v>108</v>
       </c>
-      <c r="E35" s="119"/>
-      <c r="F35" s="120"/>
+      <c r="E35" s="124"/>
+      <c r="F35" s="125"/>
       <c r="G35" s="48" t="s">
         <v>41</v>
       </c>
@@ -7440,7 +7453,7 @@
     </row>
     <row r="36" spans="1:14" ht="88.2">
       <c r="A36" s="11"/>
-      <c r="B36" s="124" t="str">
+      <c r="B36" s="117" t="str">
         <f>master!B17</f>
         <v>Java言語、Springフレームワークとは</v>
       </c>
@@ -7448,11 +7461,11 @@
         <f>master!C17</f>
         <v>Webアプリケーションを作成するためのプログラミング言語</v>
       </c>
-      <c r="D36" s="118" t="s">
+      <c r="D36" s="123" t="s">
         <v>109</v>
       </c>
-      <c r="E36" s="119"/>
-      <c r="F36" s="120"/>
+      <c r="E36" s="124"/>
+      <c r="F36" s="125"/>
       <c r="G36" s="48" t="s">
         <v>45</v>
       </c>
@@ -7470,16 +7483,16 @@
     </row>
     <row r="37" spans="1:14" ht="75.599999999999994">
       <c r="A37" s="11"/>
-      <c r="B37" s="125"/>
+      <c r="B37" s="118"/>
       <c r="C37" s="48" t="str">
         <f>master!C18</f>
         <v>Java</v>
       </c>
-      <c r="D37" s="118" t="s">
+      <c r="D37" s="123" t="s">
         <v>110</v>
       </c>
-      <c r="E37" s="119"/>
-      <c r="F37" s="120"/>
+      <c r="E37" s="124"/>
+      <c r="F37" s="125"/>
       <c r="G37" s="48" t="s">
         <v>43</v>
       </c>
@@ -7497,16 +7510,16 @@
     </row>
     <row r="38" spans="1:14" ht="75.599999999999994">
       <c r="A38" s="11"/>
-      <c r="B38" s="125"/>
+      <c r="B38" s="118"/>
       <c r="C38" s="48" t="str">
         <f>master!C19</f>
         <v>Java言語の構成要素</v>
       </c>
-      <c r="D38" s="118" t="s">
+      <c r="D38" s="123" t="s">
         <v>111</v>
       </c>
-      <c r="E38" s="119"/>
-      <c r="F38" s="120"/>
+      <c r="E38" s="124"/>
+      <c r="F38" s="125"/>
       <c r="G38" s="48" t="s">
         <v>43</v>
       </c>
@@ -7524,16 +7537,16 @@
     </row>
     <row r="39" spans="1:14" ht="50.4">
       <c r="A39" s="11"/>
-      <c r="B39" s="125"/>
+      <c r="B39" s="118"/>
       <c r="C39" s="48" t="str">
         <f>master!C20</f>
         <v>Webアプリケーションを構成するクラス</v>
       </c>
-      <c r="D39" s="118" t="s">
+      <c r="D39" s="123" t="s">
         <v>112</v>
       </c>
-      <c r="E39" s="119"/>
-      <c r="F39" s="120"/>
+      <c r="E39" s="124"/>
+      <c r="F39" s="125"/>
       <c r="G39" s="48" t="s">
         <v>42</v>
       </c>
@@ -7551,16 +7564,16 @@
     </row>
     <row r="40" spans="1:14" ht="88.2">
       <c r="A40" s="11"/>
-      <c r="B40" s="125"/>
+      <c r="B40" s="118"/>
       <c r="C40" s="48" t="str">
         <f>master!C21</f>
         <v>Nレイヤーアーキテクチャ</v>
       </c>
-      <c r="D40" s="118" t="s">
+      <c r="D40" s="123" t="s">
         <v>114</v>
       </c>
-      <c r="E40" s="119"/>
-      <c r="F40" s="120"/>
+      <c r="E40" s="124"/>
+      <c r="F40" s="125"/>
       <c r="G40" s="48" t="s">
         <v>45</v>
       </c>
@@ -7580,22 +7593,22 @@
     </row>
     <row r="41" spans="1:14" ht="201.6">
       <c r="A41" s="11"/>
-      <c r="B41" s="125"/>
+      <c r="B41" s="118"/>
       <c r="C41" s="48" t="str">
         <f>master!C22</f>
         <v>View と Controller と Service と Repository</v>
       </c>
-      <c r="D41" s="118" t="s">
+      <c r="D41" s="123" t="s">
         <v>115</v>
       </c>
-      <c r="E41" s="119"/>
-      <c r="F41" s="120"/>
+      <c r="E41" s="124"/>
+      <c r="F41" s="125"/>
       <c r="G41" s="48" t="s">
         <v>116</v>
       </c>
       <c r="H41" s="12"/>
       <c r="I41" s="46" t="s">
-        <v>48</v>
+        <v>24</v>
       </c>
       <c r="J41" s="44">
         <v>3.472222222222222E-3</v>
@@ -7607,16 +7620,16 @@
     </row>
     <row r="42" spans="1:14" ht="37.799999999999997">
       <c r="A42" s="11"/>
-      <c r="B42" s="125"/>
+      <c r="B42" s="118"/>
       <c r="C42" s="48" t="str">
         <f>master!C23</f>
         <v>Nレイヤーアーキテクチャ</v>
       </c>
-      <c r="D42" s="118" t="s">
+      <c r="D42" s="123" t="s">
         <v>117</v>
       </c>
-      <c r="E42" s="119"/>
-      <c r="F42" s="120"/>
+      <c r="E42" s="124"/>
+      <c r="F42" s="125"/>
       <c r="G42" s="48" t="s">
         <v>41</v>
       </c>
@@ -7634,16 +7647,16 @@
     </row>
     <row r="43" spans="1:14" ht="163.80000000000001">
       <c r="A43" s="11"/>
-      <c r="B43" s="125"/>
+      <c r="B43" s="118"/>
       <c r="C43" s="48" t="str">
         <f>master!C24</f>
         <v>Webアプリケーション フレームワーク</v>
       </c>
-      <c r="D43" s="118" t="s">
+      <c r="D43" s="123" t="s">
         <v>118</v>
       </c>
-      <c r="E43" s="119"/>
-      <c r="F43" s="120"/>
+      <c r="E43" s="124"/>
+      <c r="F43" s="125"/>
       <c r="G43" s="48" t="s">
         <v>119</v>
       </c>
@@ -7661,16 +7674,16 @@
     </row>
     <row r="44" spans="1:14" ht="25.2">
       <c r="A44" s="11"/>
-      <c r="B44" s="125"/>
+      <c r="B44" s="118"/>
       <c r="C44" s="48" t="str">
         <f>master!C25</f>
         <v>Java向けWebアプリケーションフレームワーク</v>
       </c>
-      <c r="D44" s="118" t="s">
+      <c r="D44" s="123" t="s">
         <v>120</v>
       </c>
-      <c r="E44" s="119"/>
-      <c r="F44" s="120"/>
+      <c r="E44" s="124"/>
+      <c r="F44" s="125"/>
       <c r="G44" s="48" t="s">
         <v>46</v>
       </c>
@@ -7688,16 +7701,16 @@
     </row>
     <row r="45" spans="1:14" ht="189">
       <c r="A45" s="11"/>
-      <c r="B45" s="125"/>
+      <c r="B45" s="118"/>
       <c r="C45" s="48" t="str">
         <f>master!C26</f>
         <v>Springフレームワーク</v>
       </c>
-      <c r="D45" s="118" t="s">
+      <c r="D45" s="123" t="s">
         <v>121</v>
       </c>
-      <c r="E45" s="119"/>
-      <c r="F45" s="120"/>
+      <c r="E45" s="124"/>
+      <c r="F45" s="125"/>
       <c r="G45" s="48" t="s">
         <v>122</v>
       </c>
@@ -7715,16 +7728,16 @@
     </row>
     <row r="46" spans="1:14" ht="88.2">
       <c r="A46" s="11"/>
-      <c r="B46" s="125"/>
+      <c r="B46" s="118"/>
       <c r="C46" s="48" t="str">
         <f>master!C27</f>
         <v>Springフレームワーク：DIコンテナとは</v>
       </c>
-      <c r="D46" s="118" t="s">
+      <c r="D46" s="123" t="s">
         <v>123</v>
       </c>
-      <c r="E46" s="119"/>
-      <c r="F46" s="120"/>
+      <c r="E46" s="124"/>
+      <c r="F46" s="125"/>
       <c r="G46" s="48" t="s">
         <v>45</v>
       </c>
@@ -7744,16 +7757,16 @@
     </row>
     <row r="47" spans="1:14" ht="63">
       <c r="A47" s="11"/>
-      <c r="B47" s="125"/>
+      <c r="B47" s="118"/>
       <c r="C47" s="48" t="str">
         <f>master!C28</f>
         <v>DIコンテナ：DIコンテナが部品を注入する</v>
       </c>
-      <c r="D47" s="118" t="s">
+      <c r="D47" s="123" t="s">
         <v>124</v>
       </c>
-      <c r="E47" s="119"/>
-      <c r="F47" s="120"/>
+      <c r="E47" s="124"/>
+      <c r="F47" s="125"/>
       <c r="G47" s="48" t="s">
         <v>40</v>
       </c>
@@ -7771,16 +7784,16 @@
     </row>
     <row r="48" spans="1:14" ht="100.8">
       <c r="A48" s="11"/>
-      <c r="B48" s="125"/>
+      <c r="B48" s="118"/>
       <c r="C48" s="48" t="str">
         <f>master!C29</f>
         <v>DIコンテナ：DIコンテナによる部品と注入対象になるための目印</v>
       </c>
-      <c r="D48" s="118" t="s">
+      <c r="D48" s="123" t="s">
         <v>125</v>
       </c>
-      <c r="E48" s="119"/>
-      <c r="F48" s="120"/>
+      <c r="E48" s="124"/>
+      <c r="F48" s="125"/>
       <c r="G48" s="48" t="s">
         <v>47</v>
       </c>
@@ -7798,16 +7811,16 @@
     </row>
     <row r="49" spans="1:14" ht="100.8">
       <c r="A49" s="11"/>
-      <c r="B49" s="125"/>
+      <c r="B49" s="118"/>
       <c r="C49" s="48" t="str">
         <f>master!C30</f>
         <v>Springフレームワークにおける部品の設定</v>
       </c>
-      <c r="D49" s="118" t="s">
+      <c r="D49" s="123" t="s">
         <v>126</v>
       </c>
-      <c r="E49" s="119"/>
-      <c r="F49" s="120"/>
+      <c r="E49" s="124"/>
+      <c r="F49" s="125"/>
       <c r="G49" s="48" t="s">
         <v>47</v>
       </c>
@@ -7825,16 +7838,16 @@
     </row>
     <row r="50" spans="1:14" ht="88.2">
       <c r="A50" s="11"/>
-      <c r="B50" s="125"/>
+      <c r="B50" s="118"/>
       <c r="C50" s="48" t="str">
         <f>master!C31</f>
         <v>Spring Boot</v>
       </c>
-      <c r="D50" s="118" t="s">
+      <c r="D50" s="123" t="s">
         <v>127</v>
       </c>
-      <c r="E50" s="119"/>
-      <c r="F50" s="120"/>
+      <c r="E50" s="124"/>
+      <c r="F50" s="125"/>
       <c r="G50" s="48" t="s">
         <v>45</v>
       </c>
@@ -7852,16 +7865,16 @@
     </row>
     <row r="51" spans="1:14" ht="63">
       <c r="A51" s="11"/>
-      <c r="B51" s="125"/>
+      <c r="B51" s="118"/>
       <c r="C51" s="48" t="str">
         <f>master!C32</f>
         <v>Spring Boot：オートコンフィグレーション</v>
       </c>
-      <c r="D51" s="118" t="s">
+      <c r="D51" s="123" t="s">
         <v>128</v>
       </c>
-      <c r="E51" s="119"/>
-      <c r="F51" s="120"/>
+      <c r="E51" s="124"/>
+      <c r="F51" s="125"/>
       <c r="G51" s="48" t="s">
         <v>40</v>
       </c>
@@ -7879,16 +7892,16 @@
     </row>
     <row r="52" spans="1:14" ht="50.4">
       <c r="A52" s="11"/>
-      <c r="B52" s="125"/>
+      <c r="B52" s="118"/>
       <c r="C52" s="48" t="str">
         <f>master!C33</f>
         <v>Spring Boot：Starters</v>
       </c>
-      <c r="D52" s="118" t="s">
+      <c r="D52" s="123" t="s">
         <v>129</v>
       </c>
-      <c r="E52" s="119"/>
-      <c r="F52" s="120"/>
+      <c r="E52" s="124"/>
+      <c r="F52" s="125"/>
       <c r="G52" s="48" t="s">
         <v>42</v>
       </c>
@@ -7906,16 +7919,16 @@
     </row>
     <row r="53" spans="1:14" ht="88.2">
       <c r="A53" s="11"/>
-      <c r="B53" s="125"/>
+      <c r="B53" s="118"/>
       <c r="C53" s="48" t="str">
         <f>master!C34</f>
         <v>Spring Boot：組込みWebAPサーバ</v>
       </c>
-      <c r="D53" s="118" t="s">
+      <c r="D53" s="123" t="s">
         <v>130</v>
       </c>
-      <c r="E53" s="119"/>
-      <c r="F53" s="120"/>
+      <c r="E53" s="124"/>
+      <c r="F53" s="125"/>
       <c r="G53" s="48" t="s">
         <v>45</v>
       </c>
@@ -7933,14 +7946,14 @@
     </row>
     <row r="54" spans="1:14" ht="25.2">
       <c r="A54" s="11"/>
-      <c r="B54" s="126"/>
+      <c r="B54" s="119"/>
       <c r="C54" s="48" t="str">
         <f>master!C35</f>
         <v>おすすめ書籍：『プロになるためのSpring入門』</v>
       </c>
-      <c r="D54" s="118"/>
-      <c r="E54" s="119"/>
-      <c r="F54" s="120"/>
+      <c r="D54" s="123"/>
+      <c r="E54" s="124"/>
+      <c r="F54" s="125"/>
       <c r="G54" s="48" t="s">
         <v>46</v>
       </c>
@@ -7958,7 +7971,7 @@
     </row>
     <row r="55" spans="1:14" ht="37.799999999999997">
       <c r="A55" s="11"/>
-      <c r="B55" s="121" t="str">
+      <c r="B55" s="120" t="str">
         <f>master!B37</f>
         <v>課題1の導入</v>
       </c>
@@ -7966,11 +7979,11 @@
         <f>master!C37</f>
         <v>演習課題の概要</v>
       </c>
-      <c r="D55" s="112" t="s">
+      <c r="D55" s="114" t="s">
         <v>163</v>
       </c>
-      <c r="E55" s="113"/>
-      <c r="F55" s="114"/>
+      <c r="E55" s="115"/>
+      <c r="F55" s="116"/>
       <c r="G55" s="58" t="s">
         <v>283</v>
       </c>
@@ -7988,16 +8001,16 @@
     </row>
     <row r="56" spans="1:14" ht="37.799999999999997">
       <c r="A56" s="11"/>
-      <c r="B56" s="122"/>
+      <c r="B56" s="121"/>
       <c r="C56" s="58" t="str">
         <f>master!C38</f>
         <v>作成物</v>
       </c>
-      <c r="D56" s="112" t="s">
+      <c r="D56" s="114" t="s">
         <v>164</v>
       </c>
-      <c r="E56" s="113"/>
-      <c r="F56" s="114"/>
+      <c r="E56" s="115"/>
+      <c r="F56" s="116"/>
       <c r="G56" s="58" t="s">
         <v>283</v>
       </c>
@@ -8015,16 +8028,16 @@
     </row>
     <row r="57" spans="1:14" ht="75.599999999999994">
       <c r="A57" s="11"/>
-      <c r="B57" s="123"/>
+      <c r="B57" s="122"/>
       <c r="C57" s="58" t="str">
         <f>master!C39</f>
         <v>演習課題の進め方</v>
       </c>
-      <c r="D57" s="112" t="s">
+      <c r="D57" s="114" t="s">
         <v>165</v>
       </c>
-      <c r="E57" s="113"/>
-      <c r="F57" s="114"/>
+      <c r="E57" s="115"/>
+      <c r="F57" s="116"/>
       <c r="G57" s="58" t="s">
         <v>284</v>
       </c>
@@ -8042,7 +8055,7 @@
     </row>
     <row r="58" spans="1:14" ht="15" customHeight="1">
       <c r="A58" s="11"/>
-      <c r="B58" s="121" t="str">
+      <c r="B58" s="120" t="str">
         <f>master!B40</f>
         <v>Spring Bootプロジェクトの_x000B_準備、起動確認</v>
       </c>
@@ -8050,9 +8063,9 @@
         <f>master!C40</f>
         <v>前提条件</v>
       </c>
-      <c r="D58" s="112"/>
-      <c r="E58" s="113"/>
-      <c r="F58" s="114"/>
+      <c r="D58" s="114"/>
+      <c r="E58" s="115"/>
+      <c r="F58" s="116"/>
       <c r="G58" s="58" t="s">
         <v>285</v>
       </c>
@@ -8070,16 +8083,16 @@
     </row>
     <row r="59" spans="1:14" ht="37.799999999999997">
       <c r="A59" s="11"/>
-      <c r="B59" s="122"/>
+      <c r="B59" s="121"/>
       <c r="C59" s="58" t="str">
         <f>master!C41</f>
         <v>Spring Bootプロジェクトの準備</v>
       </c>
-      <c r="D59" s="112" t="s">
+      <c r="D59" s="114" t="s">
         <v>166</v>
       </c>
-      <c r="E59" s="113"/>
-      <c r="F59" s="114"/>
+      <c r="E59" s="115"/>
+      <c r="F59" s="116"/>
       <c r="G59" s="58" t="s">
         <v>283</v>
       </c>
@@ -8097,16 +8110,16 @@
     </row>
     <row r="60" spans="1:14" ht="25.2">
       <c r="A60" s="11"/>
-      <c r="B60" s="122"/>
+      <c r="B60" s="121"/>
       <c r="C60" s="58" t="str">
         <f>master!C42</f>
         <v>（補足）Spring Bootプロジェクトの準備</v>
       </c>
-      <c r="D60" s="112" t="s">
+      <c r="D60" s="114" t="s">
         <v>167</v>
       </c>
-      <c r="E60" s="113"/>
-      <c r="F60" s="114"/>
+      <c r="E60" s="115"/>
+      <c r="F60" s="116"/>
       <c r="G60" s="58" t="s">
         <v>286</v>
       </c>
@@ -8124,22 +8137,22 @@
     </row>
     <row r="61" spans="1:14" ht="88.2">
       <c r="A61" s="11"/>
-      <c r="B61" s="123"/>
+      <c r="B61" s="122"/>
       <c r="C61" s="58" t="str">
         <f>master!C43</f>
         <v>Spring Bootアプリケーションの起動確認</v>
       </c>
-      <c r="D61" s="112" t="s">
+      <c r="D61" s="114" t="s">
         <v>189</v>
       </c>
-      <c r="E61" s="113"/>
-      <c r="F61" s="114"/>
+      <c r="E61" s="115"/>
+      <c r="F61" s="116"/>
       <c r="G61" s="58" t="s">
         <v>287</v>
       </c>
       <c r="H61" s="59"/>
       <c r="I61" s="60" t="s">
-        <v>48</v>
+        <v>24</v>
       </c>
       <c r="J61" s="61">
         <v>6.9444444444444441E-3</v>
@@ -8151,7 +8164,7 @@
     </row>
     <row r="62" spans="1:14" ht="50.4">
       <c r="A62" s="11"/>
-      <c r="B62" s="121" t="str">
+      <c r="B62" s="120" t="str">
         <f>master!B44</f>
         <v>ECサイト Webアプリの要件</v>
       </c>
@@ -8159,11 +8172,11 @@
         <f>master!C44</f>
         <v>ECサイト Webアプリの要件 – はじめに</v>
       </c>
-      <c r="D62" s="112" t="s">
+      <c r="D62" s="114" t="s">
         <v>168</v>
       </c>
-      <c r="E62" s="113"/>
-      <c r="F62" s="114"/>
+      <c r="E62" s="115"/>
+      <c r="F62" s="116"/>
       <c r="G62" s="58" t="s">
         <v>288</v>
       </c>
@@ -8181,16 +8194,16 @@
     </row>
     <row r="63" spans="1:14" ht="151.19999999999999">
       <c r="A63" s="11"/>
-      <c r="B63" s="122"/>
+      <c r="B63" s="121"/>
       <c r="C63" s="58" t="str">
         <f>master!C45</f>
         <v>ECサイト Webアプリの要件➊ 画面</v>
       </c>
-      <c r="D63" s="112" t="s">
+      <c r="D63" s="114" t="s">
         <v>170</v>
       </c>
-      <c r="E63" s="113"/>
-      <c r="F63" s="114"/>
+      <c r="E63" s="115"/>
+      <c r="F63" s="116"/>
       <c r="G63" s="58" t="s">
         <v>289</v>
       </c>
@@ -8208,16 +8221,16 @@
     </row>
     <row r="64" spans="1:14" ht="214.2">
       <c r="A64" s="11"/>
-      <c r="B64" s="122"/>
+      <c r="B64" s="121"/>
       <c r="C64" s="58" t="str">
         <f>master!C46</f>
         <v>ECサイト Webアプリの要件➋ 機能</v>
       </c>
-      <c r="D64" s="112" t="s">
+      <c r="D64" s="114" t="s">
         <v>171</v>
       </c>
-      <c r="E64" s="113"/>
-      <c r="F64" s="114"/>
+      <c r="E64" s="115"/>
+      <c r="F64" s="116"/>
       <c r="G64" s="58" t="s">
         <v>290</v>
       </c>
@@ -8235,16 +8248,16 @@
     </row>
     <row r="65" spans="1:14" ht="63">
       <c r="A65" s="11"/>
-      <c r="B65" s="122"/>
+      <c r="B65" s="121"/>
       <c r="C65" s="58" t="str">
         <f>master!C47</f>
         <v>ECサイト Webアプリの要件➌ 画面遷移</v>
       </c>
-      <c r="D65" s="112" t="s">
+      <c r="D65" s="114" t="s">
         <v>172</v>
       </c>
-      <c r="E65" s="113"/>
-      <c r="F65" s="114"/>
+      <c r="E65" s="115"/>
+      <c r="F65" s="116"/>
       <c r="G65" s="58" t="s">
         <v>291</v>
       </c>
@@ -8262,16 +8275,16 @@
     </row>
     <row r="66" spans="1:14" ht="163.80000000000001">
       <c r="A66" s="11"/>
-      <c r="B66" s="122"/>
+      <c r="B66" s="121"/>
       <c r="C66" s="58" t="str">
         <f>master!C48</f>
         <v>ECサイト Webアプリの要件❹ データ設計</v>
       </c>
-      <c r="D66" s="112" t="s">
+      <c r="D66" s="114" t="s">
         <v>174</v>
       </c>
-      <c r="E66" s="113"/>
-      <c r="F66" s="114"/>
+      <c r="E66" s="115"/>
+      <c r="F66" s="116"/>
       <c r="G66" s="58" t="s">
         <v>292</v>
       </c>
@@ -8289,16 +8302,16 @@
     </row>
     <row r="67" spans="1:14" ht="50.4">
       <c r="A67" s="11"/>
-      <c r="B67" s="122"/>
+      <c r="B67" s="121"/>
       <c r="C67" s="58" t="str">
         <f>master!C49</f>
         <v>ECサイト Webアプリの要件❺ 初期データ</v>
       </c>
-      <c r="D67" s="112" t="s">
+      <c r="D67" s="114" t="s">
         <v>175</v>
       </c>
-      <c r="E67" s="113"/>
-      <c r="F67" s="114"/>
+      <c r="E67" s="115"/>
+      <c r="F67" s="116"/>
       <c r="G67" s="58" t="s">
         <v>288</v>
       </c>
@@ -8316,16 +8329,16 @@
     </row>
     <row r="68" spans="1:14" ht="37.799999999999997">
       <c r="A68" s="11"/>
-      <c r="B68" s="122"/>
+      <c r="B68" s="121"/>
       <c r="C68" s="58" t="str">
         <f>master!C50</f>
         <v>ECサイト Webアプリの要件❻ ディレクトリ構成</v>
       </c>
-      <c r="D68" s="112" t="s">
+      <c r="D68" s="114" t="s">
         <v>176</v>
       </c>
-      <c r="E68" s="113"/>
-      <c r="F68" s="114"/>
+      <c r="E68" s="115"/>
+      <c r="F68" s="116"/>
       <c r="G68" s="58" t="s">
         <v>283</v>
       </c>
@@ -8343,16 +8356,16 @@
     </row>
     <row r="69" spans="1:14" ht="37.799999999999997">
       <c r="A69" s="11"/>
-      <c r="B69" s="122"/>
+      <c r="B69" s="121"/>
       <c r="C69" s="58" t="str">
         <f>master!C51</f>
         <v>ECサイト Webアプリの要件❼ パッケージ構成</v>
       </c>
-      <c r="D69" s="112" t="s">
+      <c r="D69" s="114" t="s">
         <v>178</v>
       </c>
-      <c r="E69" s="113"/>
-      <c r="F69" s="114"/>
+      <c r="E69" s="115"/>
+      <c r="F69" s="116"/>
       <c r="G69" s="58" t="s">
         <v>283</v>
       </c>
@@ -8370,16 +8383,16 @@
     </row>
     <row r="70" spans="1:14" ht="37.799999999999997">
       <c r="A70" s="11"/>
-      <c r="B70" s="123"/>
+      <c r="B70" s="122"/>
       <c r="C70" s="58" t="str">
         <f>master!C52</f>
         <v>ECサイト Webアプリの要件❽ リソース構成</v>
       </c>
-      <c r="D70" s="112" t="s">
+      <c r="D70" s="114" t="s">
         <v>177</v>
       </c>
-      <c r="E70" s="113"/>
-      <c r="F70" s="114"/>
+      <c r="E70" s="115"/>
+      <c r="F70" s="116"/>
       <c r="G70" s="58" t="s">
         <v>283</v>
       </c>
@@ -8397,7 +8410,7 @@
     </row>
     <row r="71" spans="1:14" ht="25.2">
       <c r="A71" s="11"/>
-      <c r="B71" s="121" t="str">
+      <c r="B71" s="120" t="str">
         <f>master!B53</f>
         <v>ハンズオン</v>
       </c>
@@ -8405,11 +8418,11 @@
         <f>master!C53</f>
         <v>バイブコーディング – はじめに</v>
       </c>
-      <c r="D71" s="112" t="s">
+      <c r="D71" s="114" t="s">
         <v>179</v>
       </c>
-      <c r="E71" s="113"/>
-      <c r="F71" s="114"/>
+      <c r="E71" s="115"/>
+      <c r="F71" s="116"/>
       <c r="G71" s="58" t="s">
         <v>286</v>
       </c>
@@ -8427,16 +8440,16 @@
     </row>
     <row r="72" spans="1:14" ht="138.6">
       <c r="A72" s="11"/>
-      <c r="B72" s="122"/>
+      <c r="B72" s="121"/>
       <c r="C72" s="58" t="str">
         <f>master!C54</f>
         <v>[構造理解] Webアプリケーションで必要なもの</v>
       </c>
-      <c r="D72" s="112" t="s">
+      <c r="D72" s="114" t="s">
         <v>180</v>
       </c>
-      <c r="E72" s="113"/>
-      <c r="F72" s="114"/>
+      <c r="E72" s="115"/>
+      <c r="F72" s="116"/>
       <c r="G72" s="58" t="s">
         <v>293</v>
       </c>
@@ -8454,16 +8467,16 @@
     </row>
     <row r="73" spans="1:14" ht="50.4">
       <c r="A73" s="11"/>
-      <c r="B73" s="122"/>
+      <c r="B73" s="121"/>
       <c r="C73" s="76" t="str">
         <f>master!C55</f>
         <v>バイブコーディング➊ 画面モックアップを作ってデザインを決める</v>
       </c>
-      <c r="D73" s="112" t="s">
+      <c r="D73" s="114" t="s">
         <v>190</v>
       </c>
-      <c r="E73" s="113"/>
-      <c r="F73" s="114"/>
+      <c r="E73" s="115"/>
+      <c r="F73" s="116"/>
       <c r="G73" s="58" t="s">
         <v>288</v>
       </c>
@@ -8481,38 +8494,38 @@
     </row>
     <row r="74" spans="1:14" ht="88.2" customHeight="1">
       <c r="A74" s="11"/>
-      <c r="B74" s="122"/>
+      <c r="B74" s="121"/>
       <c r="C74" s="77"/>
-      <c r="D74" s="131" t="s">
+      <c r="D74" s="129" t="s">
         <v>181</v>
       </c>
-      <c r="E74" s="132"/>
-      <c r="F74" s="133"/>
-      <c r="G74" s="130" t="s">
+      <c r="E74" s="130"/>
+      <c r="F74" s="131"/>
+      <c r="G74" s="93" t="s">
         <v>287</v>
       </c>
-      <c r="H74" s="134"/>
-      <c r="I74" s="135"/>
-      <c r="J74" s="136">
+      <c r="H74" s="94"/>
+      <c r="I74" s="95"/>
+      <c r="J74" s="96">
         <v>3.472222222222222E-3</v>
       </c>
-      <c r="K74" s="137"/>
+      <c r="K74" s="97"/>
       <c r="L74" s="6"/>
       <c r="M74" s="6"/>
       <c r="N74" s="6"/>
     </row>
     <row r="75" spans="1:14" ht="50.4">
       <c r="A75" s="11"/>
-      <c r="B75" s="122"/>
+      <c r="B75" s="121"/>
       <c r="C75" s="76" t="str">
         <f>master!C56</f>
         <v>バイブコーディング➋ データベースのテーブルを準備する</v>
       </c>
-      <c r="D75" s="112" t="s">
+      <c r="D75" s="114" t="s">
         <v>194</v>
       </c>
-      <c r="E75" s="113"/>
-      <c r="F75" s="114"/>
+      <c r="E75" s="115"/>
+      <c r="F75" s="116"/>
       <c r="G75" s="58" t="s">
         <v>288</v>
       </c>
@@ -8530,38 +8543,38 @@
     </row>
     <row r="76" spans="1:14" ht="88.2">
       <c r="A76" s="11"/>
-      <c r="B76" s="122"/>
+      <c r="B76" s="121"/>
       <c r="C76" s="77"/>
-      <c r="D76" s="131" t="s">
+      <c r="D76" s="129" t="s">
         <v>181</v>
       </c>
-      <c r="E76" s="132"/>
-      <c r="F76" s="133"/>
-      <c r="G76" s="130" t="s">
+      <c r="E76" s="130"/>
+      <c r="F76" s="131"/>
+      <c r="G76" s="93" t="s">
         <v>287</v>
       </c>
-      <c r="H76" s="134"/>
-      <c r="I76" s="135"/>
-      <c r="J76" s="136">
+      <c r="H76" s="94"/>
+      <c r="I76" s="95"/>
+      <c r="J76" s="96">
         <v>3.472222222222222E-3</v>
       </c>
-      <c r="K76" s="137"/>
+      <c r="K76" s="97"/>
       <c r="L76" s="6"/>
       <c r="M76" s="6"/>
       <c r="N76" s="6"/>
     </row>
     <row r="77" spans="1:14" ht="50.4">
       <c r="A77" s="11"/>
-      <c r="B77" s="122"/>
+      <c r="B77" s="121"/>
       <c r="C77" s="76" t="str">
         <f>master!C57</f>
         <v>バイブコーディング➌ データベースのデータを準備する</v>
       </c>
-      <c r="D77" s="112" t="s">
+      <c r="D77" s="114" t="s">
         <v>193</v>
       </c>
-      <c r="E77" s="113"/>
-      <c r="F77" s="114"/>
+      <c r="E77" s="115"/>
+      <c r="F77" s="116"/>
       <c r="G77" s="58" t="s">
         <v>288</v>
       </c>
@@ -8579,38 +8592,38 @@
     </row>
     <row r="78" spans="1:14" ht="88.2">
       <c r="A78" s="11"/>
-      <c r="B78" s="122"/>
+      <c r="B78" s="121"/>
       <c r="C78" s="77"/>
-      <c r="D78" s="131" t="s">
+      <c r="D78" s="129" t="s">
         <v>181</v>
       </c>
-      <c r="E78" s="132"/>
-      <c r="F78" s="133"/>
-      <c r="G78" s="130" t="s">
+      <c r="E78" s="130"/>
+      <c r="F78" s="131"/>
+      <c r="G78" s="93" t="s">
         <v>287</v>
       </c>
-      <c r="H78" s="134"/>
-      <c r="I78" s="135"/>
-      <c r="J78" s="136">
+      <c r="H78" s="94"/>
+      <c r="I78" s="95"/>
+      <c r="J78" s="96">
         <v>3.472222222222222E-3</v>
       </c>
-      <c r="K78" s="137"/>
+      <c r="K78" s="97"/>
       <c r="L78" s="6"/>
       <c r="M78" s="6"/>
       <c r="N78" s="6"/>
     </row>
     <row r="79" spans="1:14" ht="63">
       <c r="A79" s="11"/>
-      <c r="B79" s="122"/>
+      <c r="B79" s="121"/>
       <c r="C79" s="76" t="str">
         <f>master!C58</f>
         <v>バイブコーディング❹ データベース処理とビジネスロジックを作る</v>
       </c>
-      <c r="D79" s="112" t="s">
+      <c r="D79" s="114" t="s">
         <v>192</v>
       </c>
-      <c r="E79" s="113"/>
-      <c r="F79" s="114"/>
+      <c r="E79" s="115"/>
+      <c r="F79" s="116"/>
       <c r="G79" s="58" t="s">
         <v>291</v>
       </c>
@@ -8628,38 +8641,38 @@
     </row>
     <row r="80" spans="1:14" ht="88.2">
       <c r="A80" s="11"/>
-      <c r="B80" s="122"/>
+      <c r="B80" s="121"/>
       <c r="C80" s="77"/>
-      <c r="D80" s="131" t="s">
+      <c r="D80" s="129" t="s">
         <v>181</v>
       </c>
-      <c r="E80" s="132"/>
-      <c r="F80" s="133"/>
-      <c r="G80" s="130" t="s">
+      <c r="E80" s="130"/>
+      <c r="F80" s="131"/>
+      <c r="G80" s="93" t="s">
         <v>287</v>
       </c>
-      <c r="H80" s="134"/>
-      <c r="I80" s="135"/>
-      <c r="J80" s="136">
+      <c r="H80" s="94"/>
+      <c r="I80" s="95"/>
+      <c r="J80" s="96">
         <v>3.472222222222222E-3</v>
       </c>
-      <c r="K80" s="137"/>
+      <c r="K80" s="97"/>
       <c r="L80" s="6"/>
       <c r="M80" s="6"/>
       <c r="N80" s="6"/>
     </row>
     <row r="81" spans="1:14" ht="50.4">
       <c r="A81" s="11"/>
-      <c r="B81" s="122"/>
+      <c r="B81" s="121"/>
       <c r="C81" s="58" t="str">
         <f>master!C59</f>
         <v>[解説] RepositoryクラスとSQLの例（抜粋）</v>
       </c>
-      <c r="D81" s="112" t="s">
+      <c r="D81" s="114" t="s">
         <v>182</v>
       </c>
-      <c r="E81" s="113"/>
-      <c r="F81" s="114"/>
+      <c r="E81" s="115"/>
+      <c r="F81" s="116"/>
       <c r="G81" s="58" t="s">
         <v>288</v>
       </c>
@@ -8677,16 +8690,16 @@
     </row>
     <row r="82" spans="1:14" ht="50.4">
       <c r="A82" s="11"/>
-      <c r="B82" s="122"/>
+      <c r="B82" s="121"/>
       <c r="C82" s="58" t="str">
         <f>master!C60</f>
         <v>[解説] Entity/Modelクラスの例（抜粋）</v>
       </c>
-      <c r="D82" s="112" t="s">
+      <c r="D82" s="114" t="s">
         <v>183</v>
       </c>
-      <c r="E82" s="113"/>
-      <c r="F82" s="114"/>
+      <c r="E82" s="115"/>
+      <c r="F82" s="116"/>
       <c r="G82" s="58" t="s">
         <v>288</v>
       </c>
@@ -8704,16 +8717,16 @@
     </row>
     <row r="83" spans="1:14" ht="37.799999999999997">
       <c r="A83" s="11"/>
-      <c r="B83" s="122"/>
+      <c r="B83" s="121"/>
       <c r="C83" s="58" t="str">
         <f>master!C61</f>
         <v>[解説] Serviceクラスの例（抜粋）</v>
       </c>
-      <c r="D83" s="112" t="s">
+      <c r="D83" s="114" t="s">
         <v>184</v>
       </c>
-      <c r="E83" s="113"/>
-      <c r="F83" s="114"/>
+      <c r="E83" s="115"/>
+      <c r="F83" s="116"/>
       <c r="G83" s="58" t="s">
         <v>283</v>
       </c>
@@ -8731,16 +8744,16 @@
     </row>
     <row r="84" spans="1:14" ht="50.4">
       <c r="A84" s="11"/>
-      <c r="B84" s="122"/>
+      <c r="B84" s="121"/>
       <c r="C84" s="76" t="str">
         <f>master!C62</f>
         <v>バイブコーディング❺ モックアップをもとに画面表示/処理を作る</v>
       </c>
-      <c r="D84" s="112" t="s">
+      <c r="D84" s="114" t="s">
         <v>191</v>
       </c>
-      <c r="E84" s="113"/>
-      <c r="F84" s="114"/>
+      <c r="E84" s="115"/>
+      <c r="F84" s="116"/>
       <c r="G84" s="58" t="s">
         <v>288</v>
       </c>
@@ -8758,38 +8771,38 @@
     </row>
     <row r="85" spans="1:14" ht="88.2">
       <c r="A85" s="11"/>
-      <c r="B85" s="122"/>
+      <c r="B85" s="121"/>
       <c r="C85" s="77"/>
-      <c r="D85" s="131" t="s">
+      <c r="D85" s="129" t="s">
         <v>181</v>
       </c>
-      <c r="E85" s="132"/>
-      <c r="F85" s="133"/>
-      <c r="G85" s="130" t="s">
+      <c r="E85" s="130"/>
+      <c r="F85" s="131"/>
+      <c r="G85" s="93" t="s">
         <v>287</v>
       </c>
-      <c r="H85" s="134"/>
-      <c r="I85" s="135"/>
-      <c r="J85" s="136">
+      <c r="H85" s="94"/>
+      <c r="I85" s="95"/>
+      <c r="J85" s="96">
         <v>3.472222222222222E-3</v>
       </c>
-      <c r="K85" s="137"/>
+      <c r="K85" s="97"/>
       <c r="L85" s="6"/>
       <c r="M85" s="6"/>
       <c r="N85" s="6"/>
     </row>
     <row r="86" spans="1:14" ht="37.799999999999997">
       <c r="A86" s="11"/>
-      <c r="B86" s="122"/>
+      <c r="B86" s="121"/>
       <c r="C86" s="58" t="str">
         <f>master!C63</f>
         <v>[解説] Controllerクラスの例（抜粋）</v>
       </c>
-      <c r="D86" s="112" t="s">
+      <c r="D86" s="114" t="s">
         <v>185</v>
       </c>
-      <c r="E86" s="113"/>
-      <c r="F86" s="114"/>
+      <c r="E86" s="115"/>
+      <c r="F86" s="116"/>
       <c r="G86" s="58" t="s">
         <v>283</v>
       </c>
@@ -8807,16 +8820,16 @@
     </row>
     <row r="87" spans="1:14" ht="37.799999999999997">
       <c r="A87" s="11"/>
-      <c r="B87" s="122"/>
+      <c r="B87" s="121"/>
       <c r="C87" s="58" t="str">
         <f>master!C64</f>
         <v>[解説] Thymeleafテンプレートの例（抜粋）</v>
       </c>
-      <c r="D87" s="112" t="s">
+      <c r="D87" s="114" t="s">
         <v>186</v>
       </c>
-      <c r="E87" s="113"/>
-      <c r="F87" s="114"/>
+      <c r="E87" s="115"/>
+      <c r="F87" s="116"/>
       <c r="G87" s="58" t="s">
         <v>283</v>
       </c>
@@ -8834,16 +8847,16 @@
     </row>
     <row r="88" spans="1:14" ht="37.799999999999997">
       <c r="A88" s="11"/>
-      <c r="B88" s="122"/>
+      <c r="B88" s="121"/>
       <c r="C88" s="58" t="str">
         <f>master!C65</f>
         <v>[解説] Formクラスの例（抜粋）</v>
       </c>
-      <c r="D88" s="112" t="s">
+      <c r="D88" s="114" t="s">
         <v>187</v>
       </c>
-      <c r="E88" s="113"/>
-      <c r="F88" s="114"/>
+      <c r="E88" s="115"/>
+      <c r="F88" s="116"/>
       <c r="G88" s="58" t="s">
         <v>283</v>
       </c>
@@ -8861,16 +8874,16 @@
     </row>
     <row r="89" spans="1:14" ht="75.599999999999994">
       <c r="A89" s="11"/>
-      <c r="B89" s="122"/>
+      <c r="B89" s="121"/>
       <c r="C89" s="76" t="str">
         <f>master!C66</f>
         <v>バイブコーディング❻ 動作を確認する</v>
       </c>
-      <c r="D89" s="112" t="s">
+      <c r="D89" s="114" t="s">
         <v>188</v>
       </c>
-      <c r="E89" s="113"/>
-      <c r="F89" s="114"/>
+      <c r="E89" s="115"/>
+      <c r="F89" s="116"/>
       <c r="G89" s="58" t="s">
         <v>284</v>
       </c>
@@ -8888,31 +8901,31 @@
     </row>
     <row r="90" spans="1:14" ht="63">
       <c r="A90" s="11"/>
-      <c r="B90" s="123"/>
+      <c r="B90" s="122"/>
       <c r="C90" s="77"/>
-      <c r="D90" s="131" t="s">
+      <c r="D90" s="129" t="s">
         <v>195</v>
       </c>
-      <c r="E90" s="132"/>
-      <c r="F90" s="133"/>
-      <c r="G90" s="130" t="s">
+      <c r="E90" s="130"/>
+      <c r="F90" s="131"/>
+      <c r="G90" s="93" t="s">
         <v>291</v>
       </c>
-      <c r="H90" s="134"/>
-      <c r="I90" s="135" t="s">
-        <v>24</v>
-      </c>
-      <c r="J90" s="136">
+      <c r="H90" s="94"/>
+      <c r="I90" s="95" t="s">
+        <v>24</v>
+      </c>
+      <c r="J90" s="96">
         <v>1.0416666666666666E-2</v>
       </c>
-      <c r="K90" s="137"/>
+      <c r="K90" s="97"/>
       <c r="L90" s="6"/>
       <c r="M90" s="6"/>
       <c r="N90" s="6"/>
     </row>
     <row r="91" spans="1:14" ht="50.4">
       <c r="A91" s="11"/>
-      <c r="B91" s="124" t="str">
+      <c r="B91" s="117" t="str">
         <f>master!B69</f>
         <v>Gitとは</v>
       </c>
@@ -8920,11 +8933,11 @@
         <f>master!C69</f>
         <v>はじめに</v>
       </c>
-      <c r="D91" s="118" t="s">
-        <v>396</v>
-      </c>
-      <c r="E91" s="119"/>
-      <c r="F91" s="120"/>
+      <c r="D91" s="123" t="s">
+        <v>394</v>
+      </c>
+      <c r="E91" s="124"/>
+      <c r="F91" s="125"/>
       <c r="G91" s="48" t="s">
         <v>329</v>
       </c>
@@ -8942,16 +8955,16 @@
     </row>
     <row r="92" spans="1:14" ht="37.799999999999997">
       <c r="A92" s="11"/>
-      <c r="B92" s="125"/>
+      <c r="B92" s="118"/>
       <c r="C92" s="48" t="str">
         <f>master!C70</f>
         <v>バージョン管理とは</v>
       </c>
-      <c r="D92" s="118" t="s">
-        <v>371</v>
-      </c>
-      <c r="E92" s="119"/>
-      <c r="F92" s="120"/>
+      <c r="D92" s="123" t="s">
+        <v>370</v>
+      </c>
+      <c r="E92" s="124"/>
+      <c r="F92" s="125"/>
       <c r="G92" s="48" t="s">
         <v>328</v>
       </c>
@@ -8969,18 +8982,18 @@
     </row>
     <row r="93" spans="1:14" ht="151.19999999999999">
       <c r="A93" s="11"/>
-      <c r="B93" s="126"/>
+      <c r="B93" s="119"/>
       <c r="C93" s="48" t="str">
         <f>master!C71</f>
         <v>Gitの概要</v>
       </c>
-      <c r="D93" s="118" t="s">
-        <v>372</v>
-      </c>
-      <c r="E93" s="119"/>
-      <c r="F93" s="120"/>
+      <c r="D93" s="123" t="s">
+        <v>439</v>
+      </c>
+      <c r="E93" s="124"/>
+      <c r="F93" s="125"/>
       <c r="G93" s="48" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="H93" s="12"/>
       <c r="I93" s="46" t="s">
@@ -8996,7 +9009,7 @@
     </row>
     <row r="94" spans="1:14" ht="75.599999999999994">
       <c r="A94" s="11"/>
-      <c r="B94" s="124" t="str">
+      <c r="B94" s="117" t="str">
         <f>master!B72</f>
         <v>Gitの基本構成</v>
       </c>
@@ -9004,13 +9017,13 @@
         <f>master!C72</f>
         <v>はじめに</v>
       </c>
-      <c r="D94" s="118" t="s">
-        <v>395</v>
-      </c>
-      <c r="E94" s="119"/>
-      <c r="F94" s="120"/>
+      <c r="D94" s="123" t="s">
+        <v>393</v>
+      </c>
+      <c r="E94" s="124"/>
+      <c r="F94" s="125"/>
       <c r="G94" s="48" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="H94" s="12"/>
       <c r="I94" s="46" t="s">
@@ -9026,16 +9039,16 @@
     </row>
     <row r="95" spans="1:14" ht="37.799999999999997">
       <c r="A95" s="11"/>
-      <c r="B95" s="125"/>
+      <c r="B95" s="118"/>
       <c r="C95" s="48" t="str">
         <f>master!C73</f>
         <v>ワーキングツリー</v>
       </c>
-      <c r="D95" s="118" t="s">
-        <v>375</v>
-      </c>
-      <c r="E95" s="119"/>
-      <c r="F95" s="120"/>
+      <c r="D95" s="123" t="s">
+        <v>373</v>
+      </c>
+      <c r="E95" s="124"/>
+      <c r="F95" s="125"/>
       <c r="G95" s="48" t="s">
         <v>328</v>
       </c>
@@ -9053,16 +9066,16 @@
     </row>
     <row r="96" spans="1:14" ht="37.799999999999997">
       <c r="A96" s="11"/>
-      <c r="B96" s="125"/>
+      <c r="B96" s="118"/>
       <c r="C96" s="48" t="str">
         <f>master!C74</f>
         <v>ステージングエリア</v>
       </c>
-      <c r="D96" s="118" t="s">
-        <v>376</v>
-      </c>
-      <c r="E96" s="119"/>
-      <c r="F96" s="120"/>
+      <c r="D96" s="123" t="s">
+        <v>374</v>
+      </c>
+      <c r="E96" s="124"/>
+      <c r="F96" s="125"/>
       <c r="G96" s="48" t="s">
         <v>328</v>
       </c>
@@ -9080,16 +9093,16 @@
     </row>
     <row r="97" spans="1:14" ht="37.799999999999997">
       <c r="A97" s="11"/>
-      <c r="B97" s="125"/>
+      <c r="B97" s="118"/>
       <c r="C97" s="48" t="str">
         <f>master!C75</f>
         <v>ローカルリポジトリ</v>
       </c>
-      <c r="D97" s="118" t="s">
-        <v>377</v>
-      </c>
-      <c r="E97" s="119"/>
-      <c r="F97" s="120"/>
+      <c r="D97" s="123" t="s">
+        <v>375</v>
+      </c>
+      <c r="E97" s="124"/>
+      <c r="F97" s="125"/>
       <c r="G97" s="48" t="s">
         <v>328</v>
       </c>
@@ -9107,16 +9120,16 @@
     </row>
     <row r="98" spans="1:14" ht="50.4">
       <c r="A98" s="11"/>
-      <c r="B98" s="126"/>
+      <c r="B98" s="119"/>
       <c r="C98" s="48" t="str">
         <f>master!C76</f>
         <v>リモートリポジトリ</v>
       </c>
-      <c r="D98" s="118" t="s">
-        <v>378</v>
-      </c>
-      <c r="E98" s="119"/>
-      <c r="F98" s="120"/>
+      <c r="D98" s="123" t="s">
+        <v>376</v>
+      </c>
+      <c r="E98" s="124"/>
+      <c r="F98" s="125"/>
       <c r="G98" s="48" t="s">
         <v>329</v>
       </c>
@@ -9134,7 +9147,7 @@
     </row>
     <row r="99" spans="1:14" ht="88.2">
       <c r="A99" s="11"/>
-      <c r="B99" s="124" t="str">
+      <c r="B99" s="117" t="str">
         <f>master!B77</f>
         <v>ローカルリポジトリの操作</v>
       </c>
@@ -9142,13 +9155,13 @@
         <f>master!C77</f>
         <v>はじめに</v>
       </c>
-      <c r="D99" s="118" t="s">
-        <v>394</v>
-      </c>
-      <c r="E99" s="119"/>
-      <c r="F99" s="120"/>
+      <c r="D99" s="123" t="s">
+        <v>392</v>
+      </c>
+      <c r="E99" s="124"/>
+      <c r="F99" s="125"/>
       <c r="G99" s="48" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="H99" s="12"/>
       <c r="I99" s="46" t="s">
@@ -9164,16 +9177,16 @@
     </row>
     <row r="100" spans="1:14" ht="37.799999999999997">
       <c r="A100" s="11"/>
-      <c r="B100" s="125"/>
+      <c r="B100" s="118"/>
       <c r="C100" s="48" t="str">
         <f>master!C78</f>
         <v>リポジトリの作成</v>
       </c>
-      <c r="D100" s="118" t="s">
-        <v>380</v>
-      </c>
-      <c r="E100" s="119"/>
-      <c r="F100" s="120"/>
+      <c r="D100" s="123" t="s">
+        <v>378</v>
+      </c>
+      <c r="E100" s="124"/>
+      <c r="F100" s="125"/>
       <c r="G100" s="48" t="s">
         <v>328</v>
       </c>
@@ -9191,16 +9204,16 @@
     </row>
     <row r="101" spans="1:14" ht="37.799999999999997" customHeight="1">
       <c r="A101" s="11"/>
-      <c r="B101" s="125"/>
+      <c r="B101" s="118"/>
       <c r="C101" s="48" t="str">
         <f>master!C79</f>
         <v>ファイルの変更</v>
       </c>
-      <c r="D101" s="118" t="s">
-        <v>381</v>
-      </c>
-      <c r="E101" s="119"/>
-      <c r="F101" s="120"/>
+      <c r="D101" s="123" t="s">
+        <v>379</v>
+      </c>
+      <c r="E101" s="124"/>
+      <c r="F101" s="125"/>
       <c r="G101" s="48" t="s">
         <v>328</v>
       </c>
@@ -9218,16 +9231,16 @@
     </row>
     <row r="102" spans="1:14" ht="37.799999999999997">
       <c r="A102" s="11"/>
-      <c r="B102" s="125"/>
+      <c r="B102" s="118"/>
       <c r="C102" s="48" t="str">
         <f>master!C80</f>
         <v>変更内容の確認</v>
       </c>
-      <c r="D102" s="118" t="s">
-        <v>382</v>
-      </c>
-      <c r="E102" s="119"/>
-      <c r="F102" s="120"/>
+      <c r="D102" s="123" t="s">
+        <v>380</v>
+      </c>
+      <c r="E102" s="124"/>
+      <c r="F102" s="125"/>
       <c r="G102" s="48" t="s">
         <v>328</v>
       </c>
@@ -9245,16 +9258,16 @@
     </row>
     <row r="103" spans="1:14" ht="37.799999999999997">
       <c r="A103" s="11"/>
-      <c r="B103" s="125"/>
+      <c r="B103" s="118"/>
       <c r="C103" s="48" t="str">
         <f>master!C81</f>
         <v>変更内容のステージ</v>
       </c>
-      <c r="D103" s="118" t="s">
-        <v>383</v>
-      </c>
-      <c r="E103" s="119"/>
-      <c r="F103" s="120"/>
+      <c r="D103" s="123" t="s">
+        <v>381</v>
+      </c>
+      <c r="E103" s="124"/>
+      <c r="F103" s="125"/>
       <c r="G103" s="48" t="s">
         <v>328</v>
       </c>
@@ -9272,16 +9285,16 @@
     </row>
     <row r="104" spans="1:14" ht="37.799999999999997">
       <c r="A104" s="11"/>
-      <c r="B104" s="125"/>
+      <c r="B104" s="118"/>
       <c r="C104" s="48" t="str">
         <f>master!C82</f>
         <v>変更内容のコミット</v>
       </c>
-      <c r="D104" s="118" t="s">
-        <v>384</v>
-      </c>
-      <c r="E104" s="119"/>
-      <c r="F104" s="120"/>
+      <c r="D104" s="123" t="s">
+        <v>382</v>
+      </c>
+      <c r="E104" s="124"/>
+      <c r="F104" s="125"/>
       <c r="G104" s="48" t="s">
         <v>328</v>
       </c>
@@ -9299,16 +9312,16 @@
     </row>
     <row r="105" spans="1:14" ht="37.799999999999997">
       <c r="A105" s="11"/>
-      <c r="B105" s="125"/>
+      <c r="B105" s="118"/>
       <c r="C105" s="48" t="str">
         <f>master!C83</f>
         <v>ワーキングツリーの変更の取り消し</v>
       </c>
-      <c r="D105" s="118" t="s">
-        <v>385</v>
-      </c>
-      <c r="E105" s="119"/>
-      <c r="F105" s="120"/>
+      <c r="D105" s="123" t="s">
+        <v>383</v>
+      </c>
+      <c r="E105" s="124"/>
+      <c r="F105" s="125"/>
       <c r="G105" s="48" t="s">
         <v>328</v>
       </c>
@@ -9326,16 +9339,16 @@
     </row>
     <row r="106" spans="1:14" ht="37.799999999999997">
       <c r="A106" s="11"/>
-      <c r="B106" s="125"/>
+      <c r="B106" s="118"/>
       <c r="C106" s="48" t="str">
         <f>master!C84</f>
         <v>ステージングの取り消し</v>
       </c>
-      <c r="D106" s="118" t="s">
-        <v>386</v>
-      </c>
-      <c r="E106" s="119"/>
-      <c r="F106" s="120"/>
+      <c r="D106" s="123" t="s">
+        <v>384</v>
+      </c>
+      <c r="E106" s="124"/>
+      <c r="F106" s="125"/>
       <c r="G106" s="48" t="s">
         <v>328</v>
       </c>
@@ -9353,16 +9366,16 @@
     </row>
     <row r="107" spans="1:14" ht="37.799999999999997">
       <c r="A107" s="11"/>
-      <c r="B107" s="126"/>
+      <c r="B107" s="119"/>
       <c r="C107" s="48" t="str">
         <f>master!C85</f>
         <v>コミットの打ち消し</v>
       </c>
-      <c r="D107" s="118" t="s">
-        <v>387</v>
-      </c>
-      <c r="E107" s="119"/>
-      <c r="F107" s="120"/>
+      <c r="D107" s="123" t="s">
+        <v>385</v>
+      </c>
+      <c r="E107" s="124"/>
+      <c r="F107" s="125"/>
       <c r="G107" s="48" t="s">
         <v>328</v>
       </c>
@@ -9380,7 +9393,7 @@
     </row>
     <row r="108" spans="1:14" ht="75.599999999999994">
       <c r="A108" s="11"/>
-      <c r="B108" s="124" t="str">
+      <c r="B108" s="117" t="str">
         <f>master!B86</f>
         <v>リモートリポジトリの操作</v>
       </c>
@@ -9388,13 +9401,13 @@
         <f>master!C86</f>
         <v>はじめに</v>
       </c>
-      <c r="D108" s="118" t="s">
-        <v>392</v>
-      </c>
-      <c r="E108" s="119"/>
-      <c r="F108" s="120"/>
+      <c r="D108" s="123" t="s">
+        <v>390</v>
+      </c>
+      <c r="E108" s="124"/>
+      <c r="F108" s="125"/>
       <c r="G108" s="48" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="H108" s="12"/>
       <c r="I108" s="46" t="s">
@@ -9404,7 +9417,7 @@
         <v>0</v>
       </c>
       <c r="K108" s="89" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="L108" s="6"/>
       <c r="M108" s="6"/>
@@ -9412,16 +9425,16 @@
     </row>
     <row r="109" spans="1:14" ht="37.799999999999997">
       <c r="A109" s="11"/>
-      <c r="B109" s="125"/>
+      <c r="B109" s="118"/>
       <c r="C109" s="48" t="str">
         <f>master!C87</f>
         <v>リポジトリの複製</v>
       </c>
-      <c r="D109" s="118" t="s">
-        <v>388</v>
-      </c>
-      <c r="E109" s="119"/>
-      <c r="F109" s="120"/>
+      <c r="D109" s="123" t="s">
+        <v>386</v>
+      </c>
+      <c r="E109" s="124"/>
+      <c r="F109" s="125"/>
       <c r="G109" s="48" t="s">
         <v>328</v>
       </c>
@@ -9433,7 +9446,7 @@
         <v>0</v>
       </c>
       <c r="K109" s="89" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="L109" s="6"/>
       <c r="M109" s="6"/>
@@ -9441,16 +9454,16 @@
     </row>
     <row r="110" spans="1:14" ht="37.799999999999997">
       <c r="A110" s="11"/>
-      <c r="B110" s="125"/>
+      <c r="B110" s="118"/>
       <c r="C110" s="48" t="str">
         <f>master!C88</f>
         <v>リモートからの取得</v>
       </c>
-      <c r="D110" s="118" t="s">
-        <v>389</v>
-      </c>
-      <c r="E110" s="119"/>
-      <c r="F110" s="120"/>
+      <c r="D110" s="123" t="s">
+        <v>387</v>
+      </c>
+      <c r="E110" s="124"/>
+      <c r="F110" s="125"/>
       <c r="G110" s="48" t="s">
         <v>328</v>
       </c>
@@ -9462,7 +9475,7 @@
         <v>0</v>
       </c>
       <c r="K110" s="89" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="L110" s="6"/>
       <c r="M110" s="6"/>
@@ -9470,16 +9483,16 @@
     </row>
     <row r="111" spans="1:14" ht="37.799999999999997">
       <c r="A111" s="11"/>
-      <c r="B111" s="125"/>
+      <c r="B111" s="118"/>
       <c r="C111" s="48" t="str">
         <f>master!C89</f>
         <v>リモートからの取得と反映</v>
       </c>
-      <c r="D111" s="118" t="s">
-        <v>391</v>
-      </c>
-      <c r="E111" s="119"/>
-      <c r="F111" s="120"/>
+      <c r="D111" s="123" t="s">
+        <v>389</v>
+      </c>
+      <c r="E111" s="124"/>
+      <c r="F111" s="125"/>
       <c r="G111" s="48" t="s">
         <v>328</v>
       </c>
@@ -9491,7 +9504,7 @@
         <v>0</v>
       </c>
       <c r="K111" s="89" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="L111" s="6"/>
       <c r="M111" s="6"/>
@@ -9499,16 +9512,16 @@
     </row>
     <row r="112" spans="1:14" ht="37.799999999999997">
       <c r="A112" s="11"/>
-      <c r="B112" s="126"/>
+      <c r="B112" s="119"/>
       <c r="C112" s="48" t="str">
         <f>master!C90</f>
         <v>リモートへの反映</v>
       </c>
-      <c r="D112" s="118" t="s">
-        <v>390</v>
-      </c>
-      <c r="E112" s="119"/>
-      <c r="F112" s="120"/>
+      <c r="D112" s="123" t="s">
+        <v>388</v>
+      </c>
+      <c r="E112" s="124"/>
+      <c r="F112" s="125"/>
       <c r="G112" s="48" t="s">
         <v>328</v>
       </c>
@@ -9520,7 +9533,7 @@
         <v>0</v>
       </c>
       <c r="K112" s="89" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="L112" s="6"/>
       <c r="M112" s="6"/>
@@ -9528,7 +9541,7 @@
     </row>
     <row r="113" spans="1:14" ht="88.2">
       <c r="A113" s="11"/>
-      <c r="B113" s="124" t="str">
+      <c r="B113" s="117" t="str">
         <f>master!B91</f>
         <v>ブランチの操作</v>
       </c>
@@ -9536,13 +9549,13 @@
         <f>master!C91</f>
         <v>はじめに</v>
       </c>
-      <c r="D113" s="118" t="s">
-        <v>393</v>
-      </c>
-      <c r="E113" s="119"/>
-      <c r="F113" s="120"/>
+      <c r="D113" s="123" t="s">
+        <v>391</v>
+      </c>
+      <c r="E113" s="124"/>
+      <c r="F113" s="125"/>
       <c r="G113" s="48" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="H113" s="12"/>
       <c r="I113" s="46" t="s">
@@ -9552,7 +9565,7 @@
         <v>0</v>
       </c>
       <c r="K113" s="89" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="L113" s="6"/>
       <c r="M113" s="6"/>
@@ -9560,16 +9573,16 @@
     </row>
     <row r="114" spans="1:14" ht="37.799999999999997">
       <c r="A114" s="11"/>
-      <c r="B114" s="125"/>
+      <c r="B114" s="118"/>
       <c r="C114" s="48" t="str">
         <f>master!C92</f>
         <v>ブランチとは</v>
       </c>
-      <c r="D114" s="118" t="s">
-        <v>397</v>
-      </c>
-      <c r="E114" s="119"/>
-      <c r="F114" s="120"/>
+      <c r="D114" s="123" t="s">
+        <v>395</v>
+      </c>
+      <c r="E114" s="124"/>
+      <c r="F114" s="125"/>
       <c r="G114" s="48" t="s">
         <v>328</v>
       </c>
@@ -9587,16 +9600,16 @@
     </row>
     <row r="115" spans="1:14" ht="37.799999999999997">
       <c r="A115" s="11"/>
-      <c r="B115" s="125"/>
+      <c r="B115" s="118"/>
       <c r="C115" s="48" t="str">
         <f>master!C93</f>
         <v>ブランチの作成</v>
       </c>
-      <c r="D115" s="118" t="s">
-        <v>398</v>
-      </c>
-      <c r="E115" s="119"/>
-      <c r="F115" s="120"/>
+      <c r="D115" s="123" t="s">
+        <v>396</v>
+      </c>
+      <c r="E115" s="124"/>
+      <c r="F115" s="125"/>
       <c r="G115" s="48" t="s">
         <v>328</v>
       </c>
@@ -9614,16 +9627,16 @@
     </row>
     <row r="116" spans="1:14" ht="37.799999999999997">
       <c r="A116" s="11"/>
-      <c r="B116" s="125"/>
+      <c r="B116" s="118"/>
       <c r="C116" s="48" t="str">
         <f>master!C94</f>
         <v>ブランチの切り替え</v>
       </c>
-      <c r="D116" s="118" t="s">
-        <v>399</v>
-      </c>
-      <c r="E116" s="119"/>
-      <c r="F116" s="120"/>
+      <c r="D116" s="123" t="s">
+        <v>397</v>
+      </c>
+      <c r="E116" s="124"/>
+      <c r="F116" s="125"/>
       <c r="G116" s="48" t="s">
         <v>328</v>
       </c>
@@ -9641,16 +9654,16 @@
     </row>
     <row r="117" spans="1:14" ht="37.799999999999997">
       <c r="A117" s="11"/>
-      <c r="B117" s="125"/>
+      <c r="B117" s="118"/>
       <c r="C117" s="48" t="str">
         <f>master!C95</f>
         <v>ブランチのマージ</v>
       </c>
-      <c r="D117" s="118" t="s">
-        <v>400</v>
-      </c>
-      <c r="E117" s="119"/>
-      <c r="F117" s="120"/>
+      <c r="D117" s="123" t="s">
+        <v>398</v>
+      </c>
+      <c r="E117" s="124"/>
+      <c r="F117" s="125"/>
       <c r="G117" s="48" t="s">
         <v>328</v>
       </c>
@@ -9668,16 +9681,16 @@
     </row>
     <row r="118" spans="1:14" ht="100.8">
       <c r="A118" s="11"/>
-      <c r="B118" s="126"/>
+      <c r="B118" s="119"/>
       <c r="C118" s="48" t="str">
         <f>master!C96</f>
         <v>コンフリクトの解消</v>
       </c>
-      <c r="D118" s="118" t="s">
-        <v>402</v>
-      </c>
-      <c r="E118" s="119"/>
-      <c r="F118" s="120"/>
+      <c r="D118" s="123" t="s">
+        <v>400</v>
+      </c>
+      <c r="E118" s="124"/>
+      <c r="F118" s="125"/>
       <c r="G118" s="48" t="s">
         <v>327</v>
       </c>
@@ -9695,7 +9708,7 @@
     </row>
     <row r="119" spans="1:14" ht="75.599999999999994">
       <c r="A119" s="11"/>
-      <c r="B119" s="124" t="str">
+      <c r="B119" s="117" t="str">
         <f>master!B97</f>
         <v>VSCodeによるGitの操作</v>
       </c>
@@ -9703,13 +9716,13 @@
         <f>master!C97</f>
         <v>はじめに</v>
       </c>
-      <c r="D119" s="118" t="s">
-        <v>401</v>
-      </c>
-      <c r="E119" s="119"/>
-      <c r="F119" s="120"/>
+      <c r="D119" s="123" t="s">
+        <v>399</v>
+      </c>
+      <c r="E119" s="124"/>
+      <c r="F119" s="125"/>
       <c r="G119" s="48" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="H119" s="12"/>
       <c r="I119" s="46" t="s">
@@ -9725,18 +9738,18 @@
     </row>
     <row r="120" spans="1:14" ht="25.2">
       <c r="A120" s="11"/>
-      <c r="B120" s="125"/>
+      <c r="B120" s="118"/>
       <c r="C120" s="48" t="str">
         <f>master!C98</f>
         <v>VSCodeのソース管理機能</v>
       </c>
-      <c r="D120" s="118" t="s">
-        <v>403</v>
-      </c>
-      <c r="E120" s="119"/>
-      <c r="F120" s="120"/>
+      <c r="D120" s="123" t="s">
+        <v>401</v>
+      </c>
+      <c r="E120" s="124"/>
+      <c r="F120" s="125"/>
       <c r="G120" s="48" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="H120" s="12"/>
       <c r="I120" s="46" t="s">
@@ -9752,18 +9765,18 @@
     </row>
     <row r="121" spans="1:14" ht="126">
       <c r="A121" s="11"/>
-      <c r="B121" s="125"/>
+      <c r="B121" s="118"/>
       <c r="C121" s="48" t="str">
         <f>master!C99</f>
         <v>ローカルリポジトリの操作</v>
       </c>
-      <c r="D121" s="118" t="s">
-        <v>415</v>
-      </c>
-      <c r="E121" s="119"/>
-      <c r="F121" s="120"/>
+      <c r="D121" s="123" t="s">
+        <v>413</v>
+      </c>
+      <c r="E121" s="124"/>
+      <c r="F121" s="125"/>
       <c r="G121" s="48" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="H121" s="12"/>
       <c r="I121" s="46" t="s">
@@ -9779,16 +9792,16 @@
     </row>
     <row r="122" spans="1:14" ht="63">
       <c r="A122" s="11"/>
-      <c r="B122" s="125"/>
+      <c r="B122" s="118"/>
       <c r="C122" s="48" t="str">
         <f>master!C100</f>
         <v>リモートリポジトリの操作</v>
       </c>
-      <c r="D122" s="118" t="s">
-        <v>405</v>
-      </c>
-      <c r="E122" s="119"/>
-      <c r="F122" s="120"/>
+      <c r="D122" s="123" t="s">
+        <v>403</v>
+      </c>
+      <c r="E122" s="124"/>
+      <c r="F122" s="125"/>
       <c r="G122" s="48" t="s">
         <v>330</v>
       </c>
@@ -9800,7 +9813,7 @@
         <v>0</v>
       </c>
       <c r="K122" s="89" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="L122" s="6"/>
       <c r="M122" s="6"/>
@@ -9808,18 +9821,18 @@
     </row>
     <row r="123" spans="1:14" ht="113.4">
       <c r="A123" s="11"/>
-      <c r="B123" s="126"/>
+      <c r="B123" s="119"/>
       <c r="C123" s="48" t="str">
         <f>master!C101</f>
         <v>ブランチの操作</v>
       </c>
-      <c r="D123" s="118" t="s">
-        <v>416</v>
-      </c>
-      <c r="E123" s="119"/>
-      <c r="F123" s="120"/>
+      <c r="D123" s="123" t="s">
+        <v>414</v>
+      </c>
+      <c r="E123" s="124"/>
+      <c r="F123" s="125"/>
       <c r="G123" s="48" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="H123" s="12"/>
       <c r="I123" s="46" t="s">
@@ -9829,7 +9842,7 @@
         <v>0</v>
       </c>
       <c r="K123" s="89" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="L123" s="6"/>
       <c r="M123" s="6"/>
@@ -9837,17 +9850,17 @@
     </row>
     <row r="124" spans="1:14" ht="25.2">
       <c r="A124" s="11"/>
-      <c r="B124" s="121" t="str">
+      <c r="B124" s="120" t="str">
         <f>master!B103</f>
         <v>演習の概要について</v>
       </c>
       <c r="C124" s="58" t="str">
         <f>master!C103</f>
-        <v>はじめに</v>
-      </c>
-      <c r="D124" s="112"/>
-      <c r="E124" s="113"/>
-      <c r="F124" s="114"/>
+        <v>0.1 はじめに</v>
+      </c>
+      <c r="D124" s="114"/>
+      <c r="E124" s="115"/>
+      <c r="F124" s="116"/>
       <c r="G124" s="58" t="s">
         <v>332</v>
       </c>
@@ -9865,18 +9878,18 @@
     </row>
     <row r="125" spans="1:14" ht="50.4">
       <c r="A125" s="11"/>
-      <c r="B125" s="122"/>
+      <c r="B125" s="121"/>
       <c r="C125" s="58" t="str">
         <f>master!C104</f>
-        <v>構成</v>
-      </c>
-      <c r="D125" s="112" t="s">
-        <v>407</v>
-      </c>
-      <c r="E125" s="113"/>
-      <c r="F125" s="114"/>
+        <v>0.2 構成</v>
+      </c>
+      <c r="D125" s="114" t="s">
+        <v>405</v>
+      </c>
+      <c r="E125" s="115"/>
+      <c r="F125" s="116"/>
       <c r="G125" s="58" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="H125" s="59"/>
       <c r="I125" s="60" t="s">
@@ -9892,18 +9905,18 @@
     </row>
     <row r="126" spans="1:14" ht="50.4">
       <c r="A126" s="11"/>
-      <c r="B126" s="123"/>
+      <c r="B126" s="122"/>
       <c r="C126" s="58" t="str">
         <f>master!C105</f>
-        <v>利用するソフトウェア</v>
-      </c>
-      <c r="D126" s="112" t="s">
-        <v>408</v>
-      </c>
-      <c r="E126" s="113"/>
-      <c r="F126" s="114"/>
+        <v>0.3 利用するソフトウェア</v>
+      </c>
+      <c r="D126" s="114" t="s">
+        <v>406</v>
+      </c>
+      <c r="E126" s="115"/>
+      <c r="F126" s="116"/>
       <c r="G126" s="58" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="H126" s="59"/>
       <c r="I126" s="60" t="s">
@@ -9913,7 +9926,7 @@
         <v>6.9444444444444447E-4</v>
       </c>
       <c r="K126" s="62" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="L126" s="6"/>
       <c r="M126" s="6"/>
@@ -9921,21 +9934,21 @@
     </row>
     <row r="127" spans="1:14" ht="176.4">
       <c r="A127" s="11"/>
-      <c r="B127" s="121" t="str">
+      <c r="B127" s="120" t="str">
         <f>master!B106</f>
         <v>ローカルリポジトリの操作</v>
       </c>
       <c r="C127" s="58" t="str">
         <f>master!C106</f>
-        <v>演習の前に</v>
-      </c>
-      <c r="D127" s="112" t="s">
-        <v>412</v>
-      </c>
-      <c r="E127" s="113"/>
-      <c r="F127" s="114"/>
+        <v>1.0 演習の前に</v>
+      </c>
+      <c r="D127" s="114" t="s">
+        <v>410</v>
+      </c>
+      <c r="E127" s="115"/>
+      <c r="F127" s="116"/>
       <c r="G127" s="58" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="H127" s="59"/>
       <c r="I127" s="60" t="s">
@@ -9951,18 +9964,18 @@
     </row>
     <row r="128" spans="1:14" ht="37.799999999999997">
       <c r="A128" s="11"/>
-      <c r="B128" s="122"/>
+      <c r="B128" s="121"/>
       <c r="C128" s="58" t="str">
         <f>master!C107</f>
-        <v>リポジトリの作成</v>
-      </c>
-      <c r="D128" s="112" t="s">
-        <v>409</v>
-      </c>
-      <c r="E128" s="113"/>
-      <c r="F128" s="114"/>
+        <v>1.1 リポジトリの作成</v>
+      </c>
+      <c r="D128" s="114" t="s">
+        <v>407</v>
+      </c>
+      <c r="E128" s="115"/>
+      <c r="F128" s="116"/>
       <c r="G128" s="58" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="H128" s="59"/>
       <c r="I128" s="60" t="s">
@@ -9978,18 +9991,18 @@
     </row>
     <row r="129" spans="1:14" ht="37.799999999999997">
       <c r="A129" s="11"/>
-      <c r="B129" s="122"/>
+      <c r="B129" s="121"/>
       <c r="C129" s="58" t="str">
         <f>master!C108</f>
-        <v>変更内容の確認</v>
-      </c>
-      <c r="D129" s="112" t="s">
-        <v>409</v>
-      </c>
-      <c r="E129" s="113"/>
-      <c r="F129" s="114"/>
+        <v>1.2 変更内容の確認</v>
+      </c>
+      <c r="D129" s="114" t="s">
+        <v>407</v>
+      </c>
+      <c r="E129" s="115"/>
+      <c r="F129" s="116"/>
       <c r="G129" s="58" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="H129" s="59"/>
       <c r="I129" s="60" t="s">
@@ -10005,18 +10018,18 @@
     </row>
     <row r="130" spans="1:14" ht="37.799999999999997">
       <c r="A130" s="11"/>
-      <c r="B130" s="122"/>
+      <c r="B130" s="121"/>
       <c r="C130" s="58" t="str">
         <f>master!C109</f>
-        <v>変更内容のステージング</v>
-      </c>
-      <c r="D130" s="112" t="s">
-        <v>409</v>
-      </c>
-      <c r="E130" s="113"/>
-      <c r="F130" s="114"/>
+        <v>1.3 変更内容のステージ</v>
+      </c>
+      <c r="D130" s="114" t="s">
+        <v>407</v>
+      </c>
+      <c r="E130" s="115"/>
+      <c r="F130" s="116"/>
       <c r="G130" s="58" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="H130" s="59"/>
       <c r="I130" s="60" t="s">
@@ -10032,18 +10045,18 @@
     </row>
     <row r="131" spans="1:14" ht="37.799999999999997">
       <c r="A131" s="11"/>
-      <c r="B131" s="123"/>
+      <c r="B131" s="122"/>
       <c r="C131" s="58" t="str">
         <f>master!C110</f>
-        <v>変更内容のコミット</v>
-      </c>
-      <c r="D131" s="112" t="s">
-        <v>409</v>
-      </c>
-      <c r="E131" s="113"/>
-      <c r="F131" s="114"/>
+        <v>1.4 変更内容のコミット</v>
+      </c>
+      <c r="D131" s="114" t="s">
+        <v>407</v>
+      </c>
+      <c r="E131" s="115"/>
+      <c r="F131" s="116"/>
       <c r="G131" s="58" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="H131" s="59"/>
       <c r="I131" s="60" t="s">
@@ -10059,19 +10072,19 @@
     </row>
     <row r="132" spans="1:14" ht="163.80000000000001">
       <c r="A132" s="11"/>
-      <c r="B132" s="121" t="str">
+      <c r="B132" s="120" t="str">
         <f>master!B111</f>
         <v>ブランチの操作</v>
       </c>
       <c r="C132" s="58" t="str">
         <f>master!C111</f>
-        <v>演習の前に</v>
-      </c>
-      <c r="D132" s="112" t="s">
-        <v>413</v>
-      </c>
-      <c r="E132" s="113"/>
-      <c r="F132" s="114"/>
+        <v>2.0 演習の前に</v>
+      </c>
+      <c r="D132" s="114" t="s">
+        <v>411</v>
+      </c>
+      <c r="E132" s="115"/>
+      <c r="F132" s="116"/>
       <c r="G132" s="58" t="s">
         <v>331</v>
       </c>
@@ -10083,7 +10096,7 @@
         <v>0</v>
       </c>
       <c r="K132" s="62" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="L132" s="6"/>
       <c r="M132" s="6"/>
@@ -10091,18 +10104,18 @@
     </row>
     <row r="133" spans="1:14" ht="37.799999999999997">
       <c r="A133" s="11"/>
-      <c r="B133" s="122"/>
+      <c r="B133" s="121"/>
       <c r="C133" s="58" t="str">
         <f>master!C112</f>
-        <v>ブランチの作成</v>
-      </c>
-      <c r="D133" s="112" t="s">
-        <v>409</v>
-      </c>
-      <c r="E133" s="113"/>
-      <c r="F133" s="114"/>
+        <v>2.1 ブランチの作成</v>
+      </c>
+      <c r="D133" s="114" t="s">
+        <v>407</v>
+      </c>
+      <c r="E133" s="115"/>
+      <c r="F133" s="116"/>
       <c r="G133" s="58" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="H133" s="59"/>
       <c r="I133" s="60" t="s">
@@ -10112,7 +10125,7 @@
         <v>0</v>
       </c>
       <c r="K133" s="62" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="L133" s="6"/>
       <c r="M133" s="6"/>
@@ -10120,18 +10133,18 @@
     </row>
     <row r="134" spans="1:14" ht="37.799999999999997">
       <c r="A134" s="11"/>
-      <c r="B134" s="122"/>
+      <c r="B134" s="121"/>
       <c r="C134" s="58" t="str">
         <f>master!C113</f>
-        <v>ブランチの切り替え</v>
-      </c>
-      <c r="D134" s="112" t="s">
-        <v>409</v>
-      </c>
-      <c r="E134" s="113"/>
-      <c r="F134" s="114"/>
+        <v>2.2 ブランチの切り替え</v>
+      </c>
+      <c r="D134" s="114" t="s">
+        <v>407</v>
+      </c>
+      <c r="E134" s="115"/>
+      <c r="F134" s="116"/>
       <c r="G134" s="58" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="H134" s="59"/>
       <c r="I134" s="60" t="s">
@@ -10141,7 +10154,7 @@
         <v>0</v>
       </c>
       <c r="K134" s="62" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="L134" s="6"/>
       <c r="M134" s="6"/>
@@ -10149,18 +10162,18 @@
     </row>
     <row r="135" spans="1:14" ht="37.799999999999997">
       <c r="A135" s="11"/>
-      <c r="B135" s="123"/>
+      <c r="B135" s="122"/>
       <c r="C135" s="58" t="str">
         <f>master!C114</f>
-        <v>ブランチのマージ</v>
-      </c>
-      <c r="D135" s="112" t="s">
-        <v>409</v>
-      </c>
-      <c r="E135" s="113"/>
-      <c r="F135" s="114"/>
+        <v>2.3 ブランチのマージ</v>
+      </c>
+      <c r="D135" s="114" t="s">
+        <v>407</v>
+      </c>
+      <c r="E135" s="115"/>
+      <c r="F135" s="116"/>
       <c r="G135" s="58" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="H135" s="59"/>
       <c r="I135" s="60" t="s">
@@ -10170,7 +10183,7 @@
         <v>0</v>
       </c>
       <c r="K135" s="62" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="L135" s="6"/>
       <c r="M135" s="6"/>
@@ -10186,17 +10199,17 @@
         <f>master!C67</f>
         <v>ここから各自で演習を始めましょう。</v>
       </c>
-      <c r="D136" s="112" t="s">
+      <c r="D136" s="114" t="s">
         <v>196</v>
       </c>
-      <c r="E136" s="113"/>
-      <c r="F136" s="114"/>
+      <c r="E136" s="115"/>
+      <c r="F136" s="116"/>
       <c r="G136" s="58" t="s">
         <v>290</v>
       </c>
       <c r="H136" s="59"/>
       <c r="I136" s="60" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="J136" s="61" t="s">
         <v>335</v>
@@ -10208,7 +10221,7 @@
     </row>
     <row r="137" spans="1:14" ht="50.4">
       <c r="A137" s="11"/>
-      <c r="B137" s="109" t="str">
+      <c r="B137" s="135" t="str">
         <f>master!B116</f>
         <v>単体テストとJunitの導入</v>
       </c>
@@ -10216,11 +10229,11 @@
         <f>master!C116</f>
         <v>講義の目的</v>
       </c>
-      <c r="D137" s="118" t="s">
+      <c r="D137" s="123" t="s">
         <v>225</v>
       </c>
-      <c r="E137" s="119"/>
-      <c r="F137" s="120"/>
+      <c r="E137" s="124"/>
+      <c r="F137" s="125"/>
       <c r="G137" s="48" t="s">
         <v>294</v>
       </c>
@@ -10238,14 +10251,14 @@
     </row>
     <row r="138" spans="1:14" ht="25.2">
       <c r="A138" s="11"/>
-      <c r="B138" s="110"/>
+      <c r="B138" s="136"/>
       <c r="C138" s="78" t="str">
         <f>master!C117</f>
         <v>TERASOLUNA 開発手順　 ※再掲</v>
       </c>
-      <c r="D138" s="118"/>
-      <c r="E138" s="119"/>
-      <c r="F138" s="120"/>
+      <c r="D138" s="123"/>
+      <c r="E138" s="124"/>
+      <c r="F138" s="125"/>
       <c r="G138" s="48" t="s">
         <v>295</v>
       </c>
@@ -10263,16 +10276,16 @@
     </row>
     <row r="139" spans="1:14" ht="25.2">
       <c r="A139" s="11"/>
-      <c r="B139" s="111"/>
+      <c r="B139" s="137"/>
       <c r="C139" s="78" t="str">
         <f>master!C118</f>
         <v>V字モデル　 ※再掲</v>
       </c>
-      <c r="D139" s="118" t="s">
+      <c r="D139" s="123" t="s">
         <v>226</v>
       </c>
-      <c r="E139" s="119"/>
-      <c r="F139" s="120"/>
+      <c r="E139" s="124"/>
+      <c r="F139" s="125"/>
       <c r="G139" s="48" t="s">
         <v>295</v>
       </c>
@@ -10290,7 +10303,7 @@
     </row>
     <row r="140" spans="1:14" ht="50.4">
       <c r="A140" s="11"/>
-      <c r="B140" s="109" t="str">
+      <c r="B140" s="135" t="str">
         <f>master!B119</f>
         <v>テストとは</v>
       </c>
@@ -10298,11 +10311,11 @@
         <f>master!C119</f>
         <v>テストとは</v>
       </c>
-      <c r="D140" s="118" t="s">
+      <c r="D140" s="123" t="s">
         <v>227</v>
       </c>
-      <c r="E140" s="119"/>
-      <c r="F140" s="120"/>
+      <c r="E140" s="124"/>
+      <c r="F140" s="125"/>
       <c r="G140" s="48" t="s">
         <v>294</v>
       </c>
@@ -10320,16 +10333,16 @@
     </row>
     <row r="141" spans="1:14" ht="315">
       <c r="A141" s="11"/>
-      <c r="B141" s="110"/>
+      <c r="B141" s="136"/>
       <c r="C141" s="78" t="str">
         <f>master!C120</f>
         <v>テストの目的</v>
       </c>
-      <c r="D141" s="118" t="s">
+      <c r="D141" s="123" t="s">
         <v>228</v>
       </c>
-      <c r="E141" s="119"/>
-      <c r="F141" s="120"/>
+      <c r="E141" s="124"/>
+      <c r="F141" s="125"/>
       <c r="G141" s="48" t="s">
         <v>296</v>
       </c>
@@ -10347,16 +10360,16 @@
     </row>
     <row r="142" spans="1:14" ht="25.2">
       <c r="A142" s="11"/>
-      <c r="B142" s="110"/>
+      <c r="B142" s="136"/>
       <c r="C142" s="78" t="str">
         <f>master!C121</f>
         <v>テストを実施しなかった場合…</v>
       </c>
-      <c r="D142" s="118" t="s">
+      <c r="D142" s="123" t="s">
         <v>229</v>
       </c>
-      <c r="E142" s="119"/>
-      <c r="F142" s="120"/>
+      <c r="E142" s="124"/>
+      <c r="F142" s="125"/>
       <c r="G142" s="48" t="s">
         <v>295</v>
       </c>
@@ -10374,16 +10387,16 @@
     </row>
     <row r="143" spans="1:14" ht="100.8">
       <c r="A143" s="11"/>
-      <c r="B143" s="111"/>
+      <c r="B143" s="137"/>
       <c r="C143" s="78" t="str">
         <f>master!C122</f>
         <v>コラム：テストとデバッグ</v>
       </c>
-      <c r="D143" s="118" t="s">
+      <c r="D143" s="123" t="s">
         <v>230</v>
       </c>
-      <c r="E143" s="119"/>
-      <c r="F143" s="120"/>
+      <c r="E143" s="124"/>
+      <c r="F143" s="125"/>
       <c r="G143" s="48" t="s">
         <v>297</v>
       </c>
@@ -10401,7 +10414,7 @@
     </row>
     <row r="144" spans="1:14" ht="50.4">
       <c r="A144" s="11"/>
-      <c r="B144" s="109" t="str">
+      <c r="B144" s="135" t="str">
         <f>master!B123</f>
         <v>単体テストとは</v>
       </c>
@@ -10409,11 +10422,11 @@
         <f>master!C123</f>
         <v>単体テスト（Unit Test）とは</v>
       </c>
-      <c r="D144" s="118" t="s">
+      <c r="D144" s="123" t="s">
         <v>231</v>
       </c>
-      <c r="E144" s="119"/>
-      <c r="F144" s="120"/>
+      <c r="E144" s="124"/>
+      <c r="F144" s="125"/>
       <c r="G144" s="48" t="s">
         <v>294</v>
       </c>
@@ -10431,14 +10444,14 @@
     </row>
     <row r="145" spans="1:14" ht="25.2">
       <c r="A145" s="11"/>
-      <c r="B145" s="110"/>
+      <c r="B145" s="136"/>
       <c r="C145" s="78" t="str">
         <f>master!C124</f>
         <v xml:space="preserve">V字モデル　– 製造/単体テスト –　※再掲 </v>
       </c>
-      <c r="D145" s="118"/>
-      <c r="E145" s="119"/>
-      <c r="F145" s="120"/>
+      <c r="D145" s="123"/>
+      <c r="E145" s="124"/>
+      <c r="F145" s="125"/>
       <c r="G145" s="48" t="s">
         <v>295</v>
       </c>
@@ -10456,16 +10469,16 @@
     </row>
     <row r="146" spans="1:14" ht="302.39999999999998">
       <c r="A146" s="11"/>
-      <c r="B146" s="110"/>
+      <c r="B146" s="136"/>
       <c r="C146" s="78" t="str">
         <f>master!C125</f>
         <v>テスト設計の流れ</v>
       </c>
-      <c r="D146" s="118" t="s">
+      <c r="D146" s="123" t="s">
         <v>232</v>
       </c>
-      <c r="E146" s="119"/>
-      <c r="F146" s="120"/>
+      <c r="E146" s="124"/>
+      <c r="F146" s="125"/>
       <c r="G146" s="48" t="s">
         <v>298</v>
       </c>
@@ -10483,16 +10496,16 @@
     </row>
     <row r="147" spans="1:14" ht="37.799999999999997">
       <c r="A147" s="11"/>
-      <c r="B147" s="110"/>
+      <c r="B147" s="136"/>
       <c r="C147" s="78" t="str">
         <f>master!C126</f>
         <v>テスト設計の例</v>
       </c>
-      <c r="D147" s="118" t="s">
+      <c r="D147" s="123" t="s">
         <v>233</v>
       </c>
-      <c r="E147" s="119"/>
-      <c r="F147" s="120"/>
+      <c r="E147" s="124"/>
+      <c r="F147" s="125"/>
       <c r="G147" s="48" t="s">
         <v>299</v>
       </c>
@@ -10510,16 +10523,16 @@
     </row>
     <row r="148" spans="1:14" ht="75.599999999999994">
       <c r="A148" s="11"/>
-      <c r="B148" s="110"/>
+      <c r="B148" s="136"/>
       <c r="C148" s="78" t="str">
         <f>master!C127</f>
         <v>単体テスト（Unit Test）とは</v>
       </c>
-      <c r="D148" s="118" t="s">
+      <c r="D148" s="123" t="s">
         <v>234</v>
       </c>
-      <c r="E148" s="119"/>
-      <c r="F148" s="120"/>
+      <c r="E148" s="124"/>
+      <c r="F148" s="125"/>
       <c r="G148" s="48" t="s">
         <v>300</v>
       </c>
@@ -10537,16 +10550,16 @@
     </row>
     <row r="149" spans="1:14" ht="113.4">
       <c r="A149" s="11"/>
-      <c r="B149" s="110"/>
+      <c r="B149" s="136"/>
       <c r="C149" s="78" t="str">
         <f>master!C128</f>
         <v>テスト技法 – ブラックボックステスト技法 –</v>
       </c>
-      <c r="D149" s="118" t="s">
+      <c r="D149" s="123" t="s">
         <v>235</v>
       </c>
-      <c r="E149" s="119"/>
-      <c r="F149" s="120"/>
+      <c r="E149" s="124"/>
+      <c r="F149" s="125"/>
       <c r="G149" s="48" t="s">
         <v>301</v>
       </c>
@@ -10564,16 +10577,16 @@
     </row>
     <row r="150" spans="1:14" ht="201.6">
       <c r="A150" s="11"/>
-      <c r="B150" s="110"/>
+      <c r="B150" s="136"/>
       <c r="C150" s="78" t="str">
         <f>master!C129</f>
         <v>ブラックボックステスト：同値分割法</v>
       </c>
-      <c r="D150" s="118" t="s">
+      <c r="D150" s="123" t="s">
         <v>238</v>
       </c>
-      <c r="E150" s="119"/>
-      <c r="F150" s="120"/>
+      <c r="E150" s="124"/>
+      <c r="F150" s="125"/>
       <c r="G150" s="48" t="s">
         <v>302</v>
       </c>
@@ -10591,16 +10604,16 @@
     </row>
     <row r="151" spans="1:14" ht="113.4">
       <c r="A151" s="11"/>
-      <c r="B151" s="110"/>
+      <c r="B151" s="136"/>
       <c r="C151" s="78" t="str">
         <f>master!C130</f>
         <v>ブラックボックステスト：境界値分析</v>
       </c>
-      <c r="D151" s="118" t="s">
+      <c r="D151" s="123" t="s">
         <v>237</v>
       </c>
-      <c r="E151" s="119"/>
-      <c r="F151" s="120"/>
+      <c r="E151" s="124"/>
+      <c r="F151" s="125"/>
       <c r="G151" s="48" t="s">
         <v>301</v>
       </c>
@@ -10618,16 +10631,16 @@
     </row>
     <row r="152" spans="1:14" ht="176.4">
       <c r="A152" s="11"/>
-      <c r="B152" s="110"/>
+      <c r="B152" s="136"/>
       <c r="C152" s="78" t="str">
         <f>master!C131</f>
         <v>ブラックボックステスト：ディシジョンテーブルテスト</v>
       </c>
-      <c r="D152" s="118" t="s">
+      <c r="D152" s="123" t="s">
         <v>236</v>
       </c>
-      <c r="E152" s="119"/>
-      <c r="F152" s="120"/>
+      <c r="E152" s="124"/>
+      <c r="F152" s="125"/>
       <c r="G152" s="48" t="s">
         <v>303</v>
       </c>
@@ -10645,16 +10658,16 @@
     </row>
     <row r="153" spans="1:14" ht="37.799999999999997">
       <c r="A153" s="11"/>
-      <c r="B153" s="110"/>
+      <c r="B153" s="136"/>
       <c r="C153" s="78" t="str">
         <f>master!C132</f>
         <v>ブラックボックステスト：状態遷移テスト</v>
       </c>
-      <c r="D153" s="118" t="s">
+      <c r="D153" s="123" t="s">
         <v>239</v>
       </c>
-      <c r="E153" s="119"/>
-      <c r="F153" s="120"/>
+      <c r="E153" s="124"/>
+      <c r="F153" s="125"/>
       <c r="G153" s="48" t="s">
         <v>299</v>
       </c>
@@ -10672,16 +10685,16 @@
     </row>
     <row r="154" spans="1:14" ht="88.2">
       <c r="A154" s="11"/>
-      <c r="B154" s="110"/>
+      <c r="B154" s="136"/>
       <c r="C154" s="78" t="str">
         <f>master!C133</f>
         <v>テスト技法 – ホワイトボックステスト技法 –</v>
       </c>
-      <c r="D154" s="118" t="s">
+      <c r="D154" s="123" t="s">
         <v>240</v>
       </c>
-      <c r="E154" s="119"/>
-      <c r="F154" s="120"/>
+      <c r="E154" s="124"/>
+      <c r="F154" s="125"/>
       <c r="G154" s="48" t="s">
         <v>304</v>
       </c>
@@ -10699,16 +10712,16 @@
     </row>
     <row r="155" spans="1:14" ht="151.19999999999999">
       <c r="A155" s="11"/>
-      <c r="B155" s="110"/>
+      <c r="B155" s="136"/>
       <c r="C155" s="78" t="str">
         <f>master!C134</f>
         <v>ホワイトボックステストの評価基準</v>
       </c>
-      <c r="D155" s="118" t="s">
+      <c r="D155" s="123" t="s">
         <v>241</v>
       </c>
-      <c r="E155" s="119"/>
-      <c r="F155" s="120"/>
+      <c r="E155" s="124"/>
+      <c r="F155" s="125"/>
       <c r="G155" s="48" t="s">
         <v>305</v>
       </c>
@@ -10726,16 +10739,16 @@
     </row>
     <row r="156" spans="1:14" ht="37.799999999999997">
       <c r="A156" s="11"/>
-      <c r="B156" s="110"/>
+      <c r="B156" s="136"/>
       <c r="C156" s="78" t="str">
         <f>master!C135</f>
         <v>ホワイトボックステスト：ステートメントテスト</v>
       </c>
-      <c r="D156" s="118" t="s">
+      <c r="D156" s="123" t="s">
         <v>242</v>
       </c>
-      <c r="E156" s="119"/>
-      <c r="F156" s="120"/>
+      <c r="E156" s="124"/>
+      <c r="F156" s="125"/>
       <c r="G156" s="48" t="s">
         <v>299</v>
       </c>
@@ -10753,16 +10766,16 @@
     </row>
     <row r="157" spans="1:14" ht="37.799999999999997">
       <c r="A157" s="11"/>
-      <c r="B157" s="110"/>
+      <c r="B157" s="136"/>
       <c r="C157" s="78" t="str">
         <f>master!C136</f>
         <v>ホワイトボックステスト：ブランチテスト</v>
       </c>
-      <c r="D157" s="118" t="s">
+      <c r="D157" s="123" t="s">
         <v>243</v>
       </c>
-      <c r="E157" s="119"/>
-      <c r="F157" s="120"/>
+      <c r="E157" s="124"/>
+      <c r="F157" s="125"/>
       <c r="G157" s="48" t="s">
         <v>299</v>
       </c>
@@ -10780,16 +10793,16 @@
     </row>
     <row r="158" spans="1:14" ht="37.799999999999997">
       <c r="A158" s="11"/>
-      <c r="B158" s="110"/>
+      <c r="B158" s="136"/>
       <c r="C158" s="78" t="str">
         <f>master!C137</f>
         <v>ホワイトボックステスト：コンディションテスト</v>
       </c>
-      <c r="D158" s="118" t="s">
+      <c r="D158" s="123" t="s">
         <v>244</v>
       </c>
-      <c r="E158" s="119"/>
-      <c r="F158" s="120"/>
+      <c r="E158" s="124"/>
+      <c r="F158" s="125"/>
       <c r="G158" s="48" t="s">
         <v>299</v>
       </c>
@@ -10807,16 +10820,16 @@
     </row>
     <row r="159" spans="1:14" ht="37.799999999999997">
       <c r="A159" s="11"/>
-      <c r="B159" s="110"/>
+      <c r="B159" s="136"/>
       <c r="C159" s="78" t="str">
         <f>master!C138</f>
         <v>テスト技法 – 経験ベースの技法 –</v>
       </c>
-      <c r="D159" s="118" t="s">
+      <c r="D159" s="123" t="s">
         <v>245</v>
       </c>
-      <c r="E159" s="119"/>
-      <c r="F159" s="120"/>
+      <c r="E159" s="124"/>
+      <c r="F159" s="125"/>
       <c r="G159" s="48" t="s">
         <v>299</v>
       </c>
@@ -10834,16 +10847,16 @@
     </row>
     <row r="160" spans="1:14" ht="100.8">
       <c r="A160" s="11"/>
-      <c r="B160" s="110"/>
+      <c r="B160" s="136"/>
       <c r="C160" s="78" t="str">
         <f>master!C139</f>
         <v>スタブとドライバ</v>
       </c>
-      <c r="D160" s="118" t="s">
+      <c r="D160" s="123" t="s">
         <v>246</v>
       </c>
-      <c r="E160" s="119"/>
-      <c r="F160" s="120"/>
+      <c r="E160" s="124"/>
+      <c r="F160" s="125"/>
       <c r="G160" s="48" t="s">
         <v>297</v>
       </c>
@@ -10861,16 +10874,16 @@
     </row>
     <row r="161" spans="1:14" ht="75.599999999999994">
       <c r="A161" s="11"/>
-      <c r="B161" s="111"/>
+      <c r="B161" s="137"/>
       <c r="C161" s="78" t="str">
         <f>master!C140</f>
         <v>スタブとモック</v>
       </c>
-      <c r="D161" s="118" t="s">
+      <c r="D161" s="123" t="s">
         <v>247</v>
       </c>
-      <c r="E161" s="119"/>
-      <c r="F161" s="120"/>
+      <c r="E161" s="124"/>
+      <c r="F161" s="125"/>
       <c r="G161" s="48" t="s">
         <v>300</v>
       </c>
@@ -10888,7 +10901,7 @@
     </row>
     <row r="162" spans="1:14" ht="37.799999999999997">
       <c r="A162" s="11"/>
-      <c r="B162" s="109" t="str">
+      <c r="B162" s="135" t="str">
         <f>master!B141</f>
         <v>JUnit</v>
       </c>
@@ -10896,11 +10909,11 @@
         <f>master!C141</f>
         <v>JUnitとは</v>
       </c>
-      <c r="D162" s="118" t="s">
+      <c r="D162" s="123" t="s">
         <v>248</v>
       </c>
-      <c r="E162" s="119"/>
-      <c r="F162" s="120"/>
+      <c r="E162" s="124"/>
+      <c r="F162" s="125"/>
       <c r="G162" s="48" t="s">
         <v>299</v>
       </c>
@@ -10918,14 +10931,14 @@
     </row>
     <row r="163" spans="1:14" ht="25.2">
       <c r="A163" s="11"/>
-      <c r="B163" s="111"/>
+      <c r="B163" s="137"/>
       <c r="C163" s="78" t="str">
         <f>master!C142</f>
         <v>参考文献</v>
       </c>
-      <c r="D163" s="118"/>
-      <c r="E163" s="119"/>
-      <c r="F163" s="120"/>
+      <c r="D163" s="123"/>
+      <c r="E163" s="124"/>
+      <c r="F163" s="125"/>
       <c r="G163" s="48" t="s">
         <v>295</v>
       </c>
@@ -10941,80 +10954,77 @@
       <c r="M163" s="6"/>
       <c r="N163" s="6"/>
     </row>
-    <row r="164" spans="1:14" ht="37.799999999999997">
+    <row r="164" spans="1:14" ht="25.2">
       <c r="A164" s="11"/>
-      <c r="B164" s="88" t="str">
-        <f>master!B67</f>
-        <v>課題1の実施</v>
+      <c r="B164" s="126" t="str">
+        <f>master!B144</f>
+        <v>課題2の導入</v>
       </c>
       <c r="C164" s="58" t="str">
-        <f>master!C67</f>
-        <v>ここから各自で演習を始めましょう。</v>
-      </c>
-      <c r="D164" s="112" t="s">
-        <v>249</v>
-      </c>
-      <c r="E164" s="113"/>
-      <c r="F164" s="114"/>
+        <f>master!C144</f>
+        <v>演習課題の概要</v>
+      </c>
+      <c r="D164" s="114" t="s">
+        <v>265</v>
+      </c>
+      <c r="E164" s="115"/>
+      <c r="F164" s="116"/>
       <c r="G164" s="58" t="s">
-        <v>41</v>
+        <v>306</v>
       </c>
       <c r="H164" s="59"/>
       <c r="I164" s="60" t="s">
         <v>24</v>
       </c>
-      <c r="J164" s="61" t="s">
-        <v>335</v>
+      <c r="J164" s="61">
+        <v>6.9444444444444447E-4</v>
       </c>
       <c r="K164" s="62"/>
       <c r="L164" s="6"/>
       <c r="M164" s="6"/>
       <c r="N164" s="6"/>
     </row>
-    <row r="165" spans="1:14" ht="25.2">
+    <row r="165" spans="1:14" ht="138.6">
       <c r="A165" s="11"/>
-      <c r="B165" s="115" t="str">
-        <f>master!B144</f>
-        <v>課題2の導入</v>
-      </c>
+      <c r="B165" s="127"/>
       <c r="C165" s="58" t="str">
-        <f>master!C144</f>
-        <v>演習課題の概要</v>
-      </c>
-      <c r="D165" s="112" t="s">
-        <v>265</v>
-      </c>
-      <c r="E165" s="113"/>
-      <c r="F165" s="114"/>
+        <f>master!C145</f>
+        <v>[構造理解] Webアプリケーションで必要なもの  ※再掲</v>
+      </c>
+      <c r="D165" s="114" t="s">
+        <v>266</v>
+      </c>
+      <c r="E165" s="115"/>
+      <c r="F165" s="116"/>
       <c r="G165" s="58" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="H165" s="59"/>
       <c r="I165" s="60" t="s">
         <v>24</v>
       </c>
       <c r="J165" s="61">
-        <v>6.9444444444444447E-4</v>
+        <v>2.0833333333333333E-3</v>
       </c>
       <c r="K165" s="62"/>
       <c r="L165" s="6"/>
       <c r="M165" s="6"/>
       <c r="N165" s="6"/>
     </row>
-    <row r="166" spans="1:14" ht="138.6">
+    <row r="166" spans="1:14" ht="50.4">
       <c r="A166" s="11"/>
-      <c r="B166" s="116"/>
+      <c r="B166" s="127"/>
       <c r="C166" s="58" t="str">
-        <f>master!C145</f>
-        <v>[構造理解] Webアプリケーションで必要なもの  ※再掲</v>
-      </c>
-      <c r="D166" s="112" t="s">
-        <v>266</v>
-      </c>
-      <c r="E166" s="113"/>
-      <c r="F166" s="114"/>
+        <f>master!C146</f>
+        <v>テストクラスを作成する単位</v>
+      </c>
+      <c r="D166" s="114" t="s">
+        <v>267</v>
+      </c>
+      <c r="E166" s="115"/>
+      <c r="F166" s="116"/>
       <c r="G166" s="58" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="H166" s="59"/>
       <c r="I166" s="60" t="s">
@@ -11028,369 +11038,372 @@
       <c r="M166" s="6"/>
       <c r="N166" s="6"/>
     </row>
-    <row r="167" spans="1:14" ht="50.4">
+    <row r="167" spans="1:14" ht="113.4">
       <c r="A167" s="11"/>
-      <c r="B167" s="116"/>
+      <c r="B167" s="128"/>
       <c r="C167" s="58" t="str">
-        <f>master!C146</f>
-        <v>テストクラスを作成する単位</v>
-      </c>
-      <c r="D167" s="112" t="s">
-        <v>267</v>
-      </c>
-      <c r="E167" s="113"/>
-      <c r="F167" s="114"/>
+        <f>master!C147</f>
+        <v>JUnitで単体テスト</v>
+      </c>
+      <c r="D167" s="114" t="s">
+        <v>268</v>
+      </c>
+      <c r="E167" s="115"/>
+      <c r="F167" s="116"/>
       <c r="G167" s="58" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="H167" s="59"/>
       <c r="I167" s="60" t="s">
         <v>24</v>
       </c>
       <c r="J167" s="61">
-        <v>2.0833333333333333E-3</v>
+        <v>3.472222222222222E-3</v>
       </c>
       <c r="K167" s="62"/>
       <c r="L167" s="6"/>
       <c r="M167" s="6"/>
       <c r="N167" s="6"/>
     </row>
-    <row r="168" spans="1:14" ht="113.4">
+    <row r="168" spans="1:14" ht="25.2">
       <c r="A168" s="11"/>
-      <c r="B168" s="117"/>
+      <c r="B168" s="126" t="str">
+        <f>master!B148</f>
+        <v>ハンズオン</v>
+      </c>
       <c r="C168" s="58" t="str">
-        <f>master!C147</f>
-        <v>JUnitで単体テスト</v>
-      </c>
-      <c r="D168" s="112" t="s">
-        <v>268</v>
-      </c>
-      <c r="E168" s="113"/>
-      <c r="F168" s="114"/>
+        <f>master!C148</f>
+        <v>バイブコーディングで単体テスト – はじめに</v>
+      </c>
+      <c r="D168" s="114" t="s">
+        <v>269</v>
+      </c>
+      <c r="E168" s="115"/>
+      <c r="F168" s="116"/>
       <c r="G168" s="58" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="H168" s="59"/>
       <c r="I168" s="60" t="s">
         <v>24</v>
       </c>
       <c r="J168" s="61">
-        <v>3.472222222222222E-3</v>
+        <v>6.9444444444444447E-4</v>
       </c>
       <c r="K168" s="62"/>
       <c r="L168" s="6"/>
       <c r="M168" s="6"/>
       <c r="N168" s="6"/>
     </row>
-    <row r="169" spans="1:14" ht="25.2">
+    <row r="169" spans="1:14" ht="50.4">
       <c r="A169" s="11"/>
-      <c r="B169" s="115" t="str">
-        <f>master!B148</f>
-        <v>ハンズオン</v>
-      </c>
-      <c r="C169" s="58" t="str">
-        <f>master!C148</f>
-        <v>バイブコーディングで単体テスト – はじめに</v>
-      </c>
-      <c r="D169" s="112" t="s">
-        <v>269</v>
-      </c>
-      <c r="E169" s="113"/>
-      <c r="F169" s="114"/>
+      <c r="B169" s="127"/>
+      <c r="C169" s="76" t="str">
+        <f>master!C149</f>
+        <v>バイブコーディング単体テスト①テスト項目表を作る</v>
+      </c>
+      <c r="D169" s="114" t="s">
+        <v>270</v>
+      </c>
+      <c r="E169" s="115"/>
+      <c r="F169" s="116"/>
       <c r="G169" s="58" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="H169" s="59"/>
       <c r="I169" s="60" t="s">
         <v>24</v>
       </c>
       <c r="J169" s="61">
-        <v>6.9444444444444447E-4</v>
+        <v>3.472222222222222E-3</v>
       </c>
       <c r="K169" s="62"/>
       <c r="L169" s="6"/>
       <c r="M169" s="6"/>
       <c r="N169" s="6"/>
     </row>
-    <row r="170" spans="1:14" ht="50.4">
+    <row r="170" spans="1:14" ht="88.2">
       <c r="A170" s="11"/>
-      <c r="B170" s="116"/>
-      <c r="C170" s="76" t="str">
-        <f>master!C149</f>
-        <v>バイブコーディング単体テスト①テスト項目表を作る</v>
-      </c>
-      <c r="D170" s="112" t="s">
-        <v>270</v>
-      </c>
-      <c r="E170" s="113"/>
-      <c r="F170" s="114"/>
-      <c r="G170" s="58" t="s">
-        <v>308</v>
-      </c>
-      <c r="H170" s="59"/>
-      <c r="I170" s="60" t="s">
-        <v>24</v>
-      </c>
-      <c r="J170" s="61">
-        <v>3.472222222222222E-3</v>
-      </c>
-      <c r="K170" s="62"/>
+      <c r="B170" s="127"/>
+      <c r="C170" s="77"/>
+      <c r="D170" s="129" t="s">
+        <v>181</v>
+      </c>
+      <c r="E170" s="130"/>
+      <c r="F170" s="131"/>
+      <c r="G170" s="93" t="s">
+        <v>310</v>
+      </c>
+      <c r="H170" s="94"/>
+      <c r="I170" s="95" t="s">
+        <v>24</v>
+      </c>
+      <c r="J170" s="96">
+        <v>6.9444444444444441E-3</v>
+      </c>
+      <c r="K170" s="97"/>
       <c r="L170" s="6"/>
       <c r="M170" s="6"/>
       <c r="N170" s="6"/>
     </row>
-    <row r="171" spans="1:14" ht="88.2">
+    <row r="171" spans="1:14" ht="50.4">
       <c r="A171" s="11"/>
-      <c r="B171" s="116"/>
-      <c r="C171" s="77"/>
-      <c r="D171" s="131" t="s">
-        <v>181</v>
-      </c>
-      <c r="E171" s="132"/>
-      <c r="F171" s="133"/>
-      <c r="G171" s="130" t="s">
-        <v>310</v>
-      </c>
-      <c r="H171" s="134"/>
-      <c r="I171" s="135" t="s">
-        <v>24</v>
-      </c>
-      <c r="J171" s="136">
-        <v>6.9444444444444441E-3</v>
-      </c>
-      <c r="K171" s="137"/>
+      <c r="B171" s="127"/>
+      <c r="C171" s="76" t="str">
+        <f>master!C150</f>
+        <v>バイブコーディング単体テスト②Repositoryのテストを作る</v>
+      </c>
+      <c r="D171" s="114" t="s">
+        <v>271</v>
+      </c>
+      <c r="E171" s="115"/>
+      <c r="F171" s="116"/>
+      <c r="G171" s="58" t="s">
+        <v>308</v>
+      </c>
+      <c r="H171" s="59"/>
+      <c r="I171" s="60" t="s">
+        <v>24</v>
+      </c>
+      <c r="J171" s="61">
+        <v>3.472222222222222E-3</v>
+      </c>
+      <c r="K171" s="62"/>
       <c r="L171" s="6"/>
       <c r="M171" s="6"/>
       <c r="N171" s="6"/>
     </row>
-    <row r="172" spans="1:14" ht="50.4">
+    <row r="172" spans="1:14" ht="88.2">
       <c r="A172" s="11"/>
-      <c r="B172" s="116"/>
-      <c r="C172" s="76" t="str">
-        <f>master!C150</f>
-        <v>バイブコーディング単体テスト②Repositoryのテストを作る</v>
-      </c>
-      <c r="D172" s="112" t="s">
-        <v>271</v>
-      </c>
-      <c r="E172" s="113"/>
-      <c r="F172" s="114"/>
-      <c r="G172" s="58" t="s">
-        <v>308</v>
-      </c>
-      <c r="H172" s="59"/>
-      <c r="I172" s="60" t="s">
-        <v>24</v>
-      </c>
-      <c r="J172" s="61">
-        <v>3.472222222222222E-3</v>
-      </c>
-      <c r="K172" s="62"/>
+      <c r="B172" s="127"/>
+      <c r="C172" s="77"/>
+      <c r="D172" s="129" t="s">
+        <v>181</v>
+      </c>
+      <c r="E172" s="130"/>
+      <c r="F172" s="131"/>
+      <c r="G172" s="93" t="s">
+        <v>310</v>
+      </c>
+      <c r="H172" s="94"/>
+      <c r="I172" s="95" t="s">
+        <v>24</v>
+      </c>
+      <c r="J172" s="96">
+        <v>6.9444444444444441E-3</v>
+      </c>
+      <c r="K172" s="97"/>
       <c r="L172" s="6"/>
       <c r="M172" s="6"/>
       <c r="N172" s="6"/>
     </row>
-    <row r="173" spans="1:14" ht="88.2">
+    <row r="173" spans="1:14" ht="138.6">
       <c r="A173" s="11"/>
-      <c r="B173" s="116"/>
-      <c r="C173" s="77"/>
-      <c r="D173" s="131" t="s">
-        <v>181</v>
-      </c>
-      <c r="E173" s="132"/>
-      <c r="F173" s="133"/>
-      <c r="G173" s="130" t="s">
-        <v>310</v>
-      </c>
-      <c r="H173" s="134"/>
-      <c r="I173" s="135" t="s">
-        <v>24</v>
-      </c>
-      <c r="J173" s="136">
+      <c r="B173" s="127"/>
+      <c r="C173" s="58" t="str">
+        <f>master!C151</f>
+        <v>[解説] Repositoryのテストクラス（抜粋）</v>
+      </c>
+      <c r="D173" s="114" t="s">
+        <v>273</v>
+      </c>
+      <c r="E173" s="115"/>
+      <c r="F173" s="116"/>
+      <c r="G173" s="58" t="s">
+        <v>307</v>
+      </c>
+      <c r="H173" s="59"/>
+      <c r="I173" s="60" t="s">
+        <v>24</v>
+      </c>
+      <c r="J173" s="61">
         <v>6.9444444444444441E-3</v>
       </c>
-      <c r="K173" s="137"/>
+      <c r="K173" s="62"/>
       <c r="L173" s="6"/>
       <c r="M173" s="6"/>
       <c r="N173" s="6"/>
     </row>
-    <row r="174" spans="1:14" ht="138.6">
+    <row r="174" spans="1:14" ht="50.4">
       <c r="A174" s="11"/>
-      <c r="B174" s="116"/>
-      <c r="C174" s="58" t="str">
-        <f>master!C151</f>
-        <v>[解説] Repositoryのテストクラス（抜粋）</v>
-      </c>
-      <c r="D174" s="112" t="s">
-        <v>273</v>
-      </c>
-      <c r="E174" s="113"/>
-      <c r="F174" s="114"/>
+      <c r="B174" s="127"/>
+      <c r="C174" s="76" t="str">
+        <f>master!C152</f>
+        <v>バイブコーディング単体テスト③Serviceのテストを作る</v>
+      </c>
+      <c r="D174" s="114" t="s">
+        <v>271</v>
+      </c>
+      <c r="E174" s="115"/>
+      <c r="F174" s="116"/>
       <c r="G174" s="58" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="H174" s="59"/>
       <c r="I174" s="60" t="s">
         <v>24</v>
       </c>
       <c r="J174" s="61">
-        <v>6.9444444444444441E-3</v>
+        <v>3.472222222222222E-3</v>
       </c>
       <c r="K174" s="62"/>
       <c r="L174" s="6"/>
       <c r="M174" s="6"/>
       <c r="N174" s="6"/>
     </row>
-    <row r="175" spans="1:14" ht="50.4">
+    <row r="175" spans="1:14" ht="88.2">
       <c r="A175" s="11"/>
-      <c r="B175" s="116"/>
-      <c r="C175" s="76" t="str">
-        <f>master!C152</f>
-        <v>バイブコーディング単体テスト③Serviceのテストを作る</v>
-      </c>
-      <c r="D175" s="112" t="s">
-        <v>271</v>
-      </c>
-      <c r="E175" s="113"/>
-      <c r="F175" s="114"/>
-      <c r="G175" s="58" t="s">
-        <v>308</v>
-      </c>
-      <c r="H175" s="59"/>
-      <c r="I175" s="60" t="s">
-        <v>24</v>
-      </c>
-      <c r="J175" s="61">
-        <v>3.472222222222222E-3</v>
-      </c>
-      <c r="K175" s="62"/>
+      <c r="B175" s="127"/>
+      <c r="C175" s="77"/>
+      <c r="D175" s="129" t="s">
+        <v>181</v>
+      </c>
+      <c r="E175" s="130"/>
+      <c r="F175" s="131"/>
+      <c r="G175" s="93" t="s">
+        <v>310</v>
+      </c>
+      <c r="H175" s="94"/>
+      <c r="I175" s="95" t="s">
+        <v>24</v>
+      </c>
+      <c r="J175" s="96">
+        <v>6.9444444444444441E-3</v>
+      </c>
+      <c r="K175" s="97"/>
       <c r="L175" s="6"/>
       <c r="M175" s="6"/>
       <c r="N175" s="6"/>
     </row>
-    <row r="176" spans="1:14" ht="88.2">
+    <row r="176" spans="1:14" ht="138.6">
       <c r="A176" s="11"/>
-      <c r="B176" s="116"/>
-      <c r="C176" s="77"/>
-      <c r="D176" s="131" t="s">
-        <v>181</v>
-      </c>
-      <c r="E176" s="132"/>
-      <c r="F176" s="133"/>
-      <c r="G176" s="130" t="s">
-        <v>310</v>
-      </c>
-      <c r="H176" s="134"/>
-      <c r="I176" s="135" t="s">
-        <v>24</v>
-      </c>
-      <c r="J176" s="136">
+      <c r="B176" s="127"/>
+      <c r="C176" s="58" t="str">
+        <f>master!C153</f>
+        <v>[解説] Serviceのテストクラス（抜粋）</v>
+      </c>
+      <c r="D176" s="114" t="s">
+        <v>272</v>
+      </c>
+      <c r="E176" s="115"/>
+      <c r="F176" s="116"/>
+      <c r="G176" s="58" t="s">
+        <v>307</v>
+      </c>
+      <c r="H176" s="59"/>
+      <c r="I176" s="60" t="s">
+        <v>24</v>
+      </c>
+      <c r="J176" s="61">
         <v>6.9444444444444441E-3</v>
       </c>
-      <c r="K176" s="137"/>
+      <c r="K176" s="62"/>
       <c r="L176" s="6"/>
       <c r="M176" s="6"/>
       <c r="N176" s="6"/>
     </row>
-    <row r="177" spans="1:14" ht="138.6">
+    <row r="177" spans="1:14" ht="50.4">
       <c r="A177" s="11"/>
-      <c r="B177" s="116"/>
-      <c r="C177" s="58" t="str">
-        <f>master!C153</f>
-        <v>[解説] Serviceのテストクラス（抜粋）</v>
-      </c>
-      <c r="D177" s="112" t="s">
-        <v>272</v>
-      </c>
-      <c r="E177" s="113"/>
-      <c r="F177" s="114"/>
+      <c r="B177" s="127"/>
+      <c r="C177" s="76" t="str">
+        <f>master!C154</f>
+        <v>バイブコーディング単体テスト④Controllerのテストを作る</v>
+      </c>
+      <c r="D177" s="114" t="s">
+        <v>271</v>
+      </c>
+      <c r="E177" s="115"/>
+      <c r="F177" s="116"/>
       <c r="G177" s="58" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="H177" s="59"/>
       <c r="I177" s="60" t="s">
         <v>24</v>
       </c>
       <c r="J177" s="61">
-        <v>6.9444444444444441E-3</v>
+        <v>3.472222222222222E-3</v>
       </c>
       <c r="K177" s="62"/>
       <c r="L177" s="6"/>
       <c r="M177" s="6"/>
       <c r="N177" s="6"/>
     </row>
-    <row r="178" spans="1:14" ht="50.4">
+    <row r="178" spans="1:14" ht="88.2">
       <c r="A178" s="11"/>
-      <c r="B178" s="116"/>
-      <c r="C178" s="76" t="str">
-        <f>master!C154</f>
-        <v>バイブコーディング単体テスト④Controllerのテストを作る</v>
-      </c>
-      <c r="D178" s="112" t="s">
-        <v>271</v>
-      </c>
-      <c r="E178" s="113"/>
-      <c r="F178" s="114"/>
-      <c r="G178" s="58" t="s">
-        <v>308</v>
-      </c>
-      <c r="H178" s="59"/>
-      <c r="I178" s="60" t="s">
-        <v>24</v>
-      </c>
-      <c r="J178" s="61">
-        <v>3.472222222222222E-3</v>
-      </c>
-      <c r="K178" s="62"/>
+      <c r="B178" s="127"/>
+      <c r="C178" s="77"/>
+      <c r="D178" s="129" t="s">
+        <v>181</v>
+      </c>
+      <c r="E178" s="130"/>
+      <c r="F178" s="131"/>
+      <c r="G178" s="93" t="s">
+        <v>310</v>
+      </c>
+      <c r="H178" s="94"/>
+      <c r="I178" s="95" t="s">
+        <v>24</v>
+      </c>
+      <c r="J178" s="96">
+        <v>6.9444444444444441E-3</v>
+      </c>
+      <c r="K178" s="97"/>
       <c r="L178" s="6"/>
       <c r="M178" s="6"/>
       <c r="N178" s="6"/>
     </row>
-    <row r="179" spans="1:14" ht="88.2">
+    <row r="179" spans="1:14" ht="163.80000000000001">
       <c r="A179" s="11"/>
-      <c r="B179" s="116"/>
-      <c r="C179" s="77"/>
-      <c r="D179" s="131" t="s">
-        <v>181</v>
-      </c>
-      <c r="E179" s="132"/>
-      <c r="F179" s="133"/>
-      <c r="G179" s="130" t="s">
-        <v>310</v>
-      </c>
-      <c r="H179" s="134"/>
-      <c r="I179" s="135" t="s">
-        <v>24</v>
-      </c>
-      <c r="J179" s="136">
+      <c r="B179" s="128"/>
+      <c r="C179" s="58" t="str">
+        <f>master!C155</f>
+        <v>[解説] Controllerのテストクラス（抜粋）</v>
+      </c>
+      <c r="D179" s="114" t="s">
+        <v>274</v>
+      </c>
+      <c r="E179" s="115"/>
+      <c r="F179" s="116"/>
+      <c r="G179" s="58" t="s">
+        <v>311</v>
+      </c>
+      <c r="H179" s="59"/>
+      <c r="I179" s="60" t="s">
+        <v>24</v>
+      </c>
+      <c r="J179" s="61">
         <v>6.9444444444444441E-3</v>
       </c>
-      <c r="K179" s="137"/>
+      <c r="K179" s="62"/>
       <c r="L179" s="6"/>
       <c r="M179" s="6"/>
       <c r="N179" s="6"/>
     </row>
-    <row r="180" spans="1:14" ht="163.80000000000001">
+    <row r="180" spans="1:14" ht="37.799999999999997">
       <c r="A180" s="11"/>
-      <c r="B180" s="117"/>
+      <c r="B180" s="88" t="str">
+        <f>master!B67</f>
+        <v>課題1の実施</v>
+      </c>
       <c r="C180" s="58" t="str">
-        <f>master!C155</f>
-        <v>[解説] Controllerのテストクラス（抜粋）</v>
-      </c>
-      <c r="D180" s="112" t="s">
-        <v>274</v>
-      </c>
-      <c r="E180" s="113"/>
-      <c r="F180" s="114"/>
+        <f>master!C67</f>
+        <v>ここから各自で演習を始めましょう。</v>
+      </c>
+      <c r="D180" s="114" t="s">
+        <v>249</v>
+      </c>
+      <c r="E180" s="115"/>
+      <c r="F180" s="116"/>
       <c r="G180" s="58" t="s">
-        <v>311</v>
+        <v>41</v>
       </c>
       <c r="H180" s="59"/>
       <c r="I180" s="60" t="s">
         <v>24</v>
       </c>
-      <c r="J180" s="61">
-        <v>6.9444444444444441E-3</v>
+      <c r="J180" s="61" t="s">
+        <v>335</v>
       </c>
       <c r="K180" s="62"/>
       <c r="L180" s="6"/>
@@ -11399,7 +11412,7 @@
     </row>
     <row r="181" spans="1:14" ht="165" customHeight="1">
       <c r="A181" s="11"/>
-      <c r="B181" s="115" t="str">
+      <c r="B181" s="126" t="str">
         <f>master!B156</f>
         <v>課題2の実施</v>
       </c>
@@ -11407,11 +11420,11 @@
         <f>master!C156</f>
         <v>ここから各自で演習を始めましょう。</v>
       </c>
-      <c r="D181" s="112" t="s">
+      <c r="D181" s="114" t="s">
         <v>275</v>
       </c>
-      <c r="E181" s="113"/>
-      <c r="F181" s="114"/>
+      <c r="E181" s="115"/>
+      <c r="F181" s="116"/>
       <c r="G181" s="58" t="s">
         <v>311</v>
       </c>
@@ -11429,16 +11442,16 @@
     </row>
     <row r="182" spans="1:14" ht="151.19999999999999">
       <c r="A182" s="11"/>
-      <c r="B182" s="117"/>
+      <c r="B182" s="128"/>
       <c r="C182" s="58" t="str">
         <f>master!C157</f>
         <v>[終了条件] 講師配布のテストプログラム(JUnit)が成功すること</v>
       </c>
-      <c r="D182" s="112" t="s">
+      <c r="D182" s="114" t="s">
         <v>334</v>
       </c>
-      <c r="E182" s="113"/>
-      <c r="F182" s="114"/>
+      <c r="E182" s="115"/>
+      <c r="F182" s="116"/>
       <c r="G182" s="58" t="s">
         <v>333</v>
       </c>
@@ -11450,7 +11463,7 @@
         <v>335</v>
       </c>
       <c r="K182" s="62" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="L182" s="6"/>
       <c r="M182" s="6"/>
@@ -11458,7 +11471,7 @@
     </row>
     <row r="183" spans="1:14" ht="163.80000000000001">
       <c r="A183" s="11"/>
-      <c r="B183" s="115" t="str">
+      <c r="B183" s="126" t="str">
         <f>master!B159</f>
         <v>追加課題</v>
       </c>
@@ -11466,11 +11479,11 @@
         <f>master!C159</f>
         <v>演習課題の概要</v>
       </c>
-      <c r="D183" s="112" t="s">
+      <c r="D183" s="114" t="s">
         <v>277</v>
       </c>
-      <c r="E183" s="113"/>
-      <c r="F183" s="114"/>
+      <c r="E183" s="115"/>
+      <c r="F183" s="116"/>
       <c r="G183" s="58" t="s">
         <v>331</v>
       </c>
@@ -11482,7 +11495,7 @@
         <v>335</v>
       </c>
       <c r="K183" s="62" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="L183" s="6"/>
       <c r="M183" s="6"/>
@@ -11490,16 +11503,16 @@
     </row>
     <row r="184" spans="1:14" ht="25.2">
       <c r="A184" s="11"/>
-      <c r="B184" s="116"/>
+      <c r="B184" s="127"/>
       <c r="C184" s="58" t="str">
         <f>master!C160</f>
         <v>追加課題①：送料の表示機能</v>
       </c>
-      <c r="D184" s="112" t="s">
+      <c r="D184" s="114" t="s">
         <v>279</v>
       </c>
-      <c r="E184" s="113"/>
-      <c r="F184" s="114"/>
+      <c r="E184" s="115"/>
+      <c r="F184" s="116"/>
       <c r="G184" s="58" t="s">
         <v>332</v>
       </c>
@@ -11511,7 +11524,7 @@
         <v>335</v>
       </c>
       <c r="K184" s="62" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="L184" s="6"/>
       <c r="M184" s="6"/>
@@ -11519,16 +11532,16 @@
     </row>
     <row r="185" spans="1:14" ht="25.2">
       <c r="A185" s="11"/>
-      <c r="B185" s="116"/>
+      <c r="B185" s="127"/>
       <c r="C185" s="58" t="str">
         <f>master!C161</f>
         <v>追加課題②：クーポン機能</v>
       </c>
-      <c r="D185" s="112" t="s">
+      <c r="D185" s="114" t="s">
         <v>279</v>
       </c>
-      <c r="E185" s="113"/>
-      <c r="F185" s="114"/>
+      <c r="E185" s="115"/>
+      <c r="F185" s="116"/>
       <c r="G185" s="58" t="s">
         <v>332</v>
       </c>
@@ -11540,7 +11553,7 @@
         <v>335</v>
       </c>
       <c r="K185" s="62" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="L185" s="6"/>
       <c r="M185" s="6"/>
@@ -11548,16 +11561,16 @@
     </row>
     <row r="186" spans="1:14" ht="25.2">
       <c r="A186" s="11"/>
-      <c r="B186" s="117"/>
+      <c r="B186" s="128"/>
       <c r="C186" s="58" t="str">
         <f>master!C162</f>
         <v>追加課題③：ユーザーアカウント機能</v>
       </c>
-      <c r="D186" s="112" t="s">
+      <c r="D186" s="114" t="s">
         <v>279</v>
       </c>
-      <c r="E186" s="113"/>
-      <c r="F186" s="114"/>
+      <c r="E186" s="115"/>
+      <c r="F186" s="116"/>
       <c r="G186" s="58" t="s">
         <v>332</v>
       </c>
@@ -11569,7 +11582,7 @@
         <v>335</v>
       </c>
       <c r="K186" s="62" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="L186" s="6"/>
       <c r="M186" s="6"/>
@@ -11577,7 +11590,7 @@
     </row>
     <row r="187" spans="1:14" ht="176.4">
       <c r="A187" s="11"/>
-      <c r="B187" s="115" t="str">
+      <c r="B187" s="126" t="str">
         <f>master!B164</f>
         <v>演習の振り返り</v>
       </c>
@@ -11585,13 +11598,13 @@
         <f>master!C164</f>
         <v>アプリケーションの比較・分析</v>
       </c>
-      <c r="D187" s="112" t="s">
-        <v>435</v>
-      </c>
-      <c r="E187" s="113"/>
-      <c r="F187" s="114"/>
+      <c r="D187" s="114" t="s">
+        <v>433</v>
+      </c>
+      <c r="E187" s="115"/>
+      <c r="F187" s="116"/>
       <c r="G187" s="58" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="H187" s="59"/>
       <c r="I187" s="60" t="s">
@@ -11607,18 +11620,18 @@
     </row>
     <row r="188" spans="1:14" ht="63">
       <c r="A188" s="11"/>
-      <c r="B188" s="116"/>
+      <c r="B188" s="127"/>
       <c r="C188" s="58" t="str">
         <f>master!C165</f>
         <v>改善点の整理</v>
       </c>
-      <c r="D188" s="112" t="s">
-        <v>434</v>
-      </c>
-      <c r="E188" s="113"/>
-      <c r="F188" s="114"/>
+      <c r="D188" s="114" t="s">
+        <v>432</v>
+      </c>
+      <c r="E188" s="115"/>
+      <c r="F188" s="116"/>
       <c r="G188" s="58" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="H188" s="59"/>
       <c r="I188" s="60" t="s">
@@ -11634,18 +11647,18 @@
     </row>
     <row r="189" spans="1:14" ht="63">
       <c r="A189" s="11"/>
-      <c r="B189" s="117"/>
+      <c r="B189" s="128"/>
       <c r="C189" s="58" t="str">
         <f>master!C166</f>
         <v>分析結果の共有</v>
       </c>
-      <c r="D189" s="112" t="s">
-        <v>432</v>
-      </c>
-      <c r="E189" s="113"/>
-      <c r="F189" s="114"/>
+      <c r="D189" s="114" t="s">
+        <v>430</v>
+      </c>
+      <c r="E189" s="115"/>
+      <c r="F189" s="116"/>
       <c r="G189" s="58" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="H189" s="59"/>
       <c r="I189" s="60" t="s">
@@ -11665,6 +11678,186 @@
     <row r="191" spans="1:14" ht="15" customHeight="1"/>
   </sheetData>
   <mergeCells count="204">
+    <mergeCell ref="B137:B139"/>
+    <mergeCell ref="B162:B163"/>
+    <mergeCell ref="D180:F180"/>
+    <mergeCell ref="D187:F187"/>
+    <mergeCell ref="D184:F184"/>
+    <mergeCell ref="D183:F183"/>
+    <mergeCell ref="D164:F164"/>
+    <mergeCell ref="D165:F165"/>
+    <mergeCell ref="D166:F166"/>
+    <mergeCell ref="D179:F179"/>
+    <mergeCell ref="D181:F181"/>
+    <mergeCell ref="D167:F167"/>
+    <mergeCell ref="D168:F168"/>
+    <mergeCell ref="D176:F176"/>
+    <mergeCell ref="D170:F170"/>
+    <mergeCell ref="D172:F172"/>
+    <mergeCell ref="D173:F173"/>
+    <mergeCell ref="B168:B179"/>
+    <mergeCell ref="B164:B167"/>
+    <mergeCell ref="B140:B143"/>
+    <mergeCell ref="B144:B161"/>
+    <mergeCell ref="D139:F139"/>
+    <mergeCell ref="D140:F140"/>
+    <mergeCell ref="D141:F141"/>
+    <mergeCell ref="D160:F160"/>
+    <mergeCell ref="D161:F161"/>
+    <mergeCell ref="D143:F143"/>
+    <mergeCell ref="D155:F155"/>
+    <mergeCell ref="D156:F156"/>
+    <mergeCell ref="D157:F157"/>
+    <mergeCell ref="D158:F158"/>
+    <mergeCell ref="D159:F159"/>
+    <mergeCell ref="D154:F154"/>
+    <mergeCell ref="D153:F153"/>
+    <mergeCell ref="D149:F149"/>
+    <mergeCell ref="D150:F150"/>
+    <mergeCell ref="D151:F151"/>
+    <mergeCell ref="D152:F152"/>
+    <mergeCell ref="D115:F115"/>
+    <mergeCell ref="D114:F114"/>
+    <mergeCell ref="D113:F113"/>
+    <mergeCell ref="D142:F142"/>
+    <mergeCell ref="D144:F144"/>
+    <mergeCell ref="D145:F145"/>
+    <mergeCell ref="D146:F146"/>
+    <mergeCell ref="D147:F147"/>
+    <mergeCell ref="D148:F148"/>
+    <mergeCell ref="B55:B57"/>
+    <mergeCell ref="D69:F69"/>
+    <mergeCell ref="D70:F70"/>
+    <mergeCell ref="D71:F71"/>
+    <mergeCell ref="D72:F72"/>
+    <mergeCell ref="D62:F62"/>
+    <mergeCell ref="D56:F56"/>
+    <mergeCell ref="D57:F57"/>
+    <mergeCell ref="D58:F58"/>
+    <mergeCell ref="D59:F59"/>
+    <mergeCell ref="D66:F66"/>
+    <mergeCell ref="D67:F67"/>
+    <mergeCell ref="D60:F60"/>
+    <mergeCell ref="D61:F61"/>
+    <mergeCell ref="D63:F63"/>
+    <mergeCell ref="D64:F64"/>
+    <mergeCell ref="D65:F65"/>
+    <mergeCell ref="D68:F68"/>
+    <mergeCell ref="D55:F55"/>
+    <mergeCell ref="B62:B70"/>
+    <mergeCell ref="B58:B61"/>
+    <mergeCell ref="B71:B90"/>
+    <mergeCell ref="D84:F84"/>
+    <mergeCell ref="D86:F86"/>
+    <mergeCell ref="B28:B35"/>
+    <mergeCell ref="B36:B54"/>
+    <mergeCell ref="D49:F49"/>
+    <mergeCell ref="D50:F50"/>
+    <mergeCell ref="D51:F51"/>
+    <mergeCell ref="D52:F52"/>
+    <mergeCell ref="D53:F53"/>
+    <mergeCell ref="D37:F37"/>
+    <mergeCell ref="D38:F38"/>
+    <mergeCell ref="D39:F39"/>
+    <mergeCell ref="D40:F40"/>
+    <mergeCell ref="D41:F41"/>
+    <mergeCell ref="D42:F42"/>
+    <mergeCell ref="D43:F43"/>
+    <mergeCell ref="D44:F44"/>
+    <mergeCell ref="D45:F45"/>
+    <mergeCell ref="D46:F46"/>
+    <mergeCell ref="D47:F47"/>
+    <mergeCell ref="D48:F48"/>
+    <mergeCell ref="D54:F54"/>
+    <mergeCell ref="D36:F36"/>
+    <mergeCell ref="D34:F34"/>
+    <mergeCell ref="D29:F29"/>
+    <mergeCell ref="D30:F30"/>
+    <mergeCell ref="B4:E4"/>
+    <mergeCell ref="B5:K5"/>
+    <mergeCell ref="D19:F20"/>
+    <mergeCell ref="G19:G20"/>
+    <mergeCell ref="B19:B20"/>
+    <mergeCell ref="C19:C20"/>
+    <mergeCell ref="K19:K20"/>
+    <mergeCell ref="D7:E7"/>
+    <mergeCell ref="B22:B27"/>
+    <mergeCell ref="D25:F25"/>
+    <mergeCell ref="D27:F27"/>
+    <mergeCell ref="D24:F24"/>
+    <mergeCell ref="D26:F26"/>
+    <mergeCell ref="D91:F91"/>
+    <mergeCell ref="D76:F76"/>
+    <mergeCell ref="I19:J19"/>
+    <mergeCell ref="H19:H20"/>
+    <mergeCell ref="D78:F78"/>
+    <mergeCell ref="D80:F80"/>
+    <mergeCell ref="D74:F74"/>
+    <mergeCell ref="D85:F85"/>
+    <mergeCell ref="D90:F90"/>
+    <mergeCell ref="D82:F82"/>
+    <mergeCell ref="D83:F83"/>
+    <mergeCell ref="D87:F87"/>
+    <mergeCell ref="D88:F88"/>
+    <mergeCell ref="D89:F89"/>
+    <mergeCell ref="D77:F77"/>
+    <mergeCell ref="D79:F79"/>
+    <mergeCell ref="D81:F81"/>
+    <mergeCell ref="D75:F75"/>
+    <mergeCell ref="D73:F73"/>
+    <mergeCell ref="D21:F21"/>
+    <mergeCell ref="D35:F35"/>
+    <mergeCell ref="D22:F22"/>
+    <mergeCell ref="D28:F28"/>
+    <mergeCell ref="D23:F23"/>
+    <mergeCell ref="D31:F31"/>
+    <mergeCell ref="D32:F32"/>
+    <mergeCell ref="D33:F33"/>
+    <mergeCell ref="D189:F189"/>
+    <mergeCell ref="B187:B189"/>
+    <mergeCell ref="D169:F169"/>
+    <mergeCell ref="D171:F171"/>
+    <mergeCell ref="D174:F174"/>
+    <mergeCell ref="D175:F175"/>
+    <mergeCell ref="D177:F177"/>
+    <mergeCell ref="D178:F178"/>
+    <mergeCell ref="B183:B186"/>
+    <mergeCell ref="D182:F182"/>
+    <mergeCell ref="B181:B182"/>
+    <mergeCell ref="D93:F93"/>
+    <mergeCell ref="D94:F94"/>
+    <mergeCell ref="D95:F95"/>
+    <mergeCell ref="D96:F96"/>
+    <mergeCell ref="D97:F97"/>
+    <mergeCell ref="D98:F98"/>
+    <mergeCell ref="D100:F100"/>
+    <mergeCell ref="D122:F122"/>
+    <mergeCell ref="D186:F186"/>
+    <mergeCell ref="D185:F185"/>
+    <mergeCell ref="D101:F101"/>
+    <mergeCell ref="D102:F102"/>
+    <mergeCell ref="B119:B123"/>
+    <mergeCell ref="B113:B118"/>
+    <mergeCell ref="B108:B112"/>
+    <mergeCell ref="B99:B107"/>
+    <mergeCell ref="D162:F162"/>
+    <mergeCell ref="D163:F163"/>
+    <mergeCell ref="D138:F138"/>
+    <mergeCell ref="D137:F137"/>
+    <mergeCell ref="D111:F111"/>
+    <mergeCell ref="D110:F110"/>
+    <mergeCell ref="D109:F109"/>
+    <mergeCell ref="D112:F112"/>
+    <mergeCell ref="D103:F103"/>
+    <mergeCell ref="D104:F104"/>
+    <mergeCell ref="D105:F105"/>
+    <mergeCell ref="D106:F106"/>
+    <mergeCell ref="D107:F107"/>
+    <mergeCell ref="D120:F120"/>
+    <mergeCell ref="D119:F119"/>
+    <mergeCell ref="D118:F118"/>
+    <mergeCell ref="D117:F117"/>
+    <mergeCell ref="D116:F116"/>
     <mergeCell ref="D188:F188"/>
     <mergeCell ref="B94:B98"/>
     <mergeCell ref="B91:B93"/>
@@ -11689,186 +11882,6 @@
     <mergeCell ref="D99:F99"/>
     <mergeCell ref="D123:F123"/>
     <mergeCell ref="D136:F136"/>
-    <mergeCell ref="D101:F101"/>
-    <mergeCell ref="D102:F102"/>
-    <mergeCell ref="B119:B123"/>
-    <mergeCell ref="B113:B118"/>
-    <mergeCell ref="B108:B112"/>
-    <mergeCell ref="B99:B107"/>
-    <mergeCell ref="D162:F162"/>
-    <mergeCell ref="D163:F163"/>
-    <mergeCell ref="D138:F138"/>
-    <mergeCell ref="D137:F137"/>
-    <mergeCell ref="D111:F111"/>
-    <mergeCell ref="D110:F110"/>
-    <mergeCell ref="D109:F109"/>
-    <mergeCell ref="D112:F112"/>
-    <mergeCell ref="D103:F103"/>
-    <mergeCell ref="D104:F104"/>
-    <mergeCell ref="D105:F105"/>
-    <mergeCell ref="D106:F106"/>
-    <mergeCell ref="D107:F107"/>
-    <mergeCell ref="D120:F120"/>
-    <mergeCell ref="D119:F119"/>
-    <mergeCell ref="D118:F118"/>
-    <mergeCell ref="D117:F117"/>
-    <mergeCell ref="D116:F116"/>
-    <mergeCell ref="D31:F31"/>
-    <mergeCell ref="D32:F32"/>
-    <mergeCell ref="D33:F33"/>
-    <mergeCell ref="D189:F189"/>
-    <mergeCell ref="B187:B189"/>
-    <mergeCell ref="D170:F170"/>
-    <mergeCell ref="D172:F172"/>
-    <mergeCell ref="D175:F175"/>
-    <mergeCell ref="D176:F176"/>
-    <mergeCell ref="D178:F178"/>
-    <mergeCell ref="D179:F179"/>
-    <mergeCell ref="B183:B186"/>
-    <mergeCell ref="D182:F182"/>
-    <mergeCell ref="B181:B182"/>
-    <mergeCell ref="D93:F93"/>
-    <mergeCell ref="D94:F94"/>
-    <mergeCell ref="D95:F95"/>
-    <mergeCell ref="D96:F96"/>
-    <mergeCell ref="D97:F97"/>
-    <mergeCell ref="D98:F98"/>
-    <mergeCell ref="D100:F100"/>
-    <mergeCell ref="D122:F122"/>
-    <mergeCell ref="D186:F186"/>
-    <mergeCell ref="D185:F185"/>
-    <mergeCell ref="D91:F91"/>
-    <mergeCell ref="D76:F76"/>
-    <mergeCell ref="I19:J19"/>
-    <mergeCell ref="H19:H20"/>
-    <mergeCell ref="D78:F78"/>
-    <mergeCell ref="D80:F80"/>
-    <mergeCell ref="D74:F74"/>
-    <mergeCell ref="D85:F85"/>
-    <mergeCell ref="D90:F90"/>
-    <mergeCell ref="D82:F82"/>
-    <mergeCell ref="D83:F83"/>
-    <mergeCell ref="D87:F87"/>
-    <mergeCell ref="D88:F88"/>
-    <mergeCell ref="D89:F89"/>
-    <mergeCell ref="D77:F77"/>
-    <mergeCell ref="D79:F79"/>
-    <mergeCell ref="D81:F81"/>
-    <mergeCell ref="D75:F75"/>
-    <mergeCell ref="D73:F73"/>
-    <mergeCell ref="D21:F21"/>
-    <mergeCell ref="D35:F35"/>
-    <mergeCell ref="D22:F22"/>
-    <mergeCell ref="D28:F28"/>
-    <mergeCell ref="D23:F23"/>
-    <mergeCell ref="B4:E4"/>
-    <mergeCell ref="B5:K5"/>
-    <mergeCell ref="D19:F20"/>
-    <mergeCell ref="G19:G20"/>
-    <mergeCell ref="B19:B20"/>
-    <mergeCell ref="C19:C20"/>
-    <mergeCell ref="K19:K20"/>
-    <mergeCell ref="D7:E7"/>
-    <mergeCell ref="B22:B27"/>
-    <mergeCell ref="D25:F25"/>
-    <mergeCell ref="D27:F27"/>
-    <mergeCell ref="D24:F24"/>
-    <mergeCell ref="D26:F26"/>
-    <mergeCell ref="B28:B35"/>
-    <mergeCell ref="B36:B54"/>
-    <mergeCell ref="D49:F49"/>
-    <mergeCell ref="D50:F50"/>
-    <mergeCell ref="D51:F51"/>
-    <mergeCell ref="D52:F52"/>
-    <mergeCell ref="D53:F53"/>
-    <mergeCell ref="D37:F37"/>
-    <mergeCell ref="D38:F38"/>
-    <mergeCell ref="D39:F39"/>
-    <mergeCell ref="D40:F40"/>
-    <mergeCell ref="D41:F41"/>
-    <mergeCell ref="D42:F42"/>
-    <mergeCell ref="D43:F43"/>
-    <mergeCell ref="D44:F44"/>
-    <mergeCell ref="D45:F45"/>
-    <mergeCell ref="D46:F46"/>
-    <mergeCell ref="D47:F47"/>
-    <mergeCell ref="D48:F48"/>
-    <mergeCell ref="D54:F54"/>
-    <mergeCell ref="D36:F36"/>
-    <mergeCell ref="D34:F34"/>
-    <mergeCell ref="D29:F29"/>
-    <mergeCell ref="D30:F30"/>
-    <mergeCell ref="B55:B57"/>
-    <mergeCell ref="D69:F69"/>
-    <mergeCell ref="D70:F70"/>
-    <mergeCell ref="D71:F71"/>
-    <mergeCell ref="D72:F72"/>
-    <mergeCell ref="D62:F62"/>
-    <mergeCell ref="D56:F56"/>
-    <mergeCell ref="D57:F57"/>
-    <mergeCell ref="D58:F58"/>
-    <mergeCell ref="D59:F59"/>
-    <mergeCell ref="D66:F66"/>
-    <mergeCell ref="D67:F67"/>
-    <mergeCell ref="D60:F60"/>
-    <mergeCell ref="D61:F61"/>
-    <mergeCell ref="D63:F63"/>
-    <mergeCell ref="D64:F64"/>
-    <mergeCell ref="D65:F65"/>
-    <mergeCell ref="D68:F68"/>
-    <mergeCell ref="D55:F55"/>
-    <mergeCell ref="B62:B70"/>
-    <mergeCell ref="B58:B61"/>
-    <mergeCell ref="B71:B90"/>
-    <mergeCell ref="D84:F84"/>
-    <mergeCell ref="D86:F86"/>
-    <mergeCell ref="D115:F115"/>
-    <mergeCell ref="D114:F114"/>
-    <mergeCell ref="D113:F113"/>
-    <mergeCell ref="D142:F142"/>
-    <mergeCell ref="D144:F144"/>
-    <mergeCell ref="D145:F145"/>
-    <mergeCell ref="D146:F146"/>
-    <mergeCell ref="D147:F147"/>
-    <mergeCell ref="D148:F148"/>
-    <mergeCell ref="D160:F160"/>
-    <mergeCell ref="D161:F161"/>
-    <mergeCell ref="D143:F143"/>
-    <mergeCell ref="D155:F155"/>
-    <mergeCell ref="D156:F156"/>
-    <mergeCell ref="D157:F157"/>
-    <mergeCell ref="D158:F158"/>
-    <mergeCell ref="D159:F159"/>
-    <mergeCell ref="D154:F154"/>
-    <mergeCell ref="D153:F153"/>
-    <mergeCell ref="D149:F149"/>
-    <mergeCell ref="D150:F150"/>
-    <mergeCell ref="D151:F151"/>
-    <mergeCell ref="D152:F152"/>
-    <mergeCell ref="B137:B139"/>
-    <mergeCell ref="B162:B163"/>
-    <mergeCell ref="D164:F164"/>
-    <mergeCell ref="D187:F187"/>
-    <mergeCell ref="D184:F184"/>
-    <mergeCell ref="D183:F183"/>
-    <mergeCell ref="D165:F165"/>
-    <mergeCell ref="D166:F166"/>
-    <mergeCell ref="D167:F167"/>
-    <mergeCell ref="D180:F180"/>
-    <mergeCell ref="D181:F181"/>
-    <mergeCell ref="D168:F168"/>
-    <mergeCell ref="D169:F169"/>
-    <mergeCell ref="D177:F177"/>
-    <mergeCell ref="D171:F171"/>
-    <mergeCell ref="D173:F173"/>
-    <mergeCell ref="D174:F174"/>
-    <mergeCell ref="B169:B180"/>
-    <mergeCell ref="B165:B168"/>
-    <mergeCell ref="B140:B143"/>
-    <mergeCell ref="B144:B161"/>
-    <mergeCell ref="D139:F139"/>
-    <mergeCell ref="D140:F140"/>
-    <mergeCell ref="D141:F141"/>
   </mergeCells>
   <phoneticPr fontId="3"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -11881,7 +11894,7 @@
           <x14:formula1>
             <xm:f>master!#REF!</xm:f>
           </x14:formula1>
-          <xm:sqref>H21:H189</xm:sqref>
+          <xm:sqref>H21:H163 H164:H189</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -12358,7 +12371,7 @@
     </row>
     <row r="85" spans="2:3">
       <c r="C85" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
     </row>
     <row r="86" spans="2:3">
@@ -12371,7 +12384,7 @@
     </row>
     <row r="87" spans="2:3">
       <c r="C87" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
     </row>
     <row r="88" spans="2:3">
@@ -12456,20 +12469,20 @@
     </row>
     <row r="103" spans="2:3">
       <c r="B103" t="s">
-        <v>441</v>
+        <v>435</v>
       </c>
       <c r="C103" t="s">
-        <v>336</v>
+        <v>440</v>
       </c>
     </row>
     <row r="104" spans="2:3">
       <c r="C104" s="82" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
     </row>
     <row r="105" spans="2:3">
       <c r="C105" s="82" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
     </row>
     <row r="106" spans="2:3">
@@ -12477,27 +12490,27 @@
         <v>359</v>
       </c>
       <c r="C106" s="83" t="s">
-        <v>368</v>
+        <v>443</v>
       </c>
     </row>
     <row r="107" spans="2:3">
       <c r="C107" s="79" t="s">
-        <v>345</v>
+        <v>444</v>
       </c>
     </row>
     <row r="108" spans="2:3">
       <c r="C108" s="79" t="s">
-        <v>347</v>
+        <v>445</v>
       </c>
     </row>
     <row r="109" spans="2:3">
       <c r="C109" s="79" t="s">
-        <v>437</v>
+        <v>446</v>
       </c>
     </row>
     <row r="110" spans="2:3">
       <c r="C110" s="79" t="s">
-        <v>349</v>
+        <v>447</v>
       </c>
     </row>
     <row r="111" spans="2:3">
@@ -12505,22 +12518,22 @@
         <v>353</v>
       </c>
       <c r="C111" s="79" t="s">
-        <v>368</v>
+        <v>448</v>
       </c>
     </row>
     <row r="112" spans="2:3">
       <c r="C112" s="79" t="s">
-        <v>438</v>
+        <v>449</v>
       </c>
     </row>
     <row r="113" spans="2:3">
       <c r="C113" s="79" t="s">
-        <v>439</v>
+        <v>450</v>
       </c>
     </row>
     <row r="114" spans="2:3">
       <c r="C114" s="79" t="s">
-        <v>440</v>
+        <v>451</v>
       </c>
     </row>
     <row r="115" spans="2:3">
@@ -12791,20 +12804,20 @@
     </row>
     <row r="164" spans="2:3">
       <c r="B164" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="C164" s="79" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
     </row>
     <row r="165" spans="2:3">
       <c r="C165" s="79" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
     </row>
     <row r="166" spans="2:3">
       <c r="C166" s="79" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
     </row>
     <row r="167" spans="2:3">
